--- a/reports/latest/blotter_report.xlsx
+++ b/reports/latest/blotter_report.xlsx
@@ -944,7 +944,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-29 07:20:10.307919+00:00</t>
+          <t>2026-07-29 07:23:26.464232+00:00</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-29 07:20:10.307919+00:00</t>
+          <t>2026-06-29 07:23:26.464232+00:00</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FAILED fetched=0 truncated=False Socrata fetch failed for fdj4-gpfu: HTTP 400 for https://data.austintexas.gov/resource/fdj4-gpfu.json?%24where=latitude+between+30.39270168394081+and+30.410688116059188+AND+longitude+between+-97.73691453289148+and+-97.71606066710852+AND+occ_date+%3E+%272026-06-29T07%3A20%3A10%27&amp;%24limit=5000&amp;%24order=occ_date+DESC :: {"message":"Query coordinator error: query.soql.no-such-column; No such column: latitude; position: Map(row -&gt; 1, column -&gt; 325, line -&gt; \"SELECT `incident_report_number`, `crime_type`, `ucr_code`, `family_violence`, `occ_date_time`, `occ_date`, `occ_time`, `rep_date_time`, `rep_date`, `rep_time`, `</t>
+          <t>FAILED fetched=0 truncated=False Socrata fetch failed for fdj4-gpfu: HTTP 400 for https://data.austintexas.gov/resource/fdj4-gpfu.json?%24where=latitude+between+30.39270168394081+and+30.410688116059188+AND+longitude+between+-97.73691453289148+and+-97.71606066710852+AND+occ_date+%3E+%272026-06-29T07%3A23%3A26%27&amp;%24limit=5000&amp;%24order=occ_date+DESC :: {"message":"Query coordinator error: query.soql.no-such-column; No such column: latitude; position: Map(row -&gt; 1, column -&gt; 325, line -&gt; \"SELECT `incident_report_number`, `crime_type`, `ucr_code`, `family_violence`, `occ_date_time`, `occ_date`, `occ_time`, `rep_date_time`, `rep_date`, `rep_time`, `</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FAILED fetched=0 truncated=False Socrata fetch failed for tazs-3rd5: HTTP 400 for https://data.seattle.gov/resource/tazs-3rd5.json?%24where=latitude+between+47.69905138394081+and+47.71703781605919+AND+longitude+between+-122.33973349064095+and+-122.31300410935904+AND+offense_start_datetime+%3E+%272026-06-29T07%3A20%3A10%27&amp;%24limit=5000&amp;%24order=offense_start_datetime+DESC :: {"message":"Query coordinator error: query.soql.no-such-column; No such column: offense_start_datetime; position: Map(row -&gt; 1, column -&gt; 513, line -&gt; \"SELECT `report_number`, `report_date_time`, `offense_id`, `offense_date`, `nibrs_group_a_b`, `nibrs_crime_against_category`, `offense_sub_category`</t>
+          <t>FAILED fetched=0 truncated=False Socrata fetch failed for tazs-3rd5: HTTP 400 for https://data.seattle.gov/resource/tazs-3rd5.json?%24where=latitude+between+47.69905138394081+and+47.71703781605919+AND+longitude+between+-122.33973349064095+and+-122.31300410935904+AND+offense_start_datetime+%3E+%272026-06-29T07%3A23%3A26%27&amp;%24limit=5000&amp;%24order=offense_start_datetime+DESC :: {"message":"Query coordinator error: query.soql.no-such-column; No such column: offense_start_datetime; position: Map(row -&gt; 1, column -&gt; 513, line -&gt; \"SELECT `report_number`, `report_date_time`, `offense_id`, `offense_date`, `nibrs_group_a_b`, `nibrs_crime_against_category`, `offense_sub_category`</t>
         </is>
       </c>
     </row>

--- a/reports/latest/blotter_report.xlsx
+++ b/reports/latest/blotter_report.xlsx
@@ -944,7 +944,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-29 07:23:26.464232+00:00</t>
+          <t>2026-07-29 07:26:39.565963+00:00</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-29 07:23:26.464232+00:00</t>
+          <t>2026-06-29 07:26:39.565963+00:00</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FAILED fetched=0 truncated=False Socrata fetch failed for fdj4-gpfu: HTTP 400 for https://data.austintexas.gov/resource/fdj4-gpfu.json?%24where=latitude+between+30.39270168394081+and+30.410688116059188+AND+longitude+between+-97.73691453289148+and+-97.71606066710852+AND+occ_date+%3E+%272026-06-29T07%3A23%3A26%27&amp;%24limit=5000&amp;%24order=occ_date+DESC :: {"message":"Query coordinator error: query.soql.no-such-column; No such column: latitude; position: Map(row -&gt; 1, column -&gt; 325, line -&gt; \"SELECT `incident_report_number`, `crime_type`, `ucr_code`, `family_violence`, `occ_date_time`, `occ_date`, `occ_time`, `rep_date_time`, `rep_date`, `rep_time`, `</t>
+          <t>FAILED fetched=0 truncated=False Socrata fetch failed for fdj4-gpfu: HTTP 400 for https://data.austintexas.gov/resource/fdj4-gpfu.json?%24where=latitude+between+30.39270168394081+and+30.410688116059188+AND+longitude+between+-97.73691453289148+and+-97.71606066710852+AND+occ_date+%3E+%272026-06-29T07%3A26%3A39%27&amp;%24limit=5000&amp;%24order=occ_date+DESC :: {"message":"Query coordinator error: query.soql.no-such-column; No such column: latitude; position: Map(row -&gt; 1, column -&gt; 325, line -&gt; \"SELECT `incident_report_number`, `crime_type`, `ucr_code`, `family_violence`, `occ_date_time`, `occ_date`, `occ_time`, `rep_date_time`, `rep_date`, `rep_time`, `</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FAILED fetched=0 truncated=False Socrata fetch failed for 2u6v-ujjs: Non-JSON response from https://hub.arcgis.com/legacy :: &lt;!DOCTYPE html&gt; &lt;!--[if lt IE 9]&gt; &lt;html class="ie lt-ie9 ie8"&gt; &lt;![endif]--&gt; &lt;!--[if IE 9]&gt; &lt;html class="ie ie9"&gt; &lt;![endif]--&gt; &lt;!--[if !IE]&gt;&lt;!--&gt; &lt;html&gt; &lt;!--&lt;![endif]--&gt; &lt;head&gt; &lt;meta charset="UT</t>
+          <t>FAILED fetched=0 truncated=False ArcGIS error for Metro Nashville PD Incidents: {'code': 400, 'message': 'Cannot perform query. Invalid query parameters.', 'details': ['Unable to perform query. Please check your parameters.']}</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FAILED fetched=0 truncated=False Socrata fetch failed for tazs-3rd5: HTTP 400 for https://data.seattle.gov/resource/tazs-3rd5.json?%24where=latitude+between+47.69905138394081+and+47.71703781605919+AND+longitude+between+-122.33973349064095+and+-122.31300410935904+AND+offense_start_datetime+%3E+%272026-06-29T07%3A23%3A26%27&amp;%24limit=5000&amp;%24order=offense_start_datetime+DESC :: {"message":"Query coordinator error: query.soql.no-such-column; No such column: offense_start_datetime; position: Map(row -&gt; 1, column -&gt; 513, line -&gt; \"SELECT `report_number`, `report_date_time`, `offense_id`, `offense_date`, `nibrs_group_a_b`, `nibrs_crime_against_category`, `offense_sub_category`</t>
+          <t>FAILED fetched=0 truncated=False Socrata fetch failed for tazs-3rd5: HTTP 400 for https://data.seattle.gov/resource/tazs-3rd5.json?%24where=latitude%3A%3Anumber+between+47.69905138394081+and+47.71703781605919+AND+longitude%3A%3Anumber+between+-122.33973349064095+and+-122.31300410935904+AND+offense_date+%3E+%272026-06-29T07%3A26%3A39%27&amp;%24limit=5000&amp;%24order=offense_date+DESC :: {"message":"Query coordinator error: 400; ERROR: invalid input syntax for type numeric: \"REDACTED\"","errorCode":"400","data":{"source":"soql-server"}}</t>
         </is>
       </c>
     </row>

--- a/reports/latest/blotter_report.xlsx
+++ b/reports/latest/blotter_report.xlsx
@@ -14,8 +14,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$K$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Highlights'!$A$1:$L$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$L$178</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Highlights'!$A$1:$M$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$178</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -766,7 +766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -781,6 +781,7 @@
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -844,6 +845,11 @@
           <t>distance_m</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>synopsis</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -898,6 +904,11 @@
       <c r="L2" t="n">
         <v>145.2</v>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Simple assault on Jul 22, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-215149 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -952,6 +963,11 @@
       <c r="L3" t="n">
         <v>145.2</v>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Robbery on Jul 21, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-213187 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1006,6 +1022,11 @@
       <c r="L4" t="n">
         <v>338.4</v>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Simple assault on Jul 07, 2026, 338 m from Northgate Station (5XX BLOCK OF NE NORTHGATE WAY). Case #2026-196771 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1060,6 +1081,11 @@
       <c r="L5" t="n">
         <v>497.7</v>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Robbery-bank on Jul 01, 2026, 498 m from Cherry Creek Shopping Center (3410 E 1ST AVE). Victims: 1. Case #DP2026357948 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1114,6 +1140,11 @@
       <c r="L6" t="n">
         <v>539</v>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Weapon law violations on Jul 17, 2026, 539 m from Northgate Station (8XX BLOCK OF NE NORTHGATE WAY). Case #2026-208823 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1168,6 +1199,11 @@
       <c r="L7" t="n">
         <v>566.4</v>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Assault-simple on Jul 22, 2026, 566 m from Cherry Creek Shopping Center (300 BLOCK N ST PAUL ST). Victims: 1. Case #DP2026403380 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1222,6 +1258,11 @@
       <c r="L8" t="n">
         <v>596.2</v>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Robbery on Jul 11, 2026, 596 m from Northgate Station (5TH AVE NE / NE 103RD ST). Case #2026-202517 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1276,6 +1317,11 @@
       <c r="L9" t="n">
         <v>639.8</v>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Weapon law violations on Jul 11, 2026, 640 m from Northgate Station (ROOSEVELT WAY NE / NE NORTHGATE WAY). Case #2026-202517 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1330,6 +1376,11 @@
       <c r="L10" t="n">
         <v>798.3</v>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Aggravated assault on Jul 02, 2026, 798 m from Northgate Station (117XX BLOCK OF 5TH AVE NE). Case #2026-191308 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1380,6 +1431,11 @@
       <c r="L11" t="n">
         <v>808.3</v>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Assault- fear of bodily injury on Jul 11, 2026, 808 m from Opry Mills (OPRYLAND). Premises: HOTEL, MOTEL, ETC.. Status: OPEN. Victims: 1. Case #20260423135 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1434,6 +1490,11 @@
       <c r="L12" t="n">
         <v>936.3</v>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Assault, aggravated - deadly weapon - int/kn on Jul 19, 2026, 936 m from Opry Mills (2902 2902). Weapon: HANDGUN. Premises: RESIDENCE, HOME. Status: CLEARED BY ARREST. Victims: 1. Flags: domestic related. Case #20260440008 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1488,6 +1549,11 @@
       <c r="L13" t="n">
         <v>936.3</v>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Assault- offensive or provocative contact on Jul 19, 2026, 936 m from Opry Mills (2902 2902). Weapon: PERSONAL (HANDS). Premises: RESIDENCE, HOME. Status: CLEARED BY ARREST. Victims: 2. Case #20260440008 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1542,6 +1608,11 @@
       <c r="L14" t="n">
         <v>936.3</v>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Weapon offense, criminal attempt on Jul 19, 2026, 936 m from Opry Mills (2902 2902). Weapon: HANDGUN. Premises: RESIDENCE, HOME. Status: CLEARED BY ARREST. Victims: 3. Case #20260440008 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1596,6 +1667,11 @@
       <c r="L15" t="n">
         <v>25.7</v>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 21, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266009882 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1650,6 +1726,11 @@
       <c r="L16" t="n">
         <v>25.7</v>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Theft-from-bldg on Jul 15, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266009631 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1704,6 +1785,11 @@
       <c r="L17" t="n">
         <v>25.7</v>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 09, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266009395 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1758,6 +1844,11 @@
       <c r="L18" t="n">
         <v>25.7</v>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 09, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP2026380800 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1812,6 +1903,11 @@
       <c r="L19" t="n">
         <v>25.7</v>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 08, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP2026376323 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1866,6 +1962,11 @@
       <c r="L20" t="n">
         <v>25.7</v>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 05, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266009170 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1920,6 +2021,11 @@
       <c r="L21" t="n">
         <v>25.7</v>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 02, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266009209 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1974,6 +2080,11 @@
       <c r="L22" t="n">
         <v>25.7</v>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jun 29, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266008929 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2028,6 +2139,11 @@
       <c r="L23" t="n">
         <v>100.4</v>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Theft-other on Jul 20, 2026, 100 m from Cherry Creek Shopping Center (3030 E 1ST AVE). Victims: 1. Case #DP2026399148 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2078,6 +2194,11 @@
       <c r="L24" t="n">
         <v>111.8</v>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>594(b)(1) - pc - f - vandalism ($400 or more) - felony - 290 on Jul 04, 2026, 112 m from Beverly Center (8500 W Beverly Blvd). Premises: Parking Lot / Garage / Drop Lot. Status: Open. Victims: 1. Case #C269028320 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2132,6 +2253,11 @@
       <c r="L25" t="n">
         <v>113.7</v>
       </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 24, 2026, 114 m from Opry Mills (211 211). Premises: DEPARTMENT, DISCOUNT STORE. Status: CLEARED BY ARREST. Victims: 1. Case #20260449995 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2186,9 +2312,14 @@
       <c r="L26" t="n">
         <v>113.7</v>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 18, 2026, 114 m from Opry Mills (211 211). Premises: DEPARTMENT, DISCOUNT STORE. Status: CLEARED BY ARREST. Victims: 1. Case #20260438245 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L26"/>
+  <autoFilter ref="A1:M26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2199,7 +2330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L178"/>
+  <dimension ref="A1:M178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2214,6 +2345,7 @@
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2277,6 +2409,11 @@
           <t>distance_m</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>synopsis</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2327,6 +2464,11 @@
       <c r="L2" t="n">
         <v>394.4</v>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>459.5(a) - pc - m - petty theft - shoplifting - 23c on Jul 11, 2026, 394 m from Beverly Center (8400 Beverly Blvd). Premises: The Beverly Connection. Status: Open. Victims: 1. Case #C269029303 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2377,6 +2519,11 @@
       <c r="L3" t="n">
         <v>464.1</v>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>459.5(a) - pc - m - petty theft - shoplifting - 23c on Jul 10, 2026, 464 m from Beverly Center (8400 W 3rd St). Premises: Department / Discount Store. Status: Open. Victims: 1. Case #C269029051 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2427,6 +2574,11 @@
       <c r="L4" t="n">
         <v>229.4</v>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>459.5(a) - pc - m - petty theft - shoplifting - 23c on Jul 10, 2026, 229 m from Beverly Center (100 N La Cienega Blvd). Premises: Department / Discount Store. Status: Open. Victims: 1. Case #26134379 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2477,6 +2629,11 @@
       <c r="L5" t="n">
         <v>394.4</v>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>459.5(a) - pc - m - petty theft - shoplifting - 23c on Jul 08, 2026, 394 m from Beverly Center (8400 Beverly Blvd). Premises: Other Business. Status: Open. Victims: 1. Case #26133458 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2527,6 +2684,11 @@
       <c r="L6" t="n">
         <v>394.4</v>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>459.5(a) - pc - m - petty theft - shoplifting - 23c on Jul 08, 2026, 394 m from Beverly Center (8400 Beverly Blvd). Premises: Other Business. Status: Cleared by Arrest - CA Filed. Victims: 1. Case #26132960 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2577,6 +2739,11 @@
       <c r="L7" t="n">
         <v>394.4</v>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>459.5(a) - pc - m - petty theft - shoplifting - 23c on Jul 08, 2026, 394 m from Beverly Center (8400 Beverly Blvd). Premises: Department / Discount Store. Status: Open. Victims: 1. Case #C269028868 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2627,6 +2794,11 @@
       <c r="L8" t="n">
         <v>229.4</v>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>459.5(a) - pc - m - petty theft - shoplifting - 23c on Jul 08, 2026, 229 m from Beverly Center (100 N La Cienega Blvd). Premises: Other Business. Status: Open. Victims: 1. Case #26132830 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2677,6 +2849,11 @@
       <c r="L9" t="n">
         <v>979.6</v>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>459 - pc - f - burglary - non-residential - 220 on Jul 07, 2026, 980 m from Beverly Center (8400 Melrose Pl). Premises: Clothing Store. Status: Investigation Continued. Victims: 1. Case #26131883 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2727,6 +2904,11 @@
       <c r="L10" t="n">
         <v>111.8</v>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>594(b)(1) - pc - f - vandalism ($400 or more) - felony - 290 on Jul 04, 2026, 112 m from Beverly Center (8500 W Beverly Blvd). Premises: Parking Lot / Garage / Drop Lot. Status: Open. Victims: 1. Case #C269028320 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2777,6 +2959,11 @@
       <c r="L11" t="n">
         <v>394.4</v>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>459.5(a) - pc - m - petty theft - shoplifting - 23c on Jul 04, 2026, 394 m from Beverly Center (8400 Beverly Blvd). Premises: Department / Discount Store. Status: Open. Victims: 1. Case #26130052 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2827,6 +3014,11 @@
       <c r="L12" t="n">
         <v>464.1</v>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>459.5(a) - pc - m - petty theft - shoplifting - 23c on Jul 02, 2026, 464 m from Beverly Center (8400 W 3rd St). Premises: Department / Discount Store. Status: Investigation Continued. Victims: 1. Case #C269027969 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2877,6 +3069,11 @@
       <c r="L13" t="n">
         <v>394.4</v>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>459.5(a) - pc - m - petty theft - shoplifting - 23c on Jul 01, 2026, 394 m from Beverly Center (8400 Beverly Blvd). Premises: Clothing Store. Status: Open. Victims: 1. Case #26128108 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2931,6 +3128,11 @@
       <c r="L14" t="n">
         <v>113.7</v>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 18, 2026, 114 m from Opry Mills (211 211). Premises: DEPARTMENT, DISCOUNT STORE. Status: CLEARED BY ARREST. Victims: 1. Case #20260438245 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2985,6 +3187,11 @@
       <c r="L15" t="n">
         <v>113.7</v>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 24, 2026, 114 m from Opry Mills (211 211). Premises: DEPARTMENT, DISCOUNT STORE. Status: CLEARED BY ARREST. Victims: 1. Case #20260449995 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3035,6 +3242,11 @@
       <c r="L16" t="n">
         <v>125.9</v>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Lost property on Jul 05, 2026, 126 m from Opry Mills (433 433). Premises: Shopping Mall. Status: UNFOUNDED. Victims: 1. Case #20260411784 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3089,6 +3301,11 @@
       <c r="L17" t="n">
         <v>125.9</v>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Lost property on Jul 25, 2026, 126 m from Opry Mills (433 433). Premises: Shopping Mall. Status: UNFOUNDED. Victims: 1. Case #20260451873 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3143,6 +3360,11 @@
       <c r="L18" t="n">
         <v>125.9</v>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 10, 2026, 126 m from Opry Mills (433 433). Premises: DEPARTMENT, DISCOUNT STORE. Status: CLEARED BY ARREST. Victims: 1. Case #20260421984 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3197,6 +3419,11 @@
       <c r="L19" t="n">
         <v>125.9</v>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Police inquiry on Jul 07, 2026, 126 m from Opry Mills (433 433). Premises: Shopping Mall. Status: UNFOUNDED. Victims: 1. Flags: domestic related. Case #20260415824 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3251,6 +3478,11 @@
       <c r="L20" t="n">
         <v>125.9</v>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Theft of merchandise- $1,000 or less on Jul 09, 2026, 126 m from Opry Mills (433 433). Weapon: PERSONAL (HANDS). Premises: Shopping Mall. Status: CLEARED BY ARREST. Victims: 1. Case #20260419741 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3305,6 +3537,11 @@
       <c r="L21" t="n">
         <v>125.9</v>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Theft of merchandise- $1,000 or less on Jul 09, 2026, 126 m from Opry Mills (433 433). Weapon: PERSONAL (HANDS). Premises: Shopping Mall. Status: CLEARED BY ARREST. Victims: 2. Case #20260419741 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3359,6 +3596,11 @@
       <c r="L22" t="n">
         <v>125.9</v>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Theft of merchandise- $1,000 or less on Jul 09, 2026, 126 m from Opry Mills (433 433). Weapon: PERSONAL (HANDS). Premises: Shopping Mall. Status: CLEARED BY ARREST. Victims: 3. Case #20260419741 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3413,6 +3655,11 @@
       <c r="L23" t="n">
         <v>125.9</v>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Theft of merchandise- $1,000 or less on Jul 09, 2026, 126 m from Opry Mills (433 433). Weapon: PERSONAL (HANDS). Premises: Shopping Mall. Status: CLEARED BY ARREST. Victims: 4. Case #20260419741 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3467,6 +3714,11 @@
       <c r="L24" t="n">
         <v>125.9</v>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Possession of a controlled substance on Jul 25, 2026, 126 m from Opry Mills (433 433). Premises: SPECIALTY STORE. Status: CLEARED BY ARREST. Victims: 1. Case #20260451698 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3521,6 +3773,11 @@
       <c r="L25" t="n">
         <v>227.6</v>
       </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Theft of merchandise- $1,000 or less on Jul 19, 2026, 228 m from Opry Mills (357 357). Premises: SPECIALTY STORE. Status: CLEARED BY ARREST. Victims: 1. Case #20260439763 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3575,6 +3832,11 @@
       <c r="L26" t="n">
         <v>271</v>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Lost property on Jul 12, 2026, 271 m from Opry Mills (550 550). Premises: Shopping Mall. Status: UNFOUNDED. Victims: 1. Case #20260424643 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3629,6 +3891,11 @@
       <c r="L27" t="n">
         <v>338.4</v>
       </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Theft of merchandise- $1,000 or less on Jul 19, 2026, 338 m from Opry Mills (428 428). Premises: SPECIALTY STORE. Status: Closed. Victims: 1. Case #20260439850 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3683,6 +3950,11 @@
       <c r="L28" t="n">
         <v>343.9</v>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Harrassment (nuisance) on Jul 03, 2026, 344 m from Opry Mills (353 353). Premises: RESIDENCE, HOME. Status: REFUSED TO COOPERATE. Victims: 1. Flags: domestic related. Case #20260407934 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3737,6 +4009,11 @@
       <c r="L29" t="n">
         <v>387.3</v>
       </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Theft of merchandise 5th - $1,000 or less on Jul 04, 2026, 387 m from Opry Mills (OPRY MILLS). Weapon: PERSONAL (HANDS). Premises: SPECIALTY STORE. Status: OPEN. Victims: 1. Case #20260411424 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3791,6 +4068,11 @@
       <c r="L30" t="n">
         <v>387.3</v>
       </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Vehicle theft on Jul 05, 2026, 387 m from Opry Mills (OPRY MILLS). Premises: PARKING LOT, GARAGE. Status: OPEN. Victims: 1. Case #20260411660 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3845,6 +4127,11 @@
       <c r="L31" t="n">
         <v>387.3</v>
       </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Larc - from bldg on Jul 13, 2026, 387 m from Opry Mills (OPRY MILLS DR). Premises: DEPARTMENT, DISCOUNT STORE. Status: OPEN. Victims: 1. Case #20260427548 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3899,6 +4186,11 @@
       <c r="L32" t="n">
         <v>387.3</v>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Larc - from bldg on Jul 05, 2026, 387 m from Opry Mills (OPRY MILLS DR). Weapon: PERSONAL (HANDS). Premises: SPECIALTY STORE. Status: OPEN. Victims: 1. Case #20260411259 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3953,6 +4245,11 @@
       <c r="L33" t="n">
         <v>387.3</v>
       </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 02, 2026, 387 m from Opry Mills (OPRY MILLS DR). Weapon: PERSONAL (HANDS). Premises: Shopping Mall. Status: OPEN. Victims: 1. Case #20260405842 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4007,6 +4304,11 @@
       <c r="L34" t="n">
         <v>387.3</v>
       </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Fraud -  illeg use of credit cards on Jul 06, 2026, 387 m from Opry Mills (OPRY MILLS). Weapon: PERSONAL (HANDS). Premises: SPECIALTY STORE. Status: OPEN. Victims: 1. Case #20260423957 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4061,6 +4363,11 @@
       <c r="L35" t="n">
         <v>387.3</v>
       </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Damage prop - private on Jul 21, 2026, 387 m from Opry Mills (OPRY MILLS DR). Weapon: Unarmed. Premises: PARKING LOT, GARAGE. Status: OPEN. Victims: 1. Case #20260443304 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4115,6 +4422,11 @@
       <c r="L36" t="n">
         <v>387.3</v>
       </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 13, 2026, 387 m from Opry Mills (OPRY MILLS DR). Premises: SPECIALTY STORE. Status: OPEN. Victims: 1. Case #20260427787 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4169,6 +4481,11 @@
       <c r="L37" t="n">
         <v>387.3</v>
       </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Larc - from bldg on Jul 03, 2026, 387 m from Opry Mills (OPRY MILLS DR). Premises: SPECIALTY STORE. Status: OPEN. Victims: 1. Case #20260407874 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4223,6 +4540,11 @@
       <c r="L38" t="n">
         <v>387.3</v>
       </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Credit card, fraudulent use - $1,000 or less on Jul 09, 2026, 387 m from Opry Mills (OPRY MILLS DR). Premises: Shopping Mall. Status: OPEN. Victims: 1. Case #20260419743 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4277,6 +4599,11 @@
       <c r="L39" t="n">
         <v>441.5</v>
       </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 22, 2026, 442 m from Opry Mills (211 211). Premises: SPECIALTY STORE. Status: CLEARED BY ARREST. Victims: 1. Case #20260445712 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4331,6 +4658,11 @@
       <c r="L40" t="n">
         <v>474.9</v>
       </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Theft of merchandise 5th - $1,000 or less on Jul 16, 2026, 475 m from Opry Mills (323 323). Weapon: PERSONAL (HANDS). Premises: SPECIALTY STORE. Status: CLEARED BY ARREST. Victims: 1. Case #20260434111 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4385,6 +4717,11 @@
       <c r="L41" t="n">
         <v>525.5</v>
       </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Simple asslt on Jul 11, 2026, 526 m from Opry Mills (3725 3725). Weapon: PERSONAL (HANDS). Premises: RESIDENCE, HOME. Status: CLEARED BY ARREST. Victims: 1. Flags: domestic related. Case #20260423835 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4439,6 +4776,11 @@
       <c r="L42" t="n">
         <v>688.9</v>
       </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Police inquiry on Jul 11, 2026, 689 m from Opry Mills (211 211). Premises: PARKING LOT, GARAGE. Status: UNFOUNDED. Victims: 1. Case #20260424550 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4493,6 +4835,11 @@
       <c r="L43" t="n">
         <v>768.3</v>
       </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Fraud -  illeg use of credit cards on Jul 21, 2026, 768 m from Opry Mills (MORGANMEADE DR). Premises: RESIDENCE, HOME. Status: OPEN. Victims: 1. Case #20260443720 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4547,6 +4894,11 @@
       <c r="L44" t="n">
         <v>768.3</v>
       </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Larc - from bldg on Jul 25, 2026, 768 m from Opry Mills (OPRY MILLS). Premises: RESTAURANT. Status: OPEN. Victims: 1. Case #20260451780 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4601,6 +4953,11 @@
       <c r="L45" t="n">
         <v>808.3</v>
       </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 25, 2026, 808 m from Opry Mills (OPRY MILLS DR). Premises: SPECIALTY STORE. Status: OPEN. Victims: 1. Case #20260451462 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4655,6 +5012,11 @@
       <c r="L46" t="n">
         <v>808.3</v>
       </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Theft of property-&gt;$1,000 but &lt;$2,500 on Jul 10, 2026, 808 m from Opry Mills (OPRYLAND DR). Weapon: Unarmed. Premises: PARK. Status: OPEN. Victims: 1. Case #20260421200 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4709,6 +5071,11 @@
       <c r="L47" t="n">
         <v>808.3</v>
       </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 01, 2026, 808 m from Opry Mills (OPRY MILLS DR). Premises: SPECIALTY STORE. Status: OPEN. Victims: 1. Case #20260403493 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4759,6 +5126,11 @@
       <c r="L48" t="n">
         <v>808.3</v>
       </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Vehicle theft on Jul 08, 2026, 808 m from Opry Mills (OPRYLAND DR). Premises: HOTEL, MOTEL, ETC.. Status: OPEN. Victims: 1. Case #20260425948 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4813,6 +5185,11 @@
       <c r="L49" t="n">
         <v>808.3</v>
       </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Larc - from bldg on Jul 09, 2026, 808 m from Opry Mills (OPRYLAND DR). Premises: HOTEL, MOTEL, ETC.. Status: OPEN. Victims: 1. Case #20260418604 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4867,6 +5244,11 @@
       <c r="L50" t="n">
         <v>808.3</v>
       </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 06, 2026, 808 m from Opry Mills (OPRY MILLS DR). Premises: SPECIALTY STORE. Status: OPEN. Victims: 1. Case #20260413875 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4921,6 +5303,11 @@
       <c r="L51" t="n">
         <v>808.3</v>
       </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Burglary- motor vehicle on Jun 29, 2026, 808 m from Opry Mills (OPRY MILLS DR). Premises: PARKING LOT, GARAGE. Status: OPEN. Victims: 1. Case #20260399283 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4975,6 +5362,11 @@
       <c r="L52" t="n">
         <v>808.3</v>
       </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Theft of property- $10,000 or &gt;  but  &lt; $60,000 on Jul 02, 2026, 808 m from Opry Mills (OPRYLAND DR). Premises: PARKING LOT, GARAGE. Status: OPEN. Victims: 1. Case #20260413013 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5029,6 +5421,11 @@
       <c r="L53" t="n">
         <v>808.3</v>
       </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 27, 2026, 808 m from Opry Mills (OPRY MILLS DR). Premises: DEPARTMENT, DISCOUNT STORE. Status: OPEN. Victims: 1. Case #20260455357 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5079,6 +5476,11 @@
       <c r="L54" t="n">
         <v>808.3</v>
       </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Assault- fear of bodily injury on Jul 11, 2026, 808 m from Opry Mills (OPRYLAND). Premises: HOTEL, MOTEL, ETC.. Status: OPEN. Victims: 1. Case #20260423135 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5133,6 +5535,11 @@
       <c r="L55" t="n">
         <v>808.3</v>
       </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Larc - from bldg on Jul 06, 2026, 808 m from Opry Mills (OPRYLAND DR). Premises: Shopping Mall. Status: OPEN. Victims: 1. Case #20260419567 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5187,6 +5594,11 @@
       <c r="L56" t="n">
         <v>808.3</v>
       </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Criminal impersonation on Jun 29, 2026, 808 m from Opry Mills (OPRYLAND DR). Premises: COMMERCIAL, OFFICE BUILDING. Status: OPEN. Victims: 1. Case #20260434024 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5241,6 +5653,11 @@
       <c r="L57" t="n">
         <v>808.3</v>
       </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Fraud -  illeg use of credit cards on Jul 06, 2026, 808 m from Opry Mills (OPRY MILLS DR). Weapon: PERSONAL (HANDS). Premises: Shopping Mall. Status: OPEN. Victims: 1. Case #20260423950 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5295,6 +5712,11 @@
       <c r="L58" t="n">
         <v>808.3</v>
       </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Theft of merchandise- $1,000 or less on Jul 07, 2026, 808 m from Opry Mills (OPRY MILLS DR). Premises: SPECIALTY STORE. Status: OPEN. Victims: 1. Case #20260415793 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5349,6 +5771,11 @@
       <c r="L59" t="n">
         <v>936.3</v>
       </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Assault, aggravated - deadly weapon - int/kn on Jul 19, 2026, 936 m from Opry Mills (2902 2902). Weapon: HANDGUN. Premises: RESIDENCE, HOME. Status: CLEARED BY ARREST. Victims: 1. Flags: domestic related. Case #20260440008 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5403,6 +5830,11 @@
       <c r="L60" t="n">
         <v>936.3</v>
       </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Assault- offensive or provocative contact on Jul 19, 2026, 936 m from Opry Mills (2902 2902). Weapon: PERSONAL (HANDS). Premises: RESIDENCE, HOME. Status: CLEARED BY ARREST. Victims: 2. Case #20260440008 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5457,6 +5889,11 @@
       <c r="L61" t="n">
         <v>936.3</v>
       </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Weapon offense, criminal attempt on Jul 19, 2026, 936 m from Opry Mills (2902 2902). Weapon: HANDGUN. Premises: RESIDENCE, HOME. Status: CLEARED BY ARREST. Victims: 3. Case #20260440008 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5511,6 +5948,11 @@
       <c r="L62" t="n">
         <v>563</v>
       </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Burglary/breaking &amp; entering on Jul 24, 2026, 563 m from Northgate Station (113XX BLOCK OF CORLISS AVE N). Case #2026-216739 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5565,6 +6007,11 @@
       <c r="L63" t="n">
         <v>880.9</v>
       </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Drug/narcotic violations on Jul 23, 2026, 881 m from Northgate Station (100XX BLOCK OF COLLEGE WAY N). Case #2026-216408 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5619,6 +6066,11 @@
       <c r="L64" t="n">
         <v>145.2</v>
       </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Simple assault on Jul 22, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-215149 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5673,6 +6125,11 @@
       <c r="L65" t="n">
         <v>475.1</v>
       </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 22, 2026, 475 m from Northgate Station (21XX BLOCK OF N NORTHGATE WAY). Case #2026-215020 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5727,6 +6184,11 @@
       <c r="L66" t="n">
         <v>812.7</v>
       </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>All other larceny on Jul 21, 2026, 813 m from Northgate Station (115XX BLOCK OF MERIDIAN AVE N). Case #2026-913058 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5781,6 +6243,11 @@
       <c r="L67" t="n">
         <v>145.2</v>
       </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Robbery on Jul 21, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-213187 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5835,6 +6302,11 @@
       <c r="L68" t="n">
         <v>867.4</v>
       </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>All other larceny on Jul 20, 2026, 867 m from Northgate Station (97XX BLOCK OF 3RD AVE NE). Case #2026-913061 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5889,6 +6361,11 @@
       <c r="L69" t="n">
         <v>539</v>
       </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 20, 2026, 539 m from Northgate Station (8XX BLOCK OF NE NORTHGATE WAY). Case #2026-212215 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5943,6 +6420,11 @@
       <c r="L70" t="n">
         <v>744.2</v>
       </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Theft from motor vehicle on Jul 20, 2026, 744 m from Northgate Station (MERIDIAN AVE N / N 115TH ST). Case #2026-913040 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5997,6 +6479,11 @@
       <c r="L71" t="n">
         <v>475.1</v>
       </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Theft from building on Jul 20, 2026, 475 m from Northgate Station (21XX BLOCK OF N NORTHGATE WAY). Case #2026-211165 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6051,6 +6538,11 @@
       <c r="L72" t="n">
         <v>145.2</v>
       </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Motor vehicle theft on Jul 19, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-211277 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6105,6 +6597,11 @@
       <c r="L73" t="n">
         <v>648.8</v>
       </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>All other larceny on Jul 19, 2026, 649 m from Northgate Station (110XX BLOCK OF ROOSEVELT WAY NE). Case #2026-211080 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6159,6 +6656,11 @@
       <c r="L74" t="n">
         <v>993.9</v>
       </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Theft from motor vehicle on Jul 17, 2026, 994 m from Northgate Station (3XX BLOCK OF NE 97TH ST). Case #2026-912809 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6213,6 +6715,11 @@
       <c r="L75" t="n">
         <v>539.1</v>
       </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 17, 2026, 539 m from Northgate Station (8XX BLOCK OF NE NORTHGATE WAY). Case #2026-208823 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6267,6 +6774,11 @@
       <c r="L76" t="n">
         <v>539</v>
       </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Weapon law violations on Jul 17, 2026, 539 m from Northgate Station (8XX BLOCK OF NE NORTHGATE WAY). Case #2026-208823 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6321,6 +6833,11 @@
       <c r="L77" t="n">
         <v>539</v>
       </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Not reportable to nibrs on Jul 17, 2026, 539 m from Northgate Station (8XX BLOCK OF NE NORTHGATE WAY). Case #2026-208823 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6375,6 +6892,11 @@
       <c r="L78" t="n">
         <v>539</v>
       </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Drug/narcotic violations on Jul 17, 2026, 539 m from Northgate Station (8XX BLOCK OF NE NORTHGATE WAY). Case #2026-208823 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6429,6 +6951,11 @@
       <c r="L79" t="n">
         <v>539.1</v>
       </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Not reportable to nibrs on Jul 17, 2026, 539 m from Northgate Station (8XX BLOCK OF NE NORTHGATE WAY). Case #2026-208823 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6483,6 +7010,11 @@
       <c r="L80" t="n">
         <v>539</v>
       </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Stolen property offenses on Jul 17, 2026, 539 m from Northgate Station (8XX BLOCK OF NE NORTHGATE WAY). Case #2026-208823 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6537,6 +7069,11 @@
       <c r="L81" t="n">
         <v>539</v>
       </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 17, 2026, 539 m from Northgate Station (8XX BLOCK OF NE NORTHGATE WAY). Case #2026-208823 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6591,6 +7128,11 @@
       <c r="L82" t="n">
         <v>608.3</v>
       </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Driving under the influence on Jul 16, 2026, 608 m from Northgate Station (115XX BLOCK OF 5TH AVE NE). Case #2026-208431 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6645,6 +7187,11 @@
       <c r="L83" t="n">
         <v>608.3</v>
       </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Destruction/damage/vandalism of property on Jul 16, 2026, 608 m from Northgate Station (115XX BLOCK OF 5TH AVE NE). Case #2026-208431 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6699,6 +7246,11 @@
       <c r="L84" t="n">
         <v>539</v>
       </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 16, 2026, 539 m from Northgate Station (8XX BLOCK OF NE NORTHGATE WAY). Case #2026-207596 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6753,6 +7305,11 @@
       <c r="L85" t="n">
         <v>695.6</v>
       </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Destruction/damage/vandalism of property on Jul 16, 2026, 696 m from Northgate Station (112XX BLOCK OF ROOSEVELT WAY NE). Case #2026-207746 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6807,6 +7364,11 @@
       <c r="L86" t="n">
         <v>661.7</v>
       </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>All other larceny on Jul 16, 2026, 662 m from Northgate Station (102XX BLOCK OF 1ST AVE NE). Case #2026-912691 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6861,6 +7423,11 @@
       <c r="L87" t="n">
         <v>539.1</v>
       </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 15, 2026, 539 m from Northgate Station (8XX BLOCK OF NE NORTHGATE WAY). Case #2026-207228 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6915,6 +7482,11 @@
       <c r="L88" t="n">
         <v>627</v>
       </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Burglary/breaking &amp; entering on Jul 15, 2026, 627 m from Northgate Station (3XX BLOCK OF NE THORNTON PL). Case #2026-912675 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6969,6 +7541,11 @@
       <c r="L89" t="n">
         <v>694.1</v>
       </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Wire fraud on Jul 15, 2026, 694 m from Northgate Station (112XX BLOCK OF ROOSEVELT WAY NE). Case #2026-209244 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7023,6 +7600,11 @@
       <c r="L90" t="n">
         <v>695.6</v>
       </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Extortion/blackmail on Jul 15, 2026, 696 m from Northgate Station (112XX BLOCK OF ROOSEVELT WAY NE). Case #2026-209244 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7077,6 +7659,11 @@
       <c r="L91" t="n">
         <v>747.8</v>
       </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Not reportable to nibrs on Jul 14, 2026, 748 m from Northgate Station (N NORTHGATE WAY / N 107TH ST). Case #2026-205997 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7131,6 +7718,11 @@
       <c r="L92" t="n">
         <v>747.8</v>
       </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>All other larceny on Jul 14, 2026, 748 m from Northgate Station (N NORTHGATE WAY / N 107TH ST). Case #2026-205997 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7185,6 +7777,11 @@
       <c r="L93" t="n">
         <v>539.1</v>
       </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 14, 2026, 539 m from Northgate Station (8XX BLOCK OF NE NORTHGATE WAY). Case #2026-205238 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7239,6 +7836,11 @@
       <c r="L94" t="n">
         <v>446.4</v>
       </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Theft from building on Jul 12, 2026, 446 m from Northgate Station (106XX BLOCK OF 8TH AVE NE). Case #2026-912472 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7293,6 +7895,11 @@
       <c r="L95" t="n">
         <v>661.7</v>
       </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Not reportable to nibrs on Jul 12, 2026, 662 m from Northgate Station (102XX BLOCK OF 1ST AVE NE). Case #2026-203277 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7347,6 +7954,11 @@
       <c r="L96" t="n">
         <v>338.4</v>
       </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Theft from building on Jul 12, 2026, 338 m from Northgate Station (5XX BLOCK OF NE NORTHGATE WAY). Case #2026-912560 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7401,6 +8013,11 @@
       <c r="L97" t="n">
         <v>574.6</v>
       </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 11, 2026, 575 m from Northgate Station (MERIDIAN AVE N / N NORTHGATE WAY). Case #2026-202634 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7455,6 +8072,11 @@
       <c r="L98" t="n">
         <v>639.8</v>
       </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Weapon law violations on Jul 11, 2026, 640 m from Northgate Station (ROOSEVELT WAY NE / NE NORTHGATE WAY). Case #2026-202517 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7509,6 +8131,11 @@
       <c r="L99" t="n">
         <v>639.8</v>
       </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 11, 2026, 640 m from Northgate Station (ROOSEVELT WAY NE / NE NORTHGATE WAY). Case #2026-202517 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7563,6 +8190,11 @@
       <c r="L100" t="n">
         <v>596.2</v>
       </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Robbery on Jul 11, 2026, 596 m from Northgate Station (5TH AVE NE / NE 103RD ST). Case #2026-202517 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7617,6 +8249,11 @@
       <c r="L101" t="n">
         <v>680.6</v>
       </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Motor vehicle theft on Jul 11, 2026, 681 m from Northgate Station (N 116TH ST / CORLISS AVE N). Case #2026-202934 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7671,6 +8308,11 @@
       <c r="L102" t="n">
         <v>957.9</v>
       </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Motor vehicle theft on Jul 11, 2026, 958 m from Northgate Station (95XX BLOCK OF 1ST AVE NE). Case #2026-207923 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7725,6 +8367,11 @@
       <c r="L103" t="n">
         <v>504.5</v>
       </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Motor vehicle theft on Jul 11, 2026, 504 m from Northgate Station (113XX BLOCK OF 8TH AVE NE). Case #2026-203002 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7779,6 +8426,11 @@
       <c r="L104" t="n">
         <v>145.2</v>
       </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 10, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-700469 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7833,6 +8485,11 @@
       <c r="L105" t="n">
         <v>338.4</v>
       </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Credit card/automated teller machine fraud on Jul 10, 2026, 338 m from Northgate Station (5XX BLOCK OF NE NORTHGATE WAY). Case #2026-912276 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7887,6 +8544,11 @@
       <c r="L106" t="n">
         <v>539.1</v>
       </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 10, 2026, 539 m from Northgate Station (8XX BLOCK OF NE NORTHGATE WAY). Case #2026-200722 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7941,6 +8603,11 @@
       <c r="L107" t="n">
         <v>338.4</v>
       </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>Credit card/automated teller machine fraud on Jul 10, 2026, 338 m from Northgate Station (5XX BLOCK OF NE NORTHGATE WAY). Case #2026-912316 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7995,6 +8662,11 @@
       <c r="L108" t="n">
         <v>504.5</v>
       </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Intimidation on Jul 09, 2026, 504 m from Northgate Station (113XX BLOCK OF 8TH AVE NE). Case #2026-200096 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -8049,6 +8721,11 @@
       <c r="L109" t="n">
         <v>661.7</v>
       </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>Destruction/damage/vandalism of property on Jul 08, 2026, 662 m from Northgate Station (100XX BLOCK OF 1ST AVE NE). Case #2026-912125 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -8103,6 +8780,11 @@
       <c r="L110" t="n">
         <v>145.2</v>
       </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>All other larceny on Jul 07, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-198224 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -8157,6 +8839,11 @@
       <c r="L111" t="n">
         <v>338.4</v>
       </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Simple assault on Jul 07, 2026, 338 m from Northgate Station (5XX BLOCK OF NE NORTHGATE WAY). Case #2026-196771 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -8211,6 +8898,11 @@
       <c r="L112" t="n">
         <v>891.2</v>
       </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>Identity theft on Jul 07, 2026, 891 m from Northgate Station (113XX BLOCK OF 12TH AVE NE). Case #2026-913095 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -8265,6 +8957,11 @@
       <c r="L113" t="n">
         <v>446.4</v>
       </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>Destruction/damage/vandalism of property on Jul 06, 2026, 446 m from Northgate Station (106XX BLOCK OF 8TH AVE NE). Case #2026-197607 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -8319,6 +9016,11 @@
       <c r="L114" t="n">
         <v>316.5</v>
       </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>Theft from building on Jul 06, 2026, 316 m from Northgate Station (113XX BLOCK OF 3RD AVE NE). Case #2026-912274 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -8373,6 +9075,11 @@
       <c r="L115" t="n">
         <v>175.6</v>
       </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Theft of motor vehicle parts or accessories on Jul 06, 2026, 176 m from Northgate Station (3RD AVE NE / NE 112TH ST). Case #2026-912004 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -8427,6 +9134,11 @@
       <c r="L116" t="n">
         <v>446.4</v>
       </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>Theft from building on Jul 03, 2026, 446 m from Northgate Station (107XX BLOCK OF 8TH AVE NE). Case #2026-196223 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -8481,6 +9193,11 @@
       <c r="L117" t="n">
         <v>798.3</v>
       </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Aggravated assault on Jul 02, 2026, 798 m from Northgate Station (117XX BLOCK OF 5TH AVE NE). Case #2026-191308 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8535,6 +9252,11 @@
       <c r="L118" t="n">
         <v>438.6</v>
       </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Theft from motor vehicle on Jul 01, 2026, 439 m from Northgate Station (NE NORTHGATE WAY / 8TH AVE NE). Case #2026-911816 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8589,6 +9311,11 @@
       <c r="L119" t="n">
         <v>338.4</v>
       </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>Not reportable to nibrs on Jul 01, 2026, 338 m from Northgate Station (5XX BLOCK OF NE NORTHGATE WAY). Case #2026-190746 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -8643,6 +9370,11 @@
       <c r="L120" t="n">
         <v>880.9</v>
       </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Drug/narcotic violations on Jul 01, 2026, 881 m from Northgate Station (100XX BLOCK OF COLLEGE WAY N). Case #2026-190665 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8697,6 +9429,11 @@
       <c r="L121" t="n">
         <v>504.5</v>
       </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Not reportable to nibrs on Jul 01, 2026, 504 m from Northgate Station (110XX BLOCK OF 8TH AVE NE). Case #2026-190986 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -8751,6 +9488,11 @@
       <c r="L122" t="n">
         <v>145.2</v>
       </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>Burglary/breaking &amp; entering on Jun 30, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-189518 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -8805,6 +9547,11 @@
       <c r="L123" t="n">
         <v>661.7</v>
       </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Not reportable to nibrs on Jun 30, 2026, 662 m from Northgate Station (102XX BLOCK OF 1ST AVE NE). Case #2026-911710 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -8859,6 +9606,11 @@
       <c r="L124" t="n">
         <v>145.2</v>
       </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jun 30, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-700460 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -8913,6 +9665,11 @@
       <c r="L125" t="n">
         <v>627</v>
       </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>Impersonation on Jun 30, 2026, 627 m from Northgate Station (3XX BLOCK OF NE THORNTON PL). Case #2026-190221 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -8967,6 +9724,11 @@
       <c r="L126" t="n">
         <v>706.5</v>
       </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>Theft from motor vehicle on Jun 29, 2026, 706 m from Northgate Station (8XX BLOCK OF NE 105TH ST). Case #2026-187728 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -9021,6 +9783,11 @@
       <c r="L127" t="n">
         <v>706.5</v>
       </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>Not reportable to nibrs on Jun 29, 2026, 706 m from Northgate Station (8XX BLOCK OF NE 105TH ST). Case #2026-187728 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -9075,6 +9842,11 @@
       <c r="L128" t="n">
         <v>539</v>
       </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jun 29, 2026, 539 m from Northgate Station (8XX BLOCK OF NE NORTHGATE WAY). Case #2026-187628 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -9129,6 +9901,11 @@
       <c r="L129" t="n">
         <v>25.7</v>
       </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jun 29, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266008929 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -9183,6 +9960,11 @@
       <c r="L130" t="n">
         <v>25.7</v>
       </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>Disturbing-the-peace on Jul 06, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP2026370716 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -9237,6 +10019,11 @@
       <c r="L131" t="n">
         <v>25.7</v>
       </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 05, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266009170 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -9291,6 +10078,11 @@
       <c r="L132" t="n">
         <v>25.7</v>
       </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 02, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266009209 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -9345,6 +10137,11 @@
       <c r="L133" t="n">
         <v>25.7</v>
       </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 08, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP2026376323 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -9399,6 +10196,11 @@
       <c r="L134" t="n">
         <v>25.7</v>
       </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 09, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266009395 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -9453,6 +10255,11 @@
       <c r="L135" t="n">
         <v>25.7</v>
       </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 09, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP2026380800 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -9507,6 +10314,11 @@
       <c r="L136" t="n">
         <v>25.7</v>
       </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>Theft-from-bldg on Jul 15, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266009631 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -9561,6 +10373,11 @@
       <c r="L137" t="n">
         <v>25.7</v>
       </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 21, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266009882 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -9615,6 +10432,11 @@
       <c r="L138" t="n">
         <v>100.4</v>
       </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>Theft-other on Jul 20, 2026, 100 m from Cherry Creek Shopping Center (3030 E 1ST AVE). Victims: 1. Case #DP2026399148 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -9669,6 +10491,11 @@
       <c r="L139" t="n">
         <v>144.7</v>
       </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 07, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP20266009249 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -9723,6 +10550,11 @@
       <c r="L140" t="n">
         <v>160</v>
       </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 15, 2026, 160 m from Cherry Creek Shopping Center (3110 E 1ST AVE). Victims: 1. Case #DP2026388611 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -9777,6 +10609,11 @@
       <c r="L141" t="n">
         <v>171.5</v>
       </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>Theft-other on Jul 02, 2026, 171 m from Cherry Creek Shopping Center (100 BLOCK N FILLMORE ST). Victims: 1. Case #DP2026361915 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -9831,6 +10668,11 @@
       <c r="L142" t="n">
         <v>247.6</v>
       </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 02, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026361616 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -9885,6 +10727,11 @@
       <c r="L143" t="n">
         <v>247.6</v>
       </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>Theft-other on Jul 05, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026368528 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -9939,6 +10786,11 @@
       <c r="L144" t="n">
         <v>247.6</v>
       </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>Theft-bicycle on Jul 03, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP20266009015 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -9993,6 +10845,11 @@
       <c r="L145" t="n">
         <v>247.6</v>
       </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 07, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP20266009264 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -10047,6 +10904,11 @@
       <c r="L146" t="n">
         <v>247.6</v>
       </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 09, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026377178 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -10101,6 +10963,11 @@
       <c r="L147" t="n">
         <v>247.6</v>
       </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>Drug-methampetamine-possess on Jul 18, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026395041 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -10155,6 +11022,11 @@
       <c r="L148" t="n">
         <v>247.6</v>
       </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>Criminal-trespassing on Jul 18, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026395041 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -10209,6 +11081,11 @@
       <c r="L149" t="n">
         <v>247.6</v>
       </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 17, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026395355 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -10263,6 +11140,11 @@
       <c r="L150" t="n">
         <v>247.6</v>
       </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 18, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026395041 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -10317,6 +11199,11 @@
       <c r="L151" t="n">
         <v>247.6</v>
       </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 21, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026407757 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -10371,6 +11258,11 @@
       <c r="L152" t="n">
         <v>247.6</v>
       </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 22, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026405696 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -10425,6 +11317,11 @@
       <c r="L153" t="n">
         <v>247.6</v>
       </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 23, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026405563 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -10479,6 +11376,11 @@
       <c r="L154" t="n">
         <v>336.5</v>
       </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>Theft-other on Jul 09, 2026, 336 m from Cherry Creek Shopping Center (3200 BLK E 1ST AVE). Victims: 1. Case #DP20266009457 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -10533,6 +11435,11 @@
       <c r="L155" t="n">
         <v>448.9</v>
       </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>Fraud-criminal-impersonation on Jun 30, 2026, 449 m from Cherry Creek Shopping Center (101 N COOK ST). Victims: 1. Case #DP2026361832 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -10587,6 +11494,11 @@
       <c r="L156" t="n">
         <v>482.2</v>
       </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 14, 2026, 482 m from Cherry Creek Shopping Center (2375 E 1ST AVE). Victims: 1. Case #DP2026387192 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -10641,6 +11553,11 @@
       <c r="L157" t="n">
         <v>493.3</v>
       </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>Violation-of-court-order on Jul 01, 2026, 493 m from Cherry Creek Shopping Center (250 N STEELE ST). Victims: 1. Case #DP2026359687 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -10695,6 +11612,11 @@
       <c r="L158" t="n">
         <v>497.1</v>
       </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>Theft-items-from-vehicle on Jul 15, 2026, 497 m from Cherry Creek Shopping Center (3498 E ELLSWORTH AVE). Victims: 1. Case #DP20266009661 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -10749,6 +11671,11 @@
       <c r="L159" t="n">
         <v>497.7</v>
       </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>Robbery-bank on Jul 01, 2026, 498 m from Cherry Creek Shopping Center (3410 E 1ST AVE). Victims: 1. Case #DP2026357948 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -10803,6 +11730,11 @@
       <c r="L160" t="n">
         <v>499.1</v>
       </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>Theft-bicycle on Jul 17, 2026, 499 m from Cherry Creek Shopping Center (3300 E BAYAUD AVE). Victims: 1. Case #DP20266009730 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -10857,6 +11789,11 @@
       <c r="L161" t="n">
         <v>504.6</v>
       </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>Theft-bicycle on Jul 20, 2026, 505 m from Cherry Creek Shopping Center (2817 E 3RD AVE). Victims: 1. Case #DP20266009841 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -10911,6 +11848,11 @@
       <c r="L162" t="n">
         <v>527.7</v>
       </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>Theft-of-motor-vehicle on Jul 20, 2026, 528 m from Cherry Creek Shopping Center (E 3RD AVE / N CLAYTON ST). Victims: 1. Case #DP2026399087 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -10965,6 +11907,11 @@
       <c r="L163" t="n">
         <v>546.3</v>
       </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>Theft-of-motor-vehicle on Jul 23, 2026, 546 m from Cherry Creek Shopping Center (3333 E BAYAUD AVE). Victims: 1. Case #DP2026409948 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -11019,6 +11966,11 @@
       <c r="L164" t="n">
         <v>566.4</v>
       </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>Harassment on Jul 22, 2026, 566 m from Cherry Creek Shopping Center (300 BLOCK N ST PAUL ST). Victims: 1. Case #DP2026403380 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -11073,6 +12025,11 @@
       <c r="L165" t="n">
         <v>566.4</v>
       </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>Disturbing-the-peace on Jul 22, 2026, 566 m from Cherry Creek Shopping Center (300 BLOCK N ST PAUL ST). Victims: 1. Case #DP2026403380 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -11127,6 +12084,11 @@
       <c r="L166" t="n">
         <v>566.4</v>
       </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>Assault-simple on Jul 22, 2026, 566 m from Cherry Creek Shopping Center (300 BLOCK N ST PAUL ST). Victims: 1. Case #DP2026403380 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -11181,6 +12143,11 @@
       <c r="L167" t="n">
         <v>628.1</v>
       </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>Criminal-mischief-mtr-veh on Jul 21, 2026, 628 m from Cherry Creek Shopping Center (2445 E 3RD AVE). Victims: 1. Case #DP2026401106 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -11235,6 +12202,11 @@
       <c r="L168" t="n">
         <v>627.3</v>
       </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>Theft-other on Jul 10, 2026, 627 m from Cherry Creek Shopping Center (106 S MADISON ST). Victims: 1. Case #DP20266009356 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -11289,6 +12261,11 @@
       <c r="L169" t="n">
         <v>637.1</v>
       </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>Theft-items-from-vehicle on Jul 14, 2026, 637 m from Cherry Creek Shopping Center (3131 E ALAMEDA AVE). Victims: 1. Case #DP2026386904 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -11343,6 +12320,11 @@
       <c r="L170" t="n">
         <v>642</v>
       </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>Theft-parts-from-vehicle on Jul 06, 2026, 642 m from Cherry Creek Shopping Center (2605 E ALAMEDA AVE). Victims: 1. Case #DP20266009245 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -11397,6 +12379,11 @@
       <c r="L171" t="n">
         <v>690.8</v>
       </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>Theft-other on Jun 30, 2026, 691 m from Cherry Creek Shopping Center (191 N UNIVERSITY BLVD). Victims: 1. Case #DP20266009219 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -11451,6 +12438,11 @@
       <c r="L172" t="n">
         <v>709.2</v>
       </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>Criminal-mischief-other on Jul 21, 2026, 709 m from Cherry Creek Shopping Center (443 N MILWAUKEE ST). Victims: 1. Case #DP20266009856 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -11505,6 +12497,11 @@
       <c r="L173" t="n">
         <v>769.8</v>
       </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>Theft-other on Jun 30, 2026, 770 m from Cherry Creek Shopping Center (400 BLK N CLAYTON ST). Victims: 1. Case #DP20266008959 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -11559,6 +12556,11 @@
       <c r="L174" t="n">
         <v>779.5</v>
       </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>Burglary-residence-no-force on Jul 26, 2026, 779 m from Cherry Creek Shopping Center (100 BLK N GARFIELD ST). Victims: 1. Case #DP2026411500 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -11613,6 +12615,11 @@
       <c r="L175" t="n">
         <v>794.9</v>
       </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>Theft-from-bldg on Jul 18, 2026, 795 m from Cherry Creek Shopping Center (00 BLK N GARFIELD ST). Victims: 1. Case #DP20266009776 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -11667,6 +12674,11 @@
       <c r="L176" t="n">
         <v>868.5</v>
       </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>Theft-parts-from-vehicle on Jul 19, 2026, 869 m from Cherry Creek Shopping Center (2450 E 5TH AVE). Victims: 1. Case #DP20266009826 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -11721,6 +12733,11 @@
       <c r="L177" t="n">
         <v>952.3</v>
       </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>Theft-other on Jul 16, 2026, 952 m from Cherry Creek Shopping Center (3689 E CHERRY CREEK S DR). Victims: 1. Case #DP20266009658 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -11775,9 +12792,14 @@
       <c r="L178" t="n">
         <v>962</v>
       </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>Criminal-mischief-other on Jul 04, 2026, 962 m from Cherry Creek Shopping Center (3030 E 6TH AVE). Victims: 1. Case #DP20266009033 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L178"/>
+  <autoFilter ref="A1:M178"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11815,7 +12837,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-29 07:35:12.335477+00:00</t>
+          <t>2026-07-29 07:43:40.709434+00:00</t>
         </is>
       </c>
     </row>
@@ -11837,7 +12859,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-29 07:35:12.335477+00:00</t>
+          <t>2026-06-29 07:43:40.709434+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/latest/blotter_report.xlsx
+++ b/reports/latest/blotter_report.xlsx
@@ -12837,7 +12837,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-29 07:43:40.709434+00:00</t>
+          <t>2026-07-29 07:53:08.662629+00:00</t>
         </is>
       </c>
     </row>
@@ -12859,7 +12859,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-29 07:43:40.709434+00:00</t>
+          <t>2026-06-29 07:53:08.662629+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/latest/blotter_report.xlsx
+++ b/reports/latest/blotter_report.xlsx
@@ -12837,7 +12837,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-29 07:53:08.662629+00:00</t>
+          <t>2026-07-29 07:57:37.243492+00:00</t>
         </is>
       </c>
     </row>
@@ -12859,7 +12859,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-29 07:53:08.662629+00:00</t>
+          <t>2026-06-29 07:57:37.243492+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/latest/blotter_report.xlsx
+++ b/reports/latest/blotter_report.xlsx
@@ -13,10 +13,10 @@
     <sheet name="Run Metadata" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$K$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$K$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Highlights'!$A$1:$M$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$233</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$328</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -519,12 +519,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BEVCENTER</t>
+          <t>ABQUP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Beverly Center</t>
+          <t>ABQ Uptown</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -547,12 +547,8 @@
       <c r="H2" t="n">
         <v>0</v>
       </c>
-      <c r="I2" t="n">
-        <v>111.8</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>46214.80486111111</v>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="b">
         <v>0</v>
       </c>
@@ -560,12 +556,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>BEVCENTER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Beverly Center</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -574,25 +570,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>58</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>3</v>
+        <v>12</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>25.7</v>
+        <v>111.8</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>46231.83333333334</v>
+        <v>46214.80486111111</v>
       </c>
       <c r="K3" t="b">
         <v>0</v>
@@ -601,12 +597,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GREENHILLS</t>
+          <t>CHARLOTTE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Mall at Green Hills</t>
+          <t>Charlotte Premium Outlets</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -615,25 +611,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>186.3</v>
+        <v>151.4</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>46232.0625</v>
+        <v>46231.16666666666</v>
       </c>
       <c r="K4" t="b">
         <v>0</v>
@@ -642,36 +638,40 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LENOX</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lenox Square</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>NO COVERAGE</t>
+          <t>Cherry Creek Shopping Center</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
+        <v>58</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="I5" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>46231.83333333334</v>
+      </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
@@ -679,12 +679,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>GREENHILLS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>The Mall at Green Hills</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -693,25 +693,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I6" t="n">
-        <v>145.2</v>
+        <v>186.3</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>46232.82986111111</v>
+        <v>46232.0625</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
@@ -720,40 +720,36 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>LENOX</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>Lenox Square</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>NO COVERAGE</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>54</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>15</v>
-      </c>
-      <c r="I7" t="n">
-        <v>113.7</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>46231.92430555556</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="b">
         <v>0</v>
       </c>
@@ -761,42 +757,165 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>THEDOMAIN</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Domain</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>NO COVERAGE</t>
+          <t>Northgate Station</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
+        <v>66</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>8</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="I8" t="n">
+        <v>145.2</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>46232.82986111111</v>
+      </c>
       <c r="K8" t="b">
         <v>0</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>OPRYMILLS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Opry Mills</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>54</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>15</v>
+      </c>
+      <c r="I9" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>46231.92430555556</v>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>73</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>47</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>23</v>
+      </c>
+      <c r="I10" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>46231.16666666666</v>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>THEDOMAIN</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>The Domain</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>NO COVERAGE</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K8"/>
+  <autoFilter ref="A1:K11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1072,30 +1191,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DP2026357948121100</t>
+          <t>20260723-0938-05</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>46204.69791666666</v>
+        <v>46218.16666666666</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>robbery-bank</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1105,56 +1224,56 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>robbery</t>
+          <t>13A</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3410 E 1ST AVE</t>
+          <t>6600 FAIRVIEW RD</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>39.71748838438504</v>
+        <v>35.14845720336839</v>
       </c>
       <c r="K5" t="n">
-        <v>-104.946995728207</v>
+        <v>-80.83089079594687</v>
       </c>
       <c r="L5" t="n">
-        <v>497.7</v>
+        <v>383.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Robbery-bank on Jul 01, 2026, 498 m from Cherry Creek Shopping Center (3410 E 1ST AVE). Victims: 1. Case #DP2026357948 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 15, 2026, 384 m from Southpark (6600 FAIRVIEW RD). Status: Open. Case #20260723-0938-05 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>71712344706</t>
+          <t>DP2026357948121100</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>46220.41458333333</v>
+        <v>46204.69791666666</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Weapon Law Violations</t>
+          <t>robbery-bank</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1164,56 +1283,56 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ALL OTHER</t>
+          <t>robbery</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>3410 E 1ST AVE</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>47.708569</v>
+        <v>39.71748838438504</v>
       </c>
       <c r="K6" t="n">
-        <v>-122.319207</v>
+        <v>-104.946995728207</v>
       </c>
       <c r="L6" t="n">
-        <v>539</v>
+        <v>497.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Weapon law violations on Jul 17, 2026, 539 m from Northgate Station (8XX BLOCK OF NE NORTHGATE WAY). Case #2026-208823 (use for a records request — full narratives are not published in open data).</t>
+          <t>Robbery-bank on Jul 01, 2026, 498 m from Cherry Creek Shopping Center (3410 E 1ST AVE). Victims: 1. Case #DP2026357948 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DP2026403380131300</t>
+          <t>71712344706</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>46225.54166666666</v>
+        <v>46220.41458333333</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>assault-simple</t>
+          <t>Weapon Law Violations</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1223,56 +1342,56 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>other-crimes-against-persons</t>
+          <t>ALL OTHER</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>300 BLOCK N ST PAUL ST</t>
+          <t>8XX BLOCK OF NE NORTHGATE WAY</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>39.72175920473841</v>
+        <v>47.708569</v>
       </c>
       <c r="K7" t="n">
-        <v>-104.9509152755314</v>
+        <v>-122.319207</v>
       </c>
       <c r="L7" t="n">
-        <v>566.4</v>
+        <v>539</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Assault-simple on Jul 22, 2026, 566 m from Cherry Creek Shopping Center (300 BLOCK N ST PAUL ST). Victims: 1. Case #DP2026403380 (use for a records request — full narratives are not published in open data).</t>
+          <t>Weapon law violations on Jul 17, 2026, 539 m from Northgate Station (8XX BLOCK OF NE NORTHGATE WAY). Case #2026-208823 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>71584399485</t>
+          <t>DP2026403380131300</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>46214.825</v>
+        <v>46225.54166666666</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Robbery</t>
+          <t>assault-simple</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1282,56 +1401,56 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>VIOLENT CRIME</t>
+          <t>other-crimes-against-persons</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5TH AVE NE / NE 103RD ST</t>
+          <t>300 BLOCK N ST PAUL ST</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>47.70314032</v>
+        <v>39.72175920473841</v>
       </c>
       <c r="K8" t="n">
-        <v>-122.323148370417</v>
+        <v>-104.9509152755314</v>
       </c>
       <c r="L8" t="n">
-        <v>596.2</v>
+        <v>566.4</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Robbery on Jul 11, 2026, 596 m from Northgate Station (5TH AVE NE / NE 103RD ST). Case #2026-202517 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault-simple on Jul 22, 2026, 566 m from Cherry Creek Shopping Center (300 BLOCK N ST PAUL ST). Victims: 1. Case #DP2026403380 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GREENHILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Mall at Green Hills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GREENHILLS:Metro Nashville PD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>20260449391_11</t>
+          <t>71584399485</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>46227.02291666667</v>
+        <v>46214.825</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>BURGLARY- AGGRAVATED</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1341,56 +1460,56 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Unarmed</t>
+          <t>VIOLENT CRIME</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>GRAYBAR</t>
+          <t>5TH AVE NE / NE 103RD ST</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>36.10999999969955</v>
+        <v>47.70314032</v>
       </c>
       <c r="K9" t="n">
-        <v>-86.81000000032267</v>
+        <v>-122.323148370417</v>
       </c>
       <c r="L9" t="n">
-        <v>630.5</v>
+        <v>596.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Burglary- aggravated on Jul 24, 2026, 631 m from The Mall at Green Hills (GRAYBAR). Weapon: Unarmed. Premises: RESIDENCE, HOME. Status: OPEN. Victims: 1. Case #20260449391 (use for a records request — full narratives are not published in open data).</t>
+          <t>Robbery on Jul 11, 2026, 596 m from Northgate Station (5TH AVE NE / NE 103RD ST). Case #2026-202517 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>GREENHILLS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>The Mall at Green Hills</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>GREENHILLS:Metro Nashville PD Incidents</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>71783099253</t>
+          <t>20260449391_11</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>46214.86041666667</v>
+        <v>46227.02291666667</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Weapon Law Violations</t>
+          <t>BURGLARY- AGGRAVATED</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1400,56 +1519,56 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ALL OTHER</t>
+          <t>Unarmed</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ROOSEVELT WAY NE / NE NORTHGATE WAY</t>
+          <t>GRAYBAR</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>47.70856098</v>
+        <v>36.10999999969955</v>
       </c>
       <c r="K10" t="n">
-        <v>-122.317852210813</v>
+        <v>-86.81000000032267</v>
       </c>
       <c r="L10" t="n">
-        <v>639.8</v>
+        <v>630.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Weapon law violations on Jul 11, 2026, 640 m from Northgate Station (ROOSEVELT WAY NE / NE NORTHGATE WAY). Case #2026-202517 (use for a records request — full narratives are not published in open data).</t>
+          <t>Burglary- aggravated on Jul 24, 2026, 631 m from The Mall at Green Hills (GRAYBAR). Weapon: Unarmed. Premises: RESIDENCE, HOME. Status: OPEN. Victims: 1. Case #20260449391 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DP2026411044131300</t>
+          <t>71783099253</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>46229.1125</v>
+        <v>46214.86041666667</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>assault-simple</t>
+          <t>Weapon Law Violations</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1459,56 +1578,56 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>other-crimes-against-persons</t>
+          <t>ALL OTHER</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3200 BLOCK E CHERRY CREEK S DR</t>
+          <t>ROOSEVELT WAY NE / NE NORTHGATE WAY</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>39.71130989687384</v>
+        <v>47.70856098</v>
       </c>
       <c r="K11" t="n">
-        <v>-104.9490029653731</v>
+        <v>-122.317852210813</v>
       </c>
       <c r="L11" t="n">
-        <v>696.3</v>
+        <v>639.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Assault-simple on Jul 26, 2026, 696 m from Cherry Creek Shopping Center (3200 BLOCK E CHERRY CREEK S DR). Victims: 1. Case #DP2026411044 (use for a records request — full narratives are not published in open data).</t>
+          <t>Weapon law violations on Jul 11, 2026, 640 m from Northgate Station (ROOSEVELT WAY NE / NE NORTHGATE WAY). Case #2026-202517 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GREENHILLS</t>
+          <t>CHARLOTTE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Mall at Green Hills</t>
+          <t>Charlotte Premium Outlets</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GREENHILLS:Metro Nashville PD Incidents</t>
+          <t>CHARLOTTE:CMPD Incidents</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>20260413668_11</t>
+          <t>20260722-2124-02</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>46208.92083333333</v>
+        <v>46225.16666666666</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASSAULT- FEAR OF BODILY INJURY</t>
+          <t>Simple Assault</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1516,54 +1635,58 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>13B</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2011 2011</t>
+          <t>9400 STEELE CREEK RD</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>36.10400000035705</v>
+        <v>35.16250902126527</v>
       </c>
       <c r="K12" t="n">
-        <v>-86.81000000032267</v>
+        <v>-80.96982377170991</v>
       </c>
       <c r="L12" t="n">
-        <v>702.5</v>
+        <v>647.8</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Assault- fear of bodily injury on Jul 05, 2026, 702 m from The Mall at Green Hills (2011 2011). Premises: APARTMENT. Status: REFUSED TO COOPERATE. Victims: 1. Flags: domestic related. Case #20260413668 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 22, 2026, 648 m from Charlotte Premium Outlets (9400 STEELE CREEK RD). Status: Open. Case #20260722-2124-02 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>71275287160</t>
+          <t>DP2026411044131300</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>46205.52083333334</v>
+        <v>46229.1125</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Aggravated Assault</t>
+          <t>assault-simple</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1573,52 +1696,52 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>VIOLENT CRIME</t>
+          <t>other-crimes-against-persons</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>117XX BLOCK OF 5TH AVE NE</t>
+          <t>3200 BLOCK E CHERRY CREEK S DR</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>47.71495242</v>
+        <v>39.71130989687384</v>
       </c>
       <c r="K13" t="n">
-        <v>-122.323460201162</v>
+        <v>-104.9490029653731</v>
       </c>
       <c r="L13" t="n">
-        <v>798.3</v>
+        <v>696.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 02, 2026, 798 m from Northgate Station (117XX BLOCK OF 5TH AVE NE). Case #2026-191308 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault-simple on Jul 26, 2026, 696 m from Cherry Creek Shopping Center (3200 BLOCK E CHERRY CREEK S DR). Victims: 1. Case #DP2026411044 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>GREENHILLS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>The Mall at Green Hills</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>GREENHILLS:Metro Nashville PD Incidents</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>20260423135_11</t>
+          <t>20260413668_11</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>46214.05208333334</v>
+        <v>46208.92083333333</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1633,51 +1756,51 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>OPRYLAND</t>
+          <t>2011 2011</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>36.20999999970633</v>
+        <v>36.10400000035705</v>
       </c>
       <c r="K14" t="n">
-        <v>-86.69000000027951</v>
+        <v>-86.81000000032267</v>
       </c>
       <c r="L14" t="n">
-        <v>808.3</v>
+        <v>702.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Assault- fear of bodily injury on Jul 11, 2026, 808 m from Opry Mills (OPRYLAND). Premises: HOTEL, MOTEL, ETC.. Status: OPEN. Victims: 1. Case #20260423135 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault- fear of bodily injury on Jul 05, 2026, 702 m from The Mall at Green Hills (2011 2011). Premises: APARTMENT. Status: REFUSED TO COOPERATE. Victims: 1. Flags: domestic related. Case #20260413668 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>20260440008_11</t>
+          <t>71275287160</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>46222.99930555555</v>
+        <v>46205.52083333334</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Assault, Aggravated - Deadly Weapon - Int/Kn</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1687,26 +1810,26 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>HANDGUN</t>
+          <t>VIOLENT CRIME</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2902 2902</t>
+          <t>117XX BLOCK OF 5TH AVE NE</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>36.20599999976586</v>
+        <v>47.71495242</v>
       </c>
       <c r="K15" t="n">
-        <v>-86.70200000037366</v>
+        <v>-122.323460201162</v>
       </c>
       <c r="L15" t="n">
-        <v>936.3</v>
+        <v>798.3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Assault, aggravated - deadly weapon - int/kn on Jul 19, 2026, 936 m from Opry Mills (2902 2902). Weapon: HANDGUN. Premises: RESIDENCE, HOME. Status: CLEARED BY ARREST. Victims: 1. Flags: domestic related. Case #20260440008 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 02, 2026, 798 m from Northgate Station (117XX BLOCK OF 5TH AVE NE). Case #2026-191308 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -1728,15 +1851,15 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>20260440008_22</t>
+          <t>20260423135_11</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>46222.99930555555</v>
+        <v>46214.05208333334</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ASSAULT- OFFENSIVE OR PROVOCATIVE CONTACT</t>
+          <t>ASSAULT- FEAR OF BODILY INJURY</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1744,58 +1867,54 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>PERSONAL (HANDS)</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2902 2902</t>
+          <t>OPRYLAND</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>36.20599999976586</v>
+        <v>36.20999999970633</v>
       </c>
       <c r="K16" t="n">
-        <v>-86.70200000037366</v>
+        <v>-86.69000000027951</v>
       </c>
       <c r="L16" t="n">
-        <v>936.3</v>
+        <v>808.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Assault- offensive or provocative contact on Jul 19, 2026, 936 m from Opry Mills (2902 2902). Weapon: PERSONAL (HANDS). Premises: RESIDENCE, HOME. Status: CLEARED BY ARREST. Victims: 2. Case #20260440008 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault- fear of bodily injury on Jul 11, 2026, 808 m from Opry Mills (OPRYLAND). Premises: HOTEL, MOTEL, ETC.. Status: OPEN. Victims: 1. Case #20260423135 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>20260440008_33</t>
+          <t>20260725-0853-00</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>46222.99930555555</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>WEAPON OFFENSE, CRIMINAL ATTEMPT</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1805,56 +1924,56 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>HANDGUN</t>
+          <t>13A</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2902 2902</t>
+          <t>5700 CARNEGIE BV</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>36.20599999976586</v>
+        <v>35.15368289092867</v>
       </c>
       <c r="K17" t="n">
-        <v>-86.70200000037366</v>
+        <v>-80.8398453262274</v>
       </c>
       <c r="L17" t="n">
-        <v>936.3</v>
+        <v>877.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Weapon offense, criminal attempt on Jul 19, 2026, 936 m from Opry Mills (2902 2902). Weapon: HANDGUN. Premises: RESIDENCE, HOME. Status: CLEARED BY ARREST. Victims: 3. Case #20260440008 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 25, 2026, 877 m from Southpark (5700 CARNEGIE BV). Status: Open. Case #20260725-0853-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>71878728447</t>
+          <t>20260722-0920-00</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>46230.4375</v>
+        <v>46225.16666666666</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Robbery</t>
+          <t>Simple Assault</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1864,262 +1983,262 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>VIOLENT CRIME</t>
+          <t>13B</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>16XX BLOCK OF N 105TH ST</t>
+          <t>5300 SHARON RD</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>47.70504225</v>
+        <v>35.14420159566059</v>
       </c>
       <c r="K18" t="n">
-        <v>-122.338094779232</v>
+        <v>-80.83298000600156</v>
       </c>
       <c r="L18" t="n">
-        <v>938.8</v>
+        <v>885.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Robbery on Jul 27, 2026, 939 m from Northgate Station (16XX BLOCK OF N 105TH ST). Case #2026-220064 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 22, 2026, 885 m from Southpark (5300 SHARON RD). Status: Exceptionally Cleared. Case #20260722-0920-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>OPRYMILLS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Opry Mills</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DP20266009882230300</t>
+          <t>20260440008_11</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>46224.63194444445</v>
+        <v>46222.99930555555</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>theft-shoplift</t>
+          <t>Assault, Aggravated - Deadly Weapon - Int/Kn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>HANDGUN</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3000 E 1ST AVE</t>
+          <t>2902 2902</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>39.71700581534508</v>
+        <v>36.20599999976586</v>
       </c>
       <c r="K19" t="n">
-        <v>-104.9529964927036</v>
+        <v>-86.70200000037366</v>
       </c>
       <c r="L19" t="n">
-        <v>25.7</v>
+        <v>936.3</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Theft-shoplift on Jul 21, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266009882 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault, aggravated - deadly weapon - int/kn on Jul 19, 2026, 936 m from Opry Mills (2902 2902). Weapon: HANDGUN. Premises: RESIDENCE, HOME. Status: CLEARED BY ARREST. Victims: 1. Flags: domestic related. Case #20260440008 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>OPRYMILLS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Opry Mills</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>DP20266009631230800</t>
+          <t>20260440008_22</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>46218.5625</v>
+        <v>46222.99930555555</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>theft-from-bldg</t>
+          <t>ASSAULT- OFFENSIVE OR PROVOCATIVE CONTACT</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>PERSONAL (HANDS)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3000 E 1ST AVE</t>
+          <t>2902 2902</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>39.71700581534508</v>
+        <v>36.20599999976586</v>
       </c>
       <c r="K20" t="n">
-        <v>-104.9529964927036</v>
+        <v>-86.70200000037366</v>
       </c>
       <c r="L20" t="n">
-        <v>25.7</v>
+        <v>936.3</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Theft-from-bldg on Jul 15, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266009631 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault- offensive or provocative contact on Jul 19, 2026, 936 m from Opry Mills (2902 2902). Weapon: PERSONAL (HANDS). Premises: RESIDENCE, HOME. Status: CLEARED BY ARREST. Victims: 2. Case #20260440008 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>OPRYMILLS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Opry Mills</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DP20266009395230300</t>
+          <t>20260440008_33</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>46212.80555555555</v>
+        <v>46222.99930555555</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>theft-shoplift</t>
+          <t>WEAPON OFFENSE, CRIMINAL ATTEMPT</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>HANDGUN</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3000 E 1ST AVE</t>
+          <t>2902 2902</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>39.71700581534508</v>
+        <v>36.20599999976586</v>
       </c>
       <c r="K21" t="n">
-        <v>-104.9529964927036</v>
+        <v>-86.70200000037366</v>
       </c>
       <c r="L21" t="n">
-        <v>25.7</v>
+        <v>936.3</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Theft-shoplift on Jul 09, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266009395 (use for a records request — full narratives are not published in open data).</t>
+          <t>Weapon offense, criminal attempt on Jul 19, 2026, 936 m from Opry Mills (2902 2902). Weapon: HANDGUN. Premises: RESIDENCE, HOME. Status: CLEARED BY ARREST. Victims: 3. Case #20260440008 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>DP2026380800230300</t>
+          <t>71878728447</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>46212.60416666666</v>
+        <v>46230.4375</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>theft-shoplift</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>VIOLENT CRIME</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3000 E 1ST AVE</t>
+          <t>16XX BLOCK OF N 105TH ST</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>39.71700581534508</v>
+        <v>47.70504225</v>
       </c>
       <c r="K22" t="n">
-        <v>-104.9529964927036</v>
+        <v>-122.338094779232</v>
       </c>
       <c r="L22" t="n">
-        <v>25.7</v>
+        <v>938.8</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Theft-shoplift on Jul 09, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP2026380800 (use for a records request — full narratives are not published in open data).</t>
+          <t>Robbery on Jul 27, 2026, 939 m from Northgate Station (16XX BLOCK OF N 105TH ST). Case #2026-220064 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2141,11 +2260,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DP2026376323230300</t>
+          <t>DP20266009882230300</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>46211.75277777778</v>
+        <v>46224.63194444445</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2178,7 +2297,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Theft-shoplift on Jul 08, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP2026376323 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-shoplift on Jul 21, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266009882 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2200,15 +2319,15 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DP20266009170230300</t>
+          <t>DP20266009631230800</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>46208.67916666667</v>
+        <v>46218.5625</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>theft-shoplift</t>
+          <t>theft-from-bldg</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2237,7 +2356,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Theft-shoplift on Jul 05, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266009170 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-from-bldg on Jul 15, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266009631 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2259,11 +2378,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DP20266009209230300</t>
+          <t>DP20266009395230300</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>46205.70972222222</v>
+        <v>46212.80555555555</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2296,7 +2415,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Theft-shoplift on Jul 02, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266009209 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-shoplift on Jul 09, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266009395 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2318,15 +2437,15 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DP2026399148239900</t>
+          <t>DP2026380800230300</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>46223.54652777778</v>
+        <v>46212.60416666666</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>theft-other</t>
+          <t>theft-shoplift</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2341,21 +2460,21 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3030 E 1ST AVE</t>
+          <t>3000 E 1ST AVE</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>39.71760830239491</v>
+        <v>39.71700581534508</v>
       </c>
       <c r="K26" t="n">
-        <v>-104.9520888656285</v>
+        <v>-104.9529964927036</v>
       </c>
       <c r="L26" t="n">
-        <v>100.4</v>
+        <v>25.7</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Theft-other on Jul 20, 2026, 100 m from Cherry Creek Shopping Center (3030 E 1ST AVE). Victims: 1. Case #DP2026399148 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-shoplift on Jul 09, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP2026380800 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M233"/>
+  <dimension ref="A1:M328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16060,8 +16179,5613 @@
         </is>
       </c>
     </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>20260725-2301-00</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="n">
+        <v>46228.16666666666</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Other Unlisted Non-Criminal</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>6900 FAIRVIEW RD</t>
+        </is>
+      </c>
+      <c r="J234" t="n">
+        <v>35.14684118006692</v>
+      </c>
+      <c r="K234" t="n">
+        <v>-80.82544759809264</v>
+      </c>
+      <c r="L234" t="n">
+        <v>722.6</v>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>Other unlisted non-criminal on Jul 25, 2026, 723 m from Southpark (6900 FAIRVIEW RD). Status: Open. Case #20260725-2301-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>20260713-1954-00</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="n">
+        <v>46216.16666666666</v>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Extortion/Blackmail</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>300 SHARON TOWNSHIP LN</t>
+        </is>
+      </c>
+      <c r="J235" t="n">
+        <v>35.15734514344371</v>
+      </c>
+      <c r="K235" t="n">
+        <v>-80.82395947870275</v>
+      </c>
+      <c r="L235" t="n">
+        <v>846.2</v>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>Extortion/blackmail on Jul 13, 2026, 846 m from Southpark (300 SHARON TOWNSHIP LN). Status: Open. Case #20260713-1954-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>20260708-2322-01</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="n">
+        <v>46211.16666666666</v>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Driving Under The Influence</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>90D</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>4000 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J236" t="n">
+        <v>35.15567429979806</v>
+      </c>
+      <c r="K236" t="n">
+        <v>-80.82377486075073</v>
+      </c>
+      <c r="L236" t="n">
+        <v>738.5</v>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>Driving under the influence on Jul 08, 2026, 738 m from Southpark (4000 SHARON RD). Status: Cleared by Arrest. Case #20260708-2322-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>20260725-1345-01</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="n">
+        <v>46227.16666666666</v>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J237" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K237" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L237" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 24, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260725-1345-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>20260726-0712-02</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="n">
+        <v>46229.16666666666</v>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Theft From Motor Vehicle</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>23F</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>6300 CARNEGIE BV</t>
+        </is>
+      </c>
+      <c r="J238" t="n">
+        <v>35.15641923337007</v>
+      </c>
+      <c r="K238" t="n">
+        <v>-80.83429541207509</v>
+      </c>
+      <c r="L238" t="n">
+        <v>613</v>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>Theft from motor vehicle on Jul 26, 2026, 613 m from Southpark (6300 CARNEGIE BV). Status: Open. Case #20260726-0712-02 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>20260721-1118-01</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="n">
+        <v>46220.16666666666</v>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J239" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K239" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L239" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 17, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260721-1118-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>20260724-1414-04</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="n">
+        <v>46216.16666666666</v>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>All Other Thefts</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>23H</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>6200 FAIRVIEW RD</t>
+        </is>
+      </c>
+      <c r="J240" t="n">
+        <v>35.15078706372375</v>
+      </c>
+      <c r="K240" t="n">
+        <v>-80.8369057357377</v>
+      </c>
+      <c r="L240" t="n">
+        <v>599.6</v>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>All other thefts on Jul 13, 2026, 600 m from Southpark (6200 FAIRVIEW RD). Status: Open. Case #20260724-1414-04 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>20260703-2055-06</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="n">
+        <v>46205.16666666666</v>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Intimidation</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>13C</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J241" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K241" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L241" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>Intimidation on Jul 02, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260703-2055-06 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>20260703-0713-01</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="n">
+        <v>46205.16666666666</v>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J242" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K242" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L242" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 02, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260703-0713-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>20260717-0842-02</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="n">
+        <v>46220.16666666666</v>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Burglary/B&amp;E</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>700 GOVERNOR MORRISON ST</t>
+        </is>
+      </c>
+      <c r="J243" t="n">
+        <v>35.15648042297118</v>
+      </c>
+      <c r="K243" t="n">
+        <v>-80.82480681029648</v>
+      </c>
+      <c r="L243" t="n">
+        <v>723.7</v>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>Burglary/b&amp;e on Jul 17, 2026, 724 m from Southpark (700 GOVERNOR MORRISON ST). Status: Open. Case #20260717-0842-02 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>20260722-1722-03</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="n">
+        <v>46222.16666666666</v>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>All Other Thefts</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>23H</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>6600 FAIRVIEW RD</t>
+        </is>
+      </c>
+      <c r="J244" t="n">
+        <v>35.14845720336839</v>
+      </c>
+      <c r="K244" t="n">
+        <v>-80.83089079594687</v>
+      </c>
+      <c r="L244" t="n">
+        <v>383.9</v>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>All other thefts on Jul 19, 2026, 384 m from Southpark (6600 FAIRVIEW RD). Status: Open. Case #20260722-1722-03 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>20260707-1604-01</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="n">
+        <v>46205.16666666666</v>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>All Other Offenses</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>90Z</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>6100 FAIRVIEW RD</t>
+        </is>
+      </c>
+      <c r="J245" t="n">
+        <v>35.15108488996929</v>
+      </c>
+      <c r="K245" t="n">
+        <v>-80.83828432277107</v>
+      </c>
+      <c r="L245" t="n">
+        <v>717.8</v>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 02, 2026, 718 m from Southpark (6100 FAIRVIEW RD). Status: Open. Case #20260707-1604-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>20260713-1143-00</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="n">
+        <v>46216.16666666666</v>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J246" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K246" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L246" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 13, 2026, 179 m from Southpark (4400 SHARON RD). Status: Cleared by Arrest by Another Agency. Case #20260713-1143-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>20260726-0550-00</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="n">
+        <v>46228.16666666666</v>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Theft From Motor Vehicle</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>23F</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>6700 FAIRVIEW RD</t>
+        </is>
+      </c>
+      <c r="J247" t="n">
+        <v>35.1479657453291</v>
+      </c>
+      <c r="K247" t="n">
+        <v>-80.82922688152722</v>
+      </c>
+      <c r="L247" t="n">
+        <v>450.4</v>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>Theft from motor vehicle on Jul 25, 2026, 450 m from Southpark (6700 FAIRVIEW RD). Status: Open. Case #20260726-0550-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>20260709-1333-01</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="n">
+        <v>46212.16666666666</v>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>All Other Offenses</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>90Z</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>6500 FAIRVIEW RD</t>
+        </is>
+      </c>
+      <c r="J248" t="n">
+        <v>35.14920456105875</v>
+      </c>
+      <c r="K248" t="n">
+        <v>-80.83307576079913</v>
+      </c>
+      <c r="L248" t="n">
+        <v>382.3</v>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 09, 2026, 382 m from Southpark (6500 FAIRVIEW RD). Status: Open. Case #20260709-1333-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>20260725-0853-00</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="n">
+        <v>46228.16666666666</v>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Aggravated Assault</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>13A</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>5700 CARNEGIE BV</t>
+        </is>
+      </c>
+      <c r="J249" t="n">
+        <v>35.15368289092867</v>
+      </c>
+      <c r="K249" t="n">
+        <v>-80.8398453262274</v>
+      </c>
+      <c r="L249" t="n">
+        <v>877.1</v>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>Aggravated assault on Jul 25, 2026, 877 m from Southpark (5700 CARNEGIE BV). Status: Open. Case #20260725-0853-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>20260714-1056-01</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="n">
+        <v>46217.16666666666</v>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J250" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K250" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L250" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 14, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260714-1056-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>20260720-1826-04</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="n">
+        <v>46221.16666666666</v>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>All Other Thefts</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>23H</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J251" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K251" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L251" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>All other thefts on Jul 18, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260720-1826-04 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>20260722-1446-02</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="n">
+        <v>46205.16666666666</v>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>All Other Thefts</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>23H</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J252" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K252" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L252" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>All other thefts on Jul 02, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260722-1446-02 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>20260720-2018-00</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="n">
+        <v>46223.16666666666</v>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Intimidation</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>13C</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>1800 ROXBOROUGH RD</t>
+        </is>
+      </c>
+      <c r="J253" t="n">
+        <v>35.15693620600955</v>
+      </c>
+      <c r="K253" t="n">
+        <v>-80.8291972833448</v>
+      </c>
+      <c r="L253" t="n">
+        <v>572.5</v>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>Intimidation on Jul 20, 2026, 573 m from Southpark (1800 ROXBOROUGH RD). Status: Open. Case #20260720-2018-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>20260722-2105-02</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="n">
+        <v>46225.16666666666</v>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Driving Under The Influence</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>90D</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>5700 CARNEGIE BV</t>
+        </is>
+      </c>
+      <c r="J254" t="n">
+        <v>35.15368289092867</v>
+      </c>
+      <c r="K254" t="n">
+        <v>-80.8398453262274</v>
+      </c>
+      <c r="L254" t="n">
+        <v>877.1</v>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>Driving under the influence on Jul 22, 2026, 877 m from Southpark (5700 CARNEGIE BV). Status: Open. Case #20260722-2105-02 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>20260713-1652-03</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="n">
+        <v>46216.16666666666</v>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Theft of Motor Vehicle Parts from Vehicle</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>23G</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>4300 BARCLAY DOWNS DR</t>
+        </is>
+      </c>
+      <c r="J255" t="n">
+        <v>35.1559228958258</v>
+      </c>
+      <c r="K255" t="n">
+        <v>-80.83621502215044</v>
+      </c>
+      <c r="L255" t="n">
+        <v>689.7</v>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>Theft of motor vehicle parts from vehicle on Jul 13, 2026, 690 m from Southpark (4300 BARCLAY DOWNS DR). Status: Open. Case #20260713-1652-03 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>20260718-1206-03</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="n">
+        <v>46221.16666666666</v>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>6600 CARNEGIE BV</t>
+        </is>
+      </c>
+      <c r="J256" t="n">
+        <v>35.15368303665573</v>
+      </c>
+      <c r="K256" t="n">
+        <v>-80.82860898176955</v>
+      </c>
+      <c r="L256" t="n">
+        <v>260.3</v>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 18, 2026, 260 m from Southpark (6600 CARNEGIE BV). Status: Open. Case #20260718-1206-03 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>20260710-0852-00</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="n">
+        <v>46212.16666666666</v>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Sudden/Natural Death Investigation</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>802</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>6000 PIEDMONT ROW DR S</t>
+        </is>
+      </c>
+      <c r="J257" t="n">
+        <v>35.14895379386067</v>
+      </c>
+      <c r="K257" t="n">
+        <v>-80.83963153088133</v>
+      </c>
+      <c r="L257" t="n">
+        <v>896.3</v>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>Sudden/natural death investigation on Jul 09, 2026, 896 m from Southpark (6000 PIEDMONT ROW DR S). Status: Exceptionally Cleared. Case #20260710-0852-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>20260717-2031-00</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="n">
+        <v>46220.16666666666</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Motor Vehicle Theft</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J258" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K258" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L258" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>Motor vehicle theft on Jul 17, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260717-2031-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>20260723-1057-02</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="n">
+        <v>46225.16666666666</v>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Wire Fraud</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>26E</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>6200 FAIRVIEW RD</t>
+        </is>
+      </c>
+      <c r="J259" t="n">
+        <v>35.15078706372375</v>
+      </c>
+      <c r="K259" t="n">
+        <v>-80.8369057357377</v>
+      </c>
+      <c r="L259" t="n">
+        <v>599.6</v>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>Wire fraud on Jul 22, 2026, 600 m from Southpark (6200 FAIRVIEW RD). Status: Open. Case #20260723-1057-02 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>20260705-1411-00</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="n">
+        <v>46206.16666666666</v>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Other Unlisted Non-Criminal</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J260" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K260" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L260" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>Other unlisted non-criminal on Jul 03, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260705-1411-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>20260711-1305-00</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="n">
+        <v>46213.16666666666</v>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J261" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K261" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L261" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 10, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260711-1305-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>20260724-0557-00</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="n">
+        <v>46226.16666666666</v>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Burglary/B&amp;E</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>700 GOVERNOR MORRISON ST</t>
+        </is>
+      </c>
+      <c r="J262" t="n">
+        <v>35.15648042297118</v>
+      </c>
+      <c r="K262" t="n">
+        <v>-80.82480681029648</v>
+      </c>
+      <c r="L262" t="n">
+        <v>723.7</v>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>Burglary/b&amp;e on Jul 23, 2026, 724 m from Southpark (700 GOVERNOR MORRISON ST). Status: Open. Case #20260724-0557-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>20260713-1439-01</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="n">
+        <v>46215.16666666666</v>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>All Other Thefts</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>23H</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>5700 CARNEGIE BV</t>
+        </is>
+      </c>
+      <c r="J263" t="n">
+        <v>35.15368289092867</v>
+      </c>
+      <c r="K263" t="n">
+        <v>-80.8398453262274</v>
+      </c>
+      <c r="L263" t="n">
+        <v>877.1</v>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>All other thefts on Jul 12, 2026, 877 m from Southpark (5700 CARNEGIE BV). Status: Open. Case #20260713-1439-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>20260719-1634-00</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="n">
+        <v>46221.16666666666</v>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Credit Card/Teller Fraud</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>26B</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>5500 CARNEGIE BV</t>
+        </is>
+      </c>
+      <c r="J264" t="n">
+        <v>35.15375121029781</v>
+      </c>
+      <c r="K264" t="n">
+        <v>-80.83607576012871</v>
+      </c>
+      <c r="L264" t="n">
+        <v>551.7</v>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>Credit card/teller fraud on Jul 18, 2026, 552 m from Southpark (5500 CARNEGIE BV). Status: Open. Case #20260719-1634-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>20260717-2357-03</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="n">
+        <v>46219.16666666666</v>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Theft From Building</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>23D</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>4800 ASHLEY PARK LN</t>
+        </is>
+      </c>
+      <c r="J265" t="n">
+        <v>35.1479657453291</v>
+      </c>
+      <c r="K265" t="n">
+        <v>-80.82922688152722</v>
+      </c>
+      <c r="L265" t="n">
+        <v>450.4</v>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>Theft from building on Jul 16, 2026, 450 m from Southpark (4800 ASHLEY PARK LN). Status: Open. Case #20260717-2357-03 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>20260722-2044-03</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="n">
+        <v>46225.16666666666</v>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>All Other Offenses</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>90Z</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>6100 FAIRVIEW RD</t>
+        </is>
+      </c>
+      <c r="J266" t="n">
+        <v>35.15108488996929</v>
+      </c>
+      <c r="K266" t="n">
+        <v>-80.83828432277107</v>
+      </c>
+      <c r="L266" t="n">
+        <v>717.8</v>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 22, 2026, 718 m from Southpark (6100 FAIRVIEW RD). Status: Open. Case #20260722-2044-03 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>20260718-1425-00</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="n">
+        <v>46221.16666666666</v>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>All Other Offenses</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>90Z</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>4800 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J267" t="n">
+        <v>35.14644420018161</v>
+      </c>
+      <c r="K267" t="n">
+        <v>-80.83188614721075</v>
+      </c>
+      <c r="L267" t="n">
+        <v>619.5</v>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 18, 2026, 620 m from Southpark (4800 SHARON RD). Status: Open. Case #20260718-1425-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>20260718-1642-00</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="n">
+        <v>46221.16666666666</v>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Other Unlisted Non-Criminal</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>4800 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J268" t="n">
+        <v>35.14644420018161</v>
+      </c>
+      <c r="K268" t="n">
+        <v>-80.83188614721075</v>
+      </c>
+      <c r="L268" t="n">
+        <v>619.5</v>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>Other unlisted non-criminal on Jul 18, 2026, 620 m from Southpark (4800 SHARON RD). Status: Exceptionally Cleared. Case #20260718-1642-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>20260726-0657-00</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="n">
+        <v>46228.16666666666</v>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Theft From Motor Vehicle</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>23F</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>5500 CARNEGIE BV</t>
+        </is>
+      </c>
+      <c r="J269" t="n">
+        <v>35.15375121029781</v>
+      </c>
+      <c r="K269" t="n">
+        <v>-80.83607576012871</v>
+      </c>
+      <c r="L269" t="n">
+        <v>551.7</v>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>Theft from motor vehicle on Jul 25, 2026, 552 m from Southpark (5500 CARNEGIE BV). Status: Open. Case #20260726-0657-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>20260720-1107-04</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="n">
+        <v>46217.16666666666</v>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Other Unlisted Non-Criminal</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J270" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K270" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L270" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>Other unlisted non-criminal on Jul 14, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260720-1107-04 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>20260725-1348-05</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="n">
+        <v>46228.16666666666</v>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J271" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K271" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L271" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 25, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260725-1348-05 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>20260729-1053-01</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="n">
+        <v>46229.16666666666</v>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>All Other Thefts</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>23H</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>4500 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J272" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K272" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L272" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>All other thefts on Jul 26, 2026, 179 m from Southpark (4500 SHARON RD). Status: Open. Case #20260729-1053-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>20260706-0134-00</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="n">
+        <v>46209.16666666666</v>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>6500 FAIRVIEW RD</t>
+        </is>
+      </c>
+      <c r="J273" t="n">
+        <v>35.14920456105875</v>
+      </c>
+      <c r="K273" t="n">
+        <v>-80.83307576079913</v>
+      </c>
+      <c r="L273" t="n">
+        <v>382.3</v>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 06, 2026, 382 m from Southpark (6500 FAIRVIEW RD). Status: Open. Case #20260706-0134-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>20260727-1824-00</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="n">
+        <v>46229.16666666666</v>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J274" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K274" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L274" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 26, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260727-1824-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>20260727-1945-02</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="n">
+        <v>46228.16666666666</v>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J275" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K275" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L275" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 25, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260727-1945-02 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>20260709-0641-01</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="n">
+        <v>46211.16666666666</v>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J276" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K276" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L276" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 08, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260709-0641-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>20260722-0920-00</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="n">
+        <v>46225.16666666666</v>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Simple Assault</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>13B</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>5300 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J277" t="n">
+        <v>35.14420159566059</v>
+      </c>
+      <c r="K277" t="n">
+        <v>-80.83298000600156</v>
+      </c>
+      <c r="L277" t="n">
+        <v>885.4</v>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>Simple assault on Jul 22, 2026, 885 m from Southpark (5300 SHARON RD). Status: Exceptionally Cleared. Case #20260722-0920-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>20260704-1737-00</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="n">
+        <v>46207.16666666666</v>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Credit Card/Teller Fraud</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>26B</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>6600 FAIRVIEW RD</t>
+        </is>
+      </c>
+      <c r="J278" t="n">
+        <v>35.14845720336839</v>
+      </c>
+      <c r="K278" t="n">
+        <v>-80.83089079594687</v>
+      </c>
+      <c r="L278" t="n">
+        <v>383.9</v>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>Credit card/teller fraud on Jul 04, 2026, 384 m from Southpark (6600 FAIRVIEW RD). Status: Open. Case #20260704-1737-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>20260723-0938-05</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="n">
+        <v>46218.16666666666</v>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Aggravated Assault</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>13A</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>6600 FAIRVIEW RD</t>
+        </is>
+      </c>
+      <c r="J279" t="n">
+        <v>35.14845720336839</v>
+      </c>
+      <c r="K279" t="n">
+        <v>-80.83089079594687</v>
+      </c>
+      <c r="L279" t="n">
+        <v>383.9</v>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>Aggravated assault on Jul 15, 2026, 384 m from Southpark (6600 FAIRVIEW RD). Status: Open. Case #20260723-0938-05 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>20260714-2130-05</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="n">
+        <v>46217.16666666666</v>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Other Unlisted Non-Criminal</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J280" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K280" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L280" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>Other unlisted non-criminal on Jul 14, 2026, 179 m from Southpark (4400 SHARON RD). Status: Unfounded. Case #20260714-2130-05 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>20260722-1448-00</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="n">
+        <v>46225.16666666666</v>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>False Pretenses/Swindle</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>26A</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>3900 COLONY RD</t>
+        </is>
+      </c>
+      <c r="J281" t="n">
+        <v>35.15489615849495</v>
+      </c>
+      <c r="K281" t="n">
+        <v>-80.82453042173836</v>
+      </c>
+      <c r="L281" t="n">
+        <v>633.6</v>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>False pretenses/swindle on Jul 22, 2026, 634 m from Southpark (3900 COLONY RD). Status: Unfounded. Case #20260722-1448-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>20260724-1649-01</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="n">
+        <v>46227.16666666666</v>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Peeping Tom</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>90H</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J282" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K282" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L282" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>Peeping tom on Jul 24, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260724-1649-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>20260706-1114-01</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="n">
+        <v>46209.16666666666</v>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>4000 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J283" t="n">
+        <v>35.15567429979806</v>
+      </c>
+      <c r="K283" t="n">
+        <v>-80.82377486075073</v>
+      </c>
+      <c r="L283" t="n">
+        <v>738.5</v>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 06, 2026, 738 m from Southpark (4000 SHARON RD). Status: Open. Case #20260706-1114-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>20260703-1606-03</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="n">
+        <v>46206.16666666666</v>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J284" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K284" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L284" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 03, 2026, 179 m from Southpark (4400 SHARON RD). Status: Cleared by Arrest. Case #20260703-1606-03 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>20260726-1824-01</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="n">
+        <v>46229.16666666666</v>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>All Other Offenses</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>90Z</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J285" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K285" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L285" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 26, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260726-1824-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>20260706-1306-00</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="n">
+        <v>46209.16666666666</v>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>6600 CARNEGIE BV</t>
+        </is>
+      </c>
+      <c r="J286" t="n">
+        <v>35.15368303665573</v>
+      </c>
+      <c r="K286" t="n">
+        <v>-80.82860898176955</v>
+      </c>
+      <c r="L286" t="n">
+        <v>260.3</v>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 06, 2026, 260 m from Southpark (6600 CARNEGIE BV). Status: Open. Case #20260706-1306-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>20260710-1651-01</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="n">
+        <v>46213.16666666666</v>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J287" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K287" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L287" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 10, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260710-1651-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>20260721-1054-00</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="n">
+        <v>46224.16666666666</v>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Theft From Coin-Operated Machine Or Device</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>23E</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>6100 FAIRVIEW RD</t>
+        </is>
+      </c>
+      <c r="J288" t="n">
+        <v>35.15108488996929</v>
+      </c>
+      <c r="K288" t="n">
+        <v>-80.83828432277107</v>
+      </c>
+      <c r="L288" t="n">
+        <v>717.8</v>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>Theft from coin-operated machine or device on Jul 21, 2026, 718 m from Southpark (6100 FAIRVIEW RD). Status: Open. Case #20260721-1054-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>20260706-1754-00</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="n">
+        <v>46209.16666666666</v>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>False Pretenses/Swindle</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>26A</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>6800 LOUISBURG SQUARE LN</t>
+        </is>
+      </c>
+      <c r="J289" t="n">
+        <v>35.14541141958989</v>
+      </c>
+      <c r="K289" t="n">
+        <v>-80.83239492414555</v>
+      </c>
+      <c r="L289" t="n">
+        <v>741.8</v>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>False pretenses/swindle on Jul 06, 2026, 742 m from Southpark (6800 LOUISBURG SQUARE LN). Status: Open. Case #20260706-1754-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>20260724-0616-01</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="n">
+        <v>46226.16666666666</v>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Burglary/B&amp;E</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>700 GOVERNOR MORRISON ST</t>
+        </is>
+      </c>
+      <c r="J290" t="n">
+        <v>35.15648042297118</v>
+      </c>
+      <c r="K290" t="n">
+        <v>-80.82480681029648</v>
+      </c>
+      <c r="L290" t="n">
+        <v>723.7</v>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>Burglary/b&amp;e on Jul 23, 2026, 724 m from Southpark (700 GOVERNOR MORRISON ST). Status: Open. Case #20260724-0616-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>20260716-1025-00</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="n">
+        <v>46216.16666666666</v>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>All Other Thefts</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>23H</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>2200 REXFORD RD</t>
+        </is>
+      </c>
+      <c r="J291" t="n">
+        <v>35.15737066178394</v>
+      </c>
+      <c r="K291" t="n">
+        <v>-80.82972570752082</v>
+      </c>
+      <c r="L291" t="n">
+        <v>612.9</v>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>All other thefts on Jul 13, 2026, 613 m from Southpark (2200 REXFORD RD). Status: Open. Case #20260716-1025-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>20260707-0323-00</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="n">
+        <v>46210.16666666666</v>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>6600 CARNEGIE BV</t>
+        </is>
+      </c>
+      <c r="J292" t="n">
+        <v>35.15368303665573</v>
+      </c>
+      <c r="K292" t="n">
+        <v>-80.82860898176955</v>
+      </c>
+      <c r="L292" t="n">
+        <v>260.3</v>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 07, 2026, 260 m from Southpark (6600 CARNEGIE BV). Status: Open. Case #20260707-0323-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>20260728-1214-00</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="n">
+        <v>46220.16666666666</v>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>All Other Thefts</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>23H</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>1800 ROXBOROUGH RD</t>
+        </is>
+      </c>
+      <c r="J293" t="n">
+        <v>35.15693620600955</v>
+      </c>
+      <c r="K293" t="n">
+        <v>-80.8291972833448</v>
+      </c>
+      <c r="L293" t="n">
+        <v>572.5</v>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>All other thefts on Jul 17, 2026, 573 m from Southpark (1800 ROXBOROUGH RD). Status: Open. Case #20260728-1214-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>20260707-2104-01</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="n">
+        <v>46210.16666666666</v>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Other Unlisted Non-Criminal</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>5700 CARNEGIE BV</t>
+        </is>
+      </c>
+      <c r="J294" t="n">
+        <v>35.15368289092867</v>
+      </c>
+      <c r="K294" t="n">
+        <v>-80.8398453262274</v>
+      </c>
+      <c r="L294" t="n">
+        <v>877.1</v>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>Other unlisted non-criminal on Jul 07, 2026, 877 m from Southpark (5700 CARNEGIE BV). Status: Exceptionally Cleared. Case #20260707-2104-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>20260709-2041-01</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="n">
+        <v>46212.16666666666</v>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J295" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K295" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L295" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 09, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260709-2041-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>20260712-2051-00</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="n">
+        <v>46215.16666666666</v>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Intimidation</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>13C</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>6700 PHILLIPS PLACE CT</t>
+        </is>
+      </c>
+      <c r="J296" t="n">
+        <v>35.14659329285514</v>
+      </c>
+      <c r="K296" t="n">
+        <v>-80.8278477116156</v>
+      </c>
+      <c r="L296" t="n">
+        <v>634.8</v>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>Intimidation on Jul 12, 2026, 635 m from Southpark (6700 PHILLIPS PLACE CT). Status: Open. Case #20260712-2051-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>20260718-2022-01</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="n">
+        <v>46221.16666666666</v>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J297" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K297" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L297" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 18, 2026, 179 m from Southpark (4400 SHARON RD). Status: Cleared by Arrest. Case #20260718-2022-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>20260728-1922-01</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="n">
+        <v>46231.16666666666</v>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J298" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K298" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L298" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1922-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>20260717-1828-00</t>
+        </is>
+      </c>
+      <c r="E299" s="2" t="n">
+        <v>46220.16666666666</v>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J299" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K299" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L299" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 17, 2026, 179 m from Southpark (4400 SHARON RD). Status: Cleared by Arrest. Case #20260717-1828-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>20260713-2148-07</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="n">
+        <v>46209.16666666666</v>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>Damage/Vandalism Of Property</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>5700 CARNEGIE BV</t>
+        </is>
+      </c>
+      <c r="J300" t="n">
+        <v>35.15368289092867</v>
+      </c>
+      <c r="K300" t="n">
+        <v>-80.8398453262274</v>
+      </c>
+      <c r="L300" t="n">
+        <v>877.1</v>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>Damage/vandalism of property on Jul 06, 2026, 877 m from Southpark (5700 CARNEGIE BV). Status: Open. Case #20260713-2148-07 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>20260717-1943-01</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="n">
+        <v>46220.16666666666</v>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J301" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K301" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L301" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 17, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260717-1943-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>20260728-1130-01</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="n">
+        <v>46231.16666666666</v>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J302" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K302" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L302" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1130-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>20260721-1528-01</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="n">
+        <v>46224.16666666666</v>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Other Unlisted Non-Criminal</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>6900 FAIRVIEW RD</t>
+        </is>
+      </c>
+      <c r="J303" t="n">
+        <v>35.14684118006692</v>
+      </c>
+      <c r="K303" t="n">
+        <v>-80.82544759809264</v>
+      </c>
+      <c r="L303" t="n">
+        <v>722.6</v>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>Other unlisted non-criminal on Jul 21, 2026, 723 m from Southpark (6900 FAIRVIEW RD). Status: Open. Case #20260721-1528-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>20260722-1544-00</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="n">
+        <v>46224.16666666666</v>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>4300 BARCLAY DOWNS DR</t>
+        </is>
+      </c>
+      <c r="J304" t="n">
+        <v>35.1559228958258</v>
+      </c>
+      <c r="K304" t="n">
+        <v>-80.83621502215044</v>
+      </c>
+      <c r="L304" t="n">
+        <v>689.7</v>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 21, 2026, 690 m from Southpark (4300 BARCLAY DOWNS DR). Status: Open. Case #20260722-1544-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>20260726-0952-00</t>
+        </is>
+      </c>
+      <c r="E305" s="2" t="n">
+        <v>46228.16666666666</v>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>All Other Offenses</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>90Z</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>700 GOVERNOR MORRISON ST</t>
+        </is>
+      </c>
+      <c r="J305" t="n">
+        <v>35.15648042297118</v>
+      </c>
+      <c r="K305" t="n">
+        <v>-80.82480681029648</v>
+      </c>
+      <c r="L305" t="n">
+        <v>723.7</v>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 25, 2026, 724 m from Southpark (700 GOVERNOR MORRISON ST). Status: Open. Case #20260726-0952-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>SOUTHPARK</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Southpark</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>SOUTHPARK:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>20260714-1103-04</t>
+        </is>
+      </c>
+      <c r="E306" s="2" t="n">
+        <v>46217.16666666666</v>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>Trespass Of Real Property</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>90J</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>6600 CARNEGIE BV</t>
+        </is>
+      </c>
+      <c r="J306" t="n">
+        <v>35.15368303665573</v>
+      </c>
+      <c r="K306" t="n">
+        <v>-80.82860898176955</v>
+      </c>
+      <c r="L306" t="n">
+        <v>260.3</v>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>Trespass of real property on Jul 14, 2026, 260 m from Southpark (6600 CARNEGIE BV). Status: Open. Case #20260714-1103-04 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>20260714-1049-03</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="n">
+        <v>46217.16666666666</v>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>False Pretenses/Swindle</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>26A</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>8900 RACHEL FREEMAN WY</t>
+        </is>
+      </c>
+      <c r="J307" t="n">
+        <v>35.162796991439</v>
+      </c>
+      <c r="K307" t="n">
+        <v>-80.97457621910608</v>
+      </c>
+      <c r="L307" t="n">
+        <v>755.9</v>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>False pretenses/swindle on Jul 14, 2026, 756 m from Charlotte Premium Outlets (8900 RACHEL FREEMAN WY). Status: Open. Case #20260714-1049-03 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>20260723-0724-00</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="n">
+        <v>46226.16666666666</v>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>Theft From Building</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>23D</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>9300 STEELE CREEK RD</t>
+        </is>
+      </c>
+      <c r="J308" t="n">
+        <v>35.16373788000934</v>
+      </c>
+      <c r="K308" t="n">
+        <v>-80.9686185584536</v>
+      </c>
+      <c r="L308" t="n">
+        <v>521.4</v>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>Theft from building on Jul 23, 2026, 521 m from Charlotte Premium Outlets (9300 STEELE CREEK RD). Status: Open. Case #20260723-0724-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>20260713-2349-01</t>
+        </is>
+      </c>
+      <c r="E309" s="2" t="n">
+        <v>46216.16666666666</v>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Intimidation</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>13C</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>9300 ROBERT IRWIN DR</t>
+        </is>
+      </c>
+      <c r="J309" t="n">
+        <v>35.16491450474356</v>
+      </c>
+      <c r="K309" t="n">
+        <v>-80.97095619384244</v>
+      </c>
+      <c r="L309" t="n">
+        <v>395.7</v>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>Intimidation on Jul 13, 2026, 396 m from Charlotte Premium Outlets (9300 ROBERT IRWIN DR). Status: Exceptionally Cleared. Case #20260713-2349-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>20260717-1629-01</t>
+        </is>
+      </c>
+      <c r="E310" s="2" t="n">
+        <v>46220.16666666666</v>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>All Other Offenses</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>90Z</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>5600 KELTONWOOD RD</t>
+        </is>
+      </c>
+      <c r="J310" t="n">
+        <v>35.16655081611235</v>
+      </c>
+      <c r="K310" t="n">
+        <v>-80.97476086867614</v>
+      </c>
+      <c r="L310" t="n">
+        <v>496.6</v>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 17, 2026, 497 m from Charlotte Premium Outlets (5600 KELTONWOOD RD). Status: Open. Case #20260717-1629-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>20260725-1130-01</t>
+        </is>
+      </c>
+      <c r="E311" s="2" t="n">
+        <v>46226.16666666666</v>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>5400 NEW FASHION WY</t>
+        </is>
+      </c>
+      <c r="J311" t="n">
+        <v>35.1675584335673</v>
+      </c>
+      <c r="K311" t="n">
+        <v>-80.97212792042299</v>
+      </c>
+      <c r="L311" t="n">
+        <v>232.6</v>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 23, 2026, 233 m from Charlotte Premium Outlets (5400 NEW FASHION WY). Status: Open. Case #20260725-1130-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>20260721-1959-02</t>
+        </is>
+      </c>
+      <c r="E312" s="2" t="n">
+        <v>46224.16666666666</v>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Public Accident</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>807</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>13500 RIGSBY RD</t>
+        </is>
+      </c>
+      <c r="J312" t="n">
+        <v>35.16332668510686</v>
+      </c>
+      <c r="K312" t="n">
+        <v>-80.96669770382859</v>
+      </c>
+      <c r="L312" t="n">
+        <v>622.2</v>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>Public accident on Jul 21, 2026, 622 m from Charlotte Premium Outlets (13500 RIGSBY RD). Status: Open. Case #20260721-1959-02 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>20260710-1339-00</t>
+        </is>
+      </c>
+      <c r="E313" s="2" t="n">
+        <v>46212.16666666666</v>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>False Pretenses/Swindle</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>26A</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>5600 GARROW GLEN RD</t>
+        </is>
+      </c>
+      <c r="J313" t="n">
+        <v>35.16539493677813</v>
+      </c>
+      <c r="K313" t="n">
+        <v>-80.97704544416381</v>
+      </c>
+      <c r="L313" t="n">
+        <v>739.2</v>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>False pretenses/swindle on Jul 09, 2026, 739 m from Charlotte Premium Outlets (5600 GARROW GLEN RD). Status: Open. Case #20260710-1339-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>20260718-1639-02</t>
+        </is>
+      </c>
+      <c r="E314" s="2" t="n">
+        <v>46221.16666666666</v>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>All Other Offenses</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>90Z</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>5400 NEW FASHION WY</t>
+        </is>
+      </c>
+      <c r="J314" t="n">
+        <v>35.1675584335673</v>
+      </c>
+      <c r="K314" t="n">
+        <v>-80.97212792042299</v>
+      </c>
+      <c r="L314" t="n">
+        <v>232.6</v>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 18, 2026, 233 m from Charlotte Premium Outlets (5400 NEW FASHION WY). Status: Open. Case #20260718-1639-02 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>20260721-1652-01</t>
+        </is>
+      </c>
+      <c r="E315" s="2" t="n">
+        <v>46224.16666666666</v>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>5400 NEW FASHION WY</t>
+        </is>
+      </c>
+      <c r="J315" t="n">
+        <v>35.1675584335673</v>
+      </c>
+      <c r="K315" t="n">
+        <v>-80.97212792042299</v>
+      </c>
+      <c r="L315" t="n">
+        <v>232.6</v>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 21, 2026, 233 m from Charlotte Premium Outlets (5400 NEW FASHION WY). Status: Open. Case #20260721-1652-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>20260717-1504-02</t>
+        </is>
+      </c>
+      <c r="E316" s="2" t="n">
+        <v>46210.16666666666</v>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>4800 SHOPTON RD</t>
+        </is>
+      </c>
+      <c r="J316" t="n">
+        <v>35.17263853493539</v>
+      </c>
+      <c r="K316" t="n">
+        <v>-80.96174124648307</v>
+      </c>
+      <c r="L316" t="n">
+        <v>871.3</v>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 07, 2026, 871 m from Charlotte Premium Outlets (4800 SHOPTON RD). Status: Open. Case #20260717-1504-02 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>20260723-1659-01</t>
+        </is>
+      </c>
+      <c r="E317" s="2" t="n">
+        <v>46226.16666666666</v>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>5500 NEW FASHION WY</t>
+        </is>
+      </c>
+      <c r="J317" t="n">
+        <v>35.16919484075596</v>
+      </c>
+      <c r="K317" t="n">
+        <v>-80.9710429684888</v>
+      </c>
+      <c r="L317" t="n">
+        <v>151.4</v>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 23, 2026, 151 m from Charlotte Premium Outlets (5500 NEW FASHION WY). Status: Open. Case #20260723-1659-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>20260721-1452-01</t>
+        </is>
+      </c>
+      <c r="E318" s="2" t="n">
+        <v>46221.16666666666</v>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>5400 NEW FASHION WY</t>
+        </is>
+      </c>
+      <c r="J318" t="n">
+        <v>35.1675584335673</v>
+      </c>
+      <c r="K318" t="n">
+        <v>-80.97212792042299</v>
+      </c>
+      <c r="L318" t="n">
+        <v>232.6</v>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 18, 2026, 233 m from Charlotte Premium Outlets (5400 NEW FASHION WY). Status: Open. Case #20260721-1452-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>20260725-1934-03</t>
+        </is>
+      </c>
+      <c r="E319" s="2" t="n">
+        <v>46228.16666666666</v>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>All Other Thefts</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>23H</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>4900 TROJAN DR</t>
+        </is>
+      </c>
+      <c r="J319" t="n">
+        <v>35.16474336144204</v>
+      </c>
+      <c r="K319" t="n">
+        <v>-80.96762879799847</v>
+      </c>
+      <c r="L319" t="n">
+        <v>443.5</v>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>All other thefts on Jul 25, 2026, 444 m from Charlotte Premium Outlets (4900 TROJAN DR). Status: Open. Case #20260725-1934-03 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>20260722-2124-02</t>
+        </is>
+      </c>
+      <c r="E320" s="2" t="n">
+        <v>46225.16666666666</v>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Simple Assault</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>13B</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>9400 STEELE CREEK RD</t>
+        </is>
+      </c>
+      <c r="J320" t="n">
+        <v>35.16250902126527</v>
+      </c>
+      <c r="K320" t="n">
+        <v>-80.96982377170991</v>
+      </c>
+      <c r="L320" t="n">
+        <v>647.8</v>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>Simple assault on Jul 22, 2026, 648 m from Charlotte Premium Outlets (9400 STEELE CREEK RD). Status: Open. Case #20260722-2124-02 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>20260729-1434-02</t>
+        </is>
+      </c>
+      <c r="E321" s="2" t="n">
+        <v>46231.16666666666</v>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Damage/Vandalism Of Property</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>5600 KELTONWOOD RD</t>
+        </is>
+      </c>
+      <c r="J321" t="n">
+        <v>35.16655081611235</v>
+      </c>
+      <c r="K321" t="n">
+        <v>-80.97476086867614</v>
+      </c>
+      <c r="L321" t="n">
+        <v>496.6</v>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>Damage/vandalism of property on Jul 28, 2026, 497 m from Charlotte Premium Outlets (5600 KELTONWOOD RD). Status: Open. Case #20260729-1434-02 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>20260715-1042-04</t>
+        </is>
+      </c>
+      <c r="E322" s="2" t="n">
+        <v>46216.16666666666</v>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Theft of Motor Vehicle Parts from Vehicle</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>23G</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>5600 KELTONWOOD RD</t>
+        </is>
+      </c>
+      <c r="J322" t="n">
+        <v>35.16655081611235</v>
+      </c>
+      <c r="K322" t="n">
+        <v>-80.97476086867614</v>
+      </c>
+      <c r="L322" t="n">
+        <v>496.6</v>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>Theft of motor vehicle parts from vehicle on Jul 13, 2026, 497 m from Charlotte Premium Outlets (5600 KELTONWOOD RD). Status: Open. Case #20260715-1042-04 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>20260707-1238-01</t>
+        </is>
+      </c>
+      <c r="E323" s="2" t="n">
+        <v>46209.16666666666</v>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>5400 NEW FASHION WY</t>
+        </is>
+      </c>
+      <c r="J323" t="n">
+        <v>35.1675584335673</v>
+      </c>
+      <c r="K323" t="n">
+        <v>-80.97212792042299</v>
+      </c>
+      <c r="L323" t="n">
+        <v>232.6</v>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 06, 2026, 233 m from Charlotte Premium Outlets (5400 NEW FASHION WY). Status: Open. Case #20260707-1238-01 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>20260715-2015-02</t>
+        </is>
+      </c>
+      <c r="E324" s="2" t="n">
+        <v>46218.16666666666</v>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>5400 NEW FASHION WY</t>
+        </is>
+      </c>
+      <c r="J324" t="n">
+        <v>35.1675584335673</v>
+      </c>
+      <c r="K324" t="n">
+        <v>-80.97212792042299</v>
+      </c>
+      <c r="L324" t="n">
+        <v>232.6</v>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 15, 2026, 233 m from Charlotte Premium Outlets (5400 NEW FASHION WY). Status: Open. Case #20260715-2015-02 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>20260720-2155-00</t>
+        </is>
+      </c>
+      <c r="E325" s="2" t="n">
+        <v>46222.16666666666</v>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>All Other Thefts</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>23H</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>4900 TROJAN DR</t>
+        </is>
+      </c>
+      <c r="J325" t="n">
+        <v>35.16474336144204</v>
+      </c>
+      <c r="K325" t="n">
+        <v>-80.96762879799847</v>
+      </c>
+      <c r="L325" t="n">
+        <v>443.5</v>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>All other thefts on Jul 19, 2026, 444 m from Charlotte Premium Outlets (4900 TROJAN DR). Status: Open. Case #20260720-2155-00 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>20260721-1210-03</t>
+        </is>
+      </c>
+      <c r="E326" s="2" t="n">
+        <v>46219.16666666666</v>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>5500 NEW FASHION WY</t>
+        </is>
+      </c>
+      <c r="J326" t="n">
+        <v>35.16919484075596</v>
+      </c>
+      <c r="K326" t="n">
+        <v>-80.9710429684888</v>
+      </c>
+      <c r="L326" t="n">
+        <v>151.4</v>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 16, 2026, 151 m from Charlotte Premium Outlets (5500 NEW FASHION WY). Status: Open. Case #20260721-1210-03 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>20260715-0940-02</t>
+        </is>
+      </c>
+      <c r="E327" s="2" t="n">
+        <v>46218.16666666666</v>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>All Other Thefts</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>23H</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>9300 STEELE CREEK RD</t>
+        </is>
+      </c>
+      <c r="J327" t="n">
+        <v>35.16373788000934</v>
+      </c>
+      <c r="K327" t="n">
+        <v>-80.9686185584536</v>
+      </c>
+      <c r="L327" t="n">
+        <v>521.4</v>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>All other thefts on Jul 15, 2026, 521 m from Charlotte Premium Outlets (9300 STEELE CREEK RD). Status: Open. Case #20260715-0940-02 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>CHARLOTTE</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Charlotte Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>CHARLOTTE:CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>20260724-1333-02</t>
+        </is>
+      </c>
+      <c r="E328" s="2" t="n">
+        <v>46220.16666666666</v>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>5400 NEW FASHION WY</t>
+        </is>
+      </c>
+      <c r="J328" t="n">
+        <v>35.1675584335673</v>
+      </c>
+      <c r="K328" t="n">
+        <v>-80.97212792042299</v>
+      </c>
+      <c r="L328" t="n">
+        <v>232.6</v>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 17, 2026, 233 m from Charlotte Premium Outlets (5400 NEW FASHION WY). Status: Open. Case #20260724-1333-02 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M233"/>
+  <autoFilter ref="A1:M328"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16072,7 +21796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="51" customWidth="1" min="1" max="1"/>
@@ -16099,7 +21823,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-31 07:07:15.391218+00:00</t>
+          <t>2026-07-31 07:11:45.202134+00:00</t>
         </is>
       </c>
     </row>
@@ -16121,7 +21845,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-01 07:07:15.391218+00:00</t>
+          <t>2026-07-01 07:11:45.202134+00:00</t>
         </is>
       </c>
     </row>
@@ -16132,7 +21856,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>232</v>
+        <v>327</v>
       </c>
     </row>
     <row r="6">
@@ -16142,7 +21866,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -16217,8 +21941,44 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>source:SOUTHPARK/CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>OK fetched=73 truncated=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>source:CHARLOTTE/CMPD Incidents</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>OK fetched=22 truncated=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>source:ABQUP/Albuquerque PD Incidents</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>OK fetched=0 truncated=False</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B12"/>
+  <autoFilter ref="A1:B15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/latest/blotter_report.xlsx
+++ b/reports/latest/blotter_report.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Run Metadata" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$K$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Highlights'!$A$1:$M$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$87</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$18</definedName>
@@ -443,20 +443,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="57" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,45 +473,50 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>address</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>total</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>PROPERTY</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>QUALITY_OF_LIFE</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>OTHER</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>nearest_m</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>most_recent</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>truncated</t>
         </is>
@@ -529,11 +535,13 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>2200 Louisiana Boulevard Northeast Albuquerque NM 87110</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>OK</t>
         </is>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -547,9 +555,12 @@
       <c r="H2" t="n">
         <v>0</v>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="b">
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -566,31 +577,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>5000 South Arizona Mills Circle Tempe AZ 85282</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>16</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="F3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>6</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>2</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>6</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>14.7</v>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="K3" s="3" t="n">
         <v>46232.21041666667</v>
       </c>
-      <c r="K3" t="b">
+      <c r="L3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -607,11 +623,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>8500 Beverly Boulevard, Los Angeles CA 90048</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>OK</t>
         </is>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -625,9 +643,12 @@
       <c r="H4" t="n">
         <v>0</v>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="b">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -644,31 +665,36 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>5404 New Fashion Way Charlotte NC 28278</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>2</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>443.5</v>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="K5" s="3" t="n">
         <v>46231.16666666666</v>
       </c>
-      <c r="K5" t="b">
+      <c r="L5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -685,31 +711,36 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>3000 East 1st Avenue, Denver CO 80206</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>11</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="F6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>8</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>2</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>144.7</v>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="K6" s="3" t="n">
         <v>46231.83333333334</v>
       </c>
-      <c r="K6" t="b">
+      <c r="L6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -726,31 +757,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>2126 Abbott Martin Road, Nashville, TN 37215</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>7</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>0</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>4</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>3</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>191.2</v>
       </c>
-      <c r="J7" s="3" t="n">
+      <c r="K7" s="3" t="n">
         <v>46232.0625</v>
       </c>
-      <c r="K7" t="b">
+      <c r="L7" t="b">
         <v>0</v>
       </c>
     </row>
@@ -767,11 +803,13 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>2223 North West Shore Boulevard Tampa FL 33607</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>OK</t>
         </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -785,9 +823,12 @@
       <c r="H8" t="n">
         <v>0</v>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="b">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -802,13 +843,15 @@
           <t>Lenox Square</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3393 Peachtree Road Northeast Atlanta GA 30326</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>NO COVERAGE</t>
         </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -822,9 +865,12 @@
       <c r="H9" t="n">
         <v>0</v>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="b">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -841,31 +887,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>401 Northeast Northgate Way Seattle WA 98125</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>6</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="F10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>5</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
         <v>145.2</v>
       </c>
-      <c r="J10" s="3" t="n">
+      <c r="K10" s="3" t="n">
         <v>46232.82986111111</v>
       </c>
-      <c r="K10" t="b">
+      <c r="L10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -882,31 +933,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>433 Opry Mills Drive Nashville TN 37214</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>14</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>0</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>9</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>5</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>113.7</v>
       </c>
-      <c r="J11" s="3" t="n">
+      <c r="K11" s="3" t="n">
         <v>46231.92430555556</v>
       </c>
-      <c r="K11" t="b">
+      <c r="L11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -923,31 +979,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>4400 Sharon Road Charlotte NC 28211</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>13</v>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="F12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>9</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>3</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>178.9</v>
       </c>
-      <c r="J12" s="3" t="n">
+      <c r="K12" s="3" t="n">
         <v>46231.16666666666</v>
       </c>
-      <c r="K12" t="b">
+      <c r="L12" t="b">
         <v>0</v>
       </c>
     </row>
@@ -962,13 +1023,15 @@
           <t>The Domain</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>11410 Century Oaks Terrace Austin TX 78758</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>NO COVERAGE</t>
         </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -982,9 +1045,12 @@
       <c r="H13" t="n">
         <v>0</v>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="b">
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1001,36 +1067,41 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>7700 East Kellogg Wichita KS 67207</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>17</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>0</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>8</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>1</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>8</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>288.9</v>
       </c>
-      <c r="J14" s="3" t="n">
+      <c r="K14" s="3" t="n">
         <v>46233.63055555556</v>
       </c>
-      <c r="K14" t="b">
+      <c r="L14" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K14"/>
+  <autoFilter ref="A1:L14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7695,7 +7766,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-31 07:22:12.812075+00:00</t>
+          <t>2026-07-31 07:28:37.517868+00:00</t>
         </is>
       </c>
     </row>
@@ -7717,7 +7788,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-24 07:22:12.812075+00:00</t>
+          <t>2026-07-24 07:28:37.517868+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/latest/blotter_report.xlsx
+++ b/reports/latest/blotter_report.xlsx
@@ -572,7 +572,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>[13b] assault [dv] on Jul 27, 2026, 15 m from Arizona Mill (5XXX S ARIZONA MILLS CIR). Case #TE202675652          (use for a records request — full narratives are not published in open data).</t>
+          <t>[13b] assault [dv] on Jul 27, 2026, 15 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675652          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>[13b] assault on Jul 24, 2026, 15 m from Arizona Mill (5XXX S ARIZONA MILLS CIR). Case #TE202674783          (use for a records request — full narratives are not published in open data).</t>
+          <t>[13b] assault on Jul 24, 2026, 15 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202674783          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>[sc-0] trespass warning - private property on Jul 26, 2026, 262 m from Arizona Mill (5XXX S ARIZONA MILLS CIR). Case #TE202675399          (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] trespass warning - private property on Jul 26, 2026, 262 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675399          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>[240] motor vehicle theft on Jul 29, 2026, 316 m from Arizona Mill (5XXX S ARIZONA MILLS CIR). Case #TE202676101          (use for a records request — full narratives are not published in open data).</t>
+          <t>[240] motor vehicle theft on Jul 29, 2026, 316 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202676101          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>[sc-0] trespass warning - private property on Jul 28, 2026, 361 m from Arizona Mill (5XXX S ARIZONA MILLS CIR). Case #TE202676030          (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] trespass warning - private property on Jul 28, 2026, 361 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202676030          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6855,7 +6855,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>[13b] assault [dv] on Jul 27, 2026, 15 m from Arizona Mill (5XXX S ARIZONA MILLS CIR). Case #TE202675652          (use for a records request — full narratives are not published in open data).</t>
+          <t>[13b] assault [dv] on Jul 27, 2026, 15 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675652          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6910,7 +6910,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>[sc-0] info - information other (non-criminal) on Jul 25, 2026, 15 m from Arizona Mill (5XXX S ARIZONA MILLS CIR). Case #TE202674996          (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] info - information other (non-criminal) on Jul 25, 2026, 15 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202674996          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>[13b] assault on Jul 24, 2026, 15 m from Arizona Mill (5XXX S ARIZONA MILLS CIR). Case #TE202674783          (use for a records request — full narratives are not published in open data).</t>
+          <t>[13b] assault on Jul 24, 2026, 15 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202674783          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>[90j] trespassing on Jul 26, 2026, 69 m from Arizona Mill (5XXX S ARIZONA MILLS CIR). Case #TE202675415          (use for a records request — full narratives are not published in open data).</t>
+          <t>[90j] trespassing on Jul 26, 2026, 69 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675415          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7075,7 +7075,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>[sc-0] trespass warning - private property on Jul 26, 2026, 262 m from Arizona Mill (5XXX S ARIZONA MILLS CIR). Case #TE202675399          (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] trespass warning - private property on Jul 26, 2026, 262 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675399          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>[240] motor vehicle theft on Jul 29, 2026, 316 m from Arizona Mill (5XXX S ARIZONA MILLS CIR). Case #TE202676101          (use for a records request — full narratives are not published in open data).</t>
+          <t>[240] motor vehicle theft on Jul 29, 2026, 316 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202676101          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7185,7 +7185,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>[sc-0] trespass warning - private property on Jul 28, 2026, 361 m from Arizona Mill (5XXX S ARIZONA MILLS CIR). Case #TE202676030          (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] trespass warning - private property on Jul 28, 2026, 361 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202676030          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>[go-0] assist other agency on Jul 25, 2026, 517 m from Arizona Mill (4XXX S WENDLER DR). Case #TE202674893          (use for a records request — full narratives are not published in open data).</t>
+          <t>[go-0] assist other agency on Jul 25, 2026, 517 m from Arizona Mills (4XXX S WENDLER DR). Case #TE202674893          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7295,7 +7295,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>[sc-0] welfare check on Jul 27, 2026, 533 m from Arizona Mill (4XXX S DARROW DR). Case #TE202675649          (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] welfare check on Jul 27, 2026, 533 m from Arizona Mills (4XXX S DARROW DR). Case #TE202675649          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7350,7 +7350,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>[go-0] accident - hit and run on Jul 24, 2026, 641 m from Arizona Mill (BASELINE RD / S DARROW DR). Case #TE202674654          (use for a records request — full narratives are not published in open data).</t>
+          <t>[go-0] accident - hit and run on Jul 24, 2026, 641 m from Arizona Mills (BASELINE RD / S DARROW DR). Case #TE202674654          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>[sc-0] trespass warning - public places on Jul 26, 2026, 645 m from Arizona Mill (BASELINE RD / I10). Case #TE202675235          (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] trespass warning - public places on Jul 26, 2026, 645 m from Arizona Mills (BASELINE RD / I10). Case #TE202675235          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7460,7 +7460,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>[sc-0] trespass warning - private property on Jul 25, 2026, 650 m from Arizona Mill (1XXX W BASELINE RD). Case #TE202675001          (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] trespass warning - private property on Jul 25, 2026, 650 m from Arizona Mills (1XXX W BASELINE RD). Case #TE202675001          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7515,7 +7515,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>[sc-0] service - order of protection (oop) / injunction (p1) on Jul 28, 2026, 705 m from Arizona Mill (1XXX W LA JOLLA DR). Case #TE202676035          (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] service - order of protection (oop) / injunction (p1) on Jul 28, 2026, 705 m from Arizona Mills (1XXX W LA JOLLA DR). Case #TE202676035          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>[sc-0] trespass warning - private property on Jul 28, 2026, 774 m from Arizona Mill (1XXX W BASELINE RD). Case #TE202675946          (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] trespass warning - private property on Jul 28, 2026, 774 m from Arizona Mills (1XXX W BASELINE RD). Case #TE202675946          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7625,7 +7625,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>[sc-0] assist - mentally ill (other than mhp/emhetr) on Jul 25, 2026, 947 m from Arizona Mill (1XXX W BASELINE RD). Case #TE202674935          (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] assist - mentally ill (other than mhp/emhetr) on Jul 25, 2026, 947 m from Arizona Mills (1XXX W BASELINE RD). Case #TE202674935          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7680,7 +7680,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Arizona Mill</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>[sc-0] lost - property (non-firearm, other than gov't issued id) on Jul 25, 2026, 967 m from Arizona Mill (PARKSIDE DR / W FREMONT DR). Case #TE202674869          (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] lost - property (non-firearm, other than gov't issued id) on Jul 25, 2026, 967 m from Arizona Mills (PARKSIDE DR / W FREMONT DR). Case #TE202674869          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-31 07:28:37.517868+00:00</t>
+          <t>2026-07-31 07:31:55.362213+00:00</t>
         </is>
       </c>
     </row>
@@ -7788,7 +7788,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-24 07:28:37.517868+00:00</t>
+          <t>2026-07-24 07:31:55.362213+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/latest/blotter_report.xlsx
+++ b/reports/latest/blotter_report.xlsx
@@ -15,8 +15,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Highlights'!$A$1:$M$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$87</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J3" t="n">
         <v>14.7</v>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -683,7 +683,7 @@
         <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -896,19 +896,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>145.2</v>
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -954,13 +954,13 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J11" t="n">
         <v>113.7</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>46231.92430555556</v>
+        <v>46232.70902777778</v>
       </c>
       <c r="L11" t="b">
         <v>0</v>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1</v>
@@ -1000,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
         <v>178.9</v>
@@ -1076,25 +1076,25 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>17</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
+        <v>42</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="J14" t="n">
         <v>288.9</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>46233.63055555556</v>
+        <v>46233.7625</v>
       </c>
       <c r="L14" t="b">
         <v>0</v>
@@ -1487,443 +1487,435 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20260449995_11</t>
+          <t>26C139724</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>46227.89583333334</v>
+        <v>46227.69421296296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SHOPLIFTING</t>
+          <t>BATTERY DV</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>SIM_ASSAULT</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>211 211</t>
+          <t>600 BLOCK OF S EASTERN AVE</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>36.20300000011262</v>
+        <v>37.6774046653855</v>
       </c>
       <c r="K7" t="n">
-        <v>-86.69100000036219</v>
+        <v>-97.23656061094495</v>
       </c>
       <c r="L7" t="n">
-        <v>113.7</v>
+        <v>1122.4</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 24, 2026, 114 m from Opry Mills (211 211). Premises: DEPARTMENT, DISCOUNT STORE. Status: CLEARED BY ARREST. Victims: 1. Case #20260449995 (use for a records request — full narratives are not published in open data).</t>
+          <t>Battery dv on Jul 24, 2026, 1122 m from Towne East Square (600 BLOCK OF S EASTERN AVE). Case #26C139724 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20260451873_11</t>
+          <t>71894237115</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>46228.76041666666</v>
+        <v>46231.20833333334</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>LOST PROPERTY</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>VIOLENT CRIME</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>433 433</t>
+          <t>15XX BLOCK OF NE 107TH ST</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>36.20199999980591</v>
+        <v>47.70668788</v>
       </c>
       <c r="K8" t="n">
-        <v>-86.69299999962931</v>
+        <v>-122.311189997702</v>
       </c>
       <c r="L8" t="n">
-        <v>125.9</v>
+        <v>1145.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Lost property on Jul 25, 2026, 126 m from Opry Mills (433 433). Premises: Shopping Mall. Status: UNFOUNDED. Victims: 1. Case #20260451873 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-221056 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DP2026415473230300</t>
+          <t>71889871382</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>46231.47916666666</v>
+        <v>46231.00625</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>theft-shoplift</t>
+          <t>Simple Assault</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>ALL OTHER</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15 S STEELE ST</t>
+          <t>15XX BLOCK OF NE 107TH ST</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>39.7162154712797</v>
+        <v>47.70668788</v>
       </c>
       <c r="K9" t="n">
-        <v>-104.9512928115626</v>
+        <v>-122.311189997702</v>
       </c>
       <c r="L9" t="n">
-        <v>144.7</v>
+        <v>1145.7</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Theft-shoplift on Jul 28, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026415473 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-220636 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DP2026413358260700</t>
+          <t>26C142249</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>46230.47013888889</v>
+        <v>46230.75</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>fraud-by-telephone</t>
+          <t>BATTERY ABW</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>white-collar-crime</t>
+          <t>SIM_ASSAULT</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15 S STEELE ST</t>
+          <t>700 BLOCK OF S MISSION RD</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>39.7162154712797</v>
+        <v>37.6756469679485</v>
       </c>
       <c r="K10" t="n">
-        <v>-104.9512928115626</v>
+        <v>-97.25850032865422</v>
       </c>
       <c r="L10" t="n">
-        <v>144.7</v>
+        <v>1251.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Fraud-by-telephone on Jul 27, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026413358 (use for a records request — full narratives are not published in open data).</t>
+          <t>Battery abw on Jul 27, 2026, 1251 m from Towne East Square (700 BLOCK OF S MISSION RD). Case #26C142249 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>71913162555</t>
+          <t xml:space="preserve">TE202674714         </t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>46232.82986111111</v>
+        <v>46227.7375</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t xml:space="preserve">[13A] AGGRAVATED ASSAULT [DV]                                                   </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>PROPERTY CRIME</t>
-        </is>
-      </c>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>5XXX S HARDY DR</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>47.7086028</v>
+        <v>33.37634047797651</v>
       </c>
       <c r="K11" t="n">
-        <v>-122.324615154453</v>
+        <v>-111.9531278046354</v>
       </c>
       <c r="L11" t="n">
-        <v>145.2</v>
+        <v>1309.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 29, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-222878 (use for a records request — full narratives are not published in open data).</t>
+          <t>[13a] aggravated assault [dv] on Jul 24, 2026, 1309 m from Arizona Mills (5XXX S HARDY DR). Case #TE202674714          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>71898889573</t>
+          <t xml:space="preserve">TE202675136         </t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>46231.625</v>
+        <v>46228.97847222222</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t xml:space="preserve">[13B] ASSAULT                                                                   </t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>PROPERTY CRIME</t>
-        </is>
-      </c>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>5XXX S HARDY DR</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>47.7086028</v>
+        <v>33.3757495513233</v>
       </c>
       <c r="K12" t="n">
-        <v>-122.324615154453</v>
+        <v>-111.9531832468173</v>
       </c>
       <c r="L12" t="n">
-        <v>145.2</v>
+        <v>1345.1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-221387 (use for a records request — full narratives are not published in open data).</t>
+          <t>[13b] assault on Jul 25, 2026, 1345 m from Arizona Mills (5XXX S HARDY DR). Case #TE202675136          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>71842391876</t>
+          <t>26C139922</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>46227.5</v>
+        <v>46227.95277777778</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motor Vehicle Theft</t>
+          <t>BATTERY ABW</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>SIM_ASSAULT</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>7000 BLOCK OF E LINCOLN ST</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>47.7086028</v>
+        <v>37.67195398477438</v>
       </c>
       <c r="K13" t="n">
-        <v>-122.324615154453</v>
+        <v>-97.25533959083543</v>
       </c>
       <c r="L13" t="n">
-        <v>145.2</v>
+        <v>1383.4</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Motor vehicle theft on Jul 24, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-217106 (use for a records request — full narratives are not published in open data).</t>
+          <t>Battery abw on Jul 24, 2026, 1383 m from Towne East Square (7000 BLOCK OF E LINCOLN ST). Case #26C139922 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>OPRYMILLS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Opry Mills</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DP2026408098239901</t>
+          <t>20260449995_11</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>46227.58333333334</v>
+        <v>46227.89583333334</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>theft-bicycle</t>
+          <t>SHOPLIFTING</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1933,56 +1925,56 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>N MILWAUKEE ST / E 1ST AVE</t>
+          <t>211 211</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>39.71813319743836</v>
+        <v>36.20300000011262</v>
       </c>
       <c r="K14" t="n">
-        <v>-104.9522056316381</v>
+        <v>-86.69100000036219</v>
       </c>
       <c r="L14" t="n">
-        <v>148.6</v>
+        <v>113.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Theft-bicycle on Jul 24, 2026, 149 m from Cherry Creek Shopping Center (N MILWAUKEE ST / E 1ST AVE). Victims: 1. Case #DP2026408098 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 24, 2026, 114 m from Opry Mills (211 211). Premises: DEPARTMENT, DISCOUNT STORE. Status: CLEARED BY ARREST. Victims: 1. Case #20260449995 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>OPRYMILLS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Opry Mills</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>20260728-1922-01</t>
+          <t>20260451873_11</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>46231.16666666666</v>
+        <v>46228.76041666666</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>LOST PROPERTY</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1992,56 +1984,56 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>433 433</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>35.15120046375475</v>
+        <v>36.20199999980591</v>
       </c>
       <c r="K15" t="n">
-        <v>-80.82867375349484</v>
+        <v>-86.69299999962931</v>
       </c>
       <c r="L15" t="n">
-        <v>178.9</v>
+        <v>125.9</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1922-01 (use for a records request — full narratives are not published in open data).</t>
+          <t>Lost property on Jul 25, 2026, 126 m from Opry Mills (433 433). Premises: Shopping Mall. Status: UNFOUNDED. Victims: 1. Case #20260451873 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>20260728-1130-01</t>
+          <t>DP2026415473230300</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>46231.16666666666</v>
+        <v>46231.47916666666</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>theft-shoplift</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2051,56 +2043,56 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>larceny</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>15 S STEELE ST</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>35.15120046375475</v>
+        <v>39.7162154712797</v>
       </c>
       <c r="K16" t="n">
-        <v>-80.82867375349484</v>
+        <v>-104.9512928115626</v>
       </c>
       <c r="L16" t="n">
-        <v>178.9</v>
+        <v>144.7</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1130-01 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-shoplift on Jul 28, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026415473 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>20260729-1053-01</t>
+          <t>DP2026413358260700</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>46229.16666666666</v>
+        <v>46230.47013888889</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>All Other Thefts</t>
+          <t>fraud-by-telephone</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2110,52 +2102,52 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>23H</t>
+          <t>white-collar-crime</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4500 SHARON RD</t>
+          <t>15 S STEELE ST</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>35.15120046375475</v>
+        <v>39.7162154712797</v>
       </c>
       <c r="K17" t="n">
-        <v>-80.82867375349484</v>
+        <v>-104.9512928115626</v>
       </c>
       <c r="L17" t="n">
-        <v>178.9</v>
+        <v>144.7</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>All other thefts on Jul 26, 2026, 179 m from Southpark (4500 SHARON RD). Status: Open. Case #20260729-1053-01 (use for a records request — full narratives are not published in open data).</t>
+          <t>Fraud-by-telephone on Jul 27, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026413358 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>20260727-1824-00</t>
+          <t>71913162555</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>46229.16666666666</v>
+        <v>46232.82986111111</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2169,52 +2161,52 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>3XX BLOCK OF NE NORTHGATE WAY</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>35.15120046375475</v>
+        <v>47.7086028</v>
       </c>
       <c r="K18" t="n">
-        <v>-80.82867375349484</v>
+        <v>-122.324615154453</v>
       </c>
       <c r="L18" t="n">
-        <v>178.9</v>
+        <v>145.2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 26, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260727-1824-00 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 29, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-222878 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>20260725-1348-05</t>
+          <t>71898889573</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>46228.16666666666</v>
+        <v>46231.625</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2228,56 +2220,56 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>4XX BLOCK OF NE NORTHGATE WAY</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>35.15120046375475</v>
+        <v>47.7086028</v>
       </c>
       <c r="K19" t="n">
-        <v>-80.82867375349484</v>
+        <v>-122.324615154453</v>
       </c>
       <c r="L19" t="n">
-        <v>178.9</v>
+        <v>145.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 25, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260725-1348-05 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-221387 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>20260727-1945-02</t>
+          <t>71842391876</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>46228.16666666666</v>
+        <v>46227.5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Motor Vehicle Theft</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2287,26 +2279,26 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>3XX BLOCK OF NE NORTHGATE WAY</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>35.15120046375475</v>
+        <v>47.7086028</v>
       </c>
       <c r="K20" t="n">
-        <v>-80.82867375349484</v>
+        <v>-122.324615154453</v>
       </c>
       <c r="L20" t="n">
-        <v>178.9</v>
+        <v>145.2</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 25, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260727-1945-02 (use for a records request — full narratives are not published in open data).</t>
+          <t>Motor vehicle theft on Jul 24, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-217106 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2328,15 +2320,15 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DP2026416370230300</t>
+          <t>DP2026408098239901</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>46231.83333333334</v>
+        <v>46227.58333333334</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>theft-shoplift</t>
+          <t>theft-bicycle</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2351,51 +2343,51 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2810 E 1ST AVE</t>
+          <t>N MILWAUKEE ST / E 1ST AVE</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>39.71666393731682</v>
+        <v>39.71813319743836</v>
       </c>
       <c r="K21" t="n">
-        <v>-104.9556403659223</v>
+        <v>-104.9522056316381</v>
       </c>
       <c r="L21" t="n">
-        <v>247.6</v>
+        <v>148.6</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Theft-shoplift on Jul 28, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026416370 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-bicycle on Jul 24, 2026, 149 m from Cherry Creek Shopping Center (N MILWAUKEE ST / E 1ST AVE). Victims: 1. Case #DP2026408098 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>DP2026415590230300</t>
+          <t>20260728-1922-01</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>46231.54236111111</v>
+        <v>46231.16666666666</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>theft-shoplift</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2405,56 +2397,56 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>23C</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2810 E 1ST AVE</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>39.71666393731682</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K22" t="n">
-        <v>-104.9556403659223</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L22" t="n">
-        <v>247.6</v>
+        <v>178.9</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Theft-shoplift on Jul 28, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026415590 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1922-01 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202675399         </t>
+          <t>20260728-1130-01</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>46229.9</v>
+        <v>46231.16666666666</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2462,54 +2454,58 @@
           <t>PROPERTY</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5XXX S ARIZONA MILLS CIR</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>33.38552975305072</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K23" t="n">
-        <v>-111.965328834686</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L23" t="n">
-        <v>262</v>
+        <v>178.9</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>[sc-0] trespass warning - private property on Jul 26, 2026, 262 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675399          (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1130-01 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202676101         </t>
+          <t>20260729-1053-01</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>46232.21041666667</v>
+        <v>46229.16666666666</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">[240] MOTOR VEHICLE THEFT                                                       </t>
+          <t>All Other Thefts</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2517,54 +2513,58 @@
           <t>PROPERTY</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>23H</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5XXX S ARIZONA MILLS CIR</t>
+          <t>4500 SHARON RD</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>33.38580430470485</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K24" t="n">
-        <v>-111.9660628528483</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L24" t="n">
-        <v>315.7</v>
+        <v>178.9</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>[240] motor vehicle theft on Jul 29, 2026, 316 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202676101          (use for a records request — full narratives are not published in open data).</t>
+          <t>All other thefts on Jul 26, 2026, 179 m from Southpark (4500 SHARON RD). Status: Open. Case #20260729-1053-01 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>71909585262</t>
+          <t>20260727-1824-00</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>46231.83333333334</v>
+        <v>46229.16666666666</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motor Vehicle Theft</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2574,56 +2574,56 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>23C</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>47.70858578</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K25" t="n">
-        <v>-122.321918377919</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L25" t="n">
-        <v>338.4</v>
+        <v>178.9</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Motor vehicle theft on Jul 28, 2026, 338 m from Northgate Station (5XX BLOCK OF NE NORTHGATE WAY). Case #2026-222454 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 26, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260727-1824-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202676030         </t>
+          <t>20260725-1348-05</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>46231.83194444444</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2631,24 +2631,28 @@
           <t>PROPERTY</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5XXX S ARIZONA MILLS CIR</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>33.3805974892332</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K26" t="n">
-        <v>-111.9623154538272</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L26" t="n">
-        <v>361.4</v>
+        <v>178.9</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>[sc-0] trespass warning - private property on Jul 28, 2026, 361 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202676030          (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 25, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260725-1348-05 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:M134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3566,30 +3570,30 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GREENHILLS</t>
+          <t>OPRYMILLS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Mall at Green Hills</t>
+          <t>Opry Mills</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GREENHILLS:Metro Nashville PD Incidents</t>
+          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>20260452878_11</t>
+          <t>20260459134_11</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>46229.60694444444</v>
+        <v>46232.70902777778</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>POLICE INQUIRY</t>
+          <t>HARRASSMENT (NUISANCE)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -3597,28 +3601,24 @@
           <t>OTHER</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2131 2131</t>
+          <t>TWO RIVERS PKWY</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>36.10599999977134</v>
+        <v>36.19000000021294</v>
       </c>
       <c r="K16" t="n">
-        <v>-86.8170000000033</v>
+        <v>-86.69000000027951</v>
       </c>
       <c r="L16" t="n">
-        <v>191.2</v>
+        <v>1455.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Police inquiry on Jul 26, 2026, 191 m from The Mall at Green Hills (2131 2131). Premises: PARKING LOT, GARAGE. Status: UNFOUNDED. Victims: 1. Flags: domestic related. Case #20260452878 (use for a records request — full narratives are not published in open data).</t>
+          <t>Harrassment (nuisance) on Jul 29, 2026, 1456 m from Opry Mills (TWO RIVERS PKWY). Premises: PARK. Status: OPEN. Victims: 1. Case #20260459134 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -3640,20 +3640,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>20260451477_11</t>
+          <t>20260452878_11</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>46228.27083333334</v>
+        <v>46229.60694444444</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>BURGLARY</t>
+          <t>POLICE INQUIRY</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -3663,21 +3663,21 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>CHANNELKIRK LN</t>
+          <t>2131 2131</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>36.10999999969955</v>
+        <v>36.10599999977134</v>
       </c>
       <c r="K17" t="n">
-        <v>-86.81000000032267</v>
+        <v>-86.8170000000033</v>
       </c>
       <c r="L17" t="n">
-        <v>630.5</v>
+        <v>191.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Burglary on Jul 25, 2026, 631 m from The Mall at Green Hills (CHANNELKIRK LN). Premises: RESIDENCE, HOME. Status: OPEN. Victims: 1. Case #20260451477 (use for a records request — full narratives are not published in open data).</t>
+          <t>Police inquiry on Jul 26, 2026, 191 m from The Mall at Green Hills (2131 2131). Premises: PARKING LOT, GARAGE. Status: UNFOUNDED. Victims: 1. Flags: domestic related. Case #20260452878 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -3699,20 +3699,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>20260453759_11</t>
+          <t>20260451477_11</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>46229.91666666666</v>
+        <v>46228.27083333334</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>POLICE INQUIRY</t>
+          <t>BURGLARY</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3722,21 +3722,21 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2024 2024</t>
+          <t>CHANNELKIRK LN</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>36.09999999975003</v>
+        <v>36.10999999969955</v>
       </c>
       <c r="K18" t="n">
-        <v>-86.81499999983789</v>
+        <v>-86.81000000032267</v>
       </c>
       <c r="L18" t="n">
-        <v>859.2</v>
+        <v>630.5</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Police inquiry on Jul 26, 2026, 859 m from The Mall at Green Hills (2024 2024). Premises: RESIDENCE, HOME. Status: UNFOUNDED. Victims: 1. Flags: domestic related. Case #20260453759 (use for a records request — full narratives are not published in open data).</t>
+          <t>Burglary on Jul 25, 2026, 631 m from The Mall at Green Hills (CHANNELKIRK LN). Premises: RESIDENCE, HOME. Status: OPEN. Victims: 1. Case #20260451477 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -3758,44 +3758,44 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>20260458322_11</t>
+          <t>20260453759_11</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>46232.0625</v>
+        <v>46229.91666666666</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>BURGLARY - MOTOR VEHICLE</t>
+          <t>POLICE INQUIRY</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Unarmed</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>HILLSBORO PIKE</t>
+          <t>2024 2024</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>36.09999999975003</v>
       </c>
       <c r="K19" t="n">
-        <v>-86.82000000025143</v>
+        <v>-86.81499999983789</v>
       </c>
       <c r="L19" t="n">
-        <v>910.1</v>
+        <v>859.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Burglary - motor vehicle on Jul 29, 2026, 910 m from The Mall at Green Hills (HILLSBORO PIKE). Weapon: Unarmed. Premises: PARKING LOT, GARAGE. Status: OPEN. Victims: 1. Case #20260458322 (use for a records request — full narratives are not published in open data).</t>
+          <t>Police inquiry on Jul 26, 2026, 859 m from The Mall at Green Hills (2024 2024). Premises: RESIDENCE, HOME. Status: UNFOUNDED. Victims: 1. Flags: domestic related. Case #20260453759 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -3817,25 +3817,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>20260450411_11</t>
+          <t>20260458322_11</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>46228.02083333334</v>
+        <v>46232.0625</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SIMPLE ASSLT</t>
+          <t>BURGLARY - MOTOR VEHICLE</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>PERSONAL (HANDS)</t>
+          <t>Unarmed</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Simple asslt on Jul 25, 2026, 910 m from The Mall at Green Hills (HILLSBORO PIKE). Weapon: PERSONAL (HANDS). Premises: HIGHWAY, ROAD, ALLEY. Status: OPEN. Victims: 1. Case #20260450411 (use for a records request — full narratives are not published in open data).</t>
+          <t>Burglary - motor vehicle on Jul 29, 2026, 910 m from The Mall at Green Hills (HILLSBORO PIKE). Weapon: Unarmed. Premises: PARKING LOT, GARAGE. Status: OPEN. Victims: 1. Case #20260458322 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -3876,26 +3876,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>20260450256_11</t>
+          <t>20260450411_11</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>46228.02569444444</v>
+        <v>46228.02083333334</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>THEFT OF MERCHANDISE- &gt;$1,000 BUT &lt; $2,500</t>
+          <t>SIMPLE ASSLT</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>PERSONAL (HANDS)</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>HILLSBORO</t>
+          <t>HILLSBORO PIKE</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -3909,7 +3913,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Theft of merchandise- &gt;$1,000 but &lt; $2,500 on Jul 25, 2026, 910 m from The Mall at Green Hills (HILLSBORO). Premises: SPECIALTY STORE. Status: OPEN. Victims: 1. Case #20260450256 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple asslt on Jul 25, 2026, 910 m from The Mall at Green Hills (HILLSBORO PIKE). Weapon: PERSONAL (HANDS). Premises: HIGHWAY, ROAD, ALLEY. Status: OPEN. Victims: 1. Case #20260450411 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -3931,15 +3935,15 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>20260449408_11</t>
+          <t>20260450256_11</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>46227.61805555555</v>
+        <v>46228.02569444444</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>LOST PROPERTY</t>
+          <t>THEFT OF MERCHANDISE- &gt;$1,000 BUT &lt; $2,500</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3947,58 +3951,54 @@
           <t>PROPERTY</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2025 2025</t>
+          <t>HILLSBORO</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>36.11399999985069</v>
+        <v>36.09999999975003</v>
       </c>
       <c r="K22" t="n">
-        <v>-86.80900000023999</v>
+        <v>-86.82000000025143</v>
       </c>
       <c r="L22" t="n">
-        <v>969.2</v>
+        <v>910.1</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Lost property on Jul 24, 2026, 969 m from The Mall at Green Hills (2025 2025). Premises: RESIDENCE, HOME. Status: UNFOUNDED. Victims: 1. Case #20260449408 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft of merchandise- &gt;$1,000 but &lt; $2,500 on Jul 25, 2026, 910 m from The Mall at Green Hills (HILLSBORO). Premises: SPECIALTY STORE. Status: OPEN. Victims: 1. Case #20260450256 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>GREENHILLS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>The Mall at Green Hills</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>GREENHILLS:Metro Nashville PD Incidents</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>71913162555</t>
+          <t>20260449408_11</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>46232.82986111111</v>
+        <v>46227.61805555555</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>LOST PROPERTY</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4008,26 +4008,26 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>2025 2025</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>47.7086028</v>
+        <v>36.11399999985069</v>
       </c>
       <c r="K23" t="n">
-        <v>-122.324615154453</v>
+        <v>-86.80900000023999</v>
       </c>
       <c r="L23" t="n">
-        <v>145.2</v>
+        <v>969.2</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 29, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-222878 (use for a records request — full narratives are not published in open data).</t>
+          <t>Lost property on Jul 24, 2026, 969 m from The Mall at Green Hills (2025 2025). Premises: RESIDENCE, HOME. Status: UNFOUNDED. Victims: 1. Case #20260449408 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -4049,15 +4049,15 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>71909585262</t>
+          <t>71913162555</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>46231.83333333334</v>
+        <v>46232.82986111111</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motor Vehicle Theft</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4072,21 +4072,21 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>3XX BLOCK OF NE NORTHGATE WAY</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>47.70858578</v>
+        <v>47.7086028</v>
       </c>
       <c r="K24" t="n">
-        <v>-122.321918377919</v>
+        <v>-122.324615154453</v>
       </c>
       <c r="L24" t="n">
-        <v>338.4</v>
+        <v>145.2</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Motor vehicle theft on Jul 28, 2026, 338 m from Northgate Station (5XX BLOCK OF NE NORTHGATE WAY). Case #2026-222454 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 29, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-222878 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -4108,15 +4108,15 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>71898889573</t>
+          <t>71909585262</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>46231.625</v>
+        <v>46231.83333333334</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Motor Vehicle Theft</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4131,21 +4131,21 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>5XX BLOCK OF NE NORTHGATE WAY</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>47.7086028</v>
+        <v>47.70858578</v>
       </c>
       <c r="K25" t="n">
-        <v>-122.324615154453</v>
+        <v>-122.321918377919</v>
       </c>
       <c r="L25" t="n">
-        <v>145.2</v>
+        <v>338.4</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-221387 (use for a records request — full narratives are not published in open data).</t>
+          <t>Motor vehicle theft on Jul 28, 2026, 338 m from Northgate Station (5XX BLOCK OF NE NORTHGATE WAY). Case #2026-222454 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -4167,44 +4167,44 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>71878728447</t>
+          <t>71899643103</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>46230.4375</v>
+        <v>46231.78263888889</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Robbery</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>VIOLENT CRIME</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>16XX BLOCK OF N 105TH ST</t>
+          <t>116XX BLOCK OF AURORA AVE N</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>47.70504225</v>
+        <v>47.71354798</v>
       </c>
       <c r="K26" t="n">
-        <v>-122.338094779232</v>
+        <v>-122.344834273165</v>
       </c>
       <c r="L26" t="n">
-        <v>938.8</v>
+        <v>1511</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Robbery on Jul 27, 2026, 939 m from Northgate Station (16XX BLOCK OF N 105TH ST). Case #2026-220064 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 1511 m from Northgate Station (116XX BLOCK OF AURORA AVE N). Case #2026-221622 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -4226,15 +4226,15 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>71896083189</t>
+          <t>71898889573</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>46228.875</v>
+        <v>46231.625</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Theft From Motor Vehicle</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4249,21 +4249,21 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>NE 100TH ST / 5TH AVE NE</t>
+          <t>4XX BLOCK OF NE NORTHGATE WAY</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>47.70132479</v>
+        <v>47.7086028</v>
       </c>
       <c r="K27" t="n">
-        <v>-122.3231272219471</v>
+        <v>-122.324615154453</v>
       </c>
       <c r="L27" t="n">
-        <v>785.6</v>
+        <v>145.2</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Theft from motor vehicle on Jul 25, 2026, 786 m from Northgate Station (NE 100TH ST / 5TH AVE NE). Case #2026-913373 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-221387 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -4285,15 +4285,15 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>71842391876</t>
+          <t>71890752645</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>46227.5</v>
+        <v>46231.21458333333</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motor Vehicle Theft</t>
+          <t>Destruction/Damage/Vandalism of Property</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4303,174 +4303,174 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>ALL OTHER</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>15XX BLOCK OF NE 107TH ST</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>47.7086028</v>
+        <v>47.70668788</v>
       </c>
       <c r="K28" t="n">
-        <v>-122.324615154453</v>
+        <v>-122.311189989679</v>
       </c>
       <c r="L28" t="n">
-        <v>145.2</v>
+        <v>1145.7</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Motor vehicle theft on Jul 24, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-217106 (use for a records request — full narratives are not published in open data).</t>
+          <t>Destruction/damage/vandalism of property on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-220873 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DP2026413358260700</t>
+          <t>71894237115</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>46230.47013888889</v>
+        <v>46231.20833333334</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>fraud-by-telephone</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>white-collar-crime</t>
+          <t>VIOLENT CRIME</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>15 S STEELE ST</t>
+          <t>15XX BLOCK OF NE 107TH ST</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>39.7162154712797</v>
+        <v>47.70668788</v>
       </c>
       <c r="K29" t="n">
-        <v>-104.9512928115626</v>
+        <v>-122.311189997702</v>
       </c>
       <c r="L29" t="n">
-        <v>144.7</v>
+        <v>1145.7</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Fraud-by-telephone on Jul 27, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026413358 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-221056 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DP2026415473230300</t>
+          <t>71889871382</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>46231.47916666666</v>
+        <v>46231.00625</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>theft-shoplift</t>
+          <t>Simple Assault</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>ALL OTHER</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>15 S STEELE ST</t>
+          <t>15XX BLOCK OF NE 107TH ST</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>39.7162154712797</v>
+        <v>47.70668788</v>
       </c>
       <c r="K30" t="n">
-        <v>-104.9512928115626</v>
+        <v>-122.311189997702</v>
       </c>
       <c r="L30" t="n">
-        <v>144.7</v>
+        <v>1145.7</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Theft-shoplift on Jul 28, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026415473 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-220636 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DP2026408098239901</t>
+          <t>71906728829</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>46227.58333333334</v>
+        <v>46231</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>theft-bicycle</t>
+          <t>Theft of Motor Vehicle Parts or Accessories</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4480,174 +4480,174 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>N MILWAUKEE ST / E 1ST AVE</t>
+          <t>9XX BLOCK OF N 103RD ST</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>39.71813319743836</v>
+        <v>47.70360675</v>
       </c>
       <c r="K31" t="n">
-        <v>-104.9522056316381</v>
+        <v>-122.346021623573</v>
       </c>
       <c r="L31" t="n">
-        <v>148.6</v>
+        <v>1551.2</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Theft-bicycle on Jul 24, 2026, 149 m from Cherry Creek Shopping Center (N MILWAUKEE ST / E 1ST AVE). Victims: 1. Case #DP2026408098 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft of motor vehicle parts or accessories on Jul 28, 2026, 1551 m from Northgate Station (9XX BLOCK OF N 103RD ST). Case #2026-222196 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>DP2026416370230300</t>
+          <t>71878728447</t>
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>46231.83333333334</v>
+        <v>46230.4375</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>theft-shoplift</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>VIOLENT CRIME</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2810 E 1ST AVE</t>
+          <t>16XX BLOCK OF N 105TH ST</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>39.71666393731682</v>
+        <v>47.70504225</v>
       </c>
       <c r="K32" t="n">
-        <v>-104.9556403659223</v>
+        <v>-122.338094779232</v>
       </c>
       <c r="L32" t="n">
-        <v>247.6</v>
+        <v>938.8</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Theft-shoplift on Jul 28, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026416370 (use for a records request — full narratives are not published in open data).</t>
+          <t>Robbery on Jul 27, 2026, 939 m from Northgate Station (16XX BLOCK OF N 105TH ST). Case #2026-220064 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DP2026415590230300</t>
+          <t>71854915364</t>
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>46231.54236111111</v>
+        <v>46228.91527777778</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>theft-shoplift</t>
+          <t>Not Reportable to NIBRS</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>ALL OTHER</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2810 E 1ST AVE</t>
+          <t>N 105TH ST / AURORA AVE N</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>39.71666393731682</v>
+        <v>47.70505121</v>
       </c>
       <c r="K33" t="n">
-        <v>-104.9556403659223</v>
+        <v>-122.3446941292056</v>
       </c>
       <c r="L33" t="n">
-        <v>247.6</v>
+        <v>1411</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Theft-shoplift on Jul 28, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026415590 (use for a records request — full narratives are not published in open data).</t>
+          <t>Not reportable to nibrs on Jul 25, 2026, 1411 m from Northgate Station (N 105TH ST / AURORA AVE N). Case #2026-218646 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>DP2026413635260700</t>
+          <t>71896083189</t>
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>46230.58125</v>
+        <v>46228.875</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>fraud-by-telephone</t>
+          <t>Theft From Motor Vehicle</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4657,56 +4657,56 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>white-collar-crime</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2 N ADAMS ST</t>
+          <t>NE 100TH ST / 5TH AVE NE</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>39.71654731730718</v>
+        <v>47.70132479</v>
       </c>
       <c r="K34" t="n">
-        <v>-104.9482864243138</v>
+        <v>-122.3231272219471</v>
       </c>
       <c r="L34" t="n">
-        <v>384.1</v>
+        <v>785.6</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Fraud-by-telephone on Jul 27, 2026, 384 m from Cherry Creek Shopping Center (2 N ADAMS ST). Victims: 1. Case #DP2026413635 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft from motor vehicle on Jul 25, 2026, 786 m from Northgate Station (NE 100TH ST / 5TH AVE NE). Case #2026-913373 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>DP20266010142239900</t>
+          <t>71842391876</t>
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>46230.10416666666</v>
+        <v>46227.5</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>theft-other</t>
+          <t>Motor Vehicle Theft</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4716,26 +4716,26 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3444 E 2ND AVE</t>
+          <t>3XX BLOCK OF NE NORTHGATE WAY</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>39.7193352135378</v>
+        <v>47.7086028</v>
       </c>
       <c r="K35" t="n">
-        <v>-104.9468354191938</v>
+        <v>-122.324615154453</v>
       </c>
       <c r="L35" t="n">
-        <v>576.2</v>
+        <v>145.2</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Theft-other on Jul 27, 2026, 576 m from Cherry Creek Shopping Center (3444 E 2ND AVE). Victims: 1. Case #DP20266010142 (use for a records request — full narratives are not published in open data).</t>
+          <t>Motor vehicle theft on Jul 24, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-217106 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -4757,44 +4757,44 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>DP2026413301299900</t>
+          <t>DP2026413358260700</t>
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>46229.95833333334</v>
+        <v>46230.47013888889</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>criminal-mischief-other</t>
+          <t>fraud-by-telephone</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>public-disorder</t>
+          <t>white-collar-crime</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>201 N UNIVERSITY BLVD</t>
+          <t>15 S STEELE ST</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>39.71957373655755</v>
+        <v>39.7162154712797</v>
       </c>
       <c r="K36" t="n">
-        <v>-104.9597628432634</v>
+        <v>-104.9512928115626</v>
       </c>
       <c r="L36" t="n">
-        <v>670.6</v>
+        <v>144.7</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Criminal-mischief-other on Jul 26, 2026, 671 m from Cherry Creek Shopping Center (201 N UNIVERSITY BLVD). Victims: 1. Case #DP2026413301 (use for a records request — full narratives are not published in open data).</t>
+          <t>Fraud-by-telephone on Jul 27, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026413358 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -4816,44 +4816,44 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>DP20266010143299900</t>
+          <t>DP2026415473230300</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>46229.9375</v>
+        <v>46231.47916666666</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>criminal-mischief-other</t>
+          <t>theft-shoplift</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>public-disorder</t>
+          <t>larceny</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>201 N UNIVERSITY BLVD</t>
+          <t>15 S STEELE ST</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>39.71957373655755</v>
+        <v>39.7162154712797</v>
       </c>
       <c r="K37" t="n">
-        <v>-104.9597628432634</v>
+        <v>-104.9512928115626</v>
       </c>
       <c r="L37" t="n">
-        <v>670.6</v>
+        <v>144.7</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Criminal-mischief-other on Jul 26, 2026, 671 m from Cherry Creek Shopping Center (201 N UNIVERSITY BLVD). Victims: 1. Case #DP20266010143 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-shoplift on Jul 28, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026415473 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -4875,44 +4875,44 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>DP2026411044131300</t>
+          <t>DP2026408098239901</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>46229.1125</v>
+        <v>46227.58333333334</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>assault-simple</t>
+          <t>theft-bicycle</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>other-crimes-against-persons</t>
+          <t>larceny</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3200 BLOCK E CHERRY CREEK S DR</t>
+          <t>N MILWAUKEE ST / E 1ST AVE</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>39.71130989687384</v>
+        <v>39.71813319743836</v>
       </c>
       <c r="K38" t="n">
-        <v>-104.9490029653731</v>
+        <v>-104.9522056316381</v>
       </c>
       <c r="L38" t="n">
-        <v>696.3</v>
+        <v>148.6</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Assault-simple on Jul 26, 2026, 696 m from Cherry Creek Shopping Center (3200 BLOCK E CHERRY CREEK S DR). Victims: 1. Case #DP2026411044 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-bicycle on Jul 24, 2026, 149 m from Cherry Creek Shopping Center (N MILWAUKEE ST / E 1ST AVE). Victims: 1. Case #DP2026408098 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -4934,15 +4934,15 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>DP2026411500220400</t>
+          <t>DP2026416370230300</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>46229.08333333334</v>
+        <v>46231.83333333334</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>burglary-residence-no-force</t>
+          <t>theft-shoplift</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4952,115 +4952,115 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>burglary</t>
+          <t>larceny</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>100 BLK N GARFIELD ST</t>
+          <t>2810 E 1ST AVE</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>39.71871773048673</v>
+        <v>39.71666393731682</v>
       </c>
       <c r="K39" t="n">
-        <v>-104.9439679319565</v>
+        <v>-104.9556403659223</v>
       </c>
       <c r="L39" t="n">
-        <v>779.5</v>
+        <v>247.6</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Burglary-residence-no-force on Jul 26, 2026, 779 m from Cherry Creek Shopping Center (100 BLK N GARFIELD ST). Victims: 1. Case #DP2026411500 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-shoplift on Jul 28, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026416370 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>20260725-2301-00</t>
+          <t>DP2026415590230300</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>46228.16666666666</v>
+        <v>46231.54236111111</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Other Unlisted Non-Criminal</t>
+          <t>theft-shoplift</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>larceny</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>6900 FAIRVIEW RD</t>
+          <t>2810 E 1ST AVE</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>35.14684118006692</v>
+        <v>39.71666393731682</v>
       </c>
       <c r="K40" t="n">
-        <v>-80.82544759809264</v>
+        <v>-104.9556403659223</v>
       </c>
       <c r="L40" t="n">
-        <v>722.6</v>
+        <v>247.6</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Other unlisted non-criminal on Jul 25, 2026, 723 m from Southpark (6900 FAIRVIEW RD). Status: Open. Case #20260725-2301-00 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-shoplift on Jul 28, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026415590 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>20260726-0712-02</t>
+          <t>DP2026413635260700</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>46229.16666666666</v>
+        <v>46230.58125</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Theft From Motor Vehicle</t>
+          <t>fraud-by-telephone</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5070,56 +5070,56 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>23F</t>
+          <t>white-collar-crime</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>6300 CARNEGIE BV</t>
+          <t>2 N ADAMS ST</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>35.15641923337007</v>
+        <v>39.71654731730718</v>
       </c>
       <c r="K41" t="n">
-        <v>-80.83429541207509</v>
+        <v>-104.9482864243138</v>
       </c>
       <c r="L41" t="n">
-        <v>613</v>
+        <v>384.1</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Theft from motor vehicle on Jul 26, 2026, 613 m from Southpark (6300 CARNEGIE BV). Status: Open. Case #20260726-0712-02 (use for a records request — full narratives are not published in open data).</t>
+          <t>Fraud-by-telephone on Jul 27, 2026, 384 m from Cherry Creek Shopping Center (2 N ADAMS ST). Victims: 1. Case #DP2026413635 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>20260726-0550-00</t>
+          <t>DP20266010142239900</t>
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>46228.16666666666</v>
+        <v>46230.10416666666</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Theft From Motor Vehicle</t>
+          <t>theft-other</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5129,233 +5129,233 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>23F</t>
+          <t>larceny</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>6700 FAIRVIEW RD</t>
+          <t>3444 E 2ND AVE</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>35.1479657453291</v>
+        <v>39.7193352135378</v>
       </c>
       <c r="K42" t="n">
-        <v>-80.82922688152722</v>
+        <v>-104.9468354191938</v>
       </c>
       <c r="L42" t="n">
-        <v>450.4</v>
+        <v>576.2</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Theft from motor vehicle on Jul 25, 2026, 450 m from Southpark (6700 FAIRVIEW RD). Status: Open. Case #20260726-0550-00 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-other on Jul 27, 2026, 576 m from Cherry Creek Shopping Center (3444 E 2ND AVE). Victims: 1. Case #DP20266010142 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>20260725-0853-00</t>
+          <t>DP2026413301299900</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>46228.16666666666</v>
+        <v>46229.95833333334</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aggravated Assault</t>
+          <t>criminal-mischief-other</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>13A</t>
+          <t>public-disorder</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5700 CARNEGIE BV</t>
+          <t>201 N UNIVERSITY BLVD</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>35.15368289092867</v>
+        <v>39.71957373655755</v>
       </c>
       <c r="K43" t="n">
-        <v>-80.8398453262274</v>
+        <v>-104.9597628432634</v>
       </c>
       <c r="L43" t="n">
-        <v>877.1</v>
+        <v>670.6</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 25, 2026, 877 m from Southpark (5700 CARNEGIE BV). Status: Open. Case #20260725-0853-00 (use for a records request — full narratives are not published in open data).</t>
+          <t>Criminal-mischief-other on Jul 26, 2026, 671 m from Cherry Creek Shopping Center (201 N UNIVERSITY BLVD). Victims: 1. Case #DP2026413301 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>20260726-0657-00</t>
+          <t>DP20266010143299900</t>
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>46228.16666666666</v>
+        <v>46229.9375</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Theft From Motor Vehicle</t>
+          <t>criminal-mischief-other</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>23F</t>
+          <t>public-disorder</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>5500 CARNEGIE BV</t>
+          <t>201 N UNIVERSITY BLVD</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>35.15375121029781</v>
+        <v>39.71957373655755</v>
       </c>
       <c r="K44" t="n">
-        <v>-80.83607576012871</v>
+        <v>-104.9597628432634</v>
       </c>
       <c r="L44" t="n">
-        <v>551.7</v>
+        <v>670.6</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Theft from motor vehicle on Jul 25, 2026, 552 m from Southpark (5500 CARNEGIE BV). Status: Open. Case #20260726-0657-00 (use for a records request — full narratives are not published in open data).</t>
+          <t>Criminal-mischief-other on Jul 26, 2026, 671 m from Cherry Creek Shopping Center (201 N UNIVERSITY BLVD). Victims: 1. Case #DP20266010143 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>20260725-1348-05</t>
+          <t>DP2026411044131300</t>
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>46228.16666666666</v>
+        <v>46229.1125</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>assault-simple</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>other-crimes-against-persons</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>3200 BLOCK E CHERRY CREEK S DR</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>35.15120046375475</v>
+        <v>39.71130989687384</v>
       </c>
       <c r="K45" t="n">
-        <v>-80.82867375349484</v>
+        <v>-104.9490029653731</v>
       </c>
       <c r="L45" t="n">
-        <v>178.9</v>
+        <v>696.3</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 25, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260725-1348-05 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault-simple on Jul 26, 2026, 696 m from Cherry Creek Shopping Center (3200 BLOCK E CHERRY CREEK S DR). Victims: 1. Case #DP2026411044 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>20260729-1053-01</t>
+          <t>DP2026411500220400</t>
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>46229.16666666666</v>
+        <v>46229.08333333334</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>All Other Thefts</t>
+          <t>burglary-residence-no-force</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -5365,56 +5365,56 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>23H</t>
+          <t>burglary</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>4500 SHARON RD</t>
+          <t>100 BLK N GARFIELD ST</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>35.15120046375475</v>
+        <v>39.71871773048673</v>
       </c>
       <c r="K46" t="n">
-        <v>-80.82867375349484</v>
+        <v>-104.9439679319565</v>
       </c>
       <c r="L46" t="n">
-        <v>178.9</v>
+        <v>779.5</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>All other thefts on Jul 26, 2026, 179 m from Southpark (4500 SHARON RD). Status: Open. Case #20260729-1053-01 (use for a records request — full narratives are not published in open data).</t>
+          <t>Burglary-residence-no-force on Jul 26, 2026, 779 m from Cherry Creek Shopping Center (100 BLK N GARFIELD ST). Victims: 1. Case #DP2026411500 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>20260727-1824-00</t>
+          <t>DP2026409833230500</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>46229.16666666666</v>
+        <v>46228.56944444445</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>theft-items-from-vehicle</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5424,26 +5424,26 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>theft-from-motor-vehicle</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>373 S JACKSON ST</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>35.15120046375475</v>
+        <v>39.70992379075913</v>
       </c>
       <c r="K47" t="n">
-        <v>-80.82867375349484</v>
+        <v>-104.9426513848476</v>
       </c>
       <c r="L47" t="n">
-        <v>178.9</v>
+        <v>1159</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 26, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260727-1824-00 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-items-from-vehicle on Jul 25, 2026, 1159 m from Cherry Creek Shopping Center (373 S JACKSON ST). Victims: 1. Case #DP2026409833 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>20260727-1945-02</t>
+          <t>20260725-2301-00</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
@@ -5473,36 +5473,36 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Other Unlisted Non-Criminal</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>899</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>6900 FAIRVIEW RD</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>35.15120046375475</v>
+        <v>35.14684118006692</v>
       </c>
       <c r="K48" t="n">
-        <v>-80.82867375349484</v>
+        <v>-80.82544759809264</v>
       </c>
       <c r="L48" t="n">
-        <v>178.9</v>
+        <v>722.6</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 25, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260727-1945-02 (use for a records request — full narratives are not published in open data).</t>
+          <t>Other unlisted non-criminal on Jul 25, 2026, 723 m from Southpark (6900 FAIRVIEW RD). Status: Open. Case #20260725-2301-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>20260726-1824-01</t>
+          <t>20260726-0712-02</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
@@ -5532,36 +5532,36 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>All Other Offenses</t>
+          <t>Theft From Motor Vehicle</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>90Z</t>
+          <t>23F</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>6300 CARNEGIE BV</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>35.15120046375475</v>
+        <v>35.15641923337007</v>
       </c>
       <c r="K49" t="n">
-        <v>-80.82867375349484</v>
+        <v>-80.83429541207509</v>
       </c>
       <c r="L49" t="n">
-        <v>178.9</v>
+        <v>613</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>All other offenses on Jul 26, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260726-1824-01 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft from motor vehicle on Jul 26, 2026, 613 m from Southpark (6300 CARNEGIE BV). Status: Open. Case #20260726-0712-02 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -5583,15 +5583,15 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>20260728-1922-01</t>
+          <t>20260726-0550-00</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>46231.16666666666</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Theft From Motor Vehicle</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5601,26 +5601,26 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>23F</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>6700 FAIRVIEW RD</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>35.15120046375475</v>
+        <v>35.1479657453291</v>
       </c>
       <c r="K50" t="n">
-        <v>-80.82867375349484</v>
+        <v>-80.82922688152722</v>
       </c>
       <c r="L50" t="n">
-        <v>178.9</v>
+        <v>450.4</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1922-01 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft from motor vehicle on Jul 25, 2026, 450 m from Southpark (6700 FAIRVIEW RD). Status: Open. Case #20260726-0550-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -5642,44 +5642,44 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>20260728-1130-01</t>
+          <t>20260725-0853-00</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>46231.16666666666</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>13A</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>5700 CARNEGIE BV</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>35.15120046375475</v>
+        <v>35.15368289092867</v>
       </c>
       <c r="K51" t="n">
-        <v>-80.82867375349484</v>
+        <v>-80.8398453262274</v>
       </c>
       <c r="L51" t="n">
-        <v>178.9</v>
+        <v>877.1</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1130-01 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 25, 2026, 877 m from Southpark (5700 CARNEGIE BV). Status: Open. Case #20260725-0853-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>20260726-0952-00</t>
+          <t>20260726-0657-00</t>
         </is>
       </c>
       <c r="E52" s="3" t="n">
@@ -5709,58 +5709,58 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>All Other Offenses</t>
+          <t>Theft From Motor Vehicle</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>90Z</t>
+          <t>23F</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>700 GOVERNOR MORRISON ST</t>
+          <t>5500 CARNEGIE BV</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>35.15648042297118</v>
+        <v>35.15375121029781</v>
       </c>
       <c r="K52" t="n">
-        <v>-80.82480681029648</v>
+        <v>-80.83607576012871</v>
       </c>
       <c r="L52" t="n">
-        <v>723.7</v>
+        <v>551.7</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>All other offenses on Jul 25, 2026, 724 m from Southpark (700 GOVERNOR MORRISON ST). Status: Open. Case #20260726-0952-00 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft from motor vehicle on Jul 25, 2026, 552 m from Southpark (5500 CARNEGIE BV). Status: Open. Case #20260726-0657-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CHARLOTTE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Charlotte Premium Outlets</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CHARLOTTE:CMPD Incidents</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>20260725-1934-03</t>
+          <t>20260725-1348-05</t>
         </is>
       </c>
       <c r="E53" s="3" t="n">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>All Other Thefts</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5778,56 +5778,56 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>23H</t>
+          <t>23C</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>4900 TROJAN DR</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>35.16474336144204</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K53" t="n">
-        <v>-80.96762879799847</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L53" t="n">
-        <v>443.5</v>
+        <v>178.9</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>All other thefts on Jul 25, 2026, 444 m from Charlotte Premium Outlets (4900 TROJAN DR). Status: Open. Case #20260725-1934-03 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 25, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260725-1348-05 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CHARLOTTE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Charlotte Premium Outlets</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CHARLOTTE:CMPD Incidents</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>20260729-1434-02</t>
+          <t>20260729-1053-01</t>
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>46231.16666666666</v>
+        <v>46229.16666666666</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Damage/Vandalism Of Property</t>
+          <t>All Other Thefts</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5837,56 +5837,56 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>23H</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>5600 KELTONWOOD RD</t>
+          <t>4500 SHARON RD</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>35.16655081611235</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K54" t="n">
-        <v>-80.97476086867614</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L54" t="n">
-        <v>496.6</v>
+        <v>178.9</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Damage/vandalism of property on Jul 28, 2026, 497 m from Charlotte Premium Outlets (5600 KELTONWOOD RD). Status: Open. Case #20260729-1434-02 (use for a records request — full narratives are not published in open data).</t>
+          <t>All other thefts on Jul 26, 2026, 179 m from Southpark (4500 SHARON RD). Status: Open. Case #20260729-1053-01 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>26C140260</t>
+          <t>20260727-1824-00</t>
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>46228.77152777778</v>
+        <v>46229.16666666666</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>LARCENY B SHOPLIFT</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5896,166 +5896,174 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>LARCENY</t>
+          <t>23C</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG ST</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>37.67911394923933</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K55" t="n">
-        <v>-97.24743308095542</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L55" t="n">
-        <v>398.7</v>
+        <v>178.9</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Larceny b shoplift on Jul 25, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C140260 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 26, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260727-1824-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>26C140486</t>
+          <t>20260727-1945-02</t>
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>46228.51944444444</v>
-      </c>
-      <c r="F56" t="inlineStr"/>
+        <v>46228.16666666666</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>23C</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG ST</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>37.67911394923933</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K56" t="n">
-        <v>-97.24743308095542</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L56" t="n">
-        <v>398.7</v>
+        <v>178.9</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Incident on Jul 25, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C140486 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 25, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260727-1945-02 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>26C143336</t>
+          <t>20260726-1824-01</t>
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>46232.7125</v>
+        <v>46229.16666666666</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>TRESPASS</t>
+          <t>All Other Offenses</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>QUALITY_OF_LIFE</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>MISC_OFFENSES</t>
+          <t>90Z</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG ST</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>37.67911394923933</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K57" t="n">
-        <v>-97.24743308095542</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L57" t="n">
-        <v>398.7</v>
+        <v>178.9</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Trespass on Jul 29, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C143336 (use for a records request — full narratives are not published in open data).</t>
+          <t>All other offenses on Jul 26, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260726-1824-01 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>26C520577</t>
+          <t>20260728-1922-01</t>
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>46227.71388888889</v>
+        <v>46231.16666666666</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SUSPICIOUS CHARACTER LARCENY UNIT</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -6065,56 +6073,56 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>SUSP_CHARAC</t>
+          <t>23C</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG DR</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>37.67911394923933</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K58" t="n">
-        <v>-97.24743308095542</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L58" t="n">
-        <v>398.7</v>
+        <v>178.9</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Suspicious character larceny unit on Jul 24, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG DR). Case #26C520577 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1922-01 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>26C520675</t>
+          <t>20260728-1130-01</t>
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>46227.84236111111</v>
+        <v>46231.16666666666</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>LARCENY B SHOPLIFT</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -6124,56 +6132,56 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>LARCENY</t>
+          <t>23C</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG DR</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>37.67911394923933</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K59" t="n">
-        <v>-97.24743308095542</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L59" t="n">
-        <v>398.7</v>
+        <v>178.9</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Larceny b shoplift on Jul 24, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG DR). Case #26C520675 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1130-01 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>26C142785</t>
+          <t>20260725-1137-00</t>
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>46231.96458333333</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>EVADE POLICE</t>
+          <t>Suicide</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -6183,56 +6191,56 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>DRIVING_VIO</t>
+          <t>801</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>E KELLOGG DR &amp; S ROCK RD</t>
+          <t>5600 FAIRVIEW RD</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>37.67911842691625</v>
+        <v>35.15235596527605</v>
       </c>
       <c r="K60" t="n">
-        <v>-97.24451202953301</v>
+        <v>-80.84558404556884</v>
       </c>
       <c r="L60" t="n">
-        <v>473.3</v>
+        <v>1376.8</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Evade police on Jul 28, 2026, 473 m from Towne East Square (E KELLOGG DR &amp; S ROCK RD). Case #26C142785 (use for a records request — full narratives are not published in open data).</t>
+          <t>Suicide on Jul 25, 2026, 1377 m from Southpark (5600 FAIRVIEW RD). Status: Open. Case #20260725-1137-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>26C141216</t>
+          <t>20260726-0952-00</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>46229.90069444444</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CHECKED WELFARE OF A CHILD</t>
+          <t>All Other Offenses</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -6242,115 +6250,115 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>FAMILY</t>
+          <t>90Z</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>7300 BLOCK OF E KELLOGG ST</t>
+          <t>700 GOVERNOR MORRISON ST</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>37.67974587023429</v>
+        <v>35.15648042297118</v>
       </c>
       <c r="K61" t="n">
-        <v>-97.25225228651782</v>
+        <v>-80.82480681029648</v>
       </c>
       <c r="L61" t="n">
-        <v>537.4</v>
+        <v>723.7</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Checked welfare of a child on Jul 26, 2026, 537 m from Towne East Square (7300 BLOCK OF E KELLOGG ST). Case #26C141216 (use for a records request — full narratives are not published in open data).</t>
+          <t>All other offenses on Jul 25, 2026, 724 m from Southpark (700 GOVERNOR MORRISON ST). Status: Open. Case #20260726-0952-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>CHARLOTTE</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Charlotte Premium Outlets</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>CHARLOTTE:CMPD Incidents</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>26C141683</t>
+          <t>20260725-0631-00</t>
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>46230.58541666667</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MISC OFFICERS</t>
+          <t>Drug/Narcotic Violations</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>QUALITY_OF_LIFE</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>OUTSIDE_CASE</t>
+          <t>35A</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>8100 BLOCK OF E KELLOGG ST</t>
+          <t>8300 STEELE CREEK RD</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>37.6797148529391</v>
+        <v>35.17291837763486</v>
       </c>
       <c r="K62" t="n">
-        <v>-97.24233946631864</v>
+        <v>-80.95939837774333</v>
       </c>
       <c r="L62" t="n">
-        <v>556.7</v>
+        <v>1070.3</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Misc officers on Jul 27, 2026, 557 m from Towne East Square (8100 BLOCK OF E KELLOGG ST). Case #26C141683 (use for a records request — full narratives are not published in open data).</t>
+          <t>Drug/narcotic violations on Jul 25, 2026, 1070 m from Charlotte Premium Outlets (8300 STEELE CREEK RD). Status: Open. Case #20260725-0631-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>CHARLOTTE</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Charlotte Premium Outlets</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>CHARLOTTE:CMPD Incidents</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>26C143446</t>
+          <t>20260725-1934-03</t>
         </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v>46232.7125</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>LARCENY B SHOPLIFT</t>
+          <t>All Other Thefts</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -6360,56 +6368,56 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>LARCENY</t>
+          <t>23H</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG ST</t>
+          <t>4900 TROJAN DR</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>37.67911394923933</v>
+        <v>35.16474336144204</v>
       </c>
       <c r="K63" t="n">
-        <v>-97.24743308095542</v>
+        <v>-80.96762879799847</v>
       </c>
       <c r="L63" t="n">
-        <v>398.7</v>
+        <v>443.5</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Larceny b shoplift on Jul 29, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C143446 (use for a records request — full narratives are not published in open data).</t>
+          <t>All other thefts on Jul 25, 2026, 444 m from Charlotte Premium Outlets (4900 TROJAN DR). Status: Open. Case #20260725-1934-03 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>CHARLOTTE</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Charlotte Premium Outlets</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>CHARLOTTE:CMPD Incidents</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>26C144013</t>
+          <t>20260729-1434-02</t>
         </is>
       </c>
       <c r="E64" s="3" t="n">
-        <v>46233.63055555556</v>
+        <v>46231.16666666666</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>LARCENY B SHOPLIFT</t>
+          <t>Damage/Vandalism Of Property</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -6419,26 +6427,26 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>LARCENY</t>
+          <t>290</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG DR</t>
+          <t>5600 KELTONWOOD RD</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>37.67911394923933</v>
+        <v>35.16655081611235</v>
       </c>
       <c r="K64" t="n">
-        <v>-97.24743308095542</v>
+        <v>-80.97476086867614</v>
       </c>
       <c r="L64" t="n">
-        <v>398.7</v>
+        <v>496.6</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Larceny b shoplift on Jul 30, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG DR). Case #26C144013 (use for a records request — full narratives are not published in open data).</t>
+          <t>Damage/vandalism of property on Jul 28, 2026, 497 m from Charlotte Premium Outlets (5600 KELTONWOOD RD). Status: Open. Case #20260729-1434-02 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6460,44 +6468,44 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>26C144067</t>
+          <t>26C139456</t>
         </is>
       </c>
       <c r="E65" s="3" t="n">
-        <v>46232.71180555555</v>
+        <v>46227.42226851852</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>PRVT PROP NON-INJURY ACCIDENT</t>
+          <t>SUSPICIOUS CHARACTER BURGLARY UNIT</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>TRAFFIC</t>
+          <t>SUSP_CHARAC</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>8000 BLOCK OF E DOUGLAS AVE</t>
+          <t>7200 BLOCK OF E LINCOLN ST</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>37.6865673723019</v>
+        <v>37.67196805016872</v>
       </c>
       <c r="K65" t="n">
-        <v>-97.24449812404205</v>
+        <v>-97.25239793155058</v>
       </c>
       <c r="L65" t="n">
-        <v>501</v>
+        <v>1271.2</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Prvt prop non-injury accident on Jul 29, 2026, 501 m from Towne East Square (8000 BLOCK OF E DOUGLAS AVE). Case #26C144067 (use for a records request — full narratives are not published in open data).</t>
+          <t>Suspicious character burglary unit on Jul 24, 2026, 1271 m from Towne East Square (7200 BLOCK OF E LINCOLN ST). Case #26C139456 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6519,44 +6527,44 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>26C143812</t>
+          <t>26C139724</t>
         </is>
       </c>
       <c r="E66" s="3" t="n">
-        <v>46232.88888888889</v>
+        <v>46227.69421296296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>OTV-HIT AND RUN</t>
+          <t>BATTERY DV</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>OTHERTRAF_VIO</t>
+          <t>SIM_ASSAULT</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>400 BLOCK OF S ROCK RD</t>
+          <t>600 BLOCK OF S EASTERN AVE</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>37.68150034571348</v>
+        <v>37.6774046653855</v>
       </c>
       <c r="K66" t="n">
-        <v>-97.24450622724754</v>
+        <v>-97.23656061094495</v>
       </c>
       <c r="L66" t="n">
-        <v>288.9</v>
+        <v>1122.4</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Otv-hit and run on Jul 29, 2026, 289 m from Towne East Square (400 BLOCK OF S ROCK RD). Case #26C143812 (use for a records request — full narratives are not published in open data).</t>
+          <t>Battery dv on Jul 24, 2026, 1122 m from Towne East Square (600 BLOCK OF S EASTERN AVE). Case #26C139724 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6578,19 +6586,27 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>26C139706</t>
+          <t>26C140260</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>46227.66875</v>
-      </c>
-      <c r="F67" t="inlineStr"/>
+        <v>46228.77152777778</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>LARCENY B SHOPLIFT</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>LARCENY</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr">
         <is>
           <t>7700 BLOCK OF E KELLOGG ST</t>
@@ -6607,7 +6623,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Incident on Jul 24, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C139706 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny b shoplift on Jul 25, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C140260 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6629,44 +6645,36 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>26C142387</t>
+          <t>26C140486</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
-        <v>46230.81597222222</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>PRVT PROP NON-INJURY ACCIDENT</t>
-        </is>
-      </c>
+        <v>46228.51944444444</v>
+      </c>
+      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
           <t>OTHER</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>TRAFFIC</t>
-        </is>
-      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>100 BLOCK OF S ROCK RD</t>
+          <t>7700 BLOCK OF E KELLOGG ST</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>37.6865673723019</v>
+        <v>37.67911394923933</v>
       </c>
       <c r="K68" t="n">
-        <v>-97.24449812404205</v>
+        <v>-97.24743308095542</v>
       </c>
       <c r="L68" t="n">
-        <v>501</v>
+        <v>398.7</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Prvt prop non-injury accident on Jul 27, 2026, 501 m from Towne East Square (100 BLOCK OF S ROCK RD). Case #26C142387 (use for a records request — full narratives are not published in open data).</t>
+          <t>Incident on Jul 25, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C140486 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6688,44 +6696,44 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>26C520282</t>
+          <t>26C143336</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>46231.625</v>
+        <v>46232.7125</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>LOST MISC PROPERTY</t>
+          <t>TRESPASS</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>QUALITY_OF_LIFE</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>LOST_PROPERTY</t>
+          <t>MISC_OFFENSES</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>7000 BLOCK OF E KELLOGG ST</t>
+          <t>7700 BLOCK OF E KELLOGG ST</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>37.67951495831583</v>
+        <v>37.67911394923933</v>
       </c>
       <c r="K69" t="n">
-        <v>-97.25782989544317</v>
+        <v>-97.24743308095542</v>
       </c>
       <c r="L69" t="n">
-        <v>982.3</v>
+        <v>398.7</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Lost misc property on Jul 28, 2026, 982 m from Towne East Square (7000 BLOCK OF E KELLOGG ST). Case #26C520282 (use for a records request — full narratives are not published in open data).</t>
+          <t>Trespass on Jul 29, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C143336 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6747,44 +6755,44 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>26C520741</t>
+          <t>26C143989</t>
         </is>
       </c>
       <c r="E70" s="3" t="n">
-        <v>46228.86111111111</v>
+        <v>46233.61180555556</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>LARCENY B AUTO ACCESSORIES</t>
+          <t>MISC REPORT</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>LARCENY</t>
+          <t>MISC_REPORT</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG DR</t>
+          <t>700 BLOCK OF S APACHE DR</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>37.67911394923933</v>
+        <v>37.67384327067582</v>
       </c>
       <c r="K70" t="n">
-        <v>-97.24743308095542</v>
+        <v>-97.25634062142737</v>
       </c>
       <c r="L70" t="n">
-        <v>398.7</v>
+        <v>1259.5</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Larceny b auto accessories on Jul 25, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG DR). Case #26C520741 (use for a records request — full narratives are not published in open data).</t>
+          <t>Misc report on Jul 30, 2026, 1260 m from Towne East Square (700 BLOCK OF S APACHE DR). Case #26C143989 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6806,459 +6814,487 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>26C520933</t>
+          <t>26C144045</t>
         </is>
       </c>
       <c r="E71" s="3" t="n">
-        <v>46230.6125</v>
+        <v>46233.65833333333</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>LARCENY B SHOPLIFT</t>
+          <t>DEAD BODIES FOUND NO WITNESS</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>LARCENY</t>
+          <t>SUDDEN_DEATH</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG ST</t>
+          <t>700 BLOCK OF S EASTRIDGE DR</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>37.67911394923933</v>
+        <v>37.67625582907724</v>
       </c>
       <c r="K71" t="n">
-        <v>-97.24743308095542</v>
+        <v>-97.25926072916232</v>
       </c>
       <c r="L71" t="n">
-        <v>398.7</v>
+        <v>1264.7</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Larceny b shoplift on Jul 27, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C520933 (use for a records request — full narratives are not published in open data).</t>
+          <t>Dead bodies found no witness on Jul 30, 2026, 1265 m from Towne East Square (700 BLOCK OF S EASTRIDGE DR). Case #26C144045 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202675652         </t>
+          <t>26C520577</t>
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>46230.77569444444</v>
+        <v>46227.71388888889</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">[13B] ASSAULT [DV]                                                              </t>
+          <t>SUSPICIOUS CHARACTER LARCENY UNIT</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>SUSP_CHARAC</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>5XXX S ARIZONA MILLS CIR</t>
+          <t>7700 BLOCK OF E KELLOGG DR</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>33.38314167531927</v>
+        <v>37.67911394923933</v>
       </c>
       <c r="K72" t="n">
-        <v>-111.9645674529712</v>
+        <v>-97.24743308095542</v>
       </c>
       <c r="L72" t="n">
-        <v>14.7</v>
+        <v>398.7</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>[13b] assault [dv] on Jul 27, 2026, 15 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675652          (use for a records request — full narratives are not published in open data).</t>
+          <t>Suspicious character larceny unit on Jul 24, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG DR). Case #26C520577 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202674996         </t>
+          <t>26C520675</t>
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>46228.65694444445</v>
+        <v>46227.84236111111</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SC-0] INFO - INFORMATION OTHER (NON-CRIMINAL)                                  </t>
+          <t>LARCENY B SHOPLIFT</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>LARCENY</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>5XXX S ARIZONA MILLS CIR</t>
+          <t>7700 BLOCK OF E KELLOGG DR</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>33.38314167531927</v>
+        <v>37.67911394923933</v>
       </c>
       <c r="K73" t="n">
-        <v>-111.9645674529712</v>
+        <v>-97.24743308095542</v>
       </c>
       <c r="L73" t="n">
-        <v>14.7</v>
+        <v>398.7</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>[sc-0] info - information other (non-criminal) on Jul 25, 2026, 15 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202674996          (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny b shoplift on Jul 24, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG DR). Case #26C520675 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202674783         </t>
+          <t>26C520776</t>
         </is>
       </c>
       <c r="E74" s="3" t="n">
-        <v>46227.91319444445</v>
+        <v>46229.45833333334</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">[13B] ASSAULT                                                                   </t>
+          <t>AUTO THEFT</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>AUTOTHEFT</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>5XXX S ARIZONA MILLS CIR</t>
+          <t>500 BLOCK OF N ROCK RD</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>33.38314167531927</v>
+        <v>37.6938385342284</v>
       </c>
       <c r="K74" t="n">
-        <v>-111.9645674529712</v>
+        <v>-97.24455420498546</v>
       </c>
       <c r="L74" t="n">
-        <v>14.7</v>
+        <v>1264</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>[13b] assault on Jul 24, 2026, 15 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202674783          (use for a records request — full narratives are not published in open data).</t>
+          <t>Auto theft on Jul 26, 2026, 1264 m from Towne East Square (500 BLOCK OF N ROCK RD). Case #26C520776 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202675415         </t>
+          <t>26C139721</t>
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>46229.95</v>
+        <v>46227.625</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">[90J] TRESPASSING                                                               </t>
+          <t>OTV-HIT AND RUN</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>QUALITY_OF_LIFE</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr"/>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>OTHERTRAF_VIO</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>5XXX S ARIZONA MILLS CIR</t>
+          <t>E LINCOLN ST &amp; S ROCK RD</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>33.38341075529574</v>
+        <v>37.67198361320128</v>
       </c>
       <c r="K75" t="n">
-        <v>-111.9652490281131</v>
+        <v>-97.24446143278816</v>
       </c>
       <c r="L75" t="n">
-        <v>68.59999999999999</v>
+        <v>1219.7</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>[90j] trespassing on Jul 26, 2026, 69 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675415          (use for a records request — full narratives are not published in open data).</t>
+          <t>Otv-hit and run on Jul 24, 2026, 1220 m from Towne East Square (E LINCOLN ST &amp; S ROCK RD). Case #26C139721 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202675399         </t>
+          <t>26C139922</t>
         </is>
       </c>
       <c r="E76" s="3" t="n">
-        <v>46229.9</v>
+        <v>46227.95277777778</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
+          <t>BATTERY ABW</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>SIM_ASSAULT</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>5XXX S ARIZONA MILLS CIR</t>
+          <t>7000 BLOCK OF E LINCOLN ST</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>33.38552975305072</v>
+        <v>37.67195398477438</v>
       </c>
       <c r="K76" t="n">
-        <v>-111.965328834686</v>
+        <v>-97.25533959083543</v>
       </c>
       <c r="L76" t="n">
-        <v>262</v>
+        <v>1383.4</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>[sc-0] trespass warning - private property on Jul 26, 2026, 262 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675399          (use for a records request — full narratives are not published in open data).</t>
+          <t>Battery abw on Jul 24, 2026, 1383 m from Towne East Square (7000 BLOCK OF E LINCOLN ST). Case #26C139922 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202676101         </t>
+          <t>26C140815</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
-        <v>46232.21041666667</v>
+        <v>46229.30625</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">[240] MOTOR VEHICLE THEFT                                                       </t>
+          <t>MISC REPORT</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>MISC_REPORT</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>5XXX S ARIZONA MILLS CIR</t>
+          <t>900 BLOCK OF S APACHE DR</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>33.38580430470485</v>
+        <v>37.67195267201163</v>
       </c>
       <c r="K77" t="n">
-        <v>-111.9660628528483</v>
+        <v>-97.25741761429009</v>
       </c>
       <c r="L77" t="n">
-        <v>315.7</v>
+        <v>1484.1</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>[240] motor vehicle theft on Jul 29, 2026, 316 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202676101          (use for a records request — full narratives are not published in open data).</t>
+          <t>Misc report on Jul 26, 2026, 1484 m from Towne East Square (900 BLOCK OF S APACHE DR). Case #26C140815 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202676030         </t>
+          <t>26C142785</t>
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>46231.83194444444</v>
+        <v>46231.96458333333</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
+          <t>EVADE POLICE</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>DRIVING_VIO</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>5XXX S ARIZONA MILLS CIR</t>
+          <t>E KELLOGG DR &amp; S ROCK RD</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>33.3805974892332</v>
+        <v>37.67911842691625</v>
       </c>
       <c r="K78" t="n">
-        <v>-111.9623154538272</v>
+        <v>-97.24451202953301</v>
       </c>
       <c r="L78" t="n">
-        <v>361.4</v>
+        <v>473.3</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>[sc-0] trespass warning - private property on Jul 28, 2026, 361 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202676030          (use for a records request — full narratives are not published in open data).</t>
+          <t>Evade police on Jul 28, 2026, 473 m from Towne East Square (E KELLOGG DR &amp; S ROCK RD). Case #26C142785 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202674893         </t>
+          <t>26C142917</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>46228.35972222222</v>
+        <v>46232.18194444444</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">[GO-0] ASSIST OTHER AGENCY                                                      </t>
+          <t>WINDOWPEEPING</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -7266,54 +7302,58 @@
           <t>OTHER</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>SEX_OFFENSES1</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>4XXX S WENDLER DR</t>
+          <t>700 BLOCK OF S HUNTER ST</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>33.38130369903515</v>
+        <v>37.67688443377517</v>
       </c>
       <c r="K79" t="n">
-        <v>-111.9695754725762</v>
+        <v>-97.26003808987583</v>
       </c>
       <c r="L79" t="n">
-        <v>517</v>
+        <v>1285.1</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>[go-0] assist other agency on Jul 25, 2026, 517 m from Arizona Mills (4XXX S WENDLER DR). Case #TE202674893          (use for a records request — full narratives are not published in open data).</t>
+          <t>Windowpeeping on Jul 29, 2026, 1285 m from Towne East Square (700 BLOCK OF S HUNTER ST). Case #26C142917 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202675649         </t>
+          <t>26C141216</t>
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>46230.76944444444</v>
+        <v>46229.90069444444</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SC-0] WELFARE CHECK                                                            </t>
+          <t>CHECKED WELFARE OF A CHILD</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -7321,56 +7361,56 @@
           <t>OTHER</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>FAMILY</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>4XXX S DARROW DR</t>
+          <t>7300 BLOCK OF E KELLOGG ST</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>33.38128291577831</v>
+        <v>37.67974587023429</v>
       </c>
       <c r="K80" t="n">
-        <v>-111.9593051545489</v>
+        <v>-97.25225228651782</v>
       </c>
       <c r="L80" t="n">
-        <v>533.1</v>
+        <v>537.4</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>[sc-0] welfare check on Jul 27, 2026, 533 m from Arizona Mills (4XXX S DARROW DR). Case #TE202675649          (use for a records request — full narratives are not published in open data).</t>
+          <t>Checked welfare of a child on Jul 26, 2026, 537 m from Towne East Square (7300 BLOCK OF E KELLOGG ST). Case #26C141216 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202674654         </t>
+          <t>26C143148</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>46227.62708333333</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[GO-0] ACCIDENT - HIT AND RUN                                                   </t>
-        </is>
-      </c>
+        <v>46232.52430555555</v>
+      </c>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
           <t>OTHER</t>
@@ -7379,106 +7419,110 @@
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>BASELINE RD / S DARROW DR</t>
+          <t>900 BLOCK OF S ENOCH DR</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>33.37825351544224</v>
+        <v>37.67197658912259</v>
       </c>
       <c r="K81" t="n">
-        <v>-111.9611381808533</v>
+        <v>-97.2456018407935</v>
       </c>
       <c r="L81" t="n">
-        <v>640.6</v>
+        <v>1203</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>[go-0] accident - hit and run on Jul 24, 2026, 641 m from Arizona Mills (BASELINE RD / S DARROW DR). Case #TE202674654          (use for a records request — full narratives are not published in open data).</t>
+          <t>Incident on Jul 29, 2026, 1203 m from Towne East Square (900 BLOCK OF S ENOCH DR). Case #26C143148 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202675235         </t>
+          <t>26C141683</t>
         </is>
       </c>
       <c r="E82" s="3" t="n">
-        <v>46229.31597222222</v>
+        <v>46230.58541666667</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PUBLIC PLACES                                         </t>
+          <t>MISC OFFICERS</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>QUALITY_OF_LIFE</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr"/>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>OUTSIDE_CASE</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>BASELINE RD / I10</t>
+          <t>8100 BLOCK OF E KELLOGG ST</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>33.37824262058852</v>
+        <v>37.6797148529391</v>
       </c>
       <c r="K82" t="n">
-        <v>-111.9680044627475</v>
+        <v>-97.24233946631864</v>
       </c>
       <c r="L82" t="n">
-        <v>645.4</v>
+        <v>556.7</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>[sc-0] trespass warning - public places on Jul 26, 2026, 645 m from Arizona Mills (BASELINE RD / I10). Case #TE202675235          (use for a records request — full narratives are not published in open data).</t>
+          <t>Misc officers on Jul 27, 2026, 557 m from Towne East Square (8100 BLOCK OF E KELLOGG ST). Case #26C141683 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202675001         </t>
+          <t>26C143446</t>
         </is>
       </c>
       <c r="E83" s="3" t="n">
-        <v>46228.66944444444</v>
+        <v>46232.7125</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
+          <t>LARCENY B SHOPLIFT</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -7486,249 +7530,2918 @@
           <t>PROPERTY</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>LARCENY</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>1XXX W BASELINE RD</t>
+          <t>7700 BLOCK OF E KELLOGG ST</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>33.377865729326</v>
+        <v>37.67911394923933</v>
       </c>
       <c r="K83" t="n">
-        <v>-111.9618554026273</v>
+        <v>-97.24743308095542</v>
       </c>
       <c r="L83" t="n">
-        <v>650.2</v>
+        <v>398.7</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>[sc-0] trespass warning - private property on Jul 25, 2026, 650 m from Arizona Mills (1XXX W BASELINE RD). Case #TE202675001          (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny b shoplift on Jul 29, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C143446 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202676035         </t>
+          <t>26C144013</t>
         </is>
       </c>
       <c r="E84" s="3" t="n">
-        <v>46231.85555555556</v>
+        <v>46233.63055555556</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SC-0] SERVICE - ORDER OF PROTECTION (OOP) / INJUNCTION (P1)                    </t>
+          <t>LARCENY B SHOPLIFT</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>LARCENY</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>1XXX W LA JOLLA DR</t>
+          <t>7700 BLOCK OF E KELLOGG DR</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>33.38909587497265</v>
+        <v>37.67911394923933</v>
       </c>
       <c r="K84" t="n">
-        <v>-111.961540133513</v>
+        <v>-97.24743308095542</v>
       </c>
       <c r="L84" t="n">
-        <v>704.8</v>
+        <v>398.7</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>[sc-0] service - order of protection (oop) / injunction (p1) on Jul 28, 2026, 705 m from Arizona Mills (1XXX W LA JOLLA DR). Case #TE202676035          (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny b shoplift on Jul 30, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG DR). Case #26C144013 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202675946         </t>
+          <t>26C144067</t>
         </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v>46231.63888888889</v>
+        <v>46232.71180555555</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
+          <t>PRVT PROP NON-INJURY ACCIDENT</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>TRAFFIC</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>1XXX W BASELINE RD</t>
+          <t>8000 BLOCK OF E DOUGLAS AVE</t>
         </is>
       </c>
       <c r="J85" t="n">
-        <v>33.37795738260824</v>
+        <v>37.6865673723019</v>
       </c>
       <c r="K85" t="n">
-        <v>-111.959149564986</v>
+        <v>-97.24449812404205</v>
       </c>
       <c r="L85" t="n">
-        <v>773.7</v>
+        <v>501</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>[sc-0] trespass warning - private property on Jul 28, 2026, 774 m from Arizona Mills (1XXX W BASELINE RD). Case #TE202675946          (use for a records request — full narratives are not published in open data).</t>
+          <t>Prvt prop non-injury accident on Jul 29, 2026, 501 m from Towne East Square (8000 BLOCK OF E DOUGLAS AVE). Case #26C144067 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202674935         </t>
+          <t>26C142294</t>
         </is>
       </c>
       <c r="E86" s="3" t="n">
-        <v>46228.47222222222</v>
+        <v>46231.42847222222</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SC-0] ASSIST - MENTALLY ILL (OTHER THAN MHP/EMHETR)                            </t>
+          <t>FOUND MISC PROPERTY</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>FOUND_PROP</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>1XXX W BASELINE RD</t>
+          <t>700 BLOCK OF S MISSION RD</t>
         </is>
       </c>
       <c r="J86" t="n">
-        <v>33.37594547787401</v>
+        <v>37.6756469679485</v>
       </c>
       <c r="K86" t="n">
-        <v>-111.9593287567214</v>
+        <v>-97.25850032865422</v>
       </c>
       <c r="L86" t="n">
-        <v>946.9</v>
+        <v>1251.5</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>[sc-0] assist - mentally ill (other than mhp/emhetr) on Jul 25, 2026, 947 m from Arizona Mills (1XXX W BASELINE RD). Case #TE202674935          (use for a records request — full narratives are not published in open data).</t>
+          <t>Found misc property on Jul 28, 2026, 1251 m from Towne East Square (700 BLOCK OF S MISSION RD). Case #26C142294 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>26C144131</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>46233.7625</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>MISC REPORT</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>MISC_REPORT</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>E BAYLEY ST &amp; S GOVERNEOUR RD</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>37.67014134415807</v>
+      </c>
+      <c r="K87" t="n">
+        <v>-97.25360392908074</v>
+      </c>
+      <c r="L87" t="n">
+        <v>1498.8</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Misc report on Jul 30, 2026, 1499 m from Towne East Square (E BAYLEY ST &amp; S GOVERNEOUR RD). Case #26C144131 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>26C143812</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>46232.88888888889</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>OTV-HIT AND RUN</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>OTHERTRAF_VIO</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>400 BLOCK OF S ROCK RD</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>37.68150034571348</v>
+      </c>
+      <c r="K88" t="n">
+        <v>-97.24450622724754</v>
+      </c>
+      <c r="L88" t="n">
+        <v>288.9</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Otv-hit and run on Jul 29, 2026, 289 m from Towne East Square (400 BLOCK OF S ROCK RD). Case #26C143812 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>26C139586</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>46227.55138888889</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>MISC REPORT</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>MISC_REPORT</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>600 BLOCK OF S EASTERN AVE</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>37.6774046653855</v>
+      </c>
+      <c r="K89" t="n">
+        <v>-97.23656061094495</v>
+      </c>
+      <c r="L89" t="n">
+        <v>1122.4</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Misc report on Jul 24, 2026, 1122 m from Towne East Square (600 BLOCK OF S EASTERN AVE). Case #26C139586 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>26C144101</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>46233.72152777778</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>MISC REPORT</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>MISC_REPORT</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>600 BLOCK OF S APACHE DR</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>37.67516836949827</v>
+      </c>
+      <c r="K90" t="n">
+        <v>-97.25367616461408</v>
+      </c>
+      <c r="L90" t="n">
+        <v>1002.3</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Misc report on Jul 30, 2026, 1002 m from Towne East Square (600 BLOCK OF S APACHE DR). Case #26C144101 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>26C139706</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>46227.66875</v>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>7700 BLOCK OF E KELLOGG ST</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>37.67911394923933</v>
+      </c>
+      <c r="K91" t="n">
+        <v>-97.24743308095542</v>
+      </c>
+      <c r="L91" t="n">
+        <v>398.7</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Incident on Jul 24, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C139706 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>26C141863</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>46230.75486111111</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>RUNAWAY</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>MISC_OFFENSES</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>700 BLOCK OF S HUNTER ST</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>37.67688443377517</v>
+      </c>
+      <c r="K92" t="n">
+        <v>-97.26003808987583</v>
+      </c>
+      <c r="L92" t="n">
+        <v>1285.1</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Runaway on Jul 27, 2026, 1285 m from Towne East Square (700 BLOCK OF S HUNTER ST). Case #26C141863 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>26C142249</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>46230.75</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>BATTERY ABW</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>SIM_ASSAULT</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>700 BLOCK OF S MISSION RD</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>37.6756469679485</v>
+      </c>
+      <c r="K93" t="n">
+        <v>-97.25850032865422</v>
+      </c>
+      <c r="L93" t="n">
+        <v>1251.5</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Battery abw on Jul 27, 2026, 1251 m from Towne East Square (700 BLOCK OF S MISSION RD). Case #26C142249 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>26C142387</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>46230.81597222222</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>PRVT PROP NON-INJURY ACCIDENT</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>TRAFFIC</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>100 BLOCK OF S ROCK RD</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>37.6865673723019</v>
+      </c>
+      <c r="K94" t="n">
+        <v>-97.24449812404205</v>
+      </c>
+      <c r="L94" t="n">
+        <v>501</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Prvt prop non-injury accident on Jul 27, 2026, 501 m from Towne East Square (100 BLOCK OF S ROCK RD). Case #26C142387 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>26C142657</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>46231.79166666666</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>INTERFERENCE W PARENTAL CUSTODY</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>MISC_OFFENSES</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>900 BLOCK OF S ENOCH DR</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>37.67197658912259</v>
+      </c>
+      <c r="K95" t="n">
+        <v>-97.2456018407935</v>
+      </c>
+      <c r="L95" t="n">
+        <v>1203</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Interference w parental custody on Jul 28, 2026, 1203 m from Towne East Square (900 BLOCK OF S ENOCH DR). Case #26C142657 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>26C142768</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>46231.94305555556</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>CHECKED WELFARE OF A CHILD</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>FAMILY</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>6500 BLOCK OF E MORRIS ST</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>37.67377815761698</v>
+      </c>
+      <c r="K96" t="n">
+        <v>-97.2605034310844</v>
+      </c>
+      <c r="L96" t="n">
+        <v>1519.9</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Checked welfare of a child on Jul 28, 2026, 1520 m from Towne East Square (6500 BLOCK OF E MORRIS ST). Case #26C142768 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>26C143218</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>46232.58333333334</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>DISTURB THE PEACE</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>DISORDERLY</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>700 BLOCK OF S HUNTER ST</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>37.67688443377517</v>
+      </c>
+      <c r="K97" t="n">
+        <v>-97.26003808987583</v>
+      </c>
+      <c r="L97" t="n">
+        <v>1285.1</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Disturb the peace on Jul 29, 2026, 1285 m from Towne East Square (700 BLOCK OF S HUNTER ST). Case #26C143218 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>26C143562</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>46232.93958333333</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>MENTAL CASES</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>MENTAL_CASE</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>600 BLOCK OF S EASTERN AVE</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>37.6774046653855</v>
+      </c>
+      <c r="K98" t="n">
+        <v>-97.23656061094495</v>
+      </c>
+      <c r="L98" t="n">
+        <v>1122.4</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Mental cases on Jul 29, 2026, 1122 m from Towne East Square (600 BLOCK OF S EASTERN AVE). Case #26C143562 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>26C143576</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>46232.96111111111</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>MISC REPORT</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>MISC_REPORT</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>7500 BLOCK OF E LINCOLN ST</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>37.67197300274878</v>
+      </c>
+      <c r="K99" t="n">
+        <v>-97.24902708647107</v>
+      </c>
+      <c r="L99" t="n">
+        <v>1201.1</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Misc report on Jul 29, 2026, 1201 m from Towne East Square (7500 BLOCK OF E LINCOLN ST). Case #26C143576 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>26C143936</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>46233.55972222222</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>POSSESSION OF PARAPHERNALIA</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>DRUGS</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>500 BLOCK OF S HUNTER ST</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>37.67912059117884</v>
+      </c>
+      <c r="K100" t="n">
+        <v>-97.25894321098265</v>
+      </c>
+      <c r="L100" t="n">
+        <v>1089.5</v>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Possession of paraphernalia on Jul 30, 2026, 1090 m from Towne East Square (500 BLOCK OF S HUNTER ST). Case #26C143936 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>26C520567</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>46227.6875</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>LARCENY B FROM AUTO</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>LARCENY</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>7200 BLOCK OF E BAYLEY ST</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>37.67101904846645</v>
+      </c>
+      <c r="K101" t="n">
+        <v>-97.25239274309988</v>
+      </c>
+      <c r="L101" t="n">
+        <v>1370.6</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Larceny b from auto on Jul 24, 2026, 1371 m from Towne East Square (7200 BLOCK OF E BAYLEY ST). Case #26C520567 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>26C520979</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>46231.94583333333</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>SUSPICIOUS CHARACTER SIB UNIT</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>SUSP_CHARAC</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>500 BLOCK OF N ROCK RD</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>37.6938385342284</v>
+      </c>
+      <c r="K102" t="n">
+        <v>-97.24455420498546</v>
+      </c>
+      <c r="L102" t="n">
+        <v>1264</v>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Suspicious character sib unit on Jul 28, 2026, 1264 m from Towne East Square (500 BLOCK OF N ROCK RD). Case #26C520979 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>26C520282</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>46231.625</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>LOST MISC PROPERTY</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>LOST_PROPERTY</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>7000 BLOCK OF E KELLOGG ST</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>37.67951495831583</v>
+      </c>
+      <c r="K103" t="n">
+        <v>-97.25782989544317</v>
+      </c>
+      <c r="L103" t="n">
+        <v>982.3</v>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Lost misc property on Jul 28, 2026, 982 m from Towne East Square (7000 BLOCK OF E KELLOGG ST). Case #26C520282 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>26C520741</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>46228.86111111111</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>LARCENY B AUTO ACCESSORIES</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>LARCENY</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>7700 BLOCK OF E KELLOGG DR</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>37.67911394923933</v>
+      </c>
+      <c r="K104" t="n">
+        <v>-97.24743308095542</v>
+      </c>
+      <c r="L104" t="n">
+        <v>398.7</v>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Larceny b auto accessories on Jul 25, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG DR). Case #26C520741 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>26C520933</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>46230.6125</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>LARCENY B SHOPLIFT</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>LARCENY</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>7700 BLOCK OF E KELLOGG ST</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>37.67911394923933</v>
+      </c>
+      <c r="K105" t="n">
+        <v>-97.24743308095542</v>
+      </c>
+      <c r="L105" t="n">
+        <v>398.7</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Larceny b shoplift on Jul 27, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C520933 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>26C521105</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>46233.075</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>REVOCATION SUSP DL</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>OTHERTRAF_VIO</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>700 BLOCK OF S WOODLAWN BLVD</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>37.67556302964613</v>
+      </c>
+      <c r="K106" t="n">
+        <v>-97.26215557703324</v>
+      </c>
+      <c r="L106" t="n">
+        <v>1520.5</v>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Revocation susp dl on Jul 30, 2026, 1520 m from Towne East Square (700 BLOCK OF S WOODLAWN BLVD). Case #26C521105 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
           <t>ARZMILLS</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>Arizona Mills</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202675652         </t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>46230.77569444444</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[13B] ASSAULT [DV]                                                              </t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>5XXX S ARIZONA MILLS CIR</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>33.38314167531927</v>
+      </c>
+      <c r="K107" t="n">
+        <v>-111.9645674529712</v>
+      </c>
+      <c r="L107" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>[13b] assault [dv] on Jul 27, 2026, 15 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675652          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202674996         </t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>46228.65694444445</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SC-0] INFO - INFORMATION OTHER (NON-CRIMINAL)                                  </t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>5XXX S ARIZONA MILLS CIR</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>33.38314167531927</v>
+      </c>
+      <c r="K108" t="n">
+        <v>-111.9645674529712</v>
+      </c>
+      <c r="L108" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>[sc-0] info - information other (non-criminal) on Jul 25, 2026, 15 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202674996          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202674783         </t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>46227.91319444445</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[13B] ASSAULT                                                                   </t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>5XXX S ARIZONA MILLS CIR</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>33.38314167531927</v>
+      </c>
+      <c r="K109" t="n">
+        <v>-111.9645674529712</v>
+      </c>
+      <c r="L109" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>[13b] assault on Jul 24, 2026, 15 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202674783          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202675415         </t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>46229.95</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[90J] TRESPASSING                                                               </t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>5XXX S ARIZONA MILLS CIR</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>33.38341075529574</v>
+      </c>
+      <c r="K110" t="n">
+        <v>-111.9652490281131</v>
+      </c>
+      <c r="L110" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>[90j] trespassing on Jul 26, 2026, 69 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675415          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202675399         </t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>46229.9</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>5XXX S ARIZONA MILLS CIR</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>33.38552975305072</v>
+      </c>
+      <c r="K111" t="n">
+        <v>-111.965328834686</v>
+      </c>
+      <c r="L111" t="n">
+        <v>262</v>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>[sc-0] trespass warning - private property on Jul 26, 2026, 262 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675399          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202676101         </t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>46232.21041666667</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[240] MOTOR VEHICLE THEFT                                                       </t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>5XXX S ARIZONA MILLS CIR</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>33.38580430470485</v>
+      </c>
+      <c r="K112" t="n">
+        <v>-111.9660628528483</v>
+      </c>
+      <c r="L112" t="n">
+        <v>315.7</v>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>[240] motor vehicle theft on Jul 29, 2026, 316 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202676101          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202676030         </t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>46231.83194444444</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>5XXX S ARIZONA MILLS CIR</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>33.3805974892332</v>
+      </c>
+      <c r="K113" t="n">
+        <v>-111.9623154538272</v>
+      </c>
+      <c r="L113" t="n">
+        <v>361.4</v>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>[sc-0] trespass warning - private property on Jul 28, 2026, 361 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202676030          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202674893         </t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>46228.35972222222</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[GO-0] ASSIST OTHER AGENCY                                                      </t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>4XXX S WENDLER DR</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>33.38130369903515</v>
+      </c>
+      <c r="K114" t="n">
+        <v>-111.9695754725762</v>
+      </c>
+      <c r="L114" t="n">
+        <v>517</v>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>[go-0] assist other agency on Jul 25, 2026, 517 m from Arizona Mills (4XXX S WENDLER DR). Case #TE202674893          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202675649         </t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>46230.76944444444</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SC-0] WELFARE CHECK                                                            </t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>4XXX S DARROW DR</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>33.38128291577831</v>
+      </c>
+      <c r="K115" t="n">
+        <v>-111.9593051545489</v>
+      </c>
+      <c r="L115" t="n">
+        <v>533.1</v>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>[sc-0] welfare check on Jul 27, 2026, 533 m from Arizona Mills (4XXX S DARROW DR). Case #TE202675649          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202674654         </t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>46227.62708333333</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[GO-0] ACCIDENT - HIT AND RUN                                                   </t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>BASELINE RD / S DARROW DR</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>33.37825351544224</v>
+      </c>
+      <c r="K116" t="n">
+        <v>-111.9611381808533</v>
+      </c>
+      <c r="L116" t="n">
+        <v>640.6</v>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>[go-0] accident - hit and run on Jul 24, 2026, 641 m from Arizona Mills (BASELINE RD / S DARROW DR). Case #TE202674654          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202675235         </t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>46229.31597222222</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PUBLIC PLACES                                         </t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>BASELINE RD / I10</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>33.37824262058852</v>
+      </c>
+      <c r="K117" t="n">
+        <v>-111.9680044627475</v>
+      </c>
+      <c r="L117" t="n">
+        <v>645.4</v>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>[sc-0] trespass warning - public places on Jul 26, 2026, 645 m from Arizona Mills (BASELINE RD / I10). Case #TE202675235          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202675001         </t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>46228.66944444444</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>1XXX W BASELINE RD</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>33.377865729326</v>
+      </c>
+      <c r="K118" t="n">
+        <v>-111.9618554026273</v>
+      </c>
+      <c r="L118" t="n">
+        <v>650.2</v>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>[sc-0] trespass warning - private property on Jul 25, 2026, 650 m from Arizona Mills (1XXX W BASELINE RD). Case #TE202675001          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202676035         </t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>46231.85555555556</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SC-0] SERVICE - ORDER OF PROTECTION (OOP) / INJUNCTION (P1)                    </t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1XXX W LA JOLLA DR</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>33.38909587497265</v>
+      </c>
+      <c r="K119" t="n">
+        <v>-111.961540133513</v>
+      </c>
+      <c r="L119" t="n">
+        <v>704.8</v>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>[sc-0] service - order of protection (oop) / injunction (p1) on Jul 28, 2026, 705 m from Arizona Mills (1XXX W LA JOLLA DR). Case #TE202676035          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202675946         </t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>46231.63888888889</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>1XXX W BASELINE RD</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>33.37795738260824</v>
+      </c>
+      <c r="K120" t="n">
+        <v>-111.959149564986</v>
+      </c>
+      <c r="L120" t="n">
+        <v>773.7</v>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>[sc-0] trespass warning - private property on Jul 28, 2026, 774 m from Arizona Mills (1XXX W BASELINE RD). Case #TE202675946          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202674935         </t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>46228.47222222222</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SC-0] ASSIST - MENTALLY ILL (OTHER THAN MHP/EMHETR)                            </t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>1XXX W BASELINE RD</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>33.37594547787401</v>
+      </c>
+      <c r="K121" t="n">
+        <v>-111.9593287567214</v>
+      </c>
+      <c r="L121" t="n">
+        <v>946.9</v>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>[sc-0] assist - mentally ill (other than mhp/emhetr) on Jul 25, 2026, 947 m from Arizona Mills (1XXX W BASELINE RD). Case #TE202674935          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
         <is>
           <t xml:space="preserve">TE202674869         </t>
         </is>
       </c>
-      <c r="E87" s="3" t="n">
+      <c r="E122" s="3" t="n">
         <v>46228.26388888889</v>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F122" t="inlineStr">
         <is>
           <t xml:space="preserve">[SC-0] LOST - PROPERTY (NON-FIREARM, OTHER THAN GOV'T ISSUED ID)                </t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="G122" t="inlineStr">
         <is>
           <t>PROPERTY</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr">
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
         <is>
           <t>PARKSIDE DR / W FREMONT DR</t>
         </is>
       </c>
-      <c r="J87" t="n">
+      <c r="J122" t="n">
         <v>33.38169955020192</v>
       </c>
-      <c r="K87" t="n">
+      <c r="K122" t="n">
         <v>-111.954283203492</v>
       </c>
-      <c r="L87" t="n">
+      <c r="L122" t="n">
         <v>967.3</v>
       </c>
-      <c r="M87" t="inlineStr">
+      <c r="M122" t="inlineStr">
         <is>
           <t>[sc-0] lost - property (non-firearm, other than gov't issued id) on Jul 25, 2026, 967 m from Arizona Mills (PARKSIDE DR / W FREMONT DR). Case #TE202674869          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202674568         </t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>46227.44722222222</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>9XX W BASELINE RD</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>33.37784058487316</v>
+      </c>
+      <c r="K123" t="n">
+        <v>-111.9548908569819</v>
+      </c>
+      <c r="L123" t="n">
+        <v>1079.6</v>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>[sc-0] trespass warning - private property on Jul 24, 2026, 1080 m from Arizona Mills (9XX W BASELINE RD). Case #TE202674568          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE2026601259        </t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>46229.58055555556</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[0] CRIMINAL DAMAGE - UNDER $1000                                               </t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>1XXX W SOUTHERN AVE</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>33.39259581629993</v>
+      </c>
+      <c r="K124" t="n">
+        <v>-111.9580558007179</v>
+      </c>
+      <c r="L124" t="n">
+        <v>1198.6</v>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>[0] criminal damage - under $1000 on Jul 26, 2026, 1199 m from Arizona Mills (1XXX W SOUTHERN AVE). Case #TE2026601259         (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202676006         </t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>46231.77708333333</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[GO-0] DEATH                                                                    </t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>2XXX W SOUTHERN AVE</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>33.38855944643347</v>
+      </c>
+      <c r="K125" t="n">
+        <v>-111.9758211943486</v>
+      </c>
+      <c r="L125" t="n">
+        <v>1202.1</v>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>[go-0] death on Jul 28, 2026, 1202 m from Arizona Mills (2XXX W SOUTHERN AVE). Case #TE202676006          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202674741         </t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>46227.81666666667</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SC-0] SERVICE - ORDER OF PROTECTION (OOP) / INJUNCTION (P1)                    </t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>5XXX S HARDY DR</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>33.37634047797651</v>
+      </c>
+      <c r="K126" t="n">
+        <v>-111.9531278046354</v>
+      </c>
+      <c r="L126" t="n">
+        <v>1309.4</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>[sc-0] service - order of protection (oop) / injunction (p1) on Jul 24, 2026, 1309 m from Arizona Mills (5XXX S HARDY DR). Case #TE202674741          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202674557         </t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>46227.4125</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SC-0] WARNING - DISORDERLY CONDUCT                                             </t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>5XXX S HARDY DR</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>33.37634047797651</v>
+      </c>
+      <c r="K127" t="n">
+        <v>-111.9531278046354</v>
+      </c>
+      <c r="L127" t="n">
+        <v>1309.4</v>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>[sc-0] warning - disorderly conduct on Jul 24, 2026, 1309 m from Arizona Mills (5XXX S HARDY DR). Case #TE202674557          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202674714         </t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>46227.7375</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[13A] AGGRAVATED ASSAULT [DV]                                                   </t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>5XXX S HARDY DR</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>33.37634047797651</v>
+      </c>
+      <c r="K128" t="n">
+        <v>-111.9531278046354</v>
+      </c>
+      <c r="L128" t="n">
+        <v>1309.4</v>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>[13a] aggravated assault [dv] on Jul 24, 2026, 1309 m from Arizona Mills (5XXX S HARDY DR). Case #TE202674714          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202675136         </t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>46228.97847222222</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[13B] ASSAULT                                                                   </t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>5XXX S HARDY DR</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>33.3757495513233</v>
+      </c>
+      <c r="K129" t="n">
+        <v>-111.9531832468173</v>
+      </c>
+      <c r="L129" t="n">
+        <v>1345.1</v>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>[13b] assault on Jul 25, 2026, 1345 m from Arizona Mills (5XXX S HARDY DR). Case #TE202675136          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202676025         </t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>46231.82430555556</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SC-0] WARRANT - BOOKED INTO DETENTION                                          </t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>7XXX S 48TH ST</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>33.38154948911996</v>
+      </c>
+      <c r="K130" t="n">
+        <v>-111.9788828064167</v>
+      </c>
+      <c r="L130" t="n">
+        <v>1346.3</v>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>[sc-0] warrant - booked into detention on Jul 28, 2026, 1346 m from Arizona Mills (7XXX S 48TH ST). Case #TE202676025          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202674804         </t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>46227.98263888889</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[240] MOTOR VEHICLE THEFT                                                       </t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>MCKEMY ST / S HARDY DR</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>33.37562594922362</v>
+      </c>
+      <c r="K131" t="n">
+        <v>-111.9529211309643</v>
+      </c>
+      <c r="L131" t="n">
+        <v>1372.7</v>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>[240] motor vehicle theft on Jul 24, 2026, 1373 m from Arizona Mills (MCKEMY ST / S HARDY DR). Case #TE202674804          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202675422         </t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>46229.96111111111</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SC-0] INFO - INFORMATION OTHER (NON-CRIMINAL)                                  </t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>3XXX S 52ND ST</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>33.3959248712565</v>
+      </c>
+      <c r="K132" t="n">
+        <v>-111.9704886613678</v>
+      </c>
+      <c r="L132" t="n">
+        <v>1512</v>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>[sc-0] info - information other (non-criminal) on Jul 26, 2026, 1512 m from Arizona Mills (3XXX S 52ND ST). Case #TE202675422          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202674830         </t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>46228.05902777778</v>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>SOUTHERN AVE / S HARDY DR</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
+        <v>33.39284504948579</v>
+      </c>
+      <c r="K133" t="n">
+        <v>-111.9519846600515</v>
+      </c>
+      <c r="L133" t="n">
+        <v>1578</v>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>Incident on Jul 25, 2026, 1578 m from Arizona Mills (SOUTHERN AVE / S HARDY DR). Case #TE202674830          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>ARZMILLS</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Arizona Mills</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TE202675096         </t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>46228.88680555556</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[11D] MOLESTATION OF A CHILD                                                    </t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>7XX W BASELINE RD</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>33.37881261615141</v>
+      </c>
+      <c r="K134" t="n">
+        <v>-111.9483590935493</v>
+      </c>
+      <c r="L134" t="n">
+        <v>1581.2</v>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>[11d] molestation of a child on Jul 25, 2026, 1581 m from Arizona Mills (7XX W BASELINE RD). Case #TE202675096          (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M87"/>
+  <autoFilter ref="A1:M134"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7739,7 +10452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="51" customWidth="1" min="1" max="1"/>
@@ -7766,7 +10479,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-31 07:31:55.362213+00:00</t>
+          <t>2026-07-31 07:34:21.761817+00:00</t>
         </is>
       </c>
     </row>
@@ -7783,147 +10496,145 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cutoff</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-07-24 07:31:55.362213+00:00</t>
-        </is>
+          <t>radius_m</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1600</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>total_incidents</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>86</v>
+          <t>cutoff</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-24 07:34:21.761817+00:00</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>violent_incidents</t>
+          <t>total_incidents</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>coverage_gaps</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>LENOX, THEDOMAIN</t>
-        </is>
+          <t>violent_incidents</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>source:BEVCENTER/LAPD NIBRS Offenses 2026-present</t>
+          <t>coverage_gaps</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OK fetched=0 truncated=False</t>
+          <t>LENOX, THEDOMAIN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>source:OPRYMILLS/Metro Nashville PD Incidents</t>
+          <t>source:BEVCENTER/LAPD NIBRS Offenses 2026-present</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OK fetched=14 truncated=False</t>
+          <t>OK fetched=0 truncated=False</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>source:GREENHILLS/Metro Nashville PD Incidents</t>
+          <t>source:OPRYMILLS/Metro Nashville PD Incidents</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OK fetched=9 truncated=False</t>
+          <t>OK fetched=15 truncated=False</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>source:NORTHGATE/Seattle PD Crime Data</t>
+          <t>source:GREENHILLS/Metro Nashville PD Incidents</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OK fetched=6 truncated=False</t>
+          <t>OK fetched=9 truncated=False</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>source:CHERRYCREEK/Denver PD Crime</t>
+          <t>source:NORTHGATE/Seattle PD Crime Data</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>OK fetched=11 truncated=False</t>
+          <t>OK fetched=12 truncated=False</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>source:SOUTHPARK/CMPD Incidents</t>
+          <t>source:CHERRYCREEK/Denver PD Crime</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OK fetched=13 truncated=False</t>
+          <t>OK fetched=12 truncated=False</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>source:CHARLOTTE/CMPD Incidents</t>
+          <t>source:SOUTHPARK/CMPD Incidents</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>OK fetched=2 truncated=False</t>
+          <t>OK fetched=14 truncated=False</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>source:ABQUP/Albuquerque PD Incidents</t>
+          <t>source:CHARLOTTE/CMPD Incidents</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>OK fetched=0 truncated=False</t>
+          <t>OK fetched=3 truncated=False</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>source:INTLPLAZA/Tampa PD Crimes (365d)</t>
+          <t>source:ABQUP/Albuquerque PD Incidents</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7935,29 +10646,41 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>source:TOWNEEAST/Wichita PD Crimes (90d)</t>
+          <t>source:INTLPLAZA/Tampa PD Crimes (365d)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>OK fetched=38 truncated=False</t>
+          <t>OK fetched=0 truncated=False</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>source:TOWNEEAST/Wichita PD Crimes (90d)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>OK fetched=93 truncated=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>source:ARZMILLS/Tempe PD General Offenses</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>OK fetched=16 truncated=False</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>OK fetched=28 truncated=False</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B18"/>
+  <autoFilter ref="A1:B19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/latest/blotter_report.xlsx
+++ b/reports/latest/blotter_report.xlsx
@@ -10479,7 +10479,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-31 07:34:21.761817+00:00</t>
+          <t>2026-07-31 07:36:57.686613+00:00</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-24 07:34:21.761817+00:00</t>
+          <t>2026-07-24 07:36:57.686613+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/latest/blotter_report.xlsx
+++ b/reports/latest/blotter_report.xlsx
@@ -10479,7 +10479,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-31 07:36:57.686613+00:00</t>
+          <t>2026-07-31 07:45:48.319120+00:00</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-24 07:36:57.686613+00:00</t>
+          <t>2026-07-24 07:45:48.319120+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/latest/blotter_report.xlsx
+++ b/reports/latest/blotter_report.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Highlights'!$A$1:$M$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$109</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -595,16 +595,16 @@
         <v>8</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J3" t="n">
         <v>14.7</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>46232.21041666667</v>
+        <v>46233.33055555556</v>
       </c>
       <c r="L3" t="b">
         <v>0</v>
@@ -766,26 +766,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>191.2</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>46232.0625</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="b">
         <v>0</v>
       </c>
@@ -812,13 +808,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -826,8 +822,12 @@
       <c r="I8" t="n">
         <v>0</v>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>1534.5</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>46232.16666666666</v>
+      </c>
       <c r="L8" t="b">
         <v>0</v>
       </c>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -942,26 +942,22 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>113.7</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>46232.70902777778</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="b">
         <v>0</v>
       </c>
@@ -1076,19 +1072,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J14" t="n">
         <v>288.9</v>
@@ -1117,7 +1113,7 @@
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
@@ -1892,30 +1888,30 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>20260449995_11</t>
+          <t>DP2026415473230300</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>46227.89583333334</v>
+        <v>46231.47916666666</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SHOPLIFTING</t>
+          <t>theft-shoplift</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1925,56 +1921,56 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>larceny</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>211 211</t>
+          <t>15 S STEELE ST</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>36.20300000011262</v>
+        <v>39.7162154712797</v>
       </c>
       <c r="K14" t="n">
-        <v>-86.69100000036219</v>
+        <v>-104.9512928115626</v>
       </c>
       <c r="L14" t="n">
-        <v>113.7</v>
+        <v>144.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 24, 2026, 114 m from Opry Mills (211 211). Premises: DEPARTMENT, DISCOUNT STORE. Status: CLEARED BY ARREST. Victims: 1. Case #20260449995 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-shoplift on Jul 28, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026415473 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>20260451873_11</t>
+          <t>DP2026413358260700</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>46228.76041666666</v>
+        <v>46230.47013888889</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>LOST PROPERTY</t>
+          <t>fraud-by-telephone</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1984,56 +1980,56 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>white-collar-crime</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>433 433</t>
+          <t>15 S STEELE ST</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>36.20199999980591</v>
+        <v>39.7162154712797</v>
       </c>
       <c r="K15" t="n">
-        <v>-86.69299999962931</v>
+        <v>-104.9512928115626</v>
       </c>
       <c r="L15" t="n">
-        <v>125.9</v>
+        <v>144.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Lost property on Jul 25, 2026, 126 m from Opry Mills (433 433). Premises: Shopping Mall. Status: UNFOUNDED. Victims: 1. Case #20260451873 (use for a records request — full narratives are not published in open data).</t>
+          <t>Fraud-by-telephone on Jul 27, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026413358 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DP2026415473230300</t>
+          <t>71913162555</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>46231.47916666666</v>
+        <v>46232.82986111111</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>theft-shoplift</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2043,56 +2039,56 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>15 S STEELE ST</t>
+          <t>3XX BLOCK OF NE NORTHGATE WAY</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>39.7162154712797</v>
+        <v>47.7086028</v>
       </c>
       <c r="K16" t="n">
-        <v>-104.9512928115626</v>
+        <v>-122.324615154453</v>
       </c>
       <c r="L16" t="n">
-        <v>144.7</v>
+        <v>145.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Theft-shoplift on Jul 28, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026415473 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 29, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-222878 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DP2026413358260700</t>
+          <t>71898889573</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>46230.47013888889</v>
+        <v>46231.625</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>fraud-by-telephone</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2102,52 +2098,52 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>white-collar-crime</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>15 S STEELE ST</t>
+          <t>4XX BLOCK OF NE NORTHGATE WAY</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>39.7162154712797</v>
+        <v>47.7086028</v>
       </c>
       <c r="K17" t="n">
-        <v>-104.9512928115626</v>
+        <v>-122.324615154453</v>
       </c>
       <c r="L17" t="n">
-        <v>144.7</v>
+        <v>145.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Fraud-by-telephone on Jul 27, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026413358 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-221387 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>71913162555</t>
+          <t>20260728-1922-01</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>46232.82986111111</v>
+        <v>46231.16666666666</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2161,52 +2157,52 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>23C</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>47.7086028</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K18" t="n">
-        <v>-122.324615154453</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L18" t="n">
-        <v>145.2</v>
+        <v>178.9</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 29, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-222878 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1922-01 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>71898889573</t>
+          <t>20260728-1130-01</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>46231.625</v>
+        <v>46231.16666666666</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2220,56 +2216,56 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>23C</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>47.7086028</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K19" t="n">
-        <v>-122.324615154453</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L19" t="n">
-        <v>145.2</v>
+        <v>178.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-221387 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1130-01 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>71842391876</t>
+          <t>20260729-1053-01</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>46227.5</v>
+        <v>46229.16666666666</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motor Vehicle Theft</t>
+          <t>All Other Thefts</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2279,56 +2275,56 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>23H</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>4500 SHARON RD</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>47.7086028</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K20" t="n">
-        <v>-122.324615154453</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L20" t="n">
-        <v>145.2</v>
+        <v>178.9</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Motor vehicle theft on Jul 24, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-217106 (use for a records request — full narratives are not published in open data).</t>
+          <t>All other thefts on Jul 26, 2026, 179 m from Southpark (4500 SHARON RD). Status: Open. Case #20260729-1053-01 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DP2026408098239901</t>
+          <t>20260727-1824-00</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>46227.58333333334</v>
+        <v>46229.16666666666</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>theft-bicycle</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2338,26 +2334,26 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>23C</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>N MILWAUKEE ST / E 1ST AVE</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>39.71813319743836</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K21" t="n">
-        <v>-104.9522056316381</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L21" t="n">
-        <v>148.6</v>
+        <v>178.9</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Theft-bicycle on Jul 24, 2026, 149 m from Cherry Creek Shopping Center (N MILWAUKEE ST / E 1ST AVE). Victims: 1. Case #DP2026408098 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 26, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260727-1824-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2379,11 +2375,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>20260728-1922-01</t>
+          <t>20260725-1348-05</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>46231.16666666666</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2416,7 +2412,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1922-01 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 25, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260725-1348-05 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2438,11 +2434,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>20260728-1130-01</t>
+          <t>20260727-1945-02</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>46231.16666666666</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2475,37 +2471,37 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1130-01 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 25, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260727-1945-02 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>20260729-1053-01</t>
+          <t>DP2026416370230300</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>46229.16666666666</v>
+        <v>46231.83333333334</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>All Other Thefts</t>
+          <t>theft-shoplift</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2515,56 +2511,56 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>23H</t>
+          <t>larceny</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4500 SHARON RD</t>
+          <t>2810 E 1ST AVE</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>35.15120046375475</v>
+        <v>39.71666393731682</v>
       </c>
       <c r="K24" t="n">
-        <v>-80.82867375349484</v>
+        <v>-104.9556403659223</v>
       </c>
       <c r="L24" t="n">
-        <v>178.9</v>
+        <v>247.6</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>All other thefts on Jul 26, 2026, 179 m from Southpark (4500 SHARON RD). Status: Open. Case #20260729-1053-01 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-shoplift on Jul 28, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026416370 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>20260727-1824-00</t>
+          <t>DP2026415590230300</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>46229.16666666666</v>
+        <v>46231.54236111111</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>theft-shoplift</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2574,56 +2570,56 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>larceny</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>2810 E 1ST AVE</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>35.15120046375475</v>
+        <v>39.71666393731682</v>
       </c>
       <c r="K25" t="n">
-        <v>-80.82867375349484</v>
+        <v>-104.9556403659223</v>
       </c>
       <c r="L25" t="n">
-        <v>178.9</v>
+        <v>247.6</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 26, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260727-1824-00 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-shoplift on Jul 28, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026415590 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>20260725-1348-05</t>
+          <t xml:space="preserve">TE202675399         </t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>46228.16666666666</v>
+        <v>46229.9</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2631,28 +2627,24 @@
           <t>PROPERTY</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>23C</t>
-        </is>
-      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>5XXX S ARIZONA MILLS CIR</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>35.15120046375475</v>
+        <v>33.38552975305072</v>
       </c>
       <c r="K26" t="n">
-        <v>-80.82867375349484</v>
+        <v>-111.965328834686</v>
       </c>
       <c r="L26" t="n">
-        <v>178.9</v>
+        <v>262</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 25, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260725-1348-05 (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] trespass warning - private property on Jul 26, 2026, 262 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675399          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2668,18 +2660,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M134"/>
+  <dimension ref="A1:M109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -2756,30 +2748,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20260449995_11</t>
+          <t>71913162555</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>46227.89583333334</v>
+        <v>46232.82986111111</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SHOPLIFTING</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -2789,56 +2781,56 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>211 211</t>
+          <t>3XX BLOCK OF NE NORTHGATE WAY</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>36.20300000011262</v>
+        <v>47.7086028</v>
       </c>
       <c r="K2" t="n">
-        <v>-86.69100000036219</v>
+        <v>-122.324615154453</v>
       </c>
       <c r="L2" t="n">
-        <v>113.7</v>
+        <v>145.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 24, 2026, 114 m from Opry Mills (211 211). Premises: DEPARTMENT, DISCOUNT STORE. Status: CLEARED BY ARREST. Victims: 1. Case #20260449995 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 29, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-222878 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20260451873_11</t>
+          <t>71909585262</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>46228.76041666666</v>
+        <v>46231.83333333334</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LOST PROPERTY</t>
+          <t>Motor Vehicle Theft</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2848,115 +2840,115 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>433 433</t>
+          <t>5XX BLOCK OF NE NORTHGATE WAY</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>36.20199999980591</v>
+        <v>47.70858578</v>
       </c>
       <c r="K3" t="n">
-        <v>-86.69299999962931</v>
+        <v>-122.321918377919</v>
       </c>
       <c r="L3" t="n">
-        <v>125.9</v>
+        <v>338.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Lost property on Jul 25, 2026, 126 m from Opry Mills (433 433). Premises: Shopping Mall. Status: UNFOUNDED. Victims: 1. Case #20260451873 (use for a records request — full narratives are not published in open data).</t>
+          <t>Motor vehicle theft on Jul 28, 2026, 338 m from Northgate Station (5XX BLOCK OF NE NORTHGATE WAY). Case #2026-222454 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>20260451698_11</t>
+          <t>71899643103</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>46228.89097222222</v>
+        <v>46231.78263888889</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>POSSESSION OF A CONTROLLED SUBSTANCE</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>433 433</t>
+          <t>116XX BLOCK OF AURORA AVE N</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>36.20199999980591</v>
+        <v>47.71354798</v>
       </c>
       <c r="K4" t="n">
-        <v>-86.69299999962931</v>
+        <v>-122.344834273165</v>
       </c>
       <c r="L4" t="n">
-        <v>125.9</v>
+        <v>1511</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Possession of a controlled substance on Jul 25, 2026, 126 m from Opry Mills (433 433). Premises: SPECIALTY STORE. Status: CLEARED BY ARREST. Victims: 1. Case #20260451698 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 1511 m from Northgate Station (116XX BLOCK OF AURORA AVE N). Case #2026-221622 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20260457817_11</t>
+          <t>71898889573</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>46231.92430555556</v>
+        <v>46231.625</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>THEFT OF MERCHANDISE- $1,000 OR LESS</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2966,233 +2958,233 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>OPRY MILLS DR</t>
+          <t>4XX BLOCK OF NE NORTHGATE WAY</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>36.20000000001247</v>
+        <v>47.7086028</v>
       </c>
       <c r="K5" t="n">
-        <v>-86.69000000027951</v>
+        <v>-122.324615154453</v>
       </c>
       <c r="L5" t="n">
-        <v>387.3</v>
+        <v>145.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Theft of merchandise- $1,000 or less on Jul 28, 2026, 387 m from Opry Mills (OPRY MILLS DR). Premises: SPECIALTY STORE. Status: OPEN. Victims: 1. Case #20260457817 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-221387 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>20260451780_11</t>
+          <t>71890752645</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>46228.89583333334</v>
+        <v>46231.21458333333</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LARC - FROM BLDG</t>
+          <t>Destruction/Damage/Vandalism of Property</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>ALL OTHER</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>OPRY MILLS</t>
+          <t>15XX BLOCK OF NE 107TH ST</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>36.20000000001247</v>
+        <v>47.70668788</v>
       </c>
       <c r="K6" t="n">
-        <v>-86.70000000020825</v>
+        <v>-122.311189989679</v>
       </c>
       <c r="L6" t="n">
-        <v>768.3</v>
+        <v>1145.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Larc - from bldg on Jul 25, 2026, 768 m from Opry Mills (OPRY MILLS). Premises: RESTAURANT. Status: OPEN. Victims: 1. Case #20260451780 (use for a records request — full narratives are not published in open data).</t>
+          <t>Destruction/damage/vandalism of property on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-220873 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20260451462_11</t>
+          <t>71894237115</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>46228.6875</v>
+        <v>46231.20833333334</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SHOPLIFTING</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>VIOLENT CRIME</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>OPRY MILLS DR</t>
+          <t>15XX BLOCK OF NE 107TH ST</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>36.20999999970633</v>
+        <v>47.70668788</v>
       </c>
       <c r="K7" t="n">
-        <v>-86.69000000027951</v>
+        <v>-122.311189997702</v>
       </c>
       <c r="L7" t="n">
-        <v>808.3</v>
+        <v>1145.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 25, 2026, 808 m from Opry Mills (OPRY MILLS DR). Premises: SPECIALTY STORE. Status: OPEN. Victims: 1. Case #20260451462 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-221056 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20260455357_11</t>
+          <t>71889871382</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>46230.79166666666</v>
+        <v>46231.00625</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SHOPLIFTING</t>
+          <t>Simple Assault</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>ALL OTHER</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>OPRY MILLS DR</t>
+          <t>15XX BLOCK OF NE 107TH ST</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>36.20999999970633</v>
+        <v>47.70668788</v>
       </c>
       <c r="K8" t="n">
-        <v>-86.69000000027951</v>
+        <v>-122.311189997702</v>
       </c>
       <c r="L8" t="n">
-        <v>808.3</v>
+        <v>1145.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 27, 2026, 808 m from Opry Mills (OPRY MILLS DR). Premises: DEPARTMENT, DISCOUNT STORE. Status: OPEN. Victims: 1. Case #20260455357 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-220636 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>20260457791_11</t>
+          <t>71906728829</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>46231.9</v>
+        <v>46231</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>THEFT OF MERCHANDISE- $1,000 OR LESS</t>
+          <t>Theft of Motor Vehicle Parts or Accessories</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3202,174 +3194,174 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>OPRY MILLS DR</t>
+          <t>9XX BLOCK OF N 103RD ST</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>36.20999999970633</v>
+        <v>47.70360675</v>
       </c>
       <c r="K9" t="n">
-        <v>-86.69000000027951</v>
+        <v>-122.346021623573</v>
       </c>
       <c r="L9" t="n">
-        <v>808.3</v>
+        <v>1551.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Theft of merchandise- $1,000 or less on Jul 28, 2026, 808 m from Opry Mills (OPRY MILLS DR). Premises: SPECIALTY STORE. Status: OPEN. Victims: 1. Case #20260457791 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft of motor vehicle parts or accessories on Jul 28, 2026, 1551 m from Northgate Station (9XX BLOCK OF N 103RD ST). Case #2026-222196 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>20260456995_11</t>
+          <t>71878728447</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>46227.68333333333</v>
+        <v>46230.4375</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FRAUD -  ILLEG USE OF CREDIT CARDS</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>VIOLENT CRIME</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>OPRY MILLS DR</t>
+          <t>16XX BLOCK OF N 105TH ST</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>36.20999999970633</v>
+        <v>47.70504225</v>
       </c>
       <c r="K10" t="n">
-        <v>-86.69000000027951</v>
+        <v>-122.338094779232</v>
       </c>
       <c r="L10" t="n">
-        <v>808.3</v>
+        <v>938.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Fraud -  illeg use of credit cards on Jul 24, 2026, 808 m from Opry Mills (OPRY MILLS DR). Premises: RESTAURANT. Status: OPEN. Victims: 1. Case #20260456995 (use for a records request — full narratives are not published in open data).</t>
+          <t>Robbery on Jul 27, 2026, 939 m from Northgate Station (16XX BLOCK OF N 105TH ST). Case #2026-220064 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>20260456990_11</t>
+          <t>71854915364</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>46227.68333333333</v>
+        <v>46228.91527777778</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FRAUD -  ILLEG USE OF CREDIT CARDS</t>
+          <t>Not Reportable to NIBRS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>ALL OTHER</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>OPRY MILLS DR</t>
+          <t>N 105TH ST / AURORA AVE N</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>36.20999999970633</v>
+        <v>47.70505121</v>
       </c>
       <c r="K11" t="n">
-        <v>-86.69000000027951</v>
+        <v>-122.3446941292056</v>
       </c>
       <c r="L11" t="n">
-        <v>808.3</v>
+        <v>1411</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Fraud -  illeg use of credit cards on Jul 24, 2026, 808 m from Opry Mills (OPRY MILLS DR). Premises: SPECIALTY STORE. Status: OPEN. Victims: 1. Case #20260456990 (use for a records request — full narratives are not published in open data).</t>
+          <t>Not reportable to nibrs on Jul 25, 2026, 1411 m from Northgate Station (N 105TH ST / AURORA AVE N). Case #2026-218646 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>20260456993_11</t>
+          <t>71896083189</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>46227.68333333333</v>
+        <v>46228.875</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FRAUD -  ILLEG USE OF CREDIT CARDS</t>
+          <t>Theft From Motor Vehicle</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3379,335 +3371,351 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>OPRY MILLS DR</t>
+          <t>NE 100TH ST / 5TH AVE NE</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>36.20999999970633</v>
+        <v>47.70132479</v>
       </c>
       <c r="K12" t="n">
-        <v>-86.69000000027951</v>
+        <v>-122.3231272219471</v>
       </c>
       <c r="L12" t="n">
-        <v>808.3</v>
+        <v>785.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Fraud -  illeg use of credit cards on Jul 24, 2026, 808 m from Opry Mills (OPRY MILLS DR). Premises: SPECIALTY STORE. Status: OPEN. Victims: 1. Case #20260456993 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft from motor vehicle on Jul 25, 2026, 786 m from Northgate Station (NE 100TH ST / 5TH AVE NE). Case #2026-913373 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>20260453969_11</t>
+          <t>DP2026413358260700</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>46230.16666666666</v>
+        <v>46230.47013888889</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>POLICE INQUIRY</t>
+          <t>fraud-by-telephone</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>white-collar-crime</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>OPRYLAND DR</t>
+          <t>15 S STEELE ST</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>36.20999999970633</v>
+        <v>39.7162154712797</v>
       </c>
       <c r="K13" t="n">
-        <v>-86.69000000027951</v>
+        <v>-104.9512928115626</v>
       </c>
       <c r="L13" t="n">
-        <v>808.3</v>
+        <v>144.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Police inquiry on Jul 27, 2026, 808 m from Opry Mills (OPRYLAND DR). Premises: HOTEL, MOTEL, ETC.. Status: OPEN. Victims: 1. Case #20260453969 (use for a records request — full narratives are not published in open data).</t>
+          <t>Fraud-by-telephone on Jul 27, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026413358 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>20260453969_12</t>
+          <t>DP2026415473230300</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>46230.16666666666</v>
+        <v>46231.47916666666</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>POLICE INQUIRY</t>
+          <t>theft-shoplift</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>larceny</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>OPRYLAND DR</t>
+          <t>15 S STEELE ST</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>36.20999999970633</v>
+        <v>39.7162154712797</v>
       </c>
       <c r="K14" t="n">
-        <v>-86.69000000027951</v>
+        <v>-104.9512928115626</v>
       </c>
       <c r="L14" t="n">
-        <v>808.3</v>
+        <v>144.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Police inquiry on Jul 27, 2026, 808 m from Opry Mills (OPRYLAND DR). Premises: HOTEL, MOTEL, ETC.. Status: OPEN. Victims: 2. Case #20260453969 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-shoplift on Jul 28, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026415473 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>20260453969_13</t>
+          <t>DP2026416370230300</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>46230.16666666666</v>
+        <v>46231.83333333334</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>POLICE INQUIRY</t>
+          <t>theft-shoplift</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>larceny</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>OPRYLAND DR</t>
+          <t>2810 E 1ST AVE</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>36.20999999970633</v>
+        <v>39.71666393731682</v>
       </c>
       <c r="K15" t="n">
-        <v>-86.69000000027951</v>
+        <v>-104.9556403659223</v>
       </c>
       <c r="L15" t="n">
-        <v>808.3</v>
+        <v>247.6</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Police inquiry on Jul 27, 2026, 808 m from Opry Mills (OPRYLAND DR). Premises: HOTEL, MOTEL, ETC.. Status: OPEN. Victims: 3. Case #20260453969 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-shoplift on Jul 28, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026416370 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OPRYMILLS:Metro Nashville PD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>20260459134_11</t>
+          <t>DP2026415590230300</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>46232.70902777778</v>
+        <v>46231.54236111111</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>HARRASSMENT (NUISANCE)</t>
+          <t>theft-shoplift</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>larceny</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>TWO RIVERS PKWY</t>
+          <t>2810 E 1ST AVE</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>36.19000000021294</v>
+        <v>39.71666393731682</v>
       </c>
       <c r="K16" t="n">
-        <v>-86.69000000027951</v>
+        <v>-104.9556403659223</v>
       </c>
       <c r="L16" t="n">
-        <v>1455.9</v>
+        <v>247.6</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Harrassment (nuisance) on Jul 29, 2026, 1456 m from Opry Mills (TWO RIVERS PKWY). Premises: PARK. Status: OPEN. Victims: 1. Case #20260459134 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-shoplift on Jul 28, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026415590 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GREENHILLS</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Mall at Green Hills</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GREENHILLS:Metro Nashville PD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>20260452878_11</t>
+          <t>DP2026413635260700</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>46229.60694444444</v>
+        <v>46230.58125</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>POLICE INQUIRY</t>
+          <t>fraud-by-telephone</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>white-collar-crime</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2131 2131</t>
+          <t>2 N ADAMS ST</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>36.10599999977134</v>
+        <v>39.71654731730718</v>
       </c>
       <c r="K17" t="n">
-        <v>-86.8170000000033</v>
+        <v>-104.9482864243138</v>
       </c>
       <c r="L17" t="n">
-        <v>191.2</v>
+        <v>384.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Police inquiry on Jul 26, 2026, 191 m from The Mall at Green Hills (2131 2131). Premises: PARKING LOT, GARAGE. Status: UNFOUNDED. Victims: 1. Flags: domestic related. Case #20260452878 (use for a records request — full narratives are not published in open data).</t>
+          <t>Fraud-by-telephone on Jul 27, 2026, 384 m from Cherry Creek Shopping Center (2 N ADAMS ST). Victims: 1. Case #DP2026413635 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GREENHILLS</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Mall at Green Hills</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GREENHILLS:Metro Nashville PD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>20260451477_11</t>
+          <t>DP20266010142239900</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>46228.27083333334</v>
+        <v>46230.10416666666</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>BURGLARY</t>
+          <t>theft-other</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -3717,56 +3725,56 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>larceny</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CHANNELKIRK LN</t>
+          <t>3444 E 2ND AVE</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>36.10999999969955</v>
+        <v>39.7193352135378</v>
       </c>
       <c r="K18" t="n">
-        <v>-86.81000000032267</v>
+        <v>-104.9468354191938</v>
       </c>
       <c r="L18" t="n">
-        <v>630.5</v>
+        <v>576.2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Burglary on Jul 25, 2026, 631 m from The Mall at Green Hills (CHANNELKIRK LN). Premises: RESIDENCE, HOME. Status: OPEN. Victims: 1. Case #20260451477 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-other on Jul 27, 2026, 576 m from Cherry Creek Shopping Center (3444 E 2ND AVE). Victims: 1. Case #DP20266010142 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GREENHILLS</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Mall at Green Hills</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GREENHILLS:Metro Nashville PD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>20260453759_11</t>
+          <t>DP2026413301299900</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>46229.91666666666</v>
+        <v>46229.95833333334</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>POLICE INQUIRY</t>
+          <t>criminal-mischief-other</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -3776,174 +3784,174 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>public-disorder</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2024 2024</t>
+          <t>201 N UNIVERSITY BLVD</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>36.09999999975003</v>
+        <v>39.71957373655755</v>
       </c>
       <c r="K19" t="n">
-        <v>-86.81499999983789</v>
+        <v>-104.9597628432634</v>
       </c>
       <c r="L19" t="n">
-        <v>859.2</v>
+        <v>670.6</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Police inquiry on Jul 26, 2026, 859 m from The Mall at Green Hills (2024 2024). Premises: RESIDENCE, HOME. Status: UNFOUNDED. Victims: 1. Flags: domestic related. Case #20260453759 (use for a records request — full narratives are not published in open data).</t>
+          <t>Criminal-mischief-other on Jul 26, 2026, 671 m from Cherry Creek Shopping Center (201 N UNIVERSITY BLVD). Victims: 1. Case #DP2026413301 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GREENHILLS</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Mall at Green Hills</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GREENHILLS:Metro Nashville PD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>20260458322_11</t>
+          <t>DP20266010143299900</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>46232.0625</v>
+        <v>46229.9375</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>BURGLARY - MOTOR VEHICLE</t>
+          <t>criminal-mischief-other</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Unarmed</t>
+          <t>public-disorder</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>HILLSBORO PIKE</t>
+          <t>201 N UNIVERSITY BLVD</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>36.09999999975003</v>
+        <v>39.71957373655755</v>
       </c>
       <c r="K20" t="n">
-        <v>-86.82000000025143</v>
+        <v>-104.9597628432634</v>
       </c>
       <c r="L20" t="n">
-        <v>910.1</v>
+        <v>670.6</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Burglary - motor vehicle on Jul 29, 2026, 910 m from The Mall at Green Hills (HILLSBORO PIKE). Weapon: Unarmed. Premises: PARKING LOT, GARAGE. Status: OPEN. Victims: 1. Case #20260458322 (use for a records request — full narratives are not published in open data).</t>
+          <t>Criminal-mischief-other on Jul 26, 2026, 671 m from Cherry Creek Shopping Center (201 N UNIVERSITY BLVD). Victims: 1. Case #DP20266010143 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GREENHILLS</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Mall at Green Hills</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GREENHILLS:Metro Nashville PD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>20260450411_11</t>
+          <t>DP2026411044131300</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>46228.02083333334</v>
+        <v>46229.1125</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SIMPLE ASSLT</t>
+          <t>assault-simple</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>PERSONAL (HANDS)</t>
+          <t>other-crimes-against-persons</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>HILLSBORO PIKE</t>
+          <t>3200 BLOCK E CHERRY CREEK S DR</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>36.09999999975003</v>
+        <v>39.71130989687384</v>
       </c>
       <c r="K21" t="n">
-        <v>-86.82000000025143</v>
+        <v>-104.9490029653731</v>
       </c>
       <c r="L21" t="n">
-        <v>910.1</v>
+        <v>696.3</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Simple asslt on Jul 25, 2026, 910 m from The Mall at Green Hills (HILLSBORO PIKE). Weapon: PERSONAL (HANDS). Premises: HIGHWAY, ROAD, ALLEY. Status: OPEN. Victims: 1. Case #20260450411 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault-simple on Jul 26, 2026, 696 m from Cherry Creek Shopping Center (3200 BLOCK E CHERRY CREEK S DR). Victims: 1. Case #DP2026411044 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GREENHILLS</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Mall at Green Hills</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GREENHILLS:Metro Nashville PD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>20260450256_11</t>
+          <t>DP2026415569230400</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>46228.02569444444</v>
+        <v>46230.83333333334</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>THEFT OF MERCHANDISE- &gt;$1,000 BUT &lt; $2,500</t>
+          <t>theft-parts-from-vehicle</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3951,54 +3959,58 @@
           <t>PROPERTY</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>theft-from-motor-vehicle</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>HILLSBORO</t>
+          <t>441 N MILWAUKEE ST</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>36.09999999975003</v>
+        <v>39.72335589487053</v>
       </c>
       <c r="K22" t="n">
-        <v>-86.82000000025143</v>
+        <v>-104.9524528146586</v>
       </c>
       <c r="L22" t="n">
-        <v>910.1</v>
+        <v>722.1</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Theft of merchandise- &gt;$1,000 but &lt; $2,500 on Jul 25, 2026, 910 m from The Mall at Green Hills (HILLSBORO). Premises: SPECIALTY STORE. Status: OPEN. Victims: 1. Case #20260450256 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-parts-from-vehicle on Jul 27, 2026, 722 m from Cherry Creek Shopping Center (441 N MILWAUKEE ST). Victims: 1. Case #DP2026415569 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GREENHILLS</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Mall at Green Hills</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GREENHILLS:Metro Nashville PD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>20260449408_11</t>
+          <t>DP2026411500220400</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>46227.61805555555</v>
+        <v>46229.08333333334</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>LOST PROPERTY</t>
+          <t>burglary-residence-no-force</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4008,56 +4020,56 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>burglary</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2025 2025</t>
+          <t>100 BLK N GARFIELD ST</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>36.11399999985069</v>
+        <v>39.71871773048673</v>
       </c>
       <c r="K23" t="n">
-        <v>-86.80900000023999</v>
+        <v>-104.9439679319565</v>
       </c>
       <c r="L23" t="n">
-        <v>969.2</v>
+        <v>779.5</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Lost property on Jul 24, 2026, 969 m from The Mall at Green Hills (2025 2025). Premises: RESIDENCE, HOME. Status: UNFOUNDED. Victims: 1. Case #20260449408 (use for a records request — full narratives are not published in open data).</t>
+          <t>Burglary-residence-no-force on Jul 26, 2026, 779 m from Cherry Creek Shopping Center (100 BLK N GARFIELD ST). Victims: 1. Case #DP2026411500 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>71913162555</t>
+          <t>DP2026409833230500</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>46232.82986111111</v>
+        <v>46228.56944444445</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>theft-items-from-vehicle</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4067,115 +4079,115 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>theft-from-motor-vehicle</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>373 S JACKSON ST</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>47.7086028</v>
+        <v>39.70992379075913</v>
       </c>
       <c r="K24" t="n">
-        <v>-122.324615154453</v>
+        <v>-104.9426513848476</v>
       </c>
       <c r="L24" t="n">
-        <v>145.2</v>
+        <v>1159</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 29, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-222878 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-items-from-vehicle on Jul 25, 2026, 1159 m from Cherry Creek Shopping Center (373 S JACKSON ST). Victims: 1. Case #DP2026409833 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>71909585262</t>
+          <t>20260725-2301-00</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>46231.83333333334</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motor Vehicle Theft</t>
+          <t>Other Unlisted Non-Criminal</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>899</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>6900 FAIRVIEW RD</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>47.70858578</v>
+        <v>35.14684118006692</v>
       </c>
       <c r="K25" t="n">
-        <v>-122.321918377919</v>
+        <v>-80.82544759809264</v>
       </c>
       <c r="L25" t="n">
-        <v>338.4</v>
+        <v>722.6</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Motor vehicle theft on Jul 28, 2026, 338 m from Northgate Station (5XX BLOCK OF NE NORTHGATE WAY). Case #2026-222454 (use for a records request — full narratives are not published in open data).</t>
+          <t>Other unlisted non-criminal on Jul 25, 2026, 723 m from Southpark (6900 FAIRVIEW RD). Status: Open. Case #20260725-2301-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>71899643103</t>
+          <t>20260726-0712-02</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>46231.78263888889</v>
+        <v>46229.16666666666</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Theft From Motor Vehicle</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4185,56 +4197,56 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>23F</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>116XX BLOCK OF AURORA AVE N</t>
+          <t>6300 CARNEGIE BV</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>47.71354798</v>
+        <v>35.15641923337007</v>
       </c>
       <c r="K26" t="n">
-        <v>-122.344834273165</v>
+        <v>-80.83429541207509</v>
       </c>
       <c r="L26" t="n">
-        <v>1511</v>
+        <v>613</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 1511 m from Northgate Station (116XX BLOCK OF AURORA AVE N). Case #2026-221622 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft from motor vehicle on Jul 26, 2026, 613 m from Southpark (6300 CARNEGIE BV). Status: Open. Case #20260726-0712-02 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>71898889573</t>
+          <t>20260726-0550-00</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>46231.625</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Theft From Motor Vehicle</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4244,233 +4256,233 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>23F</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>4XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>6700 FAIRVIEW RD</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>47.7086028</v>
+        <v>35.1479657453291</v>
       </c>
       <c r="K27" t="n">
-        <v>-122.324615154453</v>
+        <v>-80.82922688152722</v>
       </c>
       <c r="L27" t="n">
-        <v>145.2</v>
+        <v>450.4</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-221387 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft from motor vehicle on Jul 25, 2026, 450 m from Southpark (6700 FAIRVIEW RD). Status: Open. Case #20260726-0550-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>71890752645</t>
+          <t>20260725-0853-00</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>46231.21458333333</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Destruction/Damage/Vandalism of Property</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>ALL OTHER</t>
+          <t>13A</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>15XX BLOCK OF NE 107TH ST</t>
+          <t>5700 CARNEGIE BV</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>47.70668788</v>
+        <v>35.15368289092867</v>
       </c>
       <c r="K28" t="n">
-        <v>-122.311189989679</v>
+        <v>-80.8398453262274</v>
       </c>
       <c r="L28" t="n">
-        <v>1145.7</v>
+        <v>877.1</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Destruction/damage/vandalism of property on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-220873 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 25, 2026, 877 m from Southpark (5700 CARNEGIE BV). Status: Open. Case #20260725-0853-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>71894237115</t>
+          <t>20260726-0657-00</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>46231.20833333334</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Aggravated Assault</t>
+          <t>Theft From Motor Vehicle</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>VIOLENT CRIME</t>
+          <t>23F</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>15XX BLOCK OF NE 107TH ST</t>
+          <t>5500 CARNEGIE BV</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>47.70668788</v>
+        <v>35.15375121029781</v>
       </c>
       <c r="K29" t="n">
-        <v>-122.311189997702</v>
+        <v>-80.83607576012871</v>
       </c>
       <c r="L29" t="n">
-        <v>1145.7</v>
+        <v>551.7</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-221056 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft from motor vehicle on Jul 25, 2026, 552 m from Southpark (5500 CARNEGIE BV). Status: Open. Case #20260726-0657-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>71889871382</t>
+          <t>20260725-1348-05</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>46231.00625</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Simple Assault</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>ALL OTHER</t>
+          <t>23C</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>15XX BLOCK OF NE 107TH ST</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>47.70668788</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K30" t="n">
-        <v>-122.311189997702</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L30" t="n">
-        <v>1145.7</v>
+        <v>178.9</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Simple assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-220636 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 25, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260725-1348-05 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>71906728829</t>
+          <t>20260729-1053-01</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>46231</v>
+        <v>46229.16666666666</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Theft of Motor Vehicle Parts or Accessories</t>
+          <t>All Other Thefts</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4480,233 +4492,233 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>23H</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>9XX BLOCK OF N 103RD ST</t>
+          <t>4500 SHARON RD</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>47.70360675</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K31" t="n">
-        <v>-122.346021623573</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L31" t="n">
-        <v>1551.2</v>
+        <v>178.9</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Theft of motor vehicle parts or accessories on Jul 28, 2026, 1551 m from Northgate Station (9XX BLOCK OF N 103RD ST). Case #2026-222196 (use for a records request — full narratives are not published in open data).</t>
+          <t>All other thefts on Jul 26, 2026, 179 m from Southpark (4500 SHARON RD). Status: Open. Case #20260729-1053-01 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>71878728447</t>
+          <t>20260727-1824-00</t>
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>46230.4375</v>
+        <v>46229.16666666666</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Robbery</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>VIOLENT CRIME</t>
+          <t>23C</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>16XX BLOCK OF N 105TH ST</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>47.70504225</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K32" t="n">
-        <v>-122.338094779232</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L32" t="n">
-        <v>938.8</v>
+        <v>178.9</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Robbery on Jul 27, 2026, 939 m from Northgate Station (16XX BLOCK OF N 105TH ST). Case #2026-220064 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 26, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260727-1824-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>71854915364</t>
+          <t>20260727-1945-02</t>
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>46228.91527777778</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Not Reportable to NIBRS</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>ALL OTHER</t>
+          <t>23C</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>N 105TH ST / AURORA AVE N</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>47.70505121</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K33" t="n">
-        <v>-122.3446941292056</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L33" t="n">
-        <v>1411</v>
+        <v>178.9</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Not reportable to nibrs on Jul 25, 2026, 1411 m from Northgate Station (N 105TH ST / AURORA AVE N). Case #2026-218646 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 25, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260727-1945-02 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>71896083189</t>
+          <t>20260726-1824-01</t>
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>46228.875</v>
+        <v>46229.16666666666</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Theft From Motor Vehicle</t>
+          <t>All Other Offenses</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>90Z</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>NE 100TH ST / 5TH AVE NE</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>47.70132479</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K34" t="n">
-        <v>-122.3231272219471</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L34" t="n">
-        <v>785.6</v>
+        <v>178.9</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Theft from motor vehicle on Jul 25, 2026, 786 m from Northgate Station (NE 100TH ST / 5TH AVE NE). Case #2026-913373 (use for a records request — full narratives are not published in open data).</t>
+          <t>All other offenses on Jul 26, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260726-1824-01 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>71842391876</t>
+          <t>20260728-1922-01</t>
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>46227.5</v>
+        <v>46231.16666666666</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motor Vehicle Theft</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4716,56 +4728,56 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>23C</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>47.7086028</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K35" t="n">
-        <v>-122.324615154453</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L35" t="n">
-        <v>145.2</v>
+        <v>178.9</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Motor vehicle theft on Jul 24, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-217106 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1922-01 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>DP2026413358260700</t>
+          <t>20260728-1130-01</t>
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>46230.47013888889</v>
+        <v>46231.16666666666</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>fraud-by-telephone</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4775,233 +4787,233 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>white-collar-crime</t>
+          <t>23C</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>15 S STEELE ST</t>
+          <t>4400 SHARON RD</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>39.7162154712797</v>
+        <v>35.15120046375475</v>
       </c>
       <c r="K36" t="n">
-        <v>-104.9512928115626</v>
+        <v>-80.82867375349484</v>
       </c>
       <c r="L36" t="n">
-        <v>144.7</v>
+        <v>178.9</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Fraud-by-telephone on Jul 27, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026413358 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1130-01 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>DP2026415473230300</t>
+          <t>20260725-1137-00</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>46231.47916666666</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>theft-shoplift</t>
+          <t>Suicide</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>801</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>15 S STEELE ST</t>
+          <t>5600 FAIRVIEW RD</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>39.7162154712797</v>
+        <v>35.15235596527605</v>
       </c>
       <c r="K37" t="n">
-        <v>-104.9512928115626</v>
+        <v>-80.84558404556884</v>
       </c>
       <c r="L37" t="n">
-        <v>144.7</v>
+        <v>1376.8</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Theft-shoplift on Jul 28, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026415473 (use for a records request — full narratives are not published in open data).</t>
+          <t>Suicide on Jul 25, 2026, 1377 m from Southpark (5600 FAIRVIEW RD). Status: Open. Case #20260725-1137-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>DP2026408098239901</t>
+          <t>20260726-0952-00</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>46227.58333333334</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>theft-bicycle</t>
+          <t>All Other Offenses</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>90Z</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>N MILWAUKEE ST / E 1ST AVE</t>
+          <t>700 GOVERNOR MORRISON ST</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>39.71813319743836</v>
+        <v>35.15648042297118</v>
       </c>
       <c r="K38" t="n">
-        <v>-104.9522056316381</v>
+        <v>-80.82480681029648</v>
       </c>
       <c r="L38" t="n">
-        <v>148.6</v>
+        <v>723.7</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Theft-bicycle on Jul 24, 2026, 149 m from Cherry Creek Shopping Center (N MILWAUKEE ST / E 1ST AVE). Victims: 1. Case #DP2026408098 (use for a records request — full narratives are not published in open data).</t>
+          <t>All other offenses on Jul 25, 2026, 724 m from Southpark (700 GOVERNOR MORRISON ST). Status: Open. Case #20260726-0952-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>CHARLOTTE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Charlotte Premium Outlets</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>CHARLOTTE:CMPD Incidents</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>DP2026416370230300</t>
+          <t>20260725-0631-00</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>46231.83333333334</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>theft-shoplift</t>
+          <t>Drug/Narcotic Violations</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>QUALITY_OF_LIFE</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>35A</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2810 E 1ST AVE</t>
+          <t>8300 STEELE CREEK RD</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>39.71666393731682</v>
+        <v>35.17291837763486</v>
       </c>
       <c r="K39" t="n">
-        <v>-104.9556403659223</v>
+        <v>-80.95939837774333</v>
       </c>
       <c r="L39" t="n">
-        <v>247.6</v>
+        <v>1070.3</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Theft-shoplift on Jul 28, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026416370 (use for a records request — full narratives are not published in open data).</t>
+          <t>Drug/narcotic violations on Jul 25, 2026, 1070 m from Charlotte Premium Outlets (8300 STEELE CREEK RD). Status: Open. Case #20260725-0631-00 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>CHARLOTTE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Charlotte Premium Outlets</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>CHARLOTTE:CMPD Incidents</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>DP2026415590230300</t>
+          <t>20260725-1934-03</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>46231.54236111111</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>theft-shoplift</t>
+          <t>All Other Thefts</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5011,56 +5023,56 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>23H</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2810 E 1ST AVE</t>
+          <t>4900 TROJAN DR</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>39.71666393731682</v>
+        <v>35.16474336144204</v>
       </c>
       <c r="K40" t="n">
-        <v>-104.9556403659223</v>
+        <v>-80.96762879799847</v>
       </c>
       <c r="L40" t="n">
-        <v>247.6</v>
+        <v>443.5</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Theft-shoplift on Jul 28, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026415590 (use for a records request — full narratives are not published in open data).</t>
+          <t>All other thefts on Jul 25, 2026, 444 m from Charlotte Premium Outlets (4900 TROJAN DR). Status: Open. Case #20260725-1934-03 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>CHARLOTTE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Charlotte Premium Outlets</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>CHARLOTTE:CMPD Incidents</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>DP2026413635260700</t>
+          <t>20260729-1434-02</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>46230.58125</v>
+        <v>46231.16666666666</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>fraud-by-telephone</t>
+          <t>Damage/Vandalism Of Property</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5070,56 +5082,56 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>white-collar-crime</t>
+          <t>290</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2 N ADAMS ST</t>
+          <t>5600 KELTONWOOD RD</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>39.71654731730718</v>
+        <v>35.16655081611235</v>
       </c>
       <c r="K41" t="n">
-        <v>-104.9482864243138</v>
+        <v>-80.97476086867614</v>
       </c>
       <c r="L41" t="n">
-        <v>384.1</v>
+        <v>496.6</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Fraud-by-telephone on Jul 27, 2026, 384 m from Cherry Creek Shopping Center (2 N ADAMS ST). Victims: 1. Case #DP2026413635 (use for a records request — full narratives are not published in open data).</t>
+          <t>Damage/vandalism of property on Jul 28, 2026, 497 m from Charlotte Premium Outlets (5600 KELTONWOOD RD). Status: Open. Case #20260729-1434-02 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>INTLPLAZA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>International Plaza</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>INTLPLAZA:Tampa PD Crimes (365d)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DP20266010142239900</t>
+          <t>2026445724</t>
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>46230.10416666666</v>
+        <v>46232.16666666666</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>theft-other</t>
+          <t>Motor Vehicle Theft</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5129,351 +5141,343 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>Motor Vehicle Theft</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3444 E 2ND AVE</t>
+          <t>SR 60 W NB - Spruce Ramp &amp; Spruce-Airport Ramp</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>39.7193352135378</v>
+        <v>27.95994382970347</v>
       </c>
       <c r="K42" t="n">
-        <v>-104.9468354191938</v>
+        <v>-82.53472608010854</v>
       </c>
       <c r="L42" t="n">
-        <v>576.2</v>
+        <v>1534.5</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Theft-other on Jul 27, 2026, 576 m from Cherry Creek Shopping Center (3444 E 2ND AVE). Victims: 1. Case #DP20266010142 (use for a records request — full narratives are not published in open data).</t>
+          <t>Motor vehicle theft on Jul 29, 2026, 1535 m from International Plaza (SR 60 W NB - Spruce Ramp &amp; Spruce-Airport Ramp). Case #2026445724 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>DP2026413301299900</t>
+          <t>26C139724</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>46229.95833333334</v>
+        <v>46227.69421296296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>criminal-mischief-other</t>
+          <t>BATTERY DV</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>public-disorder</t>
+          <t>SIM_ASSAULT</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>201 N UNIVERSITY BLVD</t>
+          <t>600 BLOCK OF S EASTERN AVE</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>39.71957373655755</v>
+        <v>37.6774046653855</v>
       </c>
       <c r="K43" t="n">
-        <v>-104.9597628432634</v>
+        <v>-97.23656061094495</v>
       </c>
       <c r="L43" t="n">
-        <v>670.6</v>
+        <v>1122.4</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Criminal-mischief-other on Jul 26, 2026, 671 m from Cherry Creek Shopping Center (201 N UNIVERSITY BLVD). Victims: 1. Case #DP2026413301 (use for a records request — full narratives are not published in open data).</t>
+          <t>Battery dv on Jul 24, 2026, 1122 m from Towne East Square (600 BLOCK OF S EASTERN AVE). Case #26C139724 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>DP20266010143299900</t>
+          <t>26C140260</t>
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>46229.9375</v>
+        <v>46228.77152777778</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>criminal-mischief-other</t>
+          <t>LARCENY B SHOPLIFT</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>public-disorder</t>
+          <t>LARCENY</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>201 N UNIVERSITY BLVD</t>
+          <t>7700 BLOCK OF E KELLOGG ST</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>39.71957373655755</v>
+        <v>37.67911394923933</v>
       </c>
       <c r="K44" t="n">
-        <v>-104.9597628432634</v>
+        <v>-97.24743308095542</v>
       </c>
       <c r="L44" t="n">
-        <v>670.6</v>
+        <v>398.7</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Criminal-mischief-other on Jul 26, 2026, 671 m from Cherry Creek Shopping Center (201 N UNIVERSITY BLVD). Victims: 1. Case #DP20266010143 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny b shoplift on Jul 25, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C140260 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DP2026411044131300</t>
+          <t>26C140486</t>
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>46229.1125</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>assault-simple</t>
-        </is>
-      </c>
+        <v>46228.51944444444</v>
+      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>other-crimes-against-persons</t>
-        </is>
-      </c>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3200 BLOCK E CHERRY CREEK S DR</t>
+          <t>7700 BLOCK OF E KELLOGG ST</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>39.71130989687384</v>
+        <v>37.67911394923933</v>
       </c>
       <c r="K45" t="n">
-        <v>-104.9490029653731</v>
+        <v>-97.24743308095542</v>
       </c>
       <c r="L45" t="n">
-        <v>696.3</v>
+        <v>398.7</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Assault-simple on Jul 26, 2026, 696 m from Cherry Creek Shopping Center (3200 BLOCK E CHERRY CREEK S DR). Victims: 1. Case #DP2026411044 (use for a records request — full narratives are not published in open data).</t>
+          <t>Incident on Jul 25, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C140486 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>DP2026411500220400</t>
+          <t>26C143336</t>
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>46229.08333333334</v>
+        <v>46232.7125</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>burglary-residence-no-force</t>
+          <t>TRESPASS</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>QUALITY_OF_LIFE</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>burglary</t>
+          <t>MISC_OFFENSES</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>100 BLK N GARFIELD ST</t>
+          <t>7700 BLOCK OF E KELLOGG ST</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>39.71871773048673</v>
+        <v>37.67911394923933</v>
       </c>
       <c r="K46" t="n">
-        <v>-104.9439679319565</v>
+        <v>-97.24743308095542</v>
       </c>
       <c r="L46" t="n">
-        <v>779.5</v>
+        <v>398.7</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Burglary-residence-no-force on Jul 26, 2026, 779 m from Cherry Creek Shopping Center (100 BLK N GARFIELD ST). Victims: 1. Case #DP2026411500 (use for a records request — full narratives are not published in open data).</t>
+          <t>Trespass on Jul 29, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C143336 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DP2026409833230500</t>
+          <t>26C143989</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>46228.56944444445</v>
+        <v>46233.61180555556</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>theft-items-from-vehicle</t>
+          <t>MISC REPORT</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>theft-from-motor-vehicle</t>
+          <t>MISC_REPORT</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>373 S JACKSON ST</t>
+          <t>700 BLOCK OF S APACHE DR</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>39.70992379075913</v>
+        <v>37.67384327067582</v>
       </c>
       <c r="K47" t="n">
-        <v>-104.9426513848476</v>
+        <v>-97.25634062142737</v>
       </c>
       <c r="L47" t="n">
-        <v>1159</v>
+        <v>1259.5</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Theft-items-from-vehicle on Jul 25, 2026, 1159 m from Cherry Creek Shopping Center (373 S JACKSON ST). Victims: 1. Case #DP2026409833 (use for a records request — full narratives are not published in open data).</t>
+          <t>Misc report on Jul 30, 2026, 1260 m from Towne East Square (700 BLOCK OF S APACHE DR). Case #26C143989 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>20260725-2301-00</t>
+          <t>26C144045</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>46228.16666666666</v>
+        <v>46233.65833333333</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Other Unlisted Non-Criminal</t>
+          <t>DEAD BODIES FOUND NO WITNESS</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5483,56 +5487,56 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>SUDDEN_DEATH</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>6900 FAIRVIEW RD</t>
+          <t>700 BLOCK OF S EASTRIDGE DR</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>35.14684118006692</v>
+        <v>37.67625582907724</v>
       </c>
       <c r="K48" t="n">
-        <v>-80.82544759809264</v>
+        <v>-97.25926072916232</v>
       </c>
       <c r="L48" t="n">
-        <v>722.6</v>
+        <v>1264.7</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Other unlisted non-criminal on Jul 25, 2026, 723 m from Southpark (6900 FAIRVIEW RD). Status: Open. Case #20260725-2301-00 (use for a records request — full narratives are not published in open data).</t>
+          <t>Dead bodies found no witness on Jul 30, 2026, 1265 m from Towne East Square (700 BLOCK OF S EASTRIDGE DR). Case #26C144045 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>20260726-0712-02</t>
+          <t>26C520577</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>46229.16666666666</v>
+        <v>46227.71388888889</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Theft From Motor Vehicle</t>
+          <t>SUSPICIOUS CHARACTER LARCENY UNIT</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5542,56 +5546,56 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>23F</t>
+          <t>SUSP_CHARAC</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>6300 CARNEGIE BV</t>
+          <t>7700 BLOCK OF E KELLOGG DR</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>35.15641923337007</v>
+        <v>37.67911394923933</v>
       </c>
       <c r="K49" t="n">
-        <v>-80.83429541207509</v>
+        <v>-97.24743308095542</v>
       </c>
       <c r="L49" t="n">
-        <v>613</v>
+        <v>398.7</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Theft from motor vehicle on Jul 26, 2026, 613 m from Southpark (6300 CARNEGIE BV). Status: Open. Case #20260726-0712-02 (use for a records request — full narratives are not published in open data).</t>
+          <t>Suspicious character larceny unit on Jul 24, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG DR). Case #26C520577 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>20260726-0550-00</t>
+          <t>26C520675</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>46228.16666666666</v>
+        <v>46227.84236111111</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Theft From Motor Vehicle</t>
+          <t>LARCENY B SHOPLIFT</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5601,528 +5605,520 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>23F</t>
+          <t>LARCENY</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>6700 FAIRVIEW RD</t>
+          <t>7700 BLOCK OF E KELLOGG DR</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>35.1479657453291</v>
+        <v>37.67911394923933</v>
       </c>
       <c r="K50" t="n">
-        <v>-80.82922688152722</v>
+        <v>-97.24743308095542</v>
       </c>
       <c r="L50" t="n">
-        <v>450.4</v>
+        <v>398.7</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Theft from motor vehicle on Jul 25, 2026, 450 m from Southpark (6700 FAIRVIEW RD). Status: Open. Case #20260726-0550-00 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny b shoplift on Jul 24, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG DR). Case #26C520675 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>20260725-0853-00</t>
+          <t>26C520776</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>46228.16666666666</v>
+        <v>46229.45833333334</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Aggravated Assault</t>
+          <t>AUTO THEFT</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>13A</t>
+          <t>AUTOTHEFT</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>5700 CARNEGIE BV</t>
+          <t>500 BLOCK OF N ROCK RD</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>35.15368289092867</v>
+        <v>37.6938385342284</v>
       </c>
       <c r="K51" t="n">
-        <v>-80.8398453262274</v>
+        <v>-97.24455420498546</v>
       </c>
       <c r="L51" t="n">
-        <v>877.1</v>
+        <v>1264</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 25, 2026, 877 m from Southpark (5700 CARNEGIE BV). Status: Open. Case #20260725-0853-00 (use for a records request — full narratives are not published in open data).</t>
+          <t>Auto theft on Jul 26, 2026, 1264 m from Towne East Square (500 BLOCK OF N ROCK RD). Case #26C520776 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>20260726-0657-00</t>
+          <t>26C139922</t>
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>46228.16666666666</v>
+        <v>46227.95277777778</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Theft From Motor Vehicle</t>
+          <t>BATTERY ABW</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>23F</t>
+          <t>SIM_ASSAULT</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>5500 CARNEGIE BV</t>
+          <t>7000 BLOCK OF E LINCOLN ST</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>35.15375121029781</v>
+        <v>37.67195398477438</v>
       </c>
       <c r="K52" t="n">
-        <v>-80.83607576012871</v>
+        <v>-97.25533959083543</v>
       </c>
       <c r="L52" t="n">
-        <v>551.7</v>
+        <v>1383.4</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Theft from motor vehicle on Jul 25, 2026, 552 m from Southpark (5500 CARNEGIE BV). Status: Open. Case #20260726-0657-00 (use for a records request — full narratives are not published in open data).</t>
+          <t>Battery abw on Jul 24, 2026, 1383 m from Towne East Square (7000 BLOCK OF E LINCOLN ST). Case #26C139922 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>20260725-1348-05</t>
+          <t>26C140815</t>
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>46228.16666666666</v>
+        <v>46229.30625</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>MISC REPORT</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>MISC_REPORT</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>900 BLOCK OF S APACHE DR</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>35.15120046375475</v>
+        <v>37.67195267201163</v>
       </c>
       <c r="K53" t="n">
-        <v>-80.82867375349484</v>
+        <v>-97.25741761429009</v>
       </c>
       <c r="L53" t="n">
-        <v>178.9</v>
+        <v>1484.1</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 25, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260725-1348-05 (use for a records request — full narratives are not published in open data).</t>
+          <t>Misc report on Jul 26, 2026, 1484 m from Towne East Square (900 BLOCK OF S APACHE DR). Case #26C140815 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>20260729-1053-01</t>
+          <t>26C142785</t>
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>46229.16666666666</v>
+        <v>46231.96458333333</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>All Other Thefts</t>
+          <t>EVADE POLICE</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>23H</t>
+          <t>DRIVING_VIO</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>4500 SHARON RD</t>
+          <t>E KELLOGG DR &amp; S ROCK RD</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>35.15120046375475</v>
+        <v>37.67911842691625</v>
       </c>
       <c r="K54" t="n">
-        <v>-80.82867375349484</v>
+        <v>-97.24451202953301</v>
       </c>
       <c r="L54" t="n">
-        <v>178.9</v>
+        <v>473.3</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>All other thefts on Jul 26, 2026, 179 m from Southpark (4500 SHARON RD). Status: Open. Case #20260729-1053-01 (use for a records request — full narratives are not published in open data).</t>
+          <t>Evade police on Jul 28, 2026, 473 m from Towne East Square (E KELLOGG DR &amp; S ROCK RD). Case #26C142785 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>20260727-1824-00</t>
+          <t>26C142917</t>
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>46229.16666666666</v>
+        <v>46232.18194444444</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>WINDOWPEEPING</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>SEX_OFFENSES1</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>700 BLOCK OF S HUNTER ST</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>35.15120046375475</v>
+        <v>37.67688443377517</v>
       </c>
       <c r="K55" t="n">
-        <v>-80.82867375349484</v>
+        <v>-97.26003808987583</v>
       </c>
       <c r="L55" t="n">
-        <v>178.9</v>
+        <v>1285.1</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 26, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260727-1824-00 (use for a records request — full narratives are not published in open data).</t>
+          <t>Windowpeeping on Jul 29, 2026, 1285 m from Towne East Square (700 BLOCK OF S HUNTER ST). Case #26C142917 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>20260727-1945-02</t>
+          <t>26C141216</t>
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>46228.16666666666</v>
+        <v>46229.90069444444</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>CHECKED WELFARE OF A CHILD</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>FAMILY</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>7300 BLOCK OF E KELLOGG ST</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>35.15120046375475</v>
+        <v>37.67974587023429</v>
       </c>
       <c r="K56" t="n">
-        <v>-80.82867375349484</v>
+        <v>-97.25225228651782</v>
       </c>
       <c r="L56" t="n">
-        <v>178.9</v>
+        <v>537.4</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 25, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260727-1945-02 (use for a records request — full narratives are not published in open data).</t>
+          <t>Checked welfare of a child on Jul 26, 2026, 537 m from Towne East Square (7300 BLOCK OF E KELLOGG ST). Case #26C141216 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>20260726-1824-01</t>
+          <t>26C143148</t>
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>46229.16666666666</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>All Other Offenses</t>
-        </is>
-      </c>
+        <v>46232.52430555555</v>
+      </c>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
           <t>OTHER</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>90Z</t>
-        </is>
-      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>900 BLOCK OF S ENOCH DR</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>35.15120046375475</v>
+        <v>37.67197658912259</v>
       </c>
       <c r="K57" t="n">
-        <v>-80.82867375349484</v>
+        <v>-97.2456018407935</v>
       </c>
       <c r="L57" t="n">
-        <v>178.9</v>
+        <v>1203</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>All other offenses on Jul 26, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260726-1824-01 (use for a records request — full narratives are not published in open data).</t>
+          <t>Incident on Jul 29, 2026, 1203 m from Towne East Square (900 BLOCK OF S ENOCH DR). Case #26C143148 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>20260728-1922-01</t>
+          <t>26C141683</t>
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>46231.16666666666</v>
+        <v>46230.58541666667</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>MISC OFFICERS</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>OUTSIDE_CASE</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>8100 BLOCK OF E KELLOGG ST</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>35.15120046375475</v>
+        <v>37.6797148529391</v>
       </c>
       <c r="K58" t="n">
-        <v>-80.82867375349484</v>
+        <v>-97.24233946631864</v>
       </c>
       <c r="L58" t="n">
-        <v>178.9</v>
+        <v>556.7</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1922-01 (use for a records request — full narratives are not published in open data).</t>
+          <t>Misc officers on Jul 27, 2026, 557 m from Towne East Square (8100 BLOCK OF E KELLOGG ST). Case #26C141683 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>20260728-1130-01</t>
+          <t>26C143446</t>
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>46231.16666666666</v>
+        <v>46232.7125</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>LARCENY B SHOPLIFT</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -6132,115 +6128,115 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>LARCENY</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>7700 BLOCK OF E KELLOGG ST</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>35.15120046375475</v>
+        <v>37.67911394923933</v>
       </c>
       <c r="K59" t="n">
-        <v>-80.82867375349484</v>
+        <v>-97.24743308095542</v>
       </c>
       <c r="L59" t="n">
-        <v>178.9</v>
+        <v>398.7</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1130-01 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny b shoplift on Jul 29, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C143446 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>20260725-1137-00</t>
+          <t>26C144013</t>
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>46228.16666666666</v>
+        <v>46233.63055555556</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Suicide</t>
+          <t>LARCENY B SHOPLIFT</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>LARCENY</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>5600 FAIRVIEW RD</t>
+          <t>7700 BLOCK OF E KELLOGG DR</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>35.15235596527605</v>
+        <v>37.67911394923933</v>
       </c>
       <c r="K60" t="n">
-        <v>-80.84558404556884</v>
+        <v>-97.24743308095542</v>
       </c>
       <c r="L60" t="n">
-        <v>1376.8</v>
+        <v>398.7</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Suicide on Jul 25, 2026, 1377 m from Southpark (5600 FAIRVIEW RD). Status: Open. Case #20260725-1137-00 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny b shoplift on Jul 30, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG DR). Case #26C144013 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>20260726-0952-00</t>
+          <t>26C144067</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>46228.16666666666</v>
+        <v>46232.71180555555</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>All Other Offenses</t>
+          <t>PRVT PROP NON-INJURY ACCIDENT</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -6250,203 +6246,203 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>90Z</t>
+          <t>TRAFFIC</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>700 GOVERNOR MORRISON ST</t>
+          <t>8000 BLOCK OF E DOUGLAS AVE</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>35.15648042297118</v>
+        <v>37.6865673723019</v>
       </c>
       <c r="K61" t="n">
-        <v>-80.82480681029648</v>
+        <v>-97.24449812404205</v>
       </c>
       <c r="L61" t="n">
-        <v>723.7</v>
+        <v>501</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>All other offenses on Jul 25, 2026, 724 m from Southpark (700 GOVERNOR MORRISON ST). Status: Open. Case #20260726-0952-00 (use for a records request — full narratives are not published in open data).</t>
+          <t>Prvt prop non-injury accident on Jul 29, 2026, 501 m from Towne East Square (8000 BLOCK OF E DOUGLAS AVE). Case #26C144067 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CHARLOTTE</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Charlotte Premium Outlets</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CHARLOTTE:CMPD Incidents</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>20260725-0631-00</t>
+          <t>26C142294</t>
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>46228.16666666666</v>
+        <v>46231.42847222222</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Drug/Narcotic Violations</t>
+          <t>FOUND MISC PROPERTY</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>QUALITY_OF_LIFE</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>35A</t>
+          <t>FOUND_PROP</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>8300 STEELE CREEK RD</t>
+          <t>700 BLOCK OF S MISSION RD</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>35.17291837763486</v>
+        <v>37.6756469679485</v>
       </c>
       <c r="K62" t="n">
-        <v>-80.95939837774333</v>
+        <v>-97.25850032865422</v>
       </c>
       <c r="L62" t="n">
-        <v>1070.3</v>
+        <v>1251.5</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Drug/narcotic violations on Jul 25, 2026, 1070 m from Charlotte Premium Outlets (8300 STEELE CREEK RD). Status: Open. Case #20260725-0631-00 (use for a records request — full narratives are not published in open data).</t>
+          <t>Found misc property on Jul 28, 2026, 1251 m from Towne East Square (700 BLOCK OF S MISSION RD). Case #26C142294 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CHARLOTTE</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Charlotte Premium Outlets</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CHARLOTTE:CMPD Incidents</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>20260725-1934-03</t>
+          <t>26C144131</t>
         </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v>46228.16666666666</v>
+        <v>46233.7625</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>All Other Thefts</t>
+          <t>MISC REPORT</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>23H</t>
+          <t>MISC_REPORT</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>4900 TROJAN DR</t>
+          <t>E BAYLEY ST &amp; S GOVERNEOUR RD</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>35.16474336144204</v>
+        <v>37.67014134415807</v>
       </c>
       <c r="K63" t="n">
-        <v>-80.96762879799847</v>
+        <v>-97.25360392908074</v>
       </c>
       <c r="L63" t="n">
-        <v>443.5</v>
+        <v>1498.8</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>All other thefts on Jul 25, 2026, 444 m from Charlotte Premium Outlets (4900 TROJAN DR). Status: Open. Case #20260725-1934-03 (use for a records request — full narratives are not published in open data).</t>
+          <t>Misc report on Jul 30, 2026, 1499 m from Towne East Square (E BAYLEY ST &amp; S GOVERNEOUR RD). Case #26C144131 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CHARLOTTE</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Charlotte Premium Outlets</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CHARLOTTE:CMPD Incidents</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>20260729-1434-02</t>
+          <t>26C143812</t>
         </is>
       </c>
       <c r="E64" s="3" t="n">
-        <v>46231.16666666666</v>
+        <v>46232.88888888889</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Damage/Vandalism Of Property</t>
+          <t>OTV-HIT AND RUN</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>OTHERTRAF_VIO</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>5600 KELTONWOOD RD</t>
+          <t>400 BLOCK OF S ROCK RD</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>35.16655081611235</v>
+        <v>37.68150034571348</v>
       </c>
       <c r="K64" t="n">
-        <v>-80.97476086867614</v>
+        <v>-97.24450622724754</v>
       </c>
       <c r="L64" t="n">
-        <v>496.6</v>
+        <v>288.9</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Damage/vandalism of property on Jul 28, 2026, 497 m from Charlotte Premium Outlets (5600 KELTONWOOD RD). Status: Open. Case #20260729-1434-02 (use for a records request — full narratives are not published in open data).</t>
+          <t>Otv-hit and run on Jul 29, 2026, 289 m from Towne East Square (400 BLOCK OF S ROCK RD). Case #26C143812 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6468,44 +6464,44 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>26C139456</t>
+          <t>26C144101</t>
         </is>
       </c>
       <c r="E65" s="3" t="n">
-        <v>46227.42226851852</v>
+        <v>46233.72152777778</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SUSPICIOUS CHARACTER BURGLARY UNIT</t>
+          <t>MISC REPORT</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>SUSP_CHARAC</t>
+          <t>MISC_REPORT</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>7200 BLOCK OF E LINCOLN ST</t>
+          <t>600 BLOCK OF S APACHE DR</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>37.67196805016872</v>
+        <v>37.67516836949827</v>
       </c>
       <c r="K65" t="n">
-        <v>-97.25239793155058</v>
+        <v>-97.25367616461408</v>
       </c>
       <c r="L65" t="n">
-        <v>1271.2</v>
+        <v>1002.3</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Suspicious character burglary unit on Jul 24, 2026, 1271 m from Towne East Square (7200 BLOCK OF E LINCOLN ST). Case #26C139456 (use for a records request — full narratives are not published in open data).</t>
+          <t>Misc report on Jul 30, 2026, 1002 m from Towne East Square (600 BLOCK OF S APACHE DR). Case #26C144101 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6527,44 +6523,36 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>26C139724</t>
+          <t>26C139706</t>
         </is>
       </c>
       <c r="E66" s="3" t="n">
-        <v>46227.69421296296</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>BATTERY DV</t>
-        </is>
-      </c>
+        <v>46227.66875</v>
+      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>SIM_ASSAULT</t>
-        </is>
-      </c>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>600 BLOCK OF S EASTERN AVE</t>
+          <t>7700 BLOCK OF E KELLOGG ST</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>37.6774046653855</v>
+        <v>37.67911394923933</v>
       </c>
       <c r="K66" t="n">
-        <v>-97.23656061094495</v>
+        <v>-97.24743308095542</v>
       </c>
       <c r="L66" t="n">
-        <v>1122.4</v>
+        <v>398.7</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Battery dv on Jul 24, 2026, 1122 m from Towne East Square (600 BLOCK OF S EASTERN AVE). Case #26C139724 (use for a records request — full narratives are not published in open data).</t>
+          <t>Incident on Jul 24, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C139706 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6586,44 +6574,44 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>26C140260</t>
+          <t>26C141863</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>46228.77152777778</v>
+        <v>46230.75486111111</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>LARCENY B SHOPLIFT</t>
+          <t>RUNAWAY</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>LARCENY</t>
+          <t>MISC_OFFENSES</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG ST</t>
+          <t>700 BLOCK OF S HUNTER ST</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>37.67911394923933</v>
+        <v>37.67688443377517</v>
       </c>
       <c r="K67" t="n">
-        <v>-97.24743308095542</v>
+        <v>-97.26003808987583</v>
       </c>
       <c r="L67" t="n">
-        <v>398.7</v>
+        <v>1285.1</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Larceny b shoplift on Jul 25, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C140260 (use for a records request — full narratives are not published in open data).</t>
+          <t>Runaway on Jul 27, 2026, 1285 m from Towne East Square (700 BLOCK OF S HUNTER ST). Case #26C141863 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6645,36 +6633,44 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>26C140486</t>
+          <t>26C142249</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
-        <v>46228.51944444444</v>
-      </c>
-      <c r="F68" t="inlineStr"/>
+        <v>46230.75</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>BATTERY ABW</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>SIM_ASSAULT</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG ST</t>
+          <t>700 BLOCK OF S MISSION RD</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>37.67911394923933</v>
+        <v>37.6756469679485</v>
       </c>
       <c r="K68" t="n">
-        <v>-97.24743308095542</v>
+        <v>-97.25850032865422</v>
       </c>
       <c r="L68" t="n">
-        <v>398.7</v>
+        <v>1251.5</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Incident on Jul 25, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C140486 (use for a records request — full narratives are not published in open data).</t>
+          <t>Battery abw on Jul 27, 2026, 1251 m from Towne East Square (700 BLOCK OF S MISSION RD). Case #26C142249 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6696,44 +6692,44 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>26C143336</t>
+          <t>26C142387</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>46232.7125</v>
+        <v>46230.81597222222</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>TRESPASS</t>
+          <t>PRVT PROP NON-INJURY ACCIDENT</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>QUALITY_OF_LIFE</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>MISC_OFFENSES</t>
+          <t>TRAFFIC</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG ST</t>
+          <t>100 BLOCK OF S ROCK RD</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>37.67911394923933</v>
+        <v>37.6865673723019</v>
       </c>
       <c r="K69" t="n">
-        <v>-97.24743308095542</v>
+        <v>-97.24449812404205</v>
       </c>
       <c r="L69" t="n">
-        <v>398.7</v>
+        <v>501</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Trespass on Jul 29, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C143336 (use for a records request — full narratives are not published in open data).</t>
+          <t>Prvt prop non-injury accident on Jul 27, 2026, 501 m from Towne East Square (100 BLOCK OF S ROCK RD). Case #26C142387 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6755,15 +6751,15 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>26C143989</t>
+          <t>26C142657</t>
         </is>
       </c>
       <c r="E70" s="3" t="n">
-        <v>46233.61180555556</v>
+        <v>46231.79166666666</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MISC REPORT</t>
+          <t>INTERFERENCE W PARENTAL CUSTODY</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -6773,26 +6769,26 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>MISC_REPORT</t>
+          <t>MISC_OFFENSES</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>700 BLOCK OF S APACHE DR</t>
+          <t>900 BLOCK OF S ENOCH DR</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>37.67384327067582</v>
+        <v>37.67197658912259</v>
       </c>
       <c r="K70" t="n">
-        <v>-97.25634062142737</v>
+        <v>-97.2456018407935</v>
       </c>
       <c r="L70" t="n">
-        <v>1259.5</v>
+        <v>1203</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Misc report on Jul 30, 2026, 1260 m from Towne East Square (700 BLOCK OF S APACHE DR). Case #26C143989 (use for a records request — full narratives are not published in open data).</t>
+          <t>Interference w parental custody on Jul 28, 2026, 1203 m from Towne East Square (900 BLOCK OF S ENOCH DR). Case #26C142657 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6814,15 +6810,15 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>26C144045</t>
+          <t>26C142768</t>
         </is>
       </c>
       <c r="E71" s="3" t="n">
-        <v>46233.65833333333</v>
+        <v>46231.94305555556</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>DEAD BODIES FOUND NO WITNESS</t>
+          <t>CHECKED WELFARE OF A CHILD</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -6832,26 +6828,26 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>SUDDEN_DEATH</t>
+          <t>FAMILY</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>700 BLOCK OF S EASTRIDGE DR</t>
+          <t>6500 BLOCK OF E MORRIS ST</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>37.67625582907724</v>
+        <v>37.67377815761698</v>
       </c>
       <c r="K71" t="n">
-        <v>-97.25926072916232</v>
+        <v>-97.2605034310844</v>
       </c>
       <c r="L71" t="n">
-        <v>1264.7</v>
+        <v>1519.9</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Dead bodies found no witness on Jul 30, 2026, 1265 m from Towne East Square (700 BLOCK OF S EASTRIDGE DR). Case #26C144045 (use for a records request — full narratives are not published in open data).</t>
+          <t>Checked welfare of a child on Jul 28, 2026, 1520 m from Towne East Square (6500 BLOCK OF E MORRIS ST). Case #26C142768 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6873,44 +6869,44 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>26C520577</t>
+          <t>26C143218</t>
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>46227.71388888889</v>
+        <v>46232.58333333334</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SUSPICIOUS CHARACTER LARCENY UNIT</t>
+          <t>DISTURB THE PEACE</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>SUSP_CHARAC</t>
+          <t>DISORDERLY</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG DR</t>
+          <t>700 BLOCK OF S HUNTER ST</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>37.67911394923933</v>
+        <v>37.67688443377517</v>
       </c>
       <c r="K72" t="n">
-        <v>-97.24743308095542</v>
+        <v>-97.26003808987583</v>
       </c>
       <c r="L72" t="n">
-        <v>398.7</v>
+        <v>1285.1</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Suspicious character larceny unit on Jul 24, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG DR). Case #26C520577 (use for a records request — full narratives are not published in open data).</t>
+          <t>Disturb the peace on Jul 29, 2026, 1285 m from Towne East Square (700 BLOCK OF S HUNTER ST). Case #26C143218 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6932,44 +6928,44 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>26C520675</t>
+          <t>26C143562</t>
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>46227.84236111111</v>
+        <v>46232.93958333333</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>LARCENY B SHOPLIFT</t>
+          <t>MENTAL CASES</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>LARCENY</t>
+          <t>MENTAL_CASE</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG DR</t>
+          <t>600 BLOCK OF S EASTERN AVE</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>37.67911394923933</v>
+        <v>37.6774046653855</v>
       </c>
       <c r="K73" t="n">
-        <v>-97.24743308095542</v>
+        <v>-97.23656061094495</v>
       </c>
       <c r="L73" t="n">
-        <v>398.7</v>
+        <v>1122.4</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Larceny b shoplift on Jul 24, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG DR). Case #26C520675 (use for a records request — full narratives are not published in open data).</t>
+          <t>Mental cases on Jul 29, 2026, 1122 m from Towne East Square (600 BLOCK OF S EASTERN AVE). Case #26C143562 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -6991,44 +6987,44 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>26C520776</t>
+          <t>26C143576</t>
         </is>
       </c>
       <c r="E74" s="3" t="n">
-        <v>46229.45833333334</v>
+        <v>46232.96111111111</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>AUTO THEFT</t>
+          <t>MISC REPORT</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>AUTOTHEFT</t>
+          <t>MISC_REPORT</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>500 BLOCK OF N ROCK RD</t>
+          <t>7500 BLOCK OF E LINCOLN ST</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>37.6938385342284</v>
+        <v>37.67197300274878</v>
       </c>
       <c r="K74" t="n">
-        <v>-97.24455420498546</v>
+        <v>-97.24902708647107</v>
       </c>
       <c r="L74" t="n">
-        <v>1264</v>
+        <v>1201.1</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Auto theft on Jul 26, 2026, 1264 m from Towne East Square (500 BLOCK OF N ROCK RD). Case #26C520776 (use for a records request — full narratives are not published in open data).</t>
+          <t>Misc report on Jul 29, 2026, 1201 m from Towne East Square (7500 BLOCK OF E LINCOLN ST). Case #26C143576 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7050,15 +7046,15 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>26C139721</t>
+          <t>26C143936</t>
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>46227.625</v>
+        <v>46233.55972222222</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>OTV-HIT AND RUN</t>
+          <t>POSSESSION OF PARAPHERNALIA</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -7068,26 +7064,26 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>OTHERTRAF_VIO</t>
+          <t>DRUGS</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>E LINCOLN ST &amp; S ROCK RD</t>
+          <t>500 BLOCK OF S HUNTER ST</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>37.67198361320128</v>
+        <v>37.67912059117884</v>
       </c>
       <c r="K75" t="n">
-        <v>-97.24446143278816</v>
+        <v>-97.25894321098265</v>
       </c>
       <c r="L75" t="n">
-        <v>1219.7</v>
+        <v>1089.5</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Otv-hit and run on Jul 24, 2026, 1220 m from Towne East Square (E LINCOLN ST &amp; S ROCK RD). Case #26C139721 (use for a records request — full narratives are not published in open data).</t>
+          <t>Possession of paraphernalia on Jul 30, 2026, 1090 m from Towne East Square (500 BLOCK OF S HUNTER ST). Case #26C143936 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7109,44 +7105,44 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>26C139922</t>
+          <t>26C520567</t>
         </is>
       </c>
       <c r="E76" s="3" t="n">
-        <v>46227.95277777778</v>
+        <v>46227.6875</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>BATTERY ABW</t>
+          <t>LARCENY B FROM AUTO</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>SIM_ASSAULT</t>
+          <t>LARCENY</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>7000 BLOCK OF E LINCOLN ST</t>
+          <t>7200 BLOCK OF E BAYLEY ST</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>37.67195398477438</v>
+        <v>37.67101904846645</v>
       </c>
       <c r="K76" t="n">
-        <v>-97.25533959083543</v>
+        <v>-97.25239274309988</v>
       </c>
       <c r="L76" t="n">
-        <v>1383.4</v>
+        <v>1370.6</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Battery abw on Jul 24, 2026, 1383 m from Towne East Square (7000 BLOCK OF E LINCOLN ST). Case #26C139922 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny b from auto on Jul 24, 2026, 1371 m from Towne East Square (7200 BLOCK OF E BAYLEY ST). Case #26C520567 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7168,15 +7164,15 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>26C140815</t>
+          <t>26C520979</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
-        <v>46229.30625</v>
+        <v>46231.94583333333</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>MISC REPORT</t>
+          <t>SUSPICIOUS CHARACTER SIB UNIT</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -7186,26 +7182,26 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>MISC_REPORT</t>
+          <t>SUSP_CHARAC</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>900 BLOCK OF S APACHE DR</t>
+          <t>500 BLOCK OF N ROCK RD</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>37.67195267201163</v>
+        <v>37.6938385342284</v>
       </c>
       <c r="K77" t="n">
-        <v>-97.25741761429009</v>
+        <v>-97.24455420498546</v>
       </c>
       <c r="L77" t="n">
-        <v>1484.1</v>
+        <v>1264</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Misc report on Jul 26, 2026, 1484 m from Towne East Square (900 BLOCK OF S APACHE DR). Case #26C140815 (use for a records request — full narratives are not published in open data).</t>
+          <t>Suspicious character sib unit on Jul 28, 2026, 1264 m from Towne East Square (500 BLOCK OF N ROCK RD). Case #26C520979 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7227,44 +7223,44 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>26C142785</t>
+          <t>26C520282</t>
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>46231.96458333333</v>
+        <v>46231.625</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>EVADE POLICE</t>
+          <t>LOST MISC PROPERTY</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>DRIVING_VIO</t>
+          <t>LOST_PROPERTY</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>E KELLOGG DR &amp; S ROCK RD</t>
+          <t>7000 BLOCK OF E KELLOGG ST</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>37.67911842691625</v>
+        <v>37.67951495831583</v>
       </c>
       <c r="K78" t="n">
-        <v>-97.24451202953301</v>
+        <v>-97.25782989544317</v>
       </c>
       <c r="L78" t="n">
-        <v>473.3</v>
+        <v>982.3</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Evade police on Jul 28, 2026, 473 m from Towne East Square (E KELLOGG DR &amp; S ROCK RD). Case #26C142785 (use for a records request — full narratives are not published in open data).</t>
+          <t>Lost misc property on Jul 28, 2026, 982 m from Towne East Square (7000 BLOCK OF E KELLOGG ST). Case #26C520282 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7286,44 +7282,44 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>26C142917</t>
+          <t>26C520741</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>46232.18194444444</v>
+        <v>46228.86111111111</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>WINDOWPEEPING</t>
+          <t>LARCENY B AUTO ACCESSORIES</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>SEX_OFFENSES1</t>
+          <t>LARCENY</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>700 BLOCK OF S HUNTER ST</t>
+          <t>7700 BLOCK OF E KELLOGG DR</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>37.67688443377517</v>
+        <v>37.67911394923933</v>
       </c>
       <c r="K79" t="n">
-        <v>-97.26003808987583</v>
+        <v>-97.24743308095542</v>
       </c>
       <c r="L79" t="n">
-        <v>1285.1</v>
+        <v>398.7</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Windowpeeping on Jul 29, 2026, 1285 m from Towne East Square (700 BLOCK OF S HUNTER ST). Case #26C142917 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny b auto accessories on Jul 25, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG DR). Case #26C520741 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7345,44 +7341,44 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>26C141216</t>
+          <t>26C520933</t>
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>46229.90069444444</v>
+        <v>46230.6125</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>CHECKED WELFARE OF A CHILD</t>
+          <t>LARCENY B SHOPLIFT</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>FAMILY</t>
+          <t>LARCENY</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>7300 BLOCK OF E KELLOGG ST</t>
+          <t>7700 BLOCK OF E KELLOGG ST</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>37.67974587023429</v>
+        <v>37.67911394923933</v>
       </c>
       <c r="K80" t="n">
-        <v>-97.25225228651782</v>
+        <v>-97.24743308095542</v>
       </c>
       <c r="L80" t="n">
-        <v>537.4</v>
+        <v>398.7</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Checked welfare of a child on Jul 26, 2026, 537 m from Towne East Square (7300 BLOCK OF E KELLOGG ST). Case #26C141216 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny b shoplift on Jul 27, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C520933 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -7404,302 +7400,294 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>26C143148</t>
+          <t>26C521105</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>46232.52430555555</v>
-      </c>
-      <c r="F81" t="inlineStr"/>
+        <v>46233.075</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>REVOCATION SUSP DL</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr">
         <is>
           <t>OTHER</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>OTHERTRAF_VIO</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>900 BLOCK OF S ENOCH DR</t>
+          <t>700 BLOCK OF S WOODLAWN BLVD</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>37.67197658912259</v>
+        <v>37.67556302964613</v>
       </c>
       <c r="K81" t="n">
-        <v>-97.2456018407935</v>
+        <v>-97.26215557703324</v>
       </c>
       <c r="L81" t="n">
-        <v>1203</v>
+        <v>1520.5</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Incident on Jul 29, 2026, 1203 m from Towne East Square (900 BLOCK OF S ENOCH DR). Case #26C143148 (use for a records request — full narratives are not published in open data).</t>
+          <t>Revocation susp dl on Jul 30, 2026, 1520 m from Towne East Square (700 BLOCK OF S WOODLAWN BLVD). Case #26C521105 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>26C141683</t>
+          <t xml:space="preserve">TE202675652         </t>
         </is>
       </c>
       <c r="E82" s="3" t="n">
-        <v>46230.58541666667</v>
+        <v>46230.77569444444</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>MISC OFFICERS</t>
+          <t xml:space="preserve">[13B] ASSAULT [DV]                                                              </t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>OUTSIDE_CASE</t>
-        </is>
-      </c>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
-          <t>8100 BLOCK OF E KELLOGG ST</t>
+          <t>5XXX S ARIZONA MILLS CIR</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>37.6797148529391</v>
+        <v>33.38314167531927</v>
       </c>
       <c r="K82" t="n">
-        <v>-97.24233946631864</v>
+        <v>-111.9645674529712</v>
       </c>
       <c r="L82" t="n">
-        <v>556.7</v>
+        <v>14.7</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Misc officers on Jul 27, 2026, 557 m from Towne East Square (8100 BLOCK OF E KELLOGG ST). Case #26C141683 (use for a records request — full narratives are not published in open data).</t>
+          <t>[13b] assault [dv] on Jul 27, 2026, 15 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675652          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>26C143446</t>
+          <t xml:space="preserve">TE202674996         </t>
         </is>
       </c>
       <c r="E83" s="3" t="n">
-        <v>46232.7125</v>
+        <v>46228.65694444445</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>LARCENY B SHOPLIFT</t>
+          <t xml:space="preserve">[SC-0] INFO - INFORMATION OTHER (NON-CRIMINAL)                                  </t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>LARCENY</t>
-        </is>
-      </c>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG ST</t>
+          <t>5XXX S ARIZONA MILLS CIR</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>37.67911394923933</v>
+        <v>33.38314167531927</v>
       </c>
       <c r="K83" t="n">
-        <v>-97.24743308095542</v>
+        <v>-111.9645674529712</v>
       </c>
       <c r="L83" t="n">
-        <v>398.7</v>
+        <v>14.7</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Larceny b shoplift on Jul 29, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C143446 (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] info - information other (non-criminal) on Jul 25, 2026, 15 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202674996          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>26C144013</t>
+          <t xml:space="preserve">TE202674783         </t>
         </is>
       </c>
       <c r="E84" s="3" t="n">
-        <v>46233.63055555556</v>
+        <v>46227.91319444445</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>LARCENY B SHOPLIFT</t>
+          <t xml:space="preserve">[13B] ASSAULT                                                                   </t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>LARCENY</t>
-        </is>
-      </c>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG DR</t>
+          <t>5XXX S ARIZONA MILLS CIR</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>37.67911394923933</v>
+        <v>33.38314167531927</v>
       </c>
       <c r="K84" t="n">
-        <v>-97.24743308095542</v>
+        <v>-111.9645674529712</v>
       </c>
       <c r="L84" t="n">
-        <v>398.7</v>
+        <v>14.7</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Larceny b shoplift on Jul 30, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG DR). Case #26C144013 (use for a records request — full narratives are not published in open data).</t>
+          <t>[13b] assault on Jul 24, 2026, 15 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202674783          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>26C144067</t>
+          <t xml:space="preserve">TE202675415         </t>
         </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v>46232.71180555555</v>
+        <v>46229.95</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>PRVT PROP NON-INJURY ACCIDENT</t>
+          <t xml:space="preserve">[90J] TRESPASSING                                                               </t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>TRAFFIC</t>
-        </is>
-      </c>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
-          <t>8000 BLOCK OF E DOUGLAS AVE</t>
+          <t>5XXX S ARIZONA MILLS CIR</t>
         </is>
       </c>
       <c r="J85" t="n">
-        <v>37.6865673723019</v>
+        <v>33.38341075529574</v>
       </c>
       <c r="K85" t="n">
-        <v>-97.24449812404205</v>
+        <v>-111.9652490281131</v>
       </c>
       <c r="L85" t="n">
-        <v>501</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Prvt prop non-injury accident on Jul 29, 2026, 501 m from Towne East Square (8000 BLOCK OF E DOUGLAS AVE). Case #26C144067 (use for a records request — full narratives are not published in open data).</t>
+          <t>[90j] trespassing on Jul 26, 2026, 69 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675415          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>26C142294</t>
+          <t xml:space="preserve">TE202675399         </t>
         </is>
       </c>
       <c r="E86" s="3" t="n">
-        <v>46231.42847222222</v>
+        <v>46229.9</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FOUND MISC PROPERTY</t>
+          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -7707,176 +7695,164 @@
           <t>PROPERTY</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>FOUND_PROP</t>
-        </is>
-      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
-          <t>700 BLOCK OF S MISSION RD</t>
+          <t>5XXX S ARIZONA MILLS CIR</t>
         </is>
       </c>
       <c r="J86" t="n">
-        <v>37.6756469679485</v>
+        <v>33.38552975305072</v>
       </c>
       <c r="K86" t="n">
-        <v>-97.25850032865422</v>
+        <v>-111.965328834686</v>
       </c>
       <c r="L86" t="n">
-        <v>1251.5</v>
+        <v>262</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Found misc property on Jul 28, 2026, 1251 m from Towne East Square (700 BLOCK OF S MISSION RD). Case #26C142294 (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] trespass warning - private property on Jul 26, 2026, 262 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675399          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>26C144131</t>
+          <t xml:space="preserve">TE202676101         </t>
         </is>
       </c>
       <c r="E87" s="3" t="n">
-        <v>46233.7625</v>
+        <v>46232.21041666667</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>MISC REPORT</t>
+          <t xml:space="preserve">[240] MOTOR VEHICLE THEFT                                                       </t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>MISC_REPORT</t>
-        </is>
-      </c>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
-          <t>E BAYLEY ST &amp; S GOVERNEOUR RD</t>
+          <t>5XXX S ARIZONA MILLS CIR</t>
         </is>
       </c>
       <c r="J87" t="n">
-        <v>37.67014134415807</v>
+        <v>33.38580430470485</v>
       </c>
       <c r="K87" t="n">
-        <v>-97.25360392908074</v>
+        <v>-111.9660628528483</v>
       </c>
       <c r="L87" t="n">
-        <v>1498.8</v>
+        <v>315.7</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Misc report on Jul 30, 2026, 1499 m from Towne East Square (E BAYLEY ST &amp; S GOVERNEOUR RD). Case #26C144131 (use for a records request — full narratives are not published in open data).</t>
+          <t>[240] motor vehicle theft on Jul 29, 2026, 316 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202676101          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>26C143812</t>
+          <t xml:space="preserve">TE202676030         </t>
         </is>
       </c>
       <c r="E88" s="3" t="n">
-        <v>46232.88888888889</v>
+        <v>46231.83194444444</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>OTV-HIT AND RUN</t>
+          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>OTHERTRAF_VIO</t>
-        </is>
-      </c>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
-          <t>400 BLOCK OF S ROCK RD</t>
+          <t>5XXX S ARIZONA MILLS CIR</t>
         </is>
       </c>
       <c r="J88" t="n">
-        <v>37.68150034571348</v>
+        <v>33.3805974892332</v>
       </c>
       <c r="K88" t="n">
-        <v>-97.24450622724754</v>
+        <v>-111.9623154538272</v>
       </c>
       <c r="L88" t="n">
-        <v>288.9</v>
+        <v>361.4</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Otv-hit and run on Jul 29, 2026, 289 m from Towne East Square (400 BLOCK OF S ROCK RD). Case #26C143812 (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] trespass warning - private property on Jul 28, 2026, 361 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202676030          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>26C139586</t>
+          <t xml:space="preserve">TE202674893         </t>
         </is>
       </c>
       <c r="E89" s="3" t="n">
-        <v>46227.55138888889</v>
+        <v>46228.35972222222</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>MISC REPORT</t>
+          <t xml:space="preserve">[GO-0] ASSIST OTHER AGENCY                                                      </t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -7884,58 +7860,54 @@
           <t>OTHER</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>MISC_REPORT</t>
-        </is>
-      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
-          <t>600 BLOCK OF S EASTERN AVE</t>
+          <t>4XXX S WENDLER DR</t>
         </is>
       </c>
       <c r="J89" t="n">
-        <v>37.6774046653855</v>
+        <v>33.38130369903515</v>
       </c>
       <c r="K89" t="n">
-        <v>-97.23656061094495</v>
+        <v>-111.9695754725762</v>
       </c>
       <c r="L89" t="n">
-        <v>1122.4</v>
+        <v>517</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Misc report on Jul 24, 2026, 1122 m from Towne East Square (600 BLOCK OF S EASTERN AVE). Case #26C139586 (use for a records request — full narratives are not published in open data).</t>
+          <t>[go-0] assist other agency on Jul 25, 2026, 517 m from Arizona Mills (4XXX S WENDLER DR). Case #TE202674893          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>26C144101</t>
+          <t xml:space="preserve">TE202675649         </t>
         </is>
       </c>
       <c r="E90" s="3" t="n">
-        <v>46233.72152777778</v>
+        <v>46230.76944444444</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>MISC REPORT</t>
+          <t xml:space="preserve">[SC-0] WELFARE CHECK                                                            </t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -7943,54 +7915,50 @@
           <t>OTHER</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>MISC_REPORT</t>
-        </is>
-      </c>
+      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
-          <t>600 BLOCK OF S APACHE DR</t>
+          <t>4XXX S DARROW DR</t>
         </is>
       </c>
       <c r="J90" t="n">
-        <v>37.67516836949827</v>
+        <v>33.38128291577831</v>
       </c>
       <c r="K90" t="n">
-        <v>-97.25367616461408</v>
+        <v>-111.9593051545489</v>
       </c>
       <c r="L90" t="n">
-        <v>1002.3</v>
+        <v>533.1</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Misc report on Jul 30, 2026, 1002 m from Towne East Square (600 BLOCK OF S APACHE DR). Case #26C144101 (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] welfare check on Jul 27, 2026, 533 m from Arizona Mills (4XXX S DARROW DR). Case #TE202675649          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>26C139706</t>
+          <t xml:space="preserve">TE202676505         </t>
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>46227.66875</v>
+        <v>46233.33055555556</v>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
@@ -8001,287 +7969,267 @@
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG ST</t>
+          <t>PRIEST DR / W US 60</t>
         </is>
       </c>
       <c r="J91" t="n">
-        <v>37.67911394923933</v>
+        <v>33.38739758078362</v>
       </c>
       <c r="K91" t="n">
-        <v>-97.24743308095542</v>
+        <v>-111.9609102222452</v>
       </c>
       <c r="L91" t="n">
-        <v>398.7</v>
+        <v>568.9</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Incident on Jul 24, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C139706 (use for a records request — full narratives are not published in open data).</t>
+          <t>Incident on Jul 30, 2026, 569 m from Arizona Mills (PRIEST DR / W US 60). Case #TE202676505          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>26C141863</t>
+          <t xml:space="preserve">TE202676469         </t>
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>46230.75486111111</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>RUNAWAY</t>
-        </is>
-      </c>
+        <v>46233.21041666667</v>
+      </c>
+      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
           <t>OTHER</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>MISC_OFFENSES</t>
-        </is>
-      </c>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
-          <t>700 BLOCK OF S HUNTER ST</t>
+          <t>4XXX S PRIEST DR</t>
         </is>
       </c>
       <c r="J92" t="n">
-        <v>37.67688443377517</v>
+        <v>33.38356449694355</v>
       </c>
       <c r="K92" t="n">
-        <v>-97.26003808987583</v>
+        <v>-111.9581399763744</v>
       </c>
       <c r="L92" t="n">
-        <v>1285.1</v>
+        <v>594.2</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Runaway on Jul 27, 2026, 1285 m from Towne East Square (700 BLOCK OF S HUNTER ST). Case #26C141863 (use for a records request — full narratives are not published in open data).</t>
+          <t>Incident on Jul 30, 2026, 594 m from Arizona Mills (4XXX S PRIEST DR). Case #TE202676469          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>26C142249</t>
+          <t xml:space="preserve">TE2026601265        </t>
         </is>
       </c>
       <c r="E93" s="3" t="n">
-        <v>46230.75</v>
+        <v>46229.48611111111</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>BATTERY ABW</t>
+          <t xml:space="preserve">[23C] SHOPLIFTING                                                               </t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>SIM_ASSAULT</t>
-        </is>
-      </c>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
-          <t>700 BLOCK OF S MISSION RD</t>
+          <t>1XXX W BASELINE RD</t>
         </is>
       </c>
       <c r="J93" t="n">
-        <v>37.6756469679485</v>
+        <v>33.37921050936001</v>
       </c>
       <c r="K93" t="n">
-        <v>-97.25850032865422</v>
+        <v>-111.9595924257048</v>
       </c>
       <c r="L93" t="n">
-        <v>1251.5</v>
+        <v>643.4</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Battery abw on Jul 27, 2026, 1251 m from Towne East Square (700 BLOCK OF S MISSION RD). Case #26C142249 (use for a records request — full narratives are not published in open data).</t>
+          <t>[23c] shoplifting on Jul 26, 2026, 643 m from Arizona Mills (1XXX W BASELINE RD). Case #TE2026601265         (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>26C142387</t>
+          <t xml:space="preserve">TE202675235         </t>
         </is>
       </c>
       <c r="E94" s="3" t="n">
-        <v>46230.81597222222</v>
+        <v>46229.31597222222</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>PRVT PROP NON-INJURY ACCIDENT</t>
+          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PUBLIC PLACES                                         </t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>TRAFFIC</t>
-        </is>
-      </c>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
-          <t>100 BLOCK OF S ROCK RD</t>
+          <t>BASELINE RD / I10</t>
         </is>
       </c>
       <c r="J94" t="n">
-        <v>37.6865673723019</v>
+        <v>33.37824262058852</v>
       </c>
       <c r="K94" t="n">
-        <v>-97.24449812404205</v>
+        <v>-111.9680044627475</v>
       </c>
       <c r="L94" t="n">
-        <v>501</v>
+        <v>645.4</v>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Prvt prop non-injury accident on Jul 27, 2026, 501 m from Towne East Square (100 BLOCK OF S ROCK RD). Case #26C142387 (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] trespass warning - public places on Jul 26, 2026, 645 m from Arizona Mills (BASELINE RD / I10). Case #TE202675235          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>26C142657</t>
+          <t xml:space="preserve">TE202675001         </t>
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>46231.79166666666</v>
+        <v>46228.66944444444</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>INTERFERENCE W PARENTAL CUSTODY</t>
+          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>MISC_OFFENSES</t>
-        </is>
-      </c>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
-          <t>900 BLOCK OF S ENOCH DR</t>
+          <t>1XXX W BASELINE RD</t>
         </is>
       </c>
       <c r="J95" t="n">
-        <v>37.67197658912259</v>
+        <v>33.377865729326</v>
       </c>
       <c r="K95" t="n">
-        <v>-97.2456018407935</v>
+        <v>-111.9618554026273</v>
       </c>
       <c r="L95" t="n">
-        <v>1203</v>
+        <v>650.2</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Interference w parental custody on Jul 28, 2026, 1203 m from Towne East Square (900 BLOCK OF S ENOCH DR). Case #26C142657 (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] trespass warning - private property on Jul 25, 2026, 650 m from Arizona Mills (1XXX W BASELINE RD). Case #TE202675001          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>26C142768</t>
+          <t xml:space="preserve">TE202676035         </t>
         </is>
       </c>
       <c r="E96" s="3" t="n">
-        <v>46231.94305555556</v>
+        <v>46231.85555555556</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>CHECKED WELFARE OF A CHILD</t>
+          <t xml:space="preserve">[SC-0] SERVICE - ORDER OF PROTECTION (OOP) / INJUNCTION (P1)                    </t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -8289,117 +8237,109 @@
           <t>OTHER</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>FAMILY</t>
-        </is>
-      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
-          <t>6500 BLOCK OF E MORRIS ST</t>
+          <t>1XXX W LA JOLLA DR</t>
         </is>
       </c>
       <c r="J96" t="n">
-        <v>37.67377815761698</v>
+        <v>33.38909587497265</v>
       </c>
       <c r="K96" t="n">
-        <v>-97.2605034310844</v>
+        <v>-111.961540133513</v>
       </c>
       <c r="L96" t="n">
-        <v>1519.9</v>
+        <v>704.8</v>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Checked welfare of a child on Jul 28, 2026, 1520 m from Towne East Square (6500 BLOCK OF E MORRIS ST). Case #26C142768 (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] service - order of protection (oop) / injunction (p1) on Jul 28, 2026, 705 m from Arizona Mills (1XXX W LA JOLLA DR). Case #TE202676035          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>26C143218</t>
+          <t xml:space="preserve">TE202675946         </t>
         </is>
       </c>
       <c r="E97" s="3" t="n">
-        <v>46232.58333333334</v>
+        <v>46231.63888888889</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>DISTURB THE PEACE</t>
+          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>DISORDERLY</t>
-        </is>
-      </c>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
-          <t>700 BLOCK OF S HUNTER ST</t>
+          <t>1XXX W BASELINE RD</t>
         </is>
       </c>
       <c r="J97" t="n">
-        <v>37.67688443377517</v>
+        <v>33.37795738260824</v>
       </c>
       <c r="K97" t="n">
-        <v>-97.26003808987583</v>
+        <v>-111.959149564986</v>
       </c>
       <c r="L97" t="n">
-        <v>1285.1</v>
+        <v>773.7</v>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Disturb the peace on Jul 29, 2026, 1285 m from Towne East Square (700 BLOCK OF S HUNTER ST). Case #26C143218 (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] trespass warning - private property on Jul 28, 2026, 774 m from Arizona Mills (1XXX W BASELINE RD). Case #TE202675946          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>26C143562</t>
+          <t xml:space="preserve">TE202674935         </t>
         </is>
       </c>
       <c r="E98" s="3" t="n">
-        <v>46232.93958333333</v>
+        <v>46228.47222222222</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>MENTAL CASES</t>
+          <t xml:space="preserve">[SC-0] ASSIST - MENTALLY ILL (OTHER THAN MHP/EMHETR)                            </t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -8407,117 +8347,109 @@
           <t>OTHER</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>MENTAL_CASE</t>
-        </is>
-      </c>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
-          <t>600 BLOCK OF S EASTERN AVE</t>
+          <t>1XXX W BASELINE RD</t>
         </is>
       </c>
       <c r="J98" t="n">
-        <v>37.6774046653855</v>
+        <v>33.37594547787401</v>
       </c>
       <c r="K98" t="n">
-        <v>-97.23656061094495</v>
+        <v>-111.9593287567214</v>
       </c>
       <c r="L98" t="n">
-        <v>1122.4</v>
+        <v>946.9</v>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Mental cases on Jul 29, 2026, 1122 m from Towne East Square (600 BLOCK OF S EASTERN AVE). Case #26C143562 (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] assist - mentally ill (other than mhp/emhetr) on Jul 25, 2026, 947 m from Arizona Mills (1XXX W BASELINE RD). Case #TE202674935          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>26C143576</t>
+          <t xml:space="preserve">TE202674869         </t>
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>46232.96111111111</v>
+        <v>46228.26388888889</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>MISC REPORT</t>
+          <t xml:space="preserve">[SC-0] LOST - PROPERTY (NON-FIREARM, OTHER THAN GOV'T ISSUED ID)                </t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>MISC_REPORT</t>
-        </is>
-      </c>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
-          <t>7500 BLOCK OF E LINCOLN ST</t>
+          <t>PARKSIDE DR / W FREMONT DR</t>
         </is>
       </c>
       <c r="J99" t="n">
-        <v>37.67197300274878</v>
+        <v>33.38169955020192</v>
       </c>
       <c r="K99" t="n">
-        <v>-97.24902708647107</v>
+        <v>-111.954283203492</v>
       </c>
       <c r="L99" t="n">
-        <v>1201.1</v>
+        <v>967.3</v>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Misc report on Jul 29, 2026, 1201 m from Towne East Square (7500 BLOCK OF E LINCOLN ST). Case #26C143576 (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] lost - property (non-firearm, other than gov't issued id) on Jul 25, 2026, 967 m from Arizona Mills (PARKSIDE DR / W FREMONT DR). Case #TE202674869          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>26C143936</t>
+          <t xml:space="preserve">TE2026601259        </t>
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>46233.55972222222</v>
+        <v>46229.58055555556</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>POSSESSION OF PARAPHERNALIA</t>
+          <t xml:space="preserve">[0] CRIMINAL DAMAGE - UNDER $1000                                               </t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -8525,117 +8457,109 @@
           <t>OTHER</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>DRUGS</t>
-        </is>
-      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
-          <t>500 BLOCK OF S HUNTER ST</t>
+          <t>1XXX W SOUTHERN AVE</t>
         </is>
       </c>
       <c r="J100" t="n">
-        <v>37.67912059117884</v>
+        <v>33.39259581629993</v>
       </c>
       <c r="K100" t="n">
-        <v>-97.25894321098265</v>
+        <v>-111.9580558007179</v>
       </c>
       <c r="L100" t="n">
-        <v>1089.5</v>
+        <v>1198.6</v>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Possession of paraphernalia on Jul 30, 2026, 1090 m from Towne East Square (500 BLOCK OF S HUNTER ST). Case #26C143936 (use for a records request — full narratives are not published in open data).</t>
+          <t>[0] criminal damage - under $1000 on Jul 26, 2026, 1199 m from Arizona Mills (1XXX W SOUTHERN AVE). Case #TE2026601259         (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>26C520567</t>
+          <t xml:space="preserve">TE202676006         </t>
         </is>
       </c>
       <c r="E101" s="3" t="n">
-        <v>46227.6875</v>
+        <v>46231.77708333333</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>LARCENY B FROM AUTO</t>
+          <t xml:space="preserve">[GO-0] DEATH                                                                    </t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>LARCENY</t>
-        </is>
-      </c>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
-          <t>7200 BLOCK OF E BAYLEY ST</t>
+          <t>2XXX W SOUTHERN AVE</t>
         </is>
       </c>
       <c r="J101" t="n">
-        <v>37.67101904846645</v>
+        <v>33.38855944643347</v>
       </c>
       <c r="K101" t="n">
-        <v>-97.25239274309988</v>
+        <v>-111.9758211943486</v>
       </c>
       <c r="L101" t="n">
-        <v>1370.6</v>
+        <v>1202.1</v>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Larceny b from auto on Jul 24, 2026, 1371 m from Towne East Square (7200 BLOCK OF E BAYLEY ST). Case #26C520567 (use for a records request — full narratives are not published in open data).</t>
+          <t>[go-0] death on Jul 28, 2026, 1202 m from Arizona Mills (2XXX W SOUTHERN AVE). Case #TE202676006          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>26C520979</t>
+          <t xml:space="preserve">TE202674741         </t>
         </is>
       </c>
       <c r="E102" s="3" t="n">
-        <v>46231.94583333333</v>
+        <v>46227.81666666667</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>SUSPICIOUS CHARACTER SIB UNIT</t>
+          <t xml:space="preserve">[SC-0] SERVICE - ORDER OF PROTECTION (OOP) / INJUNCTION (P1)                    </t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -8643,264 +8567,244 @@
           <t>OTHER</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>SUSP_CHARAC</t>
-        </is>
-      </c>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
-          <t>500 BLOCK OF N ROCK RD</t>
+          <t>5XXX S HARDY DR</t>
         </is>
       </c>
       <c r="J102" t="n">
-        <v>37.6938385342284</v>
+        <v>33.37634047797651</v>
       </c>
       <c r="K102" t="n">
-        <v>-97.24455420498546</v>
+        <v>-111.9531278046354</v>
       </c>
       <c r="L102" t="n">
-        <v>1264</v>
+        <v>1309.4</v>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Suspicious character sib unit on Jul 28, 2026, 1264 m from Towne East Square (500 BLOCK OF N ROCK RD). Case #26C520979 (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] service - order of protection (oop) / injunction (p1) on Jul 24, 2026, 1309 m from Arizona Mills (5XXX S HARDY DR). Case #TE202674741          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>26C520282</t>
+          <t xml:space="preserve">TE202674714         </t>
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>46231.625</v>
+        <v>46227.7375</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>LOST MISC PROPERTY</t>
+          <t xml:space="preserve">[13A] AGGRAVATED ASSAULT [DV]                                                   </t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>LOST_PROPERTY</t>
-        </is>
-      </c>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
-          <t>7000 BLOCK OF E KELLOGG ST</t>
+          <t>5XXX S HARDY DR</t>
         </is>
       </c>
       <c r="J103" t="n">
-        <v>37.67951495831583</v>
+        <v>33.37634047797651</v>
       </c>
       <c r="K103" t="n">
-        <v>-97.25782989544317</v>
+        <v>-111.9531278046354</v>
       </c>
       <c r="L103" t="n">
-        <v>982.3</v>
+        <v>1309.4</v>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Lost misc property on Jul 28, 2026, 982 m from Towne East Square (7000 BLOCK OF E KELLOGG ST). Case #26C520282 (use for a records request — full narratives are not published in open data).</t>
+          <t>[13a] aggravated assault [dv] on Jul 24, 2026, 1309 m from Arizona Mills (5XXX S HARDY DR). Case #TE202674714          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>26C520741</t>
+          <t xml:space="preserve">TE202675136         </t>
         </is>
       </c>
       <c r="E104" s="3" t="n">
-        <v>46228.86111111111</v>
+        <v>46228.97847222222</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>LARCENY B AUTO ACCESSORIES</t>
+          <t xml:space="preserve">[13B] ASSAULT                                                                   </t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>LARCENY</t>
-        </is>
-      </c>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG DR</t>
+          <t>5XXX S HARDY DR</t>
         </is>
       </c>
       <c r="J104" t="n">
-        <v>37.67911394923933</v>
+        <v>33.3757495513233</v>
       </c>
       <c r="K104" t="n">
-        <v>-97.24743308095542</v>
+        <v>-111.9531832468173</v>
       </c>
       <c r="L104" t="n">
-        <v>398.7</v>
+        <v>1345.1</v>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Larceny b auto accessories on Jul 25, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG DR). Case #26C520741 (use for a records request — full narratives are not published in open data).</t>
+          <t>[13b] assault on Jul 25, 2026, 1345 m from Arizona Mills (5XXX S HARDY DR). Case #TE202675136          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>26C520933</t>
+          <t xml:space="preserve">TE202676025         </t>
         </is>
       </c>
       <c r="E105" s="3" t="n">
-        <v>46230.6125</v>
+        <v>46231.82430555556</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>LARCENY B SHOPLIFT</t>
+          <t xml:space="preserve">[SC-0] WARRANT - BOOKED INTO DETENTION                                          </t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>LARCENY</t>
-        </is>
-      </c>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
-          <t>7700 BLOCK OF E KELLOGG ST</t>
+          <t>7XXX S 48TH ST</t>
         </is>
       </c>
       <c r="J105" t="n">
-        <v>37.67911394923933</v>
+        <v>33.38154948911996</v>
       </c>
       <c r="K105" t="n">
-        <v>-97.24743308095542</v>
+        <v>-111.9788828064167</v>
       </c>
       <c r="L105" t="n">
-        <v>398.7</v>
+        <v>1346.3</v>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Larceny b shoplift on Jul 27, 2026, 399 m from Towne East Square (7700 BLOCK OF E KELLOGG ST). Case #26C520933 (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] warrant - booked into detention on Jul 28, 2026, 1346 m from Arizona Mills (7XXX S 48TH ST). Case #TE202676025          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>26C521105</t>
+          <t xml:space="preserve">TE202674804         </t>
         </is>
       </c>
       <c r="E106" s="3" t="n">
-        <v>46233.075</v>
+        <v>46227.98263888889</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>REVOCATION SUSP DL</t>
+          <t xml:space="preserve">[240] MOTOR VEHICLE THEFT                                                       </t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>OTHERTRAF_VIO</t>
-        </is>
-      </c>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
-          <t>700 BLOCK OF S WOODLAWN BLVD</t>
+          <t>MCKEMY ST / S HARDY DR</t>
         </is>
       </c>
       <c r="J106" t="n">
-        <v>37.67556302964613</v>
+        <v>33.37562594922362</v>
       </c>
       <c r="K106" t="n">
-        <v>-97.26215557703324</v>
+        <v>-111.9529211309643</v>
       </c>
       <c r="L106" t="n">
-        <v>1520.5</v>
+        <v>1372.7</v>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Revocation susp dl on Jul 30, 2026, 1520 m from Towne East Square (700 BLOCK OF S WOODLAWN BLVD). Case #26C521105 (use for a records request — full narratives are not published in open data).</t>
+          <t>[240] motor vehicle theft on Jul 24, 2026, 1373 m from Arizona Mills (MCKEMY ST / S HARDY DR). Case #TE202674804          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -8922,40 +8826,40 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202675652         </t>
+          <t xml:space="preserve">TE202675422         </t>
         </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v>46230.77569444444</v>
+        <v>46229.96111111111</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">[13B] ASSAULT [DV]                                                              </t>
+          <t xml:space="preserve">[SC-0] INFO - INFORMATION OTHER (NON-CRIMINAL)                                  </t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
-          <t>5XXX S ARIZONA MILLS CIR</t>
+          <t>3XXX S 52ND ST</t>
         </is>
       </c>
       <c r="J107" t="n">
-        <v>33.38314167531927</v>
+        <v>33.3959248712565</v>
       </c>
       <c r="K107" t="n">
-        <v>-111.9645674529712</v>
+        <v>-111.9704886613678</v>
       </c>
       <c r="L107" t="n">
-        <v>14.7</v>
+        <v>1512</v>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>[13b] assault [dv] on Jul 27, 2026, 15 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675652          (use for a records request — full narratives are not published in open data).</t>
+          <t>[sc-0] info - information other (non-criminal) on Jul 26, 2026, 1512 m from Arizona Mills (3XXX S 52ND ST). Case #TE202675422          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -8977,17 +8881,13 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202674996         </t>
+          <t xml:space="preserve">TE202674830         </t>
         </is>
       </c>
       <c r="E108" s="3" t="n">
-        <v>46228.65694444445</v>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[SC-0] INFO - INFORMATION OTHER (NON-CRIMINAL)                                  </t>
-        </is>
-      </c>
+        <v>46228.05902777778</v>
+      </c>
+      <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
           <t>OTHER</t>
@@ -8996,21 +8896,21 @@
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
-          <t>5XXX S ARIZONA MILLS CIR</t>
+          <t>SOUTHERN AVE / S HARDY DR</t>
         </is>
       </c>
       <c r="J108" t="n">
-        <v>33.38314167531927</v>
+        <v>33.39284504948579</v>
       </c>
       <c r="K108" t="n">
-        <v>-111.9645674529712</v>
+        <v>-111.9519846600515</v>
       </c>
       <c r="L108" t="n">
-        <v>14.7</v>
+        <v>1578</v>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>[sc-0] info - information other (non-criminal) on Jul 25, 2026, 15 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202674996          (use for a records request — full narratives are not published in open data).</t>
+          <t>Incident on Jul 25, 2026, 1578 m from Arizona Mills (SOUTHERN AVE / S HARDY DR). Case #TE202674830          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -9032,1416 +8932,45 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202674783         </t>
+          <t xml:space="preserve">TE202675096         </t>
         </is>
       </c>
       <c r="E109" s="3" t="n">
-        <v>46227.91319444445</v>
+        <v>46228.88680555556</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">[13B] ASSAULT                                                                   </t>
+          <t xml:space="preserve">[11D] MOLESTATION OF A CHILD                                                    </t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
-          <t>5XXX S ARIZONA MILLS CIR</t>
+          <t>7XX W BASELINE RD</t>
         </is>
       </c>
       <c r="J109" t="n">
-        <v>33.38314167531927</v>
+        <v>33.37881261615141</v>
       </c>
       <c r="K109" t="n">
-        <v>-111.9645674529712</v>
+        <v>-111.9483590935493</v>
       </c>
       <c r="L109" t="n">
-        <v>14.7</v>
+        <v>1581.2</v>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>[13b] assault on Jul 24, 2026, 15 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202674783          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202675415         </t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="n">
-        <v>46229.95</v>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[90J] TRESPASSING                                                               </t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>QUALITY_OF_LIFE</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>5XXX S ARIZONA MILLS CIR</t>
-        </is>
-      </c>
-      <c r="J110" t="n">
-        <v>33.38341075529574</v>
-      </c>
-      <c r="K110" t="n">
-        <v>-111.9652490281131</v>
-      </c>
-      <c r="L110" t="n">
-        <v>68.59999999999999</v>
-      </c>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>[90j] trespassing on Jul 26, 2026, 69 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675415          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202675399         </t>
-        </is>
-      </c>
-      <c r="E111" s="3" t="n">
-        <v>46229.9</v>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>5XXX S ARIZONA MILLS CIR</t>
-        </is>
-      </c>
-      <c r="J111" t="n">
-        <v>33.38552975305072</v>
-      </c>
-      <c r="K111" t="n">
-        <v>-111.965328834686</v>
-      </c>
-      <c r="L111" t="n">
-        <v>262</v>
-      </c>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>[sc-0] trespass warning - private property on Jul 26, 2026, 262 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202675399          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202676101         </t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="n">
-        <v>46232.21041666667</v>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[240] MOTOR VEHICLE THEFT                                                       </t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>5XXX S ARIZONA MILLS CIR</t>
-        </is>
-      </c>
-      <c r="J112" t="n">
-        <v>33.38580430470485</v>
-      </c>
-      <c r="K112" t="n">
-        <v>-111.9660628528483</v>
-      </c>
-      <c r="L112" t="n">
-        <v>315.7</v>
-      </c>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>[240] motor vehicle theft on Jul 29, 2026, 316 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202676101          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202676030         </t>
-        </is>
-      </c>
-      <c r="E113" s="3" t="n">
-        <v>46231.83194444444</v>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>5XXX S ARIZONA MILLS CIR</t>
-        </is>
-      </c>
-      <c r="J113" t="n">
-        <v>33.3805974892332</v>
-      </c>
-      <c r="K113" t="n">
-        <v>-111.9623154538272</v>
-      </c>
-      <c r="L113" t="n">
-        <v>361.4</v>
-      </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>[sc-0] trespass warning - private property on Jul 28, 2026, 361 m from Arizona Mills (5XXX S ARIZONA MILLS CIR). Case #TE202676030          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202674893         </t>
-        </is>
-      </c>
-      <c r="E114" s="3" t="n">
-        <v>46228.35972222222</v>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[GO-0] ASSIST OTHER AGENCY                                                      </t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>4XXX S WENDLER DR</t>
-        </is>
-      </c>
-      <c r="J114" t="n">
-        <v>33.38130369903515</v>
-      </c>
-      <c r="K114" t="n">
-        <v>-111.9695754725762</v>
-      </c>
-      <c r="L114" t="n">
-        <v>517</v>
-      </c>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>[go-0] assist other agency on Jul 25, 2026, 517 m from Arizona Mills (4XXX S WENDLER DR). Case #TE202674893          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202675649         </t>
-        </is>
-      </c>
-      <c r="E115" s="3" t="n">
-        <v>46230.76944444444</v>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[SC-0] WELFARE CHECK                                                            </t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>4XXX S DARROW DR</t>
-        </is>
-      </c>
-      <c r="J115" t="n">
-        <v>33.38128291577831</v>
-      </c>
-      <c r="K115" t="n">
-        <v>-111.9593051545489</v>
-      </c>
-      <c r="L115" t="n">
-        <v>533.1</v>
-      </c>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>[sc-0] welfare check on Jul 27, 2026, 533 m from Arizona Mills (4XXX S DARROW DR). Case #TE202675649          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202674654         </t>
-        </is>
-      </c>
-      <c r="E116" s="3" t="n">
-        <v>46227.62708333333</v>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[GO-0] ACCIDENT - HIT AND RUN                                                   </t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>BASELINE RD / S DARROW DR</t>
-        </is>
-      </c>
-      <c r="J116" t="n">
-        <v>33.37825351544224</v>
-      </c>
-      <c r="K116" t="n">
-        <v>-111.9611381808533</v>
-      </c>
-      <c r="L116" t="n">
-        <v>640.6</v>
-      </c>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>[go-0] accident - hit and run on Jul 24, 2026, 641 m from Arizona Mills (BASELINE RD / S DARROW DR). Case #TE202674654          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202675235         </t>
-        </is>
-      </c>
-      <c r="E117" s="3" t="n">
-        <v>46229.31597222222</v>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PUBLIC PLACES                                         </t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>QUALITY_OF_LIFE</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>BASELINE RD / I10</t>
-        </is>
-      </c>
-      <c r="J117" t="n">
-        <v>33.37824262058852</v>
-      </c>
-      <c r="K117" t="n">
-        <v>-111.9680044627475</v>
-      </c>
-      <c r="L117" t="n">
-        <v>645.4</v>
-      </c>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>[sc-0] trespass warning - public places on Jul 26, 2026, 645 m from Arizona Mills (BASELINE RD / I10). Case #TE202675235          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202675001         </t>
-        </is>
-      </c>
-      <c r="E118" s="3" t="n">
-        <v>46228.66944444444</v>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>1XXX W BASELINE RD</t>
-        </is>
-      </c>
-      <c r="J118" t="n">
-        <v>33.377865729326</v>
-      </c>
-      <c r="K118" t="n">
-        <v>-111.9618554026273</v>
-      </c>
-      <c r="L118" t="n">
-        <v>650.2</v>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>[sc-0] trespass warning - private property on Jul 25, 2026, 650 m from Arizona Mills (1XXX W BASELINE RD). Case #TE202675001          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202676035         </t>
-        </is>
-      </c>
-      <c r="E119" s="3" t="n">
-        <v>46231.85555555556</v>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[SC-0] SERVICE - ORDER OF PROTECTION (OOP) / INJUNCTION (P1)                    </t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>1XXX W LA JOLLA DR</t>
-        </is>
-      </c>
-      <c r="J119" t="n">
-        <v>33.38909587497265</v>
-      </c>
-      <c r="K119" t="n">
-        <v>-111.961540133513</v>
-      </c>
-      <c r="L119" t="n">
-        <v>704.8</v>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>[sc-0] service - order of protection (oop) / injunction (p1) on Jul 28, 2026, 705 m from Arizona Mills (1XXX W LA JOLLA DR). Case #TE202676035          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202675946         </t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="n">
-        <v>46231.63888888889</v>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>1XXX W BASELINE RD</t>
-        </is>
-      </c>
-      <c r="J120" t="n">
-        <v>33.37795738260824</v>
-      </c>
-      <c r="K120" t="n">
-        <v>-111.959149564986</v>
-      </c>
-      <c r="L120" t="n">
-        <v>773.7</v>
-      </c>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>[sc-0] trespass warning - private property on Jul 28, 2026, 774 m from Arizona Mills (1XXX W BASELINE RD). Case #TE202675946          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202674935         </t>
-        </is>
-      </c>
-      <c r="E121" s="3" t="n">
-        <v>46228.47222222222</v>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[SC-0] ASSIST - MENTALLY ILL (OTHER THAN MHP/EMHETR)                            </t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>1XXX W BASELINE RD</t>
-        </is>
-      </c>
-      <c r="J121" t="n">
-        <v>33.37594547787401</v>
-      </c>
-      <c r="K121" t="n">
-        <v>-111.9593287567214</v>
-      </c>
-      <c r="L121" t="n">
-        <v>946.9</v>
-      </c>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>[sc-0] assist - mentally ill (other than mhp/emhetr) on Jul 25, 2026, 947 m from Arizona Mills (1XXX W BASELINE RD). Case #TE202674935          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202674869         </t>
-        </is>
-      </c>
-      <c r="E122" s="3" t="n">
-        <v>46228.26388888889</v>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[SC-0] LOST - PROPERTY (NON-FIREARM, OTHER THAN GOV'T ISSUED ID)                </t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>PARKSIDE DR / W FREMONT DR</t>
-        </is>
-      </c>
-      <c r="J122" t="n">
-        <v>33.38169955020192</v>
-      </c>
-      <c r="K122" t="n">
-        <v>-111.954283203492</v>
-      </c>
-      <c r="L122" t="n">
-        <v>967.3</v>
-      </c>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>[sc-0] lost - property (non-firearm, other than gov't issued id) on Jul 25, 2026, 967 m from Arizona Mills (PARKSIDE DR / W FREMONT DR). Case #TE202674869          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202674568         </t>
-        </is>
-      </c>
-      <c r="E123" s="3" t="n">
-        <v>46227.44722222222</v>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[SC-0] TRESPASS WARNING - PRIVATE PROPERTY                                      </t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>9XX W BASELINE RD</t>
-        </is>
-      </c>
-      <c r="J123" t="n">
-        <v>33.37784058487316</v>
-      </c>
-      <c r="K123" t="n">
-        <v>-111.9548908569819</v>
-      </c>
-      <c r="L123" t="n">
-        <v>1079.6</v>
-      </c>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>[sc-0] trespass warning - private property on Jul 24, 2026, 1080 m from Arizona Mills (9XX W BASELINE RD). Case #TE202674568          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE2026601259        </t>
-        </is>
-      </c>
-      <c r="E124" s="3" t="n">
-        <v>46229.58055555556</v>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[0] CRIMINAL DAMAGE - UNDER $1000                                               </t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>1XXX W SOUTHERN AVE</t>
-        </is>
-      </c>
-      <c r="J124" t="n">
-        <v>33.39259581629993</v>
-      </c>
-      <c r="K124" t="n">
-        <v>-111.9580558007179</v>
-      </c>
-      <c r="L124" t="n">
-        <v>1198.6</v>
-      </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>[0] criminal damage - under $1000 on Jul 26, 2026, 1199 m from Arizona Mills (1XXX W SOUTHERN AVE). Case #TE2026601259         (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202676006         </t>
-        </is>
-      </c>
-      <c r="E125" s="3" t="n">
-        <v>46231.77708333333</v>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[GO-0] DEATH                                                                    </t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>2XXX W SOUTHERN AVE</t>
-        </is>
-      </c>
-      <c r="J125" t="n">
-        <v>33.38855944643347</v>
-      </c>
-      <c r="K125" t="n">
-        <v>-111.9758211943486</v>
-      </c>
-      <c r="L125" t="n">
-        <v>1202.1</v>
-      </c>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>[go-0] death on Jul 28, 2026, 1202 m from Arizona Mills (2XXX W SOUTHERN AVE). Case #TE202676006          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202674741         </t>
-        </is>
-      </c>
-      <c r="E126" s="3" t="n">
-        <v>46227.81666666667</v>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[SC-0] SERVICE - ORDER OF PROTECTION (OOP) / INJUNCTION (P1)                    </t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>5XXX S HARDY DR</t>
-        </is>
-      </c>
-      <c r="J126" t="n">
-        <v>33.37634047797651</v>
-      </c>
-      <c r="K126" t="n">
-        <v>-111.9531278046354</v>
-      </c>
-      <c r="L126" t="n">
-        <v>1309.4</v>
-      </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>[sc-0] service - order of protection (oop) / injunction (p1) on Jul 24, 2026, 1309 m from Arizona Mills (5XXX S HARDY DR). Case #TE202674741          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202674557         </t>
-        </is>
-      </c>
-      <c r="E127" s="3" t="n">
-        <v>46227.4125</v>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[SC-0] WARNING - DISORDERLY CONDUCT                                             </t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>QUALITY_OF_LIFE</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>5XXX S HARDY DR</t>
-        </is>
-      </c>
-      <c r="J127" t="n">
-        <v>33.37634047797651</v>
-      </c>
-      <c r="K127" t="n">
-        <v>-111.9531278046354</v>
-      </c>
-      <c r="L127" t="n">
-        <v>1309.4</v>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>[sc-0] warning - disorderly conduct on Jul 24, 2026, 1309 m from Arizona Mills (5XXX S HARDY DR). Case #TE202674557          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202674714         </t>
-        </is>
-      </c>
-      <c r="E128" s="3" t="n">
-        <v>46227.7375</v>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[13A] AGGRAVATED ASSAULT [DV]                                                   </t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>5XXX S HARDY DR</t>
-        </is>
-      </c>
-      <c r="J128" t="n">
-        <v>33.37634047797651</v>
-      </c>
-      <c r="K128" t="n">
-        <v>-111.9531278046354</v>
-      </c>
-      <c r="L128" t="n">
-        <v>1309.4</v>
-      </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>[13a] aggravated assault [dv] on Jul 24, 2026, 1309 m from Arizona Mills (5XXX S HARDY DR). Case #TE202674714          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202675136         </t>
-        </is>
-      </c>
-      <c r="E129" s="3" t="n">
-        <v>46228.97847222222</v>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[13B] ASSAULT                                                                   </t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>5XXX S HARDY DR</t>
-        </is>
-      </c>
-      <c r="J129" t="n">
-        <v>33.3757495513233</v>
-      </c>
-      <c r="K129" t="n">
-        <v>-111.9531832468173</v>
-      </c>
-      <c r="L129" t="n">
-        <v>1345.1</v>
-      </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>[13b] assault on Jul 25, 2026, 1345 m from Arizona Mills (5XXX S HARDY DR). Case #TE202675136          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202676025         </t>
-        </is>
-      </c>
-      <c r="E130" s="3" t="n">
-        <v>46231.82430555556</v>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[SC-0] WARRANT - BOOKED INTO DETENTION                                          </t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>7XXX S 48TH ST</t>
-        </is>
-      </c>
-      <c r="J130" t="n">
-        <v>33.38154948911996</v>
-      </c>
-      <c r="K130" t="n">
-        <v>-111.9788828064167</v>
-      </c>
-      <c r="L130" t="n">
-        <v>1346.3</v>
-      </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>[sc-0] warrant - booked into detention on Jul 28, 2026, 1346 m from Arizona Mills (7XXX S 48TH ST). Case #TE202676025          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202674804         </t>
-        </is>
-      </c>
-      <c r="E131" s="3" t="n">
-        <v>46227.98263888889</v>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[240] MOTOR VEHICLE THEFT                                                       </t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>MCKEMY ST / S HARDY DR</t>
-        </is>
-      </c>
-      <c r="J131" t="n">
-        <v>33.37562594922362</v>
-      </c>
-      <c r="K131" t="n">
-        <v>-111.9529211309643</v>
-      </c>
-      <c r="L131" t="n">
-        <v>1372.7</v>
-      </c>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>[240] motor vehicle theft on Jul 24, 2026, 1373 m from Arizona Mills (MCKEMY ST / S HARDY DR). Case #TE202674804          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202675422         </t>
-        </is>
-      </c>
-      <c r="E132" s="3" t="n">
-        <v>46229.96111111111</v>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[SC-0] INFO - INFORMATION OTHER (NON-CRIMINAL)                                  </t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>3XXX S 52ND ST</t>
-        </is>
-      </c>
-      <c r="J132" t="n">
-        <v>33.3959248712565</v>
-      </c>
-      <c r="K132" t="n">
-        <v>-111.9704886613678</v>
-      </c>
-      <c r="L132" t="n">
-        <v>1512</v>
-      </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>[sc-0] info - information other (non-criminal) on Jul 26, 2026, 1512 m from Arizona Mills (3XXX S 52ND ST). Case #TE202675422          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202674830         </t>
-        </is>
-      </c>
-      <c r="E133" s="3" t="n">
-        <v>46228.05902777778</v>
-      </c>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>SOUTHERN AVE / S HARDY DR</t>
-        </is>
-      </c>
-      <c r="J133" t="n">
-        <v>33.39284504948579</v>
-      </c>
-      <c r="K133" t="n">
-        <v>-111.9519846600515</v>
-      </c>
-      <c r="L133" t="n">
-        <v>1578</v>
-      </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>Incident on Jul 25, 2026, 1578 m from Arizona Mills (SOUTHERN AVE / S HARDY DR). Case #TE202674830          (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>ARZMILLS</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Arizona Mills</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE202675096         </t>
-        </is>
-      </c>
-      <c r="E134" s="3" t="n">
-        <v>46228.88680555556</v>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[11D] MOLESTATION OF A CHILD                                                    </t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>7XX W BASELINE RD</t>
-        </is>
-      </c>
-      <c r="J134" t="n">
-        <v>33.37881261615141</v>
-      </c>
-      <c r="K134" t="n">
-        <v>-111.9483590935493</v>
-      </c>
-      <c r="L134" t="n">
-        <v>1581.2</v>
-      </c>
-      <c r="M134" t="inlineStr">
-        <is>
           <t>[11d] molestation of a child on Jul 25, 2026, 1581 m from Arizona Mills (7XX W BASELINE RD). Case #TE202675096          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M134"/>
+  <autoFilter ref="A1:M109"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10479,7 +9008,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-31 07:45:48.319120+00:00</t>
+          <t>2026-07-31 15:12:36.086883+00:00</t>
         </is>
       </c>
     </row>
@@ -10511,7 +9040,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-24 07:45:48.319120+00:00</t>
+          <t>2026-07-24 15:12:36.086883+00:00</t>
         </is>
       </c>
     </row>
@@ -10522,7 +9051,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>133</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7">
@@ -10567,7 +9096,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OK fetched=15 truncated=False</t>
+          <t>OK fetched=0 truncated=False</t>
         </is>
       </c>
     </row>
@@ -10579,7 +9108,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OK fetched=9 truncated=False</t>
+          <t>OK fetched=0 truncated=False</t>
         </is>
       </c>
     </row>
@@ -10591,7 +9120,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>OK fetched=12 truncated=False</t>
+          <t>OK fetched=11 truncated=False</t>
         </is>
       </c>
     </row>
@@ -10603,7 +9132,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OK fetched=12 truncated=False</t>
+          <t>OK fetched=13 truncated=False</t>
         </is>
       </c>
     </row>
@@ -10651,7 +9180,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>OK fetched=0 truncated=False</t>
+          <t>OK fetched=1 truncated=False</t>
         </is>
       </c>
     </row>
@@ -10675,7 +9204,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>OK fetched=28 truncated=False</t>
+          <t>OK fetched=31 truncated=False</t>
         </is>
       </c>
     </row>

--- a/reports/latest/blotter_report.xlsx
+++ b/reports/latest/blotter_report.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Highlights'!$A$1:$M$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$299</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$161</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1076,21 +1076,23 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>147</v>
+        <v>9</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>81</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>31</v>
-      </c>
-      <c r="J14" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>471.3</v>
+      </c>
       <c r="K14" s="3" t="n">
         <v>46233</v>
       </c>
@@ -1636,30 +1638,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>TACOMAMALL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Tacoma Mall</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>71878728447</t>
+          <t>2620701835</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>46230.4375</v>
+        <v>46229</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Robbery</t>
+          <t>Assault Simple</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1669,26 +1671,26 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>VIOLENT CRIME</t>
+          <t>Assault Offenses</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>16XX BLOCK OF N 105TH ST</t>
+          <t>4000 S LAWRENCE ST</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>47.70504225</v>
+        <v>47.219421</v>
       </c>
       <c r="K8" t="n">
-        <v>-122.338094779232</v>
+        <v>-122.478428</v>
       </c>
       <c r="L8" t="n">
-        <v>938.8</v>
+        <v>853.4</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Robbery on Jul 27, 2026, 939 m from Northgate Station (16XX BLOCK OF N 105TH ST). Case #2026-220064 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault simple on Jul 26, 2026, 853 m from Tacoma Mall (4000 S LAWRENCE ST). Case #2620701835 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -1710,15 +1712,15 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>71894237115</t>
+          <t>71878728447</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>46231.20833333334</v>
+        <v>46230.4375</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aggravated Assault</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1733,51 +1735,51 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15XX BLOCK OF NE 107TH ST</t>
+          <t>16XX BLOCK OF N 105TH ST</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>47.70668788</v>
+        <v>47.70504225</v>
       </c>
       <c r="K9" t="n">
-        <v>-122.311189997702</v>
+        <v>-122.338094779232</v>
       </c>
       <c r="L9" t="n">
-        <v>1145.7</v>
+        <v>938.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-221056 (use for a records request — full narratives are not published in open data).</t>
+          <t>Robbery on Jul 27, 2026, 939 m from Northgate Station (16XX BLOCK OF N 105TH ST). Case #2026-220064 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>TACOMAMALL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Tacoma Mall</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>71889871382</t>
+          <t>2621000152</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>46231.00625</v>
+        <v>46232</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Simple Assault</t>
+          <t>Assault Simple</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1787,56 +1789,56 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ALL OTHER</t>
+          <t>Assault Offenses</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15XX BLOCK OF NE 107TH ST</t>
+          <t>3500 S 45TH ST</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>47.70668788</v>
+        <v>47.216421</v>
       </c>
       <c r="K10" t="n">
-        <v>-122.311189997702</v>
+        <v>-122.482428</v>
       </c>
       <c r="L10" t="n">
-        <v>1145.7</v>
+        <v>1074.3</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Simple assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-220636 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault simple on Jul 29, 2026, 1074 m from Tacoma Mall (3500 S 45TH ST). Case #2621000152 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>26C142249</t>
+          <t>71894237115</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>46230.75</v>
+        <v>46231.20833333334</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BATTERY ABW</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1846,56 +1848,56 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>SIM_ASSAULT</t>
+          <t>VIOLENT CRIME</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>700 BLOCK OF S MISSION RD</t>
+          <t>15XX BLOCK OF NE 107TH ST</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>37.6756469679485</v>
+        <v>47.70668788</v>
       </c>
       <c r="K11" t="n">
-        <v>-97.25850032865422</v>
+        <v>-122.311189997702</v>
       </c>
       <c r="L11" t="n">
-        <v>1251.5</v>
+        <v>1145.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Battery abw on Jul 27, 2026, 1251 m from Towne East Square (700 BLOCK OF S MISSION RD). Case #26C142249 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-221056 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HOUSTONGAL:Houston PD NIBRS — Person</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>096140526</t>
+          <t>71889871382</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>46232</v>
+        <v>46231.00625</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Aggravated Assault</t>
+          <t>Simple Assault</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1905,56 +1907,56 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>13A</t>
+          <t>ALL OTHER</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1900-1999 POST OAK PARK DR</t>
+          <t>15XX BLOCK OF NE 107TH ST</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>29.74712522681273</v>
+        <v>47.70668788</v>
       </c>
       <c r="K12" t="n">
-        <v>-95.45374747370188</v>
+        <v>-122.311189997702</v>
       </c>
       <c r="L12" t="n">
-        <v>1323.4</v>
+        <v>1145.7</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 29, 2026, 1323 m from Houston Galleria (1900-1999 POST OAK PARK DR). Case #096140526 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-220636 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202675136         </t>
+          <t>26C142249</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>46228.97847222222</v>
+        <v>46230.75</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">[13B] ASSAULT                                                                   </t>
+          <t>BATTERY ABW</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1962,54 +1964,58 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>SIM_ASSAULT</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5XXX S HARDY DR</t>
+          <t>700 BLOCK OF S MISSION RD</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>33.3757495513233</v>
+        <v>37.6756469679485</v>
       </c>
       <c r="K13" t="n">
-        <v>-111.9531832468173</v>
+        <v>-97.25850032865422</v>
       </c>
       <c r="L13" t="n">
-        <v>1345.1</v>
+        <v>1251.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>[13b] assault on Jul 25, 2026, 1345 m from Arizona Mills (5XXX S HARDY DR). Case #TE202675136          (use for a records request — full narratives are not published in open data).</t>
+          <t>Battery abw on Jul 27, 2026, 1251 m from Towne East Square (700 BLOCK OF S MISSION RD). Case #26C142249 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>HOUSTONGAL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Houston Galleria</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>HOUSTONGAL:Houston PD NIBRS — Person</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2621102285</t>
+          <t>096140526</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Assault Simple</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2019,50 +2025,56 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>13A</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5100 S 58TH ST</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+          <t>1900-1999 POST OAK PARK DR</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>29.74712522681273</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-95.45374747370188</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1323.4</v>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Assault simple on Jul 30, 2026, Tacoma Mall (5100 S 58TH ST). Case #2621102285 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 29, 2026, 1323 m from Houston Galleria (1900-1999 POST OAK PARK DR). Case #096140526 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2621101093</t>
+          <t xml:space="preserve">TE202675136         </t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>46233</v>
+        <v>46228.97847222222</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Assault Aggravated</t>
+          <t xml:space="preserve">[13B] ASSAULT                                                                   </t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2070,22 +2082,24 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>8400 PACIFIC AVE</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+          <t>5XXX S HARDY DR</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>33.3757495513233</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-111.9531832468173</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1345.1</v>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Assault aggravated on Jul 30, 2026, Tacoma Mall (8400 PACIFIC AVE). Case #2621101093 (use for a records request — full narratives are not published in open data).</t>
+          <t>[13b] assault on Jul 25, 2026, 1345 m from Arizona Mills (5XXX S HARDY DR). Case #TE202675136          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2121,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2621101249</t>
+          <t>2621102013</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
@@ -2115,7 +2129,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Assault Aggravated</t>
+          <t>Assault Simple</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2130,545 +2144,611 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>400 S 23RD ST</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+          <t>5400 SOUTH TACOMA WAY</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>47.206421</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-122.483428</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1578</v>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Assault aggravated on Jul 30, 2026, Tacoma Mall (400 S 23RD ST). Case #2621101249 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault simple on Jul 30, 2026, 1578 m from Tacoma Mall (5400 SOUTH TACOMA WAY). Case #2621102013 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2621102013</t>
+          <t>DP2026415473230300</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>46233</v>
+        <v>46231.47916666666</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Assault Simple</t>
+          <t>theft-shoplift</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>larceny</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5400 SOUTH TACOMA WAY</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+          <t>15 S STEELE ST</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>39.7162154712797</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-104.9512928115626</v>
+      </c>
+      <c r="L17" t="n">
+        <v>144.7</v>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Assault simple on Jul 30, 2026, Tacoma Mall (5400 SOUTH TACOMA WAY). Case #2621102013 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-shoplift on Jul 28, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026415473 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2621100265</t>
+          <t>DP2026413358260700</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>46233</v>
+        <v>46230.47013888889</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Assault Aggravated</t>
+          <t>fraud-by-telephone</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>white-collar-crime</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2000 6TH AVE</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+          <t>15 S STEELE ST</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>39.7162154712797</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-104.9512928115626</v>
+      </c>
+      <c r="L18" t="n">
+        <v>144.7</v>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Assault aggravated on Jul 30, 2026, Tacoma Mall (2000 6TH AVE). Case #2621100265 (use for a records request — full narratives are not published in open data).</t>
+          <t>Fraud-by-telephone on Jul 27, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026413358 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2621101020</t>
+          <t>71913162555</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>46232</v>
+        <v>46232.82986111111</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Assault Simple</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3400 S 19TH ST</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+          <t>3XX BLOCK OF NE NORTHGATE WAY</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>47.7086028</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-122.324615154453</v>
+      </c>
+      <c r="L19" t="n">
+        <v>145.2</v>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Assault simple on Jul 29, 2026, Tacoma Mall (3400 S 19TH ST). Case #2621101020 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 29, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-222878 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2621001950</t>
+          <t>71898889573</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>46232</v>
+        <v>46231.625</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Assault Aggravated</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1700 S J ST</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+          <t>4XX BLOCK OF NE NORTHGATE WAY</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>47.7086028</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-122.324615154453</v>
+      </c>
+      <c r="L20" t="n">
+        <v>145.2</v>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Assault aggravated on Jul 29, 2026, Tacoma Mall (1700 S J ST). Case #2621001950 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-221387 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2621001913</t>
+          <t>71899277060</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>46232</v>
+        <v>46231.47569444445</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Assault Simple</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>7200 PACIFIC AVE</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+          <t>4XX BLOCK OF NE NORTHGATE WAY</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>47.7086028</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-122.324615154454</v>
+      </c>
+      <c r="L21" t="n">
+        <v>145.2</v>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Assault simple on Jul 29, 2026, Tacoma Mall (7200 PACIFIC AVE). Case #2621001913 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-221174 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>HOUSTONGAL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Houston Galleria</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>HOUSTONGAL:Houston PD NIBRS — Property</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2621001005</t>
+          <t>096475026</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Assault Simple</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>23C</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1900 S 72ND ST</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+          <t>5100-5199 ALABAMA ST W</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>29.73799058803365</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-95.46478253884783</v>
+      </c>
+      <c r="L22" t="n">
+        <v>163.5</v>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Assault simple on Jul 29, 2026, Tacoma Mall (1900 S 72ND ST). Case #2621001005 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 30, 2026, 163 m from Houston Galleria (5100-5199 ALABAMA ST W). Case #096475026 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>HOUSTONGAL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Houston Galleria</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>HOUSTONGAL:Houston PD NIBRS — Property</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2621001310</t>
+          <t>095621926</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Assault Aggravated</t>
+          <t>Theft from motor vehicle</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>23F</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>600 N JACKSON AVE</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+          <t>5100-5199 ALABAMA ST W</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>29.73799058803365</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-95.46478253884783</v>
+      </c>
+      <c r="L23" t="n">
+        <v>163.5</v>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Assault aggravated on Jul 29, 2026, Tacoma Mall (600 N JACKSON AVE). Case #2621001310 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft from motor vehicle on Jul 28, 2026, 163 m from Houston Galleria (5100-5199 ALABAMA ST W). Case #095621926 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>HOUSTONGAL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Houston Galleria</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>HOUSTONGAL:Houston PD NIBRS — Property</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2621000152</t>
+          <t>095601426</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Assault Simple</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>23C</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3500 S 45TH ST</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+          <t>5100-5199 ALABAMA ST W</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>29.73799058803365</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-95.46478253884783</v>
+      </c>
+      <c r="L24" t="n">
+        <v>163.5</v>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Assault simple on Jul 29, 2026, Tacoma Mall (3500 S 45TH ST). Case #2621000152 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 163 m from Houston Galleria (5100-5199 ALABAMA ST W). Case #095601426 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2621000914</t>
+          <t>20260728-1130-01</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>46232</v>
+        <v>46231.16666666666</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Assault Simple</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>23C</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1600 MARTIN LUTHER KING JR WAY</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L25" t="n">
+        <v>178.9</v>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Assault simple on Jul 29, 2026, Tacoma Mall (1600 MARTIN LUTHER KING JR WAY). Case #2621000914 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1130-01 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2621100025</t>
+          <t>20260728-1922-01</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>46232</v>
+        <v>46231.16666666666</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Assault Aggravated</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>23C</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2500 PACIFIC AVE</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L26" t="n">
+        <v>178.9</v>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Assault aggravated on Jul 29, 2026, Tacoma Mall (2500 PACIFIC AVE). Case #2621100025 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1922-01 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M299"/>
+  <dimension ref="A1:M161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2694,8 +2774,8 @@
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="53" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="49" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -11580,38 +11660,44 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2621001842</t>
+          <t>2620701835</t>
         </is>
       </c>
       <c r="E153" s="3" t="n">
-        <v>46232</v>
+        <v>46229</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Loitering/Vagrancy</t>
+          <t>Assault Simple</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>QUALITY_OF_LIFE</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Loitering/Vagrancy</t>
+          <t>Assault Offenses</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>E 25TH ST &amp; E M ST</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
+          <t>4000 S LAWRENCE ST</t>
+        </is>
+      </c>
+      <c r="J153" t="n">
+        <v>47.219421</v>
+      </c>
+      <c r="K153" t="n">
+        <v>-122.478428</v>
+      </c>
+      <c r="L153" t="n">
+        <v>853.4</v>
+      </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Loitering/vagrancy on Jul 29, 2026, Tacoma Mall (E 25TH ST &amp; E M ST). Case #2621001842 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault simple on Jul 26, 2026, 853 m from Tacoma Mall (4000 S LAWRENCE ST). Case #2620701835 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -11633,38 +11719,44 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2621000741</t>
+          <t>2620700788</t>
         </is>
       </c>
       <c r="E154" s="3" t="n">
-        <v>46230</v>
+        <v>46229</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Destruction/Damage/Vandalism</t>
+          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Destruction/Damage/Vandalism</t>
+          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>1900 FAWCETT AVE</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
+          <t>TACOMA MALL BLVD &amp; S 48TH ST</t>
+        </is>
+      </c>
+      <c r="J154" t="n">
+        <v>47.213421</v>
+      </c>
+      <c r="K154" t="n">
+        <v>-122.463428</v>
+      </c>
+      <c r="L154" t="n">
+        <v>471.3</v>
+      </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Destruction/damage/vandalism on Jul 27, 2026, Tacoma Mall (1900 FAWCETT AVE). Case #2621000741 (use for a records request — full narratives are not published in open data).</t>
+          <t>Traffic accident/collision - non fatal - injury on Jul 26, 2026, 471 m from Tacoma Mall (TACOMA MALL BLVD &amp; S 48TH ST). Case #2620700788 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -11686,7 +11778,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2620802264</t>
+          <t>2620801268</t>
         </is>
       </c>
       <c r="E155" s="3" t="n">
@@ -11694,30 +11786,36 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Larceny Theft</t>
+          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Larceny/Theft Offenses</t>
+          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>700 S 56TH ST</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
+          <t>S 48TH ST &amp; TACOMA MALL BLVD</t>
+        </is>
+      </c>
+      <c r="J155" t="n">
+        <v>47.213421</v>
+      </c>
+      <c r="K155" t="n">
+        <v>-122.463428</v>
+      </c>
+      <c r="L155" t="n">
+        <v>471.3</v>
+      </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Larceny theft on Jul 27, 2026, Tacoma Mall (700 S 56TH ST). Case #2620802264 (use for a records request — full narratives are not published in open data).</t>
+          <t>Traffic accident/collision - non fatal - injury on Jul 27, 2026, 471 m from Tacoma Mall (S 48TH ST &amp; TACOMA MALL BLVD). Case #2620801268 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -11739,15 +11837,15 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2621100741</t>
+          <t>2621001325</t>
         </is>
       </c>
       <c r="E156" s="3" t="n">
-        <v>46233</v>
+        <v>46231</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Destruction/Damage/Vandalism</t>
+          <t>Motor Vehicle Theft</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -11757,20 +11855,26 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Destruction/Damage/Vandalism</t>
+          <t>Motor Vehicle Theft</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>2200 N PEARL ST</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
+          <t>S UNION AVE &amp; S 47TH ST</t>
+        </is>
+      </c>
+      <c r="J156" t="n">
+        <v>47.214421</v>
+      </c>
+      <c r="K156" t="n">
+        <v>-122.483428</v>
+      </c>
+      <c r="L156" t="n">
+        <v>1165.2</v>
+      </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Destruction/damage/vandalism on Jul 30, 2026, Tacoma Mall (2200 N PEARL ST). Case #2621100741 (use for a records request — full narratives are not published in open data).</t>
+          <t>Motor vehicle theft on Jul 28, 2026, 1165 m from Tacoma Mall (S UNION AVE &amp; S 47TH ST). Case #2621001325 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -11792,7 +11896,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2621000943</t>
+          <t>2621000811</t>
         </is>
       </c>
       <c r="E157" s="3" t="n">
@@ -11800,7 +11904,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Destruction/Damage/Vandalism</t>
+          <t>Fraud</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -11810,20 +11914,26 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Destruction/Damage/Vandalism</t>
+          <t>Fraud Offenses</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>3800 N WATERVIEW ST</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
+          <t>3100 S 45TH ST</t>
+        </is>
+      </c>
+      <c r="J157" t="n">
+        <v>47.216421</v>
+      </c>
+      <c r="K157" t="n">
+        <v>-122.477428</v>
+      </c>
+      <c r="L157" t="n">
+        <v>696.9</v>
+      </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Destruction/damage/vandalism on Jul 29, 2026, Tacoma Mall (3800 N WATERVIEW ST). Case #2621000943 (use for a records request — full narratives are not published in open data).</t>
+          <t>Fraud on Jul 29, 2026, 697 m from Tacoma Mall (3100 S 45TH ST). Case #2621000811 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -11845,38 +11955,44 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2621109059</t>
+          <t>2621102013</t>
         </is>
       </c>
       <c r="E158" s="3" t="n">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Larceny Theft</t>
+          <t>Assault Simple</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Larceny/Theft Offenses</t>
+          <t>Assault Offenses</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>2100 S SHERIDAN AVE</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
+          <t>5400 SOUTH TACOMA WAY</t>
+        </is>
+      </c>
+      <c r="J158" t="n">
+        <v>47.206421</v>
+      </c>
+      <c r="K158" t="n">
+        <v>-122.483428</v>
+      </c>
+      <c r="L158" t="n">
+        <v>1578</v>
+      </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Larceny theft on Jul 28, 2026, Tacoma Mall (2100 S SHERIDAN AVE). Case #2621109059 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault simple on Jul 30, 2026, 1578 m from Tacoma Mall (5400 SOUTH TACOMA WAY). Case #2621102013 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -11898,7 +12014,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2620702146</t>
+          <t>2620800399</t>
         </is>
       </c>
       <c r="E159" s="3" t="n">
@@ -11906,7 +12022,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Destruction/Damage/Vandalism</t>
+          <t>Motor Vehicle Theft</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -11916,20 +12032,26 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Destruction/Damage/Vandalism</t>
+          <t>Motor Vehicle Theft</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>700 S 56TH ST</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
+          <t>4800 S M ST</t>
+        </is>
+      </c>
+      <c r="J159" t="n">
+        <v>47.212421</v>
+      </c>
+      <c r="K159" t="n">
+        <v>-122.451428</v>
+      </c>
+      <c r="L159" t="n">
+        <v>1333.5</v>
+      </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Destruction/damage/vandalism on Jul 26, 2026, Tacoma Mall (700 S 56TH ST). Case #2620702146 (use for a records request — full narratives are not published in open data).</t>
+          <t>Motor vehicle theft on Jul 26, 2026, 1333 m from Tacoma Mall (4800 S M ST). Case #2620800399 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -11951,38 +12073,44 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2621109010</t>
+          <t>2621000152</t>
         </is>
       </c>
       <c r="E160" s="3" t="n">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Larceny Theft</t>
+          <t>Assault Simple</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Larceny/Theft Offenses</t>
+          <t>Assault Offenses</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>7000 S 12TH ST</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
+          <t>3500 S 45TH ST</t>
+        </is>
+      </c>
+      <c r="J160" t="n">
+        <v>47.216421</v>
+      </c>
+      <c r="K160" t="n">
+        <v>-122.482428</v>
+      </c>
+      <c r="L160" t="n">
+        <v>1074.3</v>
+      </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Larceny theft on Jul 27, 2026, Tacoma Mall (7000 S 12TH ST). Case #2621109010 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault simple on Jul 29, 2026, 1074 m from Tacoma Mall (3500 S 45TH ST). Case #2621000152 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -12004,7357 +12132,49 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2621101504</t>
+          <t>2620901147</t>
         </is>
       </c>
       <c r="E161" s="3" t="n">
-        <v>46233</v>
+        <v>46231</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Larceny Theft</t>
+          <t>Extortion (Blackmail)</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Larceny/Theft Offenses</t>
+          <t>Extortion (Blackmail)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>400 S 23RD ST</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
+          <t>5400 S STEELE ST</t>
+        </is>
+      </c>
+      <c r="J161" t="n">
+        <v>47.206421</v>
+      </c>
+      <c r="K161" t="n">
+        <v>-122.467428</v>
+      </c>
+      <c r="L161" t="n">
+        <v>1082.7</v>
+      </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Larceny theft on Jul 30, 2026, Tacoma Mall (400 S 23RD ST). Case #2621101504 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>2621101060</t>
-        </is>
-      </c>
-      <c r="E162" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>LAKEWOOD DR W &amp; 68TH ST W</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - non injury on Jul 30, 2026, Tacoma Mall (LAKEWOOD DR W &amp; 68TH ST W). Case #2621101060 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>2621109060</t>
-        </is>
-      </c>
-      <c r="E163" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>700 S M ST</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 29, 2026, Tacoma Mall (700 S M ST). Case #2621109060 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>2621100865</t>
-        </is>
-      </c>
-      <c r="E164" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>COMMERCE ST &amp; S 11TH ST</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - injury on Jul 30, 2026, Tacoma Mall (COMMERCE ST &amp; S 11TH ST). Case #2621100865 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>2621001342</t>
-        </is>
-      </c>
-      <c r="E165" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>E 25TH ST &amp; MCKINLEY AVE</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - non injury on Jul 29, 2026, Tacoma Mall (E 25TH ST &amp; MCKINLEY AVE). Case #2621001342 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>2620701835</t>
-        </is>
-      </c>
-      <c r="E166" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>Assault Simple</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>4000 S LAWRENCE ST</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>Assault simple on Jul 26, 2026, Tacoma Mall (4000 S LAWRENCE ST). Case #2620701835 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>2620900912</t>
-        </is>
-      </c>
-      <c r="E167" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>S 12TH ST &amp; S PINE ST</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - non injury on Jul 28, 2026, Tacoma Mall (S 12TH ST &amp; S PINE ST). Case #2620900912 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>2621109027</t>
-        </is>
-      </c>
-      <c r="E168" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>2300 FREMONT ST</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 30, 2026, Tacoma Mall (2300 FREMONT ST). Case #2621109027 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>2620700133</t>
-        </is>
-      </c>
-      <c r="E169" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>Drug/Narcotics Violations</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>QUALITY_OF_LIFE</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Drug/Narcotics Violations</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>S ASH ST &amp; 96TH ST S</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>Drug/narcotics violations on Jul 26, 2026, Tacoma Mall (S ASH ST &amp; 96TH ST S). Case #2620700133 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>2621101383</t>
-        </is>
-      </c>
-      <c r="E170" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>Arson</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Arson</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>200 N I ST</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>Arson on Jul 30, 2026, Tacoma Mall (200 N I ST). Case #2621101383 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>2620900213</t>
-        </is>
-      </c>
-      <c r="E171" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>Burglary</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Burglary/Breaking &amp; Entering</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>1900 YAKIMA AVE</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>Burglary on Jul 28, 2026, Tacoma Mall (1900 YAKIMA AVE). Case #2620900213 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>2621109013</t>
-        </is>
-      </c>
-      <c r="E172" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>1000 S PUGET SOUND AVE</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 28, 2026, Tacoma Mall (1000 S PUGET SOUND AVE). Case #2621109013 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>2620801701</t>
-        </is>
-      </c>
-      <c r="E173" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>S 8TH ST &amp; S FIFE ST</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - non injury on Jul 27, 2026, Tacoma Mall (S 8TH ST &amp; S FIFE ST). Case #2620801701 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>2621109019</t>
-        </is>
-      </c>
-      <c r="E174" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>6300 N 26TH ST</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr"/>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 28, 2026, Tacoma Mall (6300 N 26TH ST). Case #2621109019 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>2620800717</t>
-        </is>
-      </c>
-      <c r="E175" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Fraud Offenses</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>5000 N 29TH ST</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>Fraud on Jul 27, 2026, Tacoma Mall (5000 N 29TH ST). Case #2620800717 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>2620700788</t>
-        </is>
-      </c>
-      <c r="E176" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>TACOMA MALL BLVD &amp; S 48TH ST</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - injury on Jul 26, 2026, Tacoma Mall (TACOMA MALL BLVD &amp; S 48TH ST). Case #2620700788 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>2620701357</t>
-        </is>
-      </c>
-      <c r="E177" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>1600 NORPOINT WAY NE</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 26, 2026, Tacoma Mall (1600 NORPOINT WAY NE). Case #2620701357 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>2620809029</t>
-        </is>
-      </c>
-      <c r="E178" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>4500 S J ST</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
-      <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 27, 2026, Tacoma Mall (4500 S J ST). Case #2620809029 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>2620902305</t>
-        </is>
-      </c>
-      <c r="E179" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>8400 PACIFIC AVE</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 28, 2026, Tacoma Mall (8400 PACIFIC AVE). Case #2620902305 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>2620901622</t>
-        </is>
-      </c>
-      <c r="E180" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>S J ST &amp; 6TH AVE</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - injury on Jul 28, 2026, Tacoma Mall (S J ST &amp; 6TH AVE). Case #2620901622 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>2620701372</t>
-        </is>
-      </c>
-      <c r="E181" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>S STEELE ST &amp; S 96TH ST</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
-      <c r="L181" t="inlineStr"/>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - non injury on Jul 26, 2026, Tacoma Mall (S STEELE ST &amp; S 96TH ST). Case #2620701372 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>2620800590</t>
-        </is>
-      </c>
-      <c r="E182" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>7000 S OAKES ST</t>
-        </is>
-      </c>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
-      <c r="L182" t="inlineStr"/>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - injury on Jul 27, 2026, Tacoma Mall (7000 S OAKES ST). Case #2620800590 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>2620702095</t>
-        </is>
-      </c>
-      <c r="E183" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>S 25TH ST &amp; JEFFERSON AVE</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - injury on Jul 26, 2026, Tacoma Mall (S 25TH ST &amp; JEFFERSON AVE). Case #2620702095 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>2620802464</t>
-        </is>
-      </c>
-      <c r="E184" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>Assault Simple</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>1000 S L ST</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr"/>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>Assault simple on Jul 27, 2026, Tacoma Mall (1000 S L ST). Case #2620802464 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>2620901957</t>
-        </is>
-      </c>
-      <c r="E185" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>Assault Simple</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>2400 RUSTON WAY</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>Assault simple on Jul 28, 2026, Tacoma Mall (2400 RUSTON WAY). Case #2620901957 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>2621109043</t>
-        </is>
-      </c>
-      <c r="E186" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>1700 MARKET ST</t>
-        </is>
-      </c>
-      <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 27, 2026, Tacoma Mall (1700 MARKET ST). Case #2621109043 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>2621102285</t>
-        </is>
-      </c>
-      <c r="E187" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>Assault Simple</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>5100 S 58TH ST</t>
-        </is>
-      </c>
-      <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>Assault simple on Jul 30, 2026, Tacoma Mall (5100 S 58TH ST). Case #2621102285 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>2621109021</t>
-        </is>
-      </c>
-      <c r="E188" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>5600 N 37TH ST</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
-      <c r="M188" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 27, 2026, Tacoma Mall (5600 N 37TH ST). Case #2621109021 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>2621109058</t>
-        </is>
-      </c>
-      <c r="E189" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>1900 LINCOLN AVE</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
-      <c r="M189" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 28, 2026, Tacoma Mall (1900 LINCOLN AVE). Case #2621109058 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>2621101020</t>
-        </is>
-      </c>
-      <c r="E190" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>Assault Simple</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>3400 S 19TH ST</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr"/>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>Assault simple on Jul 29, 2026, Tacoma Mall (3400 S 19TH ST). Case #2621101020 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>2620801790</t>
-        </is>
-      </c>
-      <c r="E191" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>400 SOUTH TACOMA WAY</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr"/>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - injury on Jul 27, 2026, Tacoma Mall (400 SOUTH TACOMA WAY). Case #2620801790 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>2621109063</t>
-        </is>
-      </c>
-      <c r="E192" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>700 S M ST</t>
-        </is>
-      </c>
-      <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 26, 2026, Tacoma Mall (700 S M ST). Case #2621109063 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>2621109049</t>
-        </is>
-      </c>
-      <c r="E193" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>1700 TACOMA AVE S</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr"/>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 29, 2026, Tacoma Mall (1700 TACOMA AVE S). Case #2621109049 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>2621109042</t>
-        </is>
-      </c>
-      <c r="E194" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>2300 S J ST</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr"/>
-      <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr"/>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 26, 2026, Tacoma Mall (2300 S J ST). Case #2621109042 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>2620800685</t>
-        </is>
-      </c>
-      <c r="E195" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>2500 N PROCTOR ST</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr"/>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 27, 2026, Tacoma Mall (2500 N PROCTOR ST). Case #2620800685 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>2620801268</t>
-        </is>
-      </c>
-      <c r="E196" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>S 48TH ST &amp; TACOMA MALL BLVD</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr"/>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - injury on Jul 27, 2026, Tacoma Mall (S 48TH ST &amp; TACOMA MALL BLVD). Case #2620801268 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>2621101391</t>
-        </is>
-      </c>
-      <c r="E197" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>2600 WESTRIDGE AVE W</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr"/>
-      <c r="K197" t="inlineStr"/>
-      <c r="L197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - injury on Jul 30, 2026, Tacoma Mall (2600 WESTRIDGE AVE W). Case #2621101391 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>2621109007</t>
-        </is>
-      </c>
-      <c r="E198" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>3200 N 30TH ST</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr"/>
-      <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr"/>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 27, 2026, Tacoma Mall (3200 N 30TH ST). Case #2621109007 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>2621001950</t>
-        </is>
-      </c>
-      <c r="E199" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>Assault Aggravated</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>1700 S J ST</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr"/>
-      <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr"/>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>Assault aggravated on Jul 29, 2026, Tacoma Mall (1700 S J ST). Case #2621001950 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>2621109057</t>
-        </is>
-      </c>
-      <c r="E200" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>1400 TACOMA AVE S</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr"/>
-      <c r="K200" t="inlineStr"/>
-      <c r="L200" t="inlineStr"/>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 26, 2026, Tacoma Mall (1400 TACOMA AVE S). Case #2621109057 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>2620709006</t>
-        </is>
-      </c>
-      <c r="E201" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>600 N K ST</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr"/>
-      <c r="K201" t="inlineStr"/>
-      <c r="L201" t="inlineStr"/>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 26, 2026, Tacoma Mall (600 N K ST). Case #2620709006 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>2621100946</t>
-        </is>
-      </c>
-      <c r="E202" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>Burglary</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>Burglary/Breaking &amp; Entering</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>1400 S SHERIDAN AVE</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr"/>
-      <c r="K202" t="inlineStr"/>
-      <c r="L202" t="inlineStr"/>
-      <c r="M202" t="inlineStr">
-        <is>
-          <t>Burglary on Jul 30, 2026, Tacoma Mall (1400 S SHERIDAN AVE). Case #2621100946 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>2621109018</t>
-        </is>
-      </c>
-      <c r="E203" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>600 S SHIRLEY ST</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr"/>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 27, 2026, Tacoma Mall (600 S SHIRLEY ST). Case #2621109018 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>2621101093</t>
-        </is>
-      </c>
-      <c r="E204" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>Assault Aggravated</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>8400 PACIFIC AVE</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr"/>
-      <c r="K204" t="inlineStr"/>
-      <c r="L204" t="inlineStr"/>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>Assault aggravated on Jul 30, 2026, Tacoma Mall (8400 PACIFIC AVE). Case #2621101093 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>2621101249</t>
-        </is>
-      </c>
-      <c r="E205" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>Assault Aggravated</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>400 S 23RD ST</t>
-        </is>
-      </c>
-      <c r="J205" t="inlineStr"/>
-      <c r="K205" t="inlineStr"/>
-      <c r="L205" t="inlineStr"/>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>Assault aggravated on Jul 30, 2026, Tacoma Mall (400 S 23RD ST). Case #2621101249 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>2620902083</t>
-        </is>
-      </c>
-      <c r="E206" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>SOUTH TACOMA WAY &amp; S FIFE ST</t>
-        </is>
-      </c>
-      <c r="J206" t="inlineStr"/>
-      <c r="K206" t="inlineStr"/>
-      <c r="L206" t="inlineStr"/>
-      <c r="M206" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 27, 2026, Tacoma Mall (SOUTH TACOMA WAY &amp; S FIFE ST). Case #2620902083 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>2620801976</t>
-        </is>
-      </c>
-      <c r="E207" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>E 25TH ST &amp; E C ST</t>
-        </is>
-      </c>
-      <c r="J207" t="inlineStr"/>
-      <c r="K207" t="inlineStr"/>
-      <c r="L207" t="inlineStr"/>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 26, 2026, Tacoma Mall (E 25TH ST &amp; E C ST). Case #2620801976 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>2620800472</t>
-        </is>
-      </c>
-      <c r="E208" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>Motor Vehicle Theft</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>Motor Vehicle Theft</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>600 N PUGET SOUND AVE</t>
-        </is>
-      </c>
-      <c r="J208" t="inlineStr"/>
-      <c r="K208" t="inlineStr"/>
-      <c r="L208" t="inlineStr"/>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>Motor vehicle theft on Jul 27, 2026, Tacoma Mall (600 N PUGET SOUND AVE). Case #2620800472 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>2621001913</t>
-        </is>
-      </c>
-      <c r="E209" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>Assault Simple</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>7200 PACIFIC AVE</t>
-        </is>
-      </c>
-      <c r="J209" t="inlineStr"/>
-      <c r="K209" t="inlineStr"/>
-      <c r="L209" t="inlineStr"/>
-      <c r="M209" t="inlineStr">
-        <is>
-          <t>Assault simple on Jul 29, 2026, Tacoma Mall (7200 PACIFIC AVE). Case #2621001913 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>2620900180</t>
-        </is>
-      </c>
-      <c r="E210" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>Weapon Law Violation</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Weapon Law Violations</t>
-        </is>
-      </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>1700 S 95TH ST</t>
-        </is>
-      </c>
-      <c r="J210" t="inlineStr"/>
-      <c r="K210" t="inlineStr"/>
-      <c r="L210" t="inlineStr"/>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>Weapon law violation on Jul 28, 2026, Tacoma Mall (1700 S 95TH ST). Case #2620900180 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>2621109048</t>
-        </is>
-      </c>
-      <c r="E211" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>700 YAKIMA AVE</t>
-        </is>
-      </c>
-      <c r="J211" t="inlineStr"/>
-      <c r="K211" t="inlineStr"/>
-      <c r="L211" t="inlineStr"/>
-      <c r="M211" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 26, 2026, Tacoma Mall (700 YAKIMA AVE). Case #2621109048 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>2620900934</t>
-        </is>
-      </c>
-      <c r="E212" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>3500 CENTER ST</t>
-        </is>
-      </c>
-      <c r="J212" t="inlineStr"/>
-      <c r="K212" t="inlineStr"/>
-      <c r="L212" t="inlineStr"/>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - non injury on Jul 28, 2026, Tacoma Mall (3500 CENTER ST). Case #2620900934 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>2620701371</t>
-        </is>
-      </c>
-      <c r="E213" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>Motor Vehicle Theft</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>Motor Vehicle Theft</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>900 FAWCETT AVE</t>
-        </is>
-      </c>
-      <c r="J213" t="inlineStr"/>
-      <c r="K213" t="inlineStr"/>
-      <c r="L213" t="inlineStr"/>
-      <c r="M213" t="inlineStr">
-        <is>
-          <t>Motor vehicle theft on Jul 26, 2026, Tacoma Mall (900 FAWCETT AVE). Case #2620701371 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>2621109022</t>
-        </is>
-      </c>
-      <c r="E214" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>3600 N ORCHARD ST</t>
-        </is>
-      </c>
-      <c r="J214" t="inlineStr"/>
-      <c r="K214" t="inlineStr"/>
-      <c r="L214" t="inlineStr"/>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 29, 2026, Tacoma Mall (3600 N ORCHARD ST). Case #2621109022 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>2620700857</t>
-        </is>
-      </c>
-      <c r="E215" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>Extortion (Blackmail)</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>Extortion (Blackmail)</t>
-        </is>
-      </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>400 E 56TH ST</t>
-        </is>
-      </c>
-      <c r="J215" t="inlineStr"/>
-      <c r="K215" t="inlineStr"/>
-      <c r="L215" t="inlineStr"/>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>Extortion (blackmail) on Jul 26, 2026, Tacoma Mall (400 E 56TH ST). Case #2620700857 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>2621001325</t>
-        </is>
-      </c>
-      <c r="E216" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>Motor Vehicle Theft</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Motor Vehicle Theft</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>S UNION AVE &amp; S 47TH ST</t>
-        </is>
-      </c>
-      <c r="J216" t="inlineStr"/>
-      <c r="K216" t="inlineStr"/>
-      <c r="L216" t="inlineStr"/>
-      <c r="M216" t="inlineStr">
-        <is>
-          <t>Motor vehicle theft on Jul 28, 2026, Tacoma Mall (S UNION AVE &amp; S 47TH ST). Case #2621001325 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>2620700384</t>
-        </is>
-      </c>
-      <c r="E217" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>CENTER ST &amp; S LAWRENCE ST</t>
-        </is>
-      </c>
-      <c r="J217" t="inlineStr"/>
-      <c r="K217" t="inlineStr"/>
-      <c r="L217" t="inlineStr"/>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - non injury on Jul 26, 2026, Tacoma Mall (CENTER ST &amp; S LAWRENCE ST). Case #2620700384 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>2620700156</t>
-        </is>
-      </c>
-      <c r="E218" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>1100 BROADWAY</t>
-        </is>
-      </c>
-      <c r="J218" t="inlineStr"/>
-      <c r="K218" t="inlineStr"/>
-      <c r="L218" t="inlineStr"/>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 26, 2026, Tacoma Mall (1100 BROADWAY). Case #2620700156 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>2621109061</t>
-        </is>
-      </c>
-      <c r="E219" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>2300 YAKIMA CT</t>
-        </is>
-      </c>
-      <c r="J219" t="inlineStr"/>
-      <c r="K219" t="inlineStr"/>
-      <c r="L219" t="inlineStr"/>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 28, 2026, Tacoma Mall (2300 YAKIMA CT). Case #2621109061 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>2621000233</t>
-        </is>
-      </c>
-      <c r="E220" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>1600 E 32ND ST</t>
-        </is>
-      </c>
-      <c r="J220" t="inlineStr"/>
-      <c r="K220" t="inlineStr"/>
-      <c r="L220" t="inlineStr"/>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 29, 2026, Tacoma Mall (1600 E 32ND ST). Case #2621000233 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>2621100101</t>
-        </is>
-      </c>
-      <c r="E221" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>Traffic - DUI (Liquor)</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>QUALITY_OF_LIFE</t>
-        </is>
-      </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>Traffic - DUI (Liquor)</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>S HOSMER ST &amp; S STEELE ST</t>
-        </is>
-      </c>
-      <c r="J221" t="inlineStr"/>
-      <c r="K221" t="inlineStr"/>
-      <c r="L221" t="inlineStr"/>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>Traffic - dui (liquor) on Jul 30, 2026, Tacoma Mall (S HOSMER ST &amp; S STEELE ST). Case #2621100101 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>2620700268</t>
-        </is>
-      </c>
-      <c r="E222" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>Assault Aggravated</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>900 PACIFIC AVE</t>
-        </is>
-      </c>
-      <c r="J222" t="inlineStr"/>
-      <c r="K222" t="inlineStr"/>
-      <c r="L222" t="inlineStr"/>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>Assault aggravated on Jul 26, 2026, Tacoma Mall (900 PACIFIC AVE). Case #2620700268 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>2620702070</t>
-        </is>
-      </c>
-      <c r="E223" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>Motor Vehicle Theft</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>Motor Vehicle Theft</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>2700 E D ST</t>
-        </is>
-      </c>
-      <c r="J223" t="inlineStr"/>
-      <c r="K223" t="inlineStr"/>
-      <c r="L223" t="inlineStr"/>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>Motor vehicle theft on Jul 26, 2026, Tacoma Mall (2700 E D ST). Case #2620702070 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>2621100925</t>
-        </is>
-      </c>
-      <c r="E224" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>Fraud Offenses</t>
-        </is>
-      </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t>6400 S L ST</t>
-        </is>
-      </c>
-      <c r="J224" t="inlineStr"/>
-      <c r="K224" t="inlineStr"/>
-      <c r="L224" t="inlineStr"/>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>Fraud on Jul 27, 2026, Tacoma Mall (6400 S L ST). Case #2621100925 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>2621100159</t>
-        </is>
-      </c>
-      <c r="E225" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr">
-        <is>
-          <t>3500 PACIFIC AVE</t>
-        </is>
-      </c>
-      <c r="J225" t="inlineStr"/>
-      <c r="K225" t="inlineStr"/>
-      <c r="L225" t="inlineStr"/>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 30, 2026, Tacoma Mall (3500 PACIFIC AVE). Case #2621100159 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>2621001005</t>
-        </is>
-      </c>
-      <c r="E226" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>Assault Simple</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>1900 S 72ND ST</t>
-        </is>
-      </c>
-      <c r="J226" t="inlineStr"/>
-      <c r="K226" t="inlineStr"/>
-      <c r="L226" t="inlineStr"/>
-      <c r="M226" t="inlineStr">
-        <is>
-          <t>Assault simple on Jul 29, 2026, Tacoma Mall (1900 S 72ND ST). Case #2621001005 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>2621109052</t>
-        </is>
-      </c>
-      <c r="E227" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>4900 32ND ST NE</t>
-        </is>
-      </c>
-      <c r="J227" t="inlineStr"/>
-      <c r="K227" t="inlineStr"/>
-      <c r="L227" t="inlineStr"/>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 28, 2026, Tacoma Mall (4900 32ND ST NE). Case #2621109052 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>2621000811</t>
-        </is>
-      </c>
-      <c r="E228" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>Fraud Offenses</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr">
-        <is>
-          <t>3100 S 45TH ST</t>
-        </is>
-      </c>
-      <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr"/>
-      <c r="L228" t="inlineStr"/>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>Fraud on Jul 29, 2026, Tacoma Mall (3100 S 45TH ST). Case #2621000811 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>2620700581</t>
-        </is>
-      </c>
-      <c r="E229" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
-        </is>
-      </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr">
-        <is>
-          <t>S 99TH ST &amp; PACIFIC AVE</t>
-        </is>
-      </c>
-      <c r="J229" t="inlineStr"/>
-      <c r="K229" t="inlineStr"/>
-      <c r="L229" t="inlineStr"/>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - injury on Jul 26, 2026, Tacoma Mall (S 99TH ST &amp; PACIFIC AVE). Case #2620700581 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>2621102013</t>
-        </is>
-      </c>
-      <c r="E230" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>Assault Simple</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>5400 SOUTH TACOMA WAY</t>
-        </is>
-      </c>
-      <c r="J230" t="inlineStr"/>
-      <c r="K230" t="inlineStr"/>
-      <c r="L230" t="inlineStr"/>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>Assault simple on Jul 30, 2026, Tacoma Mall (5400 SOUTH TACOMA WAY). Case #2621102013 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>2620900401</t>
-        </is>
-      </c>
-      <c r="E231" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>Motor Vehicle Theft</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>Motor Vehicle Theft</t>
-        </is>
-      </c>
-      <c r="I231" t="inlineStr">
-        <is>
-          <t>3200 N 27TH ST</t>
-        </is>
-      </c>
-      <c r="J231" t="inlineStr"/>
-      <c r="K231" t="inlineStr"/>
-      <c r="L231" t="inlineStr"/>
-      <c r="M231" t="inlineStr">
-        <is>
-          <t>Motor vehicle theft on Jul 28, 2026, Tacoma Mall (3200 N 27TH ST). Case #2620900401 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>2620901923</t>
-        </is>
-      </c>
-      <c r="E232" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>Fraud Offenses</t>
-        </is>
-      </c>
-      <c r="I232" t="inlineStr">
-        <is>
-          <t>6400 S 10TH ST</t>
-        </is>
-      </c>
-      <c r="J232" t="inlineStr"/>
-      <c r="K232" t="inlineStr"/>
-      <c r="L232" t="inlineStr"/>
-      <c r="M232" t="inlineStr">
-        <is>
-          <t>Fraud on Jul 27, 2026, Tacoma Mall (6400 S 10TH ST). Case #2620901923 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>2621109005</t>
-        </is>
-      </c>
-      <c r="E233" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>5800 N 35TH ST</t>
-        </is>
-      </c>
-      <c r="J233" t="inlineStr"/>
-      <c r="K233" t="inlineStr"/>
-      <c r="L233" t="inlineStr"/>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 27, 2026, Tacoma Mall (5800 N 35TH ST). Case #2621109005 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>2620701616</t>
-        </is>
-      </c>
-      <c r="E234" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>Assault Aggravated</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I234" t="inlineStr">
-        <is>
-          <t>N PEARL ST &amp; N 44TH ST</t>
-        </is>
-      </c>
-      <c r="J234" t="inlineStr"/>
-      <c r="K234" t="inlineStr"/>
-      <c r="L234" t="inlineStr"/>
-      <c r="M234" t="inlineStr">
-        <is>
-          <t>Assault aggravated on Jul 26, 2026, Tacoma Mall (N PEARL ST &amp; N 44TH ST). Case #2620701616 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>2620700320</t>
-        </is>
-      </c>
-      <c r="E235" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>Traffic - DUI (Drugs)</t>
-        </is>
-      </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>QUALITY_OF_LIFE</t>
-        </is>
-      </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>Traffic - DUI (Drugs)</t>
-        </is>
-      </c>
-      <c r="I235" t="inlineStr">
-        <is>
-          <t>3700 PACIFIC AVE</t>
-        </is>
-      </c>
-      <c r="J235" t="inlineStr"/>
-      <c r="K235" t="inlineStr"/>
-      <c r="L235" t="inlineStr"/>
-      <c r="M235" t="inlineStr">
-        <is>
-          <t>Traffic - dui (drugs) on Jul 26, 2026, Tacoma Mall (3700 PACIFIC AVE). Case #2620700320 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>2620809022</t>
-        </is>
-      </c>
-      <c r="E236" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr">
-        <is>
-          <t>4300 CENTER ST</t>
-        </is>
-      </c>
-      <c r="J236" t="inlineStr"/>
-      <c r="K236" t="inlineStr"/>
-      <c r="L236" t="inlineStr"/>
-      <c r="M236" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 27, 2026, Tacoma Mall (4300 CENTER ST). Case #2620809022 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>2620802455</t>
-        </is>
-      </c>
-      <c r="E237" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>Traffic - DUI (Liquor)</t>
-        </is>
-      </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>QUALITY_OF_LIFE</t>
-        </is>
-      </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>Traffic - DUI (Liquor)</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t>S 4TH ST &amp; S STADIUM WAY</t>
-        </is>
-      </c>
-      <c r="J237" t="inlineStr"/>
-      <c r="K237" t="inlineStr"/>
-      <c r="L237" t="inlineStr"/>
-      <c r="M237" t="inlineStr">
-        <is>
-          <t>Traffic - dui (liquor) on Jul 27, 2026, Tacoma Mall (S 4TH ST &amp; S STADIUM WAY). Case #2620802455 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>2621101760</t>
-        </is>
-      </c>
-      <c r="E238" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="I238" t="inlineStr">
-        <is>
-          <t>1200 S 56TH ST</t>
-        </is>
-      </c>
-      <c r="J238" t="inlineStr"/>
-      <c r="K238" t="inlineStr"/>
-      <c r="L238" t="inlineStr"/>
-      <c r="M238" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - non injury on Jul 30, 2026, Tacoma Mall (1200 S 56TH ST). Case #2621101760 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>2620801516</t>
-        </is>
-      </c>
-      <c r="E239" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I239" t="inlineStr">
-        <is>
-          <t>400 S I ST</t>
-        </is>
-      </c>
-      <c r="J239" t="inlineStr"/>
-      <c r="K239" t="inlineStr"/>
-      <c r="L239" t="inlineStr"/>
-      <c r="M239" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 27, 2026, Tacoma Mall (400 S I ST). Case #2620801516 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>2621000630</t>
-        </is>
-      </c>
-      <c r="E240" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I240" t="inlineStr">
-        <is>
-          <t>5100 N 26TH ST</t>
-        </is>
-      </c>
-      <c r="J240" t="inlineStr"/>
-      <c r="K240" t="inlineStr"/>
-      <c r="L240" t="inlineStr"/>
-      <c r="M240" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 29, 2026, Tacoma Mall (5100 N 26TH ST). Case #2621000630 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>2621100265</t>
-        </is>
-      </c>
-      <c r="E241" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>Assault Aggravated</t>
-        </is>
-      </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H241" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I241" t="inlineStr">
-        <is>
-          <t>2000 6TH AVE</t>
-        </is>
-      </c>
-      <c r="J241" t="inlineStr"/>
-      <c r="K241" t="inlineStr"/>
-      <c r="L241" t="inlineStr"/>
-      <c r="M241" t="inlineStr">
-        <is>
-          <t>Assault aggravated on Jul 30, 2026, Tacoma Mall (2000 6TH AVE). Case #2621100265 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>2620800399</t>
-        </is>
-      </c>
-      <c r="E242" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>Motor Vehicle Theft</t>
-        </is>
-      </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>Motor Vehicle Theft</t>
-        </is>
-      </c>
-      <c r="I242" t="inlineStr">
-        <is>
-          <t>4800 S M ST</t>
-        </is>
-      </c>
-      <c r="J242" t="inlineStr"/>
-      <c r="K242" t="inlineStr"/>
-      <c r="L242" t="inlineStr"/>
-      <c r="M242" t="inlineStr">
-        <is>
-          <t>Motor vehicle theft on Jul 26, 2026, Tacoma Mall (4800 S M ST). Case #2620800399 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>2620902259</t>
-        </is>
-      </c>
-      <c r="E243" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I243" t="inlineStr">
-        <is>
-          <t>5800 N 33RD ST</t>
-        </is>
-      </c>
-      <c r="J243" t="inlineStr"/>
-      <c r="K243" t="inlineStr"/>
-      <c r="L243" t="inlineStr"/>
-      <c r="M243" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 26, 2026, Tacoma Mall (5800 N 33RD ST). Case #2620902259 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>2620901027</t>
-        </is>
-      </c>
-      <c r="E244" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G244" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I244" t="inlineStr">
-        <is>
-          <t>8000 S D ST</t>
-        </is>
-      </c>
-      <c r="J244" t="inlineStr"/>
-      <c r="K244" t="inlineStr"/>
-      <c r="L244" t="inlineStr"/>
-      <c r="M244" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 28, 2026, Tacoma Mall (8000 S D ST). Case #2620901027 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>2621000212</t>
-        </is>
-      </c>
-      <c r="E245" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F245" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H245" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I245" t="inlineStr">
-        <is>
-          <t>1200 E 72ND ST</t>
-        </is>
-      </c>
-      <c r="J245" t="inlineStr"/>
-      <c r="K245" t="inlineStr"/>
-      <c r="L245" t="inlineStr"/>
-      <c r="M245" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 28, 2026, Tacoma Mall (1200 E 72ND ST). Case #2621000212 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>2620900849</t>
-        </is>
-      </c>
-      <c r="E246" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F246" t="inlineStr">
-        <is>
-          <t>Assault Simple</t>
-        </is>
-      </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I246" t="inlineStr">
-        <is>
-          <t>3500 S AINSWORTH AVE</t>
-        </is>
-      </c>
-      <c r="J246" t="inlineStr"/>
-      <c r="K246" t="inlineStr"/>
-      <c r="L246" t="inlineStr"/>
-      <c r="M246" t="inlineStr">
-        <is>
-          <t>Assault simple on Jul 28, 2026, Tacoma Mall (3500 S AINSWORTH AVE). Case #2620900849 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>2620701211</t>
-        </is>
-      </c>
-      <c r="E247" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F247" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I247" t="inlineStr">
-        <is>
-          <t>1400 YAKIMA AVE</t>
-        </is>
-      </c>
-      <c r="J247" t="inlineStr"/>
-      <c r="K247" t="inlineStr"/>
-      <c r="L247" t="inlineStr"/>
-      <c r="M247" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 26, 2026, Tacoma Mall (1400 YAKIMA AVE). Case #2620701211 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>2621001592</t>
-        </is>
-      </c>
-      <c r="E248" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I248" t="inlineStr">
-        <is>
-          <t>4000 S TYLER ST</t>
-        </is>
-      </c>
-      <c r="J248" t="inlineStr"/>
-      <c r="K248" t="inlineStr"/>
-      <c r="L248" t="inlineStr"/>
-      <c r="M248" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 29, 2026, Tacoma Mall (4000 S TYLER ST). Case #2621001592 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>2620701587</t>
-        </is>
-      </c>
-      <c r="E249" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F249" t="inlineStr">
-        <is>
-          <t>Burglary</t>
-        </is>
-      </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>Burglary/Breaking &amp; Entering</t>
-        </is>
-      </c>
-      <c r="I249" t="inlineStr">
-        <is>
-          <t>7400 ORCHARD ST W</t>
-        </is>
-      </c>
-      <c r="J249" t="inlineStr"/>
-      <c r="K249" t="inlineStr"/>
-      <c r="L249" t="inlineStr"/>
-      <c r="M249" t="inlineStr">
-        <is>
-          <t>Burglary on Jul 26, 2026, Tacoma Mall (7400 ORCHARD ST W). Case #2620701587 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>2620700804</t>
-        </is>
-      </c>
-      <c r="E250" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>Motor Vehicle Theft</t>
-        </is>
-      </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>Motor Vehicle Theft</t>
-        </is>
-      </c>
-      <c r="I250" t="inlineStr">
-        <is>
-          <t>PACIFIC AVE &amp; S 99TH ST</t>
-        </is>
-      </c>
-      <c r="J250" t="inlineStr"/>
-      <c r="K250" t="inlineStr"/>
-      <c r="L250" t="inlineStr"/>
-      <c r="M250" t="inlineStr">
-        <is>
-          <t>Motor vehicle theft on Jul 26, 2026, Tacoma Mall (PACIFIC AVE &amp; S 99TH ST). Case #2620700804 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>2621000176</t>
-        </is>
-      </c>
-      <c r="E251" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>Traffic - DUI (Liquor)</t>
-        </is>
-      </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>QUALITY_OF_LIFE</t>
-        </is>
-      </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>Traffic - DUI (Liquor)</t>
-        </is>
-      </c>
-      <c r="I251" t="inlineStr">
-        <is>
-          <t>S 60TH ST &amp; SOUTH TACOMA WAY</t>
-        </is>
-      </c>
-      <c r="J251" t="inlineStr"/>
-      <c r="K251" t="inlineStr"/>
-      <c r="L251" t="inlineStr"/>
-      <c r="M251" t="inlineStr">
-        <is>
-          <t>Traffic - dui (liquor) on Jul 29, 2026, Tacoma Mall (S 60TH ST &amp; SOUTH TACOMA WAY). Case #2621000176 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>2620809026</t>
-        </is>
-      </c>
-      <c r="E252" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I252" t="inlineStr">
-        <is>
-          <t>3200 S MASON AVE</t>
-        </is>
-      </c>
-      <c r="J252" t="inlineStr"/>
-      <c r="K252" t="inlineStr"/>
-      <c r="L252" t="inlineStr"/>
-      <c r="M252" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 27, 2026, Tacoma Mall (3200 S MASON AVE). Case #2620809026 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>2621101033</t>
-        </is>
-      </c>
-      <c r="E253" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I253" t="inlineStr">
-        <is>
-          <t>2300 YAKIMA CT</t>
-        </is>
-      </c>
-      <c r="J253" t="inlineStr"/>
-      <c r="K253" t="inlineStr"/>
-      <c r="L253" t="inlineStr"/>
-      <c r="M253" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 29, 2026, Tacoma Mall (2300 YAKIMA CT). Case #2621101033 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>2620801035</t>
-        </is>
-      </c>
-      <c r="E254" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F254" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="I254" t="inlineStr">
-        <is>
-          <t>S PEARL ST &amp; S 12TH ST</t>
-        </is>
-      </c>
-      <c r="J254" t="inlineStr"/>
-      <c r="K254" t="inlineStr"/>
-      <c r="L254" t="inlineStr"/>
-      <c r="M254" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - non injury on Jul 27, 2026, Tacoma Mall (S PEARL ST &amp; S 12TH ST). Case #2620801035 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>2620801833</t>
-        </is>
-      </c>
-      <c r="E255" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F255" t="inlineStr">
-        <is>
-          <t>Assault Simple</t>
-        </is>
-      </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I255" t="inlineStr">
-        <is>
-          <t>900 MARKET ST</t>
-        </is>
-      </c>
-      <c r="J255" t="inlineStr"/>
-      <c r="K255" t="inlineStr"/>
-      <c r="L255" t="inlineStr"/>
-      <c r="M255" t="inlineStr">
-        <is>
-          <t>Assault simple on Jul 27, 2026, Tacoma Mall (900 MARKET ST). Case #2620801833 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>2620801416</t>
-        </is>
-      </c>
-      <c r="E256" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I256" t="inlineStr">
-        <is>
-          <t>2100 N 30TH ST</t>
-        </is>
-      </c>
-      <c r="J256" t="inlineStr"/>
-      <c r="K256" t="inlineStr"/>
-      <c r="L256" t="inlineStr"/>
-      <c r="M256" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 27, 2026, Tacoma Mall (2100 N 30TH ST). Case #2620801416 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>2621109024</t>
-        </is>
-      </c>
-      <c r="E257" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I257" t="inlineStr">
-        <is>
-          <t>1100 S HIGHLAND AVE</t>
-        </is>
-      </c>
-      <c r="J257" t="inlineStr"/>
-      <c r="K257" t="inlineStr"/>
-      <c r="L257" t="inlineStr"/>
-      <c r="M257" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 28, 2026, Tacoma Mall (1100 S HIGHLAND AVE). Case #2621109024 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>2620802228</t>
-        </is>
-      </c>
-      <c r="E258" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>Motor Vehicle Theft</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>Motor Vehicle Theft</t>
-        </is>
-      </c>
-      <c r="I258" t="inlineStr">
-        <is>
-          <t>EARNEST S BRAZILL ST &amp; MARTIN LUTHER KING JR WAY</t>
-        </is>
-      </c>
-      <c r="J258" t="inlineStr"/>
-      <c r="K258" t="inlineStr"/>
-      <c r="L258" t="inlineStr"/>
-      <c r="M258" t="inlineStr">
-        <is>
-          <t>Motor vehicle theft on Jul 27, 2026, Tacoma Mall (EARNEST S BRAZILL ST &amp; MARTIN LUTHER KING JR WAY). Case #2620802228 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>2620809021</t>
-        </is>
-      </c>
-      <c r="E259" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I259" t="inlineStr">
-        <is>
-          <t>3700 N 8TH ST</t>
-        </is>
-      </c>
-      <c r="J259" t="inlineStr"/>
-      <c r="K259" t="inlineStr"/>
-      <c r="L259" t="inlineStr"/>
-      <c r="M259" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 26, 2026, Tacoma Mall (3700 N 8TH ST). Case #2620809021 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>2620701921</t>
-        </is>
-      </c>
-      <c r="E260" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t>Weapon Law Violation</t>
-        </is>
-      </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H260" t="inlineStr">
-        <is>
-          <t>Weapon Law Violations</t>
-        </is>
-      </c>
-      <c r="I260" t="inlineStr">
-        <is>
-          <t>400 E DIVISION LN</t>
-        </is>
-      </c>
-      <c r="J260" t="inlineStr"/>
-      <c r="K260" t="inlineStr"/>
-      <c r="L260" t="inlineStr"/>
-      <c r="M260" t="inlineStr">
-        <is>
-          <t>Weapon law violation on Jul 26, 2026, Tacoma Mall (400 E DIVISION LN). Case #2620701921 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>2620702008</t>
-        </is>
-      </c>
-      <c r="E261" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="I261" t="inlineStr">
-        <is>
-          <t>S 10TH ST &amp; S JUNETT ST</t>
-        </is>
-      </c>
-      <c r="J261" t="inlineStr"/>
-      <c r="K261" t="inlineStr"/>
-      <c r="L261" t="inlineStr"/>
-      <c r="M261" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - non injury on Jul 26, 2026, Tacoma Mall (S 10TH ST &amp; S JUNETT ST). Case #2620702008 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>2620700660</t>
-        </is>
-      </c>
-      <c r="E262" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>Assault Aggravated</t>
-        </is>
-      </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I262" t="inlineStr">
-        <is>
-          <t>800 E 25TH ST</t>
-        </is>
-      </c>
-      <c r="J262" t="inlineStr"/>
-      <c r="K262" t="inlineStr"/>
-      <c r="L262" t="inlineStr"/>
-      <c r="M262" t="inlineStr">
-        <is>
-          <t>Assault aggravated on Jul 26, 2026, Tacoma Mall (800 E 25TH ST). Case #2620700660 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>2621001973</t>
-        </is>
-      </c>
-      <c r="E263" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H263" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I263" t="inlineStr">
-        <is>
-          <t>1900 S UNION AVE</t>
-        </is>
-      </c>
-      <c r="J263" t="inlineStr"/>
-      <c r="K263" t="inlineStr"/>
-      <c r="L263" t="inlineStr"/>
-      <c r="M263" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 29, 2026, Tacoma Mall (1900 S UNION AVE). Case #2621001973 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>2620802008</t>
-        </is>
-      </c>
-      <c r="E264" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>Assault Aggravated</t>
-        </is>
-      </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I264" t="inlineStr">
-        <is>
-          <t>5500 6TH AVE</t>
-        </is>
-      </c>
-      <c r="J264" t="inlineStr"/>
-      <c r="K264" t="inlineStr"/>
-      <c r="L264" t="inlineStr"/>
-      <c r="M264" t="inlineStr">
-        <is>
-          <t>Assault aggravated on Jul 27, 2026, Tacoma Mall (5500 6TH AVE). Case #2620802008 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>2621102344</t>
-        </is>
-      </c>
-      <c r="E265" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="I265" t="inlineStr">
-        <is>
-          <t>S 74TH ST &amp; SOUTH TACOMA WAY</t>
-        </is>
-      </c>
-      <c r="J265" t="inlineStr"/>
-      <c r="K265" t="inlineStr"/>
-      <c r="L265" t="inlineStr"/>
-      <c r="M265" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - non injury on Jul 30, 2026, Tacoma Mall (S 74TH ST &amp; SOUTH TACOMA WAY). Case #2621102344 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>2620900726</t>
-        </is>
-      </c>
-      <c r="E266" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F266" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I266" t="inlineStr">
-        <is>
-          <t>3600 6TH AVE</t>
-        </is>
-      </c>
-      <c r="J266" t="inlineStr"/>
-      <c r="K266" t="inlineStr"/>
-      <c r="L266" t="inlineStr"/>
-      <c r="M266" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 28, 2026, Tacoma Mall (3600 6TH AVE). Case #2620900726 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>2621109009</t>
-        </is>
-      </c>
-      <c r="E267" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F267" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I267" t="inlineStr">
-        <is>
-          <t>3800 N PEARL ST</t>
-        </is>
-      </c>
-      <c r="J267" t="inlineStr"/>
-      <c r="K267" t="inlineStr"/>
-      <c r="L267" t="inlineStr"/>
-      <c r="M267" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 27, 2026, Tacoma Mall (3800 N PEARL ST). Case #2621109009 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>2621001310</t>
-        </is>
-      </c>
-      <c r="E268" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F268" t="inlineStr">
-        <is>
-          <t>Assault Aggravated</t>
-        </is>
-      </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H268" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I268" t="inlineStr">
-        <is>
-          <t>600 N JACKSON AVE</t>
-        </is>
-      </c>
-      <c r="J268" t="inlineStr"/>
-      <c r="K268" t="inlineStr"/>
-      <c r="L268" t="inlineStr"/>
-      <c r="M268" t="inlineStr">
-        <is>
-          <t>Assault aggravated on Jul 29, 2026, Tacoma Mall (600 N JACKSON AVE). Case #2621001310 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>2620701678</t>
-        </is>
-      </c>
-      <c r="E269" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F269" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H269" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="I269" t="inlineStr">
-        <is>
-          <t>4000 RUSTON WAY</t>
-        </is>
-      </c>
-      <c r="J269" t="inlineStr"/>
-      <c r="K269" t="inlineStr"/>
-      <c r="L269" t="inlineStr"/>
-      <c r="M269" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - non injury on Jul 26, 2026, Tacoma Mall (4000 RUSTON WAY). Case #2620701678 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>2621101218</t>
-        </is>
-      </c>
-      <c r="E270" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F270" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H270" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I270" t="inlineStr">
-        <is>
-          <t>8000 S HOSMER ST</t>
-        </is>
-      </c>
-      <c r="J270" t="inlineStr"/>
-      <c r="K270" t="inlineStr"/>
-      <c r="L270" t="inlineStr"/>
-      <c r="M270" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 30, 2026, Tacoma Mall (8000 S HOSMER ST). Case #2621101218 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>2621109023</t>
-        </is>
-      </c>
-      <c r="E271" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F271" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I271" t="inlineStr">
-        <is>
-          <t>1500 S FIFE ST</t>
-        </is>
-      </c>
-      <c r="J271" t="inlineStr"/>
-      <c r="K271" t="inlineStr"/>
-      <c r="L271" t="inlineStr"/>
-      <c r="M271" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 28, 2026, Tacoma Mall (1500 S FIFE ST). Case #2621109023 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>2621109045</t>
-        </is>
-      </c>
-      <c r="E272" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F272" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H272" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I272" t="inlineStr">
-        <is>
-          <t>1900 E D ST</t>
-        </is>
-      </c>
-      <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 28, 2026, Tacoma Mall (1900 E D ST). Case #2621109045 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>2620801831</t>
-        </is>
-      </c>
-      <c r="E273" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F273" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H273" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="I273" t="inlineStr">
-        <is>
-          <t>S 62ND ST &amp; S GOVE ST</t>
-        </is>
-      </c>
-      <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - non injury on Jul 27, 2026, Tacoma Mall (S 62ND ST &amp; S GOVE ST). Case #2620801831 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>2621109055</t>
-        </is>
-      </c>
-      <c r="E274" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F274" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H274" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I274" t="inlineStr">
-        <is>
-          <t>2100 S SHERIDAN AVE</t>
-        </is>
-      </c>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
-      <c r="M274" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 28, 2026, Tacoma Mall (2100 S SHERIDAN AVE). Case #2621109055 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>2620700616</t>
-        </is>
-      </c>
-      <c r="E275" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F275" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H275" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I275" t="inlineStr">
-        <is>
-          <t>800 S PEARL ST</t>
-        </is>
-      </c>
-      <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 26, 2026, Tacoma Mall (800 S PEARL ST). Case #2620700616 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>2621102065</t>
-        </is>
-      </c>
-      <c r="E276" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F276" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H276" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I276" t="inlineStr">
-        <is>
-          <t>1900 S UNION AVE</t>
-        </is>
-      </c>
-      <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-      <c r="M276" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 30, 2026, Tacoma Mall (1900 S UNION AVE). Case #2621102065 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>2621001907</t>
-        </is>
-      </c>
-      <c r="E277" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F277" t="inlineStr">
-        <is>
-          <t>Drug/Narcotics Violations</t>
-        </is>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>QUALITY_OF_LIFE</t>
-        </is>
-      </c>
-      <c r="H277" t="inlineStr">
-        <is>
-          <t>Drug/Narcotics Violations</t>
-        </is>
-      </c>
-      <c r="I277" t="inlineStr">
-        <is>
-          <t>200 E 64TH ST</t>
-        </is>
-      </c>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
-      <c r="M277" t="inlineStr">
-        <is>
-          <t>Drug/narcotics violations on Jul 29, 2026, Tacoma Mall (200 E 64TH ST). Case #2621001907 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>2621000152</t>
-        </is>
-      </c>
-      <c r="E278" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F278" t="inlineStr">
-        <is>
-          <t>Assault Simple</t>
-        </is>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H278" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I278" t="inlineStr">
-        <is>
-          <t>3500 S 45TH ST</t>
-        </is>
-      </c>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-      <c r="M278" t="inlineStr">
-        <is>
-          <t>Assault simple on Jul 29, 2026, Tacoma Mall (3500 S 45TH ST). Case #2621000152 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>2621109062</t>
-        </is>
-      </c>
-      <c r="E279" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F279" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H279" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I279" t="inlineStr">
-        <is>
-          <t>2300 YAKIMA CT</t>
-        </is>
-      </c>
-      <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
-      <c r="M279" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 26, 2026, Tacoma Mall (2300 YAKIMA CT). Case #2621109062 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>2620701081</t>
-        </is>
-      </c>
-      <c r="E280" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F280" t="inlineStr">
-        <is>
-          <t>Counterfeiting/Forgery</t>
-        </is>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H280" t="inlineStr">
-        <is>
-          <t>Counterfeiting/Forgery</t>
-        </is>
-      </c>
-      <c r="I280" t="inlineStr">
-        <is>
-          <t>3200 S 23RD ST</t>
-        </is>
-      </c>
-      <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
-      <c r="M280" t="inlineStr">
-        <is>
-          <t>Counterfeiting/forgery on Jul 26, 2026, Tacoma Mall (3200 S 23RD ST). Case #2620701081 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>2621101834</t>
-        </is>
-      </c>
-      <c r="E281" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F281" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H281" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="I281" t="inlineStr">
-        <is>
-          <t>19TH ST W &amp; MILDRED ST W</t>
-        </is>
-      </c>
-      <c r="J281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
-      <c r="M281" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - non injury on Jul 30, 2026, Tacoma Mall (19TH ST W &amp; MILDRED ST W). Case #2621101834 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>2620701703</t>
-        </is>
-      </c>
-      <c r="E282" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F282" t="inlineStr">
-        <is>
-          <t>Drug/Narcotics Violations</t>
-        </is>
-      </c>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>QUALITY_OF_LIFE</t>
-        </is>
-      </c>
-      <c r="H282" t="inlineStr">
-        <is>
-          <t>Drug/Narcotics Violations</t>
-        </is>
-      </c>
-      <c r="I282" t="inlineStr">
-        <is>
-          <t>S 74TH ST &amp; SOUTH TACOMA WAY</t>
-        </is>
-      </c>
-      <c r="J282" t="inlineStr"/>
-      <c r="K282" t="inlineStr"/>
-      <c r="L282" t="inlineStr"/>
-      <c r="M282" t="inlineStr">
-        <is>
-          <t>Drug/narcotics violations on Jul 26, 2026, Tacoma Mall (S 74TH ST &amp; SOUTH TACOMA WAY). Case #2620701703 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>2621002172</t>
-        </is>
-      </c>
-      <c r="E283" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F283" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Fatal</t>
-        </is>
-      </c>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H283" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Fatal</t>
-        </is>
-      </c>
-      <c r="I283" t="inlineStr">
-        <is>
-          <t>500 N SCHUSTER PKWY</t>
-        </is>
-      </c>
-      <c r="J283" t="inlineStr"/>
-      <c r="K283" t="inlineStr"/>
-      <c r="L283" t="inlineStr"/>
-      <c r="M283" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - fatal on Jul 29, 2026, Tacoma Mall (500 N SCHUSTER PKWY). Case #2621002172 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>2620701263</t>
-        </is>
-      </c>
-      <c r="E284" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>Assault Simple</t>
-        </is>
-      </c>
-      <c r="G284" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H284" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I284" t="inlineStr">
-        <is>
-          <t>400 S I ST</t>
-        </is>
-      </c>
-      <c r="J284" t="inlineStr"/>
-      <c r="K284" t="inlineStr"/>
-      <c r="L284" t="inlineStr"/>
-      <c r="M284" t="inlineStr">
-        <is>
-          <t>Assault simple on Jul 26, 2026, Tacoma Mall (400 S I ST). Case #2620701263 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>2620901147</t>
-        </is>
-      </c>
-      <c r="E285" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F285" t="inlineStr">
-        <is>
-          <t>Extortion (Blackmail)</t>
-        </is>
-      </c>
-      <c r="G285" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H285" t="inlineStr">
-        <is>
-          <t>Extortion (Blackmail)</t>
-        </is>
-      </c>
-      <c r="I285" t="inlineStr">
-        <is>
-          <t>5400 S STEELE ST</t>
-        </is>
-      </c>
-      <c r="J285" t="inlineStr"/>
-      <c r="K285" t="inlineStr"/>
-      <c r="L285" t="inlineStr"/>
-      <c r="M285" t="inlineStr">
-        <is>
-          <t>Extortion (blackmail) on Jul 28, 2026, Tacoma Mall (5400 S STEELE ST). Case #2620901147 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>2621109015</t>
-        </is>
-      </c>
-      <c r="E286" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F286" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G286" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H286" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I286" t="inlineStr">
-        <is>
-          <t>3200 S 23RD ST</t>
-        </is>
-      </c>
-      <c r="J286" t="inlineStr"/>
-      <c r="K286" t="inlineStr"/>
-      <c r="L286" t="inlineStr"/>
-      <c r="M286" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 28, 2026, Tacoma Mall (3200 S 23RD ST). Case #2621109015 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>2621000914</t>
-        </is>
-      </c>
-      <c r="E287" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F287" t="inlineStr">
-        <is>
-          <t>Assault Simple</t>
-        </is>
-      </c>
-      <c r="G287" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H287" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I287" t="inlineStr">
-        <is>
-          <t>1600 MARTIN LUTHER KING JR WAY</t>
-        </is>
-      </c>
-      <c r="J287" t="inlineStr"/>
-      <c r="K287" t="inlineStr"/>
-      <c r="L287" t="inlineStr"/>
-      <c r="M287" t="inlineStr">
-        <is>
-          <t>Assault simple on Jul 29, 2026, Tacoma Mall (1600 MARTIN LUTHER KING JR WAY). Case #2621000914 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>2620800264</t>
-        </is>
-      </c>
-      <c r="E288" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F288" t="inlineStr">
-        <is>
-          <t>Assault Simple</t>
-        </is>
-      </c>
-      <c r="G288" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H288" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I288" t="inlineStr">
-        <is>
-          <t>3500 S 56TH ST</t>
-        </is>
-      </c>
-      <c r="J288" t="inlineStr"/>
-      <c r="K288" t="inlineStr"/>
-      <c r="L288" t="inlineStr"/>
-      <c r="M288" t="inlineStr">
-        <is>
-          <t>Assault simple on Jul 27, 2026, Tacoma Mall (3500 S 56TH ST). Case #2620800264 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>2621109047</t>
-        </is>
-      </c>
-      <c r="E289" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F289" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G289" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H289" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I289" t="inlineStr">
-        <is>
-          <t>800 S 15TH ST</t>
-        </is>
-      </c>
-      <c r="J289" t="inlineStr"/>
-      <c r="K289" t="inlineStr"/>
-      <c r="L289" t="inlineStr"/>
-      <c r="M289" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 26, 2026, Tacoma Mall (800 S 15TH ST). Case #2621109047 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>2621109006</t>
-        </is>
-      </c>
-      <c r="E290" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H290" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I290" t="inlineStr">
-        <is>
-          <t>3300 S 23RD ST</t>
-        </is>
-      </c>
-      <c r="J290" t="inlineStr"/>
-      <c r="K290" t="inlineStr"/>
-      <c r="L290" t="inlineStr"/>
-      <c r="M290" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 27, 2026, Tacoma Mall (3300 S 23RD ST). Case #2621109006 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>2620809033</t>
-        </is>
-      </c>
-      <c r="E291" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F291" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G291" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H291" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I291" t="inlineStr">
-        <is>
-          <t>8600 S PARK AVE</t>
-        </is>
-      </c>
-      <c r="J291" t="inlineStr"/>
-      <c r="K291" t="inlineStr"/>
-      <c r="L291" t="inlineStr"/>
-      <c r="M291" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 26, 2026, Tacoma Mall (8600 S PARK AVE). Case #2620809033 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>2620900833</t>
-        </is>
-      </c>
-      <c r="E292" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F292" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G292" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H292" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I292" t="inlineStr">
-        <is>
-          <t>2300 S G ST</t>
-        </is>
-      </c>
-      <c r="J292" t="inlineStr"/>
-      <c r="K292" t="inlineStr"/>
-      <c r="L292" t="inlineStr"/>
-      <c r="M292" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 27, 2026, Tacoma Mall (2300 S G ST). Case #2620900833 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>2621109025</t>
-        </is>
-      </c>
-      <c r="E293" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F293" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G293" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H293" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I293" t="inlineStr">
-        <is>
-          <t>2300 WESTRIDGE AVE W</t>
-        </is>
-      </c>
-      <c r="J293" t="inlineStr"/>
-      <c r="K293" t="inlineStr"/>
-      <c r="L293" t="inlineStr"/>
-      <c r="M293" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 27, 2026, Tacoma Mall (2300 WESTRIDGE AVE W). Case #2621109025 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>2621100025</t>
-        </is>
-      </c>
-      <c r="E294" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t>Assault Aggravated</t>
-        </is>
-      </c>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H294" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I294" t="inlineStr">
-        <is>
-          <t>2500 PACIFIC AVE</t>
-        </is>
-      </c>
-      <c r="J294" t="inlineStr"/>
-      <c r="K294" t="inlineStr"/>
-      <c r="L294" t="inlineStr"/>
-      <c r="M294" t="inlineStr">
-        <is>
-          <t>Assault aggravated on Jul 29, 2026, Tacoma Mall (2500 PACIFIC AVE). Case #2621100025 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>2620801622</t>
-        </is>
-      </c>
-      <c r="E295" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F295" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="G295" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H295" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="I295" t="inlineStr">
-        <is>
-          <t>S 9TH ST &amp; S ADAMS ST</t>
-        </is>
-      </c>
-      <c r="J295" t="inlineStr"/>
-      <c r="K295" t="inlineStr"/>
-      <c r="L295" t="inlineStr"/>
-      <c r="M295" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - non injury on Jul 27, 2026, Tacoma Mall (S 9TH ST &amp; S ADAMS ST). Case #2620801622 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>2621101599</t>
-        </is>
-      </c>
-      <c r="E296" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F296" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="G296" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H296" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="I296" t="inlineStr">
-        <is>
-          <t>2600 CENTER ST</t>
-        </is>
-      </c>
-      <c r="J296" t="inlineStr"/>
-      <c r="K296" t="inlineStr"/>
-      <c r="L296" t="inlineStr"/>
-      <c r="M296" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - non injury on Jul 30, 2026, Tacoma Mall (2600 CENTER ST). Case #2621101599 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>2620700255</t>
-        </is>
-      </c>
-      <c r="E297" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F297" t="inlineStr">
-        <is>
-          <t>Assault Aggravated</t>
-        </is>
-      </c>
-      <c r="G297" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H297" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I297" t="inlineStr">
-        <is>
-          <t>700 ST HELENS AVE</t>
-        </is>
-      </c>
-      <c r="J297" t="inlineStr"/>
-      <c r="K297" t="inlineStr"/>
-      <c r="L297" t="inlineStr"/>
-      <c r="M297" t="inlineStr">
-        <is>
-          <t>Assault aggravated on Jul 26, 2026, Tacoma Mall (700 ST HELENS AVE). Case #2620700255 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>2620701640</t>
-        </is>
-      </c>
-      <c r="E298" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F298" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H298" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="I298" t="inlineStr">
-        <is>
-          <t>4000 RUSTON WAY</t>
-        </is>
-      </c>
-      <c r="J298" t="inlineStr"/>
-      <c r="K298" t="inlineStr"/>
-      <c r="L298" t="inlineStr"/>
-      <c r="M298" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - non injury on Jul 26, 2026, Tacoma Mall (4000 RUSTON WAY). Case #2620701640 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>2621000769</t>
-        </is>
-      </c>
-      <c r="E299" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>Extortion (Blackmail)</t>
-        </is>
-      </c>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H299" t="inlineStr">
-        <is>
-          <t>Extortion (Blackmail)</t>
-        </is>
-      </c>
-      <c r="I299" t="inlineStr">
-        <is>
-          <t>5800 S PUGET SOUND AVE</t>
-        </is>
-      </c>
-      <c r="J299" t="inlineStr"/>
-      <c r="K299" t="inlineStr"/>
-      <c r="L299" t="inlineStr"/>
-      <c r="M299" t="inlineStr">
-        <is>
-          <t>Extortion (blackmail) on Jul 29, 2026, Tacoma Mall (5800 S PUGET SOUND AVE). Case #2621000769 (use for a records request — full narratives are not published in open data).</t>
+          <t>Extortion (blackmail) on Jul 28, 2026, 1083 m from Tacoma Mall (5400 S STEELE ST). Case #2620901147 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M299"/>
+  <autoFilter ref="A1:M161"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19392,7 +12212,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01 04:19:08.436322+00:00</t>
+          <t>2026-08-01 04:21:05.180533+00:00</t>
         </is>
       </c>
     </row>
@@ -19424,7 +12244,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-25 04:19:08.436322+00:00</t>
+          <t>2026-07-25 04:21:05.180533+00:00</t>
         </is>
       </c>
     </row>
@@ -19435,7 +12255,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>298</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7">
@@ -19445,7 +12265,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">

--- a/reports/latest/blotter_report.xlsx
+++ b/reports/latest/blotter_report.xlsx
@@ -13,10 +13,10 @@
     <sheet name="Run Metadata" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Highlights'!$A$1:$M$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$161</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$285</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,10 +443,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="57" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -747,17 +747,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GREENHILLS</t>
+          <t>CLEARFORK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Mall at Green Hills</t>
+          <t>The Shops at Clearfork</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2126 Abbott Martin Road, Nashville, TN 37215</t>
+          <t>5188 Monahans Avenue Fort Worth TX 76109</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -780,8 +780,12 @@
       <c r="I7" t="n">
         <v>0</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>1086.4</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>46228.59375</v>
+      </c>
       <c r="L7" t="b">
         <v>0</v>
       </c>
@@ -789,17 +793,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>Empire Mall</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5085 Westheimer Houston TX 77056</t>
+          <t>5000 Empire Mall Sioux Falls SD 57106</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -808,25 +812,25 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>57</v>
+        <v>123</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="J8" t="n">
-        <v>163.5</v>
+        <v>315.5</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>46233</v>
+        <v>46234.24527777778</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
@@ -835,17 +839,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>INTLPLAZA</t>
+          <t>GREENHILLS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>International Plaza</t>
+          <t>The Mall at Green Hills</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2223 North West Shore Boulevard Tampa FL 33607</t>
+          <t>2126 Abbott Martin Road, Nashville, TN 37215</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -854,13 +858,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -868,12 +872,8 @@
       <c r="I9" t="n">
         <v>0</v>
       </c>
-      <c r="J9" t="n">
-        <v>1534.5</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>46232.16666666666</v>
-      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="b">
         <v>0</v>
       </c>
@@ -881,41 +881,45 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LENOX</t>
+          <t>HOUSTONGAL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lenox Square</t>
+          <t>Houston Galleria</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3393 Peachtree Road Northeast Atlanta GA 30326</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>NO COVERAGE</t>
+          <t>5085 Westheimer Houston TX 77056</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
+        <v>57</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>163.5</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>46233</v>
+      </c>
       <c r="L10" t="b">
         <v>0</v>
       </c>
@@ -923,17 +927,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>INTLPLAZA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>International Plaza</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>401 Northeast Northgate Way Seattle WA 98125</t>
+          <t>2223 North West Shore Boulevard Tampa FL 33607</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -942,25 +946,25 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>14</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>145.2</v>
+        <v>1534.5</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>46233.28194444445</v>
+        <v>46232.16666666666</v>
       </c>
       <c r="L11" t="b">
         <v>0</v>
@@ -969,22 +973,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>LENOX</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Lenox Square</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>433 Opry Mills Drive Nashville TN 37214</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>3393 Peachtree Road Northeast Atlanta GA 30326</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>NO COVERAGE</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1011,17 +1015,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>MALLATMILLENIA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>The Mall at Millenia</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4400 Sharon Road Charlotte NC 28211</t>
+          <t>4200 Conroy Road, Orlando, FL 32839</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1030,26 +1034,22 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>178.9</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>46232.16666666666</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="b">
         <v>0</v>
       </c>
@@ -1057,17 +1057,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4502 South Steele Street Tacoma WA 98409</t>
+          <t>401 Northeast Northgate Way Seattle WA 98125</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1076,25 +1076,25 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>471.3</v>
+        <v>145.2</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>46233</v>
+        <v>46233.28194444445</v>
       </c>
       <c r="L14" t="b">
         <v>0</v>
@@ -1103,22 +1103,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>THEDOMAIN</t>
+          <t>OPRYMILLS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Domain</t>
+          <t>Opry Mills</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>11410 Century Oaks Terrace Austin TX 78758</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>NO COVERAGE</t>
+          <t>433 Opry Mills Drive Nashville TN 37214</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1145,17 +1145,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>7700 East Kellogg Wichita KS 67207</t>
+          <t>4400 Sharon Road Charlotte NC 28211</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1164,32 +1164,208 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
         <v>1</v>
       </c>
-      <c r="I16" t="n">
-        <v>23</v>
-      </c>
       <c r="J16" t="n">
-        <v>288.9</v>
+        <v>178.9</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>46233.7625</v>
+        <v>46232.16666666666</v>
       </c>
       <c r="L16" t="b">
         <v>0</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TACOMAMALL</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tacoma Mall</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4502 South Steele Street Tacoma WA 98409</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>9</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>471.3</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>46233</v>
+      </c>
+      <c r="L17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>THEDOMAIN</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>The Domain</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>11410 Century Oaks Terrace Austin TX 78758</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>NO COVERAGE</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>7700 East Kellogg Wichita KS 67207</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>33</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>8</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>23</v>
+      </c>
+      <c r="J19" t="n">
+        <v>288.9</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>46233.7625</v>
+      </c>
+      <c r="L19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>UNIVPARKVILLAGE</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>University Park Village</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1612 South University Drive Fort Worth TX 76107</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L16"/>
+  <autoFilter ref="A1:L20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1205,7 +1381,7 @@
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
@@ -1520,30 +1696,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Empire Mall</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DP2026411044131300</t>
+          <t>CFS26-161839</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>46229.1125</v>
+        <v>46231.00275462963</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>assault-simple</t>
+          <t>Assault P3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1553,56 +1729,56 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>other-crimes-against-persons</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3200 BLOCK E CHERRY CREEK S DR</t>
+          <t>W 47TH ST &amp; S WESTPORT AVE</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>39.71130989687384</v>
+        <v>43.50940131405472</v>
       </c>
       <c r="K6" t="n">
-        <v>-104.9490029653731</v>
+        <v>-96.76746570282992</v>
       </c>
       <c r="L6" t="n">
-        <v>696.3</v>
+        <v>678.4</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Assault-simple on Jul 26, 2026, 696 m from Cherry Creek Shopping Center (3200 BLOCK E CHERRY CREEK S DR). Victims: 1. Case #DP2026411044 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault p3 on Jul 28, 2026, 678 m from Empire Mall (W 47TH ST &amp; S WESTPORT AVE). Case #CFS26-161839 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20260729-1600-11</t>
+          <t>DP2026411044131300</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>46232.16666666666</v>
+        <v>46229.1125</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Simple Assault</t>
+          <t>assault-simple</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1612,56 +1788,56 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>13B</t>
+          <t>other-crimes-against-persons</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4700 PIEDMONT ROW DR</t>
+          <t>3200 BLOCK E CHERRY CREEK S DR</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>35.15196312662653</v>
+        <v>39.71130989687384</v>
       </c>
       <c r="K7" t="n">
-        <v>-80.83980651357408</v>
+        <v>-104.9490029653731</v>
       </c>
       <c r="L7" t="n">
-        <v>850.6</v>
+        <v>696.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Simple assault on Jul 29, 2026, 851 m from Southpark (4700 PIEDMONT ROW DR). Status: Open. Case #20260729-1600-11 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault-simple on Jul 26, 2026, 696 m from Cherry Creek Shopping Center (3200 BLOCK E CHERRY CREEK S DR). Victims: 1. Case #DP2026411044 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Empire Mall</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2620701835</t>
+          <t>CFS26-161603</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>46229</v>
+        <v>46230.83325231481</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Assault Simple</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1671,56 +1847,56 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4000 S LAWRENCE ST</t>
+          <t>S WESTPORT AVE &amp; W 41ST ST</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>47.219421</v>
+        <v>43.51485103457241</v>
       </c>
       <c r="K8" t="n">
-        <v>-122.478428</v>
+        <v>-96.76794119445807</v>
       </c>
       <c r="L8" t="n">
-        <v>853.4</v>
+        <v>808.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Assault simple on Jul 26, 2026, 853 m from Tacoma Mall (4000 S LAWRENCE ST). Case #2620701835 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 27, 2026, 809 m from Empire Mall (S WESTPORT AVE &amp; W 41ST ST). Case #CFS26-161603 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>71878728447</t>
+          <t>20260729-1600-11</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>46230.4375</v>
+        <v>46232.16666666666</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Robbery</t>
+          <t>Simple Assault</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1730,26 +1906,26 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>VIOLENT CRIME</t>
+          <t>13B</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>16XX BLOCK OF N 105TH ST</t>
+          <t>4700 PIEDMONT ROW DR</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>47.70504225</v>
+        <v>35.15196312662653</v>
       </c>
       <c r="K9" t="n">
-        <v>-122.338094779232</v>
+        <v>-80.83980651357408</v>
       </c>
       <c r="L9" t="n">
-        <v>938.8</v>
+        <v>850.6</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Robbery on Jul 27, 2026, 939 m from Northgate Station (16XX BLOCK OF N 105TH ST). Case #2026-220064 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 29, 2026, 851 m from Southpark (4700 PIEDMONT ROW DR). Status: Open. Case #20260729-1600-11 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -1771,11 +1947,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2621000152</t>
+          <t>2620701835</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>46232</v>
+        <v>46229</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1794,21 +1970,21 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3500 S 45TH ST</t>
+          <t>4000 S LAWRENCE ST</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>47.216421</v>
+        <v>47.219421</v>
       </c>
       <c r="K10" t="n">
-        <v>-122.482428</v>
+        <v>-122.478428</v>
       </c>
       <c r="L10" t="n">
-        <v>1074.3</v>
+        <v>853.4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Assault simple on Jul 29, 2026, 1074 m from Tacoma Mall (3500 S 45TH ST). Case #2621000152 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault simple on Jul 26, 2026, 853 m from Tacoma Mall (4000 S LAWRENCE ST). Case #2620701835 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -1830,15 +2006,15 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>71894237115</t>
+          <t>71878728447</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>46231.20833333334</v>
+        <v>46230.4375</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aggravated Assault</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1853,51 +2029,51 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>15XX BLOCK OF NE 107TH ST</t>
+          <t>16XX BLOCK OF N 105TH ST</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>47.70668788</v>
+        <v>47.70504225</v>
       </c>
       <c r="K11" t="n">
-        <v>-122.311189997702</v>
+        <v>-122.338094779232</v>
       </c>
       <c r="L11" t="n">
-        <v>1145.7</v>
+        <v>938.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-221056 (use for a records request — full narratives are not published in open data).</t>
+          <t>Robbery on Jul 27, 2026, 939 m from Northgate Station (16XX BLOCK OF N 105TH ST). Case #2026-220064 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>TACOMAMALL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Tacoma Mall</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>71889871382</t>
+          <t>2621000152</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>46231.00625</v>
+        <v>46232</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Simple Assault</t>
+          <t>Assault Simple</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1907,56 +2083,56 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>ALL OTHER</t>
+          <t>Assault Offenses</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>15XX BLOCK OF NE 107TH ST</t>
+          <t>3500 S 45TH ST</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>47.70668788</v>
+        <v>47.216421</v>
       </c>
       <c r="K12" t="n">
-        <v>-122.311189997702</v>
+        <v>-122.482428</v>
       </c>
       <c r="L12" t="n">
-        <v>1145.7</v>
+        <v>1074.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Simple assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-220636 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault simple on Jul 29, 2026, 1074 m from Tacoma Mall (3500 S 45TH ST). Case #2621000152 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>26C142249</t>
+          <t>71894237115</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>46230.75</v>
+        <v>46231.20833333334</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>BATTERY ABW</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1966,56 +2142,56 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>SIM_ASSAULT</t>
+          <t>VIOLENT CRIME</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>700 BLOCK OF S MISSION RD</t>
+          <t>15XX BLOCK OF NE 107TH ST</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>37.6756469679485</v>
+        <v>47.70668788</v>
       </c>
       <c r="K13" t="n">
-        <v>-97.25850032865422</v>
+        <v>-122.311189997702</v>
       </c>
       <c r="L13" t="n">
-        <v>1251.5</v>
+        <v>1145.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Battery abw on Jul 27, 2026, 1251 m from Towne East Square (700 BLOCK OF S MISSION RD). Case #26C142249 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-221056 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>HOUSTONGAL:Houston PD NIBRS — Person</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>096140526</t>
+          <t>71889871382</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>46232</v>
+        <v>46231.00625</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aggravated Assault</t>
+          <t>Simple Assault</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2025,56 +2201,56 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>13A</t>
+          <t>ALL OTHER</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1900-1999 POST OAK PARK DR</t>
+          <t>15XX BLOCK OF NE 107TH ST</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>29.74712522681273</v>
+        <v>47.70668788</v>
       </c>
       <c r="K14" t="n">
-        <v>-95.45374747370188</v>
+        <v>-122.311189997702</v>
       </c>
       <c r="L14" t="n">
-        <v>1323.4</v>
+        <v>1145.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 29, 2026, 1323 m from Houston Galleria (1900-1999 POST OAK PARK DR). Case #096140526 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-220636 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202675136         </t>
+          <t>26C142249</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>46228.97847222222</v>
+        <v>46230.75</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[13B] ASSAULT                                                                   </t>
+          <t>BATTERY ABW</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2082,54 +2258,58 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>SIM_ASSAULT</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5XXX S HARDY DR</t>
+          <t>700 BLOCK OF S MISSION RD</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>33.3757495513233</v>
+        <v>37.6756469679485</v>
       </c>
       <c r="K15" t="n">
-        <v>-111.9531832468173</v>
+        <v>-97.25850032865422</v>
       </c>
       <c r="L15" t="n">
-        <v>1345.1</v>
+        <v>1251.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>[13b] assault on Jul 25, 2026, 1345 m from Arizona Mills (5XXX S HARDY DR). Case #TE202675136          (use for a records request — full narratives are not published in open data).</t>
+          <t>Battery abw on Jul 27, 2026, 1251 m from Towne East Square (700 BLOCK OF S MISSION RD). Case #26C142249 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Empire Mall</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2621102013</t>
+          <t>CFS26-164521</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>46233</v>
+        <v>46234.03421296296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Assault Simple</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2139,351 +2319,347 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5400 SOUTH TACOMA WAY</t>
+          <t>S MARION RD &amp; W 41ST ST</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>47.206421</v>
+        <v>43.51481738299845</v>
       </c>
       <c r="K16" t="n">
-        <v>-122.483428</v>
+        <v>-96.79096028032072</v>
       </c>
       <c r="L16" t="n">
-        <v>1578</v>
+        <v>1322.4</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Assault simple on Jul 30, 2026, 1578 m from Tacoma Mall (5400 SOUTH TACOMA WAY). Case #2621102013 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 31, 2026, 1322 m from Empire Mall (S MARION RD &amp; W 41ST ST). Case #CFS26-164521 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>HOUSTONGAL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Houston Galleria</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>HOUSTONGAL:Houston PD NIBRS — Person</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DP2026415473230300</t>
+          <t>096140526</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>46231.47916666666</v>
+        <v>46232</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>theft-shoplift</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>13A</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>15 S STEELE ST</t>
+          <t>1900-1999 POST OAK PARK DR</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>39.7162154712797</v>
+        <v>29.74712522681273</v>
       </c>
       <c r="K17" t="n">
-        <v>-104.9512928115626</v>
+        <v>-95.45374747370188</v>
       </c>
       <c r="L17" t="n">
-        <v>144.7</v>
+        <v>1323.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Theft-shoplift on Jul 28, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026415473 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 29, 2026, 1323 m from Houston Galleria (1900-1999 POST OAK PARK DR). Case #096140526 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DP2026413358260700</t>
+          <t xml:space="preserve">TE202675136         </t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>46230.47013888889</v>
+        <v>46228.97847222222</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>fraud-by-telephone</t>
+          <t xml:space="preserve">[13B] ASSAULT                                                                   </t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>white-collar-crime</t>
-        </is>
-      </c>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>15 S STEELE ST</t>
+          <t>5XXX S HARDY DR</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>39.7162154712797</v>
+        <v>33.3757495513233</v>
       </c>
       <c r="K18" t="n">
-        <v>-104.9512928115626</v>
+        <v>-111.9531832468173</v>
       </c>
       <c r="L18" t="n">
-        <v>144.7</v>
+        <v>1345.1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Fraud-by-telephone on Jul 27, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026413358 (use for a records request — full narratives are not published in open data).</t>
+          <t>[13b] assault on Jul 25, 2026, 1345 m from Arizona Mills (5XXX S HARDY DR). Case #TE202675136          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Empire Mall</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>71913162555</t>
+          <t>CFS26-164393</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>46232.82986111111</v>
+        <v>46233.93733796296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>S LARCH AVE &amp; W 43RD ST</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>47.7086028</v>
+        <v>43.51319846254545</v>
       </c>
       <c r="K19" t="n">
-        <v>-122.324615154453</v>
+        <v>-96.79336119066248</v>
       </c>
       <c r="L19" t="n">
-        <v>145.2</v>
+        <v>1453.4</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 29, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-222878 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 30, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-164393 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Empire Mall</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>71898889573</t>
+          <t>CFS26-159792</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>46231.625</v>
+        <v>46229.12712962963</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Weapons Violations</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>Weapons</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>S LARCH AVE &amp; W 43RD ST</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>47.7086028</v>
+        <v>43.51319846254545</v>
       </c>
       <c r="K20" t="n">
-        <v>-122.324615154453</v>
+        <v>-96.79336119066248</v>
       </c>
       <c r="L20" t="n">
-        <v>145.2</v>
+        <v>1453.4</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-221387 (use for a records request — full narratives are not published in open data).</t>
+          <t>Weapons violations on Jul 26, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-159792 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>TACOMAMALL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Tacoma Mall</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>71899277060</t>
+          <t>2621102013</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>46231.47569444445</v>
+        <v>46233</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Assault Simple</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>Assault Offenses</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>5400 SOUTH TACOMA WAY</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>47.7086028</v>
+        <v>47.206421</v>
       </c>
       <c r="K21" t="n">
-        <v>-122.324615154454</v>
+        <v>-122.483428</v>
       </c>
       <c r="L21" t="n">
-        <v>145.2</v>
+        <v>1578</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-221174 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault simple on Jul 30, 2026, 1578 m from Tacoma Mall (5400 SOUTH TACOMA WAY). Case #2621102013 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HOUSTONGAL:Houston PD NIBRS — Property</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>096475026</t>
+          <t>DP2026415473230300</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>46233</v>
+        <v>46231.47916666666</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>theft-shoplift</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2493,56 +2669,56 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>larceny</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5100-5199 ALABAMA ST W</t>
+          <t>15 S STEELE ST</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>29.73799058803365</v>
+        <v>39.7162154712797</v>
       </c>
       <c r="K22" t="n">
-        <v>-95.46478253884783</v>
+        <v>-104.9512928115626</v>
       </c>
       <c r="L22" t="n">
-        <v>163.5</v>
+        <v>144.7</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 30, 2026, 163 m from Houston Galleria (5100-5199 ALABAMA ST W). Case #096475026 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-shoplift on Jul 28, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026415473 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HOUSTONGAL:Houston PD NIBRS — Property</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>095621926</t>
+          <t>DP2026413358260700</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>46231</v>
+        <v>46230.47013888889</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Theft from motor vehicle</t>
+          <t>fraud-by-telephone</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2552,52 +2728,52 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>23F</t>
+          <t>white-collar-crime</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5100-5199 ALABAMA ST W</t>
+          <t>15 S STEELE ST</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>29.73799058803365</v>
+        <v>39.7162154712797</v>
       </c>
       <c r="K23" t="n">
-        <v>-95.46478253884783</v>
+        <v>-104.9512928115626</v>
       </c>
       <c r="L23" t="n">
-        <v>163.5</v>
+        <v>144.7</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Theft from motor vehicle on Jul 28, 2026, 163 m from Houston Galleria (5100-5199 ALABAMA ST W). Case #095621926 (use for a records request — full narratives are not published in open data).</t>
+          <t>Fraud-by-telephone on Jul 27, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026413358 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HOUSTONGAL:Houston PD NIBRS — Property</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>095601426</t>
+          <t>71913162555</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>46231</v>
+        <v>46232.82986111111</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2611,52 +2787,52 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5100-5199 ALABAMA ST W</t>
+          <t>3XX BLOCK OF NE NORTHGATE WAY</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>29.73799058803365</v>
+        <v>47.7086028</v>
       </c>
       <c r="K24" t="n">
-        <v>-95.46478253884783</v>
+        <v>-122.324615154453</v>
       </c>
       <c r="L24" t="n">
-        <v>163.5</v>
+        <v>145.2</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 163 m from Houston Galleria (5100-5199 ALABAMA ST W). Case #095601426 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 29, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-222878 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>20260728-1130-01</t>
+          <t>71898889573</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>46231.16666666666</v>
+        <v>46231.625</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2670,52 +2846,52 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>4XX BLOCK OF NE NORTHGATE WAY</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>35.15120046375475</v>
+        <v>47.7086028</v>
       </c>
       <c r="K25" t="n">
-        <v>-80.82867375349484</v>
+        <v>-122.324615154453</v>
       </c>
       <c r="L25" t="n">
-        <v>178.9</v>
+        <v>145.2</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1130-01 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-221387 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>20260728-1922-01</t>
+          <t>71899277060</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>46231.16666666666</v>
+        <v>46231.47569444445</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2729,26 +2905,26 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>4XX BLOCK OF NE NORTHGATE WAY</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>35.15120046375475</v>
+        <v>47.7086028</v>
       </c>
       <c r="K26" t="n">
-        <v>-80.82867375349484</v>
+        <v>-122.324615154454</v>
       </c>
       <c r="L26" t="n">
-        <v>178.9</v>
+        <v>145.2</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1922-01 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-221174 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2764,18 +2940,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M161"/>
+  <dimension ref="A1:M285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="49" customWidth="1" min="8" max="8"/>
-    <col width="48" customWidth="1" min="9" max="9"/>
+    <col width="53" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -12173,8 +12349,7324 @@
         </is>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>CLEARFORK</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>The Shops at Clearfork</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>CLEARFORK:Fort Worth PD Crime Data</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>260318151</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="n">
+        <v>46228.59375</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>PC 31.03(E)(3)   Theft prop&gt;=$750&lt;$2500</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>THEFT</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>2500 RIVER PARK DR</t>
+        </is>
+      </c>
+      <c r="J162" t="n">
+        <v>32.70776370720614</v>
+      </c>
+      <c r="K162" t="n">
+        <v>-97.41184118183627</v>
+      </c>
+      <c r="L162" t="n">
+        <v>1086.4</v>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>Pc 31.03(e)(3)   theft prop&gt;=$750&lt;$2500 on Jul 25, 2026, 1086 m from The Shops at Clearfork (2500 RIVER PARK DR). Premises: 20. Case #260318151 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>CFS26-159019</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="n">
+        <v>46228.31771990741</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Hit &amp; Run</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>S SOLBERG AVE &amp; W CHIPPEWA CIR</t>
+        </is>
+      </c>
+      <c r="J163" t="n">
+        <v>43.50469043243786</v>
+      </c>
+      <c r="K163" t="n">
+        <v>-96.7809382470065</v>
+      </c>
+      <c r="L163" t="n">
+        <v>750.9</v>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>Hit &amp; run on Jul 25, 2026, 751 m from Empire Mall (S SOLBERG AVE &amp; W CHIPPEWA CIR). Case #CFS26-159019 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>CFS26-160102</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="n">
+        <v>46229.22534722222</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Hit &amp; Run</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>S SHIRLEY AVE &amp; W 41ST ST &amp; W EMPIRE PL</t>
+        </is>
+      </c>
+      <c r="J164" t="n">
+        <v>43.51484546427315</v>
+      </c>
+      <c r="K164" t="n">
+        <v>-96.77443635605863</v>
+      </c>
+      <c r="L164" t="n">
+        <v>515.4</v>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>Hit &amp; run on Jul 26, 2026, 515 m from Empire Mall (S SHIRLEY AVE &amp; W 41ST ST &amp; W EMPIRE PL). Case #CFS26-160102 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>CFS26-159451</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="n">
+        <v>46228.90921296296</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Injury Accident P2</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>S MARION RD &amp; W 44TH ST</t>
+        </is>
+      </c>
+      <c r="J165" t="n">
+        <v>43.51236607235115</v>
+      </c>
+      <c r="K165" t="n">
+        <v>-96.7909260097226</v>
+      </c>
+      <c r="L165" t="n">
+        <v>1242.3</v>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>Injury accident p2 on Jul 25, 2026, 1242 m from Empire Mall (S MARION RD &amp; W 44TH ST). Case #CFS26-159451 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>CFS26-159511</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="n">
+        <v>46228.96453703703</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Check Wellbeing</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>W EMPIRE PL &amp; W EMPIRE PL &amp; W EMPIRE PL</t>
+        </is>
+      </c>
+      <c r="J166" t="n">
+        <v>43.51307477335324</v>
+      </c>
+      <c r="K166" t="n">
+        <v>-96.7766862668114</v>
+      </c>
+      <c r="L166" t="n">
+        <v>315.5</v>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>Check wellbeing on Jul 25, 2026, 316 m from Empire Mall (W EMPIRE PL &amp; W EMPIRE PL &amp; W EMPIRE PL). Case #CFS26-159511 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>CFS26-159454</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="n">
+        <v>46228.91143518518</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Check Wellbeing</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>S GATEWAY LN &amp; S GATEWAY BLVD</t>
+        </is>
+      </c>
+      <c r="J167" t="n">
+        <v>43.51281290360509</v>
+      </c>
+      <c r="K167" t="n">
+        <v>-96.7832464577892</v>
+      </c>
+      <c r="L167" t="n">
+        <v>662.9</v>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>Check wellbeing on Jul 25, 2026, 663 m from Empire Mall (S GATEWAY LN &amp; S GATEWAY BLVD). Case #CFS26-159454 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>CFS26-158981</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="n">
+        <v>46228.27228009259</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Check Wellbeing</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>S GOLDEN CREEK PL &amp; S WESTPORT AVE</t>
+        </is>
+      </c>
+      <c r="J168" t="n">
+        <v>43.51126427380821</v>
+      </c>
+      <c r="K168" t="n">
+        <v>-96.76791435426648</v>
+      </c>
+      <c r="L168" t="n">
+        <v>643.3</v>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>Check wellbeing on Jul 25, 2026, 643 m from Empire Mall (S GOLDEN CREEK PL &amp; S WESTPORT AVE). Case #CFS26-158981 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>CFS26-159792</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="n">
+        <v>46229.12712962963</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Weapons Violations</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Weapons</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>S LARCH AVE &amp; W 43RD ST</t>
+        </is>
+      </c>
+      <c r="J169" t="n">
+        <v>43.51319846254545</v>
+      </c>
+      <c r="K169" t="n">
+        <v>-96.79336119066248</v>
+      </c>
+      <c r="L169" t="n">
+        <v>1453.4</v>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>Weapons violations on Jul 26, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-159792 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>CFS26-159074</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="n">
+        <v>46228.47578703704</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Noise Disturbance</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>S MAYFAIR DR &amp; W 38TH ST</t>
+        </is>
+      </c>
+      <c r="J170" t="n">
+        <v>43.51704606425148</v>
+      </c>
+      <c r="K170" t="n">
+        <v>-96.78170076795006</v>
+      </c>
+      <c r="L170" t="n">
+        <v>887.7</v>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>Noise disturbance on Jul 25, 2026, 888 m from Empire Mall (S MAYFAIR DR &amp; W 38TH ST). Case #CFS26-159074 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>CFS26-159523</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="n">
+        <v>46228.97929398148</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Larceny</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Theft</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>S CAROLYN AVE &amp; W 38TH ST</t>
+        </is>
+      </c>
+      <c r="J171" t="n">
+        <v>43.51777966412532</v>
+      </c>
+      <c r="K171" t="n">
+        <v>-96.77850989695047</v>
+      </c>
+      <c r="L171" t="n">
+        <v>858.8</v>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>Larceny on Jul 25, 2026, 859 m from Empire Mall (S CAROLYN AVE &amp; W 38TH ST). Case #CFS26-159523 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>CFS26-158990</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="n">
+        <v>46228.28158564815</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Protection Order Violation</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>I 29 RAMP &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J172" t="n">
+        <v>43.51483782368534</v>
+      </c>
+      <c r="K172" t="n">
+        <v>-96.77936822734073</v>
+      </c>
+      <c r="L172" t="n">
+        <v>580.2</v>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>Protection order violation on Jul 25, 2026, 580 m from Empire Mall (I 29 RAMP &amp; W 41ST ST). Case #CFS26-158990 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>CFS26-159352</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="n">
+        <v>46228.84677083333</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Stalled Vehicle</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>S LOUISE AVE &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J173" t="n">
+        <v>43.51480707435041</v>
+      </c>
+      <c r="K173" t="n">
+        <v>-96.77110350565825</v>
+      </c>
+      <c r="L173" t="n">
+        <v>626.1</v>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>Stalled vehicle on Jul 25, 2026, 626 m from Empire Mall (S LOUISE AVE &amp; W 41ST ST). Case #CFS26-159352 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>CFS26-159379</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="n">
+        <v>46228.86439814815</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Man Down</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>S SHIRLEY AVE &amp; W 41ST ST &amp; W EMPIRE PL</t>
+        </is>
+      </c>
+      <c r="J174" t="n">
+        <v>43.51484546427315</v>
+      </c>
+      <c r="K174" t="n">
+        <v>-96.77443635605863</v>
+      </c>
+      <c r="L174" t="n">
+        <v>515.4</v>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>Man down on Jul 25, 2026, 515 m from Empire Mall (S SHIRLEY AVE &amp; W 41ST ST &amp; W EMPIRE PL). Case #CFS26-159379 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>CFS26-159552</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="n">
+        <v>46229.0159375</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Liquor Law Violation</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Drugs/Alcohol</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>S SOLBERG AVE &amp; W VALHALLA BLVD</t>
+        </is>
+      </c>
+      <c r="J175" t="n">
+        <v>43.50623018207514</v>
+      </c>
+      <c r="K175" t="n">
+        <v>-96.77990236625163</v>
+      </c>
+      <c r="L175" t="n">
+        <v>562.7</v>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>Liquor law violation on Jul 26, 2026, 563 m from Empire Mall (S SOLBERG AVE &amp; W VALHALLA BLVD). Case #CFS26-159552 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>CFS26-160038</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="n">
+        <v>46229.18260416666</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Suspicious Subject</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>S LARCH AVE &amp; W 43RD ST</t>
+        </is>
+      </c>
+      <c r="J176" t="n">
+        <v>43.51319846254545</v>
+      </c>
+      <c r="K176" t="n">
+        <v>-96.79336119066248</v>
+      </c>
+      <c r="L176" t="n">
+        <v>1453.4</v>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>Suspicious subject on Jul 26, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-160038 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>CFS26-159326</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="n">
+        <v>46228.81621527778</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Accident</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>S KIWANIS AVE &amp; W 49TH ST</t>
+        </is>
+      </c>
+      <c r="J177" t="n">
+        <v>43.50841031406458</v>
+      </c>
+      <c r="K177" t="n">
+        <v>-96.75802133136874</v>
+      </c>
+      <c r="L177" t="n">
+        <v>1447.9</v>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>Accident on Jul 25, 2026, 1448 m from Empire Mall (S KIWANIS AVE &amp; W 49TH ST). Case #CFS26-159326 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>CFS26-159498</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="n">
+        <v>46228.95116898148</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Theft</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>S WESTPORT AVE &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J178" t="n">
+        <v>43.51485103457241</v>
+      </c>
+      <c r="K178" t="n">
+        <v>-96.76794119445807</v>
+      </c>
+      <c r="L178" t="n">
+        <v>808.9</v>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 25, 2026, 809 m from Empire Mall (S WESTPORT AVE &amp; W 41ST ST). Case #CFS26-159498 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>CFS26-160064</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="n">
+        <v>46229.19341435185</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Loitering</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>W 41ST ST &amp; W EMPIRE PL</t>
+        </is>
+      </c>
+      <c r="J179" t="n">
+        <v>43.51484419416143</v>
+      </c>
+      <c r="K179" t="n">
+        <v>-96.77669360636062</v>
+      </c>
+      <c r="L179" t="n">
+        <v>509.1</v>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>Loitering on Jul 26, 2026, 509 m from Empire Mall (W 41ST ST &amp; W EMPIRE PL). Case #CFS26-160064 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>CFS26-159225</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="n">
+        <v>46228.71445601852</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Disorderly Subjects</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>S MARION RD &amp; W 44TH ST</t>
+        </is>
+      </c>
+      <c r="J180" t="n">
+        <v>43.51236607235115</v>
+      </c>
+      <c r="K180" t="n">
+        <v>-96.7909260097226</v>
+      </c>
+      <c r="L180" t="n">
+        <v>1242.3</v>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>Disorderly subjects on Jul 25, 2026, 1242 m from Empire Mall (S MARION RD &amp; W 44TH ST). Case #CFS26-159225 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>CFS26-159217</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="n">
+        <v>46228.70810185185</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Disorderly Subjects</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>S MARION RD &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J181" t="n">
+        <v>43.51481738299845</v>
+      </c>
+      <c r="K181" t="n">
+        <v>-96.79096028032072</v>
+      </c>
+      <c r="L181" t="n">
+        <v>1322.4</v>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>Disorderly subjects on Jul 25, 2026, 1322 m from Empire Mall (S MARION RD &amp; W 41ST ST). Case #CFS26-159217 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>CFS26-159290</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="n">
+        <v>46228.79174768519</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Disorderly Subjects</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>W 41ST ST &amp; W EMPIRE PL</t>
+        </is>
+      </c>
+      <c r="J182" t="n">
+        <v>43.51484419416143</v>
+      </c>
+      <c r="K182" t="n">
+        <v>-96.77669360636062</v>
+      </c>
+      <c r="L182" t="n">
+        <v>509.1</v>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>Disorderly subjects on Jul 25, 2026, 509 m from Empire Mall (W 41ST ST &amp; W EMPIRE PL). Case #CFS26-159290 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>CFS26-159410</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="n">
+        <v>46228.88324074074</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Disorderly Subjects</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>S LARCH AVE &amp; W 43RD ST</t>
+        </is>
+      </c>
+      <c r="J183" t="n">
+        <v>43.51319846254545</v>
+      </c>
+      <c r="K183" t="n">
+        <v>-96.79336119066248</v>
+      </c>
+      <c r="L183" t="n">
+        <v>1453.4</v>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>Disorderly subjects on Jul 25, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-159410 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>CFS26-159608</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="n">
+        <v>46229.05333333334</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Disorderly Subjects</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>S LARCH AVE &amp; W 43RD ST</t>
+        </is>
+      </c>
+      <c r="J184" t="n">
+        <v>43.51319846254545</v>
+      </c>
+      <c r="K184" t="n">
+        <v>-96.79336119066248</v>
+      </c>
+      <c r="L184" t="n">
+        <v>1453.4</v>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>Disorderly subjects on Jul 26, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-159608 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>CFS26-159063</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="n">
+        <v>46228.43545138889</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Family Dispute</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>S GATEWAY BLVD &amp; S TERRY AVE</t>
+        </is>
+      </c>
+      <c r="J185" t="n">
+        <v>43.51220536263347</v>
+      </c>
+      <c r="K185" t="n">
+        <v>-96.7859525684798</v>
+      </c>
+      <c r="L185" t="n">
+        <v>846.7</v>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>Family dispute on Jul 25, 2026, 847 m from Empire Mall (S GATEWAY BLVD &amp; S TERRY AVE). Case #CFS26-159063 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>CFS26-159009</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="n">
+        <v>46228.30119212963</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Intoxicated Subject</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Drugs/Alcohol</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>S GATEWAY LN &amp; S GATEWAY BLVD</t>
+        </is>
+      </c>
+      <c r="J186" t="n">
+        <v>43.51281290360509</v>
+      </c>
+      <c r="K186" t="n">
+        <v>-96.7832464577892</v>
+      </c>
+      <c r="L186" t="n">
+        <v>662.9</v>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>Intoxicated subject on Jul 25, 2026, 663 m from Empire Mall (S GATEWAY LN &amp; S GATEWAY BLVD). Case #CFS26-159009 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>CFS26-160089</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="n">
+        <v>46229.21228009259</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Traffic Hazard</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>S TERRY AVE &amp; W 38TH ST</t>
+        </is>
+      </c>
+      <c r="J187" t="n">
+        <v>43.51704515371051</v>
+      </c>
+      <c r="K187" t="n">
+        <v>-96.78631726005253</v>
+      </c>
+      <c r="L187" t="n">
+        <v>1132.2</v>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>Traffic hazard on Jul 26, 2026, 1132 m from Empire Mall (S TERRY AVE &amp; W 38TH ST). Case #CFS26-160089 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>CFS26-159914</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="n">
+        <v>46229.14921296296</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Traffic Hazard</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>W 35TH ST &amp; W THURMAN DR</t>
+        </is>
+      </c>
+      <c r="J188" t="n">
+        <v>43.51960763359122</v>
+      </c>
+      <c r="K188" t="n">
+        <v>-96.7878127897683</v>
+      </c>
+      <c r="L188" t="n">
+        <v>1417.4</v>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>Traffic hazard on Jul 26, 2026, 1417 m from Empire Mall (W 35TH ST &amp; W THURMAN DR). Case #CFS26-159914 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>CFS26-160048</t>
+        </is>
+      </c>
+      <c r="E189" s="3" t="n">
+        <v>46229.18739583333</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Child Custody Dispute</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>PARK SERVICE RD &amp; S OXBOW AVE &amp; W 53RD ST</t>
+        </is>
+      </c>
+      <c r="J189" t="n">
+        <v>43.50489764292522</v>
+      </c>
+      <c r="K189" t="n">
+        <v>-96.76589799216201</v>
+      </c>
+      <c r="L189" t="n">
+        <v>999.1</v>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>Child custody dispute on Jul 26, 2026, 999 m from Empire Mall (PARK SERVICE RD &amp; S OXBOW AVE &amp; W 53RD ST). Case #CFS26-160048 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>CFS26-159581</t>
+        </is>
+      </c>
+      <c r="E190" s="3" t="n">
+        <v>46229.03685185185</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Reckless Driver</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>S LOUISE AVE &amp; W 49TH ST</t>
+        </is>
+      </c>
+      <c r="J190" t="n">
+        <v>43.50759974361088</v>
+      </c>
+      <c r="K190" t="n">
+        <v>-96.77103685388698</v>
+      </c>
+      <c r="L190" t="n">
+        <v>487.4</v>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>Reckless driver on Jul 26, 2026, 487 m from Empire Mall (S LOUISE AVE &amp; W 49TH ST). Case #CFS26-159581 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>CFS26-160716</t>
+        </is>
+      </c>
+      <c r="E191" s="3" t="n">
+        <v>46229.90825231482</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Check Wellbeing</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>S TECHNOPOLIS DR &amp; S NEVADA AVE &amp; W 57TH ST</t>
+        </is>
+      </c>
+      <c r="J191" t="n">
+        <v>43.5003427218675</v>
+      </c>
+      <c r="K191" t="n">
+        <v>-96.77458843355284</v>
+      </c>
+      <c r="L191" t="n">
+        <v>1112.9</v>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>Check wellbeing on Jul 26, 2026, 1113 m from Empire Mall (S TECHNOPOLIS DR &amp; S NEVADA AVE &amp; W 57TH ST). Case #CFS26-160716 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>CFS26-160779</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="n">
+        <v>46229.96965277778</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Public Assist</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>S TENNIS LN &amp; W 55TH ST</t>
+        </is>
+      </c>
+      <c r="J192" t="n">
+        <v>43.50200894302012</v>
+      </c>
+      <c r="K192" t="n">
+        <v>-96.76842992223241</v>
+      </c>
+      <c r="L192" t="n">
+        <v>1097.5</v>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>Public assist on Jul 26, 2026, 1097 m from Empire Mall (S TENNIS LN &amp; W 55TH ST). Case #CFS26-160779 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>CFS26-160342</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="n">
+        <v>46229.62094907407</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Suspicious Activity</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>I 29 &amp; I 29 RAMP</t>
+        </is>
+      </c>
+      <c r="J193" t="n">
+        <v>43.52358822521935</v>
+      </c>
+      <c r="K193" t="n">
+        <v>-96.78066507908444</v>
+      </c>
+      <c r="L193" t="n">
+        <v>1527.6</v>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>Suspicious activity on Jul 26, 2026, 1528 m from Empire Mall (I 29 &amp; I 29 RAMP). Case #CFS26-160342 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>CFS26-160736</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="n">
+        <v>46229.93079861111</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Suspicious Subject</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>I 29 &amp; I 29 RAMP</t>
+        </is>
+      </c>
+      <c r="J194" t="n">
+        <v>43.52358822521935</v>
+      </c>
+      <c r="K194" t="n">
+        <v>-96.78066507908444</v>
+      </c>
+      <c r="L194" t="n">
+        <v>1527.6</v>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>Suspicious subject on Jul 26, 2026, 1528 m from Empire Mall (I 29 &amp; I 29 RAMP). Case #CFS26-160736 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>CFS26-160505</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="n">
+        <v>46229.75098379629</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Family Dispute</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>S LARCH AVE &amp; W 43RD ST</t>
+        </is>
+      </c>
+      <c r="J195" t="n">
+        <v>43.51319846254545</v>
+      </c>
+      <c r="K195" t="n">
+        <v>-96.79336119066248</v>
+      </c>
+      <c r="L195" t="n">
+        <v>1453.4</v>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>Family dispute on Jul 26, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-160505 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>CFS26-160511</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="n">
+        <v>46229.75467592593</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Family Dispute</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>S LARCH AVE &amp; W 43RD ST</t>
+        </is>
+      </c>
+      <c r="J196" t="n">
+        <v>43.51319846254545</v>
+      </c>
+      <c r="K196" t="n">
+        <v>-96.79336119066248</v>
+      </c>
+      <c r="L196" t="n">
+        <v>1453.4</v>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>Family dispute on Jul 26, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-160511 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>CFS26-160288</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="n">
+        <v>46229.56722222222</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Check Security</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>S WESTPORT AVE &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J197" t="n">
+        <v>43.51485103457241</v>
+      </c>
+      <c r="K197" t="n">
+        <v>-96.76794119445807</v>
+      </c>
+      <c r="L197" t="n">
+        <v>808.9</v>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>Check security on Jul 26, 2026, 809 m from Empire Mall (S WESTPORT AVE &amp; W 41ST ST). Case #CFS26-160288 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>CFS26-160875</t>
+        </is>
+      </c>
+      <c r="E198" s="3" t="n">
+        <v>46230.0453587963</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Family Dispute</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>S GATEWAY LN &amp; S GATEWAY BLVD</t>
+        </is>
+      </c>
+      <c r="J198" t="n">
+        <v>43.51281290360509</v>
+      </c>
+      <c r="K198" t="n">
+        <v>-96.7832464577892</v>
+      </c>
+      <c r="L198" t="n">
+        <v>662.9</v>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>Family dispute on Jul 27, 2026, 663 m from Empire Mall (S GATEWAY LN &amp; S GATEWAY BLVD). Case #CFS26-160875 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>CFS26-160633</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="n">
+        <v>46229.85539351852</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Suspicious Vehicle</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>S GRAND CIR &amp; W 59TH ST</t>
+        </is>
+      </c>
+      <c r="J199" t="n">
+        <v>43.49854222157047</v>
+      </c>
+      <c r="K199" t="n">
+        <v>-96.7727172028677</v>
+      </c>
+      <c r="L199" t="n">
+        <v>1332.1</v>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>Suspicious vehicle on Jul 26, 2026, 1332 m from Empire Mall (S GRAND CIR &amp; W 59TH ST). Case #CFS26-160633 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>CFS26-160199</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="n">
+        <v>46229.36001157408</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Family Dispute</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>S GOLDEN CREEK PL &amp; S WESTPORT AVE</t>
+        </is>
+      </c>
+      <c r="J200" t="n">
+        <v>43.51126427380821</v>
+      </c>
+      <c r="K200" t="n">
+        <v>-96.76791435426648</v>
+      </c>
+      <c r="L200" t="n">
+        <v>643.3</v>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>Family dispute on Jul 26, 2026, 643 m from Empire Mall (S GOLDEN CREEK PL &amp; S WESTPORT AVE). Case #CFS26-160199 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>CFS26-160492</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="n">
+        <v>46229.74104166667</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Reckless Driver</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>S MEADOW AVE &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J201" t="n">
+        <v>43.51483469375145</v>
+      </c>
+      <c r="K201" t="n">
+        <v>-96.78305741794478</v>
+      </c>
+      <c r="L201" t="n">
+        <v>772.5</v>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>Reckless driver on Jul 26, 2026, 773 m from Empire Mall (S MEADOW AVE &amp; W 41ST ST). Case #CFS26-160492 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>CFS26-161737</t>
+        </is>
+      </c>
+      <c r="E202" s="3" t="n">
+        <v>46230.9250925926</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Larceny</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Theft</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>S MARION RD &amp; W 44TH ST</t>
+        </is>
+      </c>
+      <c r="J202" t="n">
+        <v>43.51236607235115</v>
+      </c>
+      <c r="K202" t="n">
+        <v>-96.7909260097226</v>
+      </c>
+      <c r="L202" t="n">
+        <v>1242.3</v>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>Larceny on Jul 27, 2026, 1242 m from Empire Mall (S MARION RD &amp; W 44TH ST). Case #CFS26-161737 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>CFS26-161544</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="n">
+        <v>46230.79988425926</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Larceny</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Theft</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>S TERRY AVE &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J203" t="n">
+        <v>43.51482816316226</v>
+      </c>
+      <c r="K203" t="n">
+        <v>-96.78634901931601</v>
+      </c>
+      <c r="L203" t="n">
+        <v>988.9</v>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>Larceny on Jul 27, 2026, 989 m from Empire Mall (S TERRY AVE &amp; W 41ST ST). Case #CFS26-161544 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>CFS26-161498</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="n">
+        <v>46230.76065972223</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Hit &amp; Run</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>S SHIRLEY AVE &amp; W 38TH ST</t>
+        </is>
+      </c>
+      <c r="J204" t="n">
+        <v>43.51777845484326</v>
+      </c>
+      <c r="K204" t="n">
+        <v>-96.77437979679537</v>
+      </c>
+      <c r="L204" t="n">
+        <v>837.7</v>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>Hit &amp; run on Jul 27, 2026, 838 m from Empire Mall (S SHIRLEY AVE &amp; W 38TH ST). Case #CFS26-161498 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>CFS26-161973</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="n">
+        <v>46231.13439814815</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Disorderly Subjects</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>S ARIZONA DR &amp; S ROLLING GREEN AVE</t>
+        </is>
+      </c>
+      <c r="J205" t="n">
+        <v>43.49801125109279</v>
+      </c>
+      <c r="K205" t="n">
+        <v>-96.77724004489316</v>
+      </c>
+      <c r="L205" t="n">
+        <v>1373.1</v>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>Disorderly subjects on Jul 28, 2026, 1373 m from Empire Mall (S ARIZONA DR &amp; S ROLLING GREEN AVE). Case #CFS26-161973 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>CFS26-161649</t>
+        </is>
+      </c>
+      <c r="E206" s="3" t="n">
+        <v>46230.8672337963</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Injury Accident P3</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>S LOUISE AVE &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J206" t="n">
+        <v>43.51480707435041</v>
+      </c>
+      <c r="K206" t="n">
+        <v>-96.77110350565825</v>
+      </c>
+      <c r="L206" t="n">
+        <v>626.1</v>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>Injury accident p3 on Jul 27, 2026, 626 m from Empire Mall (S LOUISE AVE &amp; W 41ST ST). Case #CFS26-161649 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>CFS26-161603</t>
+        </is>
+      </c>
+      <c r="E207" s="3" t="n">
+        <v>46230.83325231481</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Assault</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Assault</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>S WESTPORT AVE &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J207" t="n">
+        <v>43.51485103457241</v>
+      </c>
+      <c r="K207" t="n">
+        <v>-96.76794119445807</v>
+      </c>
+      <c r="L207" t="n">
+        <v>808.9</v>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>Assault on Jul 27, 2026, 809 m from Empire Mall (S WESTPORT AVE &amp; W 41ST ST). Case #CFS26-161603 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>CFS26-161727</t>
+        </is>
+      </c>
+      <c r="E208" s="3" t="n">
+        <v>46230.92016203704</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Family Dispute</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>S GOLDEN CREEK PL &amp; S WESTPORT AVE</t>
+        </is>
+      </c>
+      <c r="J208" t="n">
+        <v>43.51126427380821</v>
+      </c>
+      <c r="K208" t="n">
+        <v>-96.76791435426648</v>
+      </c>
+      <c r="L208" t="n">
+        <v>643.3</v>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>Family dispute on Jul 27, 2026, 643 m from Empire Mall (S GOLDEN CREEK PL &amp; S WESTPORT AVE). Case #CFS26-161727 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>CFS26-161531</t>
+        </is>
+      </c>
+      <c r="E209" s="3" t="n">
+        <v>46230.79126157407</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Family Dispute</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>W ROYAL ST &amp; W COTTAGE TRL</t>
+        </is>
+      </c>
+      <c r="J209" t="n">
+        <v>43.50235624174632</v>
+      </c>
+      <c r="K209" t="n">
+        <v>-96.78809349742139</v>
+      </c>
+      <c r="L209" t="n">
+        <v>1330</v>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>Family dispute on Jul 27, 2026, 1330 m from Empire Mall (W ROYAL ST &amp; W COTTAGE TRL). Case #CFS26-161531 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>CFS26-161096</t>
+        </is>
+      </c>
+      <c r="E210" s="3" t="n">
+        <v>46230.29450231481</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Family Dispute</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>S MADELYN AVE &amp; W 40TH ST</t>
+        </is>
+      </c>
+      <c r="J210" t="n">
+        <v>43.51538966329255</v>
+      </c>
+      <c r="K210" t="n">
+        <v>-96.78441883878321</v>
+      </c>
+      <c r="L210" t="n">
+        <v>896.4</v>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>Family dispute on Jul 27, 2026, 896 m from Empire Mall (S MADELYN AVE &amp; W 40TH ST). Case #CFS26-161096 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>CFS26-161785</t>
+        </is>
+      </c>
+      <c r="E211" s="3" t="n">
+        <v>46230.95932870371</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Child Custody Dispute</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>S TECHNOLOGY DR &amp; W VALHALLA BLVD</t>
+        </is>
+      </c>
+      <c r="J211" t="n">
+        <v>43.50660996268574</v>
+      </c>
+      <c r="K211" t="n">
+        <v>-96.77575207566703</v>
+      </c>
+      <c r="L211" t="n">
+        <v>411.9</v>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>Child custody dispute on Jul 27, 2026, 412 m from Empire Mall (S TECHNOLOGY DR &amp; W VALHALLA BLVD). Case #CFS26-161785 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>CFS26-161660</t>
+        </is>
+      </c>
+      <c r="E212" s="3" t="n">
+        <v>46230.87556712963</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Child Custody Dispute</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>W ST JAMES CIR &amp; W ST JAMES DR &amp; W VICTORIA DR</t>
+        </is>
+      </c>
+      <c r="J212" t="n">
+        <v>43.50653056252924</v>
+      </c>
+      <c r="K212" t="n">
+        <v>-96.78533738843498</v>
+      </c>
+      <c r="L212" t="n">
+        <v>877.9</v>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>Child custody dispute on Jul 27, 2026, 878 m from Empire Mall (W ST JAMES CIR &amp; W ST JAMES DR &amp; W VICTORIA DR). Case #CFS26-161660 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>CFS26-162016</t>
+        </is>
+      </c>
+      <c r="E213" s="3" t="n">
+        <v>46231.18817129629</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Noise Disturbance</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>S LARCH AVE &amp; W 43RD ST</t>
+        </is>
+      </c>
+      <c r="J213" t="n">
+        <v>43.51319846254545</v>
+      </c>
+      <c r="K213" t="n">
+        <v>-96.79336119066248</v>
+      </c>
+      <c r="L213" t="n">
+        <v>1453.4</v>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>Noise disturbance on Jul 28, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-162016 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>CFS26-161878</t>
+        </is>
+      </c>
+      <c r="E214" s="3" t="n">
+        <v>46231.03434027778</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Noise Disturbance</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>S LARCH AVE &amp; W 43RD ST</t>
+        </is>
+      </c>
+      <c r="J214" t="n">
+        <v>43.51319846254545</v>
+      </c>
+      <c r="K214" t="n">
+        <v>-96.79336119066248</v>
+      </c>
+      <c r="L214" t="n">
+        <v>1453.4</v>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>Noise disturbance on Jul 28, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-161878 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>CFS26-161852</t>
+        </is>
+      </c>
+      <c r="E215" s="3" t="n">
+        <v>46231.01834490741</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Customer Dispute</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>S TECHLINK CIR &amp; S TECHNOLOGY DR &amp; W 53RD ST</t>
+        </is>
+      </c>
+      <c r="J215" t="n">
+        <v>43.504010843024</v>
+      </c>
+      <c r="K215" t="n">
+        <v>-96.77367136420254</v>
+      </c>
+      <c r="L215" t="n">
+        <v>721.3</v>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>Customer dispute on Jul 28, 2026, 721 m from Empire Mall (S TECHLINK CIR &amp; S TECHNOLOGY DR &amp; W 53RD ST). Case #CFS26-161852 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>CFS26-161905</t>
+        </is>
+      </c>
+      <c r="E216" s="3" t="n">
+        <v>46231.05966435185</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Suspicious Vehicle</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>S GATEWAY LN &amp; S GATEWAY BLVD</t>
+        </is>
+      </c>
+      <c r="J216" t="n">
+        <v>43.51281290360509</v>
+      </c>
+      <c r="K216" t="n">
+        <v>-96.7832464577892</v>
+      </c>
+      <c r="L216" t="n">
+        <v>662.9</v>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>Suspicious vehicle on Jul 28, 2026, 663 m from Empire Mall (S GATEWAY LN &amp; S GATEWAY BLVD). Case #CFS26-161905 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>CFS26-161839</t>
+        </is>
+      </c>
+      <c r="E217" s="3" t="n">
+        <v>46231.00275462963</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Assault P3</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Assault</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>W 47TH ST &amp; S WESTPORT AVE</t>
+        </is>
+      </c>
+      <c r="J217" t="n">
+        <v>43.50940131405472</v>
+      </c>
+      <c r="K217" t="n">
+        <v>-96.76746570282992</v>
+      </c>
+      <c r="L217" t="n">
+        <v>678.4</v>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>Assault p3 on Jul 28, 2026, 678 m from Empire Mall (W 47TH ST &amp; S WESTPORT AVE). Case #CFS26-161839 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>CFS26-161599</t>
+        </is>
+      </c>
+      <c r="E218" s="3" t="n">
+        <v>46230.83100694444</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Public Assist</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>S MARION RD &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J218" t="n">
+        <v>43.51481738299845</v>
+      </c>
+      <c r="K218" t="n">
+        <v>-96.79096028032072</v>
+      </c>
+      <c r="L218" t="n">
+        <v>1322.4</v>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>Public assist on Jul 27, 2026, 1322 m from Empire Mall (S MARION RD &amp; W 41ST ST). Case #CFS26-161599 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>CFS26-161152</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="n">
+        <v>46230.51356481481</v>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Burglary Alarm</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Burglary</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>S LOUISE AVE &amp; W KENTUCKY PL</t>
+        </is>
+      </c>
+      <c r="J219" t="n">
+        <v>43.51601560446141</v>
+      </c>
+      <c r="K219" t="n">
+        <v>-96.77111077469445</v>
+      </c>
+      <c r="L219" t="n">
+        <v>737.5</v>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>Burglary alarm on Jul 27, 2026, 737 m from Empire Mall (S LOUISE AVE &amp; W KENTUCKY PL). Case #CFS26-161152 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>CFS26-161167</t>
+        </is>
+      </c>
+      <c r="E220" s="3" t="n">
+        <v>46230.53862268518</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Burglary Alarm</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Burglary</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>PARK SERVICE RD &amp; PARK SERVICE RD &amp; PARK SERVICE RD</t>
+        </is>
+      </c>
+      <c r="J220" t="n">
+        <v>43.5063858340459</v>
+      </c>
+      <c r="K220" t="n">
+        <v>-96.7618683317002</v>
+      </c>
+      <c r="L220" t="n">
+        <v>1204.2</v>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>Burglary alarm on Jul 27, 2026, 1204 m from Empire Mall (PARK SERVICE RD &amp; PARK SERVICE RD &amp; PARK SERVICE RD). Case #CFS26-161167 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>CFS26-161121</t>
+        </is>
+      </c>
+      <c r="E221" s="3" t="n">
+        <v>46230.38135416667</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Standby To Pick Up Property</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>S GATEWAY LN &amp; S GATEWAY BLVD</t>
+        </is>
+      </c>
+      <c r="J221" t="n">
+        <v>43.51281290360509</v>
+      </c>
+      <c r="K221" t="n">
+        <v>-96.7832464577892</v>
+      </c>
+      <c r="L221" t="n">
+        <v>662.9</v>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>Standby to pick up property on Jul 27, 2026, 663 m from Empire Mall (S GATEWAY LN &amp; S GATEWAY BLVD). Case #CFS26-161121 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>CFS26-161158</t>
+        </is>
+      </c>
+      <c r="E222" s="3" t="n">
+        <v>46230.52385416667</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Traffic Control</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>S OXBOW AVE &amp; W 57TH ST</t>
+        </is>
+      </c>
+      <c r="J222" t="n">
+        <v>43.50034566225657</v>
+      </c>
+      <c r="K222" t="n">
+        <v>-96.76586341187955</v>
+      </c>
+      <c r="L222" t="n">
+        <v>1367</v>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>Traffic control on Jul 27, 2026, 1367 m from Empire Mall (S OXBOW AVE &amp; W 57TH ST). Case #CFS26-161158 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>CFS26-161654</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="n">
+        <v>46230.86913194445</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Traffic Control</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>S KIWANIS AVE &amp; W 49TH ST</t>
+        </is>
+      </c>
+      <c r="J223" t="n">
+        <v>43.50841031406458</v>
+      </c>
+      <c r="K223" t="n">
+        <v>-96.75802133136874</v>
+      </c>
+      <c r="L223" t="n">
+        <v>1447.9</v>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>Traffic control on Jul 27, 2026, 1448 m from Empire Mall (S KIWANIS AVE &amp; W 49TH ST). Case #CFS26-161654 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>CFS26-161756</t>
+        </is>
+      </c>
+      <c r="E224" s="3" t="n">
+        <v>46230.94164351852</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Reckless Driver</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>S MARION RD &amp; W COTTAGE TRL</t>
+        </is>
+      </c>
+      <c r="J224" t="n">
+        <v>43.501643341026</v>
+      </c>
+      <c r="K224" t="n">
+        <v>-96.79084966877771</v>
+      </c>
+      <c r="L224" t="n">
+        <v>1551.2</v>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>Reckless driver on Jul 27, 2026, 1551 m from Empire Mall (S MARION RD &amp; W COTTAGE TRL). Case #CFS26-161756 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>CFS26-161851</t>
+        </is>
+      </c>
+      <c r="E225" s="3" t="n">
+        <v>46231.01702546296</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Accident</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>W 41ST ST &amp; W EMPIRE PL</t>
+        </is>
+      </c>
+      <c r="J225" t="n">
+        <v>43.51484419416143</v>
+      </c>
+      <c r="K225" t="n">
+        <v>-96.77669360636062</v>
+      </c>
+      <c r="L225" t="n">
+        <v>509.1</v>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>Accident on Jul 28, 2026, 509 m from Empire Mall (W 41ST ST &amp; W EMPIRE PL). Case #CFS26-161851 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>CFS26-162280</t>
+        </is>
+      </c>
+      <c r="E226" s="3" t="n">
+        <v>46231.63763888889</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Man Down</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>S LOUISE AVE &amp; W KENTUCKY PL</t>
+        </is>
+      </c>
+      <c r="J226" t="n">
+        <v>43.51601560446141</v>
+      </c>
+      <c r="K226" t="n">
+        <v>-96.77111077469445</v>
+      </c>
+      <c r="L226" t="n">
+        <v>737.5</v>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>Man down on Jul 28, 2026, 737 m from Empire Mall (S LOUISE AVE &amp; W KENTUCKY PL). Case #CFS26-162280 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>CFS26-162861</t>
+        </is>
+      </c>
+      <c r="E227" s="3" t="n">
+        <v>46232.11736111111</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Man Down</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>W ST JAMES CIR &amp; W ST JAMES DR &amp; W VICTORIA DR</t>
+        </is>
+      </c>
+      <c r="J227" t="n">
+        <v>43.50653056252924</v>
+      </c>
+      <c r="K227" t="n">
+        <v>-96.78533738843498</v>
+      </c>
+      <c r="L227" t="n">
+        <v>877.9</v>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>Man down on Jul 29, 2026, 878 m from Empire Mall (W ST JAMES CIR &amp; W ST JAMES DR &amp; W VICTORIA DR). Case #CFS26-162861 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>CFS26-162901</t>
+        </is>
+      </c>
+      <c r="E228" s="3" t="n">
+        <v>46232.16435185185</v>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Abandoned Vehicles</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>S TERRY AVE &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J228" t="n">
+        <v>43.51482816316226</v>
+      </c>
+      <c r="K228" t="n">
+        <v>-96.78634901931601</v>
+      </c>
+      <c r="L228" t="n">
+        <v>988.9</v>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>Abandoned vehicles on Jul 29, 2026, 989 m from Empire Mall (S TERRY AVE &amp; W 41ST ST). Case #CFS26-162901 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>CFS26-162736</t>
+        </is>
+      </c>
+      <c r="E229" s="3" t="n">
+        <v>46231.9900462963</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Hit &amp; Run</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>S MARION RD &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J229" t="n">
+        <v>43.51481738299845</v>
+      </c>
+      <c r="K229" t="n">
+        <v>-96.79096028032072</v>
+      </c>
+      <c r="L229" t="n">
+        <v>1322.4</v>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>Hit &amp; run on Jul 28, 2026, 1322 m from Empire Mall (S MARION RD &amp; W 41ST ST). Case #CFS26-162736 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>CFS26-162920</t>
+        </is>
+      </c>
+      <c r="E230" s="3" t="n">
+        <v>46232.18731481482</v>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Disorderly Subjects</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>W CHIPPEWA PL &amp; W CHIPPEWA CIR</t>
+        </is>
+      </c>
+      <c r="J230" t="n">
+        <v>43.50415214191399</v>
+      </c>
+      <c r="K230" t="n">
+        <v>-96.78340912722523</v>
+      </c>
+      <c r="L230" t="n">
+        <v>920.7</v>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>Disorderly subjects on Jul 29, 2026, 921 m from Empire Mall (W CHIPPEWA PL &amp; W CHIPPEWA CIR). Case #CFS26-162920 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>CFS26-162449</t>
+        </is>
+      </c>
+      <c r="E231" s="3" t="n">
+        <v>46231.78344907407</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Burglary</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Burglary</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>S MADELYN AVE &amp; W 40TH ST</t>
+        </is>
+      </c>
+      <c r="J231" t="n">
+        <v>43.51538966329255</v>
+      </c>
+      <c r="K231" t="n">
+        <v>-96.78441883878321</v>
+      </c>
+      <c r="L231" t="n">
+        <v>896.4</v>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>Burglary on Jul 28, 2026, 896 m from Empire Mall (S MADELYN AVE &amp; W 40TH ST). Case #CFS26-162449 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>CFS26-162689</t>
+        </is>
+      </c>
+      <c r="E232" s="3" t="n">
+        <v>46231.94540509259</v>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Check Wellbeing</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>S GATEWAY LN &amp; S GATEWAY BLVD</t>
+        </is>
+      </c>
+      <c r="J232" t="n">
+        <v>43.51281290360509</v>
+      </c>
+      <c r="K232" t="n">
+        <v>-96.7832464577892</v>
+      </c>
+      <c r="L232" t="n">
+        <v>662.9</v>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>Check wellbeing on Jul 28, 2026, 663 m from Empire Mall (S GATEWAY LN &amp; S GATEWAY BLVD). Case #CFS26-162689 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>CFS26-162800</t>
+        </is>
+      </c>
+      <c r="E233" s="3" t="n">
+        <v>46232.04965277778</v>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Check Wellbeing</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>S KIWANIS AVE &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J233" t="n">
+        <v>43.5148316053277</v>
+      </c>
+      <c r="K233" t="n">
+        <v>-96.76108050220627</v>
+      </c>
+      <c r="L233" t="n">
+        <v>1287.6</v>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>Check wellbeing on Jul 29, 2026, 1288 m from Empire Mall (S KIWANIS AVE &amp; W 41ST ST). Case #CFS26-162800 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>CFS26-162937</t>
+        </is>
+      </c>
+      <c r="E234" s="3" t="n">
+        <v>46232.20616898148</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Suspicious Vehicle</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>S TECHNOPOLIS DR &amp; S NEVADA AVE &amp; W 57TH ST</t>
+        </is>
+      </c>
+      <c r="J234" t="n">
+        <v>43.5003427218675</v>
+      </c>
+      <c r="K234" t="n">
+        <v>-96.77458843355284</v>
+      </c>
+      <c r="L234" t="n">
+        <v>1112.9</v>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>Suspicious vehicle on Jul 29, 2026, 1113 m from Empire Mall (S TECHNOPOLIS DR &amp; S NEVADA AVE &amp; W 57TH ST). Case #CFS26-162937 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>CFS26-162812</t>
+        </is>
+      </c>
+      <c r="E235" s="3" t="n">
+        <v>46232.06216435185</v>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Neighbor Dispute</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>S BAHA AVE &amp; W 55TH ST</t>
+        </is>
+      </c>
+      <c r="J235" t="n">
+        <v>43.50196079221673</v>
+      </c>
+      <c r="K235" t="n">
+        <v>-96.76954183339693</v>
+      </c>
+      <c r="L235" t="n">
+        <v>1056.4</v>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>Neighbor dispute on Jul 29, 2026, 1056 m from Empire Mall (S BAHA AVE &amp; W 55TH ST). Case #CFS26-162812 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>CFS26-162458</t>
+        </is>
+      </c>
+      <c r="E236" s="3" t="n">
+        <v>46231.788125</v>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Family Dispute</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>S TECHNOPOLIS DR &amp; W 53RD ST</t>
+        </is>
+      </c>
+      <c r="J236" t="n">
+        <v>43.50364750236709</v>
+      </c>
+      <c r="K236" t="n">
+        <v>-96.7753931947034</v>
+      </c>
+      <c r="L236" t="n">
+        <v>742</v>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>Family dispute on Jul 28, 2026, 742 m from Empire Mall (S TECHNOPOLIS DR &amp; W 53RD ST). Case #CFS26-162458 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>CFS26-162677</t>
+        </is>
+      </c>
+      <c r="E237" s="3" t="n">
+        <v>46231.93572916667</v>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Intoxicated Subject</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Drugs/Alcohol</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>S LOUISE AVE &amp; W KENTUCKY PL</t>
+        </is>
+      </c>
+      <c r="J237" t="n">
+        <v>43.51601560446141</v>
+      </c>
+      <c r="K237" t="n">
+        <v>-96.77111077469445</v>
+      </c>
+      <c r="L237" t="n">
+        <v>737.5</v>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>Intoxicated subject on Jul 28, 2026, 737 m from Empire Mall (S LOUISE AVE &amp; W KENTUCKY PL). Case #CFS26-162677 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>CFS26-162423</t>
+        </is>
+      </c>
+      <c r="E238" s="3" t="n">
+        <v>46231.75775462963</v>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Accident</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>S SHIRLEY AVE &amp; W SWENSON DR</t>
+        </is>
+      </c>
+      <c r="J238" t="n">
+        <v>43.52370102520238</v>
+      </c>
+      <c r="K238" t="n">
+        <v>-96.77699254769605</v>
+      </c>
+      <c r="L238" t="n">
+        <v>1491.8</v>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>Accident on Jul 28, 2026, 1492 m from Empire Mall (S SHIRLEY AVE &amp; W SWENSON DR). Case #CFS26-162423 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>CFS26-162896</t>
+        </is>
+      </c>
+      <c r="E239" s="3" t="n">
+        <v>46232.15972222222</v>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Stolen Vehicle</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Stolen Vehicles</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>S TECHNOPOLIS DR &amp; W 53RD ST</t>
+        </is>
+      </c>
+      <c r="J239" t="n">
+        <v>43.50364750236709</v>
+      </c>
+      <c r="K239" t="n">
+        <v>-96.7753931947034</v>
+      </c>
+      <c r="L239" t="n">
+        <v>742</v>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>Stolen vehicle on Jul 29, 2026, 742 m from Empire Mall (S TECHNOPOLIS DR &amp; W 53RD ST). Case #CFS26-162896 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>CFS26-162910</t>
+        </is>
+      </c>
+      <c r="E240" s="3" t="n">
+        <v>46232.17696759259</v>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Customer Dispute</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>S CAROLYN AVE &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J240" t="n">
+        <v>43.51484141407607</v>
+      </c>
+      <c r="K240" t="n">
+        <v>-96.77853636764556</v>
+      </c>
+      <c r="L240" t="n">
+        <v>550.2</v>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>Customer dispute on Jul 29, 2026, 550 m from Empire Mall (S CAROLYN AVE &amp; W 41ST ST). Case #CFS26-162910 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>CFS26-162629</t>
+        </is>
+      </c>
+      <c r="E241" s="3" t="n">
+        <v>46231.90168981482</v>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Accident</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>S LOUISE AVE &amp; W 55TH ST</t>
+        </is>
+      </c>
+      <c r="J241" t="n">
+        <v>43.50195752221772</v>
+      </c>
+      <c r="K241" t="n">
+        <v>-96.77102644399517</v>
+      </c>
+      <c r="L241" t="n">
+        <v>1005.3</v>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>Accident on Jul 28, 2026, 1005 m from Empire Mall (S LOUISE AVE &amp; W 55TH ST). Case #CFS26-162629 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>CFS26-163580</t>
+        </is>
+      </c>
+      <c r="E242" s="3" t="n">
+        <v>46232.96297453704</v>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Protection Order Violation</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>S COTTAGE CIR &amp; W ST JAMES DR</t>
+        </is>
+      </c>
+      <c r="J242" t="n">
+        <v>43.50478034152432</v>
+      </c>
+      <c r="K242" t="n">
+        <v>-96.78663732772262</v>
+      </c>
+      <c r="L242" t="n">
+        <v>1070</v>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>Protection order violation on Jul 29, 2026, 1070 m from Empire Mall (S COTTAGE CIR &amp; W ST JAMES DR). Case #CFS26-163580 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>CFS26-163692</t>
+        </is>
+      </c>
+      <c r="E243" s="3" t="n">
+        <v>46233.060625</v>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Stalled Vehicle</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>S LOUISE AVE &amp; W 59TH ST</t>
+        </is>
+      </c>
+      <c r="J243" t="n">
+        <v>43.49878851194642</v>
+      </c>
+      <c r="K243" t="n">
+        <v>-96.77094963245196</v>
+      </c>
+      <c r="L243" t="n">
+        <v>1339.6</v>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>Stalled vehicle on Jul 30, 2026, 1340 m from Empire Mall (S LOUISE AVE &amp; W 59TH ST). Case #CFS26-163692 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>CFS26-163539</t>
+        </is>
+      </c>
+      <c r="E244" s="3" t="n">
+        <v>46232.93219907407</v>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Check Wellbeing</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>S CAROLYN AVE &amp; W 38TH ST</t>
+        </is>
+      </c>
+      <c r="J244" t="n">
+        <v>43.51777966412532</v>
+      </c>
+      <c r="K244" t="n">
+        <v>-96.77850989695047</v>
+      </c>
+      <c r="L244" t="n">
+        <v>858.8</v>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>Check wellbeing on Jul 29, 2026, 859 m from Empire Mall (S CAROLYN AVE &amp; W 38TH ST). Case #CFS26-163539 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>CFS26-162972</t>
+        </is>
+      </c>
+      <c r="E245" s="3" t="n">
+        <v>46232.25686342592</v>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Intoxicated Subject</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Drugs/Alcohol</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>S MARION RD &amp; W 44TH ST</t>
+        </is>
+      </c>
+      <c r="J245" t="n">
+        <v>43.51236607235115</v>
+      </c>
+      <c r="K245" t="n">
+        <v>-96.7909260097226</v>
+      </c>
+      <c r="L245" t="n">
+        <v>1242.3</v>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>Intoxicated subject on Jul 29, 2026, 1242 m from Empire Mall (S MARION RD &amp; W 44TH ST). Case #CFS26-162972 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>CFS26-163689</t>
+        </is>
+      </c>
+      <c r="E246" s="3" t="n">
+        <v>46233.05902777778</v>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Injury Accident P3</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>W 41ST ST &amp; W EMPIRE PL</t>
+        </is>
+      </c>
+      <c r="J246" t="n">
+        <v>43.51484419416143</v>
+      </c>
+      <c r="K246" t="n">
+        <v>-96.77669360636062</v>
+      </c>
+      <c r="L246" t="n">
+        <v>509.1</v>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>Injury accident p3 on Jul 30, 2026, 509 m from Empire Mall (W 41ST ST &amp; W EMPIRE PL). Case #CFS26-163689 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>CFS26-162985</t>
+        </is>
+      </c>
+      <c r="E247" s="3" t="n">
+        <v>46232.27642361111</v>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Disorderly Subjects</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>S SHIRLEY AVE &amp; W SHIRLEY PL</t>
+        </is>
+      </c>
+      <c r="J247" t="n">
+        <v>43.51586590399282</v>
+      </c>
+      <c r="K247" t="n">
+        <v>-96.77448526595956</v>
+      </c>
+      <c r="L247" t="n">
+        <v>626.1</v>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>Disorderly subjects on Jul 29, 2026, 626 m from Empire Mall (S SHIRLEY AVE &amp; W SHIRLEY PL). Case #CFS26-162985 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>CFS26-163675</t>
+        </is>
+      </c>
+      <c r="E248" s="3" t="n">
+        <v>46233.04778935185</v>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Disorderly Subjects</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>S MADELYN AVE &amp; W 40TH ST</t>
+        </is>
+      </c>
+      <c r="J248" t="n">
+        <v>43.51538966329255</v>
+      </c>
+      <c r="K248" t="n">
+        <v>-96.78441883878321</v>
+      </c>
+      <c r="L248" t="n">
+        <v>896.4</v>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>Disorderly subjects on Jul 30, 2026, 896 m from Empire Mall (S MADELYN AVE &amp; W 40TH ST). Case #CFS26-163675 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>CFS26-163782</t>
+        </is>
+      </c>
+      <c r="E249" s="3" t="n">
+        <v>46233.15675925926</v>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Disorderly Subjects</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>S MADELYN AVE &amp; W 40TH ST</t>
+        </is>
+      </c>
+      <c r="J249" t="n">
+        <v>43.51538966329255</v>
+      </c>
+      <c r="K249" t="n">
+        <v>-96.78441883878321</v>
+      </c>
+      <c r="L249" t="n">
+        <v>896.4</v>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>Disorderly subjects on Jul 30, 2026, 896 m from Empire Mall (S MADELYN AVE &amp; W 40TH ST). Case #CFS26-163782 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>CFS26-163779</t>
+        </is>
+      </c>
+      <c r="E250" s="3" t="n">
+        <v>46233.15428240741</v>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Disorderly Subjects</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>S TECHNOPOLIS DR &amp; W 53RD ST</t>
+        </is>
+      </c>
+      <c r="J250" t="n">
+        <v>43.50364750236709</v>
+      </c>
+      <c r="K250" t="n">
+        <v>-96.7753931947034</v>
+      </c>
+      <c r="L250" t="n">
+        <v>742</v>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>Disorderly subjects on Jul 30, 2026, 742 m from Empire Mall (S TECHNOPOLIS DR &amp; W 53RD ST). Case #CFS26-163779 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>CFS26-163772</t>
+        </is>
+      </c>
+      <c r="E251" s="3" t="n">
+        <v>46233.1472337963</v>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Disorderly Subjects</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>S WESTPORT AVE &amp; W 43RD ST</t>
+        </is>
+      </c>
+      <c r="J251" t="n">
+        <v>43.5130372443594</v>
+      </c>
+      <c r="K251" t="n">
+        <v>-96.76793865443652</v>
+      </c>
+      <c r="L251" t="n">
+        <v>701.3</v>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>Disorderly subjects on Jul 30, 2026, 701 m from Empire Mall (S WESTPORT AVE &amp; W 43RD ST). Case #CFS26-163772 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>CFS26-163815</t>
+        </is>
+      </c>
+      <c r="E252" s="3" t="n">
+        <v>46233.19416666667</v>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Disorderly Phone Calls</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>W CHIPPEWA PL &amp; W CHIPPEWA CIR</t>
+        </is>
+      </c>
+      <c r="J252" t="n">
+        <v>43.50415214191399</v>
+      </c>
+      <c r="K252" t="n">
+        <v>-96.78340912722523</v>
+      </c>
+      <c r="L252" t="n">
+        <v>920.7</v>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>Disorderly phone calls on Jul 30, 2026, 921 m from Empire Mall (W CHIPPEWA PL &amp; W CHIPPEWA CIR). Case #CFS26-163815 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>CFS26-163515</t>
+        </is>
+      </c>
+      <c r="E253" s="3" t="n">
+        <v>46232.92128472222</v>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Accident</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>S SHIRLEY AVE &amp; W 38TH ST</t>
+        </is>
+      </c>
+      <c r="J253" t="n">
+        <v>43.51777845484326</v>
+      </c>
+      <c r="K253" t="n">
+        <v>-96.77437979679537</v>
+      </c>
+      <c r="L253" t="n">
+        <v>837.7</v>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>Accident on Jul 29, 2026, 838 m from Empire Mall (S SHIRLEY AVE &amp; W 38TH ST). Case #CFS26-163515 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>CFS26-163812</t>
+        </is>
+      </c>
+      <c r="E254" s="3" t="n">
+        <v>46233.19130787037</v>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Suspicious Vehicle</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>S LARCH AVE &amp; W 43RD ST</t>
+        </is>
+      </c>
+      <c r="J254" t="n">
+        <v>43.51319846254545</v>
+      </c>
+      <c r="K254" t="n">
+        <v>-96.79336119066248</v>
+      </c>
+      <c r="L254" t="n">
+        <v>1453.4</v>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>Suspicious vehicle on Jul 30, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-163812 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>CFS26-163677</t>
+        </is>
+      </c>
+      <c r="E255" s="3" t="n">
+        <v>46233.04851851852</v>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Customer Dispute</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>S LOUISE AVE &amp; W KENTUCKY PL</t>
+        </is>
+      </c>
+      <c r="J255" t="n">
+        <v>43.51601560446141</v>
+      </c>
+      <c r="K255" t="n">
+        <v>-96.77111077469445</v>
+      </c>
+      <c r="L255" t="n">
+        <v>737.5</v>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>Customer dispute on Jul 30, 2026, 737 m from Empire Mall (S LOUISE AVE &amp; W KENTUCKY PL). Case #CFS26-163677 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>CFS26-163900</t>
+        </is>
+      </c>
+      <c r="E256" s="3" t="n">
+        <v>46233.38151620371</v>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Burglary Alarm</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Burglary</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>S BUR OAK PL &amp; W 57TH ST</t>
+        </is>
+      </c>
+      <c r="J256" t="n">
+        <v>43.5003453731365</v>
+      </c>
+      <c r="K256" t="n">
+        <v>-96.76225601111084</v>
+      </c>
+      <c r="L256" t="n">
+        <v>1555.3</v>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>Burglary alarm on Jul 30, 2026, 1555 m from Empire Mall (S BUR OAK PL &amp; W 57TH ST). Case #CFS26-163900 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>CFS26-164551</t>
+        </is>
+      </c>
+      <c r="E257" s="3" t="n">
+        <v>46234.08541666667</v>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Check Wellbeing</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>S GATEWAY BLVD &amp; S MADELYN AVE &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J257" t="n">
+        <v>43.51483006334468</v>
+      </c>
+      <c r="K257" t="n">
+        <v>-96.78442152875238</v>
+      </c>
+      <c r="L257" t="n">
+        <v>858.8</v>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>Check wellbeing on Jul 31, 2026, 859 m from Empire Mall (S GATEWAY BLVD &amp; S MADELYN AVE &amp; W 41ST ST). Case #CFS26-164551 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>CFS26-164565</t>
+        </is>
+      </c>
+      <c r="E258" s="3" t="n">
+        <v>46234.09699074074</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Check Wellbeing</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>S LOUISE AVE &amp; W 43RD ST &amp; W EMPIRE PL</t>
+        </is>
+      </c>
+      <c r="J258" t="n">
+        <v>43.51305131378995</v>
+      </c>
+      <c r="K258" t="n">
+        <v>-96.77107093496716</v>
+      </c>
+      <c r="L258" t="n">
+        <v>486.8</v>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>Check wellbeing on Jul 31, 2026, 487 m from Empire Mall (S LOUISE AVE &amp; W 43RD ST &amp; W EMPIRE PL). Case #CFS26-164565 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>CFS26-164420</t>
+        </is>
+      </c>
+      <c r="E259" s="3" t="n">
+        <v>46233.95097222222</v>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Check Wellbeing</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>S GATEWAY LN &amp; S GATEWAY BLVD</t>
+        </is>
+      </c>
+      <c r="J259" t="n">
+        <v>43.51281290360509</v>
+      </c>
+      <c r="K259" t="n">
+        <v>-96.7832464577892</v>
+      </c>
+      <c r="L259" t="n">
+        <v>662.9</v>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>Check wellbeing on Jul 30, 2026, 663 m from Empire Mall (S GATEWAY LN &amp; S GATEWAY BLVD). Case #CFS26-164420 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>CFS26-163938</t>
+        </is>
+      </c>
+      <c r="E260" s="3" t="n">
+        <v>46233.51668981482</v>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Intoxicated Subject</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>Drugs/Alcohol</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>S SHIRLEY AVE &amp; W 38TH ST</t>
+        </is>
+      </c>
+      <c r="J260" t="n">
+        <v>43.51777845484326</v>
+      </c>
+      <c r="K260" t="n">
+        <v>-96.77437979679537</v>
+      </c>
+      <c r="L260" t="n">
+        <v>837.7</v>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>Intoxicated subject on Jul 30, 2026, 838 m from Empire Mall (S SHIRLEY AVE &amp; W 38TH ST). Case #CFS26-163938 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>CFS26-164198</t>
+        </is>
+      </c>
+      <c r="E261" s="3" t="n">
+        <v>46233.79908564815</v>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Check Wellbeing</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>S SHIRLEY AVE &amp; W 38TH ST</t>
+        </is>
+      </c>
+      <c r="J261" t="n">
+        <v>43.51777845484326</v>
+      </c>
+      <c r="K261" t="n">
+        <v>-96.77437979679537</v>
+      </c>
+      <c r="L261" t="n">
+        <v>837.7</v>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>Check wellbeing on Jul 30, 2026, 838 m from Empire Mall (S SHIRLEY AVE &amp; W 38TH ST). Case #CFS26-164198 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>CFS26-164532</t>
+        </is>
+      </c>
+      <c r="E262" s="3" t="n">
+        <v>46234.05094907407</v>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Disorderly Phone Calls</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>W 56TH ST &amp; W CREEKSIDE CIR &amp; W CREEKSIDE DR</t>
+        </is>
+      </c>
+      <c r="J262" t="n">
+        <v>43.50145532175087</v>
+      </c>
+      <c r="K262" t="n">
+        <v>-96.77903768516548</v>
+      </c>
+      <c r="L262" t="n">
+        <v>1019.4</v>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>Disorderly phone calls on Jul 31, 2026, 1019 m from Empire Mall (W 56TH ST &amp; W CREEKSIDE CIR &amp; W CREEKSIDE DR). Case #CFS26-164532 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>CFS26-164458</t>
+        </is>
+      </c>
+      <c r="E263" s="3" t="n">
+        <v>46233.97483796296</v>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Family Dispute</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>S LARCH AVE &amp; W 43RD ST</t>
+        </is>
+      </c>
+      <c r="J263" t="n">
+        <v>43.51319846254545</v>
+      </c>
+      <c r="K263" t="n">
+        <v>-96.79336119066248</v>
+      </c>
+      <c r="L263" t="n">
+        <v>1453.4</v>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>Family dispute on Jul 30, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-164458 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>CFS26-164034</t>
+        </is>
+      </c>
+      <c r="E264" s="3" t="n">
+        <v>46233.6452199074</v>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Abandoned Vehicles</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>S GATEWAY LN &amp; S GATEWAY BLVD</t>
+        </is>
+      </c>
+      <c r="J264" t="n">
+        <v>43.51281290360509</v>
+      </c>
+      <c r="K264" t="n">
+        <v>-96.7832464577892</v>
+      </c>
+      <c r="L264" t="n">
+        <v>662.9</v>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>Abandoned vehicles on Jul 30, 2026, 663 m from Empire Mall (S GATEWAY LN &amp; S GATEWAY BLVD). Case #CFS26-164034 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>CFS26-164393</t>
+        </is>
+      </c>
+      <c r="E265" s="3" t="n">
+        <v>46233.93733796296</v>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Assault</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Assault</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>S LARCH AVE &amp; W 43RD ST</t>
+        </is>
+      </c>
+      <c r="J265" t="n">
+        <v>43.51319846254545</v>
+      </c>
+      <c r="K265" t="n">
+        <v>-96.79336119066248</v>
+      </c>
+      <c r="L265" t="n">
+        <v>1453.4</v>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>Assault on Jul 30, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-164393 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>CFS26-163932</t>
+        </is>
+      </c>
+      <c r="E266" s="3" t="n">
+        <v>46233.4896875</v>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Larceny</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Theft</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>S GATEWAY BLVD &amp; S TERRY AVE</t>
+        </is>
+      </c>
+      <c r="J266" t="n">
+        <v>43.51220536263347</v>
+      </c>
+      <c r="K266" t="n">
+        <v>-96.7859525684798</v>
+      </c>
+      <c r="L266" t="n">
+        <v>846.7</v>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>Larceny on Jul 30, 2026, 847 m from Empire Mall (S GATEWAY BLVD &amp; S TERRY AVE). Case #CFS26-163932 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>CFS26-164418</t>
+        </is>
+      </c>
+      <c r="E267" s="3" t="n">
+        <v>46233.94917824074</v>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Accident</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>S SHIRLEY AVE &amp; W 38TH ST</t>
+        </is>
+      </c>
+      <c r="J267" t="n">
+        <v>43.51777845484326</v>
+      </c>
+      <c r="K267" t="n">
+        <v>-96.77437979679537</v>
+      </c>
+      <c r="L267" t="n">
+        <v>837.7</v>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>Accident on Jul 30, 2026, 838 m from Empire Mall (S SHIRLEY AVE &amp; W 38TH ST). Case #CFS26-164418 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>CFS26-164353</t>
+        </is>
+      </c>
+      <c r="E268" s="3" t="n">
+        <v>46233.91128472222</v>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Accident</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>S LOUISE AVE &amp; W 49TH ST</t>
+        </is>
+      </c>
+      <c r="J268" t="n">
+        <v>43.50759974361088</v>
+      </c>
+      <c r="K268" t="n">
+        <v>-96.77103685388698</v>
+      </c>
+      <c r="L268" t="n">
+        <v>487.4</v>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>Accident on Jul 30, 2026, 487 m from Empire Mall (S LOUISE AVE &amp; W 49TH ST). Case #CFS26-164353 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>CFS26-164234</t>
+        </is>
+      </c>
+      <c r="E269" s="3" t="n">
+        <v>46233.82494212963</v>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Accident</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>S MARION RD &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J269" t="n">
+        <v>43.51481738299845</v>
+      </c>
+      <c r="K269" t="n">
+        <v>-96.79096028032072</v>
+      </c>
+      <c r="L269" t="n">
+        <v>1322.4</v>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>Accident on Jul 30, 2026, 1322 m from Empire Mall (S MARION RD &amp; W 41ST ST). Case #CFS26-164234 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>CFS26-163978</t>
+        </is>
+      </c>
+      <c r="E270" s="3" t="n">
+        <v>46233.59060185185</v>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Accident</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>S KIWANIS AVE &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J270" t="n">
+        <v>43.5148316053277</v>
+      </c>
+      <c r="K270" t="n">
+        <v>-96.76108050220627</v>
+      </c>
+      <c r="L270" t="n">
+        <v>1287.6</v>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>Accident on Jul 30, 2026, 1288 m from Empire Mall (S KIWANIS AVE &amp; W 41ST ST). Case #CFS26-163978 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>CFS26-164089</t>
+        </is>
+      </c>
+      <c r="E271" s="3" t="n">
+        <v>46233.70215277778</v>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Accident</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>S LOUISE AVE &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J271" t="n">
+        <v>43.51480707435041</v>
+      </c>
+      <c r="K271" t="n">
+        <v>-96.77110350565825</v>
+      </c>
+      <c r="L271" t="n">
+        <v>626.1</v>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>Accident on Jul 30, 2026, 626 m from Empire Mall (S LOUISE AVE &amp; W 41ST ST). Case #CFS26-164089 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>CFS26-164075</t>
+        </is>
+      </c>
+      <c r="E272" s="3" t="n">
+        <v>46233.69127314815</v>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Suspicious Subject</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>S KIWANIS AVE &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J272" t="n">
+        <v>43.5148316053277</v>
+      </c>
+      <c r="K272" t="n">
+        <v>-96.76108050220627</v>
+      </c>
+      <c r="L272" t="n">
+        <v>1287.6</v>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>Suspicious subject on Jul 30, 2026, 1288 m from Empire Mall (S KIWANIS AVE &amp; W 41ST ST). Case #CFS26-164075 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>CFS26-164113</t>
+        </is>
+      </c>
+      <c r="E273" s="3" t="n">
+        <v>46233.72401620371</v>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Disorderly Subjects</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>S LOUISE AVE &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J273" t="n">
+        <v>43.51480707435041</v>
+      </c>
+      <c r="K273" t="n">
+        <v>-96.77110350565825</v>
+      </c>
+      <c r="L273" t="n">
+        <v>626.1</v>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>Disorderly subjects on Jul 30, 2026, 626 m from Empire Mall (S LOUISE AVE &amp; W 41ST ST). Case #CFS26-164113 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>CFS26-164293</t>
+        </is>
+      </c>
+      <c r="E274" s="3" t="n">
+        <v>46233.87532407408</v>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Disorderly Subjects</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>W EMPIRE PL &amp; W EMPIRE PL &amp; W EMPIRE PL</t>
+        </is>
+      </c>
+      <c r="J274" t="n">
+        <v>43.51307477335324</v>
+      </c>
+      <c r="K274" t="n">
+        <v>-96.7766862668114</v>
+      </c>
+      <c r="L274" t="n">
+        <v>315.5</v>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>Disorderly subjects on Jul 30, 2026, 316 m from Empire Mall (W EMPIRE PL &amp; W EMPIRE PL &amp; W EMPIRE PL). Case #CFS26-164293 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>CFS26-164668</t>
+        </is>
+      </c>
+      <c r="E275" s="3" t="n">
+        <v>46234.24527777778</v>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Disorderly Subjects</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>S GATEWAY LN &amp; S GATEWAY BLVD</t>
+        </is>
+      </c>
+      <c r="J275" t="n">
+        <v>43.51281290360509</v>
+      </c>
+      <c r="K275" t="n">
+        <v>-96.7832464577892</v>
+      </c>
+      <c r="L275" t="n">
+        <v>662.9</v>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>Disorderly subjects on Jul 31, 2026, 663 m from Empire Mall (S GATEWAY LN &amp; S GATEWAY BLVD). Case #CFS26-164668 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>CFS26-164564</t>
+        </is>
+      </c>
+      <c r="E276" s="3" t="n">
+        <v>46234.09667824074</v>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Found Child</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>S LOUISE AVE &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J276" t="n">
+        <v>43.51480707435041</v>
+      </c>
+      <c r="K276" t="n">
+        <v>-96.77110350565825</v>
+      </c>
+      <c r="L276" t="n">
+        <v>626.1</v>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>Found child on Jul 31, 2026, 626 m from Empire Mall (S LOUISE AVE &amp; W 41ST ST). Case #CFS26-164564 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>CFS26-164621</t>
+        </is>
+      </c>
+      <c r="E277" s="3" t="n">
+        <v>46234.17833333334</v>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Noise Disturbance</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>S SOLBERG AVE &amp; W CHIPPEWA CIR</t>
+        </is>
+      </c>
+      <c r="J277" t="n">
+        <v>43.50469043243786</v>
+      </c>
+      <c r="K277" t="n">
+        <v>-96.7809382470065</v>
+      </c>
+      <c r="L277" t="n">
+        <v>750.9</v>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>Noise disturbance on Jul 31, 2026, 751 m from Empire Mall (S SOLBERG AVE &amp; W CHIPPEWA CIR). Case #CFS26-164621 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>CFS26-164170</t>
+        </is>
+      </c>
+      <c r="E278" s="3" t="n">
+        <v>46233.77346064815</v>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Suspicious Subject</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>W EMPIRE PL &amp; W EMPIRE PL &amp; W EMPIRE PL</t>
+        </is>
+      </c>
+      <c r="J278" t="n">
+        <v>43.51307477335324</v>
+      </c>
+      <c r="K278" t="n">
+        <v>-96.7766862668114</v>
+      </c>
+      <c r="L278" t="n">
+        <v>315.5</v>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>Suspicious subject on Jul 30, 2026, 316 m from Empire Mall (W EMPIRE PL &amp; W EMPIRE PL &amp; W EMPIRE PL). Case #CFS26-164170 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>CFS26-164521</t>
+        </is>
+      </c>
+      <c r="E279" s="3" t="n">
+        <v>46234.03421296296</v>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Aggravated Assault</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>Assault</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>S MARION RD &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J279" t="n">
+        <v>43.51481738299845</v>
+      </c>
+      <c r="K279" t="n">
+        <v>-96.79096028032072</v>
+      </c>
+      <c r="L279" t="n">
+        <v>1322.4</v>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>Aggravated assault on Jul 31, 2026, 1322 m from Empire Mall (S MARION RD &amp; W 41ST ST). Case #CFS26-164521 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>CFS26-163988</t>
+        </is>
+      </c>
+      <c r="E280" s="3" t="n">
+        <v>46233.60233796296</v>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Found Property</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>S GATEWAY LN &amp; S GATEWAY BLVD</t>
+        </is>
+      </c>
+      <c r="J280" t="n">
+        <v>43.51281290360509</v>
+      </c>
+      <c r="K280" t="n">
+        <v>-96.7832464577892</v>
+      </c>
+      <c r="L280" t="n">
+        <v>662.9</v>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>Found property on Jul 30, 2026, 663 m from Empire Mall (S GATEWAY LN &amp; S GATEWAY BLVD). Case #CFS26-163988 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>CFS26-164120</t>
+        </is>
+      </c>
+      <c r="E281" s="3" t="n">
+        <v>46233.72950231482</v>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Man Down</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>S LOUISE AVE &amp; W KENTUCKY PL</t>
+        </is>
+      </c>
+      <c r="J281" t="n">
+        <v>43.51601560446141</v>
+      </c>
+      <c r="K281" t="n">
+        <v>-96.77111077469445</v>
+      </c>
+      <c r="L281" t="n">
+        <v>737.5</v>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>Man down on Jul 30, 2026, 737 m from Empire Mall (S LOUISE AVE &amp; W KENTUCKY PL). Case #CFS26-164120 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>CFS26-164224</t>
+        </is>
+      </c>
+      <c r="E282" s="3" t="n">
+        <v>46233.81635416667</v>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Man Down</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>S LOUISE AVE &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J282" t="n">
+        <v>43.51480707435041</v>
+      </c>
+      <c r="K282" t="n">
+        <v>-96.77110350565825</v>
+      </c>
+      <c r="L282" t="n">
+        <v>626.1</v>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>Man down on Jul 30, 2026, 626 m from Empire Mall (S LOUISE AVE &amp; W 41ST ST). Case #CFS26-164224 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>CFS26-163961</t>
+        </is>
+      </c>
+      <c r="E283" s="3" t="n">
+        <v>46233.55917824074</v>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Man Down</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>S OXBOW AVE &amp; W 49TH ST</t>
+        </is>
+      </c>
+      <c r="J283" t="n">
+        <v>43.50760687329769</v>
+      </c>
+      <c r="K283" t="n">
+        <v>-96.76591290307073</v>
+      </c>
+      <c r="L283" t="n">
+        <v>851</v>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>Man down on Jul 30, 2026, 851 m from Empire Mall (S OXBOW AVE &amp; W 49TH ST). Case #CFS26-163961 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>CFS26-163882</t>
+        </is>
+      </c>
+      <c r="E284" s="3" t="n">
+        <v>46233.329375</v>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Man Down</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>S RACKET DR &amp; W 49TH ST</t>
+        </is>
+      </c>
+      <c r="J284" t="n">
+        <v>43.50761161336476</v>
+      </c>
+      <c r="K284" t="n">
+        <v>-96.76881681294817</v>
+      </c>
+      <c r="L284" t="n">
+        <v>637.1</v>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>Man down on Jul 30, 2026, 637 m from Empire Mall (S RACKET DR &amp; W 49TH ST). Case #CFS26-163882 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>CFS26-164060</t>
+        </is>
+      </c>
+      <c r="E285" s="3" t="n">
+        <v>46233.67805555555</v>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Suspicious Vehicle</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>W CHIPPEWA PL &amp; W CHIPPEWA CIR</t>
+        </is>
+      </c>
+      <c r="J285" t="n">
+        <v>43.50415214191399</v>
+      </c>
+      <c r="K285" t="n">
+        <v>-96.78340912722523</v>
+      </c>
+      <c r="L285" t="n">
+        <v>920.7</v>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>Suspicious vehicle on Jul 30, 2026, 921 m from Empire Mall (W CHIPPEWA PL &amp; W CHIPPEWA CIR). Case #CFS26-164060 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M161"/>
+  <autoFilter ref="A1:M285"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12185,7 +19677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="51" customWidth="1" min="1" max="1"/>
@@ -12212,7 +19704,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01 04:21:05.180533+00:00</t>
+          <t>2026-08-01 04:22:40.060082+00:00</t>
         </is>
       </c>
     </row>
@@ -12244,7 +19736,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-25 04:21:05.180533+00:00</t>
+          <t>2026-07-25 04:22:40.060082+00:00</t>
         </is>
       </c>
     </row>
@@ -12255,7 +19747,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>160</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7">
@@ -12265,7 +19757,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -12472,8 +19964,56 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>source:CLEARFORK/Fort Worth PD Crime Data</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>OK fetched=1 truncated=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>source:UNIVPARKVILLAGE/Fort Worth PD Crime Data</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>OK fetched=0 truncated=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>source:EMPIRE/Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>OK fetched=123 truncated=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>source:MALLATMILLENIA/Orlando PD Crimes</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>OK fetched=0 truncated=False</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B24"/>
+  <autoFilter ref="A1:B28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/latest/blotter_report.xlsx
+++ b/reports/latest/blotter_report.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Run Metadata" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Highlights'!$A$1:$M$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$285</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$28</definedName>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -655,45 +655,41 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CHARLOTTE</t>
+          <t>CASTLETON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Charlotte Premium Outlets</t>
+          <t>Castleton Square</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5404 New Fashion Way Charlotte NC 28278</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>6020 East 82nd Street Indianapolis IN 46250</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>NO COVERAGE</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>232.6</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>46233.16666666666</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="b">
         <v>0</v>
       </c>
@@ -701,17 +697,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>CHARLOTTE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Charlotte Premium Outlets</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3000 East 1st Avenue, Denver CO 80206</t>
+          <t>5404 New Fashion Way Charlotte NC 28278</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -720,25 +716,25 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>12</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>144.7</v>
+        <v>232.6</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>46231.83333333334</v>
+        <v>46233.16666666666</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
@@ -747,17 +743,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CLEARFORK</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Shops at Clearfork</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5188 Monahans Avenue Fort Worth TX 76109</t>
+          <t>3000 East 1st Avenue, Denver CO 80206</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -766,25 +762,25 @@
         </is>
       </c>
       <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>1086.4</v>
+        <v>144.7</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>46228.59375</v>
+        <v>46231.83333333334</v>
       </c>
       <c r="L7" t="b">
         <v>0</v>
@@ -793,17 +789,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>CLEARFORK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Empire Mall</t>
+          <t>The Shops at Clearfork</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5000 Empire Mall Sioux Falls SD 57106</t>
+          <t>5188 Monahans Avenue Fort Worth TX 76109</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -812,25 +808,25 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>123</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>315.5</v>
+        <v>1086.4</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>46234.24527777778</v>
+        <v>46228.59375</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
@@ -839,17 +835,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GREENHILLS</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Mall at Green Hills</t>
+          <t>Empire Mall</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2126 Abbott Martin Road, Nashville, TN 37215</t>
+          <t>5000 Empire Mall Sioux Falls SD 57106</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -858,22 +854,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
+        <v>123</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+        <v>79</v>
+      </c>
+      <c r="J9" t="n">
+        <v>315.5</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>46234.24527777778</v>
+      </c>
       <c r="L9" t="b">
         <v>0</v>
       </c>
@@ -881,17 +881,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>GREENHILLS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>The Mall at Green Hills</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5085 Westheimer Houston TX 77056</t>
+          <t>2126 Abbott Martin Road, Nashville, TN 37215</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -900,26 +900,22 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>57</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>163.5</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>46233</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="b">
         <v>0</v>
       </c>
@@ -927,17 +923,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>INTLPLAZA</t>
+          <t>HOUSTONGAL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>International Plaza</t>
+          <t>Houston Galleria</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2223 North West Shore Boulevard Tampa FL 33607</t>
+          <t>5085 Westheimer Houston TX 77056</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -946,25 +942,25 @@
         </is>
       </c>
       <c r="E11" t="n">
+        <v>57</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>43</v>
+      </c>
+      <c r="H11" t="n">
         <v>1</v>
       </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J11" t="n">
-        <v>1534.5</v>
+        <v>163.5</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>46232.16666666666</v>
+        <v>46233</v>
       </c>
       <c r="L11" t="b">
         <v>0</v>
@@ -973,32 +969,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LENOX</t>
+          <t>INTLPLAZA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lenox Square</t>
+          <t>International Plaza</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3393 Peachtree Road Northeast Atlanta GA 30326</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>NO COVERAGE</t>
+          <t>2223 North West Shore Boulevard Tampa FL 33607</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1006,8 +1002,12 @@
       <c r="I12" t="n">
         <v>0</v>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="J12" t="n">
+        <v>1534.5</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>46232.16666666666</v>
+      </c>
       <c r="L12" t="b">
         <v>0</v>
       </c>
@@ -1015,22 +1015,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MALLATMILLENIA</t>
+          <t>LENOX</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Mall at Millenia</t>
+          <t>Lenox Square</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4200 Conroy Road, Orlando, FL 32839</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>3393 Peachtree Road Northeast Atlanta GA 30326</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>NO COVERAGE</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1057,17 +1057,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>MALLATMILLENIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>The Mall at Millenia</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>401 Northeast Northgate Way Seattle WA 98125</t>
+          <t>4200 Conroy Road, Orlando, FL 32839</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1076,26 +1076,22 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>14</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" t="n">
-        <v>145.2</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>46233.28194444445</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="b">
         <v>0</v>
       </c>
@@ -1103,17 +1099,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>433 Opry Mills Drive Nashville TN 37214</t>
+          <t>401 Northeast Northgate Way Seattle WA 98125</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1122,22 +1118,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>145.2</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>46233.28194444445</v>
+      </c>
       <c r="L15" t="b">
         <v>0</v>
       </c>
@@ -1145,17 +1145,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>OPRYMILLS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Opry Mills</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4400 Sharon Road Charlotte NC 28211</t>
+          <t>433 Opry Mills Drive Nashville TN 37214</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1164,26 +1164,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>7</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>178.9</v>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>46232.16666666666</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="b">
         <v>0</v>
       </c>
@@ -1191,17 +1187,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4502 South Steele Street Tacoma WA 98409</t>
+          <t>4400 Sharon Road Charlotte NC 28211</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1210,25 +1206,25 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>471.3</v>
+        <v>178.9</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>46233</v>
+        <v>46232.16666666666</v>
       </c>
       <c r="L17" t="b">
         <v>0</v>
@@ -1237,41 +1233,45 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>THEDOMAIN</t>
+          <t>TACOMAMALL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Domain</t>
+          <t>Tacoma Mall</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>11410 Century Oaks Terrace Austin TX 78758</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>NO COVERAGE</t>
+          <t>4502 South Steele Street Tacoma WA 98409</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>471.3</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>46233</v>
+      </c>
       <c r="L18" t="b">
         <v>0</v>
       </c>
@@ -1279,45 +1279,41 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>THEDOMAIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>The Domain</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>7700 East Kellogg Wichita KS 67207</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>11410 Century Oaks Terrace Austin TX 78758</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>NO COVERAGE</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>33</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>23</v>
-      </c>
-      <c r="J19" t="n">
-        <v>288.9</v>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>46233.7625</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="b">
         <v>0</v>
       </c>
@@ -1325,17 +1321,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UNIVPARKVILLAGE</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>University Park Village</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1612 South University Drive Fort Worth TX 76107</t>
+          <t>7700 East Kellogg Wichita KS 67207</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1344,28 +1340,74 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="J20" t="n">
+        <v>288.9</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>46233.7625</v>
+      </c>
       <c r="L20" t="b">
         <v>0</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>UNIVPARKVILLAGE</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>University Park Village</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1612 South University Drive Fort Worth TX 76107</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L20"/>
+  <autoFilter ref="A1:L21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19704,7 +19746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01 04:22:40.060082+00:00</t>
+          <t>2026-08-01 04:25:02.895488+00:00</t>
         </is>
       </c>
     </row>
@@ -19736,7 +19778,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-25 04:22:40.060082+00:00</t>
+          <t>2026-07-25 04:25:02.895488+00:00</t>
         </is>
       </c>
     </row>
@@ -19768,7 +19810,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LENOX, THEDOMAIN</t>
+          <t>CASTLETON, LENOX, THEDOMAIN</t>
         </is>
       </c>
     </row>

--- a/reports/latest/blotter_report.xlsx
+++ b/reports/latest/blotter_report.xlsx
@@ -19746,7 +19746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01 04:25:02.895488+00:00</t>
+          <t>2026-08-01 04:32:25.991636+00:00</t>
         </is>
       </c>
     </row>
@@ -19778,7 +19778,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-25 04:25:02.895488+00:00</t>
+          <t>2026-07-25 04:32:25.991636+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/latest/blotter_report.xlsx
+++ b/reports/latest/blotter_report.xlsx
@@ -13,10 +13,10 @@
     <sheet name="Run Metadata" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Highlights'!$A$1:$M$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$285</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$286</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -789,17 +789,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CLEARFORK</t>
+          <t>CLARKSBURG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Shops at Clearfork</t>
+          <t>Clarksburg Premium Outlets</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5188 Monahans Avenue Fort Worth TX 76109</t>
+          <t>22705 Clarksburg Rd Clarksburg MD 20871</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -814,19 +814,19 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>1086.4</v>
+        <v>1135.3</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>46228.59375</v>
+        <v>46232.38263888889</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
@@ -835,17 +835,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>CLEARFORK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Empire Mall</t>
+          <t>The Shops at Clearfork</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5000 Empire Mall Sioux Falls SD 57106</t>
+          <t>5188 Monahans Avenue Fort Worth TX 76109</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -854,25 +854,25 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>123</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>315.5</v>
+        <v>1086.4</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>46234.24527777778</v>
+        <v>46228.59375</v>
       </c>
       <c r="L9" t="b">
         <v>0</v>
@@ -881,17 +881,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GREENHILLS</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Mall at Green Hills</t>
+          <t>Empire Mall</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2126 Abbott Martin Road, Nashville, TN 37215</t>
+          <t>5000 Empire Mall Sioux Falls SD 57106</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -900,22 +900,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
+        <v>123</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+        <v>79</v>
+      </c>
+      <c r="J10" t="n">
+        <v>315.5</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>46234.24527777778</v>
+      </c>
       <c r="L10" t="b">
         <v>0</v>
       </c>
@@ -923,17 +927,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>GREENHILLS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>The Mall at Green Hills</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5085 Westheimer Houston TX 77056</t>
+          <t>2126 Abbott Martin Road, Nashville, TN 37215</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -942,26 +946,22 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>57</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>163.5</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>46233</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="b">
         <v>0</v>
       </c>
@@ -969,17 +969,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>INTLPLAZA</t>
+          <t>HOUSTONGAL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>International Plaza</t>
+          <t>Houston Galleria</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2223 North West Shore Boulevard Tampa FL 33607</t>
+          <t>5085 Westheimer Houston TX 77056</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -988,25 +988,25 @@
         </is>
       </c>
       <c r="E12" t="n">
+        <v>57</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" t="n">
+        <v>43</v>
+      </c>
+      <c r="H12" t="n">
         <v>1</v>
       </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J12" t="n">
-        <v>1534.5</v>
+        <v>163.5</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>46232.16666666666</v>
+        <v>46233</v>
       </c>
       <c r="L12" t="b">
         <v>0</v>
@@ -1015,32 +1015,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LENOX</t>
+          <t>INTLPLAZA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lenox Square</t>
+          <t>International Plaza</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3393 Peachtree Road Northeast Atlanta GA 30326</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>NO COVERAGE</t>
+          <t>2223 North West Shore Boulevard Tampa FL 33607</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1048,8 +1048,12 @@
       <c r="I13" t="n">
         <v>0</v>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="J13" t="n">
+        <v>1534.5</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>46232.16666666666</v>
+      </c>
       <c r="L13" t="b">
         <v>0</v>
       </c>
@@ -1057,22 +1061,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MALLATMILLENIA</t>
+          <t>LENOX</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Mall at Millenia</t>
+          <t>Lenox Square</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4200 Conroy Road, Orlando, FL 32839</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>3393 Peachtree Road Northeast Atlanta GA 30326</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>NO COVERAGE</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1099,17 +1103,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>MALLATMILLENIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>The Mall at Millenia</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>401 Northeast Northgate Way Seattle WA 98125</t>
+          <t>4200 Conroy Road, Orlando, FL 32839</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1118,26 +1122,22 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>14</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>145.2</v>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>46233.28194444445</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="b">
         <v>0</v>
       </c>
@@ -1145,17 +1145,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>433 Opry Mills Drive Nashville TN 37214</t>
+          <t>401 Northeast Northgate Way Seattle WA 98125</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1164,22 +1164,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>145.2</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>46233.28194444445</v>
+      </c>
       <c r="L16" t="b">
         <v>0</v>
       </c>
@@ -1187,17 +1191,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>OPRYMILLS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Opry Mills</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4400 Sharon Road Charlotte NC 28211</t>
+          <t>433 Opry Mills Drive Nashville TN 37214</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1206,26 +1210,22 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>178.9</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>46232.16666666666</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="b">
         <v>0</v>
       </c>
@@ -1233,17 +1233,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4502 South Steele Street Tacoma WA 98409</t>
+          <t>4400 Sharon Road Charlotte NC 28211</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1252,25 +1252,25 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>471.3</v>
+        <v>178.9</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>46233</v>
+        <v>46232.16666666666</v>
       </c>
       <c r="L18" t="b">
         <v>0</v>
@@ -1279,41 +1279,45 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>THEDOMAIN</t>
+          <t>TACOMAMALL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Domain</t>
+          <t>Tacoma Mall</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>11410 Century Oaks Terrace Austin TX 78758</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>NO COVERAGE</t>
+          <t>4502 South Steele Street Tacoma WA 98409</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>471.3</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>46233</v>
+      </c>
       <c r="L19" t="b">
         <v>0</v>
       </c>
@@ -1321,45 +1325,41 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>THEDOMAIN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>The Domain</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>7700 East Kellogg Wichita KS 67207</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>11410 Century Oaks Terrace Austin TX 78758</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>NO COVERAGE</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>33</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>23</v>
-      </c>
-      <c r="J20" t="n">
-        <v>288.9</v>
-      </c>
-      <c r="K20" s="3" t="n">
-        <v>46233.7625</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="b">
         <v>0</v>
       </c>
@@ -1367,17 +1367,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>UNIVPARKVILLAGE</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>University Park Village</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1612 South University Drive Fort Worth TX 76107</t>
+          <t>7700 East Kellogg Wichita KS 67207</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1386,28 +1386,74 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="J21" t="n">
+        <v>288.9</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>46233.7625</v>
+      </c>
       <c r="L21" t="b">
         <v>0</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>UNIVPARKVILLAGE</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>University Park Village</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1612 South University Drive Fort Worth TX 76107</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L21"/>
+  <autoFilter ref="A1:L22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2982,7 +3028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M285"/>
+  <dimension ref="A1:M286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2992,7 +3038,7 @@
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="49" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
     <col width="53" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
@@ -19707,8 +19753,67 @@
         </is>
       </c>
     </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>CLARKSBURG</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Clarksburg Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>CLARKSBURG:icn6-v9z3</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>201584985</t>
+        </is>
+      </c>
+      <c r="E286" s="3" t="n">
+        <v>46232.38263888889</v>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Family Offenses, NonViolent</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>FAMILY OFFENSE - NEGLECT CHILD (INCLUDES NONSUPPOR</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>13400 BLK  BLUEBEARD TER</t>
+        </is>
+      </c>
+      <c r="J286" t="n">
+        <v>39.235</v>
+      </c>
+      <c r="K286" t="n">
+        <v>-77.27719999999999</v>
+      </c>
+      <c r="L286" t="n">
+        <v>1135.3</v>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>Family offenses, nonviolent on Jul 29, 2026, 1135 m from Clarksburg Premium Outlets (13400 BLK  BLUEBEARD TER). Case #201584985 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M285"/>
+  <autoFilter ref="A1:M286"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19719,7 +19824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="51" customWidth="1" min="1" max="1"/>
@@ -19746,7 +19851,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01 04:32:25.991636+00:00</t>
+          <t>2026-08-01 04:35:44.705888+00:00</t>
         </is>
       </c>
     </row>
@@ -19778,7 +19883,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-25 04:32:25.991636+00:00</t>
+          <t>2026-07-25 04:35:44.705888+00:00</t>
         </is>
       </c>
     </row>
@@ -19789,7 +19894,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7">
@@ -20054,8 +20159,20 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>source:CLARKSBURG/Montgomery County Police Crime</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>OK fetched=1 truncated=False</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B28"/>
+  <autoFilter ref="A1:B29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/latest/blotter_report.xlsx
+++ b/reports/latest/blotter_report.xlsx
@@ -19851,7 +19851,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01 04:35:44.705888+00:00</t>
+          <t>2026-08-01 04:54:04.147095+00:00</t>
         </is>
       </c>
     </row>
@@ -19883,7 +19883,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-25 04:35:44.705888+00:00</t>
+          <t>2026-07-25 04:54:04.147095+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/latest/blotter_report.xlsx
+++ b/reports/latest/blotter_report.xlsx
@@ -19851,7 +19851,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01 04:54:04.147095+00:00</t>
+          <t>2026-08-01 04:55:55.470379+00:00</t>
         </is>
       </c>
     </row>
@@ -19883,7 +19883,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-25 04:54:04.147095+00:00</t>
+          <t>2026-07-25 04:55:55.470379+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/latest/blotter_report.xlsx
+++ b/reports/latest/blotter_report.xlsx
@@ -13,10 +13,10 @@
     <sheet name="Run Metadata" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Highlights'!$A$1:$M$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$286</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$288</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -789,26 +789,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CLARKSBURG</t>
+          <t>CHESTNUTHILL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Clarksburg Premium Outlets</t>
+          <t>The Shops at Chestnut Hill</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>22705 Clarksburg Rd Clarksburg MD 20871</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>199 Boylston Street Chestnut Hill MA 02467</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -820,14 +820,10 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1135.3</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>46232.38263888889</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="b">
         <v>0</v>
       </c>
@@ -835,17 +831,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CLEARFORK</t>
+          <t>CLARKSBURG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Shops at Clearfork</t>
+          <t>Clarksburg Premium Outlets</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5188 Monahans Avenue Fort Worth TX 76109</t>
+          <t>22705 Clarksburg Rd Clarksburg MD 20871</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -860,19 +856,19 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>1086.4</v>
+        <v>1135.3</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>46228.59375</v>
+        <v>46232.38263888889</v>
       </c>
       <c r="L9" t="b">
         <v>0</v>
@@ -881,17 +877,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>CLEARFORK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Empire Mall</t>
+          <t>The Shops at Clearfork</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5000 Empire Mall Sioux Falls SD 57106</t>
+          <t>5188 Monahans Avenue Fort Worth TX 76109</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -900,25 +896,25 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>123</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>315.5</v>
+        <v>1086.4</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>46234.24527777778</v>
+        <v>46228.59375</v>
       </c>
       <c r="L10" t="b">
         <v>0</v>
@@ -927,22 +923,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GREENHILLS</t>
+          <t>COPLEY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Mall at Green Hills</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2126 Abbott Martin Road, Nashville, TN 37215</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>2 Copley Place Boston MA 02116</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -969,17 +965,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>Empire Mall</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5085 Westheimer Houston TX 77056</t>
+          <t>5000 Empire Mall Sioux Falls SD 57106</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -988,25 +984,25 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>57</v>
+        <v>123</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="J12" t="n">
-        <v>163.5</v>
+        <v>315.5</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>46233</v>
+        <v>46234.24527777778</v>
       </c>
       <c r="L12" t="b">
         <v>0</v>
@@ -1015,17 +1011,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>INTLPLAZA</t>
+          <t>GREENHILLS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>International Plaza</t>
+          <t>The Mall at Green Hills</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2223 North West Shore Boulevard Tampa FL 33607</t>
+          <t>2126 Abbott Martin Road, Nashville, TN 37215</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1034,13 +1030,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1048,12 +1044,8 @@
       <c r="I13" t="n">
         <v>0</v>
       </c>
-      <c r="J13" t="n">
-        <v>1534.5</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>46232.16666666666</v>
-      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="b">
         <v>0</v>
       </c>
@@ -1061,41 +1053,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LENOX</t>
+          <t>HOUSTONGAL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lenox Square</t>
+          <t>Houston Galleria</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3393 Peachtree Road Northeast Atlanta GA 30326</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>NO COVERAGE</t>
+          <t>5085 Westheimer Houston TX 77056</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
+        <v>57</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="J14" t="n">
+        <v>163.5</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>46233</v>
+      </c>
       <c r="L14" t="b">
         <v>0</v>
       </c>
@@ -1103,17 +1099,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MALLATMILLENIA</t>
+          <t>INTLPLAZA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Mall at Millenia</t>
+          <t>International Plaza</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4200 Conroy Road, Orlando, FL 32839</t>
+          <t>2223 North West Shore Boulevard Tampa FL 33607</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1122,13 +1118,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1136,8 +1132,12 @@
       <c r="I15" t="n">
         <v>0</v>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="J15" t="n">
+        <v>1534.5</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>46232.16666666666</v>
+      </c>
       <c r="L15" t="b">
         <v>0</v>
       </c>
@@ -1145,45 +1145,41 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>LENOX</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Lenox Square</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>401 Northeast Northgate Way Seattle WA 98125</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>3393 Peachtree Road Northeast Atlanta GA 30326</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>NO COVERAGE</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>14</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>145.2</v>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>46233.28194444445</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="b">
         <v>0</v>
       </c>
@@ -1191,17 +1187,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>MALLATMILLENIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>The Mall at Millenia</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>433 Opry Mills Drive Nashville TN 37214</t>
+          <t>4200 Conroy Road, Orlando, FL 32839</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1233,17 +1229,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>NORFOLKPO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Norfolk Premium Outlets</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4400 Sharon Road Charlotte NC 28211</t>
+          <t>1600 Premium Outlets Boulevard Norfolk VA 23502</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1252,25 +1248,25 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>7</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>178.9</v>
+        <v>1118.9</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>46232.16666666666</v>
+        <v>46233</v>
       </c>
       <c r="L18" t="b">
         <v>0</v>
@@ -1279,17 +1275,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4502 South Steele Street Tacoma WA 98409</t>
+          <t>401 Northeast Northgate Way Seattle WA 98125</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1298,25 +1294,25 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>471.3</v>
+        <v>145.2</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>46233</v>
+        <v>46233.28194444445</v>
       </c>
       <c r="L19" t="b">
         <v>0</v>
@@ -1325,22 +1321,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>THEDOMAIN</t>
+          <t>OPRYMILLS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Domain</t>
+          <t>Opry Mills</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>11410 Century Oaks Terrace Austin TX 78758</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>NO COVERAGE</t>
+          <t>433 Opry Mills Drive Nashville TN 37214</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1367,17 +1363,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>7700 East Kellogg Wichita KS 67207</t>
+          <t>4400 Sharon Road Charlotte NC 28211</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1386,25 +1382,25 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
         <v>1</v>
       </c>
-      <c r="I21" t="n">
-        <v>23</v>
-      </c>
       <c r="J21" t="n">
-        <v>288.9</v>
+        <v>178.9</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>46233.7625</v>
+        <v>46232.16666666666</v>
       </c>
       <c r="L21" t="b">
         <v>0</v>
@@ -1413,17 +1409,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>UNIVPARKVILLAGE</t>
+          <t>TACOMAMALL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>University Park Village</t>
+          <t>Tacoma Mall</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1612 South University Drive Fort Worth TX 76107</t>
+          <t>4502 South Steele Street Tacoma WA 98409</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1432,28 +1428,162 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>471.3</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>46233</v>
+      </c>
       <c r="L22" t="b">
         <v>0</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>THEDOMAIN</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>The Domain</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>11410 Century Oaks Terrace Austin TX 78758</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>NO COVERAGE</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>7700 East Kellogg Wichita KS 67207</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>33</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>8</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>23</v>
+      </c>
+      <c r="J24" t="n">
+        <v>288.9</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>46233.7625</v>
+      </c>
+      <c r="L24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>UNIVPARKVILLAGE</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>University Park Village</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1612 South University Drive Fort Worth TX 76107</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L22"/>
+  <autoFilter ref="A1:L25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3028,7 +3158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M286"/>
+  <dimension ref="A1:M288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -19812,8 +19942,118 @@
         </is>
       </c>
     </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>NORFOLKPO</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Norfolk Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>NORFOLKPO:r7bn-2egr</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>260730001961</t>
+        </is>
+      </c>
+      <c r="E287" s="3" t="n">
+        <v>46233</v>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>SHOOT INTO OCCUPIED DWELLING</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr"/>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>1400 DURE RD</t>
+        </is>
+      </c>
+      <c r="J287" t="n">
+        <v>36.872248203692</v>
+      </c>
+      <c r="K287" t="n">
+        <v>-76.209734788037</v>
+      </c>
+      <c r="L287" t="n">
+        <v>1387.8</v>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>Shoot into occupied dwelling on Jul 30, 2026, 1388 m from Norfolk Premium Outlets (1400 DURE RD). Case #260730001961 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>NORFOLKPO</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Norfolk Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>NORFOLKPO:r7bn-2egr</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>260730001974</t>
+        </is>
+      </c>
+      <c r="E288" s="3" t="n">
+        <v>46233</v>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>HIT &amp; RUN - PERSONAL INJURY</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr"/>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>2500 MILITARY HIGHWAY</t>
+        </is>
+      </c>
+      <c r="J288" t="n">
+        <v>36.879766119132</v>
+      </c>
+      <c r="K288" t="n">
+        <v>-76.212427576002</v>
+      </c>
+      <c r="L288" t="n">
+        <v>1118.9</v>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>Hit &amp; run - personal injury on Jul 30, 2026, 1119 m from Norfolk Premium Outlets (2500 MILITARY HIGHWAY). Case #260730001974 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M286"/>
+  <autoFilter ref="A1:M288"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19824,11 +20064,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="51" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19851,7 +20091,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01 04:55:55.470379+00:00</t>
+          <t>2026-08-01 04:58:47.637225+00:00</t>
         </is>
       </c>
     </row>
@@ -19883,7 +20123,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-25 04:55:55.470379+00:00</t>
+          <t>2026-07-25 04:58:47.637225+00:00</t>
         </is>
       </c>
     </row>
@@ -19894,7 +20134,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7">
@@ -20171,8 +20411,44 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>source:COPLEY/Boston PD Crime Incident Reports</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>FAILED fetched=0 truncated=False CKAN fetch failed for b973d8cb-eeb2-4e7e-99da-c92938efc9c0: HTTP 403 for https://data.boston.gov/api/3/action/datastore_search_sql?sql=SELECT+%2A+FROM+%22b973d8cb-eeb2-4e7e-99da-c92938efc9c0%22+WHERE+CAST%28NULLIF%28%22Lat%22%2C+%27%27%29+AS+float8%29+BETWEEN+42.3332261543053+AND+42.3620044456947+AND+CAST%28NULLIF%28%22Long%22%2C+%27%27%29+AS+float8%29+BETWEEN+-71.09710221911952+AND+-71.05816378088049+AND+%22OCCURRED_ON_DATE%22+%3E%3D+%272026-07-25T04%3A58%3A47%27+LIMIT+5000 :: {"help": "https://data.boston.gov/api/3/action/help_show?name=datastore_search_sql", "error": {"__type": "Authorization Error", "message": "Access denied: {'permissions': ['Not authorized to call function NULLIF']}"}, "success": false}</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>source:CHESTNUTHILL/Boston PD Crime Incident Reports (Boston-side only)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>FAILED fetched=0 truncated=False CKAN fetch failed for b973d8cb-eeb2-4e7e-99da-c92938efc9c0: HTTP 403 for https://data.boston.gov/api/3/action/datastore_search_sql?sql=SELECT+%2A+FROM+%22b973d8cb-eeb2-4e7e-99da-c92938efc9c0%22+WHERE+CAST%28NULLIF%28%22Lat%22%2C+%27%27%29+AS+float8%29+BETWEEN+42.3071233543053+AND+42.3359016456947+AND+CAST%28NULLIF%28%22Long%22%2C+%27%27%29+AS+float8%29+BETWEEN+-71.19513294012805+AND+-71.15621065987196+AND+%22OCCURRED_ON_DATE%22+%3E%3D+%272026-07-25T04%3A58%3A47%27+LIMIT+5000 :: {"help": "https://data.boston.gov/api/3/action/help_show?name=datastore_search_sql", "error": {"__type": "Authorization Error", "message": "Access denied: {'permissions': ['Not authorized to call function NULLIF']}"}, "success": false}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>source:NORFOLKPO/Norfolk Police Incident Reports</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>OK fetched=281 truncated=False</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B29"/>
+  <autoFilter ref="A1:B32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/latest/blotter_report.xlsx
+++ b/reports/latest/blotter_report.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Highlights'!$A$1:$M$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$288</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$350</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -802,9 +802,9 @@
           <t>199 Boylston Street Chestnut Hill MA 02467</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -936,28 +936,32 @@
           <t>2 Copley Place Boston MA 02116</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
+        <v>61</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="J11" t="n">
+        <v>129.3</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>46230.89583333334</v>
+      </c>
       <c r="L11" t="b">
         <v>0</v>
       </c>
@@ -1248,7 +1252,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1260,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
         <v>1118.9</v>
@@ -1599,7 +1603,7 @@
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
@@ -2032,30 +2036,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>COPLEY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Empire Mall</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CFS26-161603</t>
+          <t>262064756</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>46230.83325231481</v>
+        <v>46230.80347222222</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>ASSAULT - SIMPLE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2063,58 +2067,54 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Assault</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>S WESTPORT AVE &amp; W 41ST ST</t>
+          <t>MASSACHUSETTS AVE</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>43.51485103457241</v>
+        <v>42.34439568415441</v>
       </c>
       <c r="K8" t="n">
-        <v>-96.76794119445807</v>
+        <v>-71.08632016344815</v>
       </c>
       <c r="L8" t="n">
-        <v>808.9</v>
+        <v>798.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Assault on Jul 27, 2026, 809 m from Empire Mall (S WESTPORT AVE &amp; W 41ST ST). Case #CFS26-161603 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault - simple on Jul 27, 2026, 799 m from Copley Place (MASSACHUSETTS AVE). Case #262064756 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Empire Mall</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>20260729-1600-11</t>
+          <t>CFS26-161603</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>46232.16666666666</v>
+        <v>46230.83325231481</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Simple Assault</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2124,56 +2124,56 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>13B</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4700 PIEDMONT ROW DR</t>
+          <t>S WESTPORT AVE &amp; W 41ST ST</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>35.15196312662653</v>
+        <v>43.51485103457241</v>
       </c>
       <c r="K9" t="n">
-        <v>-80.83980651357408</v>
+        <v>-96.76794119445807</v>
       </c>
       <c r="L9" t="n">
-        <v>850.6</v>
+        <v>808.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Simple assault on Jul 29, 2026, 851 m from Southpark (4700 PIEDMONT ROW DR). Status: Open. Case #20260729-1600-11 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 27, 2026, 809 m from Empire Mall (S WESTPORT AVE &amp; W 41ST ST). Case #CFS26-161603 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2620701835</t>
+          <t>20260729-1600-11</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>46229</v>
+        <v>46232.16666666666</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Assault Simple</t>
+          <t>Simple Assault</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2183,56 +2183,56 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>13B</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4000 S LAWRENCE ST</t>
+          <t>4700 PIEDMONT ROW DR</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>47.219421</v>
+        <v>35.15196312662653</v>
       </c>
       <c r="K10" t="n">
-        <v>-122.478428</v>
+        <v>-80.83980651357408</v>
       </c>
       <c r="L10" t="n">
-        <v>853.4</v>
+        <v>850.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Assault simple on Jul 26, 2026, 853 m from Tacoma Mall (4000 S LAWRENCE ST). Case #2620701835 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 29, 2026, 851 m from Southpark (4700 PIEDMONT ROW DR). Status: Open. Case #20260729-1600-11 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>TACOMAMALL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Tacoma Mall</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>71878728447</t>
+          <t>2620701835</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>46230.4375</v>
+        <v>46229</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Robbery</t>
+          <t>Assault Simple</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2242,56 +2242,56 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>VIOLENT CRIME</t>
+          <t>Assault Offenses</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>16XX BLOCK OF N 105TH ST</t>
+          <t>4000 S LAWRENCE ST</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>47.70504225</v>
+        <v>47.219421</v>
       </c>
       <c r="K11" t="n">
-        <v>-122.338094779232</v>
+        <v>-122.478428</v>
       </c>
       <c r="L11" t="n">
-        <v>938.8</v>
+        <v>853.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Robbery on Jul 27, 2026, 939 m from Northgate Station (16XX BLOCK OF N 105TH ST). Case #2026-220064 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault simple on Jul 26, 2026, 853 m from Tacoma Mall (4000 S LAWRENCE ST). Case #2620701835 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>COPLEY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2621000152</t>
+          <t>262064416</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>46232</v>
+        <v>46229.87569444445</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Assault Simple</t>
+          <t>ASSAULT - AGGRAVATED</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2299,28 +2299,24 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3500 S 45TH ST</t>
+          <t>HUNTINGTON AVE</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>47.216421</v>
+        <v>42.34221543503831</v>
       </c>
       <c r="K12" t="n">
-        <v>-122.482428</v>
+        <v>-71.08577074656198</v>
       </c>
       <c r="L12" t="n">
-        <v>1074.3</v>
+        <v>898.8</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Assault simple on Jul 29, 2026, 1074 m from Tacoma Mall (3500 S 45TH ST). Case #2621000152 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault - aggravated on Jul 26, 2026, 899 m from Copley Place (HUNTINGTON AVE). Case #262064416 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2342,15 +2338,15 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>71894237115</t>
+          <t>71878728447</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>46231.20833333334</v>
+        <v>46230.4375</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Aggravated Assault</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2365,51 +2361,51 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>15XX BLOCK OF NE 107TH ST</t>
+          <t>16XX BLOCK OF N 105TH ST</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>47.70668788</v>
+        <v>47.70504225</v>
       </c>
       <c r="K13" t="n">
-        <v>-122.311189997702</v>
+        <v>-122.338094779232</v>
       </c>
       <c r="L13" t="n">
-        <v>1145.7</v>
+        <v>938.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-221056 (use for a records request — full narratives are not published in open data).</t>
+          <t>Robbery on Jul 27, 2026, 939 m from Northgate Station (16XX BLOCK OF N 105TH ST). Case #2026-220064 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>TACOMAMALL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Tacoma Mall</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>71889871382</t>
+          <t>2621000152</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>46231.00625</v>
+        <v>46232</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Simple Assault</t>
+          <t>Assault Simple</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2419,56 +2415,56 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>ALL OTHER</t>
+          <t>Assault Offenses</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>15XX BLOCK OF NE 107TH ST</t>
+          <t>3500 S 45TH ST</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>47.70668788</v>
+        <v>47.216421</v>
       </c>
       <c r="K14" t="n">
-        <v>-122.311189997702</v>
+        <v>-122.482428</v>
       </c>
       <c r="L14" t="n">
-        <v>1145.7</v>
+        <v>1074.3</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Simple assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-220636 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault simple on Jul 29, 2026, 1074 m from Tacoma Mall (3500 S 45TH ST). Case #2621000152 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>COPLEY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>26C142249</t>
+          <t>262064432</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>46230.75</v>
+        <v>46229.91666666666</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>BATTERY ABW</t>
+          <t>ROBBERY</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2476,58 +2472,54 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>SIM_ASSAULT</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>700 BLOCK OF S MISSION RD</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>37.6756469679485</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K15" t="n">
-        <v>-97.25850032865422</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L15" t="n">
-        <v>1251.5</v>
+        <v>1123.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Battery abw on Jul 27, 2026, 1251 m from Towne East Square (700 BLOCK OF S MISSION RD). Case #26C142249 (use for a records request — full narratives are not published in open data).</t>
+          <t>Robbery on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064432 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>COPLEY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Empire Mall</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CFS26-164521</t>
+          <t>262064298</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>46234.03421296296</v>
+        <v>46229.08611111111</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aggravated Assault</t>
+          <t>FIREARM/WEAPON - LOST</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2535,54 +2527,50 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Assault</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>S MARION RD &amp; W 41ST ST</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>43.51481738299845</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K16" t="n">
-        <v>-96.79096028032072</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L16" t="n">
-        <v>1322.4</v>
+        <v>1123.7</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 31, 2026, 1322 m from Empire Mall (S MARION RD &amp; W 41ST ST). Case #CFS26-164521 (use for a records request — full narratives are not published in open data).</t>
+          <t>Firearm/weapon - lost on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064298 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HOUSTONGAL:Houston PD NIBRS — Person</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>096140526</t>
+          <t>71894237115</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>46232</v>
+        <v>46231.20833333334</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2596,56 +2584,56 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>13A</t>
+          <t>VIOLENT CRIME</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1900-1999 POST OAK PARK DR</t>
+          <t>15XX BLOCK OF NE 107TH ST</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>29.74712522681273</v>
+        <v>47.70668788</v>
       </c>
       <c r="K17" t="n">
-        <v>-95.45374747370188</v>
+        <v>-122.311189997702</v>
       </c>
       <c r="L17" t="n">
-        <v>1323.4</v>
+        <v>1145.7</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 29, 2026, 1323 m from Houston Galleria (1900-1999 POST OAK PARK DR). Case #096140526 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-221056 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202675136         </t>
+          <t>71889871382</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>46228.97847222222</v>
+        <v>46231.00625</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">[13B] ASSAULT                                                                   </t>
+          <t>Simple Assault</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2653,54 +2641,58 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ALL OTHER</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5XXX S HARDY DR</t>
+          <t>15XX BLOCK OF NE 107TH ST</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>33.3757495513233</v>
+        <v>47.70668788</v>
       </c>
       <c r="K18" t="n">
-        <v>-111.9531832468173</v>
+        <v>-122.311189997702</v>
       </c>
       <c r="L18" t="n">
-        <v>1345.1</v>
+        <v>1145.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>[13b] assault on Jul 25, 2026, 1345 m from Arizona Mills (5XXX S HARDY DR). Case #TE202675136          (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-220636 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Empire Mall</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CFS26-164393</t>
+          <t>26C142249</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>46233.93733796296</v>
+        <v>46230.75</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>BATTERY ABW</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2710,26 +2702,26 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>SIM_ASSAULT</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>S LARCH AVE &amp; W 43RD ST</t>
+          <t>700 BLOCK OF S MISSION RD</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>43.51319846254545</v>
+        <v>37.6756469679485</v>
       </c>
       <c r="K19" t="n">
-        <v>-96.79336119066248</v>
+        <v>-97.25850032865422</v>
       </c>
       <c r="L19" t="n">
-        <v>1453.4</v>
+        <v>1251.5</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Assault on Jul 30, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-164393 (use for a records request — full narratives are not published in open data).</t>
+          <t>Battery abw on Jul 27, 2026, 1251 m from Towne East Square (700 BLOCK OF S MISSION RD). Case #26C142249 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2751,15 +2743,15 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CFS26-159792</t>
+          <t>CFS26-164521</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>46229.12712962963</v>
+        <v>46234.03421296296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Weapons Violations</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2769,56 +2761,56 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Weapons</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>S LARCH AVE &amp; W 43RD ST</t>
+          <t>S MARION RD &amp; W 41ST ST</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>43.51319846254545</v>
+        <v>43.51481738299845</v>
       </c>
       <c r="K20" t="n">
-        <v>-96.79336119066248</v>
+        <v>-96.79096028032072</v>
       </c>
       <c r="L20" t="n">
-        <v>1453.4</v>
+        <v>1322.4</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Weapons violations on Jul 26, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-159792 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 31, 2026, 1322 m from Empire Mall (S MARION RD &amp; W 41ST ST). Case #CFS26-164521 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>HOUSTONGAL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Houston Galleria</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>HOUSTONGAL:Houston PD NIBRS — Person</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2621102013</t>
+          <t>096140526</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Assault Simple</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2828,321 +2820,309 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>13A</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5400 SOUTH TACOMA WAY</t>
+          <t>1900-1999 POST OAK PARK DR</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>47.206421</v>
+        <v>29.74712522681273</v>
       </c>
       <c r="K21" t="n">
-        <v>-122.483428</v>
+        <v>-95.45374747370188</v>
       </c>
       <c r="L21" t="n">
-        <v>1578</v>
+        <v>1323.4</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Assault simple on Jul 30, 2026, 1578 m from Tacoma Mall (5400 SOUTH TACOMA WAY). Case #2621102013 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 29, 2026, 1323 m from Houston Galleria (1900-1999 POST OAK PARK DR). Case #096140526 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>DP2026415473230300</t>
+          <t xml:space="preserve">TE202675136         </t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>46231.47916666666</v>
+        <v>46228.97847222222</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>theft-shoplift</t>
+          <t xml:space="preserve">[13B] ASSAULT                                                                   </t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>larceny</t>
-        </is>
-      </c>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>15 S STEELE ST</t>
+          <t>5XXX S HARDY DR</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>39.7162154712797</v>
+        <v>33.3757495513233</v>
       </c>
       <c r="K22" t="n">
-        <v>-104.9512928115626</v>
+        <v>-111.9531832468173</v>
       </c>
       <c r="L22" t="n">
-        <v>144.7</v>
+        <v>1345.1</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Theft-shoplift on Jul 28, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026415473 (use for a records request — full narratives are not published in open data).</t>
+          <t>[13b] assault on Jul 25, 2026, 1345 m from Arizona Mills (5XXX S HARDY DR). Case #TE202675136          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>COPLEY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DP2026413358260700</t>
+          <t>262064339</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>46230.47013888889</v>
+        <v>46229.63333333333</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>fraud-by-telephone</t>
+          <t>ASSAULT - AGGRAVATED</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>white-collar-crime</t>
-        </is>
-      </c>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>15 S STEELE ST</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>39.7162154712797</v>
+        <v>42.33511903946613</v>
       </c>
       <c r="K23" t="n">
-        <v>-104.9512928115626</v>
+        <v>-71.07491709613726</v>
       </c>
       <c r="L23" t="n">
-        <v>144.7</v>
+        <v>1407.3</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Fraud-by-telephone on Jul 27, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026413358 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault - aggravated on Jul 26, 2026, 1407 m from Copley Place (HARRISON AVE). Case #262064339 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Empire Mall</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>71913162555</t>
+          <t>CFS26-164393</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>46232.82986111111</v>
+        <v>46233.93733796296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>S LARCH AVE &amp; W 43RD ST</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>47.7086028</v>
+        <v>43.51319846254545</v>
       </c>
       <c r="K24" t="n">
-        <v>-122.324615154453</v>
+        <v>-96.79336119066248</v>
       </c>
       <c r="L24" t="n">
-        <v>145.2</v>
+        <v>1453.4</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 29, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-222878 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 30, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-164393 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Empire Mall</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>71898889573</t>
+          <t>CFS26-159792</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>46231.625</v>
+        <v>46229.12712962963</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Weapons Violations</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>Weapons</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>S LARCH AVE &amp; W 43RD ST</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>47.7086028</v>
+        <v>43.51319846254545</v>
       </c>
       <c r="K25" t="n">
-        <v>-122.324615154453</v>
+        <v>-96.79336119066248</v>
       </c>
       <c r="L25" t="n">
-        <v>145.2</v>
+        <v>1453.4</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-221387 (use for a records request — full narratives are not published in open data).</t>
+          <t>Weapons violations on Jul 26, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-159792 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>COPLEY</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>71899277060</t>
+          <t>262064587</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>46231.47569444445</v>
+        <v>46230.5</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>ASSAULT - AGGRAVATED</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>PROPERTY CRIME</t>
-        </is>
-      </c>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>MASSACHUSETTS AVE</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>47.7086028</v>
+        <v>42.3342194178955</v>
       </c>
       <c r="K26" t="n">
-        <v>-122.324615154454</v>
+        <v>-71.07434615707857</v>
       </c>
       <c r="L26" t="n">
-        <v>145.2</v>
+        <v>1513.9</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-221174 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault - aggravated on Jul 27, 2026, 1514 m from Copley Place (MASSACHUSETTS AVE). Case #262064587 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -3158,12 +3138,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M288"/>
+  <dimension ref="A1:M350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
@@ -19945,30 +19925,30 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>NORFOLKPO</t>
+          <t>COPLEY</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Norfolk Premium Outlets</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>NORFOLKPO:r7bn-2egr</t>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>260730001961</t>
+          <t>262064284</t>
         </is>
       </c>
       <c r="E287" s="3" t="n">
-        <v>46233</v>
+        <v>46229.54305555556</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>SHOOT INTO OCCUPIED DWELLING</t>
+          <t>M/V ACCIDENT - INVOLVING PEDESTRIAN - INJURY</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -19979,51 +19959,51 @@
       <c r="H287" t="inlineStr"/>
       <c r="I287" t="inlineStr">
         <is>
-          <t>1400 DURE RD</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J287" t="n">
-        <v>36.872248203692</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K287" t="n">
-        <v>-76.209734788037</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L287" t="n">
-        <v>1387.8</v>
+        <v>1123.7</v>
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Shoot into occupied dwelling on Jul 30, 2026, 1388 m from Norfolk Premium Outlets (1400 DURE RD). Case #260730001961 (use for a records request — full narratives are not published in open data).</t>
+          <t>M/v accident - involving pedestrian - injury on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064284 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>NORFOLKPO</t>
+          <t>COPLEY</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Norfolk Premium Outlets</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>NORFOLKPO:r7bn-2egr</t>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>260730001974</t>
+          <t>262064275</t>
         </is>
       </c>
       <c r="E288" s="3" t="n">
-        <v>46233</v>
+        <v>46229.51111111111</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>HIT &amp; RUN - PERSONAL INJURY</t>
+          <t>FORGERY / COUNTERFEITING</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -20034,26 +20014,3468 @@
       <c r="H288" t="inlineStr"/>
       <c r="I288" t="inlineStr">
         <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J288" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K288" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L288" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>Forgery / counterfeiting on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064275 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>262064650</t>
+        </is>
+      </c>
+      <c r="E289" s="3" t="n">
+        <v>46230.61875</v>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>M/V ACCIDENT - INVOLVING BICYCLE - INJURY</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr"/>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>MASSACHUSETTS AVE &amp; TREMONT ST
+BOSTON, MA 02118
+UN</t>
+        </is>
+      </c>
+      <c r="J289" t="n">
+        <v>42.33929095757131</v>
+      </c>
+      <c r="K289" t="n">
+        <v>-71.08041395047391</v>
+      </c>
+      <c r="L289" t="n">
+        <v>953.4</v>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>M/v accident - involving bicycle - injury on Jul 27, 2026, 953 m from Copley Place (MASSACHUSETTS AVE &amp; TREMONT ST
+BOSTON, MA 02118
+UN). Case #262064650 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>262064295</t>
+        </is>
+      </c>
+      <c r="E290" s="3" t="n">
+        <v>46229.54791666667</v>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>SICK ASSIST</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr"/>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>BOYLSTON ST</t>
+        </is>
+      </c>
+      <c r="J290" t="n">
+        <v>42.34862381555496</v>
+      </c>
+      <c r="K290" t="n">
+        <v>-71.08277637086411</v>
+      </c>
+      <c r="L290" t="n">
+        <v>437.3</v>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>Sick assist on Jul 26, 2026, 437 m from Copley Place (BOYLSTON ST). Case #262064295 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>262064382</t>
+        </is>
+      </c>
+      <c r="E291" s="3" t="n">
+        <v>46229.78680555556</v>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>VERBAL DISPUTE</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr"/>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>HUDSON ST</t>
+        </is>
+      </c>
+      <c r="J291" t="n">
+        <v>42.34976401607222</v>
+      </c>
+      <c r="K291" t="n">
+        <v>-71.06045076420118</v>
+      </c>
+      <c r="L291" t="n">
+        <v>1432.1</v>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>Verbal dispute on Jul 26, 2026, 1432 m from Copley Place (HUDSON ST). Case #262064382 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>262064432</t>
+        </is>
+      </c>
+      <c r="E292" s="3" t="n">
+        <v>46229.91666666666</v>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>ROBBERY</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr"/>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J292" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K292" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L292" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>Robbery on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064432 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>262064822</t>
+        </is>
+      </c>
+      <c r="E293" s="3" t="n">
+        <v>46230.83541666667</v>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>INVESTIGATE PERSON</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr"/>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>COLUMBUS SQ</t>
+        </is>
+      </c>
+      <c r="J293" t="n">
+        <v>42.34332879779392</v>
+      </c>
+      <c r="K293" t="n">
+        <v>-71.07788857963692</v>
+      </c>
+      <c r="L293" t="n">
+        <v>477.1</v>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>Investigate person on Jul 27, 2026, 477 m from Copley Place (COLUMBUS SQ). Case #262064822 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>262064697</t>
+        </is>
+      </c>
+      <c r="E294" s="3" t="n">
+        <v>46230.70277777778</v>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>INVESTIGATE PERSON</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr"/>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>MASSACHUSETTS AVE</t>
+        </is>
+      </c>
+      <c r="J294" t="n">
+        <v>42.34867437636976</v>
+      </c>
+      <c r="K294" t="n">
+        <v>-71.08841866225799</v>
+      </c>
+      <c r="L294" t="n">
+        <v>894.2</v>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>Investigate person on Jul 27, 2026, 894 m from Copley Place (MASSACHUSETTS AVE). Case #262064697 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>262064696</t>
+        </is>
+      </c>
+      <c r="E295" s="3" t="n">
+        <v>46230.57777777778</v>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>LARCENY THEFT FROM BUILDING</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr"/>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>LINCOLN ST</t>
+        </is>
+      </c>
+      <c r="J295" t="n">
+        <v>42.35043296884182</v>
+      </c>
+      <c r="K295" t="n">
+        <v>-71.05873157807835</v>
+      </c>
+      <c r="L295" t="n">
+        <v>1584.6</v>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>Larceny theft from building on Jul 27, 2026, 1585 m from Copley Place (LINCOLN ST). Case #262064696 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>262064796</t>
+        </is>
+      </c>
+      <c r="E296" s="3" t="n">
+        <v>46230.75</v>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>PROPERTY - LOST/ MISSING</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr"/>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J296" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K296" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L296" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>Property - lost/ missing on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064796 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>262064756</t>
+        </is>
+      </c>
+      <c r="E297" s="3" t="n">
+        <v>46230.80347222222</v>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>ASSAULT - SIMPLE</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr"/>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>MASSACHUSETTS AVE</t>
+        </is>
+      </c>
+      <c r="J297" t="n">
+        <v>42.34439568415441</v>
+      </c>
+      <c r="K297" t="n">
+        <v>-71.08632016344815</v>
+      </c>
+      <c r="L297" t="n">
+        <v>798.7</v>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>Assault - simple on Jul 27, 2026, 799 m from Copley Place (MASSACHUSETTS AVE). Case #262064756 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>262064716</t>
+        </is>
+      </c>
+      <c r="E298" s="3" t="n">
+        <v>46230.72638888889</v>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>LARCENY SHOPLIFTING</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr"/>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>NEWBURY ST</t>
+        </is>
+      </c>
+      <c r="J298" t="n">
+        <v>42.35059716982988</v>
+      </c>
+      <c r="K298" t="n">
+        <v>-71.07881030689927</v>
+      </c>
+      <c r="L298" t="n">
+        <v>345.4</v>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>Larceny shoplifting on Jul 27, 2026, 345 m from Copley Place (NEWBURY ST). Case #262064716 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>262064587</t>
+        </is>
+      </c>
+      <c r="E299" s="3" t="n">
+        <v>46230.5</v>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>ASSAULT - AGGRAVATED</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr"/>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>MASSACHUSETTS AVE</t>
+        </is>
+      </c>
+      <c r="J299" t="n">
+        <v>42.3342194178955</v>
+      </c>
+      <c r="K299" t="n">
+        <v>-71.07434615707857</v>
+      </c>
+      <c r="L299" t="n">
+        <v>1513.9</v>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>Assault - aggravated on Jul 27, 2026, 1514 m from Copley Place (MASSACHUSETTS AVE). Case #262064587 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>262064392</t>
+        </is>
+      </c>
+      <c r="E300" s="3" t="n">
+        <v>46229.82222222222</v>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>M/V ACCIDENT - OTHER</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr"/>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>TYLER ST</t>
+        </is>
+      </c>
+      <c r="J300" t="n">
+        <v>42.3509005960865</v>
+      </c>
+      <c r="K300" t="n">
+        <v>-71.06068690177561</v>
+      </c>
+      <c r="L300" t="n">
+        <v>1439.7</v>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>M/v accident - other on Jul 26, 2026, 1440 m from Copley Place (TYLER ST). Case #262064392 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>262064350</t>
+        </is>
+      </c>
+      <c r="E301" s="3" t="n">
+        <v>46229.70486111111</v>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>INVESTIGATE PERSON</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr"/>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>HUNTINGTON AVE</t>
+        </is>
+      </c>
+      <c r="J301" t="n">
+        <v>42.3473097976345</v>
+      </c>
+      <c r="K301" t="n">
+        <v>-71.0791516658207</v>
+      </c>
+      <c r="L301" t="n">
+        <v>129.3</v>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>Investigate person on Jul 26, 2026, 129 m from Copley Place (HUNTINGTON AVE). Case #262064350 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>262064616</t>
+        </is>
+      </c>
+      <c r="E302" s="3" t="n">
+        <v>46230.50347222222</v>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>DRUGS - POSSESSION/ SALE/ MANUFACTURING/ USE</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr"/>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>BOYLSTON SQ</t>
+        </is>
+      </c>
+      <c r="J302" t="n">
+        <v>42.35197501205302</v>
+      </c>
+      <c r="K302" t="n">
+        <v>-71.06332910808086</v>
+      </c>
+      <c r="L302" t="n">
+        <v>1271.5</v>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>Drugs - possession/ sale/ manufacturing/ use on Jul 27, 2026, 1272 m from Copley Place (BOYLSTON SQ). Case #262064616 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>262064640</t>
+        </is>
+      </c>
+      <c r="E303" s="3" t="n">
+        <v>46230.3125</v>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>INVESTIGATE PERSON</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr"/>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J303" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K303" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L303" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>Investigate person on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064640 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>262064573</t>
+        </is>
+      </c>
+      <c r="E304" s="3" t="n">
+        <v>46230.45833333334</v>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>SICK ASSIST - DRUG RELATED ILLNESS</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr"/>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>ALBANY ST</t>
+        </is>
+      </c>
+      <c r="J304" t="n">
+        <v>42.33428840659414</v>
+      </c>
+      <c r="K304" t="n">
+        <v>-71.07239517543796</v>
+      </c>
+      <c r="L304" t="n">
+        <v>1543.1</v>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>Sick assist - drug related illness on Jul 27, 2026, 1543 m from Copley Place (ALBANY ST). Case #262064573 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>262064608</t>
+        </is>
+      </c>
+      <c r="E305" s="3" t="n">
+        <v>46230</v>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>THREATS TO DO BODILY HARM</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr"/>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J305" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K305" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L305" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>Threats to do bodily harm on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064608 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>262064378</t>
+        </is>
+      </c>
+      <c r="E306" s="3" t="n">
+        <v>46229.79097222222</v>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>LARCENY ALL OTHERS</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr"/>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>W CONCORD ST</t>
+        </is>
+      </c>
+      <c r="J306" t="n">
+        <v>42.33961961800693</v>
+      </c>
+      <c r="K306" t="n">
+        <v>-71.07699236739417</v>
+      </c>
+      <c r="L306" t="n">
+        <v>890.6</v>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>Larceny all others on Jul 26, 2026, 891 m from Copley Place (W CONCORD ST). Case #262064378 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>262064152</t>
+        </is>
+      </c>
+      <c r="E307" s="3" t="n">
+        <v>46229.01458333333</v>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>NOISY PARTY/RADIO-NO ARREST</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr"/>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>PHILLIPS ST</t>
+        </is>
+      </c>
+      <c r="J307" t="n">
+        <v>42.36027809483424</v>
+      </c>
+      <c r="K307" t="n">
+        <v>-71.06899804851336</v>
+      </c>
+      <c r="L307" t="n">
+        <v>1576.7</v>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>Noisy party/radio-no arrest on Jul 26, 2026, 1577 m from Copley Place (PHILLIPS ST). Case #262064152 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>262064312</t>
+        </is>
+      </c>
+      <c r="E308" s="3" t="n">
+        <v>46229.60625</v>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>SICK ASSIST - DRUG RELATED ILLNESS</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr"/>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>ALBANY ST</t>
+        </is>
+      </c>
+      <c r="J308" t="n">
+        <v>42.33428840659414</v>
+      </c>
+      <c r="K308" t="n">
+        <v>-71.07239517543796</v>
+      </c>
+      <c r="L308" t="n">
+        <v>1543.1</v>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>Sick assist - drug related illness on Jul 26, 2026, 1543 m from Copley Place (ALBANY ST). Case #262064312 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>262064770</t>
+        </is>
+      </c>
+      <c r="E309" s="3" t="n">
+        <v>46230.52083333334</v>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>LARCENY THEFT FROM MV - NON-ACCESSORY</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr"/>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J309" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K309" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L309" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>Larceny theft from mv - non-accessory on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064770 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>262064532</t>
+        </is>
+      </c>
+      <c r="E310" s="3" t="n">
+        <v>46230.29166666666</v>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>PROPERTY - LOST/ MISSING</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr"/>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J310" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K310" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L310" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>Property - lost/ missing on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064532 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>262064590</t>
+        </is>
+      </c>
+      <c r="E311" s="3" t="n">
+        <v>46230.50625</v>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>LARCENY ALL OTHERS</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr"/>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>W BROOKLINE ST</t>
+        </is>
+      </c>
+      <c r="J311" t="n">
+        <v>42.34172590358821</v>
+      </c>
+      <c r="K311" t="n">
+        <v>-71.07501847816492</v>
+      </c>
+      <c r="L311" t="n">
+        <v>689.2</v>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>Larceny all others on Jul 27, 2026, 689 m from Copley Place (W BROOKLINE ST). Case #262064590 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>262064674</t>
+        </is>
+      </c>
+      <c r="E312" s="3" t="n">
+        <v>46229.33333333334</v>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>PROPERTY - LOST/ MISSING</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr"/>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J312" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K312" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L312" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>Property - lost/ missing on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064674 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>262064591</t>
+        </is>
+      </c>
+      <c r="E313" s="3" t="n">
+        <v>46229.77847222222</v>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>INVESTIGATE PERSON</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr"/>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>AVERY ST</t>
+        </is>
+      </c>
+      <c r="J313" t="n">
+        <v>42.35327560751949</v>
+      </c>
+      <c r="K313" t="n">
+        <v>-71.06345772204415</v>
+      </c>
+      <c r="L313" t="n">
+        <v>1324</v>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>Investigate person on Jul 26, 2026, 1324 m from Copley Place (AVERY ST). Case #262064591 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>262064579</t>
+        </is>
+      </c>
+      <c r="E314" s="3" t="n">
+        <v>46230.43402777778</v>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>SICK/INJURED/MEDICAL - PERSON</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr"/>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>NORTHAMPTON ST</t>
+        </is>
+      </c>
+      <c r="J314" t="n">
+        <v>42.33395124839377</v>
+      </c>
+      <c r="K314" t="n">
+        <v>-71.07538938822692</v>
+      </c>
+      <c r="L314" t="n">
+        <v>1530.5</v>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>Sick/injured/medical - person on Jul 27, 2026, 1531 m from Copley Place (NORTHAMPTON ST). Case #262064579 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>262064357</t>
+        </is>
+      </c>
+      <c r="E315" s="3" t="n">
+        <v>46229.72638888889</v>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>LARCENY SHOPLIFTING</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr"/>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>HUNTINGTON AVE</t>
+        </is>
+      </c>
+      <c r="J315" t="n">
+        <v>42.3473097976345</v>
+      </c>
+      <c r="K315" t="n">
+        <v>-71.0791516658207</v>
+      </c>
+      <c r="L315" t="n">
+        <v>129.3</v>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>Larceny shoplifting on Jul 26, 2026, 129 m from Copley Place (HUNTINGTON AVE). Case #262064357 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>262064198</t>
+        </is>
+      </c>
+      <c r="E316" s="3" t="n">
+        <v>46229.16736111111</v>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>TOWED MOTOR VEHICLE</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr"/>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>STUART ST &amp; CHARLES ST S
+BOSTON, MA 02116
+UNITED S</t>
+        </is>
+      </c>
+      <c r="J316" t="n">
+        <v>42.35095701392956</v>
+      </c>
+      <c r="K316" t="n">
+        <v>-71.06685999332976</v>
+      </c>
+      <c r="L316" t="n">
+        <v>960.1</v>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>Towed motor vehicle on Jul 26, 2026, 960 m from Copley Place (STUART ST &amp; CHARLES ST S
+BOSTON, MA 02116
+UNITED S). Case #262064198 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>262064309</t>
+        </is>
+      </c>
+      <c r="E317" s="3" t="n">
+        <v>46229.39444444444</v>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>INVESTIGATE PERSON</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr"/>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>SAINT BOTOLPH ST</t>
+        </is>
+      </c>
+      <c r="J317" t="n">
+        <v>42.34617475544754</v>
+      </c>
+      <c r="K317" t="n">
+        <v>-71.07925920373032</v>
+      </c>
+      <c r="L317" t="n">
+        <v>208.6</v>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>Investigate person on Jul 26, 2026, 209 m from Copley Place (SAINT BOTOLPH ST). Case #262064309 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>262064283</t>
+        </is>
+      </c>
+      <c r="E318" s="3" t="n">
+        <v>46229.51736111111</v>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>LARCENY SHOPLIFTING</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr"/>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>HUNTINGTON AVE</t>
+        </is>
+      </c>
+      <c r="J318" t="n">
+        <v>42.3473097976345</v>
+      </c>
+      <c r="K318" t="n">
+        <v>-71.0791516658207</v>
+      </c>
+      <c r="L318" t="n">
+        <v>129.3</v>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>Larceny shoplifting on Jul 26, 2026, 129 m from Copley Place (HUNTINGTON AVE). Case #262064283 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>262064226</t>
+        </is>
+      </c>
+      <c r="E319" s="3" t="n">
+        <v>46229.375</v>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>M/V ACCIDENT - PROPERTY DAMAGE</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr"/>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>BERKELEY ST &amp; SAINT JAMES AVE
+BOSTON, MA 02116
+UNI</t>
+        </is>
+      </c>
+      <c r="J319" t="n">
+        <v>42.3504290420294</v>
+      </c>
+      <c r="K319" t="n">
+        <v>-71.07264798093048</v>
+      </c>
+      <c r="L319" t="n">
+        <v>515.5</v>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>M/v accident - property damage on Jul 26, 2026, 515 m from Copley Place (BERKELEY ST &amp; SAINT JAMES AVE
+BOSTON, MA 02116
+UNI). Case #262064226 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>262064268</t>
+        </is>
+      </c>
+      <c r="E320" s="3" t="n">
+        <v>46229.48680555556</v>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>LARCENY THEFT FROM BUILDING</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr"/>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>REED ST &amp; E LENOX ST
+ROXBURY, MA 02118
+UNITED STAT</t>
+        </is>
+      </c>
+      <c r="J320" t="n">
+        <v>42.33406097367816</v>
+      </c>
+      <c r="K320" t="n">
+        <v>-71.07756301316894</v>
+      </c>
+      <c r="L320" t="n">
+        <v>1507.2</v>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>Larceny theft from building on Jul 26, 2026, 1507 m from Copley Place (REED ST &amp; E LENOX ST
+ROXBURY, MA 02118
+UNITED STAT). Case #262064268 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>262064394</t>
+        </is>
+      </c>
+      <c r="E321" s="3" t="n">
+        <v>46229.82152777778</v>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>M/V ACCIDENT - OTHER</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr"/>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>HARRISON AVE &amp; PLYMPTON ST
+BOSTON, MA 02118
+UNITED</t>
+        </is>
+      </c>
+      <c r="J321" t="n">
+        <v>42.33973998780085</v>
+      </c>
+      <c r="K321" t="n">
+        <v>-71.0691099454142</v>
+      </c>
+      <c r="L321" t="n">
+        <v>1121.4</v>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>M/v accident - other on Jul 26, 2026, 1121 m from Copley Place (HARRISON AVE &amp; PLYMPTON ST
+BOSTON, MA 02118
+UNITED). Case #262064394 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>262064321</t>
+        </is>
+      </c>
+      <c r="E322" s="3" t="n">
+        <v>46229.59166666667</v>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>M/V - LEAVING SCENE - PROPERTY DAMAGE</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr"/>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J322" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K322" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L322" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>M/v - leaving scene - property damage on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064321 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>262064179</t>
+        </is>
+      </c>
+      <c r="E323" s="3" t="n">
+        <v>46229.07361111111</v>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>INVESTIGATE PROPERTY</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr"/>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>BOYLSTON ST</t>
+        </is>
+      </c>
+      <c r="J323" t="n">
+        <v>42.35234109431519</v>
+      </c>
+      <c r="K323" t="n">
+        <v>-71.06432465046424</v>
+      </c>
+      <c r="L323" t="n">
+        <v>1213.3</v>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>Investigate property on Jul 26, 2026, 1213 m from Copley Place (BOYLSTON ST). Case #262064179 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>262064772</t>
+        </is>
+      </c>
+      <c r="E324" s="3" t="n">
+        <v>46230.82569444444</v>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>LARCENY SHOPLIFTING</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr"/>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>BOYLSTON ST</t>
+        </is>
+      </c>
+      <c r="J324" t="n">
+        <v>42.34862381555496</v>
+      </c>
+      <c r="K324" t="n">
+        <v>-71.08277637086411</v>
+      </c>
+      <c r="L324" t="n">
+        <v>437.3</v>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>Larceny shoplifting on Jul 27, 2026, 437 m from Copley Place (BOYLSTON ST). Case #262064772 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>262064289</t>
+        </is>
+      </c>
+      <c r="E325" s="3" t="n">
+        <v>46229.54583333333</v>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>LARCENY SHOPLIFTING</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr"/>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>BOYLSTON ST</t>
+        </is>
+      </c>
+      <c r="J325" t="n">
+        <v>42.35095908794595</v>
+      </c>
+      <c r="K325" t="n">
+        <v>-71.07412780075079</v>
+      </c>
+      <c r="L325" t="n">
+        <v>470.3</v>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>Larceny shoplifting on Jul 26, 2026, 470 m from Copley Place (BOYLSTON ST). Case #262064289 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>262064298</t>
+        </is>
+      </c>
+      <c r="E326" s="3" t="n">
+        <v>46229.08611111111</v>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>FIREARM/WEAPON - LOST</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr"/>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J326" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K326" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L326" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>Firearm/weapon - lost on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064298 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>262064416</t>
+        </is>
+      </c>
+      <c r="E327" s="3" t="n">
+        <v>46229.87569444445</v>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>ASSAULT - AGGRAVATED</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr"/>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>HUNTINGTON AVE</t>
+        </is>
+      </c>
+      <c r="J327" t="n">
+        <v>42.34221543503831</v>
+      </c>
+      <c r="K327" t="n">
+        <v>-71.08577074656198</v>
+      </c>
+      <c r="L327" t="n">
+        <v>898.8</v>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>Assault - aggravated on Jul 26, 2026, 899 m from Copley Place (HUNTINGTON AVE). Case #262064416 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>262064700</t>
+        </is>
+      </c>
+      <c r="E328" s="3" t="n">
+        <v>46230.71458333333</v>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>BREAKING AND ENTERING (B&amp;E) MOTOR VEHICLE</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr"/>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J328" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K328" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L328" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>Breaking and entering (b&amp;e) motor vehicle on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064700 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>262064491</t>
+        </is>
+      </c>
+      <c r="E329" s="3" t="n">
+        <v>46230.22916666666</v>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>LARCENY ALL OTHERS</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr"/>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>RUTLAND ST</t>
+        </is>
+      </c>
+      <c r="J329" t="n">
+        <v>42.34020387362647</v>
+      </c>
+      <c r="K329" t="n">
+        <v>-71.07645111113312</v>
+      </c>
+      <c r="L329" t="n">
+        <v>829.8</v>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>Larceny all others on Jul 27, 2026, 830 m from Copley Place (RUTLAND ST). Case #262064491 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>262064492</t>
+        </is>
+      </c>
+      <c r="E330" s="3" t="n">
+        <v>46230.10972222222</v>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>VANDALISM</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr"/>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>NORTHAMPTON ST</t>
+        </is>
+      </c>
+      <c r="J330" t="n">
+        <v>42.33798932384219</v>
+      </c>
+      <c r="K330" t="n">
+        <v>-71.08003745874711</v>
+      </c>
+      <c r="L330" t="n">
+        <v>1088.4</v>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>Vandalism on Jul 27, 2026, 1088 m from Copley Place (NORTHAMPTON ST). Case #262064492 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>262064766</t>
+        </is>
+      </c>
+      <c r="E331" s="3" t="n">
+        <v>46230.75416666667</v>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>PROPERTY - LOST/ MISSING</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr"/>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>COLUMBUS AVE</t>
+        </is>
+      </c>
+      <c r="J331" t="n">
+        <v>42.34294800069079</v>
+      </c>
+      <c r="K331" t="n">
+        <v>-71.07888700104606</v>
+      </c>
+      <c r="L331" t="n">
+        <v>529.1</v>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>Property - lost/ missing on Jul 27, 2026, 529 m from Copley Place (COLUMBUS AVE). Case #262064766 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>262064548</t>
+        </is>
+      </c>
+      <c r="E332" s="3" t="n">
+        <v>46230.44236111111</v>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>M/V - LEAVING SCENE - PROPERTY DAMAGE</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr"/>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J332" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K332" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L332" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>M/v - leaving scene - property damage on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064548 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>262064504</t>
+        </is>
+      </c>
+      <c r="E333" s="3" t="n">
+        <v>46230.34791666667</v>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>LARCENY SHOPLIFTING</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr"/>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>CHARLES ST</t>
+        </is>
+      </c>
+      <c r="J333" t="n">
+        <v>42.36064469554803</v>
+      </c>
+      <c r="K333" t="n">
+        <v>-71.07086192011141</v>
+      </c>
+      <c r="L333" t="n">
+        <v>1552</v>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>Larceny shoplifting on Jul 27, 2026, 1552 m from Copley Place (CHARLES ST). Case #262064504 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>262064506</t>
+        </is>
+      </c>
+      <c r="E334" s="3" t="n">
+        <v>46230.34375</v>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>SICK ASSIST</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr"/>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>BOYLSTON ST</t>
+        </is>
+      </c>
+      <c r="J334" t="n">
+        <v>42.35037869977646</v>
+      </c>
+      <c r="K334" t="n">
+        <v>-71.07626098382806</v>
+      </c>
+      <c r="L334" t="n">
+        <v>327.3</v>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>Sick assist on Jul 27, 2026, 327 m from Copley Place (BOYLSTON ST). Case #262064506 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>262064752</t>
+        </is>
+      </c>
+      <c r="E335" s="3" t="n">
+        <v>46230.79166666666</v>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>STOLEN PROPERTY - BUYING / RECEIVING / POSSESSING</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr"/>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>HUDSON ST</t>
+        </is>
+      </c>
+      <c r="J335" t="n">
+        <v>42.35074197291232</v>
+      </c>
+      <c r="K335" t="n">
+        <v>-71.06006134581432</v>
+      </c>
+      <c r="L335" t="n">
+        <v>1485.3</v>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>Stolen property - buying / receiving / possessing on Jul 27, 2026, 1485 m from Copley Place (HUDSON ST). Case #262064752 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>262064383</t>
+        </is>
+      </c>
+      <c r="E336" s="3" t="n">
+        <v>46229.79375</v>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>M/V ACCIDENT - INVOLVING PEDESTRIAN - INJURY</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr"/>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>BOYLSTON ST &amp; DALTON ST
+BOSTON, MA 02115
+UNITED ST</t>
+        </is>
+      </c>
+      <c r="J336" t="n">
+        <v>42.34787097987171</v>
+      </c>
+      <c r="K336" t="n">
+        <v>-71.08556796747074</v>
+      </c>
+      <c r="L336" t="n">
+        <v>652.7</v>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>M/v accident - involving pedestrian - injury on Jul 26, 2026, 653 m from Copley Place (BOYLSTON ST &amp; DALTON ST
+BOSTON, MA 02115
+UNITED ST). Case #262064383 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>262064391</t>
+        </is>
+      </c>
+      <c r="E337" s="3" t="n">
+        <v>46229.83125</v>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>DRUGS - POSSESSION/ SALE/ MANUFACTURING/ USE</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr"/>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOYLSTON ST &amp; BOYLSTON SQ
+BOSTON, MA 02111
+UNITED </t>
+        </is>
+      </c>
+      <c r="J337" t="n">
+        <v>42.35231098936428</v>
+      </c>
+      <c r="K337" t="n">
+        <v>-71.06350996526169</v>
+      </c>
+      <c r="L337" t="n">
+        <v>1272.6</v>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>Drugs - possession/ sale/ manufacturing/ use on Jul 26, 2026, 1273 m from Copley Place (BOYLSTON ST &amp; BOYLSTON SQ
+BOSTON, MA 02111
+UNITED ). Case #262064391 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>262064802</t>
+        </is>
+      </c>
+      <c r="E338" s="3" t="n">
+        <v>46230.89583333334</v>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>LARCENY SHOPLIFTING</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr"/>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>BOYLSTON ST</t>
+        </is>
+      </c>
+      <c r="J338" t="n">
+        <v>42.34862381555496</v>
+      </c>
+      <c r="K338" t="n">
+        <v>-71.08277637086411</v>
+      </c>
+      <c r="L338" t="n">
+        <v>437.3</v>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>Larceny shoplifting on Jul 27, 2026, 437 m from Copley Place (BOYLSTON ST). Case #262064802 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>262064409</t>
+        </is>
+      </c>
+      <c r="E339" s="3" t="n">
+        <v>46229.85833333333</v>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>SICK ASSIST</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr"/>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>OXFORD ST</t>
+        </is>
+      </c>
+      <c r="J339" t="n">
+        <v>42.35193460488232</v>
+      </c>
+      <c r="K339" t="n">
+        <v>-71.06048592223925</v>
+      </c>
+      <c r="L339" t="n">
+        <v>1488.7</v>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>Sick assist on Jul 26, 2026, 1489 m from Copley Place (OXFORD ST). Case #262064409 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>262064318</t>
+        </is>
+      </c>
+      <c r="E340" s="3" t="n">
+        <v>46229.53958333333</v>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>INVESTIGATE PERSON</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr"/>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>SHAWMUT AVE</t>
+        </is>
+      </c>
+      <c r="J340" t="n">
+        <v>42.34319452771496</v>
+      </c>
+      <c r="K340" t="n">
+        <v>-71.06880536524001</v>
+      </c>
+      <c r="L340" t="n">
+        <v>876.3</v>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>Investigate person on Jul 26, 2026, 876 m from Copley Place (SHAWMUT AVE). Case #262064318 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>262064412</t>
+        </is>
+      </c>
+      <c r="E341" s="3" t="n">
+        <v>46229.87638888889</v>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>SICK/INJURED/MEDICAL - PERSON</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr"/>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>TREMONT ST</t>
+        </is>
+      </c>
+      <c r="J341" t="n">
+        <v>42.35428377241487</v>
+      </c>
+      <c r="K341" t="n">
+        <v>-71.06380403747467</v>
+      </c>
+      <c r="L341" t="n">
+        <v>1356.9</v>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>Sick/injured/medical - person on Jul 26, 2026, 1357 m from Copley Place (TREMONT ST). Case #262064412 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>262064362</t>
+        </is>
+      </c>
+      <c r="E342" s="3" t="n">
+        <v>46229.64305555556</v>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>M/V ACCIDENT - INVOLVING PEDESTRIAN - INJURY</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr"/>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>DARTMOUTH ST</t>
+        </is>
+      </c>
+      <c r="J342" t="n">
+        <v>42.35029374297969</v>
+      </c>
+      <c r="K342" t="n">
+        <v>-71.07744671381569</v>
+      </c>
+      <c r="L342" t="n">
+        <v>298.2</v>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>M/v accident - involving pedestrian - injury on Jul 26, 2026, 298 m from Copley Place (DARTMOUTH ST). Case #262064362 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>262064307</t>
+        </is>
+      </c>
+      <c r="E343" s="3" t="n">
+        <v>46229.59027777778</v>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>SICK ASSIST</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr"/>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>TREMONT ST &amp; TEMPLE PL
+BOSTON, MA 02111
+UNITED STA</t>
+        </is>
+      </c>
+      <c r="J343" t="n">
+        <v>42.35561100811422</v>
+      </c>
+      <c r="K343" t="n">
+        <v>-71.06289400004533</v>
+      </c>
+      <c r="L343" t="n">
+        <v>1502.5</v>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>Sick assist on Jul 26, 2026, 1502 m from Copley Place (TREMONT ST &amp; TEMPLE PL
+BOSTON, MA 02111
+UNITED STA). Case #262064307 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>262064419</t>
+        </is>
+      </c>
+      <c r="E344" s="3" t="n">
+        <v>46229.90138888889</v>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>HARASSMENT/ CRIMINAL HARASSMENT</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr"/>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>NASSAU ST</t>
+        </is>
+      </c>
+      <c r="J344" t="n">
+        <v>42.34880604399623</v>
+      </c>
+      <c r="K344" t="n">
+        <v>-71.06285446968663</v>
+      </c>
+      <c r="L344" t="n">
+        <v>1221.7</v>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>Harassment/ criminal harassment on Jul 26, 2026, 1222 m from Copley Place (NASSAU ST). Case #262064419 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>262064339</t>
+        </is>
+      </c>
+      <c r="E345" s="3" t="n">
+        <v>46229.63333333333</v>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>ASSAULT - AGGRAVATED</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr"/>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J345" t="n">
+        <v>42.33511903946613</v>
+      </c>
+      <c r="K345" t="n">
+        <v>-71.07491709613726</v>
+      </c>
+      <c r="L345" t="n">
+        <v>1407.3</v>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>Assault - aggravated on Jul 26, 2026, 1407 m from Copley Place (HARRISON AVE). Case #262064339 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>262064236</t>
+        </is>
+      </c>
+      <c r="E346" s="3" t="n">
+        <v>46229.37638888889</v>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>SICK ASSIST</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr"/>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>TREMONT ST</t>
+        </is>
+      </c>
+      <c r="J346" t="n">
+        <v>42.34470135794417</v>
+      </c>
+      <c r="K346" t="n">
+        <v>-71.0703760849388</v>
+      </c>
+      <c r="L346" t="n">
+        <v>678.7</v>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>Sick assist on Jul 26, 2026, 679 m from Copley Place (TREMONT ST). Case #262064236 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>262064234</t>
+        </is>
+      </c>
+      <c r="E347" s="3" t="n">
+        <v>46229.31944444445</v>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>INVESTIGATE PERSON</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr"/>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>SAINT JAMES AVE</t>
+        </is>
+      </c>
+      <c r="J347" t="n">
+        <v>42.34947585701249</v>
+      </c>
+      <c r="K347" t="n">
+        <v>-71.07640149637847</v>
+      </c>
+      <c r="L347" t="n">
+        <v>230.3</v>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>Investigate person on Jul 26, 2026, 230 m from Copley Place (SAINT JAMES AVE). Case #262064234 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>NORFOLKPO</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Norfolk Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>NORFOLKPO:r7bn-2egr</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>260730001961</t>
+        </is>
+      </c>
+      <c r="E348" s="3" t="n">
+        <v>46233</v>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>SHOOT INTO OCCUPIED DWELLING</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr"/>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>1400 DURE RD</t>
+        </is>
+      </c>
+      <c r="J348" t="n">
+        <v>36.872248203692</v>
+      </c>
+      <c r="K348" t="n">
+        <v>-76.209734788037</v>
+      </c>
+      <c r="L348" t="n">
+        <v>1387.8</v>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>Shoot into occupied dwelling on Jul 30, 2026, 1388 m from Norfolk Premium Outlets (1400 DURE RD). Case #260730001961 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>NORFOLKPO</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Norfolk Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>NORFOLKPO:r7bn-2egr</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>260730001974</t>
+        </is>
+      </c>
+      <c r="E349" s="3" t="n">
+        <v>46233</v>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>HIT &amp; RUN - PERSONAL INJURY</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr"/>
+      <c r="I349" t="inlineStr">
+        <is>
           <t>2500 MILITARY HIGHWAY</t>
         </is>
       </c>
-      <c r="J288" t="n">
+      <c r="J349" t="n">
         <v>36.879766119132</v>
       </c>
-      <c r="K288" t="n">
+      <c r="K349" t="n">
         <v>-76.212427576002</v>
       </c>
-      <c r="L288" t="n">
+      <c r="L349" t="n">
         <v>1118.9</v>
       </c>
-      <c r="M288" t="inlineStr">
+      <c r="M349" t="inlineStr">
         <is>
           <t>Hit &amp; run - personal injury on Jul 30, 2026, 1119 m from Norfolk Premium Outlets (2500 MILITARY HIGHWAY). Case #260730001974 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>NORFOLKPO</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Norfolk Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>NORFOLKPO:r7bn-2egr</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>260726001633</t>
+        </is>
+      </c>
+      <c r="E350" s="3" t="n">
+        <v>46229</v>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>ABDUCTION</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr"/>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>1500 MILITARY HIGHWAY</t>
+        </is>
+      </c>
+      <c r="J350" t="n">
+        <v>36.875468779419</v>
+      </c>
+      <c r="K350" t="n">
+        <v>-76.210483896081</v>
+      </c>
+      <c r="L350" t="n">
+        <v>1176.8</v>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>Abduction on Jul 26, 2026, 1177 m from Norfolk Premium Outlets (1500 MILITARY HIGHWAY). Case #260726001633 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M288"/>
+  <autoFilter ref="A1:M350"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20068,7 +23490,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20091,7 +23513,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01 04:58:47.637225+00:00</t>
+          <t>2026-08-01 05:00:58.075328+00:00</t>
         </is>
       </c>
     </row>
@@ -20123,7 +23545,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-25 04:58:47.637225+00:00</t>
+          <t>2026-07-25 05:00:58.075328+00:00</t>
         </is>
       </c>
     </row>
@@ -20134,7 +23556,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>287</v>
+        <v>349</v>
       </c>
     </row>
     <row r="7">
@@ -20144,7 +23566,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
@@ -20419,7 +23841,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FAILED fetched=0 truncated=False CKAN fetch failed for b973d8cb-eeb2-4e7e-99da-c92938efc9c0: HTTP 403 for https://data.boston.gov/api/3/action/datastore_search_sql?sql=SELECT+%2A+FROM+%22b973d8cb-eeb2-4e7e-99da-c92938efc9c0%22+WHERE+CAST%28NULLIF%28%22Lat%22%2C+%27%27%29+AS+float8%29+BETWEEN+42.3332261543053+AND+42.3620044456947+AND+CAST%28NULLIF%28%22Long%22%2C+%27%27%29+AS+float8%29+BETWEEN+-71.09710221911952+AND+-71.05816378088049+AND+%22OCCURRED_ON_DATE%22+%3E%3D+%272026-07-25T04%3A58%3A47%27+LIMIT+5000 :: {"help": "https://data.boston.gov/api/3/action/help_show?name=datastore_search_sql", "error": {"__type": "Authorization Error", "message": "Access denied: {'permissions': ['Not authorized to call function NULLIF']}"}, "success": false}</t>
+          <t>OK fetched=67 truncated=False</t>
         </is>
       </c>
     </row>
@@ -20431,7 +23853,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FAILED fetched=0 truncated=False CKAN fetch failed for b973d8cb-eeb2-4e7e-99da-c92938efc9c0: HTTP 403 for https://data.boston.gov/api/3/action/datastore_search_sql?sql=SELECT+%2A+FROM+%22b973d8cb-eeb2-4e7e-99da-c92938efc9c0%22+WHERE+CAST%28NULLIF%28%22Lat%22%2C+%27%27%29+AS+float8%29+BETWEEN+42.3071233543053+AND+42.3359016456947+AND+CAST%28NULLIF%28%22Long%22%2C+%27%27%29+AS+float8%29+BETWEEN+-71.19513294012805+AND+-71.15621065987196+AND+%22OCCURRED_ON_DATE%22+%3E%3D+%272026-07-25T04%3A58%3A47%27+LIMIT+5000 :: {"help": "https://data.boston.gov/api/3/action/help_show?name=datastore_search_sql", "error": {"__type": "Authorization Error", "message": "Access denied: {'permissions': ['Not authorized to call function NULLIF']}"}, "success": false}</t>
+          <t>OK fetched=0 truncated=False</t>
         </is>
       </c>
     </row>

--- a/reports/latest/blotter_report.xlsx
+++ b/reports/latest/blotter_report.xlsx
@@ -19940,40 +19940,40 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>262064284</t>
+          <t>262064179</t>
         </is>
       </c>
       <c r="E287" s="3" t="n">
-        <v>46229.54305555556</v>
+        <v>46229.07361111111</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>M/V ACCIDENT - INVOLVING PEDESTRIAN - INJURY</t>
+          <t>INVESTIGATE PROPERTY</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H287" t="inlineStr"/>
       <c r="I287" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>BOYLSTON ST</t>
         </is>
       </c>
       <c r="J287" t="n">
-        <v>42.33954198983015</v>
+        <v>42.35234109431519</v>
       </c>
       <c r="K287" t="n">
-        <v>-71.06940876967543</v>
+        <v>-71.06432465046424</v>
       </c>
       <c r="L287" t="n">
-        <v>1123.7</v>
+        <v>1213.3</v>
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>M/v accident - involving pedestrian - injury on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064284 (use for a records request — full narratives are not published in open data).</t>
+          <t>Investigate property on Jul 26, 2026, 1213 m from Copley Place (BOYLSTON ST). Case #262064179 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -19995,15 +19995,15 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>262064275</t>
+          <t>262064284</t>
         </is>
       </c>
       <c r="E288" s="3" t="n">
-        <v>46229.51111111111</v>
+        <v>46229.54305555556</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>FORGERY / COUNTERFEITING</t>
+          <t>M/V ACCIDENT - INVOLVING PEDESTRIAN - INJURY</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -20028,7 +20028,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Forgery / counterfeiting on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064275 (use for a records request — full narratives are not published in open data).</t>
+          <t>M/v accident - involving pedestrian - injury on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064284 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20050,15 +20050,15 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>262064650</t>
+          <t>262064275</t>
         </is>
       </c>
       <c r="E289" s="3" t="n">
-        <v>46230.61875</v>
+        <v>46229.51111111111</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>M/V ACCIDENT - INVOLVING BICYCLE - INJURY</t>
+          <t>FORGERY / COUNTERFEITING</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -20068,22 +20068,77 @@
       </c>
       <c r="H289" t="inlineStr"/>
       <c r="I289" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J289" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K289" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L289" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>Forgery / counterfeiting on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064275 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>262064650</t>
+        </is>
+      </c>
+      <c r="E290" s="3" t="n">
+        <v>46230.61875</v>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>M/V ACCIDENT - INVOLVING BICYCLE - INJURY</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr"/>
+      <c r="I290" t="inlineStr">
         <is>
           <t>MASSACHUSETTS AVE &amp; TREMONT ST
 BOSTON, MA 02118
 UN</t>
         </is>
       </c>
-      <c r="J289" t="n">
+      <c r="J290" t="n">
         <v>42.33929095757131</v>
       </c>
-      <c r="K289" t="n">
+      <c r="K290" t="n">
         <v>-71.08041395047391</v>
       </c>
-      <c r="L289" t="n">
+      <c r="L290" t="n">
         <v>953.4</v>
       </c>
-      <c r="M289" t="inlineStr">
+      <c r="M290" t="inlineStr">
         <is>
           <t>M/v accident - involving bicycle - injury on Jul 27, 2026, 953 m from Copley Place (MASSACHUSETTS AVE &amp; TREMONT ST
 BOSTON, MA 02118
@@ -20091,61 +20146,6 @@
         </is>
       </c>
     </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>262064295</t>
-        </is>
-      </c>
-      <c r="E290" s="3" t="n">
-        <v>46229.54791666667</v>
-      </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>SICK ASSIST</t>
-        </is>
-      </c>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H290" t="inlineStr"/>
-      <c r="I290" t="inlineStr">
-        <is>
-          <t>BOYLSTON ST</t>
-        </is>
-      </c>
-      <c r="J290" t="n">
-        <v>42.34862381555496</v>
-      </c>
-      <c r="K290" t="n">
-        <v>-71.08277637086411</v>
-      </c>
-      <c r="L290" t="n">
-        <v>437.3</v>
-      </c>
-      <c r="M290" t="inlineStr">
-        <is>
-          <t>Sick assist on Jul 26, 2026, 437 m from Copley Place (BOYLSTON ST). Case #262064295 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
@@ -20164,15 +20164,15 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>262064382</t>
+          <t>262064295</t>
         </is>
       </c>
       <c r="E291" s="3" t="n">
-        <v>46229.78680555556</v>
+        <v>46229.54791666667</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>VERBAL DISPUTE</t>
+          <t>SICK ASSIST</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -20183,21 +20183,21 @@
       <c r="H291" t="inlineStr"/>
       <c r="I291" t="inlineStr">
         <is>
-          <t>HUDSON ST</t>
+          <t>BOYLSTON ST</t>
         </is>
       </c>
       <c r="J291" t="n">
-        <v>42.34976401607222</v>
+        <v>42.34862381555496</v>
       </c>
       <c r="K291" t="n">
-        <v>-71.06045076420118</v>
+        <v>-71.08277637086411</v>
       </c>
       <c r="L291" t="n">
-        <v>1432.1</v>
+        <v>437.3</v>
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Verbal dispute on Jul 26, 2026, 1432 m from Copley Place (HUDSON ST). Case #262064382 (use for a records request — full narratives are not published in open data).</t>
+          <t>Sick assist on Jul 26, 2026, 437 m from Copley Place (BOYLSTON ST). Case #262064295 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20219,40 +20219,40 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>262064432</t>
+          <t>262064382</t>
         </is>
       </c>
       <c r="E292" s="3" t="n">
-        <v>46229.91666666666</v>
+        <v>46229.78680555556</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>ROBBERY</t>
+          <t>VERBAL DISPUTE</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H292" t="inlineStr"/>
       <c r="I292" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>HUDSON ST</t>
         </is>
       </c>
       <c r="J292" t="n">
-        <v>42.33954198983015</v>
+        <v>42.34976401607222</v>
       </c>
       <c r="K292" t="n">
-        <v>-71.06940876967543</v>
+        <v>-71.06045076420118</v>
       </c>
       <c r="L292" t="n">
-        <v>1123.7</v>
+        <v>1432.1</v>
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Robbery on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064432 (use for a records request — full narratives are not published in open data).</t>
+          <t>Verbal dispute on Jul 26, 2026, 1432 m from Copley Place (HUDSON ST). Case #262064382 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20274,40 +20274,40 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>262064822</t>
+          <t>262064432</t>
         </is>
       </c>
       <c r="E293" s="3" t="n">
-        <v>46230.83541666667</v>
+        <v>46229.91666666666</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>INVESTIGATE PERSON</t>
+          <t>ROBBERY</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H293" t="inlineStr"/>
       <c r="I293" t="inlineStr">
         <is>
-          <t>COLUMBUS SQ</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J293" t="n">
-        <v>42.34332879779392</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K293" t="n">
-        <v>-71.07788857963692</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L293" t="n">
-        <v>477.1</v>
+        <v>1123.7</v>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Investigate person on Jul 27, 2026, 477 m from Copley Place (COLUMBUS SQ). Case #262064822 (use for a records request — full narratives are not published in open data).</t>
+          <t>Robbery on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064432 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20329,11 +20329,11 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>262064697</t>
+          <t>262064822</t>
         </is>
       </c>
       <c r="E294" s="3" t="n">
-        <v>46230.70277777778</v>
+        <v>46230.83541666667</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -20348,21 +20348,21 @@
       <c r="H294" t="inlineStr"/>
       <c r="I294" t="inlineStr">
         <is>
-          <t>MASSACHUSETTS AVE</t>
+          <t>COLUMBUS SQ</t>
         </is>
       </c>
       <c r="J294" t="n">
-        <v>42.34867437636976</v>
+        <v>42.34332879779392</v>
       </c>
       <c r="K294" t="n">
-        <v>-71.08841866225799</v>
+        <v>-71.07788857963692</v>
       </c>
       <c r="L294" t="n">
-        <v>894.2</v>
+        <v>477.1</v>
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Investigate person on Jul 27, 2026, 894 m from Copley Place (MASSACHUSETTS AVE). Case #262064697 (use for a records request — full narratives are not published in open data).</t>
+          <t>Investigate person on Jul 27, 2026, 477 m from Copley Place (COLUMBUS SQ). Case #262064822 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20384,40 +20384,40 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>262064696</t>
+          <t>262064697</t>
         </is>
       </c>
       <c r="E295" s="3" t="n">
-        <v>46230.57777777778</v>
+        <v>46230.70277777778</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>LARCENY THEFT FROM BUILDING</t>
+          <t>INVESTIGATE PERSON</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H295" t="inlineStr"/>
       <c r="I295" t="inlineStr">
         <is>
-          <t>LINCOLN ST</t>
+          <t>MASSACHUSETTS AVE</t>
         </is>
       </c>
       <c r="J295" t="n">
-        <v>42.35043296884182</v>
+        <v>42.34867437636976</v>
       </c>
       <c r="K295" t="n">
-        <v>-71.05873157807835</v>
+        <v>-71.08841866225799</v>
       </c>
       <c r="L295" t="n">
-        <v>1584.6</v>
+        <v>894.2</v>
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Larceny theft from building on Jul 27, 2026, 1585 m from Copley Place (LINCOLN ST). Case #262064696 (use for a records request — full narratives are not published in open data).</t>
+          <t>Investigate person on Jul 27, 2026, 894 m from Copley Place (MASSACHUSETTS AVE). Case #262064697 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20439,15 +20439,15 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>262064796</t>
+          <t>262064696</t>
         </is>
       </c>
       <c r="E296" s="3" t="n">
-        <v>46230.75</v>
+        <v>46230.57777777778</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>PROPERTY - LOST/ MISSING</t>
+          <t>LARCENY THEFT FROM BUILDING</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -20458,21 +20458,21 @@
       <c r="H296" t="inlineStr"/>
       <c r="I296" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>LINCOLN ST</t>
         </is>
       </c>
       <c r="J296" t="n">
-        <v>42.33954198983015</v>
+        <v>42.35043296884182</v>
       </c>
       <c r="K296" t="n">
-        <v>-71.06940876967543</v>
+        <v>-71.05873157807835</v>
       </c>
       <c r="L296" t="n">
-        <v>1123.7</v>
+        <v>1584.6</v>
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Property - lost/ missing on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064796 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny theft from building on Jul 27, 2026, 1585 m from Copley Place (LINCOLN ST). Case #262064696 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20494,40 +20494,40 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>262064756</t>
+          <t>262064796</t>
         </is>
       </c>
       <c r="E297" s="3" t="n">
-        <v>46230.80347222222</v>
+        <v>46230.75</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>ASSAULT - SIMPLE</t>
+          <t>PROPERTY - LOST/ MISSING</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H297" t="inlineStr"/>
       <c r="I297" t="inlineStr">
         <is>
-          <t>MASSACHUSETTS AVE</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J297" t="n">
-        <v>42.34439568415441</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K297" t="n">
-        <v>-71.08632016344815</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L297" t="n">
-        <v>798.7</v>
+        <v>1123.7</v>
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Assault - simple on Jul 27, 2026, 799 m from Copley Place (MASSACHUSETTS AVE). Case #262064756 (use for a records request — full narratives are not published in open data).</t>
+          <t>Property - lost/ missing on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064796 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20549,40 +20549,40 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>262064716</t>
+          <t>262064756</t>
         </is>
       </c>
       <c r="E298" s="3" t="n">
-        <v>46230.72638888889</v>
+        <v>46230.80347222222</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>LARCENY SHOPLIFTING</t>
+          <t>ASSAULT - SIMPLE</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H298" t="inlineStr"/>
       <c r="I298" t="inlineStr">
         <is>
-          <t>NEWBURY ST</t>
+          <t>MASSACHUSETTS AVE</t>
         </is>
       </c>
       <c r="J298" t="n">
-        <v>42.35059716982988</v>
+        <v>42.34439568415441</v>
       </c>
       <c r="K298" t="n">
-        <v>-71.07881030689927</v>
+        <v>-71.08632016344815</v>
       </c>
       <c r="L298" t="n">
-        <v>345.4</v>
+        <v>798.7</v>
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Larceny shoplifting on Jul 27, 2026, 345 m from Copley Place (NEWBURY ST). Case #262064716 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault - simple on Jul 27, 2026, 799 m from Copley Place (MASSACHUSETTS AVE). Case #262064756 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20604,40 +20604,40 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>262064587</t>
+          <t>262064716</t>
         </is>
       </c>
       <c r="E299" s="3" t="n">
-        <v>46230.5</v>
+        <v>46230.72638888889</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>ASSAULT - AGGRAVATED</t>
+          <t>LARCENY SHOPLIFTING</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H299" t="inlineStr"/>
       <c r="I299" t="inlineStr">
         <is>
-          <t>MASSACHUSETTS AVE</t>
+          <t>NEWBURY ST</t>
         </is>
       </c>
       <c r="J299" t="n">
-        <v>42.3342194178955</v>
+        <v>42.35059716982988</v>
       </c>
       <c r="K299" t="n">
-        <v>-71.07434615707857</v>
+        <v>-71.07881030689927</v>
       </c>
       <c r="L299" t="n">
-        <v>1513.9</v>
+        <v>345.4</v>
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Assault - aggravated on Jul 27, 2026, 1514 m from Copley Place (MASSACHUSETTS AVE). Case #262064587 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny shoplifting on Jul 27, 2026, 345 m from Copley Place (NEWBURY ST). Case #262064716 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20659,40 +20659,40 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>262064392</t>
+          <t>262064587</t>
         </is>
       </c>
       <c r="E300" s="3" t="n">
-        <v>46229.82222222222</v>
+        <v>46230.5</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>M/V ACCIDENT - OTHER</t>
+          <t>ASSAULT - AGGRAVATED</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H300" t="inlineStr"/>
       <c r="I300" t="inlineStr">
         <is>
-          <t>TYLER ST</t>
+          <t>MASSACHUSETTS AVE</t>
         </is>
       </c>
       <c r="J300" t="n">
-        <v>42.3509005960865</v>
+        <v>42.3342194178955</v>
       </c>
       <c r="K300" t="n">
-        <v>-71.06068690177561</v>
+        <v>-71.07434615707857</v>
       </c>
       <c r="L300" t="n">
-        <v>1439.7</v>
+        <v>1513.9</v>
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>M/v accident - other on Jul 26, 2026, 1440 m from Copley Place (TYLER ST). Case #262064392 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault - aggravated on Jul 27, 2026, 1514 m from Copley Place (MASSACHUSETTS AVE). Case #262064587 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20714,15 +20714,15 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>262064350</t>
+          <t>262064392</t>
         </is>
       </c>
       <c r="E301" s="3" t="n">
-        <v>46229.70486111111</v>
+        <v>46229.82222222222</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>INVESTIGATE PERSON</t>
+          <t>M/V ACCIDENT - OTHER</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
@@ -20733,21 +20733,21 @@
       <c r="H301" t="inlineStr"/>
       <c r="I301" t="inlineStr">
         <is>
-          <t>HUNTINGTON AVE</t>
+          <t>TYLER ST</t>
         </is>
       </c>
       <c r="J301" t="n">
-        <v>42.3473097976345</v>
+        <v>42.3509005960865</v>
       </c>
       <c r="K301" t="n">
-        <v>-71.0791516658207</v>
+        <v>-71.06068690177561</v>
       </c>
       <c r="L301" t="n">
-        <v>129.3</v>
+        <v>1439.7</v>
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Investigate person on Jul 26, 2026, 129 m from Copley Place (HUNTINGTON AVE). Case #262064350 (use for a records request — full narratives are not published in open data).</t>
+          <t>M/v accident - other on Jul 26, 2026, 1440 m from Copley Place (TYLER ST). Case #262064392 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20769,40 +20769,40 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>262064616</t>
+          <t>262064350</t>
         </is>
       </c>
       <c r="E302" s="3" t="n">
-        <v>46230.50347222222</v>
+        <v>46229.70486111111</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>DRUGS - POSSESSION/ SALE/ MANUFACTURING/ USE</t>
+          <t>INVESTIGATE PERSON</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>QUALITY_OF_LIFE</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H302" t="inlineStr"/>
       <c r="I302" t="inlineStr">
         <is>
-          <t>BOYLSTON SQ</t>
+          <t>HUNTINGTON AVE</t>
         </is>
       </c>
       <c r="J302" t="n">
-        <v>42.35197501205302</v>
+        <v>42.3473097976345</v>
       </c>
       <c r="K302" t="n">
-        <v>-71.06332910808086</v>
+        <v>-71.0791516658207</v>
       </c>
       <c r="L302" t="n">
-        <v>1271.5</v>
+        <v>129.3</v>
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Drugs - possession/ sale/ manufacturing/ use on Jul 27, 2026, 1272 m from Copley Place (BOYLSTON SQ). Case #262064616 (use for a records request — full narratives are not published in open data).</t>
+          <t>Investigate person on Jul 26, 2026, 129 m from Copley Place (HUNTINGTON AVE). Case #262064350 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20824,40 +20824,40 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>262064640</t>
+          <t>262064616</t>
         </is>
       </c>
       <c r="E303" s="3" t="n">
-        <v>46230.3125</v>
+        <v>46230.50347222222</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>INVESTIGATE PERSON</t>
+          <t>DRUGS - POSSESSION/ SALE/ MANUFACTURING/ USE</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>QUALITY_OF_LIFE</t>
         </is>
       </c>
       <c r="H303" t="inlineStr"/>
       <c r="I303" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>BOYLSTON SQ</t>
         </is>
       </c>
       <c r="J303" t="n">
-        <v>42.33954198983015</v>
+        <v>42.35197501205302</v>
       </c>
       <c r="K303" t="n">
-        <v>-71.06940876967543</v>
+        <v>-71.06332910808086</v>
       </c>
       <c r="L303" t="n">
-        <v>1123.7</v>
+        <v>1271.5</v>
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Investigate person on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064640 (use for a records request — full narratives are not published in open data).</t>
+          <t>Drugs - possession/ sale/ manufacturing/ use on Jul 27, 2026, 1272 m from Copley Place (BOYLSTON SQ). Case #262064616 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20879,40 +20879,40 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>262064573</t>
+          <t>262064640</t>
         </is>
       </c>
       <c r="E304" s="3" t="n">
-        <v>46230.45833333334</v>
+        <v>46230.3125</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>SICK ASSIST - DRUG RELATED ILLNESS</t>
+          <t>INVESTIGATE PERSON</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>QUALITY_OF_LIFE</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H304" t="inlineStr"/>
       <c r="I304" t="inlineStr">
         <is>
-          <t>ALBANY ST</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J304" t="n">
-        <v>42.33428840659414</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K304" t="n">
-        <v>-71.07239517543796</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L304" t="n">
-        <v>1543.1</v>
+        <v>1123.7</v>
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Sick assist - drug related illness on Jul 27, 2026, 1543 m from Copley Place (ALBANY ST). Case #262064573 (use for a records request — full narratives are not published in open data).</t>
+          <t>Investigate person on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064640 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20934,40 +20934,40 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>262064608</t>
+          <t>262064573</t>
         </is>
       </c>
       <c r="E305" s="3" t="n">
-        <v>46230</v>
+        <v>46230.45833333334</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>THREATS TO DO BODILY HARM</t>
+          <t>SICK ASSIST - DRUG RELATED ILLNESS</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>QUALITY_OF_LIFE</t>
         </is>
       </c>
       <c r="H305" t="inlineStr"/>
       <c r="I305" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>ALBANY ST</t>
         </is>
       </c>
       <c r="J305" t="n">
-        <v>42.33954198983015</v>
+        <v>42.33428840659414</v>
       </c>
       <c r="K305" t="n">
-        <v>-71.06940876967543</v>
+        <v>-71.07239517543796</v>
       </c>
       <c r="L305" t="n">
-        <v>1123.7</v>
+        <v>1543.1</v>
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Threats to do bodily harm on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064608 (use for a records request — full narratives are not published in open data).</t>
+          <t>Sick assist - drug related illness on Jul 27, 2026, 1543 m from Copley Place (ALBANY ST). Case #262064573 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20989,40 +20989,40 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>262064378</t>
+          <t>262064608</t>
         </is>
       </c>
       <c r="E306" s="3" t="n">
-        <v>46229.79097222222</v>
+        <v>46230</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>LARCENY ALL OTHERS</t>
+          <t>THREATS TO DO BODILY HARM</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H306" t="inlineStr"/>
       <c r="I306" t="inlineStr">
         <is>
-          <t>W CONCORD ST</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J306" t="n">
-        <v>42.33961961800693</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K306" t="n">
-        <v>-71.07699236739417</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L306" t="n">
-        <v>890.6</v>
+        <v>1123.7</v>
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Larceny all others on Jul 26, 2026, 891 m from Copley Place (W CONCORD ST). Case #262064378 (use for a records request — full narratives are not published in open data).</t>
+          <t>Threats to do bodily harm on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064608 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21044,40 +21044,40 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>262064152</t>
+          <t>262064378</t>
         </is>
       </c>
       <c r="E307" s="3" t="n">
-        <v>46229.01458333333</v>
+        <v>46229.79097222222</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>NOISY PARTY/RADIO-NO ARREST</t>
+          <t>LARCENY ALL OTHERS</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H307" t="inlineStr"/>
       <c r="I307" t="inlineStr">
         <is>
-          <t>PHILLIPS ST</t>
+          <t>W CONCORD ST</t>
         </is>
       </c>
       <c r="J307" t="n">
-        <v>42.36027809483424</v>
+        <v>42.33961961800693</v>
       </c>
       <c r="K307" t="n">
-        <v>-71.06899804851336</v>
+        <v>-71.07699236739417</v>
       </c>
       <c r="L307" t="n">
-        <v>1576.7</v>
+        <v>890.6</v>
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Noisy party/radio-no arrest on Jul 26, 2026, 1577 m from Copley Place (PHILLIPS ST). Case #262064152 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny all others on Jul 26, 2026, 891 m from Copley Place (W CONCORD ST). Case #262064378 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21099,40 +21099,40 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>262064312</t>
+          <t>262064152</t>
         </is>
       </c>
       <c r="E308" s="3" t="n">
-        <v>46229.60625</v>
+        <v>46229.01458333333</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>SICK ASSIST - DRUG RELATED ILLNESS</t>
+          <t>NOISY PARTY/RADIO-NO ARREST</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>QUALITY_OF_LIFE</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H308" t="inlineStr"/>
       <c r="I308" t="inlineStr">
         <is>
-          <t>ALBANY ST</t>
+          <t>PHILLIPS ST</t>
         </is>
       </c>
       <c r="J308" t="n">
-        <v>42.33428840659414</v>
+        <v>42.36027809483424</v>
       </c>
       <c r="K308" t="n">
-        <v>-71.07239517543796</v>
+        <v>-71.06899804851336</v>
       </c>
       <c r="L308" t="n">
-        <v>1543.1</v>
+        <v>1576.7</v>
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Sick assist - drug related illness on Jul 26, 2026, 1543 m from Copley Place (ALBANY ST). Case #262064312 (use for a records request — full narratives are not published in open data).</t>
+          <t>Noisy party/radio-no arrest on Jul 26, 2026, 1577 m from Copley Place (PHILLIPS ST). Case #262064152 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21154,40 +21154,40 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>262064770</t>
+          <t>262064312</t>
         </is>
       </c>
       <c r="E309" s="3" t="n">
-        <v>46230.52083333334</v>
+        <v>46229.60625</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>LARCENY THEFT FROM MV - NON-ACCESSORY</t>
+          <t>SICK ASSIST - DRUG RELATED ILLNESS</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>QUALITY_OF_LIFE</t>
         </is>
       </c>
       <c r="H309" t="inlineStr"/>
       <c r="I309" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>ALBANY ST</t>
         </is>
       </c>
       <c r="J309" t="n">
-        <v>42.33954198983015</v>
+        <v>42.33428840659414</v>
       </c>
       <c r="K309" t="n">
-        <v>-71.06940876967543</v>
+        <v>-71.07239517543796</v>
       </c>
       <c r="L309" t="n">
-        <v>1123.7</v>
+        <v>1543.1</v>
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Larceny theft from mv - non-accessory on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064770 (use for a records request — full narratives are not published in open data).</t>
+          <t>Sick assist - drug related illness on Jul 26, 2026, 1543 m from Copley Place (ALBANY ST). Case #262064312 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21209,15 +21209,15 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>262064532</t>
+          <t>262064770</t>
         </is>
       </c>
       <c r="E310" s="3" t="n">
-        <v>46230.29166666666</v>
+        <v>46230.52083333334</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>PROPERTY - LOST/ MISSING</t>
+          <t>LARCENY THEFT FROM MV - NON-ACCESSORY</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
@@ -21242,7 +21242,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Property - lost/ missing on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064532 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny theft from mv - non-accessory on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064770 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21264,15 +21264,15 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>262064590</t>
+          <t>262064532</t>
         </is>
       </c>
       <c r="E311" s="3" t="n">
-        <v>46230.50625</v>
+        <v>46230.29166666666</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>LARCENY ALL OTHERS</t>
+          <t>PROPERTY - LOST/ MISSING</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
@@ -21283,21 +21283,21 @@
       <c r="H311" t="inlineStr"/>
       <c r="I311" t="inlineStr">
         <is>
-          <t>W BROOKLINE ST</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J311" t="n">
-        <v>42.34172590358821</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K311" t="n">
-        <v>-71.07501847816492</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L311" t="n">
-        <v>689.2</v>
+        <v>1123.7</v>
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Larceny all others on Jul 27, 2026, 689 m from Copley Place (W BROOKLINE ST). Case #262064590 (use for a records request — full narratives are not published in open data).</t>
+          <t>Property - lost/ missing on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064532 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21319,15 +21319,15 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>262064674</t>
+          <t>262064590</t>
         </is>
       </c>
       <c r="E312" s="3" t="n">
-        <v>46229.33333333334</v>
+        <v>46230.50625</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>PROPERTY - LOST/ MISSING</t>
+          <t>LARCENY ALL OTHERS</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
@@ -21338,21 +21338,21 @@
       <c r="H312" t="inlineStr"/>
       <c r="I312" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>W BROOKLINE ST</t>
         </is>
       </c>
       <c r="J312" t="n">
-        <v>42.33954198983015</v>
+        <v>42.34172590358821</v>
       </c>
       <c r="K312" t="n">
-        <v>-71.06940876967543</v>
+        <v>-71.07501847816492</v>
       </c>
       <c r="L312" t="n">
-        <v>1123.7</v>
+        <v>689.2</v>
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Property - lost/ missing on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064674 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny all others on Jul 27, 2026, 689 m from Copley Place (W BROOKLINE ST). Case #262064590 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21374,40 +21374,40 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>262064591</t>
+          <t>262064674</t>
         </is>
       </c>
       <c r="E313" s="3" t="n">
-        <v>46229.77847222222</v>
+        <v>46229.33333333334</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>INVESTIGATE PERSON</t>
+          <t>PROPERTY - LOST/ MISSING</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H313" t="inlineStr"/>
       <c r="I313" t="inlineStr">
         <is>
-          <t>AVERY ST</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J313" t="n">
-        <v>42.35327560751949</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K313" t="n">
-        <v>-71.06345772204415</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L313" t="n">
-        <v>1324</v>
+        <v>1123.7</v>
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Investigate person on Jul 26, 2026, 1324 m from Copley Place (AVERY ST). Case #262064591 (use for a records request — full narratives are not published in open data).</t>
+          <t>Property - lost/ missing on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064674 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21429,15 +21429,15 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>262064579</t>
+          <t>262064591</t>
         </is>
       </c>
       <c r="E314" s="3" t="n">
-        <v>46230.43402777778</v>
+        <v>46229.77847222222</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>SICK/INJURED/MEDICAL - PERSON</t>
+          <t>INVESTIGATE PERSON</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
@@ -21448,21 +21448,21 @@
       <c r="H314" t="inlineStr"/>
       <c r="I314" t="inlineStr">
         <is>
-          <t>NORTHAMPTON ST</t>
+          <t>AVERY ST</t>
         </is>
       </c>
       <c r="J314" t="n">
-        <v>42.33395124839377</v>
+        <v>42.35327560751949</v>
       </c>
       <c r="K314" t="n">
-        <v>-71.07538938822692</v>
+        <v>-71.06345772204415</v>
       </c>
       <c r="L314" t="n">
-        <v>1530.5</v>
+        <v>1324</v>
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Sick/injured/medical - person on Jul 27, 2026, 1531 m from Copley Place (NORTHAMPTON ST). Case #262064579 (use for a records request — full narratives are not published in open data).</t>
+          <t>Investigate person on Jul 26, 2026, 1324 m from Copley Place (AVERY ST). Case #262064591 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21484,40 +21484,40 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>262064357</t>
+          <t>262064579</t>
         </is>
       </c>
       <c r="E315" s="3" t="n">
-        <v>46229.72638888889</v>
+        <v>46230.43402777778</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>LARCENY SHOPLIFTING</t>
+          <t>SICK/INJURED/MEDICAL - PERSON</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H315" t="inlineStr"/>
       <c r="I315" t="inlineStr">
         <is>
-          <t>HUNTINGTON AVE</t>
+          <t>NORTHAMPTON ST</t>
         </is>
       </c>
       <c r="J315" t="n">
-        <v>42.3473097976345</v>
+        <v>42.33395124839377</v>
       </c>
       <c r="K315" t="n">
-        <v>-71.0791516658207</v>
+        <v>-71.07538938822692</v>
       </c>
       <c r="L315" t="n">
-        <v>129.3</v>
+        <v>1530.5</v>
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Larceny shoplifting on Jul 26, 2026, 129 m from Copley Place (HUNTINGTON AVE). Case #262064357 (use for a records request — full narratives are not published in open data).</t>
+          <t>Sick/injured/medical - person on Jul 27, 2026, 1531 m from Copley Place (NORTHAMPTON ST). Case #262064579 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21539,15 +21539,15 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>262064198</t>
+          <t>262064802</t>
         </is>
       </c>
       <c r="E316" s="3" t="n">
-        <v>46229.16736111111</v>
+        <v>46230.89583333334</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>TOWED MOTOR VEHICLE</t>
+          <t>LARCENY SHOPLIFTING</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
@@ -21557,22 +21557,631 @@
       </c>
       <c r="H316" t="inlineStr"/>
       <c r="I316" t="inlineStr">
+        <is>
+          <t>BOYLSTON ST</t>
+        </is>
+      </c>
+      <c r="J316" t="n">
+        <v>42.34862381555496</v>
+      </c>
+      <c r="K316" t="n">
+        <v>-71.08277637086411</v>
+      </c>
+      <c r="L316" t="n">
+        <v>437.3</v>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>Larceny shoplifting on Jul 27, 2026, 437 m from Copley Place (BOYLSTON ST). Case #262064802 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>262064409</t>
+        </is>
+      </c>
+      <c r="E317" s="3" t="n">
+        <v>46229.85833333333</v>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>SICK ASSIST</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr"/>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>OXFORD ST</t>
+        </is>
+      </c>
+      <c r="J317" t="n">
+        <v>42.35193460488232</v>
+      </c>
+      <c r="K317" t="n">
+        <v>-71.06048592223925</v>
+      </c>
+      <c r="L317" t="n">
+        <v>1488.7</v>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>Sick assist on Jul 26, 2026, 1489 m from Copley Place (OXFORD ST). Case #262064409 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>262064318</t>
+        </is>
+      </c>
+      <c r="E318" s="3" t="n">
+        <v>46229.53958333333</v>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>INVESTIGATE PERSON</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr"/>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>SHAWMUT AVE</t>
+        </is>
+      </c>
+      <c r="J318" t="n">
+        <v>42.34319452771496</v>
+      </c>
+      <c r="K318" t="n">
+        <v>-71.06880536524001</v>
+      </c>
+      <c r="L318" t="n">
+        <v>876.3</v>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>Investigate person on Jul 26, 2026, 876 m from Copley Place (SHAWMUT AVE). Case #262064318 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>262064412</t>
+        </is>
+      </c>
+      <c r="E319" s="3" t="n">
+        <v>46229.87638888889</v>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>SICK/INJURED/MEDICAL - PERSON</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr"/>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>TREMONT ST</t>
+        </is>
+      </c>
+      <c r="J319" t="n">
+        <v>42.35428377241487</v>
+      </c>
+      <c r="K319" t="n">
+        <v>-71.06380403747467</v>
+      </c>
+      <c r="L319" t="n">
+        <v>1356.9</v>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>Sick/injured/medical - person on Jul 26, 2026, 1357 m from Copley Place (TREMONT ST). Case #262064412 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>262064362</t>
+        </is>
+      </c>
+      <c r="E320" s="3" t="n">
+        <v>46229.64305555556</v>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>M/V ACCIDENT - INVOLVING PEDESTRIAN - INJURY</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr"/>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>DARTMOUTH ST</t>
+        </is>
+      </c>
+      <c r="J320" t="n">
+        <v>42.35029374297969</v>
+      </c>
+      <c r="K320" t="n">
+        <v>-71.07744671381569</v>
+      </c>
+      <c r="L320" t="n">
+        <v>298.2</v>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>M/v accident - involving pedestrian - injury on Jul 26, 2026, 298 m from Copley Place (DARTMOUTH ST). Case #262064362 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>262064307</t>
+        </is>
+      </c>
+      <c r="E321" s="3" t="n">
+        <v>46229.59027777778</v>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>SICK ASSIST</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr"/>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>TREMONT ST &amp; TEMPLE PL
+BOSTON, MA 02111
+UNITED STA</t>
+        </is>
+      </c>
+      <c r="J321" t="n">
+        <v>42.35561100811422</v>
+      </c>
+      <c r="K321" t="n">
+        <v>-71.06289400004533</v>
+      </c>
+      <c r="L321" t="n">
+        <v>1502.5</v>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>Sick assist on Jul 26, 2026, 1502 m from Copley Place (TREMONT ST &amp; TEMPLE PL
+BOSTON, MA 02111
+UNITED STA). Case #262064307 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>262064419</t>
+        </is>
+      </c>
+      <c r="E322" s="3" t="n">
+        <v>46229.90138888889</v>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>HARASSMENT/ CRIMINAL HARASSMENT</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr"/>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>NASSAU ST</t>
+        </is>
+      </c>
+      <c r="J322" t="n">
+        <v>42.34880604399623</v>
+      </c>
+      <c r="K322" t="n">
+        <v>-71.06285446968663</v>
+      </c>
+      <c r="L322" t="n">
+        <v>1221.7</v>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>Harassment/ criminal harassment on Jul 26, 2026, 1222 m from Copley Place (NASSAU ST). Case #262064419 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>262064339</t>
+        </is>
+      </c>
+      <c r="E323" s="3" t="n">
+        <v>46229.63333333333</v>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>ASSAULT - AGGRAVATED</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr"/>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J323" t="n">
+        <v>42.33511903946613</v>
+      </c>
+      <c r="K323" t="n">
+        <v>-71.07491709613726</v>
+      </c>
+      <c r="L323" t="n">
+        <v>1407.3</v>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>Assault - aggravated on Jul 26, 2026, 1407 m from Copley Place (HARRISON AVE). Case #262064339 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>262064236</t>
+        </is>
+      </c>
+      <c r="E324" s="3" t="n">
+        <v>46229.37638888889</v>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>SICK ASSIST</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr"/>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>TREMONT ST</t>
+        </is>
+      </c>
+      <c r="J324" t="n">
+        <v>42.34470135794417</v>
+      </c>
+      <c r="K324" t="n">
+        <v>-71.0703760849388</v>
+      </c>
+      <c r="L324" t="n">
+        <v>678.7</v>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>Sick assist on Jul 26, 2026, 679 m from Copley Place (TREMONT ST). Case #262064236 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>262064234</t>
+        </is>
+      </c>
+      <c r="E325" s="3" t="n">
+        <v>46229.31944444445</v>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>INVESTIGATE PERSON</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr"/>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>SAINT JAMES AVE</t>
+        </is>
+      </c>
+      <c r="J325" t="n">
+        <v>42.34947585701249</v>
+      </c>
+      <c r="K325" t="n">
+        <v>-71.07640149637847</v>
+      </c>
+      <c r="L325" t="n">
+        <v>230.3</v>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>Investigate person on Jul 26, 2026, 230 m from Copley Place (SAINT JAMES AVE). Case #262064234 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>262064357</t>
+        </is>
+      </c>
+      <c r="E326" s="3" t="n">
+        <v>46229.72638888889</v>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>LARCENY SHOPLIFTING</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr"/>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>HUNTINGTON AVE</t>
+        </is>
+      </c>
+      <c r="J326" t="n">
+        <v>42.3473097976345</v>
+      </c>
+      <c r="K326" t="n">
+        <v>-71.0791516658207</v>
+      </c>
+      <c r="L326" t="n">
+        <v>129.3</v>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>Larceny shoplifting on Jul 26, 2026, 129 m from Copley Place (HUNTINGTON AVE). Case #262064357 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>262064198</t>
+        </is>
+      </c>
+      <c r="E327" s="3" t="n">
+        <v>46229.16736111111</v>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>TOWED MOTOR VEHICLE</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr"/>
+      <c r="I327" t="inlineStr">
         <is>
           <t>STUART ST &amp; CHARLES ST S
 BOSTON, MA 02116
 UNITED S</t>
         </is>
       </c>
-      <c r="J316" t="n">
+      <c r="J327" t="n">
         <v>42.35095701392956</v>
       </c>
-      <c r="K316" t="n">
+      <c r="K327" t="n">
         <v>-71.06685999332976</v>
       </c>
-      <c r="L316" t="n">
+      <c r="L327" t="n">
         <v>960.1</v>
       </c>
-      <c r="M316" t="inlineStr">
+      <c r="M327" t="inlineStr">
         <is>
           <t>Towed motor vehicle on Jul 26, 2026, 960 m from Copley Place (STUART ST &amp; CHARLES ST S
 BOSTON, MA 02116
@@ -21580,168 +22189,168 @@
         </is>
       </c>
     </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
+    <row r="328">
+      <c r="A328" t="inlineStr">
         <is>
           <t>COPLEY</t>
         </is>
       </c>
-      <c r="B317" t="inlineStr">
+      <c r="B328" t="inlineStr">
         <is>
           <t>Copley Place</t>
         </is>
       </c>
-      <c r="C317" t="inlineStr">
+      <c r="C328" t="inlineStr">
         <is>
           <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr">
+      <c r="D328" t="inlineStr">
         <is>
           <t>262064309</t>
         </is>
       </c>
-      <c r="E317" s="3" t="n">
+      <c r="E328" s="3" t="n">
         <v>46229.39444444444</v>
       </c>
-      <c r="F317" t="inlineStr">
+      <c r="F328" t="inlineStr">
         <is>
           <t>INVESTIGATE PERSON</t>
         </is>
       </c>
-      <c r="G317" t="inlineStr">
+      <c r="G328" t="inlineStr">
         <is>
           <t>OTHER</t>
         </is>
       </c>
-      <c r="H317" t="inlineStr"/>
-      <c r="I317" t="inlineStr">
+      <c r="H328" t="inlineStr"/>
+      <c r="I328" t="inlineStr">
         <is>
           <t>SAINT BOTOLPH ST</t>
         </is>
       </c>
-      <c r="J317" t="n">
+      <c r="J328" t="n">
         <v>42.34617475544754</v>
       </c>
-      <c r="K317" t="n">
+      <c r="K328" t="n">
         <v>-71.07925920373032</v>
       </c>
-      <c r="L317" t="n">
+      <c r="L328" t="n">
         <v>208.6</v>
       </c>
-      <c r="M317" t="inlineStr">
+      <c r="M328" t="inlineStr">
         <is>
           <t>Investigate person on Jul 26, 2026, 209 m from Copley Place (SAINT BOTOLPH ST). Case #262064309 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
+    <row r="329">
+      <c r="A329" t="inlineStr">
         <is>
           <t>COPLEY</t>
         </is>
       </c>
-      <c r="B318" t="inlineStr">
+      <c r="B329" t="inlineStr">
         <is>
           <t>Copley Place</t>
         </is>
       </c>
-      <c r="C318" t="inlineStr">
+      <c r="C329" t="inlineStr">
         <is>
           <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr">
+      <c r="D329" t="inlineStr">
         <is>
           <t>262064283</t>
         </is>
       </c>
-      <c r="E318" s="3" t="n">
+      <c r="E329" s="3" t="n">
         <v>46229.51736111111</v>
       </c>
-      <c r="F318" t="inlineStr">
+      <c r="F329" t="inlineStr">
         <is>
           <t>LARCENY SHOPLIFTING</t>
         </is>
       </c>
-      <c r="G318" t="inlineStr">
+      <c r="G329" t="inlineStr">
         <is>
           <t>PROPERTY</t>
         </is>
       </c>
-      <c r="H318" t="inlineStr"/>
-      <c r="I318" t="inlineStr">
+      <c r="H329" t="inlineStr"/>
+      <c r="I329" t="inlineStr">
         <is>
           <t>HUNTINGTON AVE</t>
         </is>
       </c>
-      <c r="J318" t="n">
+      <c r="J329" t="n">
         <v>42.3473097976345</v>
       </c>
-      <c r="K318" t="n">
+      <c r="K329" t="n">
         <v>-71.0791516658207</v>
       </c>
-      <c r="L318" t="n">
+      <c r="L329" t="n">
         <v>129.3</v>
       </c>
-      <c r="M318" t="inlineStr">
+      <c r="M329" t="inlineStr">
         <is>
           <t>Larceny shoplifting on Jul 26, 2026, 129 m from Copley Place (HUNTINGTON AVE). Case #262064283 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
+    <row r="330">
+      <c r="A330" t="inlineStr">
         <is>
           <t>COPLEY</t>
         </is>
       </c>
-      <c r="B319" t="inlineStr">
+      <c r="B330" t="inlineStr">
         <is>
           <t>Copley Place</t>
         </is>
       </c>
-      <c r="C319" t="inlineStr">
+      <c r="C330" t="inlineStr">
         <is>
           <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr">
+      <c r="D330" t="inlineStr">
         <is>
           <t>262064226</t>
         </is>
       </c>
-      <c r="E319" s="3" t="n">
+      <c r="E330" s="3" t="n">
         <v>46229.375</v>
       </c>
-      <c r="F319" t="inlineStr">
+      <c r="F330" t="inlineStr">
         <is>
           <t>M/V ACCIDENT - PROPERTY DAMAGE</t>
         </is>
       </c>
-      <c r="G319" t="inlineStr">
+      <c r="G330" t="inlineStr">
         <is>
           <t>PROPERTY</t>
         </is>
       </c>
-      <c r="H319" t="inlineStr"/>
-      <c r="I319" t="inlineStr">
+      <c r="H330" t="inlineStr"/>
+      <c r="I330" t="inlineStr">
         <is>
           <t>BERKELEY ST &amp; SAINT JAMES AVE
 BOSTON, MA 02116
 UNI</t>
         </is>
       </c>
-      <c r="J319" t="n">
+      <c r="J330" t="n">
         <v>42.3504290420294</v>
       </c>
-      <c r="K319" t="n">
+      <c r="K330" t="n">
         <v>-71.07264798093048</v>
       </c>
-      <c r="L319" t="n">
+      <c r="L330" t="n">
         <v>515.5</v>
       </c>
-      <c r="M319" t="inlineStr">
+      <c r="M330" t="inlineStr">
         <is>
           <t>M/v accident - property damage on Jul 26, 2026, 515 m from Copley Place (BERKELEY ST &amp; SAINT JAMES AVE
 BOSTON, MA 02116
@@ -21749,58 +22358,58 @@
         </is>
       </c>
     </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
+    <row r="331">
+      <c r="A331" t="inlineStr">
         <is>
           <t>COPLEY</t>
         </is>
       </c>
-      <c r="B320" t="inlineStr">
+      <c r="B331" t="inlineStr">
         <is>
           <t>Copley Place</t>
         </is>
       </c>
-      <c r="C320" t="inlineStr">
+      <c r="C331" t="inlineStr">
         <is>
           <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr">
+      <c r="D331" t="inlineStr">
         <is>
           <t>262064268</t>
         </is>
       </c>
-      <c r="E320" s="3" t="n">
+      <c r="E331" s="3" t="n">
         <v>46229.48680555556</v>
       </c>
-      <c r="F320" t="inlineStr">
+      <c r="F331" t="inlineStr">
         <is>
           <t>LARCENY THEFT FROM BUILDING</t>
         </is>
       </c>
-      <c r="G320" t="inlineStr">
+      <c r="G331" t="inlineStr">
         <is>
           <t>PROPERTY</t>
         </is>
       </c>
-      <c r="H320" t="inlineStr"/>
-      <c r="I320" t="inlineStr">
+      <c r="H331" t="inlineStr"/>
+      <c r="I331" t="inlineStr">
         <is>
           <t>REED ST &amp; E LENOX ST
 ROXBURY, MA 02118
 UNITED STAT</t>
         </is>
       </c>
-      <c r="J320" t="n">
+      <c r="J331" t="n">
         <v>42.33406097367816</v>
       </c>
-      <c r="K320" t="n">
+      <c r="K331" t="n">
         <v>-71.07756301316894</v>
       </c>
-      <c r="L320" t="n">
+      <c r="L331" t="n">
         <v>1507.2</v>
       </c>
-      <c r="M320" t="inlineStr">
+      <c r="M331" t="inlineStr">
         <is>
           <t>Larceny theft from building on Jul 26, 2026, 1507 m from Copley Place (REED ST &amp; E LENOX ST
 ROXBURY, MA 02118
@@ -21808,58 +22417,58 @@
         </is>
       </c>
     </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
+    <row r="332">
+      <c r="A332" t="inlineStr">
         <is>
           <t>COPLEY</t>
         </is>
       </c>
-      <c r="B321" t="inlineStr">
+      <c r="B332" t="inlineStr">
         <is>
           <t>Copley Place</t>
         </is>
       </c>
-      <c r="C321" t="inlineStr">
+      <c r="C332" t="inlineStr">
         <is>
           <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr">
+      <c r="D332" t="inlineStr">
         <is>
           <t>262064394</t>
         </is>
       </c>
-      <c r="E321" s="3" t="n">
+      <c r="E332" s="3" t="n">
         <v>46229.82152777778</v>
       </c>
-      <c r="F321" t="inlineStr">
+      <c r="F332" t="inlineStr">
         <is>
           <t>M/V ACCIDENT - OTHER</t>
         </is>
       </c>
-      <c r="G321" t="inlineStr">
+      <c r="G332" t="inlineStr">
         <is>
           <t>OTHER</t>
         </is>
       </c>
-      <c r="H321" t="inlineStr"/>
-      <c r="I321" t="inlineStr">
+      <c r="H332" t="inlineStr"/>
+      <c r="I332" t="inlineStr">
         <is>
           <t>HARRISON AVE &amp; PLYMPTON ST
 BOSTON, MA 02118
 UNITED</t>
         </is>
       </c>
-      <c r="J321" t="n">
+      <c r="J332" t="n">
         <v>42.33973998780085</v>
       </c>
-      <c r="K321" t="n">
+      <c r="K332" t="n">
         <v>-71.0691099454142</v>
       </c>
-      <c r="L321" t="n">
+      <c r="L332" t="n">
         <v>1121.4</v>
       </c>
-      <c r="M321" t="inlineStr">
+      <c r="M332" t="inlineStr">
         <is>
           <t>M/v accident - other on Jul 26, 2026, 1121 m from Copley Place (HARRISON AVE &amp; PLYMPTON ST
 BOSTON, MA 02118
@@ -21867,611 +22476,6 @@
         </is>
       </c>
     </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>262064321</t>
-        </is>
-      </c>
-      <c r="E322" s="3" t="n">
-        <v>46229.59166666667</v>
-      </c>
-      <c r="F322" t="inlineStr">
-        <is>
-          <t>M/V - LEAVING SCENE - PROPERTY DAMAGE</t>
-        </is>
-      </c>
-      <c r="G322" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H322" t="inlineStr"/>
-      <c r="I322" t="inlineStr">
-        <is>
-          <t>HARRISON AVE</t>
-        </is>
-      </c>
-      <c r="J322" t="n">
-        <v>42.33954198983015</v>
-      </c>
-      <c r="K322" t="n">
-        <v>-71.06940876967543</v>
-      </c>
-      <c r="L322" t="n">
-        <v>1123.7</v>
-      </c>
-      <c r="M322" t="inlineStr">
-        <is>
-          <t>M/v - leaving scene - property damage on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064321 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>262064179</t>
-        </is>
-      </c>
-      <c r="E323" s="3" t="n">
-        <v>46229.07361111111</v>
-      </c>
-      <c r="F323" t="inlineStr">
-        <is>
-          <t>INVESTIGATE PROPERTY</t>
-        </is>
-      </c>
-      <c r="G323" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H323" t="inlineStr"/>
-      <c r="I323" t="inlineStr">
-        <is>
-          <t>BOYLSTON ST</t>
-        </is>
-      </c>
-      <c r="J323" t="n">
-        <v>42.35234109431519</v>
-      </c>
-      <c r="K323" t="n">
-        <v>-71.06432465046424</v>
-      </c>
-      <c r="L323" t="n">
-        <v>1213.3</v>
-      </c>
-      <c r="M323" t="inlineStr">
-        <is>
-          <t>Investigate property on Jul 26, 2026, 1213 m from Copley Place (BOYLSTON ST). Case #262064179 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>262064772</t>
-        </is>
-      </c>
-      <c r="E324" s="3" t="n">
-        <v>46230.82569444444</v>
-      </c>
-      <c r="F324" t="inlineStr">
-        <is>
-          <t>LARCENY SHOPLIFTING</t>
-        </is>
-      </c>
-      <c r="G324" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H324" t="inlineStr"/>
-      <c r="I324" t="inlineStr">
-        <is>
-          <t>BOYLSTON ST</t>
-        </is>
-      </c>
-      <c r="J324" t="n">
-        <v>42.34862381555496</v>
-      </c>
-      <c r="K324" t="n">
-        <v>-71.08277637086411</v>
-      </c>
-      <c r="L324" t="n">
-        <v>437.3</v>
-      </c>
-      <c r="M324" t="inlineStr">
-        <is>
-          <t>Larceny shoplifting on Jul 27, 2026, 437 m from Copley Place (BOYLSTON ST). Case #262064772 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>262064289</t>
-        </is>
-      </c>
-      <c r="E325" s="3" t="n">
-        <v>46229.54583333333</v>
-      </c>
-      <c r="F325" t="inlineStr">
-        <is>
-          <t>LARCENY SHOPLIFTING</t>
-        </is>
-      </c>
-      <c r="G325" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H325" t="inlineStr"/>
-      <c r="I325" t="inlineStr">
-        <is>
-          <t>BOYLSTON ST</t>
-        </is>
-      </c>
-      <c r="J325" t="n">
-        <v>42.35095908794595</v>
-      </c>
-      <c r="K325" t="n">
-        <v>-71.07412780075079</v>
-      </c>
-      <c r="L325" t="n">
-        <v>470.3</v>
-      </c>
-      <c r="M325" t="inlineStr">
-        <is>
-          <t>Larceny shoplifting on Jul 26, 2026, 470 m from Copley Place (BOYLSTON ST). Case #262064289 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>262064298</t>
-        </is>
-      </c>
-      <c r="E326" s="3" t="n">
-        <v>46229.08611111111</v>
-      </c>
-      <c r="F326" t="inlineStr">
-        <is>
-          <t>FIREARM/WEAPON - LOST</t>
-        </is>
-      </c>
-      <c r="G326" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H326" t="inlineStr"/>
-      <c r="I326" t="inlineStr">
-        <is>
-          <t>HARRISON AVE</t>
-        </is>
-      </c>
-      <c r="J326" t="n">
-        <v>42.33954198983015</v>
-      </c>
-      <c r="K326" t="n">
-        <v>-71.06940876967543</v>
-      </c>
-      <c r="L326" t="n">
-        <v>1123.7</v>
-      </c>
-      <c r="M326" t="inlineStr">
-        <is>
-          <t>Firearm/weapon - lost on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064298 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>262064416</t>
-        </is>
-      </c>
-      <c r="E327" s="3" t="n">
-        <v>46229.87569444445</v>
-      </c>
-      <c r="F327" t="inlineStr">
-        <is>
-          <t>ASSAULT - AGGRAVATED</t>
-        </is>
-      </c>
-      <c r="G327" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H327" t="inlineStr"/>
-      <c r="I327" t="inlineStr">
-        <is>
-          <t>HUNTINGTON AVE</t>
-        </is>
-      </c>
-      <c r="J327" t="n">
-        <v>42.34221543503831</v>
-      </c>
-      <c r="K327" t="n">
-        <v>-71.08577074656198</v>
-      </c>
-      <c r="L327" t="n">
-        <v>898.8</v>
-      </c>
-      <c r="M327" t="inlineStr">
-        <is>
-          <t>Assault - aggravated on Jul 26, 2026, 899 m from Copley Place (HUNTINGTON AVE). Case #262064416 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>262064700</t>
-        </is>
-      </c>
-      <c r="E328" s="3" t="n">
-        <v>46230.71458333333</v>
-      </c>
-      <c r="F328" t="inlineStr">
-        <is>
-          <t>BREAKING AND ENTERING (B&amp;E) MOTOR VEHICLE</t>
-        </is>
-      </c>
-      <c r="G328" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H328" t="inlineStr"/>
-      <c r="I328" t="inlineStr">
-        <is>
-          <t>HARRISON AVE</t>
-        </is>
-      </c>
-      <c r="J328" t="n">
-        <v>42.33954198983015</v>
-      </c>
-      <c r="K328" t="n">
-        <v>-71.06940876967543</v>
-      </c>
-      <c r="L328" t="n">
-        <v>1123.7</v>
-      </c>
-      <c r="M328" t="inlineStr">
-        <is>
-          <t>Breaking and entering (b&amp;e) motor vehicle on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064700 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>262064491</t>
-        </is>
-      </c>
-      <c r="E329" s="3" t="n">
-        <v>46230.22916666666</v>
-      </c>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t>LARCENY ALL OTHERS</t>
-        </is>
-      </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H329" t="inlineStr"/>
-      <c r="I329" t="inlineStr">
-        <is>
-          <t>RUTLAND ST</t>
-        </is>
-      </c>
-      <c r="J329" t="n">
-        <v>42.34020387362647</v>
-      </c>
-      <c r="K329" t="n">
-        <v>-71.07645111113312</v>
-      </c>
-      <c r="L329" t="n">
-        <v>829.8</v>
-      </c>
-      <c r="M329" t="inlineStr">
-        <is>
-          <t>Larceny all others on Jul 27, 2026, 830 m from Copley Place (RUTLAND ST). Case #262064491 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>262064492</t>
-        </is>
-      </c>
-      <c r="E330" s="3" t="n">
-        <v>46230.10972222222</v>
-      </c>
-      <c r="F330" t="inlineStr">
-        <is>
-          <t>VANDALISM</t>
-        </is>
-      </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H330" t="inlineStr"/>
-      <c r="I330" t="inlineStr">
-        <is>
-          <t>NORTHAMPTON ST</t>
-        </is>
-      </c>
-      <c r="J330" t="n">
-        <v>42.33798932384219</v>
-      </c>
-      <c r="K330" t="n">
-        <v>-71.08003745874711</v>
-      </c>
-      <c r="L330" t="n">
-        <v>1088.4</v>
-      </c>
-      <c r="M330" t="inlineStr">
-        <is>
-          <t>Vandalism on Jul 27, 2026, 1088 m from Copley Place (NORTHAMPTON ST). Case #262064492 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>262064766</t>
-        </is>
-      </c>
-      <c r="E331" s="3" t="n">
-        <v>46230.75416666667</v>
-      </c>
-      <c r="F331" t="inlineStr">
-        <is>
-          <t>PROPERTY - LOST/ MISSING</t>
-        </is>
-      </c>
-      <c r="G331" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H331" t="inlineStr"/>
-      <c r="I331" t="inlineStr">
-        <is>
-          <t>COLUMBUS AVE</t>
-        </is>
-      </c>
-      <c r="J331" t="n">
-        <v>42.34294800069079</v>
-      </c>
-      <c r="K331" t="n">
-        <v>-71.07888700104606</v>
-      </c>
-      <c r="L331" t="n">
-        <v>529.1</v>
-      </c>
-      <c r="M331" t="inlineStr">
-        <is>
-          <t>Property - lost/ missing on Jul 27, 2026, 529 m from Copley Place (COLUMBUS AVE). Case #262064766 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>262064548</t>
-        </is>
-      </c>
-      <c r="E332" s="3" t="n">
-        <v>46230.44236111111</v>
-      </c>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>M/V - LEAVING SCENE - PROPERTY DAMAGE</t>
-        </is>
-      </c>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H332" t="inlineStr"/>
-      <c r="I332" t="inlineStr">
-        <is>
-          <t>HARRISON AVE</t>
-        </is>
-      </c>
-      <c r="J332" t="n">
-        <v>42.33954198983015</v>
-      </c>
-      <c r="K332" t="n">
-        <v>-71.06940876967543</v>
-      </c>
-      <c r="L332" t="n">
-        <v>1123.7</v>
-      </c>
-      <c r="M332" t="inlineStr">
-        <is>
-          <t>M/v - leaving scene - property damage on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064548 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
@@ -22490,15 +22494,15 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>262064504</t>
+          <t>262064321</t>
         </is>
       </c>
       <c r="E333" s="3" t="n">
-        <v>46230.34791666667</v>
+        <v>46229.59166666667</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>LARCENY SHOPLIFTING</t>
+          <t>M/V - LEAVING SCENE - PROPERTY DAMAGE</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
@@ -22509,21 +22513,21 @@
       <c r="H333" t="inlineStr"/>
       <c r="I333" t="inlineStr">
         <is>
-          <t>CHARLES ST</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J333" t="n">
-        <v>42.36064469554803</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K333" t="n">
-        <v>-71.07086192011141</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L333" t="n">
-        <v>1552</v>
+        <v>1123.7</v>
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Larceny shoplifting on Jul 27, 2026, 1552 m from Copley Place (CHARLES ST). Case #262064504 (use for a records request — full narratives are not published in open data).</t>
+          <t>M/v - leaving scene - property damage on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064321 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -22545,20 +22549,20 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>262064506</t>
+          <t>262064772</t>
         </is>
       </c>
       <c r="E334" s="3" t="n">
-        <v>46230.34375</v>
+        <v>46230.82569444444</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>SICK ASSIST</t>
+          <t>LARCENY SHOPLIFTING</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H334" t="inlineStr"/>
@@ -22568,17 +22572,17 @@
         </is>
       </c>
       <c r="J334" t="n">
-        <v>42.35037869977646</v>
+        <v>42.34862381555496</v>
       </c>
       <c r="K334" t="n">
-        <v>-71.07626098382806</v>
+        <v>-71.08277637086411</v>
       </c>
       <c r="L334" t="n">
-        <v>327.3</v>
+        <v>437.3</v>
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Sick assist on Jul 27, 2026, 327 m from Copley Place (BOYLSTON ST). Case #262064506 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny shoplifting on Jul 27, 2026, 437 m from Copley Place (BOYLSTON ST). Case #262064772 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -22600,15 +22604,15 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>262064752</t>
+          <t>262064289</t>
         </is>
       </c>
       <c r="E335" s="3" t="n">
-        <v>46230.79166666666</v>
+        <v>46229.54583333333</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>STOLEN PROPERTY - BUYING / RECEIVING / POSSESSING</t>
+          <t>LARCENY SHOPLIFTING</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
@@ -22619,21 +22623,21 @@
       <c r="H335" t="inlineStr"/>
       <c r="I335" t="inlineStr">
         <is>
-          <t>HUDSON ST</t>
+          <t>BOYLSTON ST</t>
         </is>
       </c>
       <c r="J335" t="n">
-        <v>42.35074197291232</v>
+        <v>42.35095908794595</v>
       </c>
       <c r="K335" t="n">
-        <v>-71.06006134581432</v>
+        <v>-71.07412780075079</v>
       </c>
       <c r="L335" t="n">
-        <v>1485.3</v>
+        <v>470.3</v>
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Stolen property - buying / receiving / possessing on Jul 27, 2026, 1485 m from Copley Place (HUDSON ST). Case #262064752 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny shoplifting on Jul 26, 2026, 470 m from Copley Place (BOYLSTON ST). Case #262064289 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -22655,40 +22659,590 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>262064383</t>
+          <t>262064298</t>
         </is>
       </c>
       <c r="E336" s="3" t="n">
-        <v>46229.79375</v>
+        <v>46229.08611111111</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>M/V ACCIDENT - INVOLVING PEDESTRIAN - INJURY</t>
+          <t>FIREARM/WEAPON - LOST</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H336" t="inlineStr"/>
       <c r="I336" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J336" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K336" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L336" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>Firearm/weapon - lost on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064298 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>262064416</t>
+        </is>
+      </c>
+      <c r="E337" s="3" t="n">
+        <v>46229.87569444445</v>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>ASSAULT - AGGRAVATED</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr"/>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>HUNTINGTON AVE</t>
+        </is>
+      </c>
+      <c r="J337" t="n">
+        <v>42.34221543503831</v>
+      </c>
+      <c r="K337" t="n">
+        <v>-71.08577074656198</v>
+      </c>
+      <c r="L337" t="n">
+        <v>898.8</v>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>Assault - aggravated on Jul 26, 2026, 899 m from Copley Place (HUNTINGTON AVE). Case #262064416 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>262064700</t>
+        </is>
+      </c>
+      <c r="E338" s="3" t="n">
+        <v>46230.71458333333</v>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>BREAKING AND ENTERING (B&amp;E) MOTOR VEHICLE</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr"/>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J338" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K338" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L338" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>Breaking and entering (b&amp;e) motor vehicle on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064700 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>262064491</t>
+        </is>
+      </c>
+      <c r="E339" s="3" t="n">
+        <v>46230.22916666666</v>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>LARCENY ALL OTHERS</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr"/>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>RUTLAND ST</t>
+        </is>
+      </c>
+      <c r="J339" t="n">
+        <v>42.34020387362647</v>
+      </c>
+      <c r="K339" t="n">
+        <v>-71.07645111113312</v>
+      </c>
+      <c r="L339" t="n">
+        <v>829.8</v>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>Larceny all others on Jul 27, 2026, 830 m from Copley Place (RUTLAND ST). Case #262064491 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>262064492</t>
+        </is>
+      </c>
+      <c r="E340" s="3" t="n">
+        <v>46230.10972222222</v>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>VANDALISM</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr"/>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>NORTHAMPTON ST</t>
+        </is>
+      </c>
+      <c r="J340" t="n">
+        <v>42.33798932384219</v>
+      </c>
+      <c r="K340" t="n">
+        <v>-71.08003745874711</v>
+      </c>
+      <c r="L340" t="n">
+        <v>1088.4</v>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>Vandalism on Jul 27, 2026, 1088 m from Copley Place (NORTHAMPTON ST). Case #262064492 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>262064766</t>
+        </is>
+      </c>
+      <c r="E341" s="3" t="n">
+        <v>46230.75416666667</v>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>PROPERTY - LOST/ MISSING</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr"/>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>COLUMBUS AVE</t>
+        </is>
+      </c>
+      <c r="J341" t="n">
+        <v>42.34294800069079</v>
+      </c>
+      <c r="K341" t="n">
+        <v>-71.07888700104606</v>
+      </c>
+      <c r="L341" t="n">
+        <v>529.1</v>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>Property - lost/ missing on Jul 27, 2026, 529 m from Copley Place (COLUMBUS AVE). Case #262064766 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>262064548</t>
+        </is>
+      </c>
+      <c r="E342" s="3" t="n">
+        <v>46230.44236111111</v>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>M/V - LEAVING SCENE - PROPERTY DAMAGE</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr"/>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J342" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K342" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L342" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>M/v - leaving scene - property damage on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064548 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>262064504</t>
+        </is>
+      </c>
+      <c r="E343" s="3" t="n">
+        <v>46230.34791666667</v>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>LARCENY SHOPLIFTING</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr"/>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>CHARLES ST</t>
+        </is>
+      </c>
+      <c r="J343" t="n">
+        <v>42.36064469554803</v>
+      </c>
+      <c r="K343" t="n">
+        <v>-71.07086192011141</v>
+      </c>
+      <c r="L343" t="n">
+        <v>1552</v>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>Larceny shoplifting on Jul 27, 2026, 1552 m from Copley Place (CHARLES ST). Case #262064504 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>262064506</t>
+        </is>
+      </c>
+      <c r="E344" s="3" t="n">
+        <v>46230.34375</v>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>SICK ASSIST</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr"/>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>BOYLSTON ST</t>
+        </is>
+      </c>
+      <c r="J344" t="n">
+        <v>42.35037869977646</v>
+      </c>
+      <c r="K344" t="n">
+        <v>-71.07626098382806</v>
+      </c>
+      <c r="L344" t="n">
+        <v>327.3</v>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>Sick assist on Jul 27, 2026, 327 m from Copley Place (BOYLSTON ST). Case #262064506 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>262064752</t>
+        </is>
+      </c>
+      <c r="E345" s="3" t="n">
+        <v>46230.79166666666</v>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>STOLEN PROPERTY - BUYING / RECEIVING / POSSESSING</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr"/>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>HUDSON ST</t>
+        </is>
+      </c>
+      <c r="J345" t="n">
+        <v>42.35074197291232</v>
+      </c>
+      <c r="K345" t="n">
+        <v>-71.06006134581432</v>
+      </c>
+      <c r="L345" t="n">
+        <v>1485.3</v>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>Stolen property - buying / receiving / possessing on Jul 27, 2026, 1485 m from Copley Place (HUDSON ST). Case #262064752 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>262064383</t>
+        </is>
+      </c>
+      <c r="E346" s="3" t="n">
+        <v>46229.79375</v>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>M/V ACCIDENT - INVOLVING PEDESTRIAN - INJURY</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr"/>
+      <c r="I346" t="inlineStr">
         <is>
           <t>BOYLSTON ST &amp; DALTON ST
 BOSTON, MA 02115
 UNITED ST</t>
         </is>
       </c>
-      <c r="J336" t="n">
+      <c r="J346" t="n">
         <v>42.34787097987171</v>
       </c>
-      <c r="K336" t="n">
+      <c r="K346" t="n">
         <v>-71.08556796747074</v>
       </c>
-      <c r="L336" t="n">
+      <c r="L346" t="n">
         <v>652.7</v>
       </c>
-      <c r="M336" t="inlineStr">
+      <c r="M346" t="inlineStr">
         <is>
           <t>M/v accident - involving pedestrian - injury on Jul 26, 2026, 653 m from Copley Place (BOYLSTON ST &amp; DALTON ST
 BOSTON, MA 02115
@@ -22696,616 +23250,62 @@
         </is>
       </c>
     </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
+    <row r="347">
+      <c r="A347" t="inlineStr">
         <is>
           <t>COPLEY</t>
         </is>
       </c>
-      <c r="B337" t="inlineStr">
+      <c r="B347" t="inlineStr">
         <is>
           <t>Copley Place</t>
         </is>
       </c>
-      <c r="C337" t="inlineStr">
+      <c r="C347" t="inlineStr">
         <is>
           <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr">
+      <c r="D347" t="inlineStr">
         <is>
           <t>262064391</t>
         </is>
       </c>
-      <c r="E337" s="3" t="n">
+      <c r="E347" s="3" t="n">
         <v>46229.83125</v>
       </c>
-      <c r="F337" t="inlineStr">
+      <c r="F347" t="inlineStr">
         <is>
           <t>DRUGS - POSSESSION/ SALE/ MANUFACTURING/ USE</t>
         </is>
       </c>
-      <c r="G337" t="inlineStr">
+      <c r="G347" t="inlineStr">
         <is>
           <t>QUALITY_OF_LIFE</t>
         </is>
       </c>
-      <c r="H337" t="inlineStr"/>
-      <c r="I337" t="inlineStr">
+      <c r="H347" t="inlineStr"/>
+      <c r="I347" t="inlineStr">
         <is>
           <t xml:space="preserve">BOYLSTON ST &amp; BOYLSTON SQ
 BOSTON, MA 02111
 UNITED </t>
         </is>
       </c>
-      <c r="J337" t="n">
+      <c r="J347" t="n">
         <v>42.35231098936428</v>
       </c>
-      <c r="K337" t="n">
+      <c r="K347" t="n">
         <v>-71.06350996526169</v>
       </c>
-      <c r="L337" t="n">
+      <c r="L347" t="n">
         <v>1272.6</v>
       </c>
-      <c r="M337" t="inlineStr">
+      <c r="M347" t="inlineStr">
         <is>
           <t>Drugs - possession/ sale/ manufacturing/ use on Jul 26, 2026, 1273 m from Copley Place (BOYLSTON ST &amp; BOYLSTON SQ
 BOSTON, MA 02111
 UNITED ). Case #262064391 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>262064802</t>
-        </is>
-      </c>
-      <c r="E338" s="3" t="n">
-        <v>46230.89583333334</v>
-      </c>
-      <c r="F338" t="inlineStr">
-        <is>
-          <t>LARCENY SHOPLIFTING</t>
-        </is>
-      </c>
-      <c r="G338" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H338" t="inlineStr"/>
-      <c r="I338" t="inlineStr">
-        <is>
-          <t>BOYLSTON ST</t>
-        </is>
-      </c>
-      <c r="J338" t="n">
-        <v>42.34862381555496</v>
-      </c>
-      <c r="K338" t="n">
-        <v>-71.08277637086411</v>
-      </c>
-      <c r="L338" t="n">
-        <v>437.3</v>
-      </c>
-      <c r="M338" t="inlineStr">
-        <is>
-          <t>Larceny shoplifting on Jul 27, 2026, 437 m from Copley Place (BOYLSTON ST). Case #262064802 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>262064409</t>
-        </is>
-      </c>
-      <c r="E339" s="3" t="n">
-        <v>46229.85833333333</v>
-      </c>
-      <c r="F339" t="inlineStr">
-        <is>
-          <t>SICK ASSIST</t>
-        </is>
-      </c>
-      <c r="G339" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H339" t="inlineStr"/>
-      <c r="I339" t="inlineStr">
-        <is>
-          <t>OXFORD ST</t>
-        </is>
-      </c>
-      <c r="J339" t="n">
-        <v>42.35193460488232</v>
-      </c>
-      <c r="K339" t="n">
-        <v>-71.06048592223925</v>
-      </c>
-      <c r="L339" t="n">
-        <v>1488.7</v>
-      </c>
-      <c r="M339" t="inlineStr">
-        <is>
-          <t>Sick assist on Jul 26, 2026, 1489 m from Copley Place (OXFORD ST). Case #262064409 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>262064318</t>
-        </is>
-      </c>
-      <c r="E340" s="3" t="n">
-        <v>46229.53958333333</v>
-      </c>
-      <c r="F340" t="inlineStr">
-        <is>
-          <t>INVESTIGATE PERSON</t>
-        </is>
-      </c>
-      <c r="G340" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H340" t="inlineStr"/>
-      <c r="I340" t="inlineStr">
-        <is>
-          <t>SHAWMUT AVE</t>
-        </is>
-      </c>
-      <c r="J340" t="n">
-        <v>42.34319452771496</v>
-      </c>
-      <c r="K340" t="n">
-        <v>-71.06880536524001</v>
-      </c>
-      <c r="L340" t="n">
-        <v>876.3</v>
-      </c>
-      <c r="M340" t="inlineStr">
-        <is>
-          <t>Investigate person on Jul 26, 2026, 876 m from Copley Place (SHAWMUT AVE). Case #262064318 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>262064412</t>
-        </is>
-      </c>
-      <c r="E341" s="3" t="n">
-        <v>46229.87638888889</v>
-      </c>
-      <c r="F341" t="inlineStr">
-        <is>
-          <t>SICK/INJURED/MEDICAL - PERSON</t>
-        </is>
-      </c>
-      <c r="G341" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H341" t="inlineStr"/>
-      <c r="I341" t="inlineStr">
-        <is>
-          <t>TREMONT ST</t>
-        </is>
-      </c>
-      <c r="J341" t="n">
-        <v>42.35428377241487</v>
-      </c>
-      <c r="K341" t="n">
-        <v>-71.06380403747467</v>
-      </c>
-      <c r="L341" t="n">
-        <v>1356.9</v>
-      </c>
-      <c r="M341" t="inlineStr">
-        <is>
-          <t>Sick/injured/medical - person on Jul 26, 2026, 1357 m from Copley Place (TREMONT ST). Case #262064412 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>262064362</t>
-        </is>
-      </c>
-      <c r="E342" s="3" t="n">
-        <v>46229.64305555556</v>
-      </c>
-      <c r="F342" t="inlineStr">
-        <is>
-          <t>M/V ACCIDENT - INVOLVING PEDESTRIAN - INJURY</t>
-        </is>
-      </c>
-      <c r="G342" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H342" t="inlineStr"/>
-      <c r="I342" t="inlineStr">
-        <is>
-          <t>DARTMOUTH ST</t>
-        </is>
-      </c>
-      <c r="J342" t="n">
-        <v>42.35029374297969</v>
-      </c>
-      <c r="K342" t="n">
-        <v>-71.07744671381569</v>
-      </c>
-      <c r="L342" t="n">
-        <v>298.2</v>
-      </c>
-      <c r="M342" t="inlineStr">
-        <is>
-          <t>M/v accident - involving pedestrian - injury on Jul 26, 2026, 298 m from Copley Place (DARTMOUTH ST). Case #262064362 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>262064307</t>
-        </is>
-      </c>
-      <c r="E343" s="3" t="n">
-        <v>46229.59027777778</v>
-      </c>
-      <c r="F343" t="inlineStr">
-        <is>
-          <t>SICK ASSIST</t>
-        </is>
-      </c>
-      <c r="G343" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H343" t="inlineStr"/>
-      <c r="I343" t="inlineStr">
-        <is>
-          <t>TREMONT ST &amp; TEMPLE PL
-BOSTON, MA 02111
-UNITED STA</t>
-        </is>
-      </c>
-      <c r="J343" t="n">
-        <v>42.35561100811422</v>
-      </c>
-      <c r="K343" t="n">
-        <v>-71.06289400004533</v>
-      </c>
-      <c r="L343" t="n">
-        <v>1502.5</v>
-      </c>
-      <c r="M343" t="inlineStr">
-        <is>
-          <t>Sick assist on Jul 26, 2026, 1502 m from Copley Place (TREMONT ST &amp; TEMPLE PL
-BOSTON, MA 02111
-UNITED STA). Case #262064307 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>262064419</t>
-        </is>
-      </c>
-      <c r="E344" s="3" t="n">
-        <v>46229.90138888889</v>
-      </c>
-      <c r="F344" t="inlineStr">
-        <is>
-          <t>HARASSMENT/ CRIMINAL HARASSMENT</t>
-        </is>
-      </c>
-      <c r="G344" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H344" t="inlineStr"/>
-      <c r="I344" t="inlineStr">
-        <is>
-          <t>NASSAU ST</t>
-        </is>
-      </c>
-      <c r="J344" t="n">
-        <v>42.34880604399623</v>
-      </c>
-      <c r="K344" t="n">
-        <v>-71.06285446968663</v>
-      </c>
-      <c r="L344" t="n">
-        <v>1221.7</v>
-      </c>
-      <c r="M344" t="inlineStr">
-        <is>
-          <t>Harassment/ criminal harassment on Jul 26, 2026, 1222 m from Copley Place (NASSAU ST). Case #262064419 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>262064339</t>
-        </is>
-      </c>
-      <c r="E345" s="3" t="n">
-        <v>46229.63333333333</v>
-      </c>
-      <c r="F345" t="inlineStr">
-        <is>
-          <t>ASSAULT - AGGRAVATED</t>
-        </is>
-      </c>
-      <c r="G345" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H345" t="inlineStr"/>
-      <c r="I345" t="inlineStr">
-        <is>
-          <t>HARRISON AVE</t>
-        </is>
-      </c>
-      <c r="J345" t="n">
-        <v>42.33511903946613</v>
-      </c>
-      <c r="K345" t="n">
-        <v>-71.07491709613726</v>
-      </c>
-      <c r="L345" t="n">
-        <v>1407.3</v>
-      </c>
-      <c r="M345" t="inlineStr">
-        <is>
-          <t>Assault - aggravated on Jul 26, 2026, 1407 m from Copley Place (HARRISON AVE). Case #262064339 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>262064236</t>
-        </is>
-      </c>
-      <c r="E346" s="3" t="n">
-        <v>46229.37638888889</v>
-      </c>
-      <c r="F346" t="inlineStr">
-        <is>
-          <t>SICK ASSIST</t>
-        </is>
-      </c>
-      <c r="G346" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H346" t="inlineStr"/>
-      <c r="I346" t="inlineStr">
-        <is>
-          <t>TREMONT ST</t>
-        </is>
-      </c>
-      <c r="J346" t="n">
-        <v>42.34470135794417</v>
-      </c>
-      <c r="K346" t="n">
-        <v>-71.0703760849388</v>
-      </c>
-      <c r="L346" t="n">
-        <v>678.7</v>
-      </c>
-      <c r="M346" t="inlineStr">
-        <is>
-          <t>Sick assist on Jul 26, 2026, 679 m from Copley Place (TREMONT ST). Case #262064236 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>262064234</t>
-        </is>
-      </c>
-      <c r="E347" s="3" t="n">
-        <v>46229.31944444445</v>
-      </c>
-      <c r="F347" t="inlineStr">
-        <is>
-          <t>INVESTIGATE PERSON</t>
-        </is>
-      </c>
-      <c r="G347" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H347" t="inlineStr"/>
-      <c r="I347" t="inlineStr">
-        <is>
-          <t>SAINT JAMES AVE</t>
-        </is>
-      </c>
-      <c r="J347" t="n">
-        <v>42.34947585701249</v>
-      </c>
-      <c r="K347" t="n">
-        <v>-71.07640149637847</v>
-      </c>
-      <c r="L347" t="n">
-        <v>230.3</v>
-      </c>
-      <c r="M347" t="inlineStr">
-        <is>
-          <t>Investigate person on Jul 26, 2026, 230 m from Copley Place (SAINT JAMES AVE). Case #262064234 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -23513,7 +23513,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01 05:00:58.075328+00:00</t>
+          <t>2026-08-01 05:06:16.167337+00:00</t>
         </is>
       </c>
     </row>
@@ -23545,7 +23545,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-25 05:00:58.075328+00:00</t>
+          <t>2026-07-25 05:06:16.167337+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/latest/blotter_report.xlsx
+++ b/reports/latest/blotter_report.xlsx
@@ -13,10 +13,10 @@
     <sheet name="Run Metadata" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Highlights'!$A$1:$M$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$350</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$391</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1103,17 +1103,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>INTLPLAZA</t>
+          <t>INTLMARKET</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>International Plaza</t>
+          <t>International Market Place</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2223 North West Shore Boulevard Tampa FL 33607</t>
+          <t>2330 Kalakaua Avenue, Honolulu HI 96815</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1122,25 +1122,25 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
+        <v>41</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>1534.5</v>
+        <v>99.7</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>46232.16666666666</v>
+        <v>46233.78047453704</v>
       </c>
       <c r="L15" t="b">
         <v>0</v>
@@ -1149,32 +1149,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LENOX</t>
+          <t>INTLPLAZA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lenox Square</t>
+          <t>International Plaza</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3393 Peachtree Road Northeast Atlanta GA 30326</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>NO COVERAGE</t>
+          <t>2223 North West Shore Boulevard Tampa FL 33607</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1182,8 +1182,12 @@
       <c r="I16" t="n">
         <v>0</v>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="J16" t="n">
+        <v>1534.5</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>46232.16666666666</v>
+      </c>
       <c r="L16" t="b">
         <v>0</v>
       </c>
@@ -1191,22 +1195,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MALLATMILLENIA</t>
+          <t>LENOX</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Mall at Millenia</t>
+          <t>Lenox Square</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4200 Conroy Road, Orlando, FL 32839</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>3393 Peachtree Road Northeast Atlanta GA 30326</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>NO COVERAGE</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1233,17 +1237,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NORFOLKPO</t>
+          <t>MALLATMILLENIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Norfolk Premium Outlets</t>
+          <t>The Mall at Millenia</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1600 Premium Outlets Boulevard Norfolk VA 23502</t>
+          <t>4200 Conroy Road, Orlando, FL 32839</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1252,7 +1256,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1264,14 +1268,10 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1118.9</v>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v>46233</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="b">
         <v>0</v>
       </c>
@@ -1279,17 +1279,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>NORFOLKPO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Norfolk Premium Outlets</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>401 Northeast Northgate Way Seattle WA 98125</t>
+          <t>1600 Premium Outlets Boulevard Norfolk VA 23502</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1298,25 +1298,25 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>14</v>
-      </c>
-      <c r="F19" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
       <c r="G19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>145.2</v>
+        <v>1118.9</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>46233.28194444445</v>
+        <v>46233</v>
       </c>
       <c r="L19" t="b">
         <v>0</v>
@@ -1325,17 +1325,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>433 Opry Mills Drive Nashville TN 37214</t>
+          <t>401 Northeast Northgate Way Seattle WA 98125</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1344,22 +1344,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>145.2</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>46233.28194444445</v>
+      </c>
       <c r="L20" t="b">
         <v>0</v>
       </c>
@@ -1367,17 +1371,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>OPRYMILLS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Opry Mills</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4400 Sharon Road Charlotte NC 28211</t>
+          <t>433 Opry Mills Drive Nashville TN 37214</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1386,26 +1390,22 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>7</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>178.9</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>46232.16666666666</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="b">
         <v>0</v>
       </c>
@@ -1413,17 +1413,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4502 South Steele Street Tacoma WA 98409</t>
+          <t>4400 Sharon Road Charlotte NC 28211</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1432,25 +1432,25 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>471.3</v>
+        <v>178.9</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>46233</v>
+        <v>46232.16666666666</v>
       </c>
       <c r="L22" t="b">
         <v>0</v>
@@ -1459,41 +1459,45 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>THEDOMAIN</t>
+          <t>TACOMAMALL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Domain</t>
+          <t>Tacoma Mall</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>11410 Century Oaks Terrace Austin TX 78758</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>NO COVERAGE</t>
+          <t>4502 South Steele Street Tacoma WA 98409</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>471.3</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>46233</v>
+      </c>
       <c r="L23" t="b">
         <v>0</v>
       </c>
@@ -1501,45 +1505,41 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>THEDOMAIN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>The Domain</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>7700 East Kellogg Wichita KS 67207</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>11410 Century Oaks Terrace Austin TX 78758</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>NO COVERAGE</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>33</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>23</v>
-      </c>
-      <c r="J24" t="n">
-        <v>288.9</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>46233.7625</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="b">
         <v>0</v>
       </c>
@@ -1547,17 +1547,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UNIVPARKVILLAGE</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>University Park Village</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1612 South University Drive Fort Worth TX 76107</t>
+          <t>7700 East Kellogg Wichita KS 67207</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1566,28 +1566,116 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="J25" t="n">
+        <v>288.9</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>46233.7625</v>
+      </c>
       <c r="L25" t="b">
         <v>0</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>UNIVPARKVILLAGE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>University Park Village</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1612 South University Drive Fort Worth TX 76107</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>WAIKELE</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Waikele Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>94-790 Lumiaina Street Waipahu HI 96797</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L25"/>
+  <autoFilter ref="A1:L27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1741,30 +1829,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>INTLMARKET</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>International Market Place</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HOUSTONGAL:Houston PD NIBRS — Person</t>
+          <t>INTLMARKET:vg88-5rn5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>094686126</t>
+          <t>260725-1158</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>46229</v>
+        <v>46228.70266203704</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Simple assault</t>
+          <t>ASSAULT</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1774,26 +1862,26 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>13B</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5000-5099 WESTHEIMER RD</t>
+          <t>2300 BLOCK KALAKAUA AVE</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>29.74071090457959</v>
+        <v>21.27805648814</v>
       </c>
       <c r="K3" t="n">
-        <v>-95.46251430091121</v>
+        <v>-157.827664940544</v>
       </c>
       <c r="L3" t="n">
-        <v>217.1</v>
+        <v>99.7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Simple assault on Jul 26, 2026, 217 m from Houston Galleria (5000-5099 WESTHEIMER RD). Case #094686126 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 25, 2026, 100 m from International Market Place (2300 BLOCK KALAKAUA AVE). Case #260725-1158 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1903,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>094513626</t>
+          <t>094686126</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
@@ -1823,7 +1911,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aggravated Assault</t>
+          <t>Simple assault</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1833,56 +1921,56 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>13A</t>
+          <t>13B</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5100-5199 HIDALGO ST</t>
+          <t>5000-5099 WESTHEIMER RD</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>29.73535149549964</v>
+        <v>29.74071090457959</v>
       </c>
       <c r="K4" t="n">
-        <v>-95.46474014804627</v>
+        <v>-95.46251430091121</v>
       </c>
       <c r="L4" t="n">
-        <v>447.9</v>
+        <v>217.1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 26, 2026, 448 m from Houston Galleria (5100-5199 HIDALGO ST). Case #094513626 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 26, 2026, 217 m from Houston Galleria (5000-5099 WESTHEIMER RD). Case #094686126 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>INTLMARKET</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>International Market Place</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HOUSTONGAL:Houston PD NIBRS — Property</t>
+          <t>INTLMARKET:vg88-5rn5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>095242126</t>
+          <t>260726-0222</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>46230</v>
+        <v>46229.15130787037</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Robbery</t>
+          <t>ASSAULT</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1892,56 +1980,56 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2700-2799 LOOP N</t>
+          <t>2200 BLOCK KALAKAUA AVE</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>29.7388306267185</v>
+        <v>21.280046658192</v>
       </c>
       <c r="K5" t="n">
-        <v>-95.45805588032616</v>
+        <v>-157.829687791355</v>
       </c>
       <c r="L5" t="n">
-        <v>588.1</v>
+        <v>384.6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Robbery on Jul 27, 2026, 588 m from Houston Galleria (2700-2799 LOOP N). Case #095242126 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 26, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260726-0222 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>HOUSTONGAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Empire Mall</t>
+          <t>Houston Galleria</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+          <t>HOUSTONGAL:Houston PD NIBRS — Person</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CFS26-161839</t>
+          <t>094513626</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>46231.00275462963</v>
+        <v>46229</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Assault P3</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1951,56 +2039,56 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>13A</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>W 47TH ST &amp; S WESTPORT AVE</t>
+          <t>5100-5199 HIDALGO ST</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>43.50940131405472</v>
+        <v>29.73535149549964</v>
       </c>
       <c r="K6" t="n">
-        <v>-96.76746570282992</v>
+        <v>-95.46474014804627</v>
       </c>
       <c r="L6" t="n">
-        <v>678.4</v>
+        <v>447.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Assault p3 on Jul 28, 2026, 678 m from Empire Mall (W 47TH ST &amp; S WESTPORT AVE). Case #CFS26-161839 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 26, 2026, 448 m from Houston Galleria (5100-5199 HIDALGO ST). Case #094513626 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>INTLMARKET</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>International Market Place</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>INTLMARKET:vg88-5rn5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DP2026411044131300</t>
+          <t>260729-0737</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>46229.1125</v>
+        <v>46232.46952546296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>assault-simple</t>
+          <t>ASSAULT</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2010,56 +2098,56 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>other-crimes-against-persons</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3200 BLOCK E CHERRY CREEK S DR</t>
+          <t>2500 BLOCK KALAKAUA AVE</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>39.71130989687384</v>
+        <v>21.273862837838</v>
       </c>
       <c r="K7" t="n">
-        <v>-104.9490029653731</v>
+        <v>-157.82387239543</v>
       </c>
       <c r="L7" t="n">
-        <v>696.3</v>
+        <v>544.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Assault-simple on Jul 26, 2026, 696 m from Cherry Creek Shopping Center (3200 BLOCK E CHERRY CREEK S DR). Victims: 1. Case #DP2026411044 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 29, 2026, 545 m from International Market Place (2500 BLOCK KALAKAUA AVE). Case #260729-0737 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COPLEY</t>
+          <t>INTLMARKET</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Copley Place</t>
+          <t>International Market Place</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+          <t>INTLMARKET:vg88-5rn5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>262064756</t>
+          <t>260725-1627</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>46230.80347222222</v>
+        <v>46228.93998842593</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ASSAULT - SIMPLE</t>
+          <t>ASSAULT</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2067,54 +2155,58 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MASSACHUSETTS AVE</t>
+          <t>200 BLOCK BEACH WALK</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>42.34439568415441</v>
+        <v>21.278930465176</v>
       </c>
       <c r="K8" t="n">
-        <v>-71.08632016344815</v>
+        <v>-157.832248174365</v>
       </c>
       <c r="L8" t="n">
-        <v>798.7</v>
+        <v>583.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Assault - simple on Jul 27, 2026, 799 m from Copley Place (MASSACHUSETTS AVE). Case #262064756 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 25, 2026, 584 m from International Market Place (200 BLOCK BEACH WALK). Case #260725-1627 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>HOUSTONGAL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Empire Mall</t>
+          <t>Houston Galleria</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+          <t>HOUSTONGAL:Houston PD NIBRS — Property</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CFS26-161603</t>
+          <t>095242126</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>46230.83325231481</v>
+        <v>46230</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2124,56 +2216,56 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>S WESTPORT AVE &amp; W 41ST ST</t>
+          <t>2700-2799 LOOP N</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>43.51485103457241</v>
+        <v>29.7388306267185</v>
       </c>
       <c r="K9" t="n">
-        <v>-96.76794119445807</v>
+        <v>-95.45805588032616</v>
       </c>
       <c r="L9" t="n">
-        <v>808.9</v>
+        <v>588.1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Assault on Jul 27, 2026, 809 m from Empire Mall (S WESTPORT AVE &amp; W 41ST ST). Case #CFS26-161603 (use for a records request — full narratives are not published in open data).</t>
+          <t>Robbery on Jul 27, 2026, 588 m from Houston Galleria (2700-2799 LOOP N). Case #095242126 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Empire Mall</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>20260729-1600-11</t>
+          <t>CFS26-161839</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>46232.16666666666</v>
+        <v>46231.00275462963</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Simple Assault</t>
+          <t>Assault P3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2183,56 +2275,56 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>13B</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4700 PIEDMONT ROW DR</t>
+          <t>W 47TH ST &amp; S WESTPORT AVE</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>35.15196312662653</v>
+        <v>43.50940131405472</v>
       </c>
       <c r="K10" t="n">
-        <v>-80.83980651357408</v>
+        <v>-96.76746570282992</v>
       </c>
       <c r="L10" t="n">
-        <v>850.6</v>
+        <v>678.4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Simple assault on Jul 29, 2026, 851 m from Southpark (4700 PIEDMONT ROW DR). Status: Open. Case #20260729-1600-11 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault p3 on Jul 28, 2026, 678 m from Empire Mall (W 47TH ST &amp; S WESTPORT AVE). Case #CFS26-161839 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2620701835</t>
+          <t>DP2026411044131300</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>46229</v>
+        <v>46229.1125</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Assault Simple</t>
+          <t>assault-simple</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2242,26 +2334,26 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>other-crimes-against-persons</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4000 S LAWRENCE ST</t>
+          <t>3200 BLOCK E CHERRY CREEK S DR</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>47.219421</v>
+        <v>39.71130989687384</v>
       </c>
       <c r="K11" t="n">
-        <v>-122.478428</v>
+        <v>-104.9490029653731</v>
       </c>
       <c r="L11" t="n">
-        <v>853.4</v>
+        <v>696.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Assault simple on Jul 26, 2026, 853 m from Tacoma Mall (4000 S LAWRENCE ST). Case #2620701835 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault-simple on Jul 26, 2026, 696 m from Cherry Creek Shopping Center (3200 BLOCK E CHERRY CREEK S DR). Victims: 1. Case #DP2026411044 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2283,15 +2375,15 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>262064416</t>
+          <t>262064756</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>46229.87569444445</v>
+        <v>46230.80347222222</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASSAULT - AGGRAVATED</t>
+          <t>ASSAULT - SIMPLE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2302,51 +2394,51 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>HUNTINGTON AVE</t>
+          <t>MASSACHUSETTS AVE</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>42.34221543503831</v>
+        <v>42.34439568415441</v>
       </c>
       <c r="K12" t="n">
-        <v>-71.08577074656198</v>
+        <v>-71.08632016344815</v>
       </c>
       <c r="L12" t="n">
-        <v>898.8</v>
+        <v>798.7</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Assault - aggravated on Jul 26, 2026, 899 m from Copley Place (HUNTINGTON AVE). Case #262064416 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault - simple on Jul 27, 2026, 799 m from Copley Place (MASSACHUSETTS AVE). Case #262064756 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Empire Mall</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>71878728447</t>
+          <t>CFS26-161603</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>46230.4375</v>
+        <v>46230.83325231481</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Robbery</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2356,56 +2448,56 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>VIOLENT CRIME</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>16XX BLOCK OF N 105TH ST</t>
+          <t>S WESTPORT AVE &amp; W 41ST ST</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>47.70504225</v>
+        <v>43.51485103457241</v>
       </c>
       <c r="K13" t="n">
-        <v>-122.338094779232</v>
+        <v>-96.76794119445807</v>
       </c>
       <c r="L13" t="n">
-        <v>938.8</v>
+        <v>808.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Robbery on Jul 27, 2026, 939 m from Northgate Station (16XX BLOCK OF N 105TH ST). Case #2026-220064 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 27, 2026, 809 m from Empire Mall (S WESTPORT AVE &amp; W 41ST ST). Case #CFS26-161603 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>INTLMARKET</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>International Market Place</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>INTLMARKET:vg88-5rn5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2621000152</t>
+          <t>260729-0943</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>46232</v>
+        <v>46232.56469907407</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Assault Simple</t>
+          <t>ASSAULT</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2415,56 +2507,56 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3500 S 45TH ST</t>
+          <t>2600 BLOCK KALAKAUA AVE</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>47.216421</v>
+        <v>21.271474893966</v>
       </c>
       <c r="K14" t="n">
-        <v>-122.482428</v>
+        <v>-157.82264961775</v>
       </c>
       <c r="L14" t="n">
-        <v>1074.3</v>
+        <v>837.3</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Assault simple on Jul 29, 2026, 1074 m from Tacoma Mall (3500 S 45TH ST). Case #2621000152 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 29, 2026, 837 m from International Market Place (2600 BLOCK KALAKAUA AVE). Case #260729-0943 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COPLEY</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Copley Place</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>262064432</t>
+          <t>20260729-1600-11</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>46229.91666666666</v>
+        <v>46232.16666666666</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ROBBERY</t>
+          <t>Simple Assault</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2472,54 +2564,58 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>13B</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>4700 PIEDMONT ROW DR</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>42.33954198983015</v>
+        <v>35.15196312662653</v>
       </c>
       <c r="K15" t="n">
-        <v>-71.06940876967543</v>
+        <v>-80.83980651357408</v>
       </c>
       <c r="L15" t="n">
-        <v>1123.7</v>
+        <v>850.6</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Robbery on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064432 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 29, 2026, 851 m from Southpark (4700 PIEDMONT ROW DR). Status: Open. Case #20260729-1600-11 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COPLEY</t>
+          <t>TACOMAMALL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Copley Place</t>
+          <t>Tacoma Mall</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>262064298</t>
+          <t>2620701835</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>46229.08611111111</v>
+        <v>46229</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FIREARM/WEAPON - LOST</t>
+          <t>Assault Simple</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2527,54 +2623,58 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Assault Offenses</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>4000 S LAWRENCE ST</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>42.33954198983015</v>
+        <v>47.219421</v>
       </c>
       <c r="K16" t="n">
-        <v>-71.06940876967543</v>
+        <v>-122.478428</v>
       </c>
       <c r="L16" t="n">
-        <v>1123.7</v>
+        <v>853.4</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Firearm/weapon - lost on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064298 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault simple on Jul 26, 2026, 853 m from Tacoma Mall (4000 S LAWRENCE ST). Case #2620701835 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>COPLEY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>71894237115</t>
+          <t>262064416</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>46231.20833333334</v>
+        <v>46229.87569444445</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aggravated Assault</t>
+          <t>ASSAULT - AGGRAVATED</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2582,28 +2682,24 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>VIOLENT CRIME</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>15XX BLOCK OF NE 107TH ST</t>
+          <t>HUNTINGTON AVE</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>47.70668788</v>
+        <v>42.34221543503831</v>
       </c>
       <c r="K17" t="n">
-        <v>-122.311189997702</v>
+        <v>-71.08577074656198</v>
       </c>
       <c r="L17" t="n">
-        <v>1145.7</v>
+        <v>898.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-221056 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault - aggravated on Jul 26, 2026, 899 m from Copley Place (HUNTINGTON AVE). Case #262064416 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2625,15 +2721,15 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>71889871382</t>
+          <t>71878728447</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>46231.00625</v>
+        <v>46230.4375</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Simple Assault</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2643,56 +2739,56 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>ALL OTHER</t>
+          <t>VIOLENT CRIME</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>15XX BLOCK OF NE 107TH ST</t>
+          <t>16XX BLOCK OF N 105TH ST</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>47.70668788</v>
+        <v>47.70504225</v>
       </c>
       <c r="K18" t="n">
-        <v>-122.311189997702</v>
+        <v>-122.338094779232</v>
       </c>
       <c r="L18" t="n">
-        <v>1145.7</v>
+        <v>938.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Simple assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-220636 (use for a records request — full narratives are not published in open data).</t>
+          <t>Robbery on Jul 27, 2026, 939 m from Northgate Station (16XX BLOCK OF N 105TH ST). Case #2026-220064 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>TACOMAMALL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Tacoma Mall</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>26C142249</t>
+          <t>2621000152</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>46230.75</v>
+        <v>46232</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>BATTERY ABW</t>
+          <t>Assault Simple</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2702,56 +2798,56 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>SIM_ASSAULT</t>
+          <t>Assault Offenses</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>700 BLOCK OF S MISSION RD</t>
+          <t>3500 S 45TH ST</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>37.6756469679485</v>
+        <v>47.216421</v>
       </c>
       <c r="K19" t="n">
-        <v>-97.25850032865422</v>
+        <v>-122.482428</v>
       </c>
       <c r="L19" t="n">
-        <v>1251.5</v>
+        <v>1074.3</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Battery abw on Jul 27, 2026, 1251 m from Towne East Square (700 BLOCK OF S MISSION RD). Case #26C142249 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault simple on Jul 29, 2026, 1074 m from Tacoma Mall (3500 S 45TH ST). Case #2621000152 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>COPLEY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Empire Mall</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CFS26-164521</t>
+          <t>262064432</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>46234.03421296296</v>
+        <v>46229.91666666666</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aggravated Assault</t>
+          <t>ROBBERY</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2759,58 +2855,54 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Assault</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>S MARION RD &amp; W 41ST ST</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>43.51481738299845</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K20" t="n">
-        <v>-96.79096028032072</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L20" t="n">
-        <v>1322.4</v>
+        <v>1123.7</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 31, 2026, 1322 m from Empire Mall (S MARION RD &amp; W 41ST ST). Case #CFS26-164521 (use for a records request — full narratives are not published in open data).</t>
+          <t>Robbery on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064432 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>COPLEY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HOUSTONGAL:Houston PD NIBRS — Person</t>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>096140526</t>
+          <t>262064298</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>46232</v>
+        <v>46229.08611111111</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aggravated Assault</t>
+          <t>FIREARM/WEAPON - LOST</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2818,58 +2910,54 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>13A</t>
-        </is>
-      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1900-1999 POST OAK PARK DR</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>29.74712522681273</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K21" t="n">
-        <v>-95.45374747370188</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L21" t="n">
-        <v>1323.4</v>
+        <v>1123.7</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 29, 2026, 1323 m from Houston Galleria (1900-1999 POST OAK PARK DR). Case #096140526 (use for a records request — full narratives are not published in open data).</t>
+          <t>Firearm/weapon - lost on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064298 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202675136         </t>
+          <t>71894237115</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>46228.97847222222</v>
+        <v>46231.20833333334</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">[13B] ASSAULT                                                                   </t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2877,54 +2965,58 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>VIOLENT CRIME</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5XXX S HARDY DR</t>
+          <t>15XX BLOCK OF NE 107TH ST</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>33.3757495513233</v>
+        <v>47.70668788</v>
       </c>
       <c r="K22" t="n">
-        <v>-111.9531832468173</v>
+        <v>-122.311189997702</v>
       </c>
       <c r="L22" t="n">
-        <v>1345.1</v>
+        <v>1145.7</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>[13b] assault on Jul 25, 2026, 1345 m from Arizona Mills (5XXX S HARDY DR). Case #TE202675136          (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-221056 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>COPLEY</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Copley Place</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>262064339</t>
+          <t>71889871382</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>46229.63333333333</v>
+        <v>46231.00625</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ASSAULT - AGGRAVATED</t>
+          <t>Simple Assault</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2932,54 +3024,58 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>ALL OTHER</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>15XX BLOCK OF NE 107TH ST</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>42.33511903946613</v>
+        <v>47.70668788</v>
       </c>
       <c r="K23" t="n">
-        <v>-71.07491709613726</v>
+        <v>-122.311189997702</v>
       </c>
       <c r="L23" t="n">
-        <v>1407.3</v>
+        <v>1145.7</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Assault - aggravated on Jul 26, 2026, 1407 m from Copley Place (HARRISON AVE). Case #262064339 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-220636 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Empire Mall</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CFS26-164393</t>
+          <t>26C142249</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>46233.93733796296</v>
+        <v>46230.75</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>BATTERY ABW</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2989,26 +3085,26 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>SIM_ASSAULT</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>S LARCH AVE &amp; W 43RD ST</t>
+          <t>700 BLOCK OF S MISSION RD</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>43.51319846254545</v>
+        <v>37.6756469679485</v>
       </c>
       <c r="K24" t="n">
-        <v>-96.79336119066248</v>
+        <v>-97.25850032865422</v>
       </c>
       <c r="L24" t="n">
-        <v>1453.4</v>
+        <v>1251.5</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Assault on Jul 30, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-164393 (use for a records request — full narratives are not published in open data).</t>
+          <t>Battery abw on Jul 27, 2026, 1251 m from Towne East Square (700 BLOCK OF S MISSION RD). Case #26C142249 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -3030,15 +3126,15 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CFS26-159792</t>
+          <t>CFS26-164521</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>46229.12712962963</v>
+        <v>46234.03421296296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Weapons Violations</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3048,56 +3144,56 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Weapons</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>S LARCH AVE &amp; W 43RD ST</t>
+          <t>S MARION RD &amp; W 41ST ST</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>43.51319846254545</v>
+        <v>43.51481738299845</v>
       </c>
       <c r="K25" t="n">
-        <v>-96.79336119066248</v>
+        <v>-96.79096028032072</v>
       </c>
       <c r="L25" t="n">
-        <v>1453.4</v>
+        <v>1322.4</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Weapons violations on Jul 26, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-159792 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 31, 2026, 1322 m from Empire Mall (S MARION RD &amp; W 41ST ST). Case #CFS26-164521 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>COPLEY</t>
+          <t>HOUSTONGAL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Copley Place</t>
+          <t>Houston Galleria</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+          <t>HOUSTONGAL:Houston PD NIBRS — Person</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>262064587</t>
+          <t>096140526</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>46230.5</v>
+        <v>46232</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ASSAULT - AGGRAVATED</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3105,24 +3201,28 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>13A</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>MASSACHUSETTS AVE</t>
+          <t>1900-1999 POST OAK PARK DR</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>42.3342194178955</v>
+        <v>29.74712522681273</v>
       </c>
       <c r="K26" t="n">
-        <v>-71.07434615707857</v>
+        <v>-95.45374747370188</v>
       </c>
       <c r="L26" t="n">
-        <v>1513.9</v>
+        <v>1323.4</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Assault - aggravated on Jul 27, 2026, 1514 m from Copley Place (MASSACHUSETTS AVE). Case #262064587 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 29, 2026, 1323 m from Houston Galleria (1900-1999 POST OAK PARK DR). Case #096140526 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M350"/>
+  <dimension ref="A1:M391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -19940,40 +20040,40 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>262064179</t>
+          <t>262064284</t>
         </is>
       </c>
       <c r="E287" s="3" t="n">
-        <v>46229.07361111111</v>
+        <v>46229.54305555556</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>INVESTIGATE PROPERTY</t>
+          <t>M/V ACCIDENT - INVOLVING PEDESTRIAN - INJURY</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H287" t="inlineStr"/>
       <c r="I287" t="inlineStr">
         <is>
-          <t>BOYLSTON ST</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J287" t="n">
-        <v>42.35234109431519</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K287" t="n">
-        <v>-71.06432465046424</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L287" t="n">
-        <v>1213.3</v>
+        <v>1123.7</v>
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Investigate property on Jul 26, 2026, 1213 m from Copley Place (BOYLSTON ST). Case #262064179 (use for a records request — full narratives are not published in open data).</t>
+          <t>M/v accident - involving pedestrian - injury on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064284 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -19995,15 +20095,15 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>262064284</t>
+          <t>262064275</t>
         </is>
       </c>
       <c r="E288" s="3" t="n">
-        <v>46229.54305555556</v>
+        <v>46229.51111111111</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>M/V ACCIDENT - INVOLVING PEDESTRIAN - INJURY</t>
+          <t>FORGERY / COUNTERFEITING</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -20028,7 +20128,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>M/v accident - involving pedestrian - injury on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064284 (use for a records request — full narratives are not published in open data).</t>
+          <t>Forgery / counterfeiting on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064275 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20050,15 +20150,15 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>262064275</t>
+          <t>262064650</t>
         </is>
       </c>
       <c r="E289" s="3" t="n">
-        <v>46229.51111111111</v>
+        <v>46230.61875</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>FORGERY / COUNTERFEITING</t>
+          <t>M/V ACCIDENT - INVOLVING BICYCLE - INJURY</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -20068,77 +20168,22 @@
       </c>
       <c r="H289" t="inlineStr"/>
       <c r="I289" t="inlineStr">
-        <is>
-          <t>HARRISON AVE</t>
-        </is>
-      </c>
-      <c r="J289" t="n">
-        <v>42.33954198983015</v>
-      </c>
-      <c r="K289" t="n">
-        <v>-71.06940876967543</v>
-      </c>
-      <c r="L289" t="n">
-        <v>1123.7</v>
-      </c>
-      <c r="M289" t="inlineStr">
-        <is>
-          <t>Forgery / counterfeiting on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064275 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>262064650</t>
-        </is>
-      </c>
-      <c r="E290" s="3" t="n">
-        <v>46230.61875</v>
-      </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>M/V ACCIDENT - INVOLVING BICYCLE - INJURY</t>
-        </is>
-      </c>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H290" t="inlineStr"/>
-      <c r="I290" t="inlineStr">
         <is>
           <t>MASSACHUSETTS AVE &amp; TREMONT ST
 BOSTON, MA 02118
 UN</t>
         </is>
       </c>
-      <c r="J290" t="n">
+      <c r="J289" t="n">
         <v>42.33929095757131</v>
       </c>
-      <c r="K290" t="n">
+      <c r="K289" t="n">
         <v>-71.08041395047391</v>
       </c>
-      <c r="L290" t="n">
+      <c r="L289" t="n">
         <v>953.4</v>
       </c>
-      <c r="M290" t="inlineStr">
+      <c r="M289" t="inlineStr">
         <is>
           <t>M/v accident - involving bicycle - injury on Jul 27, 2026, 953 m from Copley Place (MASSACHUSETTS AVE &amp; TREMONT ST
 BOSTON, MA 02118
@@ -20146,6 +20191,61 @@
         </is>
       </c>
     </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>262064295</t>
+        </is>
+      </c>
+      <c r="E290" s="3" t="n">
+        <v>46229.54791666667</v>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>SICK ASSIST</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr"/>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>BOYLSTON ST</t>
+        </is>
+      </c>
+      <c r="J290" t="n">
+        <v>42.34862381555496</v>
+      </c>
+      <c r="K290" t="n">
+        <v>-71.08277637086411</v>
+      </c>
+      <c r="L290" t="n">
+        <v>437.3</v>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>Sick assist on Jul 26, 2026, 437 m from Copley Place (BOYLSTON ST). Case #262064295 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
@@ -20164,15 +20264,15 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>262064295</t>
+          <t>262064382</t>
         </is>
       </c>
       <c r="E291" s="3" t="n">
-        <v>46229.54791666667</v>
+        <v>46229.78680555556</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>SICK ASSIST</t>
+          <t>VERBAL DISPUTE</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -20183,21 +20283,21 @@
       <c r="H291" t="inlineStr"/>
       <c r="I291" t="inlineStr">
         <is>
-          <t>BOYLSTON ST</t>
+          <t>HUDSON ST</t>
         </is>
       </c>
       <c r="J291" t="n">
-        <v>42.34862381555496</v>
+        <v>42.34976401607222</v>
       </c>
       <c r="K291" t="n">
-        <v>-71.08277637086411</v>
+        <v>-71.06045076420118</v>
       </c>
       <c r="L291" t="n">
-        <v>437.3</v>
+        <v>1432.1</v>
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Sick assist on Jul 26, 2026, 437 m from Copley Place (BOYLSTON ST). Case #262064295 (use for a records request — full narratives are not published in open data).</t>
+          <t>Verbal dispute on Jul 26, 2026, 1432 m from Copley Place (HUDSON ST). Case #262064382 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20219,40 +20319,40 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>262064382</t>
+          <t>262064432</t>
         </is>
       </c>
       <c r="E292" s="3" t="n">
-        <v>46229.78680555556</v>
+        <v>46229.91666666666</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>VERBAL DISPUTE</t>
+          <t>ROBBERY</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H292" t="inlineStr"/>
       <c r="I292" t="inlineStr">
         <is>
-          <t>HUDSON ST</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J292" t="n">
-        <v>42.34976401607222</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K292" t="n">
-        <v>-71.06045076420118</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L292" t="n">
-        <v>1432.1</v>
+        <v>1123.7</v>
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Verbal dispute on Jul 26, 2026, 1432 m from Copley Place (HUDSON ST). Case #262064382 (use for a records request — full narratives are not published in open data).</t>
+          <t>Robbery on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064432 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20274,40 +20374,40 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>262064432</t>
+          <t>262064822</t>
         </is>
       </c>
       <c r="E293" s="3" t="n">
-        <v>46229.91666666666</v>
+        <v>46230.83541666667</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>ROBBERY</t>
+          <t>INVESTIGATE PERSON</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H293" t="inlineStr"/>
       <c r="I293" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>COLUMBUS SQ</t>
         </is>
       </c>
       <c r="J293" t="n">
-        <v>42.33954198983015</v>
+        <v>42.34332879779392</v>
       </c>
       <c r="K293" t="n">
-        <v>-71.06940876967543</v>
+        <v>-71.07788857963692</v>
       </c>
       <c r="L293" t="n">
-        <v>1123.7</v>
+        <v>477.1</v>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Robbery on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064432 (use for a records request — full narratives are not published in open data).</t>
+          <t>Investigate person on Jul 27, 2026, 477 m from Copley Place (COLUMBUS SQ). Case #262064822 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20329,11 +20429,11 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>262064822</t>
+          <t>262064697</t>
         </is>
       </c>
       <c r="E294" s="3" t="n">
-        <v>46230.83541666667</v>
+        <v>46230.70277777778</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -20348,21 +20448,21 @@
       <c r="H294" t="inlineStr"/>
       <c r="I294" t="inlineStr">
         <is>
-          <t>COLUMBUS SQ</t>
+          <t>MASSACHUSETTS AVE</t>
         </is>
       </c>
       <c r="J294" t="n">
-        <v>42.34332879779392</v>
+        <v>42.34867437636976</v>
       </c>
       <c r="K294" t="n">
-        <v>-71.07788857963692</v>
+        <v>-71.08841866225799</v>
       </c>
       <c r="L294" t="n">
-        <v>477.1</v>
+        <v>894.2</v>
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Investigate person on Jul 27, 2026, 477 m from Copley Place (COLUMBUS SQ). Case #262064822 (use for a records request — full narratives are not published in open data).</t>
+          <t>Investigate person on Jul 27, 2026, 894 m from Copley Place (MASSACHUSETTS AVE). Case #262064697 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20384,40 +20484,40 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>262064697</t>
+          <t>262064696</t>
         </is>
       </c>
       <c r="E295" s="3" t="n">
-        <v>46230.70277777778</v>
+        <v>46230.57777777778</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>INVESTIGATE PERSON</t>
+          <t>LARCENY THEFT FROM BUILDING</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H295" t="inlineStr"/>
       <c r="I295" t="inlineStr">
         <is>
-          <t>MASSACHUSETTS AVE</t>
+          <t>LINCOLN ST</t>
         </is>
       </c>
       <c r="J295" t="n">
-        <v>42.34867437636976</v>
+        <v>42.35043296884182</v>
       </c>
       <c r="K295" t="n">
-        <v>-71.08841866225799</v>
+        <v>-71.05873157807835</v>
       </c>
       <c r="L295" t="n">
-        <v>894.2</v>
+        <v>1584.6</v>
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Investigate person on Jul 27, 2026, 894 m from Copley Place (MASSACHUSETTS AVE). Case #262064697 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny theft from building on Jul 27, 2026, 1585 m from Copley Place (LINCOLN ST). Case #262064696 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20439,15 +20539,15 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>262064696</t>
+          <t>262064796</t>
         </is>
       </c>
       <c r="E296" s="3" t="n">
-        <v>46230.57777777778</v>
+        <v>46230.75</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>LARCENY THEFT FROM BUILDING</t>
+          <t>PROPERTY - LOST/ MISSING</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -20458,21 +20558,21 @@
       <c r="H296" t="inlineStr"/>
       <c r="I296" t="inlineStr">
         <is>
-          <t>LINCOLN ST</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J296" t="n">
-        <v>42.35043296884182</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K296" t="n">
-        <v>-71.05873157807835</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L296" t="n">
-        <v>1584.6</v>
+        <v>1123.7</v>
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Larceny theft from building on Jul 27, 2026, 1585 m from Copley Place (LINCOLN ST). Case #262064696 (use for a records request — full narratives are not published in open data).</t>
+          <t>Property - lost/ missing on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064796 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20494,40 +20594,40 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>262064796</t>
+          <t>262064756</t>
         </is>
       </c>
       <c r="E297" s="3" t="n">
-        <v>46230.75</v>
+        <v>46230.80347222222</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>PROPERTY - LOST/ MISSING</t>
+          <t>ASSAULT - SIMPLE</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H297" t="inlineStr"/>
       <c r="I297" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>MASSACHUSETTS AVE</t>
         </is>
       </c>
       <c r="J297" t="n">
-        <v>42.33954198983015</v>
+        <v>42.34439568415441</v>
       </c>
       <c r="K297" t="n">
-        <v>-71.06940876967543</v>
+        <v>-71.08632016344815</v>
       </c>
       <c r="L297" t="n">
-        <v>1123.7</v>
+        <v>798.7</v>
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Property - lost/ missing on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064796 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault - simple on Jul 27, 2026, 799 m from Copley Place (MASSACHUSETTS AVE). Case #262064756 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20549,40 +20649,40 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>262064756</t>
+          <t>262064716</t>
         </is>
       </c>
       <c r="E298" s="3" t="n">
-        <v>46230.80347222222</v>
+        <v>46230.72638888889</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>ASSAULT - SIMPLE</t>
+          <t>LARCENY SHOPLIFTING</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H298" t="inlineStr"/>
       <c r="I298" t="inlineStr">
         <is>
-          <t>MASSACHUSETTS AVE</t>
+          <t>NEWBURY ST</t>
         </is>
       </c>
       <c r="J298" t="n">
-        <v>42.34439568415441</v>
+        <v>42.35059716982988</v>
       </c>
       <c r="K298" t="n">
-        <v>-71.08632016344815</v>
+        <v>-71.07881030689927</v>
       </c>
       <c r="L298" t="n">
-        <v>798.7</v>
+        <v>345.4</v>
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Assault - simple on Jul 27, 2026, 799 m from Copley Place (MASSACHUSETTS AVE). Case #262064756 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny shoplifting on Jul 27, 2026, 345 m from Copley Place (NEWBURY ST). Case #262064716 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20604,40 +20704,40 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>262064716</t>
+          <t>262064587</t>
         </is>
       </c>
       <c r="E299" s="3" t="n">
-        <v>46230.72638888889</v>
+        <v>46230.5</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>LARCENY SHOPLIFTING</t>
+          <t>ASSAULT - AGGRAVATED</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H299" t="inlineStr"/>
       <c r="I299" t="inlineStr">
         <is>
-          <t>NEWBURY ST</t>
+          <t>MASSACHUSETTS AVE</t>
         </is>
       </c>
       <c r="J299" t="n">
-        <v>42.35059716982988</v>
+        <v>42.3342194178955</v>
       </c>
       <c r="K299" t="n">
-        <v>-71.07881030689927</v>
+        <v>-71.07434615707857</v>
       </c>
       <c r="L299" t="n">
-        <v>345.4</v>
+        <v>1513.9</v>
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Larceny shoplifting on Jul 27, 2026, 345 m from Copley Place (NEWBURY ST). Case #262064716 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault - aggravated on Jul 27, 2026, 1514 m from Copley Place (MASSACHUSETTS AVE). Case #262064587 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20659,40 +20759,40 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>262064587</t>
+          <t>262064392</t>
         </is>
       </c>
       <c r="E300" s="3" t="n">
-        <v>46230.5</v>
+        <v>46229.82222222222</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>ASSAULT - AGGRAVATED</t>
+          <t>M/V ACCIDENT - OTHER</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H300" t="inlineStr"/>
       <c r="I300" t="inlineStr">
         <is>
-          <t>MASSACHUSETTS AVE</t>
+          <t>TYLER ST</t>
         </is>
       </c>
       <c r="J300" t="n">
-        <v>42.3342194178955</v>
+        <v>42.3509005960865</v>
       </c>
       <c r="K300" t="n">
-        <v>-71.07434615707857</v>
+        <v>-71.06068690177561</v>
       </c>
       <c r="L300" t="n">
-        <v>1513.9</v>
+        <v>1439.7</v>
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Assault - aggravated on Jul 27, 2026, 1514 m from Copley Place (MASSACHUSETTS AVE). Case #262064587 (use for a records request — full narratives are not published in open data).</t>
+          <t>M/v accident - other on Jul 26, 2026, 1440 m from Copley Place (TYLER ST). Case #262064392 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20714,15 +20814,15 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>262064392</t>
+          <t>262064350</t>
         </is>
       </c>
       <c r="E301" s="3" t="n">
-        <v>46229.82222222222</v>
+        <v>46229.70486111111</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>M/V ACCIDENT - OTHER</t>
+          <t>INVESTIGATE PERSON</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
@@ -20733,21 +20833,21 @@
       <c r="H301" t="inlineStr"/>
       <c r="I301" t="inlineStr">
         <is>
-          <t>TYLER ST</t>
+          <t>HUNTINGTON AVE</t>
         </is>
       </c>
       <c r="J301" t="n">
-        <v>42.3509005960865</v>
+        <v>42.3473097976345</v>
       </c>
       <c r="K301" t="n">
-        <v>-71.06068690177561</v>
+        <v>-71.0791516658207</v>
       </c>
       <c r="L301" t="n">
-        <v>1439.7</v>
+        <v>129.3</v>
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>M/v accident - other on Jul 26, 2026, 1440 m from Copley Place (TYLER ST). Case #262064392 (use for a records request — full narratives are not published in open data).</t>
+          <t>Investigate person on Jul 26, 2026, 129 m from Copley Place (HUNTINGTON AVE). Case #262064350 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20769,40 +20869,40 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>262064350</t>
+          <t>262064616</t>
         </is>
       </c>
       <c r="E302" s="3" t="n">
-        <v>46229.70486111111</v>
+        <v>46230.50347222222</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>INVESTIGATE PERSON</t>
+          <t>DRUGS - POSSESSION/ SALE/ MANUFACTURING/ USE</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>QUALITY_OF_LIFE</t>
         </is>
       </c>
       <c r="H302" t="inlineStr"/>
       <c r="I302" t="inlineStr">
         <is>
-          <t>HUNTINGTON AVE</t>
+          <t>BOYLSTON SQ</t>
         </is>
       </c>
       <c r="J302" t="n">
-        <v>42.3473097976345</v>
+        <v>42.35197501205302</v>
       </c>
       <c r="K302" t="n">
-        <v>-71.0791516658207</v>
+        <v>-71.06332910808086</v>
       </c>
       <c r="L302" t="n">
-        <v>129.3</v>
+        <v>1271.5</v>
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Investigate person on Jul 26, 2026, 129 m from Copley Place (HUNTINGTON AVE). Case #262064350 (use for a records request — full narratives are not published in open data).</t>
+          <t>Drugs - possession/ sale/ manufacturing/ use on Jul 27, 2026, 1272 m from Copley Place (BOYLSTON SQ). Case #262064616 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20824,40 +20924,40 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>262064616</t>
+          <t>262064640</t>
         </is>
       </c>
       <c r="E303" s="3" t="n">
-        <v>46230.50347222222</v>
+        <v>46230.3125</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>DRUGS - POSSESSION/ SALE/ MANUFACTURING/ USE</t>
+          <t>INVESTIGATE PERSON</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>QUALITY_OF_LIFE</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H303" t="inlineStr"/>
       <c r="I303" t="inlineStr">
         <is>
-          <t>BOYLSTON SQ</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J303" t="n">
-        <v>42.35197501205302</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K303" t="n">
-        <v>-71.06332910808086</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L303" t="n">
-        <v>1271.5</v>
+        <v>1123.7</v>
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Drugs - possession/ sale/ manufacturing/ use on Jul 27, 2026, 1272 m from Copley Place (BOYLSTON SQ). Case #262064616 (use for a records request — full narratives are not published in open data).</t>
+          <t>Investigate person on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064640 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20879,40 +20979,40 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>262064640</t>
+          <t>262064573</t>
         </is>
       </c>
       <c r="E304" s="3" t="n">
-        <v>46230.3125</v>
+        <v>46230.45833333334</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>INVESTIGATE PERSON</t>
+          <t>SICK ASSIST - DRUG RELATED ILLNESS</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>QUALITY_OF_LIFE</t>
         </is>
       </c>
       <c r="H304" t="inlineStr"/>
       <c r="I304" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>ALBANY ST</t>
         </is>
       </c>
       <c r="J304" t="n">
-        <v>42.33954198983015</v>
+        <v>42.33428840659414</v>
       </c>
       <c r="K304" t="n">
-        <v>-71.06940876967543</v>
+        <v>-71.07239517543796</v>
       </c>
       <c r="L304" t="n">
-        <v>1123.7</v>
+        <v>1543.1</v>
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Investigate person on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064640 (use for a records request — full narratives are not published in open data).</t>
+          <t>Sick assist - drug related illness on Jul 27, 2026, 1543 m from Copley Place (ALBANY ST). Case #262064573 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20934,40 +21034,40 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>262064573</t>
+          <t>262064608</t>
         </is>
       </c>
       <c r="E305" s="3" t="n">
-        <v>46230.45833333334</v>
+        <v>46230</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>SICK ASSIST - DRUG RELATED ILLNESS</t>
+          <t>THREATS TO DO BODILY HARM</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>QUALITY_OF_LIFE</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H305" t="inlineStr"/>
       <c r="I305" t="inlineStr">
         <is>
-          <t>ALBANY ST</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J305" t="n">
-        <v>42.33428840659414</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K305" t="n">
-        <v>-71.07239517543796</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L305" t="n">
-        <v>1543.1</v>
+        <v>1123.7</v>
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Sick assist - drug related illness on Jul 27, 2026, 1543 m from Copley Place (ALBANY ST). Case #262064573 (use for a records request — full narratives are not published in open data).</t>
+          <t>Threats to do bodily harm on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064608 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20989,40 +21089,40 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>262064608</t>
+          <t>262064378</t>
         </is>
       </c>
       <c r="E306" s="3" t="n">
-        <v>46230</v>
+        <v>46229.79097222222</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>THREATS TO DO BODILY HARM</t>
+          <t>LARCENY ALL OTHERS</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H306" t="inlineStr"/>
       <c r="I306" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>W CONCORD ST</t>
         </is>
       </c>
       <c r="J306" t="n">
-        <v>42.33954198983015</v>
+        <v>42.33961961800693</v>
       </c>
       <c r="K306" t="n">
-        <v>-71.06940876967543</v>
+        <v>-71.07699236739417</v>
       </c>
       <c r="L306" t="n">
-        <v>1123.7</v>
+        <v>890.6</v>
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Threats to do bodily harm on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064608 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny all others on Jul 26, 2026, 891 m from Copley Place (W CONCORD ST). Case #262064378 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21044,40 +21144,40 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>262064378</t>
+          <t>262064152</t>
         </is>
       </c>
       <c r="E307" s="3" t="n">
-        <v>46229.79097222222</v>
+        <v>46229.01458333333</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>LARCENY ALL OTHERS</t>
+          <t>NOISY PARTY/RADIO-NO ARREST</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H307" t="inlineStr"/>
       <c r="I307" t="inlineStr">
         <is>
-          <t>W CONCORD ST</t>
+          <t>PHILLIPS ST</t>
         </is>
       </c>
       <c r="J307" t="n">
-        <v>42.33961961800693</v>
+        <v>42.36027809483424</v>
       </c>
       <c r="K307" t="n">
-        <v>-71.07699236739417</v>
+        <v>-71.06899804851336</v>
       </c>
       <c r="L307" t="n">
-        <v>890.6</v>
+        <v>1576.7</v>
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Larceny all others on Jul 26, 2026, 891 m from Copley Place (W CONCORD ST). Case #262064378 (use for a records request — full narratives are not published in open data).</t>
+          <t>Noisy party/radio-no arrest on Jul 26, 2026, 1577 m from Copley Place (PHILLIPS ST). Case #262064152 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21099,40 +21199,40 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>262064152</t>
+          <t>262064312</t>
         </is>
       </c>
       <c r="E308" s="3" t="n">
-        <v>46229.01458333333</v>
+        <v>46229.60625</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>NOISY PARTY/RADIO-NO ARREST</t>
+          <t>SICK ASSIST - DRUG RELATED ILLNESS</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>QUALITY_OF_LIFE</t>
         </is>
       </c>
       <c r="H308" t="inlineStr"/>
       <c r="I308" t="inlineStr">
         <is>
-          <t>PHILLIPS ST</t>
+          <t>ALBANY ST</t>
         </is>
       </c>
       <c r="J308" t="n">
-        <v>42.36027809483424</v>
+        <v>42.33428840659414</v>
       </c>
       <c r="K308" t="n">
-        <v>-71.06899804851336</v>
+        <v>-71.07239517543796</v>
       </c>
       <c r="L308" t="n">
-        <v>1576.7</v>
+        <v>1543.1</v>
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Noisy party/radio-no arrest on Jul 26, 2026, 1577 m from Copley Place (PHILLIPS ST). Case #262064152 (use for a records request — full narratives are not published in open data).</t>
+          <t>Sick assist - drug related illness on Jul 26, 2026, 1543 m from Copley Place (ALBANY ST). Case #262064312 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21154,40 +21254,40 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>262064312</t>
+          <t>262064770</t>
         </is>
       </c>
       <c r="E309" s="3" t="n">
-        <v>46229.60625</v>
+        <v>46230.52083333334</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>SICK ASSIST - DRUG RELATED ILLNESS</t>
+          <t>LARCENY THEFT FROM MV - NON-ACCESSORY</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>QUALITY_OF_LIFE</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H309" t="inlineStr"/>
       <c r="I309" t="inlineStr">
         <is>
-          <t>ALBANY ST</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J309" t="n">
-        <v>42.33428840659414</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K309" t="n">
-        <v>-71.07239517543796</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L309" t="n">
-        <v>1543.1</v>
+        <v>1123.7</v>
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Sick assist - drug related illness on Jul 26, 2026, 1543 m from Copley Place (ALBANY ST). Case #262064312 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny theft from mv - non-accessory on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064770 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21209,15 +21309,15 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>262064770</t>
+          <t>262064532</t>
         </is>
       </c>
       <c r="E310" s="3" t="n">
-        <v>46230.52083333334</v>
+        <v>46230.29166666666</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>LARCENY THEFT FROM MV - NON-ACCESSORY</t>
+          <t>PROPERTY - LOST/ MISSING</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
@@ -21242,7 +21342,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Larceny theft from mv - non-accessory on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064770 (use for a records request — full narratives are not published in open data).</t>
+          <t>Property - lost/ missing on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064532 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21264,15 +21364,15 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>262064532</t>
+          <t>262064590</t>
         </is>
       </c>
       <c r="E311" s="3" t="n">
-        <v>46230.29166666666</v>
+        <v>46230.50625</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>PROPERTY - LOST/ MISSING</t>
+          <t>LARCENY ALL OTHERS</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
@@ -21283,21 +21383,21 @@
       <c r="H311" t="inlineStr"/>
       <c r="I311" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>W BROOKLINE ST</t>
         </is>
       </c>
       <c r="J311" t="n">
-        <v>42.33954198983015</v>
+        <v>42.34172590358821</v>
       </c>
       <c r="K311" t="n">
-        <v>-71.06940876967543</v>
+        <v>-71.07501847816492</v>
       </c>
       <c r="L311" t="n">
-        <v>1123.7</v>
+        <v>689.2</v>
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Property - lost/ missing on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064532 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny all others on Jul 27, 2026, 689 m from Copley Place (W BROOKLINE ST). Case #262064590 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21319,15 +21419,15 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>262064590</t>
+          <t>262064674</t>
         </is>
       </c>
       <c r="E312" s="3" t="n">
-        <v>46230.50625</v>
+        <v>46229.33333333334</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>LARCENY ALL OTHERS</t>
+          <t>PROPERTY - LOST/ MISSING</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
@@ -21338,21 +21438,21 @@
       <c r="H312" t="inlineStr"/>
       <c r="I312" t="inlineStr">
         <is>
-          <t>W BROOKLINE ST</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J312" t="n">
-        <v>42.34172590358821</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K312" t="n">
-        <v>-71.07501847816492</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L312" t="n">
-        <v>689.2</v>
+        <v>1123.7</v>
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Larceny all others on Jul 27, 2026, 689 m from Copley Place (W BROOKLINE ST). Case #262064590 (use for a records request — full narratives are not published in open data).</t>
+          <t>Property - lost/ missing on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064674 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21374,40 +21474,40 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>262064674</t>
+          <t>262064591</t>
         </is>
       </c>
       <c r="E313" s="3" t="n">
-        <v>46229.33333333334</v>
+        <v>46229.77847222222</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>PROPERTY - LOST/ MISSING</t>
+          <t>INVESTIGATE PERSON</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H313" t="inlineStr"/>
       <c r="I313" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>AVERY ST</t>
         </is>
       </c>
       <c r="J313" t="n">
-        <v>42.33954198983015</v>
+        <v>42.35327560751949</v>
       </c>
       <c r="K313" t="n">
-        <v>-71.06940876967543</v>
+        <v>-71.06345772204415</v>
       </c>
       <c r="L313" t="n">
-        <v>1123.7</v>
+        <v>1324</v>
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Property - lost/ missing on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064674 (use for a records request — full narratives are not published in open data).</t>
+          <t>Investigate person on Jul 26, 2026, 1324 m from Copley Place (AVERY ST). Case #262064591 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21429,15 +21529,15 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>262064591</t>
+          <t>262064579</t>
         </is>
       </c>
       <c r="E314" s="3" t="n">
-        <v>46229.77847222222</v>
+        <v>46230.43402777778</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>INVESTIGATE PERSON</t>
+          <t>SICK/INJURED/MEDICAL - PERSON</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
@@ -21448,21 +21548,21 @@
       <c r="H314" t="inlineStr"/>
       <c r="I314" t="inlineStr">
         <is>
-          <t>AVERY ST</t>
+          <t>NORTHAMPTON ST</t>
         </is>
       </c>
       <c r="J314" t="n">
-        <v>42.35327560751949</v>
+        <v>42.33395124839377</v>
       </c>
       <c r="K314" t="n">
-        <v>-71.06345772204415</v>
+        <v>-71.07538938822692</v>
       </c>
       <c r="L314" t="n">
-        <v>1324</v>
+        <v>1530.5</v>
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Investigate person on Jul 26, 2026, 1324 m from Copley Place (AVERY ST). Case #262064591 (use for a records request — full narratives are not published in open data).</t>
+          <t>Sick/injured/medical - person on Jul 27, 2026, 1531 m from Copley Place (NORTHAMPTON ST). Case #262064579 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21484,40 +21584,40 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>262064579</t>
+          <t>262064357</t>
         </is>
       </c>
       <c r="E315" s="3" t="n">
-        <v>46230.43402777778</v>
+        <v>46229.72638888889</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>SICK/INJURED/MEDICAL - PERSON</t>
+          <t>LARCENY SHOPLIFTING</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H315" t="inlineStr"/>
       <c r="I315" t="inlineStr">
         <is>
-          <t>NORTHAMPTON ST</t>
+          <t>HUNTINGTON AVE</t>
         </is>
       </c>
       <c r="J315" t="n">
-        <v>42.33395124839377</v>
+        <v>42.3473097976345</v>
       </c>
       <c r="K315" t="n">
-        <v>-71.07538938822692</v>
+        <v>-71.0791516658207</v>
       </c>
       <c r="L315" t="n">
-        <v>1530.5</v>
+        <v>129.3</v>
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Sick/injured/medical - person on Jul 27, 2026, 1531 m from Copley Place (NORTHAMPTON ST). Case #262064579 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny shoplifting on Jul 26, 2026, 129 m from Copley Place (HUNTINGTON AVE). Case #262064357 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21539,15 +21639,15 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>262064802</t>
+          <t>262064198</t>
         </is>
       </c>
       <c r="E316" s="3" t="n">
-        <v>46230.89583333334</v>
+        <v>46229.16736111111</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>LARCENY SHOPLIFTING</t>
+          <t>TOWED MOTOR VEHICLE</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
@@ -21558,21 +21658,25 @@
       <c r="H316" t="inlineStr"/>
       <c r="I316" t="inlineStr">
         <is>
-          <t>BOYLSTON ST</t>
+          <t>STUART ST &amp; CHARLES ST S
+BOSTON, MA 02116
+UNITED S</t>
         </is>
       </c>
       <c r="J316" t="n">
-        <v>42.34862381555496</v>
+        <v>42.35095701392956</v>
       </c>
       <c r="K316" t="n">
-        <v>-71.08277637086411</v>
+        <v>-71.06685999332976</v>
       </c>
       <c r="L316" t="n">
-        <v>437.3</v>
+        <v>960.1</v>
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Larceny shoplifting on Jul 27, 2026, 437 m from Copley Place (BOYLSTON ST). Case #262064802 (use for a records request — full narratives are not published in open data).</t>
+          <t>Towed motor vehicle on Jul 26, 2026, 960 m from Copley Place (STUART ST &amp; CHARLES ST S
+BOSTON, MA 02116
+UNITED S). Case #262064198 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21594,15 +21698,15 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>262064409</t>
+          <t>262064309</t>
         </is>
       </c>
       <c r="E317" s="3" t="n">
-        <v>46229.85833333333</v>
+        <v>46229.39444444444</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>SICK ASSIST</t>
+          <t>INVESTIGATE PERSON</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
@@ -21613,21 +21717,21 @@
       <c r="H317" t="inlineStr"/>
       <c r="I317" t="inlineStr">
         <is>
-          <t>OXFORD ST</t>
+          <t>SAINT BOTOLPH ST</t>
         </is>
       </c>
       <c r="J317" t="n">
-        <v>42.35193460488232</v>
+        <v>42.34617475544754</v>
       </c>
       <c r="K317" t="n">
-        <v>-71.06048592223925</v>
+        <v>-71.07925920373032</v>
       </c>
       <c r="L317" t="n">
-        <v>1488.7</v>
+        <v>208.6</v>
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Sick assist on Jul 26, 2026, 1489 m from Copley Place (OXFORD ST). Case #262064409 (use for a records request — full narratives are not published in open data).</t>
+          <t>Investigate person on Jul 26, 2026, 209 m from Copley Place (SAINT BOTOLPH ST). Case #262064309 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21649,40 +21753,40 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>262064318</t>
+          <t>262064283</t>
         </is>
       </c>
       <c r="E318" s="3" t="n">
-        <v>46229.53958333333</v>
+        <v>46229.51736111111</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>INVESTIGATE PERSON</t>
+          <t>LARCENY SHOPLIFTING</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H318" t="inlineStr"/>
       <c r="I318" t="inlineStr">
         <is>
-          <t>SHAWMUT AVE</t>
+          <t>HUNTINGTON AVE</t>
         </is>
       </c>
       <c r="J318" t="n">
-        <v>42.34319452771496</v>
+        <v>42.3473097976345</v>
       </c>
       <c r="K318" t="n">
-        <v>-71.06880536524001</v>
+        <v>-71.0791516658207</v>
       </c>
       <c r="L318" t="n">
-        <v>876.3</v>
+        <v>129.3</v>
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Investigate person on Jul 26, 2026, 876 m from Copley Place (SHAWMUT AVE). Case #262064318 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny shoplifting on Jul 26, 2026, 129 m from Copley Place (HUNTINGTON AVE). Case #262064283 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21704,40 +21808,44 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>262064412</t>
+          <t>262064226</t>
         </is>
       </c>
       <c r="E319" s="3" t="n">
-        <v>46229.87638888889</v>
+        <v>46229.375</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>SICK/INJURED/MEDICAL - PERSON</t>
+          <t>M/V ACCIDENT - PROPERTY DAMAGE</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H319" t="inlineStr"/>
       <c r="I319" t="inlineStr">
         <is>
-          <t>TREMONT ST</t>
+          <t>BERKELEY ST &amp; SAINT JAMES AVE
+BOSTON, MA 02116
+UNI</t>
         </is>
       </c>
       <c r="J319" t="n">
-        <v>42.35428377241487</v>
+        <v>42.3504290420294</v>
       </c>
       <c r="K319" t="n">
-        <v>-71.06380403747467</v>
+        <v>-71.07264798093048</v>
       </c>
       <c r="L319" t="n">
-        <v>1356.9</v>
+        <v>515.5</v>
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Sick/injured/medical - person on Jul 26, 2026, 1357 m from Copley Place (TREMONT ST). Case #262064412 (use for a records request — full narratives are not published in open data).</t>
+          <t>M/v accident - property damage on Jul 26, 2026, 515 m from Copley Place (BERKELEY ST &amp; SAINT JAMES AVE
+BOSTON, MA 02116
+UNI). Case #262064226 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21759,40 +21867,44 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>262064362</t>
+          <t>262064268</t>
         </is>
       </c>
       <c r="E320" s="3" t="n">
-        <v>46229.64305555556</v>
+        <v>46229.48680555556</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>M/V ACCIDENT - INVOLVING PEDESTRIAN - INJURY</t>
+          <t>LARCENY THEFT FROM BUILDING</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H320" t="inlineStr"/>
       <c r="I320" t="inlineStr">
         <is>
-          <t>DARTMOUTH ST</t>
+          <t>REED ST &amp; E LENOX ST
+ROXBURY, MA 02118
+UNITED STAT</t>
         </is>
       </c>
       <c r="J320" t="n">
-        <v>42.35029374297969</v>
+        <v>42.33406097367816</v>
       </c>
       <c r="K320" t="n">
-        <v>-71.07744671381569</v>
+        <v>-71.07756301316894</v>
       </c>
       <c r="L320" t="n">
-        <v>298.2</v>
+        <v>1507.2</v>
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>M/v accident - involving pedestrian - injury on Jul 26, 2026, 298 m from Copley Place (DARTMOUTH ST). Case #262064362 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny theft from building on Jul 26, 2026, 1507 m from Copley Place (REED ST &amp; E LENOX ST
+ROXBURY, MA 02118
+UNITED STAT). Case #262064268 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21814,15 +21926,15 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>262064307</t>
+          <t>262064394</t>
         </is>
       </c>
       <c r="E321" s="3" t="n">
-        <v>46229.59027777778</v>
+        <v>46229.82152777778</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>SICK ASSIST</t>
+          <t>M/V ACCIDENT - OTHER</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -21832,22 +21944,466 @@
       </c>
       <c r="H321" t="inlineStr"/>
       <c r="I321" t="inlineStr">
+        <is>
+          <t>HARRISON AVE &amp; PLYMPTON ST
+BOSTON, MA 02118
+UNITED</t>
+        </is>
+      </c>
+      <c r="J321" t="n">
+        <v>42.33973998780085</v>
+      </c>
+      <c r="K321" t="n">
+        <v>-71.0691099454142</v>
+      </c>
+      <c r="L321" t="n">
+        <v>1121.4</v>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>M/v accident - other on Jul 26, 2026, 1121 m from Copley Place (HARRISON AVE &amp; PLYMPTON ST
+BOSTON, MA 02118
+UNITED). Case #262064394 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>262064321</t>
+        </is>
+      </c>
+      <c r="E322" s="3" t="n">
+        <v>46229.59166666667</v>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>M/V - LEAVING SCENE - PROPERTY DAMAGE</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr"/>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J322" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K322" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L322" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>M/v - leaving scene - property damage on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064321 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>262064179</t>
+        </is>
+      </c>
+      <c r="E323" s="3" t="n">
+        <v>46229.07361111111</v>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>INVESTIGATE PROPERTY</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr"/>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>BOYLSTON ST</t>
+        </is>
+      </c>
+      <c r="J323" t="n">
+        <v>42.35234109431519</v>
+      </c>
+      <c r="K323" t="n">
+        <v>-71.06432465046424</v>
+      </c>
+      <c r="L323" t="n">
+        <v>1213.3</v>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>Investigate property on Jul 26, 2026, 1213 m from Copley Place (BOYLSTON ST). Case #262064179 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>262064802</t>
+        </is>
+      </c>
+      <c r="E324" s="3" t="n">
+        <v>46230.89583333334</v>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>LARCENY SHOPLIFTING</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr"/>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>BOYLSTON ST</t>
+        </is>
+      </c>
+      <c r="J324" t="n">
+        <v>42.34862381555496</v>
+      </c>
+      <c r="K324" t="n">
+        <v>-71.08277637086411</v>
+      </c>
+      <c r="L324" t="n">
+        <v>437.3</v>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>Larceny shoplifting on Jul 27, 2026, 437 m from Copley Place (BOYLSTON ST). Case #262064802 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>262064409</t>
+        </is>
+      </c>
+      <c r="E325" s="3" t="n">
+        <v>46229.85833333333</v>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>SICK ASSIST</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr"/>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>OXFORD ST</t>
+        </is>
+      </c>
+      <c r="J325" t="n">
+        <v>42.35193460488232</v>
+      </c>
+      <c r="K325" t="n">
+        <v>-71.06048592223925</v>
+      </c>
+      <c r="L325" t="n">
+        <v>1488.7</v>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>Sick assist on Jul 26, 2026, 1489 m from Copley Place (OXFORD ST). Case #262064409 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>262064318</t>
+        </is>
+      </c>
+      <c r="E326" s="3" t="n">
+        <v>46229.53958333333</v>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>INVESTIGATE PERSON</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr"/>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>SHAWMUT AVE</t>
+        </is>
+      </c>
+      <c r="J326" t="n">
+        <v>42.34319452771496</v>
+      </c>
+      <c r="K326" t="n">
+        <v>-71.06880536524001</v>
+      </c>
+      <c r="L326" t="n">
+        <v>876.3</v>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>Investigate person on Jul 26, 2026, 876 m from Copley Place (SHAWMUT AVE). Case #262064318 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>262064412</t>
+        </is>
+      </c>
+      <c r="E327" s="3" t="n">
+        <v>46229.87638888889</v>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>SICK/INJURED/MEDICAL - PERSON</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr"/>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>TREMONT ST</t>
+        </is>
+      </c>
+      <c r="J327" t="n">
+        <v>42.35428377241487</v>
+      </c>
+      <c r="K327" t="n">
+        <v>-71.06380403747467</v>
+      </c>
+      <c r="L327" t="n">
+        <v>1356.9</v>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>Sick/injured/medical - person on Jul 26, 2026, 1357 m from Copley Place (TREMONT ST). Case #262064412 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>262064362</t>
+        </is>
+      </c>
+      <c r="E328" s="3" t="n">
+        <v>46229.64305555556</v>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>M/V ACCIDENT - INVOLVING PEDESTRIAN - INJURY</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr"/>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>DARTMOUTH ST</t>
+        </is>
+      </c>
+      <c r="J328" t="n">
+        <v>42.35029374297969</v>
+      </c>
+      <c r="K328" t="n">
+        <v>-71.07744671381569</v>
+      </c>
+      <c r="L328" t="n">
+        <v>298.2</v>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>M/v accident - involving pedestrian - injury on Jul 26, 2026, 298 m from Copley Place (DARTMOUTH ST). Case #262064362 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>262064307</t>
+        </is>
+      </c>
+      <c r="E329" s="3" t="n">
+        <v>46229.59027777778</v>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>SICK ASSIST</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr"/>
+      <c r="I329" t="inlineStr">
         <is>
           <t>TREMONT ST &amp; TEMPLE PL
 BOSTON, MA 02111
 UNITED STA</t>
         </is>
       </c>
-      <c r="J321" t="n">
+      <c r="J329" t="n">
         <v>42.35561100811422</v>
       </c>
-      <c r="K321" t="n">
+      <c r="K329" t="n">
         <v>-71.06289400004533</v>
       </c>
-      <c r="L321" t="n">
+      <c r="L329" t="n">
         <v>1502.5</v>
       </c>
-      <c r="M321" t="inlineStr">
+      <c r="M329" t="inlineStr">
         <is>
           <t>Sick assist on Jul 26, 2026, 1502 m from Copley Place (TREMONT ST &amp; TEMPLE PL
 BOSTON, MA 02111
@@ -21855,450 +22411,6 @@
         </is>
       </c>
     </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>262064419</t>
-        </is>
-      </c>
-      <c r="E322" s="3" t="n">
-        <v>46229.90138888889</v>
-      </c>
-      <c r="F322" t="inlineStr">
-        <is>
-          <t>HARASSMENT/ CRIMINAL HARASSMENT</t>
-        </is>
-      </c>
-      <c r="G322" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H322" t="inlineStr"/>
-      <c r="I322" t="inlineStr">
-        <is>
-          <t>NASSAU ST</t>
-        </is>
-      </c>
-      <c r="J322" t="n">
-        <v>42.34880604399623</v>
-      </c>
-      <c r="K322" t="n">
-        <v>-71.06285446968663</v>
-      </c>
-      <c r="L322" t="n">
-        <v>1221.7</v>
-      </c>
-      <c r="M322" t="inlineStr">
-        <is>
-          <t>Harassment/ criminal harassment on Jul 26, 2026, 1222 m from Copley Place (NASSAU ST). Case #262064419 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>262064339</t>
-        </is>
-      </c>
-      <c r="E323" s="3" t="n">
-        <v>46229.63333333333</v>
-      </c>
-      <c r="F323" t="inlineStr">
-        <is>
-          <t>ASSAULT - AGGRAVATED</t>
-        </is>
-      </c>
-      <c r="G323" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H323" t="inlineStr"/>
-      <c r="I323" t="inlineStr">
-        <is>
-          <t>HARRISON AVE</t>
-        </is>
-      </c>
-      <c r="J323" t="n">
-        <v>42.33511903946613</v>
-      </c>
-      <c r="K323" t="n">
-        <v>-71.07491709613726</v>
-      </c>
-      <c r="L323" t="n">
-        <v>1407.3</v>
-      </c>
-      <c r="M323" t="inlineStr">
-        <is>
-          <t>Assault - aggravated on Jul 26, 2026, 1407 m from Copley Place (HARRISON AVE). Case #262064339 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>262064236</t>
-        </is>
-      </c>
-      <c r="E324" s="3" t="n">
-        <v>46229.37638888889</v>
-      </c>
-      <c r="F324" t="inlineStr">
-        <is>
-          <t>SICK ASSIST</t>
-        </is>
-      </c>
-      <c r="G324" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H324" t="inlineStr"/>
-      <c r="I324" t="inlineStr">
-        <is>
-          <t>TREMONT ST</t>
-        </is>
-      </c>
-      <c r="J324" t="n">
-        <v>42.34470135794417</v>
-      </c>
-      <c r="K324" t="n">
-        <v>-71.0703760849388</v>
-      </c>
-      <c r="L324" t="n">
-        <v>678.7</v>
-      </c>
-      <c r="M324" t="inlineStr">
-        <is>
-          <t>Sick assist on Jul 26, 2026, 679 m from Copley Place (TREMONT ST). Case #262064236 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>262064234</t>
-        </is>
-      </c>
-      <c r="E325" s="3" t="n">
-        <v>46229.31944444445</v>
-      </c>
-      <c r="F325" t="inlineStr">
-        <is>
-          <t>INVESTIGATE PERSON</t>
-        </is>
-      </c>
-      <c r="G325" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H325" t="inlineStr"/>
-      <c r="I325" t="inlineStr">
-        <is>
-          <t>SAINT JAMES AVE</t>
-        </is>
-      </c>
-      <c r="J325" t="n">
-        <v>42.34947585701249</v>
-      </c>
-      <c r="K325" t="n">
-        <v>-71.07640149637847</v>
-      </c>
-      <c r="L325" t="n">
-        <v>230.3</v>
-      </c>
-      <c r="M325" t="inlineStr">
-        <is>
-          <t>Investigate person on Jul 26, 2026, 230 m from Copley Place (SAINT JAMES AVE). Case #262064234 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>262064357</t>
-        </is>
-      </c>
-      <c r="E326" s="3" t="n">
-        <v>46229.72638888889</v>
-      </c>
-      <c r="F326" t="inlineStr">
-        <is>
-          <t>LARCENY SHOPLIFTING</t>
-        </is>
-      </c>
-      <c r="G326" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H326" t="inlineStr"/>
-      <c r="I326" t="inlineStr">
-        <is>
-          <t>HUNTINGTON AVE</t>
-        </is>
-      </c>
-      <c r="J326" t="n">
-        <v>42.3473097976345</v>
-      </c>
-      <c r="K326" t="n">
-        <v>-71.0791516658207</v>
-      </c>
-      <c r="L326" t="n">
-        <v>129.3</v>
-      </c>
-      <c r="M326" t="inlineStr">
-        <is>
-          <t>Larceny shoplifting on Jul 26, 2026, 129 m from Copley Place (HUNTINGTON AVE). Case #262064357 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>262064198</t>
-        </is>
-      </c>
-      <c r="E327" s="3" t="n">
-        <v>46229.16736111111</v>
-      </c>
-      <c r="F327" t="inlineStr">
-        <is>
-          <t>TOWED MOTOR VEHICLE</t>
-        </is>
-      </c>
-      <c r="G327" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H327" t="inlineStr"/>
-      <c r="I327" t="inlineStr">
-        <is>
-          <t>STUART ST &amp; CHARLES ST S
-BOSTON, MA 02116
-UNITED S</t>
-        </is>
-      </c>
-      <c r="J327" t="n">
-        <v>42.35095701392956</v>
-      </c>
-      <c r="K327" t="n">
-        <v>-71.06685999332976</v>
-      </c>
-      <c r="L327" t="n">
-        <v>960.1</v>
-      </c>
-      <c r="M327" t="inlineStr">
-        <is>
-          <t>Towed motor vehicle on Jul 26, 2026, 960 m from Copley Place (STUART ST &amp; CHARLES ST S
-BOSTON, MA 02116
-UNITED S). Case #262064198 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>262064309</t>
-        </is>
-      </c>
-      <c r="E328" s="3" t="n">
-        <v>46229.39444444444</v>
-      </c>
-      <c r="F328" t="inlineStr">
-        <is>
-          <t>INVESTIGATE PERSON</t>
-        </is>
-      </c>
-      <c r="G328" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H328" t="inlineStr"/>
-      <c r="I328" t="inlineStr">
-        <is>
-          <t>SAINT BOTOLPH ST</t>
-        </is>
-      </c>
-      <c r="J328" t="n">
-        <v>42.34617475544754</v>
-      </c>
-      <c r="K328" t="n">
-        <v>-71.07925920373032</v>
-      </c>
-      <c r="L328" t="n">
-        <v>208.6</v>
-      </c>
-      <c r="M328" t="inlineStr">
-        <is>
-          <t>Investigate person on Jul 26, 2026, 209 m from Copley Place (SAINT BOTOLPH ST). Case #262064309 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>262064283</t>
-        </is>
-      </c>
-      <c r="E329" s="3" t="n">
-        <v>46229.51736111111</v>
-      </c>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t>LARCENY SHOPLIFTING</t>
-        </is>
-      </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H329" t="inlineStr"/>
-      <c r="I329" t="inlineStr">
-        <is>
-          <t>HUNTINGTON AVE</t>
-        </is>
-      </c>
-      <c r="J329" t="n">
-        <v>42.3473097976345</v>
-      </c>
-      <c r="K329" t="n">
-        <v>-71.0791516658207</v>
-      </c>
-      <c r="L329" t="n">
-        <v>129.3</v>
-      </c>
-      <c r="M329" t="inlineStr">
-        <is>
-          <t>Larceny shoplifting on Jul 26, 2026, 129 m from Copley Place (HUNTINGTON AVE). Case #262064283 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
@@ -22317,44 +22429,40 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>262064226</t>
+          <t>262064419</t>
         </is>
       </c>
       <c r="E330" s="3" t="n">
-        <v>46229.375</v>
+        <v>46229.90138888889</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>M/V ACCIDENT - PROPERTY DAMAGE</t>
+          <t>HARASSMENT/ CRIMINAL HARASSMENT</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H330" t="inlineStr"/>
       <c r="I330" t="inlineStr">
         <is>
-          <t>BERKELEY ST &amp; SAINT JAMES AVE
-BOSTON, MA 02116
-UNI</t>
+          <t>NASSAU ST</t>
         </is>
       </c>
       <c r="J330" t="n">
-        <v>42.3504290420294</v>
+        <v>42.34880604399623</v>
       </c>
       <c r="K330" t="n">
-        <v>-71.07264798093048</v>
+        <v>-71.06285446968663</v>
       </c>
       <c r="L330" t="n">
-        <v>515.5</v>
+        <v>1221.7</v>
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>M/v accident - property damage on Jul 26, 2026, 515 m from Copley Place (BERKELEY ST &amp; SAINT JAMES AVE
-BOSTON, MA 02116
-UNI). Case #262064226 (use for a records request — full narratives are not published in open data).</t>
+          <t>Harassment/ criminal harassment on Jul 26, 2026, 1222 m from Copley Place (NASSAU ST). Case #262064419 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -22376,44 +22484,40 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>262064268</t>
+          <t>262064339</t>
         </is>
       </c>
       <c r="E331" s="3" t="n">
-        <v>46229.48680555556</v>
+        <v>46229.63333333333</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>LARCENY THEFT FROM BUILDING</t>
+          <t>ASSAULT - AGGRAVATED</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H331" t="inlineStr"/>
       <c r="I331" t="inlineStr">
         <is>
-          <t>REED ST &amp; E LENOX ST
-ROXBURY, MA 02118
-UNITED STAT</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J331" t="n">
-        <v>42.33406097367816</v>
+        <v>42.33511903946613</v>
       </c>
       <c r="K331" t="n">
-        <v>-71.07756301316894</v>
+        <v>-71.07491709613726</v>
       </c>
       <c r="L331" t="n">
-        <v>1507.2</v>
+        <v>1407.3</v>
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Larceny theft from building on Jul 26, 2026, 1507 m from Copley Place (REED ST &amp; E LENOX ST
-ROXBURY, MA 02118
-UNITED STAT). Case #262064268 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault - aggravated on Jul 26, 2026, 1407 m from Copley Place (HARRISON AVE). Case #262064339 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -22435,15 +22539,15 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>262064394</t>
+          <t>262064236</t>
         </is>
       </c>
       <c r="E332" s="3" t="n">
-        <v>46229.82152777778</v>
+        <v>46229.37638888889</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>M/V ACCIDENT - OTHER</t>
+          <t>SICK ASSIST</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
@@ -22454,25 +22558,21 @@
       <c r="H332" t="inlineStr"/>
       <c r="I332" t="inlineStr">
         <is>
-          <t>HARRISON AVE &amp; PLYMPTON ST
-BOSTON, MA 02118
-UNITED</t>
+          <t>TREMONT ST</t>
         </is>
       </c>
       <c r="J332" t="n">
-        <v>42.33973998780085</v>
+        <v>42.34470135794417</v>
       </c>
       <c r="K332" t="n">
-        <v>-71.0691099454142</v>
+        <v>-71.0703760849388</v>
       </c>
       <c r="L332" t="n">
-        <v>1121.4</v>
+        <v>678.7</v>
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>M/v accident - other on Jul 26, 2026, 1121 m from Copley Place (HARRISON AVE &amp; PLYMPTON ST
-BOSTON, MA 02118
-UNITED). Case #262064394 (use for a records request — full narratives are not published in open data).</t>
+          <t>Sick assist on Jul 26, 2026, 679 m from Copley Place (TREMONT ST). Case #262064236 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -22494,40 +22594,40 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>262064321</t>
+          <t>262064234</t>
         </is>
       </c>
       <c r="E333" s="3" t="n">
-        <v>46229.59166666667</v>
+        <v>46229.31944444445</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>M/V - LEAVING SCENE - PROPERTY DAMAGE</t>
+          <t>INVESTIGATE PERSON</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H333" t="inlineStr"/>
       <c r="I333" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>SAINT JAMES AVE</t>
         </is>
       </c>
       <c r="J333" t="n">
-        <v>42.33954198983015</v>
+        <v>42.34947585701249</v>
       </c>
       <c r="K333" t="n">
-        <v>-71.06940876967543</v>
+        <v>-71.07640149637847</v>
       </c>
       <c r="L333" t="n">
-        <v>1123.7</v>
+        <v>230.3</v>
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>M/v - leaving scene - property damage on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064321 (use for a records request — full narratives are not published in open data).</t>
+          <t>Investigate person on Jul 26, 2026, 230 m from Copley Place (SAINT JAMES AVE). Case #262064234 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -23474,8 +23574,2427 @@
         </is>
       </c>
     </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>260730-1542</t>
+        </is>
+      </c>
+      <c r="E351" s="3" t="n">
+        <v>46233.78047453704</v>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>DRUGS/ALCOHOL VIOLATIONS</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>2700 BLOCK MONSARRAT AVE</t>
+        </is>
+      </c>
+      <c r="J351" t="n">
+        <v>21.271072368884</v>
+      </c>
+      <c r="K351" t="n">
+        <v>-157.822447621636</v>
+      </c>
+      <c r="L351" t="n">
+        <v>886.5</v>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>Drugs/alcohol violations on Jul 30, 2026, 887 m from International Market Place (2700 BLOCK MONSARRAT AVE). Case #260730-1542 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>260730-1522</t>
+        </is>
+      </c>
+      <c r="E352" s="3" t="n">
+        <v>46233.76790509259</v>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>2400 BLOCK TUSITALA ST</t>
+        </is>
+      </c>
+      <c r="J352" t="n">
+        <v>21.278259926502</v>
+      </c>
+      <c r="K352" t="n">
+        <v>-157.822935782893</v>
+      </c>
+      <c r="L352" t="n">
+        <v>391.8</v>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 30, 2026, 392 m from International Market Place (2400 BLOCK TUSITALA ST). Case #260730-1522 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>260730-1520</t>
+        </is>
+      </c>
+      <c r="E353" s="3" t="n">
+        <v>46233.76768518519</v>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>2200 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J353" t="n">
+        <v>21.280046658192</v>
+      </c>
+      <c r="K353" t="n">
+        <v>-157.829687791355</v>
+      </c>
+      <c r="L353" t="n">
+        <v>384.6</v>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 30, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260730-1520 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>260730-1019</t>
+        </is>
+      </c>
+      <c r="E354" s="3" t="n">
+        <v>46233.56648148148</v>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>DRUGS/ALCOHOL VIOLATIONS</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>300 BLOCK KALAIMOKU ST</t>
+        </is>
+      </c>
+      <c r="J354" t="n">
+        <v>21.282350597517</v>
+      </c>
+      <c r="K354" t="n">
+        <v>-157.830982023446</v>
+      </c>
+      <c r="L354" t="n">
+        <v>657</v>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>Drugs/alcohol violations on Jul 30, 2026, 657 m from International Market Place (300 BLOCK KALAIMOKU ST). Case #260730-1019 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>260730-0815</t>
+        </is>
+      </c>
+      <c r="E355" s="3" t="n">
+        <v>46233.48552083333</v>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>800 BLOCK OLOKELE AVE</t>
+        </is>
+      </c>
+      <c r="J355" t="n">
+        <v>21.284576073594</v>
+      </c>
+      <c r="K355" t="n">
+        <v>-157.816508656221</v>
+      </c>
+      <c r="L355" t="n">
+        <v>1285.7</v>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 30, 2026, 1286 m from International Market Place (800 BLOCK OLOKELE AVE). Case #260730-0815 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>260730-0686</t>
+        </is>
+      </c>
+      <c r="E356" s="3" t="n">
+        <v>46233.43194444444</v>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>MOTOR VEHICLE THEFT</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>2000 BLOCK FERN ST</t>
+        </is>
+      </c>
+      <c r="J356" t="n">
+        <v>21.291077860315</v>
+      </c>
+      <c r="K356" t="n">
+        <v>-157.831592308337</v>
+      </c>
+      <c r="L356" t="n">
+        <v>1541.1</v>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>Motor vehicle theft on Jul 30, 2026, 1541 m from International Market Place (2000 BLOCK FERN ST). Case #260730-0686 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>260730-0665</t>
+        </is>
+      </c>
+      <c r="E357" s="3" t="n">
+        <v>46233.4228125</v>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>MOTOR VEHICLE THEFT</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>700 BLOCK MCCULLY ST</t>
+        </is>
+      </c>
+      <c r="J357" t="n">
+        <v>21.289543723588</v>
+      </c>
+      <c r="K357" t="n">
+        <v>-157.832336665095</v>
+      </c>
+      <c r="L357" t="n">
+        <v>1411.2</v>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>Motor vehicle theft on Jul 30, 2026, 1411 m from International Market Place (700 BLOCK MCCULLY ST). Case #260730-0665 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>260730-0644</t>
+        </is>
+      </c>
+      <c r="E358" s="3" t="n">
+        <v>46233.41398148148</v>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>MOTOR VEHICLE THEFT</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>2600 BLOCK PUALANI WAY</t>
+        </is>
+      </c>
+      <c r="J358" t="n">
+        <v>21.274324486506</v>
+      </c>
+      <c r="K358" t="n">
+        <v>-157.819632666016</v>
+      </c>
+      <c r="L358" t="n">
+        <v>838.5</v>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>Motor vehicle theft on Jul 30, 2026, 838 m from International Market Place (2600 BLOCK PUALANI WAY). Case #260730-0644 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>260730-0478</t>
+        </is>
+      </c>
+      <c r="E359" s="3" t="n">
+        <v>46233.34556712963</v>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>MOTOR VEHICLE THEFT</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>700 BLOCK MCCULLY ST</t>
+        </is>
+      </c>
+      <c r="J359" t="n">
+        <v>21.289543723588</v>
+      </c>
+      <c r="K359" t="n">
+        <v>-157.832336665095</v>
+      </c>
+      <c r="L359" t="n">
+        <v>1411.2</v>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>Motor vehicle theft on Jul 30, 2026, 1411 m from International Market Place (700 BLOCK MCCULLY ST). Case #260730-0478 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>260730-0471</t>
+        </is>
+      </c>
+      <c r="E360" s="3" t="n">
+        <v>46233.34482638889</v>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>VANDALISM</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>300 BLOCK OHUA AVE</t>
+        </is>
+      </c>
+      <c r="J360" t="n">
+        <v>21.275639514153</v>
+      </c>
+      <c r="K360" t="n">
+        <v>-157.820878627839</v>
+      </c>
+      <c r="L360" t="n">
+        <v>657.8</v>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>Vandalism on Jul 30, 2026, 658 m from International Market Place (300 BLOCK OHUA AVE). Case #260730-0471 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>260730-0103</t>
+        </is>
+      </c>
+      <c r="E361" s="3" t="n">
+        <v>46233.07450231481</v>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>DISTURBING THE PEACE</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>2300 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J361" t="n">
+        <v>21.27805648814</v>
+      </c>
+      <c r="K361" t="n">
+        <v>-157.827664940544</v>
+      </c>
+      <c r="L361" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>Disturbing the peace on Jul 30, 2026, 100 m from International Market Place (2300 BLOCK KALAKAUA AVE). Case #260730-0103 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>260729-1797</t>
+        </is>
+      </c>
+      <c r="E362" s="3" t="n">
+        <v>46232.92472222223</v>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>BURGLARY</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>2400 BLOCK KUHIO AVE</t>
+        </is>
+      </c>
+      <c r="J362" t="n">
+        <v>21.277342437556</v>
+      </c>
+      <c r="K362" t="n">
+        <v>-157.824038253672</v>
+      </c>
+      <c r="L362" t="n">
+        <v>285.6</v>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>Burglary on Jul 29, 2026, 286 m from International Market Place (2400 BLOCK KUHIO AVE). Case #260729-1797 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>260729-1765</t>
+        </is>
+      </c>
+      <c r="E363" s="3" t="n">
+        <v>46232.91365740741</v>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>2400 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J363" t="n">
+        <v>21.276010351182</v>
+      </c>
+      <c r="K363" t="n">
+        <v>-157.825469259274</v>
+      </c>
+      <c r="L363" t="n">
+        <v>254.5</v>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 29, 2026, 254 m from International Market Place (2400 BLOCK KALAKAUA AVE). Case #260729-1765 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>260729-1729</t>
+        </is>
+      </c>
+      <c r="E364" s="3" t="n">
+        <v>46232.89675925926</v>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>MOTOR VEHICLE THEFT</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>400 BLOCK LAUNIU ST</t>
+        </is>
+      </c>
+      <c r="J364" t="n">
+        <v>21.283477123129</v>
+      </c>
+      <c r="K364" t="n">
+        <v>-157.828862979048</v>
+      </c>
+      <c r="L364" t="n">
+        <v>650</v>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>Motor vehicle theft on Jul 29, 2026, 650 m from International Market Place (400 BLOCK LAUNIU ST). Case #260729-1729 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>260729-1717</t>
+        </is>
+      </c>
+      <c r="E365" s="3" t="n">
+        <v>46232.8941087963</v>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>VANDALISM</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>2300 BLOCK KUHIO AVE</t>
+        </is>
+      </c>
+      <c r="J365" t="n">
+        <v>21.279653508688</v>
+      </c>
+      <c r="K365" t="n">
+        <v>-157.826261195987</v>
+      </c>
+      <c r="L365" t="n">
+        <v>190.9</v>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>Vandalism on Jul 29, 2026, 191 m from International Market Place (2300 BLOCK KUHIO AVE). Case #260729-1717 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>260729-1602</t>
+        </is>
+      </c>
+      <c r="E366" s="3" t="n">
+        <v>46232.84670138889</v>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>200 BLOCK BEACH WALK</t>
+        </is>
+      </c>
+      <c r="J366" t="n">
+        <v>21.278930465176</v>
+      </c>
+      <c r="K366" t="n">
+        <v>-157.832248174365</v>
+      </c>
+      <c r="L366" t="n">
+        <v>583.7</v>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 29, 2026, 584 m from International Market Place (200 BLOCK BEACH WALK). Case #260729-1602 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>260729-1588</t>
+        </is>
+      </c>
+      <c r="E367" s="3" t="n">
+        <v>46232.84131944444</v>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>2100 BLOCK KALIA RD</t>
+        </is>
+      </c>
+      <c r="J367" t="n">
+        <v>21.278855725117</v>
+      </c>
+      <c r="K367" t="n">
+        <v>-157.832156390487</v>
+      </c>
+      <c r="L367" t="n">
+        <v>572.9</v>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 29, 2026, 573 m from International Market Place (2100 BLOCK KALIA RD). Case #260729-1588 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>260729-1549</t>
+        </is>
+      </c>
+      <c r="E368" s="3" t="n">
+        <v>46232.82087962963</v>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>2200 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J368" t="n">
+        <v>21.280046658192</v>
+      </c>
+      <c r="K368" t="n">
+        <v>-157.829687791355</v>
+      </c>
+      <c r="L368" t="n">
+        <v>384.6</v>
+      </c>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 29, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260729-1549 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>260729-1507</t>
+        </is>
+      </c>
+      <c r="E369" s="3" t="n">
+        <v>46232.8008912037</v>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>VANDALISM</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>2200 BLOCK KAPIOLANI BLVD</t>
+        </is>
+      </c>
+      <c r="J369" t="n">
+        <v>21.288755371647</v>
+      </c>
+      <c r="K369" t="n">
+        <v>-157.829913575344</v>
+      </c>
+      <c r="L369" t="n">
+        <v>1242.6</v>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>Vandalism on Jul 29, 2026, 1243 m from International Market Place (2200 BLOCK KAPIOLANI BLVD). Case #260729-1507 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>260729-1309</t>
+        </is>
+      </c>
+      <c r="E370" s="3" t="n">
+        <v>46232.72003472222</v>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>2400 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J370" t="n">
+        <v>21.276010351182</v>
+      </c>
+      <c r="K370" t="n">
+        <v>-157.825469259274</v>
+      </c>
+      <c r="L370" t="n">
+        <v>254.5</v>
+      </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 29, 2026, 254 m from International Market Place (2400 BLOCK KALAKAUA AVE). Case #260729-1309 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>260729-0943</t>
+        </is>
+      </c>
+      <c r="E371" s="3" t="n">
+        <v>46232.56469907407</v>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>ASSAULT</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>2600 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J371" t="n">
+        <v>21.271474893966</v>
+      </c>
+      <c r="K371" t="n">
+        <v>-157.82264961775</v>
+      </c>
+      <c r="L371" t="n">
+        <v>837.3</v>
+      </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>Assault on Jul 29, 2026, 837 m from International Market Place (2600 BLOCK KALAKAUA AVE). Case #260729-0943 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>260729-0896</t>
+        </is>
+      </c>
+      <c r="E372" s="3" t="n">
+        <v>46232.54393518518</v>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>FRAUD</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>2500 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J372" t="n">
+        <v>21.273862837838</v>
+      </c>
+      <c r="K372" t="n">
+        <v>-157.82387239543</v>
+      </c>
+      <c r="L372" t="n">
+        <v>544.6</v>
+      </c>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>Fraud on Jul 29, 2026, 545 m from International Market Place (2500 BLOCK KALAKAUA AVE). Case #260729-0896 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>260729-0762</t>
+        </is>
+      </c>
+      <c r="E373" s="3" t="n">
+        <v>46232.47961805556</v>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>BURGLARY</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>2400 BLOCK KUHIO AVE</t>
+        </is>
+      </c>
+      <c r="J373" t="n">
+        <v>21.277342437556</v>
+      </c>
+      <c r="K373" t="n">
+        <v>-157.824038253672</v>
+      </c>
+      <c r="L373" t="n">
+        <v>285.6</v>
+      </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>Burglary on Jul 29, 2026, 286 m from International Market Place (2400 BLOCK KUHIO AVE). Case #260729-0762 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>260729-0758</t>
+        </is>
+      </c>
+      <c r="E374" s="3" t="n">
+        <v>46232.47920138889</v>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>FRAUD</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>300 BLOCK HOBRON LN</t>
+        </is>
+      </c>
+      <c r="J374" t="n">
+        <v>21.286120798599</v>
+      </c>
+      <c r="K374" t="n">
+        <v>-157.838143867296</v>
+      </c>
+      <c r="L374" t="n">
+        <v>1490.8</v>
+      </c>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>Fraud on Jul 29, 2026, 1491 m from International Market Place (300 BLOCK HOBRON LN). Case #260729-0758 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>260729-0737</t>
+        </is>
+      </c>
+      <c r="E375" s="3" t="n">
+        <v>46232.46952546296</v>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>ASSAULT</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>2500 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J375" t="n">
+        <v>21.273862837838</v>
+      </c>
+      <c r="K375" t="n">
+        <v>-157.82387239543</v>
+      </c>
+      <c r="L375" t="n">
+        <v>544.6</v>
+      </c>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>Assault on Jul 29, 2026, 545 m from International Market Place (2500 BLOCK KALAKAUA AVE). Case #260729-0737 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>260728-1209</t>
+        </is>
+      </c>
+      <c r="E376" s="3" t="n">
+        <v>46231.68509259259</v>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>DRUGS/ALCOHOL VIOLATIONS</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>2400 BLOCK KUHIO AVE</t>
+        </is>
+      </c>
+      <c r="J376" t="n">
+        <v>21.277342437556</v>
+      </c>
+      <c r="K376" t="n">
+        <v>-157.824038253672</v>
+      </c>
+      <c r="L376" t="n">
+        <v>285.6</v>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>Drugs/alcohol violations on Jul 28, 2026, 286 m from International Market Place (2400 BLOCK KUHIO AVE). Case #260728-1209 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>260728-1191</t>
+        </is>
+      </c>
+      <c r="E377" s="3" t="n">
+        <v>46231.67745370371</v>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>2300 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J377" t="n">
+        <v>21.27805648814</v>
+      </c>
+      <c r="K377" t="n">
+        <v>-157.827664940544</v>
+      </c>
+      <c r="L377" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 28, 2026, 100 m from International Market Place (2300 BLOCK KALAKAUA AVE). Case #260728-1191 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>260728-1126</t>
+        </is>
+      </c>
+      <c r="E378" s="3" t="n">
+        <v>46231.65560185185</v>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>2300 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J378" t="n">
+        <v>21.27805648814</v>
+      </c>
+      <c r="K378" t="n">
+        <v>-157.827664940544</v>
+      </c>
+      <c r="L378" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 28, 2026, 100 m from International Market Place (2300 BLOCK KALAKAUA AVE). Case #260728-1126 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>260727-1381</t>
+        </is>
+      </c>
+      <c r="E379" s="3" t="n">
+        <v>46230.75506944444</v>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>2200 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J379" t="n">
+        <v>21.280046658192</v>
+      </c>
+      <c r="K379" t="n">
+        <v>-157.829687791355</v>
+      </c>
+      <c r="L379" t="n">
+        <v>384.6</v>
+      </c>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 27, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260727-1381 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>260727-1302</t>
+        </is>
+      </c>
+      <c r="E380" s="3" t="n">
+        <v>46230.71513888889</v>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>300 BLOCK KALAIMOKU ST</t>
+        </is>
+      </c>
+      <c r="J380" t="n">
+        <v>21.282350597517</v>
+      </c>
+      <c r="K380" t="n">
+        <v>-157.830982023446</v>
+      </c>
+      <c r="L380" t="n">
+        <v>657</v>
+      </c>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 27, 2026, 657 m from International Market Place (300 BLOCK KALAIMOKU ST). Case #260727-1302 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>260727-0958</t>
+        </is>
+      </c>
+      <c r="E381" s="3" t="n">
+        <v>46230.57681712963</v>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>2200 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J381" t="n">
+        <v>21.280046658192</v>
+      </c>
+      <c r="K381" t="n">
+        <v>-157.829687791355</v>
+      </c>
+      <c r="L381" t="n">
+        <v>384.6</v>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 27, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260727-0958 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>260727-0160</t>
+        </is>
+      </c>
+      <c r="E382" s="3" t="n">
+        <v>46230.1952662037</v>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>VANDALISM</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>2400 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J382" t="n">
+        <v>21.276010351182</v>
+      </c>
+      <c r="K382" t="n">
+        <v>-157.825469259274</v>
+      </c>
+      <c r="L382" t="n">
+        <v>254.5</v>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>Vandalism on Jul 27, 2026, 254 m from International Market Place (2400 BLOCK KALAKAUA AVE). Case #260727-0160 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>260726-0935</t>
+        </is>
+      </c>
+      <c r="E383" s="3" t="n">
+        <v>46229.61716435185</v>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>2400 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J383" t="n">
+        <v>21.276010351182</v>
+      </c>
+      <c r="K383" t="n">
+        <v>-157.825469259274</v>
+      </c>
+      <c r="L383" t="n">
+        <v>254.5</v>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 26, 2026, 254 m from International Market Place (2400 BLOCK KALAKAUA AVE). Case #260726-0935 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>260726-0313</t>
+        </is>
+      </c>
+      <c r="E384" s="3" t="n">
+        <v>46229.25769675926</v>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>2500 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J384" t="n">
+        <v>21.273862837838</v>
+      </c>
+      <c r="K384" t="n">
+        <v>-157.82387239543</v>
+      </c>
+      <c r="L384" t="n">
+        <v>544.6</v>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 26, 2026, 545 m from International Market Place (2500 BLOCK KALAKAUA AVE). Case #260726-0313 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>260726-0222</t>
+        </is>
+      </c>
+      <c r="E385" s="3" t="n">
+        <v>46229.15130787037</v>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>ASSAULT</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>2200 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J385" t="n">
+        <v>21.280046658192</v>
+      </c>
+      <c r="K385" t="n">
+        <v>-157.829687791355</v>
+      </c>
+      <c r="L385" t="n">
+        <v>384.6</v>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>Assault on Jul 26, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260726-0222 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>260725-1627</t>
+        </is>
+      </c>
+      <c r="E386" s="3" t="n">
+        <v>46228.93998842593</v>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>ASSAULT</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>200 BLOCK BEACH WALK</t>
+        </is>
+      </c>
+      <c r="J386" t="n">
+        <v>21.278930465176</v>
+      </c>
+      <c r="K386" t="n">
+        <v>-157.832248174365</v>
+      </c>
+      <c r="L386" t="n">
+        <v>583.7</v>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>Assault on Jul 25, 2026, 584 m from International Market Place (200 BLOCK BEACH WALK). Case #260725-1627 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>260725-1228</t>
+        </is>
+      </c>
+      <c r="E387" s="3" t="n">
+        <v>46228.75162037037</v>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>2200 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J387" t="n">
+        <v>21.280046658192</v>
+      </c>
+      <c r="K387" t="n">
+        <v>-157.829687791355</v>
+      </c>
+      <c r="L387" t="n">
+        <v>384.6</v>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 25, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260725-1228 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>260725-1158</t>
+        </is>
+      </c>
+      <c r="E388" s="3" t="n">
+        <v>46228.70266203704</v>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>ASSAULT</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>2300 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J388" t="n">
+        <v>21.27805648814</v>
+      </c>
+      <c r="K388" t="n">
+        <v>-157.827664940544</v>
+      </c>
+      <c r="L388" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>Assault on Jul 25, 2026, 100 m from International Market Place (2300 BLOCK KALAKAUA AVE). Case #260725-1158 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>260725-0503</t>
+        </is>
+      </c>
+      <c r="E389" s="3" t="n">
+        <v>46228.35734953704</v>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>MOTOR VEHICLE THEFT</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>2400 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J389" t="n">
+        <v>21.276010351182</v>
+      </c>
+      <c r="K389" t="n">
+        <v>-157.825469259274</v>
+      </c>
+      <c r="L389" t="n">
+        <v>254.5</v>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>Motor vehicle theft on Jul 25, 2026, 254 m from International Market Place (2400 BLOCK KALAKAUA AVE). Case #260725-0503 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>260725-0383</t>
+        </is>
+      </c>
+      <c r="E390" s="3" t="n">
+        <v>46228.28726851852</v>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>DISTURBING THE PEACE</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>2300 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J390" t="n">
+        <v>21.27805648814</v>
+      </c>
+      <c r="K390" t="n">
+        <v>-157.827664940544</v>
+      </c>
+      <c r="L390" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>Disturbing the peace on Jul 25, 2026, 100 m from International Market Place (2300 BLOCK KALAKAUA AVE). Case #260725-0383 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>260725-0324</t>
+        </is>
+      </c>
+      <c r="E391" s="3" t="n">
+        <v>46228.26383101852</v>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>2400 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J391" t="n">
+        <v>21.276010351182</v>
+      </c>
+      <c r="K391" t="n">
+        <v>-157.825469259274</v>
+      </c>
+      <c r="L391" t="n">
+        <v>254.5</v>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 25, 2026, 254 m from International Market Place (2400 BLOCK KALAKAUA AVE). Case #260725-0324 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M350"/>
+  <autoFilter ref="A1:M391"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -23486,7 +26005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -23513,7 +26032,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01 05:06:16.167337+00:00</t>
+          <t>2026-08-01 05:08:21.498984+00:00</t>
         </is>
       </c>
     </row>
@@ -23545,7 +26064,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-25 05:06:16.167337+00:00</t>
+          <t>2026-07-25 05:08:21.498984+00:00</t>
         </is>
       </c>
     </row>
@@ -23556,7 +26075,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>349</v>
+        <v>390</v>
       </c>
     </row>
     <row r="7">
@@ -23566,7 +26085,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -23869,8 +26388,32 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>source:INTLMARKET/Honolulu PD Crime Incidents</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>OK fetched=479 truncated=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>source:WAIKELE/Honolulu PD Crime Incidents</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>OK fetched=479 truncated=False</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B32"/>
+  <autoFilter ref="A1:B34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/latest/blotter_report.xlsx
+++ b/reports/latest/blotter_report.xlsx
@@ -13,10 +13,10 @@
     <sheet name="Run Metadata" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Highlights'!$A$1:$M$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$391</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$412</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1015,17 +1015,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GREENHILLS</t>
+          <t>FASHIONVAL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Mall at Green Hills</t>
+          <t>Fashion Valley</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2126 Abbott Martin Road, Nashville, TN 37215</t>
+          <t>7007 Friars Road San Diego CA 92108</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1051,23 +1051,23 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>GREENHILLS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>The Mall at Green Hills</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>5085 Westheimer Houston TX 77056</t>
+          <t>2126 Abbott Martin Road, Nashville, TN 37215</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1076,26 +1076,22 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>57</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>9</v>
-      </c>
-      <c r="J14" t="n">
-        <v>163.5</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>46233</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="b">
         <v>0</v>
       </c>
@@ -1103,17 +1099,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>INTLMARKET</t>
+          <t>HOUSTONGAL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>International Market Place</t>
+          <t>Houston Galleria</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2330 Kalakaua Avenue, Honolulu HI 96815</t>
+          <t>5085 Westheimer Houston TX 77056</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1122,25 +1118,25 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J15" t="n">
-        <v>99.7</v>
+        <v>163.5</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>46233.78047453704</v>
+        <v>46233</v>
       </c>
       <c r="L15" t="b">
         <v>0</v>
@@ -1149,17 +1145,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>INTLPLAZA</t>
+          <t>INTLMARKET</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>International Plaza</t>
+          <t>International Market Place</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2223 North West Shore Boulevard Tampa FL 33607</t>
+          <t>2330 Kalakaua Avenue, Honolulu HI 96815</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1168,25 +1164,25 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
+        <v>62</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>1534.5</v>
+        <v>99.7</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>46232.16666666666</v>
+        <v>46233.78047453704</v>
       </c>
       <c r="L16" t="b">
         <v>0</v>
@@ -1195,32 +1191,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LENOX</t>
+          <t>INTLPLAZA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lenox Square</t>
+          <t>International Plaza</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3393 Peachtree Road Northeast Atlanta GA 30326</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>NO COVERAGE</t>
+          <t>2223 North West Shore Boulevard Tampa FL 33607</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1228,8 +1224,12 @@
       <c r="I17" t="n">
         <v>0</v>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="J17" t="n">
+        <v>1534.5</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>46232.16666666666</v>
+      </c>
       <c r="L17" t="b">
         <v>0</v>
       </c>
@@ -1237,22 +1237,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MALLATMILLENIA</t>
+          <t>LENOX</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Mall at Millenia</t>
+          <t>Lenox Square</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4200 Conroy Road, Orlando, FL 32839</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>3393 Peachtree Road Northeast Atlanta GA 30326</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>NO COVERAGE</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1279,17 +1279,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NORFOLKPO</t>
+          <t>MALLATMILLENIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Norfolk Premium Outlets</t>
+          <t>The Mall at Millenia</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1600 Premium Outlets Boulevard Norfolk VA 23502</t>
+          <t>4200 Conroy Road, Orlando, FL 32839</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1298,7 +1298,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1310,14 +1310,10 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1118.9</v>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>46233</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="b">
         <v>0</v>
       </c>
@@ -1325,17 +1321,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>NORFOLKPO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Norfolk Premium Outlets</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>401 Northeast Northgate Way Seattle WA 98125</t>
+          <t>1600 Premium Outlets Boulevard Norfolk VA 23502</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1344,25 +1340,25 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>14</v>
-      </c>
-      <c r="F20" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
       <c r="G20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
-        <v>145.2</v>
+        <v>1118.9</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>46233.28194444445</v>
+        <v>46233</v>
       </c>
       <c r="L20" t="b">
         <v>0</v>
@@ -1371,17 +1367,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>433 Opry Mills Drive Nashville TN 37214</t>
+          <t>401 Northeast Northgate Way Seattle WA 98125</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1390,22 +1386,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>145.2</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>46233.28194444445</v>
+      </c>
       <c r="L21" t="b">
         <v>0</v>
       </c>
@@ -1413,17 +1413,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>OPRYMILLS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Opry Mills</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4400 Sharon Road Charlotte NC 28211</t>
+          <t>433 Opry Mills Drive Nashville TN 37214</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1432,26 +1432,22 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>7</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" t="n">
-        <v>178.9</v>
-      </c>
-      <c r="K22" s="3" t="n">
-        <v>46232.16666666666</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="b">
         <v>0</v>
       </c>
@@ -1459,17 +1455,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4502 South Steele Street Tacoma WA 98409</t>
+          <t>4400 Sharon Road Charlotte NC 28211</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1478,25 +1474,25 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>471.3</v>
+        <v>178.9</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>46233</v>
+        <v>46232.16666666666</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
@@ -1505,41 +1501,45 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>THEDOMAIN</t>
+          <t>TACOMAMALL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The Domain</t>
+          <t>Tacoma Mall</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>11410 Century Oaks Terrace Austin TX 78758</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>NO COVERAGE</t>
+          <t>4502 South Steele Street Tacoma WA 98409</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>471.3</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>46233</v>
+      </c>
       <c r="L24" t="b">
         <v>0</v>
       </c>
@@ -1547,45 +1547,41 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>THEDOMAIN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>The Domain</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>7700 East Kellogg Wichita KS 67207</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>11410 Century Oaks Terrace Austin TX 78758</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>NO COVERAGE</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>33</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>23</v>
-      </c>
-      <c r="J25" t="n">
-        <v>288.9</v>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v>46233.7625</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="b">
         <v>0</v>
       </c>
@@ -1593,17 +1589,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>UNIVPARKVILLAGE</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>University Park Village</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1612 South University Drive Fort Worth TX 76107</t>
+          <t>7700 East Kellogg Wichita KS 67207</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1612,22 +1608,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="J26" t="n">
+        <v>288.9</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>46233.7625</v>
+      </c>
       <c r="L26" t="b">
         <v>0</v>
       </c>
@@ -1635,17 +1635,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WAIKELE</t>
+          <t>UNIVPARKVILLAGE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Waikele Premium Outlets</t>
+          <t>University Park Village</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>94-790 Lumiaina Street Waipahu HI 96797</t>
+          <t>1612 South University Drive Fort Worth TX 76107</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1674,8 +1674,50 @@
         <v>0</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>WAIKELE</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Waikele Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>94-790 Lumiaina Street Waipahu HI 96797</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L27"/>
+  <autoFilter ref="A1:L28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1962,11 +2004,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>260726-0222</t>
+          <t>260728-1185</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>46229.15130787037</v>
+        <v>46231.67606481481</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1985,51 +2027,51 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2200 BLOCK KALAKAUA AVE</t>
+          <t>2200 BLOCK KUHIO AVE</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>21.280046658192</v>
+        <v>21.280829509204</v>
       </c>
       <c r="K5" t="n">
-        <v>-157.829687791355</v>
+        <v>-157.827642638381</v>
       </c>
       <c r="L5" t="n">
-        <v>384.6</v>
+        <v>330.6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Assault on Jul 26, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260726-0222 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 28, 2026, 331 m from International Market Place (2200 BLOCK KUHIO AVE). Case #260728-1185 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>INTLMARKET</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>International Market Place</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HOUSTONGAL:Houston PD NIBRS — Person</t>
+          <t>INTLMARKET:vg88-5rn5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>094513626</t>
+          <t>260726-0222</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>46229</v>
+        <v>46229.15130787037</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aggravated Assault</t>
+          <t>ASSAULT</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2039,26 +2081,26 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>13A</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5100-5199 HIDALGO ST</t>
+          <t>2200 BLOCK KALAKAUA AVE</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>29.73535149549964</v>
+        <v>21.280046658192</v>
       </c>
       <c r="K6" t="n">
-        <v>-95.46474014804627</v>
+        <v>-157.829687791355</v>
       </c>
       <c r="L6" t="n">
-        <v>447.9</v>
+        <v>384.6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 26, 2026, 448 m from Houston Galleria (5100-5199 HIDALGO ST). Case #094513626 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 26, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260726-0222 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2080,11 +2122,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>260729-0737</t>
+          <t>260727-0609</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>46232.46952546296</v>
+        <v>46230.42018518518</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2103,51 +2145,51 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2500 BLOCK KALAKAUA AVE</t>
+          <t>300 BLOCK LEWERS ST</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>21.273862837838</v>
+        <v>21.280145465259</v>
       </c>
       <c r="K7" t="n">
-        <v>-157.82387239543</v>
+        <v>-157.829777674689</v>
       </c>
       <c r="L7" t="n">
-        <v>544.6</v>
+        <v>398.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Assault on Jul 29, 2026, 545 m from International Market Place (2500 BLOCK KALAKAUA AVE). Case #260729-0737 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 27, 2026, 399 m from International Market Place (300 BLOCK LEWERS ST). Case #260727-0609 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>INTLMARKET</t>
+          <t>HOUSTONGAL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>International Market Place</t>
+          <t>Houston Galleria</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>INTLMARKET:vg88-5rn5</t>
+          <t>HOUSTONGAL:Houston PD NIBRS — Person</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>260725-1627</t>
+          <t>094513626</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>46228.93998842593</v>
+        <v>46229</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ASSAULT</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2157,56 +2199,56 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>13A</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>200 BLOCK BEACH WALK</t>
+          <t>5100-5199 HIDALGO ST</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>21.278930465176</v>
+        <v>29.73535149549964</v>
       </c>
       <c r="K8" t="n">
-        <v>-157.832248174365</v>
+        <v>-95.46474014804627</v>
       </c>
       <c r="L8" t="n">
-        <v>583.7</v>
+        <v>447.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Assault on Jul 25, 2026, 584 m from International Market Place (200 BLOCK BEACH WALK). Case #260725-1627 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 26, 2026, 448 m from Houston Galleria (5100-5199 HIDALGO ST). Case #094513626 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>INTLMARKET</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>International Market Place</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HOUSTONGAL:Houston PD NIBRS — Property</t>
+          <t>INTLMARKET:vg88-5rn5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>095242126</t>
+          <t>260729-0737</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>46230</v>
+        <v>46232.46952546296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Robbery</t>
+          <t>ASSAULT</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2216,56 +2258,56 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2700-2799 LOOP N</t>
+          <t>2500 BLOCK KALAKAUA AVE</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>29.7388306267185</v>
+        <v>21.273862837838</v>
       </c>
       <c r="K9" t="n">
-        <v>-95.45805588032616</v>
+        <v>-157.82387239543</v>
       </c>
       <c r="L9" t="n">
-        <v>588.1</v>
+        <v>544.6</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Robbery on Jul 27, 2026, 588 m from Houston Galleria (2700-2799 LOOP N). Case #095242126 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 29, 2026, 545 m from International Market Place (2500 BLOCK KALAKAUA AVE). Case #260729-0737 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>INTLMARKET</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Empire Mall</t>
+          <t>International Market Place</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+          <t>INTLMARKET:vg88-5rn5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CFS26-161839</t>
+          <t>260725-1627</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>46231.00275462963</v>
+        <v>46228.93998842593</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Assault P3</t>
+          <t>ASSAULT</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2275,56 +2317,56 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>W 47TH ST &amp; S WESTPORT AVE</t>
+          <t>200 BLOCK BEACH WALK</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>43.50940131405472</v>
+        <v>21.278930465176</v>
       </c>
       <c r="K10" t="n">
-        <v>-96.76746570282992</v>
+        <v>-157.832248174365</v>
       </c>
       <c r="L10" t="n">
-        <v>678.4</v>
+        <v>583.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Assault p3 on Jul 28, 2026, 678 m from Empire Mall (W 47TH ST &amp; S WESTPORT AVE). Case #CFS26-161839 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 25, 2026, 584 m from International Market Place (200 BLOCK BEACH WALK). Case #260725-1627 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>HOUSTONGAL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Houston Galleria</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>HOUSTONGAL:Houston PD NIBRS — Property</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DP2026411044131300</t>
+          <t>095242126</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>46229.1125</v>
+        <v>46230</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>assault-simple</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2334,56 +2376,56 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>other-crimes-against-persons</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3200 BLOCK E CHERRY CREEK S DR</t>
+          <t>2700-2799 LOOP N</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>39.71130989687384</v>
+        <v>29.7388306267185</v>
       </c>
       <c r="K11" t="n">
-        <v>-104.9490029653731</v>
+        <v>-95.45805588032616</v>
       </c>
       <c r="L11" t="n">
-        <v>696.3</v>
+        <v>588.1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Assault-simple on Jul 26, 2026, 696 m from Cherry Creek Shopping Center (3200 BLOCK E CHERRY CREEK S DR). Victims: 1. Case #DP2026411044 (use for a records request — full narratives are not published in open data).</t>
+          <t>Robbery on Jul 27, 2026, 588 m from Houston Galleria (2700-2799 LOOP N). Case #095242126 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COPLEY</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Copley Place</t>
+          <t>Empire Mall</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>262064756</t>
+          <t>CFS26-161839</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>46230.80347222222</v>
+        <v>46231.00275462963</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASSAULT - SIMPLE</t>
+          <t>Assault P3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2391,54 +2433,58 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Assault</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MASSACHUSETTS AVE</t>
+          <t>W 47TH ST &amp; S WESTPORT AVE</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>42.34439568415441</v>
+        <v>43.50940131405472</v>
       </c>
       <c r="K12" t="n">
-        <v>-71.08632016344815</v>
+        <v>-96.76746570282992</v>
       </c>
       <c r="L12" t="n">
-        <v>798.7</v>
+        <v>678.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Assault - simple on Jul 27, 2026, 799 m from Copley Place (MASSACHUSETTS AVE). Case #262064756 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault p3 on Jul 28, 2026, 678 m from Empire Mall (W 47TH ST &amp; S WESTPORT AVE). Case #CFS26-161839 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Empire Mall</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CFS26-161603</t>
+          <t>DP2026411044131300</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>46230.83325231481</v>
+        <v>46229.1125</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>assault-simple</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2448,56 +2494,56 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>other-crimes-against-persons</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>S WESTPORT AVE &amp; W 41ST ST</t>
+          <t>3200 BLOCK E CHERRY CREEK S DR</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>43.51485103457241</v>
+        <v>39.71130989687384</v>
       </c>
       <c r="K13" t="n">
-        <v>-96.76794119445807</v>
+        <v>-104.9490029653731</v>
       </c>
       <c r="L13" t="n">
-        <v>808.9</v>
+        <v>696.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Assault on Jul 27, 2026, 809 m from Empire Mall (S WESTPORT AVE &amp; W 41ST ST). Case #CFS26-161603 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault-simple on Jul 26, 2026, 696 m from Cherry Creek Shopping Center (3200 BLOCK E CHERRY CREEK S DR). Victims: 1. Case #DP2026411044 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>INTLMARKET</t>
+          <t>COPLEY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>International Market Place</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>INTLMARKET:vg88-5rn5</t>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>260729-0943</t>
+          <t>262064756</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>46232.56469907407</v>
+        <v>46230.80347222222</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ASSAULT</t>
+          <t>ASSAULT - SIMPLE</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2505,58 +2551,54 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2600 BLOCK KALAKAUA AVE</t>
+          <t>MASSACHUSETTS AVE</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>21.271474893966</v>
+        <v>42.34439568415441</v>
       </c>
       <c r="K14" t="n">
-        <v>-157.82264961775</v>
+        <v>-71.08632016344815</v>
       </c>
       <c r="L14" t="n">
-        <v>837.3</v>
+        <v>798.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Assault on Jul 29, 2026, 837 m from International Market Place (2600 BLOCK KALAKAUA AVE). Case #260729-0943 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault - simple on Jul 27, 2026, 799 m from Copley Place (MASSACHUSETTS AVE). Case #262064756 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Empire Mall</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>20260729-1600-11</t>
+          <t>CFS26-161603</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>46232.16666666666</v>
+        <v>46230.83325231481</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Simple Assault</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2566,56 +2608,56 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>13B</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4700 PIEDMONT ROW DR</t>
+          <t>S WESTPORT AVE &amp; W 41ST ST</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>35.15196312662653</v>
+        <v>43.51485103457241</v>
       </c>
       <c r="K15" t="n">
-        <v>-80.83980651357408</v>
+        <v>-96.76794119445807</v>
       </c>
       <c r="L15" t="n">
-        <v>850.6</v>
+        <v>808.9</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Simple assault on Jul 29, 2026, 851 m from Southpark (4700 PIEDMONT ROW DR). Status: Open. Case #20260729-1600-11 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 27, 2026, 809 m from Empire Mall (S WESTPORT AVE &amp; W 41ST ST). Case #CFS26-161603 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>INTLMARKET</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>International Market Place</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>INTLMARKET:vg88-5rn5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2620701835</t>
+          <t>260729-0943</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>46229</v>
+        <v>46232.56469907407</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Assault Simple</t>
+          <t>ASSAULT</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2625,56 +2667,56 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4000 S LAWRENCE ST</t>
+          <t>2600 BLOCK KALAKAUA AVE</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>47.219421</v>
+        <v>21.271474893966</v>
       </c>
       <c r="K16" t="n">
-        <v>-122.478428</v>
+        <v>-157.82264961775</v>
       </c>
       <c r="L16" t="n">
-        <v>853.4</v>
+        <v>837.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Assault simple on Jul 26, 2026, 853 m from Tacoma Mall (4000 S LAWRENCE ST). Case #2620701835 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 29, 2026, 837 m from International Market Place (2600 BLOCK KALAKAUA AVE). Case #260729-0943 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>COPLEY</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Copley Place</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>262064416</t>
+          <t>20260729-1600-11</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>46229.87569444445</v>
+        <v>46232.16666666666</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ASSAULT - AGGRAVATED</t>
+          <t>Simple Assault</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2682,54 +2724,58 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>13B</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>HUNTINGTON AVE</t>
+          <t>4700 PIEDMONT ROW DR</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>42.34221543503831</v>
+        <v>35.15196312662653</v>
       </c>
       <c r="K17" t="n">
-        <v>-71.08577074656198</v>
+        <v>-80.83980651357408</v>
       </c>
       <c r="L17" t="n">
-        <v>898.8</v>
+        <v>850.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Assault - aggravated on Jul 26, 2026, 899 m from Copley Place (HUNTINGTON AVE). Case #262064416 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 29, 2026, 851 m from Southpark (4700 PIEDMONT ROW DR). Status: Open. Case #20260729-1600-11 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>TACOMAMALL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Tacoma Mall</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>71878728447</t>
+          <t>2620701835</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>46230.4375</v>
+        <v>46229</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Robbery</t>
+          <t>Assault Simple</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2739,56 +2785,56 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>VIOLENT CRIME</t>
+          <t>Assault Offenses</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>16XX BLOCK OF N 105TH ST</t>
+          <t>4000 S LAWRENCE ST</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>47.70504225</v>
+        <v>47.219421</v>
       </c>
       <c r="K18" t="n">
-        <v>-122.338094779232</v>
+        <v>-122.478428</v>
       </c>
       <c r="L18" t="n">
-        <v>938.8</v>
+        <v>853.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Robbery on Jul 27, 2026, 939 m from Northgate Station (16XX BLOCK OF N 105TH ST). Case #2026-220064 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault simple on Jul 26, 2026, 853 m from Tacoma Mall (4000 S LAWRENCE ST). Case #2620701835 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>COPLEY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2621000152</t>
+          <t>262064416</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>46232</v>
+        <v>46229.87569444445</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Assault Simple</t>
+          <t>ASSAULT - AGGRAVATED</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2796,58 +2842,54 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3500 S 45TH ST</t>
+          <t>HUNTINGTON AVE</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>47.216421</v>
+        <v>42.34221543503831</v>
       </c>
       <c r="K19" t="n">
-        <v>-122.482428</v>
+        <v>-71.08577074656198</v>
       </c>
       <c r="L19" t="n">
-        <v>1074.3</v>
+        <v>898.8</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Assault simple on Jul 29, 2026, 1074 m from Tacoma Mall (3500 S 45TH ST). Case #2621000152 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault - aggravated on Jul 26, 2026, 899 m from Copley Place (HUNTINGTON AVE). Case #262064416 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>COPLEY</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Copley Place</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>262064432</t>
+          <t>71878728447</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>46229.91666666666</v>
+        <v>46230.4375</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ROBBERY</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2855,54 +2897,58 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>VIOLENT CRIME</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>16XX BLOCK OF N 105TH ST</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>42.33954198983015</v>
+        <v>47.70504225</v>
       </c>
       <c r="K20" t="n">
-        <v>-71.06940876967543</v>
+        <v>-122.338094779232</v>
       </c>
       <c r="L20" t="n">
-        <v>1123.7</v>
+        <v>938.8</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Robbery on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064432 (use for a records request — full narratives are not published in open data).</t>
+          <t>Robbery on Jul 27, 2026, 939 m from Northgate Station (16XX BLOCK OF N 105TH ST). Case #2026-220064 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>COPLEY</t>
+          <t>TACOMAMALL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Copley Place</t>
+          <t>Tacoma Mall</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>262064298</t>
+          <t>2621000152</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>46229.08611111111</v>
+        <v>46232</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FIREARM/WEAPON - LOST</t>
+          <t>Assault Simple</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2910,54 +2956,58 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Assault Offenses</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>3500 S 45TH ST</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>42.33954198983015</v>
+        <v>47.216421</v>
       </c>
       <c r="K21" t="n">
-        <v>-71.06940876967543</v>
+        <v>-122.482428</v>
       </c>
       <c r="L21" t="n">
-        <v>1123.7</v>
+        <v>1074.3</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Firearm/weapon - lost on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064298 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault simple on Jul 29, 2026, 1074 m from Tacoma Mall (3500 S 45TH ST). Case #2621000152 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>INTLMARKET</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>International Market Place</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>INTLMARKET:vg88-5rn5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>71894237115</t>
+          <t>260727-1127</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>46231.20833333334</v>
+        <v>46230.64813657408</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aggravated Assault</t>
+          <t>ASSAULT</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2967,56 +3017,56 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>VIOLENT CRIME</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>15XX BLOCK OF NE 107TH ST</t>
+          <t>1900 BLOCK KALAKAUA AVE</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>47.70668788</v>
+        <v>21.28609383604</v>
       </c>
       <c r="K22" t="n">
-        <v>-122.311189997702</v>
+        <v>-157.833074890083</v>
       </c>
       <c r="L22" t="n">
-        <v>1145.7</v>
+        <v>1117.1</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-221056 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 27, 2026, 1117 m from International Market Place (1900 BLOCK KALAKAUA AVE). Case #260727-1127 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>COPLEY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>71889871382</t>
+          <t>262064432</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>46231.00625</v>
+        <v>46229.91666666666</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Simple Assault</t>
+          <t>ROBBERY</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3024,58 +3074,54 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>ALL OTHER</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>15XX BLOCK OF NE 107TH ST</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>47.70668788</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K23" t="n">
-        <v>-122.311189997702</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L23" t="n">
-        <v>1145.7</v>
+        <v>1123.7</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Simple assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-220636 (use for a records request — full narratives are not published in open data).</t>
+          <t>Robbery on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064432 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>COPLEY</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>26C142249</t>
+          <t>262064298</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>46230.75</v>
+        <v>46229.08611111111</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BATTERY ABW</t>
+          <t>FIREARM/WEAPON - LOST</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3083,54 +3129,50 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>SIM_ASSAULT</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>700 BLOCK OF S MISSION RD</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>37.6756469679485</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K24" t="n">
-        <v>-97.25850032865422</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L24" t="n">
-        <v>1251.5</v>
+        <v>1123.7</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Battery abw on Jul 27, 2026, 1251 m from Towne East Square (700 BLOCK OF S MISSION RD). Case #26C142249 (use for a records request — full narratives are not published in open data).</t>
+          <t>Firearm/weapon - lost on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064298 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Empire Mall</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CFS26-164521</t>
+          <t>71894237115</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>46234.03421296296</v>
+        <v>46231.20833333334</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3144,56 +3186,56 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>VIOLENT CRIME</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>S MARION RD &amp; W 41ST ST</t>
+          <t>15XX BLOCK OF NE 107TH ST</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>43.51481738299845</v>
+        <v>47.70668788</v>
       </c>
       <c r="K25" t="n">
-        <v>-96.79096028032072</v>
+        <v>-122.311189997702</v>
       </c>
       <c r="L25" t="n">
-        <v>1322.4</v>
+        <v>1145.7</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 31, 2026, 1322 m from Empire Mall (S MARION RD &amp; W 41ST ST). Case #CFS26-164521 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-221056 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HOUSTONGAL:Houston PD NIBRS — Person</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>096140526</t>
+          <t>71889871382</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>46232</v>
+        <v>46231.00625</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aggravated Assault</t>
+          <t>Simple Assault</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3203,26 +3245,26 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>13A</t>
+          <t>ALL OTHER</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1900-1999 POST OAK PARK DR</t>
+          <t>15XX BLOCK OF NE 107TH ST</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>29.74712522681273</v>
+        <v>47.70668788</v>
       </c>
       <c r="K26" t="n">
-        <v>-95.45374747370188</v>
+        <v>-122.311189997702</v>
       </c>
       <c r="L26" t="n">
-        <v>1323.4</v>
+        <v>1145.7</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 29, 2026, 1323 m from Houston Galleria (1900-1999 POST OAK PARK DR). Case #096140526 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-220636 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M391"/>
+  <dimension ref="A1:M412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -25185,20 +25227,20 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>260728-1126</t>
+          <t>260728-1185</t>
         </is>
       </c>
       <c r="E378" s="3" t="n">
-        <v>46231.65560185185</v>
+        <v>46231.67606481481</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>THEFT/LARCENY</t>
+          <t>ASSAULT</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -25208,21 +25250,21 @@
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>2300 BLOCK KALAKAUA AVE</t>
+          <t>2200 BLOCK KUHIO AVE</t>
         </is>
       </c>
       <c r="J378" t="n">
-        <v>21.27805648814</v>
+        <v>21.280829509204</v>
       </c>
       <c r="K378" t="n">
-        <v>-157.827664940544</v>
+        <v>-157.827642638381</v>
       </c>
       <c r="L378" t="n">
-        <v>99.7</v>
+        <v>330.6</v>
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Theft/larceny on Jul 28, 2026, 100 m from International Market Place (2300 BLOCK KALAKAUA AVE). Case #260728-1126 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 28, 2026, 331 m from International Market Place (2200 BLOCK KUHIO AVE). Case #260728-1185 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -25244,11 +25286,11 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>260727-1381</t>
+          <t>260728-1126</t>
         </is>
       </c>
       <c r="E379" s="3" t="n">
-        <v>46230.75506944444</v>
+        <v>46231.65560185185</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -25267,21 +25309,21 @@
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>2200 BLOCK KALAKAUA AVE</t>
+          <t>2300 BLOCK KALAKAUA AVE</t>
         </is>
       </c>
       <c r="J379" t="n">
-        <v>21.280046658192</v>
+        <v>21.27805648814</v>
       </c>
       <c r="K379" t="n">
-        <v>-157.829687791355</v>
+        <v>-157.827664940544</v>
       </c>
       <c r="L379" t="n">
-        <v>384.6</v>
+        <v>99.7</v>
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Theft/larceny on Jul 27, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260727-1381 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft/larceny on Jul 28, 2026, 100 m from International Market Place (2300 BLOCK KALAKAUA AVE). Case #260728-1126 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -25303,15 +25345,15 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>260727-1302</t>
+          <t>260728-0991</t>
         </is>
       </c>
       <c r="E380" s="3" t="n">
-        <v>46230.71513888889</v>
+        <v>46231.59506944445</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>THEFT/LARCENY</t>
+          <t>BURGLARY</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
@@ -25326,21 +25368,21 @@
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>300 BLOCK KALAIMOKU ST</t>
+          <t>2400 BLOCK DATE ST</t>
         </is>
       </c>
       <c r="J380" t="n">
-        <v>21.282350597517</v>
+        <v>21.289130371817</v>
       </c>
       <c r="K380" t="n">
-        <v>-157.830982023446</v>
+        <v>-157.825374685262</v>
       </c>
       <c r="L380" t="n">
-        <v>657</v>
+        <v>1246.7</v>
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Theft/larceny on Jul 27, 2026, 657 m from International Market Place (300 BLOCK KALAIMOKU ST). Case #260727-1302 (use for a records request — full narratives are not published in open data).</t>
+          <t>Burglary on Jul 28, 2026, 1247 m from International Market Place (2400 BLOCK DATE ST). Case #260728-0991 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -25362,15 +25404,15 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>260727-0958</t>
+          <t>260728-0332</t>
         </is>
       </c>
       <c r="E381" s="3" t="n">
-        <v>46230.57681712963</v>
+        <v>46231.30905092593</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>THEFT/LARCENY</t>
+          <t>MOTOR VEHICLE THEFT</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
@@ -25385,21 +25427,21 @@
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>2200 BLOCK KALAKAUA AVE</t>
+          <t>2500 BLOCK DATE ST</t>
         </is>
       </c>
       <c r="J381" t="n">
-        <v>21.280046658192</v>
+        <v>21.28755766535</v>
       </c>
       <c r="K381" t="n">
-        <v>-157.829687791355</v>
+        <v>-157.82360180606</v>
       </c>
       <c r="L381" t="n">
-        <v>384.6</v>
+        <v>1111.7</v>
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Theft/larceny on Jul 27, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260727-0958 (use for a records request — full narratives are not published in open data).</t>
+          <t>Motor vehicle theft on Jul 28, 2026, 1112 m from International Market Place (2500 BLOCK DATE ST). Case #260728-0332 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -25421,15 +25463,15 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>260727-0160</t>
+          <t>260728-0204</t>
         </is>
       </c>
       <c r="E382" s="3" t="n">
-        <v>46230.1952662037</v>
+        <v>46231.24877314815</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>VANDALISM</t>
+          <t>MOTOR VEHICLE THEFT</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
@@ -25444,21 +25486,21 @@
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>2400 BLOCK KALAKAUA AVE</t>
+          <t>400 BLOCK NAHUA ST</t>
         </is>
       </c>
       <c r="J382" t="n">
-        <v>21.276010351182</v>
+        <v>21.279119553163</v>
       </c>
       <c r="K382" t="n">
-        <v>-157.825469259274</v>
+        <v>-157.825676162889</v>
       </c>
       <c r="L382" t="n">
-        <v>254.5</v>
+        <v>165</v>
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Vandalism on Jul 27, 2026, 254 m from International Market Place (2400 BLOCK KALAKAUA AVE). Case #260727-0160 (use for a records request — full narratives are not published in open data).</t>
+          <t>Motor vehicle theft on Jul 28, 2026, 165 m from International Market Place (400 BLOCK NAHUA ST). Case #260728-0204 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -25480,11 +25522,11 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>260726-0935</t>
+          <t>260728-0136</t>
         </is>
       </c>
       <c r="E383" s="3" t="n">
-        <v>46229.61716435185</v>
+        <v>46231.18006944445</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -25503,21 +25545,21 @@
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>2400 BLOCK KALAKAUA AVE</t>
+          <t>3200 BLOCK HOOLULU ST</t>
         </is>
       </c>
       <c r="J383" t="n">
-        <v>21.276010351182</v>
+        <v>21.278479806365</v>
       </c>
       <c r="K383" t="n">
-        <v>-157.825469259274</v>
+        <v>-157.813873146982</v>
       </c>
       <c r="L383" t="n">
-        <v>254.5</v>
+        <v>1330.8</v>
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Theft/larceny on Jul 26, 2026, 254 m from International Market Place (2400 BLOCK KALAKAUA AVE). Case #260726-0935 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft/larceny on Jul 28, 2026, 1331 m from International Market Place (3200 BLOCK HOOLULU ST). Case #260728-0136 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -25539,11 +25581,11 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>260726-0313</t>
+          <t>260728-0078</t>
         </is>
       </c>
       <c r="E384" s="3" t="n">
-        <v>46229.25769675926</v>
+        <v>46231.08966435185</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -25562,21 +25604,21 @@
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>2500 BLOCK KALAKAUA AVE</t>
+          <t>1900 BLOCK KALAKAUA AVE</t>
         </is>
       </c>
       <c r="J384" t="n">
-        <v>21.273862837838</v>
+        <v>21.28609383604</v>
       </c>
       <c r="K384" t="n">
-        <v>-157.82387239543</v>
+        <v>-157.833074890083</v>
       </c>
       <c r="L384" t="n">
-        <v>544.6</v>
+        <v>1117.1</v>
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Theft/larceny on Jul 26, 2026, 545 m from International Market Place (2500 BLOCK KALAKAUA AVE). Case #260726-0313 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft/larceny on Jul 28, 2026, 1117 m from International Market Place (1900 BLOCK KALAKAUA AVE). Case #260728-0078 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -25598,20 +25640,20 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>260726-0222</t>
+          <t>260727-1787</t>
         </is>
       </c>
       <c r="E385" s="3" t="n">
-        <v>46229.15130787037</v>
+        <v>46230.9887037037</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>ASSAULT</t>
+          <t>THEFT/LARCENY</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -25621,21 +25663,21 @@
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>2200 BLOCK KALAKAUA AVE</t>
+          <t>200 BLOCK LEWERS ST</t>
         </is>
       </c>
       <c r="J385" t="n">
-        <v>21.280046658192</v>
+        <v>21.278993587418</v>
       </c>
       <c r="K385" t="n">
-        <v>-157.829687791355</v>
+        <v>-157.83122782776</v>
       </c>
       <c r="L385" t="n">
-        <v>384.6</v>
+        <v>481.7</v>
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Assault on Jul 26, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260726-0222 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft/larceny on Jul 27, 2026, 482 m from International Market Place (200 BLOCK LEWERS ST). Case #260727-1787 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -25657,20 +25699,20 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>260725-1627</t>
+          <t>260727-1586</t>
         </is>
       </c>
       <c r="E386" s="3" t="n">
-        <v>46228.93998842593</v>
+        <v>46230.86315972222</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>ASSAULT</t>
+          <t>VANDALISM</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -25680,21 +25722,21 @@
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>200 BLOCK BEACH WALK</t>
+          <t>400 BLOCK NAMAHANA ST</t>
         </is>
       </c>
       <c r="J386" t="n">
-        <v>21.278930465176</v>
+        <v>21.283997526549</v>
       </c>
       <c r="K386" t="n">
-        <v>-157.832248174365</v>
+        <v>-157.831319892615</v>
       </c>
       <c r="L386" t="n">
-        <v>583.7</v>
+        <v>821.7</v>
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Assault on Jul 25, 2026, 584 m from International Market Place (200 BLOCK BEACH WALK). Case #260725-1627 (use for a records request — full narratives are not published in open data).</t>
+          <t>Vandalism on Jul 27, 2026, 822 m from International Market Place (400 BLOCK NAMAHANA ST). Case #260727-1586 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -25716,11 +25758,11 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>260725-1228</t>
+          <t>260727-1381</t>
         </is>
       </c>
       <c r="E387" s="3" t="n">
-        <v>46228.75162037037</v>
+        <v>46230.75506944444</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -25753,7 +25795,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Theft/larceny on Jul 25, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260725-1228 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft/larceny on Jul 27, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260727-1381 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -25775,20 +25817,20 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>260725-1158</t>
+          <t>260727-1340</t>
         </is>
       </c>
       <c r="E388" s="3" t="n">
-        <v>46228.70266203704</v>
+        <v>46230.73439814815</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>ASSAULT</t>
+          <t>THEFT/LARCENY</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -25798,21 +25840,21 @@
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>2300 BLOCK KALAKAUA AVE</t>
+          <t>100 BLOCK PAOA PL</t>
         </is>
       </c>
       <c r="J388" t="n">
-        <v>21.27805648814</v>
+        <v>21.28152934735</v>
       </c>
       <c r="K388" t="n">
-        <v>-157.827664940544</v>
+        <v>-157.836992718528</v>
       </c>
       <c r="L388" t="n">
-        <v>99.7</v>
+        <v>1136.3</v>
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Assault on Jul 25, 2026, 100 m from International Market Place (2300 BLOCK KALAKAUA AVE). Case #260725-1158 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft/larceny on Jul 27, 2026, 1136 m from International Market Place (100 BLOCK PAOA PL). Case #260727-1340 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -25834,15 +25876,15 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>260725-0503</t>
+          <t>260727-1304</t>
         </is>
       </c>
       <c r="E389" s="3" t="n">
-        <v>46228.35734953704</v>
+        <v>46230.71633101852</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>MOTOR VEHICLE THEFT</t>
+          <t>VANDALISM</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
@@ -25857,21 +25899,21 @@
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>2400 BLOCK KALAKAUA AVE</t>
+          <t>600 BLOCK HAUSTEN ST</t>
         </is>
       </c>
       <c r="J389" t="n">
-        <v>21.276010351182</v>
+        <v>21.287732337343</v>
       </c>
       <c r="K389" t="n">
-        <v>-157.825469259274</v>
+        <v>-157.82689064649</v>
       </c>
       <c r="L389" t="n">
-        <v>254.5</v>
+        <v>1083.7</v>
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Motor vehicle theft on Jul 25, 2026, 254 m from International Market Place (2400 BLOCK KALAKAUA AVE). Case #260725-0503 (use for a records request — full narratives are not published in open data).</t>
+          <t>Vandalism on Jul 27, 2026, 1084 m from International Market Place (600 BLOCK HAUSTEN ST). Case #260727-1304 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -25893,20 +25935,20 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>260725-0383</t>
+          <t>260727-1302</t>
         </is>
       </c>
       <c r="E390" s="3" t="n">
-        <v>46228.28726851852</v>
+        <v>46230.71513888889</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>DISTURBING THE PEACE</t>
+          <t>THEFT/LARCENY</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -25916,21 +25958,21 @@
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>2300 BLOCK KALAKAUA AVE</t>
+          <t>300 BLOCK KALAIMOKU ST</t>
         </is>
       </c>
       <c r="J390" t="n">
-        <v>21.27805648814</v>
+        <v>21.282350597517</v>
       </c>
       <c r="K390" t="n">
-        <v>-157.827664940544</v>
+        <v>-157.830982023446</v>
       </c>
       <c r="L390" t="n">
-        <v>99.7</v>
+        <v>657</v>
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Disturbing the peace on Jul 25, 2026, 100 m from International Market Place (2300 BLOCK KALAKAUA AVE). Case #260725-0383 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft/larceny on Jul 27, 2026, 657 m from International Market Place (300 BLOCK KALAIMOKU ST). Case #260727-1302 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -25952,49 +25994,1288 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
+          <t>260727-1278</t>
+        </is>
+      </c>
+      <c r="E391" s="3" t="n">
+        <v>46230.70094907407</v>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>MOTOR VEHICLE THEFT</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>1800 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J391" t="n">
+        <v>21.288652807916</v>
+      </c>
+      <c r="K391" t="n">
+        <v>-157.834591426424</v>
+      </c>
+      <c r="L391" t="n">
+        <v>1440.1</v>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>Motor vehicle theft on Jul 27, 2026, 1440 m from International Market Place (1800 BLOCK KALAKAUA AVE). Case #260727-1278 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>260727-1127</t>
+        </is>
+      </c>
+      <c r="E392" s="3" t="n">
+        <v>46230.64813657408</v>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>ASSAULT</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>1900 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J392" t="n">
+        <v>21.28609383604</v>
+      </c>
+      <c r="K392" t="n">
+        <v>-157.833074890083</v>
+      </c>
+      <c r="L392" t="n">
+        <v>1117.1</v>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>Assault on Jul 27, 2026, 1117 m from International Market Place (1900 BLOCK KALAKAUA AVE). Case #260727-1127 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>260727-0958</t>
+        </is>
+      </c>
+      <c r="E393" s="3" t="n">
+        <v>46230.57681712963</v>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>2200 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J393" t="n">
+        <v>21.280046658192</v>
+      </c>
+      <c r="K393" t="n">
+        <v>-157.829687791355</v>
+      </c>
+      <c r="L393" t="n">
+        <v>384.6</v>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 27, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260727-0958 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>260727-0745</t>
+        </is>
+      </c>
+      <c r="E394" s="3" t="n">
+        <v>46230.48368055555</v>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>DRUGS/ALCOHOL VIOLATIONS</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>100 BLOCK KAIULANI AVE</t>
+        </is>
+      </c>
+      <c r="J394" t="n">
+        <v>21.277067198668</v>
+      </c>
+      <c r="K394" t="n">
+        <v>-157.82544391535</v>
+      </c>
+      <c r="L394" t="n">
+        <v>166.1</v>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>Drugs/alcohol violations on Jul 27, 2026, 166 m from International Market Place (100 BLOCK KAIULANI AVE). Case #260727-0745 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>260727-0609</t>
+        </is>
+      </c>
+      <c r="E395" s="3" t="n">
+        <v>46230.42018518518</v>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>ASSAULT</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>300 BLOCK LEWERS ST</t>
+        </is>
+      </c>
+      <c r="J395" t="n">
+        <v>21.280145465259</v>
+      </c>
+      <c r="K395" t="n">
+        <v>-157.829777674689</v>
+      </c>
+      <c r="L395" t="n">
+        <v>398.6</v>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>Assault on Jul 27, 2026, 399 m from International Market Place (300 BLOCK LEWERS ST). Case #260727-0609 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>260727-0604</t>
+        </is>
+      </c>
+      <c r="E396" s="3" t="n">
+        <v>46230.41591435186</v>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>800 BLOCK KAPAHULU AVE</t>
+        </is>
+      </c>
+      <c r="J396" t="n">
+        <v>21.281867877215</v>
+      </c>
+      <c r="K396" t="n">
+        <v>-157.814203084308</v>
+      </c>
+      <c r="L396" t="n">
+        <v>1365.4</v>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 27, 2026, 1365 m from International Market Place (800 BLOCK KAPAHULU AVE). Case #260727-0604 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>260727-0261</t>
+        </is>
+      </c>
+      <c r="E397" s="3" t="n">
+        <v>46230.27378472222</v>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>200 BLOCK LILIUOKALANI AVE</t>
+        </is>
+      </c>
+      <c r="J397" t="n">
+        <v>21.275580844298</v>
+      </c>
+      <c r="K397" t="n">
+        <v>-157.822410575513</v>
+      </c>
+      <c r="L397" t="n">
+        <v>519.3</v>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 27, 2026, 519 m from International Market Place (200 BLOCK LILIUOKALANI AVE). Case #260727-0261 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>260727-0160</t>
+        </is>
+      </c>
+      <c r="E398" s="3" t="n">
+        <v>46230.1952662037</v>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>VANDALISM</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>2400 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J398" t="n">
+        <v>21.276010351182</v>
+      </c>
+      <c r="K398" t="n">
+        <v>-157.825469259274</v>
+      </c>
+      <c r="L398" t="n">
+        <v>254.5</v>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>Vandalism on Jul 27, 2026, 254 m from International Market Place (2400 BLOCK KALAKAUA AVE). Case #260727-0160 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>260726-1509</t>
+        </is>
+      </c>
+      <c r="E399" s="3" t="n">
+        <v>46229.94366898148</v>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>VANDALISM</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>100 BLOCK KAPAHULU AVE</t>
+        </is>
+      </c>
+      <c r="J399" t="n">
+        <v>21.271580290957</v>
+      </c>
+      <c r="K399" t="n">
+        <v>-157.822696449285</v>
+      </c>
+      <c r="L399" t="n">
+        <v>824.7</v>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>Vandalism on Jul 26, 2026, 825 m from International Market Place (100 BLOCK KAPAHULU AVE). Case #260726-1509 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>260726-1307</t>
+        </is>
+      </c>
+      <c r="E400" s="3" t="n">
+        <v>46229.82886574074</v>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>600 BLOCK KAPAHULU AVE</t>
+        </is>
+      </c>
+      <c r="J400" t="n">
+        <v>21.277595864317</v>
+      </c>
+      <c r="K400" t="n">
+        <v>-157.814205924306</v>
+      </c>
+      <c r="L400" t="n">
+        <v>1295.9</v>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 26, 2026, 1296 m from International Market Place (600 BLOCK KAPAHULU AVE). Case #260726-1307 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>260726-0935</t>
+        </is>
+      </c>
+      <c r="E401" s="3" t="n">
+        <v>46229.61716435185</v>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>2400 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J401" t="n">
+        <v>21.276010351182</v>
+      </c>
+      <c r="K401" t="n">
+        <v>-157.825469259274</v>
+      </c>
+      <c r="L401" t="n">
+        <v>254.5</v>
+      </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 26, 2026, 254 m from International Market Place (2400 BLOCK KALAKAUA AVE). Case #260726-0935 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>260726-0313</t>
+        </is>
+      </c>
+      <c r="E402" s="3" t="n">
+        <v>46229.25769675926</v>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>2500 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J402" t="n">
+        <v>21.273862837838</v>
+      </c>
+      <c r="K402" t="n">
+        <v>-157.82387239543</v>
+      </c>
+      <c r="L402" t="n">
+        <v>544.6</v>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 26, 2026, 545 m from International Market Place (2500 BLOCK KALAKAUA AVE). Case #260726-0313 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>260726-0222</t>
+        </is>
+      </c>
+      <c r="E403" s="3" t="n">
+        <v>46229.15130787037</v>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>ASSAULT</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>2200 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J403" t="n">
+        <v>21.280046658192</v>
+      </c>
+      <c r="K403" t="n">
+        <v>-157.829687791355</v>
+      </c>
+      <c r="L403" t="n">
+        <v>384.6</v>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>Assault on Jul 26, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260726-0222 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>260725-1627</t>
+        </is>
+      </c>
+      <c r="E404" s="3" t="n">
+        <v>46228.93998842593</v>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>ASSAULT</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>200 BLOCK BEACH WALK</t>
+        </is>
+      </c>
+      <c r="J404" t="n">
+        <v>21.278930465176</v>
+      </c>
+      <c r="K404" t="n">
+        <v>-157.832248174365</v>
+      </c>
+      <c r="L404" t="n">
+        <v>583.7</v>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>Assault on Jul 25, 2026, 584 m from International Market Place (200 BLOCK BEACH WALK). Case #260725-1627 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <